--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="49过程输入输出工具" sheetId="1" r:id="rId1"/>
-    <sheet name="49子过程图表实例" sheetId="2" r:id="rId2"/>
+    <sheet name="49子过程图表实例（自己画的）" sheetId="2" r:id="rId2"/>
     <sheet name="必背默写知识点" sheetId="3" r:id="rId3"/>
     <sheet name="计算公式汇总" sheetId="4" r:id="rId4"/>
     <sheet name="案例分析技巧汇总" sheetId="5" r:id="rId5"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="369">
   <si>
     <t>项目整合管理</t>
   </si>
@@ -353,7 +353,7 @@
   </si>
   <si>
     <r>
-      <t>估算活动时间</t>
+      <t>估算活动持续时间</t>
     </r>
     <r>
       <rPr>
@@ -942,8 +942,548 @@
     </r>
   </si>
   <si>
-    <t>定义：
-  是为了</t>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是为了实现目标而确定、记录并管理干系人的需要和需求的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是制定项目和产品详细描述的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  创建工作分解结构WBS是把项目可交付成果和项目工作分解成较小、更易于管理的组件的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是正式验收已完成的项目可交付成果的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是监督项目和产品的范围状态，管理范围基准变更的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是为规划、编制、管理、执行和控制项目进度而制定政策、程序和文档的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是识别和记录为完成项目可交付成果而须采取的具体行动的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是识别和记录项目活动之间关系的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是根据资源估算的结果，估算完成单项活动所需工作时段数的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是分析活动顺序、持续时间、资源需求和进度制约因素，创建进度模型，从而落实项目执行和监控的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是监督项目状态，以更新项目进度和管理进度基准变更的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是确定如何估算、预算、管理、监督和控制项目成本的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是对完成项目工作所需资源成本进行近似估算的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是汇总所有单个活动或工作包的估算成本，建立一个经批准的成本基准的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是监督项目状态，以更新项目成本和管理成本基准变更的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是识别项目及其可交付成果的质量要求、标准，并书面描述项目将如何证明符合质量要求、标准的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是把组织的质量政策用于项目，并将质量管理计划转化为可执行的质量活动的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是为了评估绩效，确保项目输出完整、正确且满足客户期望，而监督和记录质量管理活动执行结果的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是定义如何估算、获取、管理和利用团队及其实物资源的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是估算执行项目所需的团队资源，以及材料、设备和用品的类型和数量的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是获取项目所需的团队成员、设施、设备、材料、用品和其他资源的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是提高工作能力，促进团队成员互动，改善团队整体氛围，以提高项目绩效的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是跟踪团队成员工作表现、提供反馈、解决问题并管理团队变更以优化项目绩效的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是确保按计划为项目分配实物资源，以及根据资源使用计划监督资源实际使用情况，并采取必要纠正措施的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是基于每个干系人或干系人群体的信息需求、可用的组织资产，以及具体项目的需求，为项目沟通活动制定恰当的方法和计划的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是确保项目信息及时且恰当的收集、生成、发布、存储、检索、管理、监督和最终处置的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是确保满足项目及其干系人的信息需求的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是定义如何实施项目风险管理活动的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是识别单个项目风险以及整体项目风险的来源，并记录风险特征的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是通过评估单个项目风险发生的概率和影响及其他特征，对风险进行优先级排序，从而为后续分析或行动提供基础的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是就已识别的单个项目风险和不确定性的其他来源对整体项目目标的影响进行定量分析的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是为了应对项目风险，而制定可选方案、选择应对策略并商定应对行动的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是执行商定的风险应对计划的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是在整个项目期间，监督风险应对计划的实施，并跟踪已识别风险、识别和分析新风险，以及评估风险管理有效性的过程</t>
+    </r>
   </si>
   <si>
     <t>定义：</t>
@@ -1079,6 +1619,562 @@
         <scheme val="minor"/>
       </rPr>
       <t>在整个项目期间对如何管理范围提供指南和方向</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是为定义产品范围和项目范围奠定基础</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是描述产品、服务或成果的边界和验收标准</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>为所要交付的内容提供架构</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  1、使验收过程具有客观性
+  2、通过确认每个可交付成果来提高最终产品、服务或成果获得验收的可能性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是在整个项目期间保持对范围基准的维护</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是为如何在整个项目期间管理项目进度提供指南和方向</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 将工作包分解为进度活动，作为对项目工作进行进度估算、规划、执行、监督和控制的基础</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  定义工作之间的逻辑顺序，以便在既定的所有项目制约因素下获得最高的效率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是确定完成每个活动所需花费的时间量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  为完成项目活动而制定具有计划日期的进度模型</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  在整个项目期间保持对进度基准的维护</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  在整个项目期间为如何管理项目成本提供指南和方向</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  确定项目所需的资金</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  确定可以依据其来进行监督和控制项目绩效的成本基准</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  在整个项目期间保持对成本基准的维护</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是为在整个项目期间如何管理和核实质量提供指南和方向</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  1、提高实现质量目标的可能性
+  2、识别无效过程和导致质量低劣的原因
+  3、使用控制质量过程的数据和结果向干系人展示项目的总体质量状态</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  1、核实项目可交付成果和工作已经达到主要干系人的质量要求，可供最终验收
+  2、确定项目输出是否达到预期目的，这些输出需要满足所有适用标准、要求、法规和规范</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>根据项目类型和复杂程度确定适用于项目资源的管理方法和管理程度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  明确完成项目所需的资源种类、数量和特性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  1、概述和指导资源的选择
+  2、将选择的资源分配给相应的活动</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>改进团队协作、增强人际关系技能、激励员工，减少摩擦以及提升整体项目绩效</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 影响团队行为、管理冲突以及解决问题</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  1、确保所分配的资源适时、适地可用于项目
+  2、资源在不再需要时被释放</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1、及时向干系人提供相关信息
+  2、引导干系人有效参与项目
+  3、编制书面沟通计划</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>促成项目团队与干系人之间的有效信息流动</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 按沟通管理计划和干系人参与计划的要求优化信息传递流程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>确保风险管理的水平、方法和可见度与项目风险程度相匹配，与对组织和其他干系人的重要程度相匹配</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 1、记录现有的单个项目风险，以及整体项目风险的来源
+  2、汇总相关信息，以便项目团队能够恰当地应对已识别的风险</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是重点关注高优先级的风险</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  1、量化整体项目风险最大可能性
+  2、提供额外的定量风险信息，以支持风险应对规划</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  1、制定应对整体项目风险和单个项目风险的适当方法
+  2、分配资源，并根据需要将相关活动添加进项目文件和项目管理计划中</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  1、确保按计划执行商定的风险应对措施
+  2、管理整体项目风险入口、最小化单个项目威胁，以及最大化单个项目机会</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  保证项目决策是在整体项目风险和单个项目风险当前信息的基础上运行</t>
     </r>
   </si>
   <si>
@@ -3035,7 +4131,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2794000" y="17538700"/>
+          <a:off x="2794000" y="17881600"/>
           <a:ext cx="11544300" cy="6191250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3320,7 +4416,9 @@
     <col min="14" max="15" width="24.875" customWidth="1"/>
     <col min="16" max="16" width="29.375" customWidth="1"/>
     <col min="17" max="17" width="24.875" customWidth="1"/>
-    <col min="18" max="20" width="29.375" customWidth="1"/>
+    <col min="18" max="18" width="29.375" customWidth="1"/>
+    <col min="19" max="19" width="32.5" customWidth="1"/>
+    <col min="20" max="20" width="29.375" customWidth="1"/>
     <col min="21" max="21" width="24.875" customWidth="1"/>
     <col min="22" max="22" width="29.375" customWidth="1"/>
     <col min="23" max="25" width="24.875" customWidth="1"/>
@@ -3638,7 +4736,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" s="8" customFormat="1" ht="67.5" spans="1:51">
+    <row r="4" s="8" customFormat="1" ht="81" spans="1:51">
       <c r="A4" s="21"/>
       <c r="B4" s="21"/>
       <c r="C4" s="24" t="s">
@@ -3668,741 +4766,741 @@
       <c r="K4" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="25" t="s">
+      <c r="L4" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="N4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="O4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="P4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="R4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="S4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="T4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="U4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="V4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="W4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="X4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AF4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AK4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AM4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AP4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AQ4" s="25" t="s">
-        <v>78</v>
-      </c>
-      <c r="AR4" s="25" t="s">
-        <v>78</v>
+      <c r="M4" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="N4" s="24" t="s">
+        <v>80</v>
+      </c>
+      <c r="O4" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="P4" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="R4" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="S4" s="24" t="s">
+        <v>85</v>
+      </c>
+      <c r="T4" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="U4" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="V4" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="W4" s="24" t="s">
+        <v>89</v>
+      </c>
+      <c r="X4" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="Y4" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="Z4" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="AA4" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="AB4" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="AC4" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="AD4" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="AE4" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="AF4" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="AG4" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="AH4" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="AI4" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="AJ4" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="AK4" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="AL4" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="AM4" s="24" t="s">
+        <v>105</v>
+      </c>
+      <c r="AN4" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="AO4" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="AP4" s="24" t="s">
+        <v>108</v>
+      </c>
+      <c r="AQ4" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="AR4" s="24" t="s">
+        <v>110</v>
       </c>
       <c r="AS4" s="25" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="AT4" s="25" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="AU4" s="25" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="AV4" s="25" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="AW4" s="25" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="AX4" s="25" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
       <c r="AY4" s="25" t="s">
-        <v>78</v>
+        <v>111</v>
       </c>
     </row>
-    <row r="5" s="8" customFormat="1" ht="81" spans="1:51">
+    <row r="5" s="8" customFormat="1" ht="108" spans="1:51">
       <c r="A5" s="21"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24" t="s">
-        <v>79</v>
+        <v>112</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>80</v>
+        <v>113</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>81</v>
+        <v>114</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>84</v>
+        <v>117</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>86</v>
-      </c>
-      <c r="K5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="L5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="M5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="N5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="O5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="P5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="R5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="S5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="T5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="U5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="V5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="W5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="X5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="Y5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="Z5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AB5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AC5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AD5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AE5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AF5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AG5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AH5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AI5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AJ5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AK5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AL5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AM5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AN5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AO5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AP5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AQ5" s="25" t="s">
-        <v>87</v>
-      </c>
-      <c r="AR5" s="25" t="s">
-        <v>87</v>
+        <v>119</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="L5" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="M5" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="N5" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="O5" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="P5" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q5" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="R5" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="S5" s="24" t="s">
+        <v>128</v>
+      </c>
+      <c r="T5" s="24" t="s">
+        <v>129</v>
+      </c>
+      <c r="U5" s="24" t="s">
+        <v>130</v>
+      </c>
+      <c r="V5" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="W5" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="X5" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y5" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z5" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="AA5" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="AB5" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="AC5" s="24" t="s">
+        <v>138</v>
+      </c>
+      <c r="AD5" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="AE5" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="AF5" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="AG5" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="AH5" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="AI5" s="24" t="s">
+        <v>144</v>
+      </c>
+      <c r="AJ5" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="AK5" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="AL5" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="AM5" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="AN5" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="AO5" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="AP5" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="AQ5" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="AR5" s="24" t="s">
+        <v>153</v>
       </c>
       <c r="AS5" s="25" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="AT5" s="25" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="AU5" s="25" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="AV5" s="25" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="AW5" s="25" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="AX5" s="25" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
       <c r="AY5" s="25" t="s">
-        <v>87</v>
+        <v>154</v>
       </c>
     </row>
-    <row r="6" s="8" customFormat="1" ht="40.5" spans="1:51">
+    <row r="6" s="8" customFormat="1" ht="27" spans="1:51">
       <c r="A6" s="21"/>
       <c r="B6" s="21"/>
       <c r="C6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="G6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="N6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="O6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="P6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="Q6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="R6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="S6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="T6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="U6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="V6" s="24" t="s">
-        <v>89</v>
+        <v>156</v>
       </c>
       <c r="W6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="X6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="Y6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="Z6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AA6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AB6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AC6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AD6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AE6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AF6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AG6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AH6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AI6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AJ6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AK6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AL6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AM6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AN6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AO6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AP6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AQ6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AR6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AS6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AT6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AU6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AV6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AW6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AX6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="AY6" s="25" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" s="8" customFormat="1" ht="67.5" spans="1:51">
       <c r="A7" s="26" t="s">
-        <v>90</v>
+        <v>157</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="L7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="P7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="Q7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="R7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="S7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="T7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="U7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="V7" s="24" t="s">
-        <v>93</v>
+        <v>160</v>
       </c>
       <c r="W7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="X7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="Y7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="Z7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AA7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AB7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AC7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AD7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AE7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AF7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AG7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AH7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AI7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AJ7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AK7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AL7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AM7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AN7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AO7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AP7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AQ7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AR7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AS7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AT7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AU7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AV7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AW7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AX7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
       <c r="AY7" s="25" t="s">
-        <v>92</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" ht="67.5" spans="1:51">
       <c r="A8" s="28"/>
       <c r="B8" s="29" t="s">
-        <v>94</v>
+        <v>161</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>95</v>
+        <v>162</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>96</v>
+        <v>163</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>98</v>
+        <v>165</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>99</v>
+        <v>166</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>101</v>
+        <v>168</v>
       </c>
       <c r="J8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="K8" s="30" t="s">
-        <v>103</v>
+        <v>170</v>
       </c>
       <c r="L8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="M8" s="30" t="s">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="N8" s="30" t="s">
-        <v>105</v>
+        <v>172</v>
       </c>
       <c r="O8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="P8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="R8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="S8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="T8" s="30" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="U8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="V8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="W8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="X8" s="30" t="s">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="Y8" s="30" t="s">
-        <v>108</v>
+        <v>175</v>
       </c>
       <c r="Z8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AA8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AB8" s="30" t="s">
-        <v>109</v>
+        <v>176</v>
       </c>
       <c r="AC8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AD8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AE8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AF8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AG8" s="30" t="s">
-        <v>110</v>
+        <v>177</v>
       </c>
       <c r="AH8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AI8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AJ8" s="30" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="AK8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AL8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AM8" s="30" t="s">
-        <v>112</v>
+        <v>179</v>
       </c>
       <c r="AN8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AO8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AP8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AQ8" s="30" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AR8" s="30" t="s">
-        <v>111</v>
+        <v>178</v>
       </c>
       <c r="AS8" s="31" t="s">
-        <v>113</v>
+        <v>180</v>
       </c>
       <c r="AT8" s="31" t="s">
-        <v>114</v>
+        <v>181</v>
       </c>
       <c r="AU8" s="31" t="s">
-        <v>115</v>
+        <v>182</v>
       </c>
       <c r="AV8" s="31" t="s">
-        <v>116</v>
+        <v>183</v>
       </c>
       <c r="AW8" s="31" t="s">
-        <v>106</v>
+        <v>173</v>
       </c>
       <c r="AX8" s="32" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AY8" s="32" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" ht="40.5" spans="1:51">
       <c r="A9" s="28"/>
       <c r="B9" s="33" t="s">
-        <v>117</v>
+        <v>184</v>
       </c>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
@@ -4413,12 +5511,12 @@
       <c r="I9" s="31"/>
       <c r="J9" s="31"/>
       <c r="K9" s="31" t="s">
-        <v>118</v>
+        <v>185</v>
       </c>
       <c r="L9" s="31"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31" t="s">
-        <v>119</v>
+        <v>186</v>
       </c>
       <c r="O9" s="31"/>
       <c r="P9" s="31"/>
@@ -4461,7 +5559,7 @@
     <row r="10" ht="81" spans="1:51">
       <c r="A10" s="34"/>
       <c r="B10" s="33" t="s">
-        <v>120</v>
+        <v>187</v>
       </c>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
@@ -4472,14 +5570,14 @@
       <c r="I10" s="31"/>
       <c r="J10" s="31"/>
       <c r="K10" s="31" t="s">
-        <v>121</v>
+        <v>188</v>
       </c>
       <c r="L10" s="31" t="s">
-        <v>122</v>
+        <v>189</v>
       </c>
       <c r="M10" s="31"/>
       <c r="N10" s="31" t="s">
-        <v>123</v>
+        <v>190</v>
       </c>
       <c r="O10" s="31"/>
       <c r="P10" s="31"/>
@@ -4494,7 +5592,7 @@
       <c r="Y10" s="31"/>
       <c r="Z10" s="31"/>
       <c r="AA10" s="31" t="s">
-        <v>124</v>
+        <v>191</v>
       </c>
       <c r="AB10" s="31"/>
       <c r="AC10" s="31"/>
@@ -4505,7 +5603,7 @@
       <c r="AH10" s="31"/>
       <c r="AI10" s="31"/>
       <c r="AJ10" s="31" t="s">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c r="AK10" s="31"/>
       <c r="AL10" s="31"/>
@@ -4525,10 +5623,10 @@
     </row>
     <row r="11" spans="1:51">
       <c r="A11" s="35" t="s">
-        <v>126</v>
+        <v>193</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>127</v>
+        <v>194</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -4582,10 +5680,10 @@
     </row>
     <row r="12" spans="1:51">
       <c r="A12" s="35" t="s">
-        <v>128</v>
+        <v>195</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>129</v>
+        <v>196</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -4639,131 +5737,131 @@
     </row>
     <row r="14" ht="121.5" spans="1:51">
       <c r="A14" s="38" t="s">
-        <v>130</v>
+        <v>197</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>131</v>
+        <v>198</v>
       </c>
       <c r="C14" s="40"/>
       <c r="D14" s="41"/>
       <c r="E14" s="41"/>
       <c r="F14" s="41" t="s">
-        <v>132</v>
+        <v>199</v>
       </c>
       <c r="G14" s="41"/>
       <c r="H14" s="41" t="s">
-        <v>133</v>
+        <v>200</v>
       </c>
       <c r="I14" s="41"/>
       <c r="J14" s="41"/>
       <c r="K14" s="41" t="s">
-        <v>134</v>
+        <v>201</v>
       </c>
       <c r="L14" s="41" t="s">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="M14" s="41" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="N14" s="41" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="O14" s="41"/>
       <c r="P14" s="41"/>
       <c r="Q14" s="41" t="s">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="R14" s="41" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="S14" s="41" t="s">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="T14" s="41" t="s">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="U14" s="41" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="V14" s="41"/>
       <c r="W14" s="41" t="s">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="X14" s="41" t="s">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="Y14" s="41" t="s">
-        <v>144</v>
+        <v>211</v>
       </c>
       <c r="Z14" s="41" t="s">
-        <v>145</v>
+        <v>212</v>
       </c>
       <c r="AA14" s="41" t="s">
-        <v>146</v>
+        <v>213</v>
       </c>
       <c r="AB14" s="41" t="s">
-        <v>147</v>
+        <v>214</v>
       </c>
       <c r="AC14" s="41" t="s">
-        <v>148</v>
+        <v>215</v>
       </c>
       <c r="AD14" s="41" t="s">
-        <v>149</v>
+        <v>216</v>
       </c>
       <c r="AE14" s="41" t="s">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="AF14" s="41" t="s">
-        <v>151</v>
+        <v>218</v>
       </c>
       <c r="AG14" s="41"/>
       <c r="AH14" s="41" t="s">
-        <v>152</v>
+        <v>219</v>
       </c>
       <c r="AI14" s="41" t="s">
-        <v>153</v>
+        <v>220</v>
       </c>
       <c r="AJ14" s="41" t="s">
-        <v>154</v>
+        <v>221</v>
       </c>
       <c r="AK14" s="41"/>
       <c r="AL14" s="41"/>
       <c r="AM14" s="41" t="s">
-        <v>155</v>
+        <v>222</v>
       </c>
       <c r="AN14" s="41" t="s">
-        <v>156</v>
+        <v>223</v>
       </c>
       <c r="AO14" s="41" t="s">
-        <v>157</v>
+        <v>224</v>
       </c>
       <c r="AP14" s="41" t="s">
-        <v>158</v>
+        <v>225</v>
       </c>
       <c r="AQ14" s="41"/>
       <c r="AR14" s="41" t="s">
-        <v>159</v>
+        <v>226</v>
       </c>
       <c r="AS14" s="42" t="s">
-        <v>160</v>
+        <v>227</v>
       </c>
       <c r="AT14" s="41" t="s">
-        <v>161</v>
+        <v>228</v>
       </c>
       <c r="AU14" s="41" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="AV14" s="32"/>
       <c r="AW14" s="32"/>
       <c r="AX14" s="31" t="s">
-        <v>163</v>
+        <v>230</v>
       </c>
       <c r="AY14" s="31"/>
     </row>
     <row r="15" spans="1:51">
       <c r="A15" s="43"/>
       <c r="B15" s="44" t="s">
-        <v>164</v>
+        <v>231</v>
       </c>
       <c r="C15" s="45"/>
       <c r="D15" s="37"/>
@@ -4818,13 +5916,13 @@
     <row r="16" ht="67.5" spans="1:51">
       <c r="A16" s="43"/>
       <c r="B16" s="44" t="s">
-        <v>165</v>
+        <v>232</v>
       </c>
       <c r="C16" s="46" t="s">
-        <v>166</v>
+        <v>233</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>167</v>
+        <v>234</v>
       </c>
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
@@ -4833,7 +5931,7 @@
       <c r="I16" s="37"/>
       <c r="J16" s="37"/>
       <c r="K16" s="47" t="s">
-        <v>168</v>
+        <v>235</v>
       </c>
       <c r="L16" s="37"/>
       <c r="M16" s="37"/>
@@ -4850,13 +5948,13 @@
       <c r="X16" s="37"/>
       <c r="Y16" s="37"/>
       <c r="Z16" s="47" t="s">
-        <v>169</v>
+        <v>236</v>
       </c>
       <c r="AA16" s="37" t="s">
-        <v>170</v>
+        <v>237</v>
       </c>
       <c r="AB16" s="47" t="s">
-        <v>171</v>
+        <v>238</v>
       </c>
       <c r="AC16" s="37"/>
       <c r="AD16" s="37"/>
@@ -4869,24 +5967,24 @@
       <c r="AK16" s="37"/>
       <c r="AL16" s="37"/>
       <c r="AM16" s="47" t="s">
-        <v>172</v>
+        <v>239</v>
       </c>
       <c r="AN16" s="37"/>
       <c r="AO16" s="37" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="AP16" s="37" t="s">
-        <v>173</v>
+        <v>240</v>
       </c>
       <c r="AQ16" s="37"/>
       <c r="AR16" s="37"/>
       <c r="AS16" s="37" t="s">
-        <v>174</v>
+        <v>241</v>
       </c>
       <c r="AT16" s="37"/>
       <c r="AU16" s="37"/>
       <c r="AV16" s="47" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
       <c r="AW16" s="37"/>
       <c r="AX16" s="37"/>
@@ -4895,61 +5993,61 @@
     <row r="17" ht="81" spans="1:51">
       <c r="A17" s="43"/>
       <c r="B17" s="44" t="s">
-        <v>176</v>
+        <v>243</v>
       </c>
       <c r="C17" s="45"/>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
       <c r="F17" s="37"/>
       <c r="G17" s="47" t="s">
-        <v>177</v>
+        <v>244</v>
       </c>
       <c r="H17" s="37"/>
       <c r="I17" s="47" t="s">
-        <v>178</v>
+        <v>245</v>
       </c>
       <c r="J17" s="37"/>
       <c r="K17" s="37" t="s">
-        <v>179</v>
+        <v>246</v>
       </c>
       <c r="L17" s="37" t="s">
-        <v>180</v>
+        <v>247</v>
       </c>
       <c r="M17" s="37"/>
       <c r="N17" s="37"/>
       <c r="O17" s="47" t="s">
-        <v>181</v>
+        <v>248</v>
       </c>
       <c r="P17" s="37"/>
       <c r="Q17" s="37"/>
       <c r="R17" s="37"/>
       <c r="S17" s="47" t="s">
-        <v>182</v>
+        <v>249</v>
       </c>
       <c r="T17" s="47" t="s">
-        <v>183</v>
+        <v>250</v>
       </c>
       <c r="U17" s="47" t="s">
-        <v>184</v>
+        <v>251</v>
       </c>
       <c r="V17" s="37"/>
       <c r="W17" s="47" t="s">
-        <v>185</v>
+        <v>252</v>
       </c>
       <c r="X17" s="37" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="Y17" s="47" t="s">
-        <v>187</v>
+        <v>254</v>
       </c>
       <c r="Z17" s="47" t="s">
-        <v>188</v>
+        <v>255</v>
       </c>
       <c r="AA17" s="47" t="s">
-        <v>189</v>
+        <v>256</v>
       </c>
       <c r="AB17" s="47" t="s">
-        <v>190</v>
+        <v>257</v>
       </c>
       <c r="AC17" s="37"/>
       <c r="AD17" s="37"/>
@@ -4957,54 +6055,54 @@
       <c r="AF17" s="37"/>
       <c r="AG17" s="37"/>
       <c r="AH17" s="47" t="s">
-        <v>191</v>
+        <v>258</v>
       </c>
       <c r="AI17" s="37"/>
       <c r="AJ17" s="37"/>
       <c r="AK17" s="37"/>
       <c r="AL17" s="37" t="s">
-        <v>192</v>
+        <v>259</v>
       </c>
       <c r="AM17" s="47" t="s">
-        <v>193</v>
+        <v>260</v>
       </c>
       <c r="AN17" s="47" t="s">
-        <v>194</v>
+        <v>261</v>
       </c>
       <c r="AO17" s="47" t="s">
-        <v>195</v>
+        <v>262</v>
       </c>
       <c r="AP17" s="47" t="s">
-        <v>196</v>
+        <v>263</v>
       </c>
       <c r="AQ17" s="37"/>
       <c r="AR17" s="47" t="s">
-        <v>197</v>
+        <v>264</v>
       </c>
       <c r="AS17" s="37" t="s">
-        <v>198</v>
+        <v>265</v>
       </c>
       <c r="AT17" s="37" t="s">
-        <v>199</v>
+        <v>266</v>
       </c>
       <c r="AU17" s="47" t="s">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c r="AV17" s="47" t="s">
-        <v>201</v>
+        <v>268</v>
       </c>
       <c r="AW17" s="47" t="s">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="AX17" s="37"/>
       <c r="AY17" s="47" t="s">
-        <v>203</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" ht="81" spans="1:51">
       <c r="A18" s="43"/>
       <c r="B18" s="44" t="s">
-        <v>204</v>
+        <v>271</v>
       </c>
       <c r="C18" s="45"/>
       <c r="D18" s="37"/>
@@ -5015,7 +6113,7 @@
       <c r="I18" s="37"/>
       <c r="J18" s="37"/>
       <c r="K18" s="47" t="s">
-        <v>205</v>
+        <v>272</v>
       </c>
       <c r="L18" s="37"/>
       <c r="M18" s="37"/>
@@ -5032,16 +6130,16 @@
       <c r="X18" s="37"/>
       <c r="Y18" s="37"/>
       <c r="Z18" s="47" t="s">
-        <v>206</v>
+        <v>273</v>
       </c>
       <c r="AA18" s="47" t="s">
-        <v>207</v>
+        <v>274</v>
       </c>
       <c r="AB18" s="47" t="s">
-        <v>208</v>
+        <v>275</v>
       </c>
       <c r="AC18" s="47" t="s">
-        <v>209</v>
+        <v>276</v>
       </c>
       <c r="AD18" s="37"/>
       <c r="AE18" s="37"/>
@@ -5049,16 +6147,16 @@
       <c r="AG18" s="37"/>
       <c r="AH18" s="37"/>
       <c r="AI18" s="37" t="s">
-        <v>210</v>
+        <v>277</v>
       </c>
       <c r="AJ18" s="37"/>
       <c r="AK18" s="37" t="s">
-        <v>210</v>
+        <v>277</v>
       </c>
       <c r="AL18" s="37"/>
       <c r="AM18" s="37"/>
       <c r="AN18" s="47" t="s">
-        <v>211</v>
+        <v>278</v>
       </c>
       <c r="AO18" s="37"/>
       <c r="AP18" s="37"/>
@@ -5068,20 +6166,20 @@
       <c r="AT18" s="37"/>
       <c r="AU18" s="37"/>
       <c r="AV18" s="47" t="s">
-        <v>212</v>
+        <v>279</v>
       </c>
       <c r="AW18" s="47" t="s">
-        <v>213</v>
+        <v>280</v>
       </c>
       <c r="AX18" s="37"/>
       <c r="AY18" s="47" t="s">
-        <v>210</v>
+        <v>277</v>
       </c>
     </row>
     <row r="19" ht="40.5" spans="1:51">
       <c r="A19" s="43"/>
       <c r="B19" s="44" t="s">
-        <v>214</v>
+        <v>281</v>
       </c>
       <c r="C19" s="45"/>
       <c r="D19" s="37"/>
@@ -5089,15 +6187,15 @@
       <c r="F19" s="37"/>
       <c r="G19" s="37"/>
       <c r="H19" s="47" t="s">
-        <v>215</v>
+        <v>282</v>
       </c>
       <c r="I19" s="37"/>
       <c r="J19" s="37"/>
       <c r="K19" s="47" t="s">
-        <v>215</v>
+        <v>282</v>
       </c>
       <c r="L19" s="37" t="s">
-        <v>216</v>
+        <v>283</v>
       </c>
       <c r="M19" s="37"/>
       <c r="N19" s="37"/>
@@ -5118,7 +6216,7 @@
       <c r="AC19" s="37"/>
       <c r="AD19" s="37"/>
       <c r="AE19" s="37" t="s">
-        <v>216</v>
+        <v>283</v>
       </c>
       <c r="AF19" s="37"/>
       <c r="AG19" s="37"/>
@@ -5131,7 +6229,7 @@
       <c r="AN19" s="37"/>
       <c r="AO19" s="37"/>
       <c r="AP19" s="37" t="s">
-        <v>216</v>
+        <v>283</v>
       </c>
       <c r="AQ19" s="37"/>
       <c r="AR19" s="37"/>
@@ -5142,13 +6240,13 @@
       <c r="AW19" s="47"/>
       <c r="AX19" s="37"/>
       <c r="AY19" s="47" t="s">
-        <v>217</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" ht="54" spans="1:51">
       <c r="A20" s="43"/>
       <c r="B20" s="44" t="s">
-        <v>218</v>
+        <v>285</v>
       </c>
       <c r="C20" s="45"/>
       <c r="D20" s="37"/>
@@ -5184,7 +6282,7 @@
       <c r="AH20" s="37"/>
       <c r="AI20" s="37"/>
       <c r="AJ20" s="47" t="s">
-        <v>219</v>
+        <v>286</v>
       </c>
       <c r="AK20" s="37"/>
       <c r="AL20" s="37"/>
@@ -5205,13 +6303,13 @@
     <row r="21" ht="81" spans="1:51">
       <c r="A21" s="43"/>
       <c r="B21" s="48" t="s">
-        <v>220</v>
+        <v>287</v>
       </c>
       <c r="C21" s="46" t="s">
-        <v>221</v>
+        <v>288</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>221</v>
+        <v>288</v>
       </c>
       <c r="E21" s="37"/>
       <c r="F21" s="37"/>
@@ -5220,10 +6318,10 @@
       <c r="I21" s="37"/>
       <c r="J21" s="37"/>
       <c r="K21" s="47" t="s">
-        <v>222</v>
+        <v>289</v>
       </c>
       <c r="L21" s="37" t="s">
-        <v>223</v>
+        <v>290</v>
       </c>
       <c r="M21" s="37"/>
       <c r="N21" s="37"/>
@@ -5244,51 +6342,51 @@
       <c r="AC21" s="37"/>
       <c r="AD21" s="37"/>
       <c r="AE21" s="37" t="s">
-        <v>224</v>
+        <v>291</v>
       </c>
       <c r="AF21" s="47" t="s">
-        <v>225</v>
+        <v>292</v>
       </c>
       <c r="AG21" s="47" t="s">
-        <v>226</v>
+        <v>293</v>
       </c>
       <c r="AH21" s="37"/>
       <c r="AI21" s="47" t="s">
-        <v>227</v>
+        <v>294</v>
       </c>
       <c r="AJ21" s="47" t="s">
-        <v>228</v>
+        <v>295</v>
       </c>
       <c r="AK21" s="37"/>
       <c r="AL21" s="37"/>
       <c r="AM21" s="37"/>
       <c r="AN21" s="37"/>
       <c r="AO21" s="37" t="s">
-        <v>223</v>
+        <v>290</v>
       </c>
       <c r="AP21" s="37" t="s">
-        <v>223</v>
+        <v>290</v>
       </c>
       <c r="AQ21" s="37"/>
       <c r="AR21" s="37"/>
       <c r="AS21" s="37"/>
       <c r="AT21" s="37" t="s">
-        <v>224</v>
+        <v>291</v>
       </c>
       <c r="AU21" s="37"/>
       <c r="AV21" s="37"/>
       <c r="AW21" s="37"/>
       <c r="AX21" s="47" t="s">
-        <v>229</v>
+        <v>296</v>
       </c>
       <c r="AY21" s="47" t="s">
-        <v>230</v>
+        <v>297</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:51">
       <c r="A22" s="49"/>
       <c r="B22" s="44" t="s">
-        <v>231</v>
+        <v>298</v>
       </c>
       <c r="C22" s="45"/>
       <c r="D22" s="37"/>
@@ -5342,161 +6440,161 @@
     </row>
     <row r="24" ht="108" spans="1:51">
       <c r="A24" s="26" t="s">
-        <v>232</v>
+        <v>299</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>233</v>
+        <v>300</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>234</v>
+        <v>301</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>117</v>
+        <v>184</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>235</v>
+        <v>302</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>236</v>
+        <v>303</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>237</v>
+        <v>304</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="I24" s="31" t="s">
-        <v>238</v>
+        <v>305</v>
       </c>
       <c r="J24" s="31" t="s">
-        <v>239</v>
+        <v>306</v>
       </c>
       <c r="K24" s="31" t="s">
-        <v>240</v>
+        <v>307</v>
       </c>
       <c r="L24" s="31" t="s">
-        <v>241</v>
+        <v>308</v>
       </c>
       <c r="M24" s="31" t="s">
-        <v>242</v>
+        <v>309</v>
       </c>
       <c r="N24" s="31" t="s">
-        <v>243</v>
+        <v>310</v>
       </c>
       <c r="O24" s="31" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="P24" s="31" t="s">
-        <v>244</v>
+        <v>311</v>
       </c>
       <c r="Q24" s="31" t="s">
-        <v>245</v>
+        <v>312</v>
       </c>
       <c r="R24" s="31" t="s">
-        <v>246</v>
+        <v>313</v>
       </c>
       <c r="S24" s="31" t="s">
-        <v>247</v>
+        <v>314</v>
       </c>
       <c r="T24" s="31" t="s">
-        <v>248</v>
+        <v>315</v>
       </c>
       <c r="U24" s="31" t="s">
-        <v>249</v>
+        <v>316</v>
       </c>
       <c r="V24" s="31" t="s">
-        <v>250</v>
+        <v>317</v>
       </c>
       <c r="W24" s="31" t="s">
-        <v>251</v>
+        <v>318</v>
       </c>
       <c r="X24" s="31" t="s">
-        <v>252</v>
+        <v>319</v>
       </c>
       <c r="Y24" s="31" t="s">
-        <v>253</v>
+        <v>320</v>
       </c>
       <c r="Z24" s="31" t="s">
-        <v>254</v>
+        <v>321</v>
       </c>
       <c r="AA24" s="31" t="s">
-        <v>255</v>
+        <v>322</v>
       </c>
       <c r="AB24" s="31" t="s">
-        <v>256</v>
+        <v>323</v>
       </c>
       <c r="AC24" s="31" t="s">
-        <v>257</v>
+        <v>324</v>
       </c>
       <c r="AD24" s="31" t="s">
-        <v>258</v>
+        <v>325</v>
       </c>
       <c r="AE24" s="31" t="s">
-        <v>259</v>
+        <v>326</v>
       </c>
       <c r="AF24" s="31" t="s">
-        <v>260</v>
+        <v>327</v>
       </c>
       <c r="AG24" s="31" t="s">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c r="AH24" s="31" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AI24" s="31" t="s">
-        <v>262</v>
+        <v>329</v>
       </c>
       <c r="AJ24" s="31" t="s">
-        <v>263</v>
+        <v>330</v>
       </c>
       <c r="AK24" s="31" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AL24" s="31" t="s">
-        <v>264</v>
+        <v>331</v>
       </c>
       <c r="AM24" s="31" t="s">
-        <v>265</v>
+        <v>332</v>
       </c>
       <c r="AN24" s="31" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AO24" s="31"/>
       <c r="AP24" s="31" t="s">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c r="AQ24" s="31" t="s">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c r="AR24" s="31" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
       <c r="AS24" s="31" t="s">
-        <v>266</v>
+        <v>333</v>
       </c>
       <c r="AT24" s="31" t="s">
-        <v>267</v>
+        <v>334</v>
       </c>
       <c r="AU24" s="31" t="s">
-        <v>268</v>
+        <v>335</v>
       </c>
       <c r="AV24" s="31" t="s">
-        <v>269</v>
+        <v>336</v>
       </c>
       <c r="AW24" s="32" t="s">
-        <v>270</v>
+        <v>337</v>
       </c>
       <c r="AX24" s="32" t="s">
-        <v>261</v>
+        <v>328</v>
       </c>
       <c r="AY24" s="32" t="s">
-        <v>102</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:51">
       <c r="A25" s="28"/>
       <c r="B25" s="33" t="s">
-        <v>271</v>
+        <v>338</v>
       </c>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
@@ -5551,14 +6649,14 @@
     <row r="26" customFormat="1" ht="94.5" spans="1:51">
       <c r="A26" s="34"/>
       <c r="B26" s="33" t="s">
-        <v>272</v>
+        <v>339</v>
       </c>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
       <c r="G26" s="31" t="s">
-        <v>273</v>
+        <v>340</v>
       </c>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
@@ -5566,10 +6664,10 @@
       <c r="K26" s="31"/>
       <c r="L26" s="31"/>
       <c r="M26" s="31" t="s">
-        <v>274</v>
+        <v>341</v>
       </c>
       <c r="N26" s="31" t="s">
-        <v>275</v>
+        <v>342</v>
       </c>
       <c r="O26" s="31"/>
       <c r="P26" s="31"/>
@@ -5598,10 +6696,10 @@
       <c r="AM26" s="31"/>
       <c r="AN26" s="31"/>
       <c r="AO26" s="31" t="s">
-        <v>276</v>
+        <v>343</v>
       </c>
       <c r="AP26" s="31" t="s">
-        <v>277</v>
+        <v>344</v>
       </c>
       <c r="AQ26" s="31"/>
       <c r="AR26" s="31"/>
@@ -5615,10 +6713,10 @@
     </row>
     <row r="27" s="9" customFormat="1" ht="27" spans="1:51">
       <c r="A27" s="35" t="s">
-        <v>278</v>
+        <v>345</v>
       </c>
       <c r="B27" s="47" t="s">
-        <v>279</v>
+        <v>346</v>
       </c>
       <c r="C27" s="50"/>
       <c r="D27" s="50"/>
@@ -5721,7 +6819,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>280</v>
+        <v>347</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
@@ -5729,31 +6827,31 @@
     <row r="2" spans="1:3">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
-        <v>281</v>
+        <v>348</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>282</v>
+        <v>349</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>283</v>
+        <v>350</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>284</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>285</v>
+        <v>352</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -5764,31 +6862,31 @@
     <row r="7" spans="1:3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>286</v>
+        <v>353</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>287</v>
+        <v>354</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>288</v>
+        <v>355</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5" t="s">
-        <v>289</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5" t="s">
-        <v>290</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -5799,38 +6897,38 @@
     <row r="12" spans="1:3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
-        <v>291</v>
+        <v>358</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>292</v>
+        <v>359</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="6"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5" t="s">
-        <v>293</v>
+        <v>360</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6"/>
       <c r="B14" s="4"/>
       <c r="C14" s="5" t="s">
-        <v>294</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6"/>
       <c r="B15" s="4"/>
       <c r="C15" s="5" t="s">
-        <v>295</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="6"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5" t="s">
-        <v>296</v>
+        <v>363</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -5841,31 +6939,31 @@
     <row r="18" spans="1:3">
       <c r="A18" s="6"/>
       <c r="B18" s="4" t="s">
-        <v>297</v>
+        <v>364</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>298</v>
+        <v>365</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
       <c r="C19" s="7" t="s">
-        <v>299</v>
+        <v>366</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6"/>
       <c r="B20" s="4"/>
       <c r="C20" s="7" t="s">
-        <v>300</v>
+        <v>367</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="6"/>
       <c r="B21" s="4"/>
       <c r="C21" s="7" t="s">
-        <v>301</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="369">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="381">
   <si>
     <t>项目整合管理</t>
   </si>
@@ -129,6 +129,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>制定项目章程</t>
     </r>
     <r>
@@ -143,6 +151,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>制定项目管理计划</t>
     </r>
     <r>
@@ -157,6 +173,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>指导与管理项目工作</t>
     </r>
     <r>
@@ -171,6 +195,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>管理项目知识</t>
     </r>
     <r>
@@ -185,6 +217,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>监控项目工作</t>
     </r>
     <r>
@@ -199,6 +239,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>实施整体变更控制</t>
     </r>
     <r>
@@ -213,6 +261,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>结束项目或阶段</t>
     </r>
     <r>
@@ -227,6 +283,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>规划范围管理</t>
     </r>
     <r>
@@ -241,6 +305,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>收集需求</t>
     </r>
     <r>
@@ -255,6 +327,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>定义范围</t>
     </r>
     <r>
@@ -269,6 +349,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>创建WBS</t>
     </r>
     <r>
@@ -283,6 +371,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>确认范围</t>
     </r>
     <r>
@@ -297,6 +393,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>控制范围</t>
     </r>
     <r>
@@ -311,6 +415,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>规划进度管理</t>
     </r>
     <r>
@@ -325,6 +437,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>定义活动</t>
     </r>
     <r>
@@ -339,6 +459,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>排列活动顺序</t>
     </r>
     <r>
@@ -353,6 +481,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>估算活动持续时间</t>
     </r>
     <r>
@@ -367,6 +503,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>制定进度计划</t>
     </r>
     <r>
@@ -381,6 +525,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>控制进度</t>
     </r>
     <r>
@@ -395,6 +547,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>规划成本管理</t>
     </r>
     <r>
@@ -409,6 +569,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>估算成本</t>
     </r>
     <r>
@@ -423,6 +591,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>制定预算</t>
     </r>
     <r>
@@ -437,6 +613,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>控制成本</t>
     </r>
     <r>
@@ -451,6 +635,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>规划质量管理</t>
     </r>
     <r>
@@ -465,6 +657,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>管理质量</t>
     </r>
     <r>
@@ -479,6 +679,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>控制质量</t>
     </r>
     <r>
@@ -493,6 +701,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>规划资源管理</t>
     </r>
     <r>
@@ -507,6 +723,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>估算活动资源</t>
     </r>
     <r>
@@ -521,6 +745,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>获取资源</t>
     </r>
     <r>
@@ -535,6 +767,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>建设团队</t>
     </r>
     <r>
@@ -549,6 +789,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>管理团队</t>
     </r>
     <r>
@@ -563,6 +811,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>控制资源</t>
     </r>
     <r>
@@ -577,6 +833,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>规划沟通管理</t>
     </r>
     <r>
@@ -591,6 +855,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>管理沟通</t>
     </r>
     <r>
@@ -605,6 +877,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>监督沟通</t>
     </r>
     <r>
@@ -619,6 +899,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>规划风险管理</t>
     </r>
     <r>
@@ -633,6 +921,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>识别风险</t>
     </r>
     <r>
@@ -647,6 +943,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>实施定性风险分析</t>
     </r>
     <r>
@@ -661,6 +965,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>实施定量风险分析</t>
     </r>
     <r>
@@ -675,6 +987,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>规划风险应对</t>
     </r>
     <r>
@@ -689,6 +1009,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>实施风险应对</t>
     </r>
     <r>
@@ -703,6 +1031,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>监督风险</t>
     </r>
     <r>
@@ -717,6 +1053,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>规划采购管理</t>
     </r>
     <r>
@@ -731,6 +1075,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>实施采购</t>
     </r>
     <r>
@@ -745,6 +1097,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>控制采购</t>
     </r>
     <r>
@@ -759,6 +1119,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>识别干系人</t>
     </r>
     <r>
@@ -773,6 +1141,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>规划干系人参与</t>
     </r>
     <r>
@@ -787,6 +1163,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>管理干系人参与</t>
     </r>
     <r>
@@ -801,6 +1185,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>监督干系人参与</t>
     </r>
     <r>
@@ -815,6 +1207,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -831,6 +1231,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -847,6 +1255,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -863,6 +1279,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -879,6 +1303,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义： 
  </t>
     </r>
@@ -895,6 +1327,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -911,6 +1351,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -927,6 +1375,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -943,6 +1399,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -959,6 +1423,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -975,6 +1447,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -991,6 +1471,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -1007,6 +1495,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -1023,6 +1519,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1039,6 +1543,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1055,6 +1567,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1071,6 +1591,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1087,6 +1615,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -1103,6 +1639,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1119,6 +1663,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -1135,6 +1687,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1151,6 +1711,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1167,6 +1735,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1183,6 +1759,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1199,6 +1783,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1215,6 +1807,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1231,6 +1831,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1247,6 +1855,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1263,6 +1879,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1279,6 +1903,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1295,6 +1927,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -1311,6 +1951,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1327,6 +1975,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1343,6 +1999,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1359,6 +2023,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1375,6 +2047,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1391,6 +2071,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1407,6 +2095,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1423,6 +2119,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1439,6 +2143,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -1455,6 +2167,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1471,6 +2191,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1486,10 +2214,175 @@
     </r>
   </si>
   <si>
-    <t>定义：</t>
-  </si>
-  <si>
-    <r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是记录项目采购决策、明确采购方法，及识别潜在卖方的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是获取卖方应答、选择卖方并授予合同的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是管理采购关系、监督合同绩效、实施必要的变更和纠偏，以及关闭合同的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是定期识别项目干系人，分析和记录他们的利益、参与度、项目依赖性、影响力和对项目成功的潜在影响的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是根据干系人的需求、期望、利益和对项目的潜在影响，制定项目干系人参与项目的方法的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是通过与干系人进行沟通协作，以满足其需求与期望、处理问题，并促进干系人合理参与的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是监督项目干系人的关系，并通过修订参与策略和计划来引导干系人合理参与项目的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1508,6 +2401,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -1524,6 +2425,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1540,6 +2449,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1557,6 +2474,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1574,6 +2499,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1590,6 +2523,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1607,6 +2548,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -1623,6 +2572,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1639,6 +2596,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -1655,6 +2620,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -1671,6 +2644,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1688,6 +2669,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1704,6 +2693,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1720,6 +2717,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
  </t>
     </r>
@@ -1736,6 +2741,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1752,6 +2765,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -1768,6 +2789,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1784,6 +2813,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1800,6 +2837,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1816,6 +2861,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1832,6 +2885,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1848,6 +2909,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1864,6 +2933,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1880,6 +2957,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1898,6 +2983,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1915,6 +3008,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -1931,6 +3032,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1947,6 +3056,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -1964,6 +3081,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -1980,6 +3105,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
  </t>
     </r>
@@ -1996,6 +3129,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2013,6 +3154,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -2031,6 +3180,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -2047,6 +3204,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
  </t>
     </r>
@@ -2063,6 +3228,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -2079,6 +3252,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
  </t>
     </r>
@@ -2096,6 +3277,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -2112,6 +3301,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2129,6 +3326,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2146,6 +3351,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2163,6 +3376,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2178,7 +3399,164 @@
     </r>
   </si>
   <si>
-    <t>作用：</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">作用：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是确定是否从项目外部获取货物和服务，如果是，则还要确定将在什么时间、以什么方式获取什么货物和服务</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  选定合格卖方并签署关于货物或服务交付的法律协议</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  确保买卖双方履行法律协议，满足项目需求</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">作用：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 使项目团队能够建立对每个干系人或干系人群体的适度关注</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>提供与干系人进行有效互动的可行计划</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  尽可能提高干系人的支持度，并降低干系人的抵制程度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>随着项目进展和环境变化，维持或提升干系人参与会随着项目进展和环境变化，维持或提升干系人参与活动的效率和效果</t>
+    </r>
   </si>
   <si>
     <t>口语解释：</t>
@@ -4131,7 +5509,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2794000" y="17881600"/>
+          <a:off x="2794000" y="17367250"/>
           <a:ext cx="11544300" cy="6191250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -4865,642 +6243,642 @@
       <c r="AR4" s="24" t="s">
         <v>110</v>
       </c>
-      <c r="AS4" s="25" t="s">
+      <c r="AS4" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="AT4" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="AU4" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="AV4" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="AW4" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="AX4" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="AY4" s="25" t="s">
-        <v>111</v>
+      <c r="AT4" s="24" t="s">
+        <v>112</v>
+      </c>
+      <c r="AU4" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="AV4" s="24" t="s">
+        <v>114</v>
+      </c>
+      <c r="AW4" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="AX4" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="AY4" s="24" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="5" s="8" customFormat="1" ht="108" spans="1:51">
       <c r="A5" s="21"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="G5" s="24" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="H5" s="24" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="I5" s="24" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="J5" s="24" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="K5" s="24" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="L5" s="24" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="M5" s="24" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="N5" s="24" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="O5" s="24" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="P5" s="24" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="Q5" s="24" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="R5" s="24" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="S5" s="24" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="T5" s="24" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="U5" s="24" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="V5" s="24" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="W5" s="24" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="X5" s="24" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="Y5" s="24" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="Z5" s="24" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="AA5" s="24" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="AB5" s="24" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="AC5" s="24" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="AD5" s="24" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="AE5" s="24" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="AF5" s="24" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="AG5" s="24" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="AH5" s="24" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="AI5" s="24" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="AJ5" s="24" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="AK5" s="24" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="AL5" s="24" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="AM5" s="24" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="AN5" s="24" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="AO5" s="24" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="AP5" s="24" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="AQ5" s="24" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="AR5" s="24" t="s">
-        <v>153</v>
-      </c>
-      <c r="AS5" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="AT5" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="AU5" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="AV5" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="AW5" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="AX5" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="AY5" s="25" t="s">
-        <v>154</v>
+        <v>159</v>
+      </c>
+      <c r="AS5" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="AT5" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="AU5" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="AV5" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="AW5" s="24" t="s">
+        <v>164</v>
+      </c>
+      <c r="AX5" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="AY5" s="24" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="6" s="8" customFormat="1" ht="27" spans="1:51">
       <c r="A6" s="21"/>
       <c r="B6" s="21"/>
       <c r="C6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="D6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="G6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="M6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="N6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="O6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="P6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="Q6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="R6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="S6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="T6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="U6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="V6" s="24" t="s">
-        <v>156</v>
+        <v>168</v>
       </c>
       <c r="W6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="X6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="Y6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="Z6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AA6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AB6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AC6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AD6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AE6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AF6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AG6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AH6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AI6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AJ6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AK6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AL6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AM6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AN6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AO6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AP6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AQ6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AR6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AS6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AT6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AU6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AV6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AW6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AX6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
       <c r="AY6" s="25" t="s">
-        <v>155</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="7" s="8" customFormat="1" ht="67.5" spans="1:51">
+    <row r="7" s="8" customFormat="1" ht="54" spans="1:51">
       <c r="A7" s="26" t="s">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>158</v>
+        <v>170</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="D7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="F7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="H7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="J7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="L7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="N7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="O7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="P7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="Q7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="R7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="S7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="T7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="U7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="V7" s="24" t="s">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="W7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="X7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="Y7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="Z7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AA7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AB7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AC7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AD7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AE7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AF7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AG7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AH7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AI7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AJ7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AK7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AL7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AM7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AN7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AO7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AP7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AQ7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AR7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AS7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AT7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AU7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AV7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AW7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AX7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
       <c r="AY7" s="25" t="s">
-        <v>159</v>
+        <v>171</v>
       </c>
     </row>
     <row r="8" ht="67.5" spans="1:51">
       <c r="A8" s="28"/>
       <c r="B8" s="29" t="s">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="C8" s="30" t="s">
-        <v>162</v>
+        <v>174</v>
       </c>
       <c r="D8" s="30" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="E8" s="30" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F8" s="30" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="G8" s="30" t="s">
-        <v>166</v>
+        <v>178</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="J8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="K8" s="30" t="s">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="L8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="M8" s="30" t="s">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="N8" s="30" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="O8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="P8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="Q8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="R8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="S8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="T8" s="30" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="U8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="V8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="W8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="X8" s="30" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="Y8" s="30" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="Z8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AA8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AB8" s="30" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="AC8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AD8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AE8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AF8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AG8" s="30" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="AH8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AI8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AJ8" s="30" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="AK8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AL8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AM8" s="30" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="AN8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AO8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AP8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AQ8" s="30" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AR8" s="30" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="AS8" s="31" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="AT8" s="31" t="s">
+        <v>193</v>
+      </c>
+      <c r="AU8" s="31" t="s">
+        <v>194</v>
+      </c>
+      <c r="AV8" s="31" t="s">
+        <v>195</v>
+      </c>
+      <c r="AW8" s="31" t="s">
+        <v>185</v>
+      </c>
+      <c r="AX8" s="32" t="s">
         <v>181</v>
       </c>
-      <c r="AU8" s="31" t="s">
-        <v>182</v>
-      </c>
-      <c r="AV8" s="31" t="s">
-        <v>183</v>
-      </c>
-      <c r="AW8" s="31" t="s">
-        <v>173</v>
-      </c>
-      <c r="AX8" s="32" t="s">
-        <v>169</v>
-      </c>
       <c r="AY8" s="32" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="9" ht="40.5" spans="1:51">
       <c r="A9" s="28"/>
       <c r="B9" s="33" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
@@ -5511,12 +6889,12 @@
       <c r="I9" s="31"/>
       <c r="J9" s="31"/>
       <c r="K9" s="31" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="L9" s="31"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="O9" s="31"/>
       <c r="P9" s="31"/>
@@ -5559,7 +6937,7 @@
     <row r="10" ht="81" spans="1:51">
       <c r="A10" s="34"/>
       <c r="B10" s="33" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
@@ -5570,14 +6948,14 @@
       <c r="I10" s="31"/>
       <c r="J10" s="31"/>
       <c r="K10" s="31" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="L10" s="31" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="M10" s="31"/>
       <c r="N10" s="31" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="O10" s="31"/>
       <c r="P10" s="31"/>
@@ -5592,7 +6970,7 @@
       <c r="Y10" s="31"/>
       <c r="Z10" s="31"/>
       <c r="AA10" s="31" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="AB10" s="31"/>
       <c r="AC10" s="31"/>
@@ -5603,7 +6981,7 @@
       <c r="AH10" s="31"/>
       <c r="AI10" s="31"/>
       <c r="AJ10" s="31" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="AK10" s="31"/>
       <c r="AL10" s="31"/>
@@ -5623,10 +7001,10 @@
     </row>
     <row r="11" spans="1:51">
       <c r="A11" s="35" t="s">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="B11" s="36" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -5680,10 +7058,10 @@
     </row>
     <row r="12" spans="1:51">
       <c r="A12" s="35" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>196</v>
+        <v>208</v>
       </c>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
@@ -5735,133 +7113,133 @@
       <c r="AX12" s="9"/>
       <c r="AY12" s="9"/>
     </row>
-    <row r="14" ht="121.5" spans="1:51">
+    <row r="14" ht="94.5" spans="1:51">
       <c r="A14" s="38" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="B14" s="39" t="s">
-        <v>198</v>
+        <v>210</v>
       </c>
       <c r="C14" s="40"/>
       <c r="D14" s="41"/>
       <c r="E14" s="41"/>
       <c r="F14" s="41" t="s">
-        <v>199</v>
+        <v>211</v>
       </c>
       <c r="G14" s="41"/>
       <c r="H14" s="41" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="I14" s="41"/>
       <c r="J14" s="41"/>
       <c r="K14" s="41" t="s">
-        <v>201</v>
+        <v>213</v>
       </c>
       <c r="L14" s="41" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="M14" s="41" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="N14" s="41" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="O14" s="41"/>
       <c r="P14" s="41"/>
       <c r="Q14" s="41" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="R14" s="41" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="S14" s="41" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="T14" s="41" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="U14" s="41" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="V14" s="41"/>
       <c r="W14" s="41" t="s">
-        <v>207</v>
+        <v>219</v>
       </c>
       <c r="X14" s="41" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="Y14" s="41" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="Z14" s="41" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="AA14" s="41" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="AB14" s="41" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="AC14" s="41" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="AD14" s="41" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="AE14" s="41" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="AF14" s="41" t="s">
-        <v>218</v>
+        <v>230</v>
       </c>
       <c r="AG14" s="41"/>
       <c r="AH14" s="41" t="s">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="AI14" s="41" t="s">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="AJ14" s="41" t="s">
-        <v>221</v>
+        <v>233</v>
       </c>
       <c r="AK14" s="41"/>
       <c r="AL14" s="41"/>
       <c r="AM14" s="41" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="AN14" s="41" t="s">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="AO14" s="41" t="s">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="AP14" s="41" t="s">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="AQ14" s="41"/>
       <c r="AR14" s="41" t="s">
-        <v>226</v>
+        <v>238</v>
       </c>
       <c r="AS14" s="42" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="AT14" s="41" t="s">
-        <v>228</v>
+        <v>240</v>
       </c>
       <c r="AU14" s="41" t="s">
-        <v>229</v>
+        <v>241</v>
       </c>
       <c r="AV14" s="32"/>
       <c r="AW14" s="32"/>
       <c r="AX14" s="31" t="s">
-        <v>230</v>
+        <v>242</v>
       </c>
       <c r="AY14" s="31"/>
     </row>
     <row r="15" spans="1:51">
       <c r="A15" s="43"/>
       <c r="B15" s="44" t="s">
-        <v>231</v>
+        <v>243</v>
       </c>
       <c r="C15" s="45"/>
       <c r="D15" s="37"/>
@@ -5916,13 +7294,13 @@
     <row r="16" ht="67.5" spans="1:51">
       <c r="A16" s="43"/>
       <c r="B16" s="44" t="s">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="C16" s="46" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="D16" s="47" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
@@ -5931,7 +7309,7 @@
       <c r="I16" s="37"/>
       <c r="J16" s="37"/>
       <c r="K16" s="47" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="L16" s="37"/>
       <c r="M16" s="37"/>
@@ -5948,13 +7326,13 @@
       <c r="X16" s="37"/>
       <c r="Y16" s="37"/>
       <c r="Z16" s="47" t="s">
-        <v>236</v>
+        <v>248</v>
       </c>
       <c r="AA16" s="37" t="s">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="AB16" s="47" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="AC16" s="37"/>
       <c r="AD16" s="37"/>
@@ -5967,24 +7345,24 @@
       <c r="AK16" s="37"/>
       <c r="AL16" s="37"/>
       <c r="AM16" s="47" t="s">
-        <v>239</v>
+        <v>251</v>
       </c>
       <c r="AN16" s="37"/>
       <c r="AO16" s="37" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="AP16" s="37" t="s">
-        <v>240</v>
+        <v>252</v>
       </c>
       <c r="AQ16" s="37"/>
       <c r="AR16" s="37"/>
       <c r="AS16" s="37" t="s">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="AT16" s="37"/>
       <c r="AU16" s="37"/>
       <c r="AV16" s="47" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="AW16" s="37"/>
       <c r="AX16" s="37"/>
@@ -5993,61 +7371,61 @@
     <row r="17" ht="81" spans="1:51">
       <c r="A17" s="43"/>
       <c r="B17" s="44" t="s">
-        <v>243</v>
+        <v>255</v>
       </c>
       <c r="C17" s="45"/>
       <c r="D17" s="37"/>
       <c r="E17" s="37"/>
       <c r="F17" s="37"/>
       <c r="G17" s="47" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="H17" s="37"/>
       <c r="I17" s="47" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="J17" s="37"/>
       <c r="K17" s="37" t="s">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="L17" s="37" t="s">
-        <v>247</v>
+        <v>259</v>
       </c>
       <c r="M17" s="37"/>
       <c r="N17" s="37"/>
       <c r="O17" s="47" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="P17" s="37"/>
       <c r="Q17" s="37"/>
       <c r="R17" s="37"/>
       <c r="S17" s="47" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="T17" s="47" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="U17" s="47" t="s">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="V17" s="37"/>
       <c r="W17" s="47" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="X17" s="37" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="Y17" s="47" t="s">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="Z17" s="47" t="s">
-        <v>255</v>
+        <v>267</v>
       </c>
       <c r="AA17" s="47" t="s">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="AB17" s="47" t="s">
-        <v>257</v>
+        <v>269</v>
       </c>
       <c r="AC17" s="37"/>
       <c r="AD17" s="37"/>
@@ -6055,54 +7433,54 @@
       <c r="AF17" s="37"/>
       <c r="AG17" s="37"/>
       <c r="AH17" s="47" t="s">
-        <v>258</v>
+        <v>270</v>
       </c>
       <c r="AI17" s="37"/>
       <c r="AJ17" s="37"/>
       <c r="AK17" s="37"/>
       <c r="AL17" s="37" t="s">
-        <v>259</v>
+        <v>271</v>
       </c>
       <c r="AM17" s="47" t="s">
-        <v>260</v>
+        <v>272</v>
       </c>
       <c r="AN17" s="47" t="s">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="AO17" s="47" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="AP17" s="47" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="AQ17" s="37"/>
       <c r="AR17" s="47" t="s">
-        <v>264</v>
+        <v>276</v>
       </c>
       <c r="AS17" s="37" t="s">
-        <v>265</v>
+        <v>277</v>
       </c>
       <c r="AT17" s="37" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="AU17" s="47" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="AV17" s="47" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="AW17" s="47" t="s">
-        <v>269</v>
+        <v>281</v>
       </c>
       <c r="AX17" s="37"/>
       <c r="AY17" s="47" t="s">
-        <v>270</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" ht="81" spans="1:51">
       <c r="A18" s="43"/>
       <c r="B18" s="44" t="s">
-        <v>271</v>
+        <v>283</v>
       </c>
       <c r="C18" s="45"/>
       <c r="D18" s="37"/>
@@ -6113,7 +7491,7 @@
       <c r="I18" s="37"/>
       <c r="J18" s="37"/>
       <c r="K18" s="47" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="L18" s="37"/>
       <c r="M18" s="37"/>
@@ -6130,16 +7508,16 @@
       <c r="X18" s="37"/>
       <c r="Y18" s="37"/>
       <c r="Z18" s="47" t="s">
-        <v>273</v>
+        <v>285</v>
       </c>
       <c r="AA18" s="47" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="AB18" s="47" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="AC18" s="47" t="s">
-        <v>276</v>
+        <v>288</v>
       </c>
       <c r="AD18" s="37"/>
       <c r="AE18" s="37"/>
@@ -6147,16 +7525,16 @@
       <c r="AG18" s="37"/>
       <c r="AH18" s="37"/>
       <c r="AI18" s="37" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AJ18" s="37"/>
       <c r="AK18" s="37" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
       <c r="AL18" s="37"/>
       <c r="AM18" s="37"/>
       <c r="AN18" s="47" t="s">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="AO18" s="37"/>
       <c r="AP18" s="37"/>
@@ -6166,20 +7544,20 @@
       <c r="AT18" s="37"/>
       <c r="AU18" s="37"/>
       <c r="AV18" s="47" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="AW18" s="47" t="s">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="AX18" s="37"/>
       <c r="AY18" s="47" t="s">
-        <v>277</v>
+        <v>289</v>
       </c>
     </row>
     <row r="19" ht="40.5" spans="1:51">
       <c r="A19" s="43"/>
       <c r="B19" s="44" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="C19" s="45"/>
       <c r="D19" s="37"/>
@@ -6187,15 +7565,15 @@
       <c r="F19" s="37"/>
       <c r="G19" s="37"/>
       <c r="H19" s="47" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="I19" s="37"/>
       <c r="J19" s="37"/>
       <c r="K19" s="47" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="L19" s="37" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="M19" s="37"/>
       <c r="N19" s="37"/>
@@ -6216,7 +7594,7 @@
       <c r="AC19" s="37"/>
       <c r="AD19" s="37"/>
       <c r="AE19" s="37" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="AF19" s="37"/>
       <c r="AG19" s="37"/>
@@ -6229,7 +7607,7 @@
       <c r="AN19" s="37"/>
       <c r="AO19" s="37"/>
       <c r="AP19" s="37" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="AQ19" s="37"/>
       <c r="AR19" s="37"/>
@@ -6240,13 +7618,13 @@
       <c r="AW19" s="47"/>
       <c r="AX19" s="37"/>
       <c r="AY19" s="47" t="s">
-        <v>284</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" ht="54" spans="1:51">
       <c r="A20" s="43"/>
       <c r="B20" s="44" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="C20" s="45"/>
       <c r="D20" s="37"/>
@@ -6282,7 +7660,7 @@
       <c r="AH20" s="37"/>
       <c r="AI20" s="37"/>
       <c r="AJ20" s="47" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="AK20" s="37"/>
       <c r="AL20" s="37"/>
@@ -6303,13 +7681,13 @@
     <row r="21" ht="81" spans="1:51">
       <c r="A21" s="43"/>
       <c r="B21" s="48" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
       <c r="C21" s="46" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="E21" s="37"/>
       <c r="F21" s="37"/>
@@ -6318,10 +7696,10 @@
       <c r="I21" s="37"/>
       <c r="J21" s="37"/>
       <c r="K21" s="47" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="L21" s="37" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="M21" s="37"/>
       <c r="N21" s="37"/>
@@ -6342,51 +7720,51 @@
       <c r="AC21" s="37"/>
       <c r="AD21" s="37"/>
       <c r="AE21" s="37" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="AF21" s="47" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="AG21" s="47" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="AH21" s="37"/>
       <c r="AI21" s="47" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="AJ21" s="47" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="AK21" s="37"/>
       <c r="AL21" s="37"/>
       <c r="AM21" s="37"/>
       <c r="AN21" s="37"/>
       <c r="AO21" s="37" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AP21" s="37" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="AQ21" s="37"/>
       <c r="AR21" s="37"/>
       <c r="AS21" s="37"/>
       <c r="AT21" s="37" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="AU21" s="37"/>
       <c r="AV21" s="37"/>
       <c r="AW21" s="37"/>
       <c r="AX21" s="47" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="AY21" s="47" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:51">
       <c r="A22" s="49"/>
       <c r="B22" s="44" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C22" s="45"/>
       <c r="D22" s="37"/>
@@ -6440,161 +7818,161 @@
     </row>
     <row r="24" ht="108" spans="1:51">
       <c r="A24" s="26" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="C24" s="31" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="D24" s="31" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="F24" s="31" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="G24" s="31" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="I24" s="31" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="J24" s="31" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="K24" s="31" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="L24" s="31" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="M24" s="31" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="N24" s="31" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="O24" s="31" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="P24" s="31" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="Q24" s="31" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="R24" s="31" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="S24" s="31" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="T24" s="31" t="s">
-        <v>315</v>
+        <v>327</v>
       </c>
       <c r="U24" s="31" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="V24" s="31" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="W24" s="31" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="X24" s="31" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="Y24" s="31" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="Z24" s="31" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="AA24" s="31" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="AB24" s="31" t="s">
-        <v>323</v>
+        <v>335</v>
       </c>
       <c r="AC24" s="31" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="AD24" s="31" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="AE24" s="31" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="AF24" s="31" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="AG24" s="31" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="AH24" s="31" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AI24" s="31" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="AJ24" s="31" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="AK24" s="31" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AL24" s="31" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="AM24" s="31" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="AN24" s="31" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AO24" s="31"/>
       <c r="AP24" s="31" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="AQ24" s="31" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="AR24" s="31" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="AS24" s="31" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="AT24" s="31" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="AU24" s="31" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="AV24" s="31" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="AW24" s="32" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="AX24" s="32" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="AY24" s="32" t="s">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:51">
       <c r="A25" s="28"/>
       <c r="B25" s="33" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
@@ -6649,14 +8027,14 @@
     <row r="26" customFormat="1" ht="94.5" spans="1:51">
       <c r="A26" s="34"/>
       <c r="B26" s="33" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
       <c r="G26" s="31" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
@@ -6664,10 +8042,10 @@
       <c r="K26" s="31"/>
       <c r="L26" s="31"/>
       <c r="M26" s="31" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="N26" s="31" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="O26" s="31"/>
       <c r="P26" s="31"/>
@@ -6696,10 +8074,10 @@
       <c r="AM26" s="31"/>
       <c r="AN26" s="31"/>
       <c r="AO26" s="31" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="AP26" s="31" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="AQ26" s="31"/>
       <c r="AR26" s="31"/>
@@ -6713,10 +8091,10 @@
     </row>
     <row r="27" s="9" customFormat="1" ht="27" spans="1:51">
       <c r="A27" s="35" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="B27" s="47" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="C27" s="50"/>
       <c r="D27" s="50"/>
@@ -6819,7 +8197,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
@@ -6827,31 +8205,31 @@
     <row r="2" spans="1:3">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -6862,31 +8240,31 @@
     <row r="7" spans="1:3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -6897,38 +8275,38 @@
     <row r="12" spans="1:3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="6"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6"/>
       <c r="B14" s="4"/>
       <c r="C14" s="5" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6"/>
       <c r="B15" s="4"/>
       <c r="C15" s="5" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="6"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -6939,31 +8317,31 @@
     <row r="18" spans="1:3">
       <c r="A18" s="6"/>
       <c r="B18" s="4" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
       <c r="C19" s="7" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6"/>
       <c r="B20" s="4"/>
       <c r="C20" s="7" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="6"/>
       <c r="B21" s="4"/>
       <c r="C21" s="7" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="382">
   <si>
     <t>项目整合管理</t>
   </si>
@@ -65,13 +65,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>识别、定义、组合、统一和协调项目管理过程组的各个过程和项目管理管理活动</t>
     </r>
     <r>
@@ -283,6 +276,20 @@
   </si>
   <si>
     <r>
+      <t>规划范围管理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（规划过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <rPr>
         <b/>
         <sz val="11"/>
@@ -291,7 +298,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>规划范围管理</t>
+      <t>收集需求</t>
     </r>
     <r>
       <rPr>
@@ -313,7 +320,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>收集需求</t>
+      <t>定义范围</t>
     </r>
     <r>
       <rPr>
@@ -335,7 +342,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>定义范围</t>
+      <t>创建WBS</t>
     </r>
     <r>
       <rPr>
@@ -357,7 +364,51 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>创建WBS</t>
+      <t>确认范围</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（监控过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>控制范围</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（监控过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>规划进度管理</t>
     </r>
     <r>
       <rPr>
@@ -379,7 +430,95 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>确认范围</t>
+      <t>定义活动</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（规划过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>排列活动顺序</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（规划过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>估算活动持续时间</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（规划过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>制定进度计划</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（规划过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>控制进度</t>
     </r>
     <r>
       <rPr>
@@ -401,7 +540,73 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>控制范围</t>
+      <t>规划成本管理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（规划过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>估算成本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（规划过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>制定预算</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（规划过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>控制成本</t>
     </r>
     <r>
       <rPr>
@@ -423,7 +628,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>规划进度管理</t>
+      <t>规划质量管理</t>
     </r>
     <r>
       <rPr>
@@ -445,7 +650,51 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>定义活动</t>
+      <t>管理质量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（执行过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>控制质量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（监控过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>规划资源管理</t>
     </r>
     <r>
       <rPr>
@@ -467,7 +716,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>排列活动顺序</t>
+      <t>估算活动资源</t>
     </r>
     <r>
       <rPr>
@@ -489,7 +738,95 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>估算活动持续时间</t>
+      <t>获取资源</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（执行过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>建设团队</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（执行过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>管理团队</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（执行过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>控制资源</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（监控过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>规划沟通管理</t>
     </r>
     <r>
       <rPr>
@@ -511,7 +848,51 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>制定进度计划</t>
+      <t>管理沟通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（执行过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>监督沟通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（监控过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>规划风险管理</t>
     </r>
     <r>
       <rPr>
@@ -533,7 +914,117 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>控制进度</t>
+      <t>识别风险</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（规划过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>实施定性风险分析</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（规划过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>实施定量风险分析</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（规划过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>规划风险应对</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（规划过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>实施风险应对</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（执行过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>监督风险</t>
     </r>
     <r>
       <rPr>
@@ -555,7 +1046,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>规划成本管理</t>
+      <t>规划采购管理</t>
     </r>
     <r>
       <rPr>
@@ -577,7 +1068,73 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>估算成本</t>
+      <t>实施采购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（执行过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>控制采购</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（监控过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>识别干系人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（启动过程组）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>规划干系人参与</t>
     </r>
     <r>
       <rPr>
@@ -599,16 +1156,16 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>制定预算</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（规划过程组）</t>
+      <t>管理干系人参与</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>（执行过程组）</t>
     </r>
   </si>
   <si>
@@ -621,7 +1178,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>控制成本</t>
+      <t>监督干系人参与</t>
     </r>
     <r>
       <rPr>
@@ -635,586 +1192,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>规划质量管理</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（规划过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>管理质量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（执行过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>控制质量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（监控过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>规划资源管理</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（规划过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>估算活动资源</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（规划过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>获取资源</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（执行过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>建设团队</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（执行过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>管理团队</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（执行过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>控制资源</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（监控过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>规划沟通管理</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（规划过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>管理沟通</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（执行过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>监督沟通</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（监控过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>规划风险管理</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（规划过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>识别风险</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（规划过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>实施定性风险分析</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（规划过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>实施定量风险分析</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（规划过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>规划风险应对</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（规划过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>实施风险应对</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（执行过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>监督风险</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（监控过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>规划采购管理</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（规划过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>实施采购</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（执行过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>控制采购</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（监控过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>识别干系人</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（启动过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>规划干系人参与</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（规划过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>管理干系人参与</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（执行过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>监督干系人参与</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（监控过程组）</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1231,14 +1208,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1255,14 +1224,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1279,14 +1240,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -1303,14 +1256,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">定义： 
  </t>
     </r>
@@ -1327,14 +1272,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1351,14 +1288,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1375,14 +1304,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1447,14 +1368,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1471,14 +1384,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -1495,14 +1400,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -2359,6 +2256,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -2375,14 +2280,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2401,14 +2298,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -2425,14 +2314,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2449,14 +2330,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2474,14 +2347,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2499,14 +2364,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2523,14 +2380,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2548,14 +2397,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -2620,14 +2461,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -2644,14 +2477,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2669,14 +2494,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -3544,6 +3361,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -4254,6 +4079,9 @@
   </si>
   <si>
     <t>工作绩效报告（非信息）</t>
+  </si>
+  <si>
+    <t>批准的变更请求（非变求）</t>
   </si>
   <si>
     <t>最终产品、服务或成果
@@ -7839,131 +7667,133 @@
         <v>316</v>
       </c>
       <c r="H24" s="31" t="s">
-        <v>176</v>
+        <v>317</v>
       </c>
       <c r="I24" s="31" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="J24" s="31" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K24" s="31" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="L24" s="31" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M24" s="31" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N24" s="31" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="O24" s="31" t="s">
         <v>181</v>
       </c>
       <c r="P24" s="31" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q24" s="31" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="R24" s="31" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="S24" s="31" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="T24" s="31" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="U24" s="31" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="V24" s="31" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="W24" s="31" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="X24" s="31" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Y24" s="31" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Z24" s="31" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AA24" s="31" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AB24" s="31" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AC24" s="31" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AD24" s="31" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AE24" s="31" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AF24" s="31" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG24" s="31" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AH24" s="31" t="s">
         <v>181</v>
       </c>
       <c r="AI24" s="31" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AJ24" s="31" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AK24" s="31" t="s">
         <v>181</v>
       </c>
       <c r="AL24" s="31" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AM24" s="31" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="AN24" s="31" t="s">
         <v>181</v>
       </c>
-      <c r="AO24" s="31"/>
+      <c r="AO24" s="31" t="s">
+        <v>181</v>
+      </c>
       <c r="AP24" s="31" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AQ24" s="31" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AR24" s="31" t="s">
         <v>181</v>
       </c>
       <c r="AS24" s="31" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AT24" s="31" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AU24" s="31" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AV24" s="31" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AW24" s="32" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AX24" s="32" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AY24" s="32" t="s">
         <v>181</v>
@@ -7972,7 +7802,7 @@
     <row r="25" customFormat="1" spans="1:51">
       <c r="A25" s="28"/>
       <c r="B25" s="33" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
@@ -8027,14 +7857,14 @@
     <row r="26" customFormat="1" ht="94.5" spans="1:51">
       <c r="A26" s="34"/>
       <c r="B26" s="33" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
       <c r="E26" s="31"/>
       <c r="F26" s="31"/>
       <c r="G26" s="31" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
@@ -8042,10 +7872,10 @@
       <c r="K26" s="31"/>
       <c r="L26" s="31"/>
       <c r="M26" s="31" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N26" s="31" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O26" s="31"/>
       <c r="P26" s="31"/>
@@ -8074,10 +7904,10 @@
       <c r="AM26" s="31"/>
       <c r="AN26" s="31"/>
       <c r="AO26" s="31" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AP26" s="31" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AQ26" s="31"/>
       <c r="AR26" s="31"/>
@@ -8091,10 +7921,10 @@
     </row>
     <row r="27" s="9" customFormat="1" ht="27" spans="1:51">
       <c r="A27" s="35" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B27" s="47" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C27" s="50"/>
       <c r="D27" s="50"/>
@@ -8197,7 +8027,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
@@ -8205,31 +8035,31 @@
     <row r="2" spans="1:3">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8240,31 +8070,31 @@
     <row r="7" spans="1:3">
       <c r="A7" s="6"/>
       <c r="B7" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8275,38 +8105,38 @@
     <row r="12" spans="1:3">
       <c r="A12" s="6"/>
       <c r="B12" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="6"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6"/>
       <c r="B14" s="4"/>
       <c r="C14" s="5" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6"/>
       <c r="B15" s="4"/>
       <c r="C15" s="5" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="6"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8317,31 +8147,31 @@
     <row r="18" spans="1:3">
       <c r="A18" s="6"/>
       <c r="B18" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
       <c r="C19" s="7" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6"/>
       <c r="B20" s="4"/>
       <c r="C20" s="7" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="6"/>
       <c r="B21" s="4"/>
       <c r="C21" s="7" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="15360" windowHeight="4560"/>
   </bookViews>
   <sheets>
     <sheet name="49过程输入输出工具" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="413">
   <si>
     <t>项目整合管理</t>
   </si>
@@ -65,6 +65,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>识别、定义、组合、统一和协调项目管理过程组的各个过程和项目管理管理活动</t>
     </r>
     <r>
@@ -276,6 +283,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>规划范围管理</t>
     </r>
     <r>
@@ -1192,6 +1207,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1208,6 +1231,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1224,6 +1255,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1240,6 +1279,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -1256,6 +1303,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义： 
  </t>
     </r>
@@ -1272,6 +1327,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1288,6 +1351,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1304,6 +1375,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1368,6 +1447,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1384,6 +1471,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -1400,6 +1495,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -1680,14 +1783,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -2280,6 +2375,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2298,6 +2401,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -2314,6 +2425,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2330,6 +2449,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2347,6 +2474,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2364,6 +2499,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2380,6 +2523,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2397,6 +2548,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -2461,6 +2620,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -2477,6 +2644,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2494,6 +2669,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2774,14 +2957,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -4327,6 +4502,110 @@
   </si>
   <si>
     <t>4）物资（产品）的可用性</t>
+  </si>
+  <si>
+    <t>进度管理</t>
+  </si>
+  <si>
+    <t>计划评审技术PERT-三点估算技术</t>
+  </si>
+  <si>
+    <t>三角分布公式</t>
+  </si>
+  <si>
+    <t>Te(期望值) = (To(最乐观)+Tm(最可能)+Tp(最悲观))/3</t>
+  </si>
+  <si>
+    <t>β分布公式</t>
+  </si>
+  <si>
+    <t>Te(期望值) = (To(最乐观)+4*Tm(最可能)+Tp(最悲观))/6</t>
+  </si>
+  <si>
+    <t>三点估算的标准差公式</t>
+  </si>
+  <si>
+    <t>σ(标准差) = (Tp(最悲观)-To(最乐观))/6</t>
+  </si>
+  <si>
+    <t>三点估算的标准差概率正
+太分布图及其规律</t>
+  </si>
+  <si>
+    <t>μ=Te期望值
+±1σ=68.26%
+±2σ=95.46%
+±3σ=99.73%
+记忆技巧1：168 295 399
+记忆技巧2：1682 2954 3997
+记忆技巧3：34.1 13.6 2.1 0.1</t>
+  </si>
+  <si>
+    <t>风险管理</t>
+  </si>
+  <si>
+    <t>风险管理-决策树分析、EMV期望货币价值</t>
+  </si>
+  <si>
+    <t>沟通管理</t>
+  </si>
+  <si>
+    <t>沟通渠道</t>
+  </si>
+  <si>
+    <t>沟通渠道数计算公式</t>
+  </si>
+  <si>
+    <t>沟通渠道数=n x (n-1)/2</t>
+  </si>
+  <si>
+    <t>采购管理</t>
+  </si>
+  <si>
+    <t>加权标准</t>
+  </si>
+  <si>
+    <t>加权得分计算公式</t>
+  </si>
+  <si>
+    <t>q1x(f11+f21+..+fn1)/n+q2x(f12+f22+..+fn2)/n+...+qnx(f1n+f2n+..+fnn)/n</t>
+  </si>
+  <si>
+    <t>净现值分析、投资收益率分析</t>
+  </si>
+  <si>
+    <t>折现率</t>
+  </si>
+  <si>
+    <t>折现是把未来资金换算成现在等值金额，折现率也称贴现率，是折现用的利率，如利息利率</t>
+  </si>
+  <si>
+    <t>折现系数</t>
+  </si>
+  <si>
+    <t>折现系数为 1/(1+i)^n
+P(现值) = F(未来值)/(1 + i)^n</t>
+  </si>
+  <si>
+    <t>净现值NPV</t>
+  </si>
+  <si>
+    <t>将项目各年净现金流量按基准收益率折现到建设初期的现值之和，也称累计净现值</t>
+  </si>
+  <si>
+    <t>投资回收期</t>
+  </si>
+  <si>
+    <t>T为累计现金流量首次为正的年数
+静态投资回收期=(T-1) + 第(T-1)年累计现金流绝对值/第T年现金流
+动态投资回收期=(T-1) + 第(T-1)年累计折现值绝对值/第T年折现值</t>
+  </si>
+  <si>
+    <t>投入开始年的选择</t>
+  </si>
+  <si>
+    <t>题目是按年如2014、2015等，则投产年按第0年开始计算
+题目指出第一年是投产年的，则投产年按第1年开始计算</t>
   </si>
 </sst>
 </file>
@@ -4747,6 +5026,43 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right/>
       <top style="thin">
         <color auto="1"/>
@@ -4785,43 +5101,6 @@
         <color auto="1"/>
       </top>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -5092,17 +5371,35 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5123,7 +5420,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5135,25 +5432,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5162,7 +5459,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5171,73 +5468,73 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5646,2328 +5943,2328 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:51">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6"/>
-      <c r="C1" s="10" t="s">
+      <c r="A1" s="12"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11" t="s">
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11" t="s">
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
-      <c r="U1" s="11"/>
-      <c r="V1" s="11" t="s">
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17"/>
+      <c r="V1" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="11"/>
-      <c r="X1" s="11"/>
-      <c r="Y1" s="11"/>
-      <c r="Z1" s="11" t="s">
+      <c r="W1" s="17"/>
+      <c r="X1" s="17"/>
+      <c r="Y1" s="17"/>
+      <c r="Z1" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="11"/>
-      <c r="AB1" s="11"/>
-      <c r="AC1" s="11" t="s">
+      <c r="AA1" s="17"/>
+      <c r="AB1" s="17"/>
+      <c r="AC1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="11"/>
-      <c r="AE1" s="11"/>
-      <c r="AF1" s="11"/>
-      <c r="AG1" s="11"/>
-      <c r="AH1" s="11"/>
-      <c r="AI1" s="11" t="s">
+      <c r="AD1" s="17"/>
+      <c r="AE1" s="17"/>
+      <c r="AF1" s="17"/>
+      <c r="AG1" s="17"/>
+      <c r="AH1" s="17"/>
+      <c r="AI1" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="AJ1" s="11"/>
-      <c r="AK1" s="11"/>
-      <c r="AL1" s="11" t="s">
+      <c r="AJ1" s="17"/>
+      <c r="AK1" s="17"/>
+      <c r="AL1" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="AM1" s="11"/>
-      <c r="AN1" s="11"/>
-      <c r="AO1" s="11"/>
-      <c r="AP1" s="11"/>
-      <c r="AQ1" s="11"/>
-      <c r="AR1" s="11"/>
-      <c r="AS1" s="11" t="s">
+      <c r="AM1" s="17"/>
+      <c r="AN1" s="17"/>
+      <c r="AO1" s="17"/>
+      <c r="AP1" s="17"/>
+      <c r="AQ1" s="17"/>
+      <c r="AR1" s="17"/>
+      <c r="AS1" s="17" t="s">
         <v>8</v>
       </c>
-      <c r="AT1" s="11"/>
-      <c r="AU1" s="11"/>
-      <c r="AV1" s="11" t="s">
+      <c r="AT1" s="17"/>
+      <c r="AU1" s="17"/>
+      <c r="AV1" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="AW1" s="11"/>
-      <c r="AX1" s="11"/>
-      <c r="AY1" s="11"/>
+      <c r="AW1" s="17"/>
+      <c r="AX1" s="17"/>
+      <c r="AY1" s="17"/>
     </row>
     <row r="2" customFormat="1" ht="58" customHeight="1" spans="1:51">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="12" t="s">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-      <c r="I2" s="13"/>
-      <c r="J2" s="14" t="s">
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="15"/>
-      <c r="O2" s="15"/>
-      <c r="P2" s="16" t="s">
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+      <c r="M2" s="21"/>
+      <c r="N2" s="21"/>
+      <c r="O2" s="21"/>
+      <c r="P2" s="22" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="15"/>
-      <c r="R2" s="15"/>
-      <c r="S2" s="15"/>
-      <c r="T2" s="15"/>
-      <c r="U2" s="17"/>
-      <c r="V2" s="16" t="s">
+      <c r="Q2" s="21"/>
+      <c r="R2" s="21"/>
+      <c r="S2" s="21"/>
+      <c r="T2" s="21"/>
+      <c r="U2" s="23"/>
+      <c r="V2" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="W2" s="15"/>
-      <c r="X2" s="15"/>
-      <c r="Y2" s="17"/>
-      <c r="Z2" s="14" t="s">
+      <c r="W2" s="21"/>
+      <c r="X2" s="21"/>
+      <c r="Y2" s="23"/>
+      <c r="Z2" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="15"/>
-      <c r="AB2" s="17"/>
-      <c r="AC2" s="16" t="s">
+      <c r="AA2" s="21"/>
+      <c r="AB2" s="23"/>
+      <c r="AC2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="AD2" s="15"/>
-      <c r="AE2" s="15"/>
-      <c r="AF2" s="15"/>
-      <c r="AG2" s="15"/>
-      <c r="AH2" s="17"/>
-      <c r="AI2" s="16" t="s">
+      <c r="AD2" s="21"/>
+      <c r="AE2" s="21"/>
+      <c r="AF2" s="21"/>
+      <c r="AG2" s="21"/>
+      <c r="AH2" s="23"/>
+      <c r="AI2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="AJ2" s="15"/>
-      <c r="AK2" s="17"/>
-      <c r="AL2" s="16" t="s">
+      <c r="AJ2" s="21"/>
+      <c r="AK2" s="23"/>
+      <c r="AL2" s="22" t="s">
         <v>17</v>
       </c>
-      <c r="AM2" s="15"/>
-      <c r="AN2" s="15"/>
-      <c r="AO2" s="15"/>
-      <c r="AP2" s="15"/>
-      <c r="AQ2" s="15"/>
-      <c r="AR2" s="17"/>
-      <c r="AS2" s="18" t="s">
+      <c r="AM2" s="21"/>
+      <c r="AN2" s="21"/>
+      <c r="AO2" s="21"/>
+      <c r="AP2" s="21"/>
+      <c r="AQ2" s="21"/>
+      <c r="AR2" s="23"/>
+      <c r="AS2" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="AT2" s="19"/>
-      <c r="AU2" s="20"/>
-      <c r="AV2" s="16" t="s">
+      <c r="AT2" s="25"/>
+      <c r="AU2" s="26"/>
+      <c r="AV2" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="AW2" s="15"/>
-      <c r="AX2" s="15"/>
-      <c r="AY2" s="17"/>
+      <c r="AW2" s="21"/>
+      <c r="AX2" s="21"/>
+      <c r="AY2" s="23"/>
     </row>
-    <row r="3" s="8" customFormat="1" spans="1:51">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="22" t="s">
+    <row r="3" s="14" customFormat="1" spans="1:51">
+      <c r="A3" s="27"/>
+      <c r="B3" s="27"/>
+      <c r="C3" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="22" t="s">
+      <c r="I3" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="23" t="s">
+      <c r="J3" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="23" t="s">
+      <c r="K3" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="23" t="s">
+      <c r="L3" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="23" t="s">
+      <c r="M3" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="23" t="s">
+      <c r="N3" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="23" t="s">
+      <c r="O3" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="23" t="s">
+      <c r="P3" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="23" t="s">
+      <c r="Q3" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="R3" s="23" t="s">
+      <c r="R3" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="23" t="s">
+      <c r="S3" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="T3" s="23" t="s">
+      <c r="T3" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="23" t="s">
+      <c r="U3" s="29" t="s">
         <v>38</v>
       </c>
-      <c r="V3" s="23" t="s">
+      <c r="V3" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="W3" s="23" t="s">
+      <c r="W3" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="X3" s="23" t="s">
+      <c r="X3" s="29" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="23" t="s">
+      <c r="Y3" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="Z3" s="23" t="s">
+      <c r="Z3" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="AA3" s="23" t="s">
+      <c r="AA3" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="AB3" s="23" t="s">
+      <c r="AB3" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="AC3" s="23" t="s">
+      <c r="AC3" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="AD3" s="23" t="s">
+      <c r="AD3" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="AE3" s="23" t="s">
+      <c r="AE3" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="AF3" s="23" t="s">
+      <c r="AF3" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="AG3" s="23" t="s">
+      <c r="AG3" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="AH3" s="23" t="s">
+      <c r="AH3" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="AI3" s="23" t="s">
+      <c r="AI3" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="AJ3" s="23" t="s">
+      <c r="AJ3" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="AK3" s="23" t="s">
+      <c r="AK3" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="AL3" s="23" t="s">
+      <c r="AL3" s="29" t="s">
         <v>55</v>
       </c>
-      <c r="AM3" s="23" t="s">
+      <c r="AM3" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="AN3" s="23" t="s">
+      <c r="AN3" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="AO3" s="23" t="s">
+      <c r="AO3" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="AP3" s="23" t="s">
+      <c r="AP3" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="AQ3" s="23" t="s">
+      <c r="AQ3" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="AR3" s="23" t="s">
+      <c r="AR3" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="AS3" s="22" t="s">
+      <c r="AS3" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="AT3" s="22" t="s">
+      <c r="AT3" s="28" t="s">
         <v>63</v>
       </c>
-      <c r="AU3" s="22" t="s">
+      <c r="AU3" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="AV3" s="22" t="s">
+      <c r="AV3" s="28" t="s">
         <v>65</v>
       </c>
-      <c r="AW3" s="22" t="s">
+      <c r="AW3" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="AX3" s="22" t="s">
+      <c r="AX3" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="AY3" s="22" t="s">
+      <c r="AY3" s="28" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" s="8" customFormat="1" ht="81" spans="1:51">
-      <c r="A4" s="21"/>
-      <c r="B4" s="21"/>
-      <c r="C4" s="24" t="s">
+    <row r="4" s="14" customFormat="1" ht="81" spans="1:51">
+      <c r="A4" s="27"/>
+      <c r="B4" s="27"/>
+      <c r="C4" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="D4" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="E4" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="F4" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="G4" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="J4" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="24" t="s">
+      <c r="L4" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="24" t="s">
+      <c r="M4" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="N4" s="24" t="s">
+      <c r="N4" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="O4" s="24" t="s">
+      <c r="O4" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="P4" s="24" t="s">
+      <c r="P4" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="Q4" s="24" t="s">
+      <c r="Q4" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="R4" s="24" t="s">
+      <c r="R4" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="S4" s="24" t="s">
+      <c r="S4" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="T4" s="24" t="s">
+      <c r="T4" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="U4" s="24" t="s">
+      <c r="U4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="V4" s="24" t="s">
+      <c r="V4" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="W4" s="24" t="s">
+      <c r="W4" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="X4" s="24" t="s">
+      <c r="X4" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="Y4" s="24" t="s">
+      <c r="Y4" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="Z4" s="24" t="s">
+      <c r="Z4" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="AA4" s="24" t="s">
+      <c r="AA4" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="AB4" s="24" t="s">
+      <c r="AB4" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="AC4" s="24" t="s">
+      <c r="AC4" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AD4" s="24" t="s">
+      <c r="AD4" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AE4" s="24" t="s">
+      <c r="AE4" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="AF4" s="24" t="s">
+      <c r="AF4" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="AG4" s="24" t="s">
+      <c r="AG4" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="AH4" s="24" t="s">
+      <c r="AH4" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="AI4" s="24" t="s">
+      <c r="AI4" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="AJ4" s="24" t="s">
+      <c r="AJ4" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="AK4" s="24" t="s">
+      <c r="AK4" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="AL4" s="24" t="s">
+      <c r="AL4" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="AM4" s="24" t="s">
+      <c r="AM4" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AN4" s="24" t="s">
+      <c r="AN4" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AO4" s="24" t="s">
+      <c r="AO4" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AP4" s="24" t="s">
+      <c r="AP4" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="AQ4" s="24" t="s">
+      <c r="AQ4" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="AR4" s="24" t="s">
+      <c r="AR4" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="AS4" s="24" t="s">
+      <c r="AS4" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="AT4" s="24" t="s">
+      <c r="AT4" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="AU4" s="24" t="s">
+      <c r="AU4" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="AV4" s="24" t="s">
+      <c r="AV4" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="AW4" s="24" t="s">
+      <c r="AW4" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="AX4" s="24" t="s">
+      <c r="AX4" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="AY4" s="24" t="s">
+      <c r="AY4" s="30" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" s="8" customFormat="1" ht="108" spans="1:51">
-      <c r="A5" s="21"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="24" t="s">
+    <row r="5" s="14" customFormat="1" ht="108" spans="1:51">
+      <c r="A5" s="27"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="D5" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="F5" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="G5" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="I5" s="24" t="s">
+      <c r="I5" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="J5" s="24" t="s">
+      <c r="J5" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="L5" s="24" t="s">
+      <c r="L5" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="M5" s="24" t="s">
+      <c r="M5" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="N5" s="24" t="s">
+      <c r="N5" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="O5" s="24" t="s">
+      <c r="O5" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="P5" s="24" t="s">
+      <c r="P5" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="Q5" s="24" t="s">
+      <c r="Q5" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="R5" s="24" t="s">
+      <c r="R5" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="S5" s="24" t="s">
+      <c r="S5" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="T5" s="24" t="s">
+      <c r="T5" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="U5" s="24" t="s">
+      <c r="U5" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="V5" s="24" t="s">
+      <c r="V5" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="W5" s="24" t="s">
+      <c r="W5" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="X5" s="24" t="s">
+      <c r="X5" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="Y5" s="24" t="s">
+      <c r="Y5" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="Z5" s="24" t="s">
+      <c r="Z5" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="AA5" s="24" t="s">
+      <c r="AA5" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="AB5" s="24" t="s">
+      <c r="AB5" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="AC5" s="24" t="s">
+      <c r="AC5" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="AD5" s="24" t="s">
+      <c r="AD5" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="AE5" s="24" t="s">
+      <c r="AE5" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="AF5" s="24" t="s">
+      <c r="AF5" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="AG5" s="24" t="s">
+      <c r="AG5" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="AH5" s="24" t="s">
+      <c r="AH5" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="AI5" s="24" t="s">
+      <c r="AI5" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="AJ5" s="24" t="s">
+      <c r="AJ5" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="AK5" s="24" t="s">
+      <c r="AK5" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="AL5" s="24" t="s">
+      <c r="AL5" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="AM5" s="24" t="s">
+      <c r="AM5" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="AN5" s="24" t="s">
+      <c r="AN5" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="AO5" s="24" t="s">
+      <c r="AO5" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="AP5" s="24" t="s">
+      <c r="AP5" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="AQ5" s="24" t="s">
+      <c r="AQ5" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="AR5" s="24" t="s">
+      <c r="AR5" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="AS5" s="24" t="s">
+      <c r="AS5" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="AT5" s="24" t="s">
+      <c r="AT5" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="AU5" s="24" t="s">
+      <c r="AU5" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="AV5" s="24" t="s">
+      <c r="AV5" s="30" t="s">
         <v>163</v>
       </c>
-      <c r="AW5" s="24" t="s">
+      <c r="AW5" s="30" t="s">
         <v>164</v>
       </c>
-      <c r="AX5" s="24" t="s">
+      <c r="AX5" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="AY5" s="24" t="s">
+      <c r="AY5" s="30" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="6" s="8" customFormat="1" ht="27" spans="1:51">
-      <c r="A6" s="21"/>
-      <c r="B6" s="21"/>
-      <c r="C6" s="25" t="s">
+    <row r="6" s="14" customFormat="1" ht="27" spans="1:51">
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="25" t="s">
+      <c r="D6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="E6" s="25" t="s">
+      <c r="E6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="H6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="I6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="J6" s="25" t="s">
+      <c r="J6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="K6" s="25" t="s">
+      <c r="K6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="L6" s="25" t="s">
+      <c r="L6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="M6" s="25" t="s">
+      <c r="M6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="N6" s="25" t="s">
+      <c r="N6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="O6" s="25" t="s">
+      <c r="O6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="P6" s="25" t="s">
+      <c r="P6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="Q6" s="25" t="s">
+      <c r="Q6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="R6" s="25" t="s">
+      <c r="R6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="S6" s="25" t="s">
+      <c r="S6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="T6" s="25" t="s">
+      <c r="T6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="U6" s="25" t="s">
+      <c r="U6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="V6" s="24" t="s">
+      <c r="V6" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="W6" s="25" t="s">
+      <c r="W6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="X6" s="25" t="s">
+      <c r="X6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="Y6" s="25" t="s">
+      <c r="Y6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="Z6" s="25" t="s">
+      <c r="Z6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AA6" s="25" t="s">
+      <c r="AA6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AB6" s="25" t="s">
+      <c r="AB6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AC6" s="25" t="s">
+      <c r="AC6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AD6" s="25" t="s">
+      <c r="AD6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AE6" s="25" t="s">
+      <c r="AE6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AF6" s="25" t="s">
+      <c r="AF6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AG6" s="25" t="s">
+      <c r="AG6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AH6" s="25" t="s">
+      <c r="AH6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AI6" s="25" t="s">
+      <c r="AI6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AJ6" s="25" t="s">
+      <c r="AJ6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AK6" s="25" t="s">
+      <c r="AK6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AL6" s="25" t="s">
+      <c r="AL6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AM6" s="25" t="s">
+      <c r="AM6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AN6" s="25" t="s">
+      <c r="AN6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AO6" s="25" t="s">
+      <c r="AO6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AP6" s="25" t="s">
+      <c r="AP6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AQ6" s="25" t="s">
+      <c r="AQ6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AR6" s="25" t="s">
+      <c r="AR6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AS6" s="25" t="s">
+      <c r="AS6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AT6" s="25" t="s">
+      <c r="AT6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AU6" s="25" t="s">
+      <c r="AU6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AV6" s="25" t="s">
+      <c r="AV6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AW6" s="25" t="s">
+      <c r="AW6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AX6" s="25" t="s">
+      <c r="AX6" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="AY6" s="25" t="s">
+      <c r="AY6" s="31" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="7" s="8" customFormat="1" ht="54" spans="1:51">
-      <c r="A7" s="26" t="s">
+    <row r="7" s="14" customFormat="1" ht="54" spans="1:51">
+      <c r="A7" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="25" t="s">
+      <c r="B7" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="E7" s="25" t="s">
+      <c r="E7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="F7" s="25" t="s">
+      <c r="F7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="G7" s="25" t="s">
+      <c r="G7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="H7" s="25" t="s">
+      <c r="H7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="I7" s="25" t="s">
+      <c r="I7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="J7" s="25" t="s">
+      <c r="J7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="K7" s="25" t="s">
+      <c r="K7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="L7" s="25" t="s">
+      <c r="L7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="M7" s="25" t="s">
+      <c r="M7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="N7" s="25" t="s">
+      <c r="N7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="O7" s="25" t="s">
+      <c r="O7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="P7" s="25" t="s">
+      <c r="P7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="Q7" s="25" t="s">
+      <c r="Q7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="R7" s="25" t="s">
+      <c r="R7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="S7" s="25" t="s">
+      <c r="S7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="T7" s="25" t="s">
+      <c r="T7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="U7" s="25" t="s">
+      <c r="U7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="V7" s="24" t="s">
+      <c r="V7" s="30" t="s">
         <v>172</v>
       </c>
-      <c r="W7" s="25" t="s">
+      <c r="W7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="X7" s="25" t="s">
+      <c r="X7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="Y7" s="25" t="s">
+      <c r="Y7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="Z7" s="25" t="s">
+      <c r="Z7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AA7" s="25" t="s">
+      <c r="AA7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AB7" s="25" t="s">
+      <c r="AB7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AC7" s="25" t="s">
+      <c r="AC7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AD7" s="25" t="s">
+      <c r="AD7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AE7" s="25" t="s">
+      <c r="AE7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AF7" s="25" t="s">
+      <c r="AF7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AG7" s="25" t="s">
+      <c r="AG7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AH7" s="25" t="s">
+      <c r="AH7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AI7" s="25" t="s">
+      <c r="AI7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AJ7" s="25" t="s">
+      <c r="AJ7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AK7" s="25" t="s">
+      <c r="AK7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AL7" s="25" t="s">
+      <c r="AL7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AM7" s="25" t="s">
+      <c r="AM7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AN7" s="25" t="s">
+      <c r="AN7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AO7" s="25" t="s">
+      <c r="AO7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AP7" s="25" t="s">
+      <c r="AP7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AQ7" s="25" t="s">
+      <c r="AQ7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AR7" s="25" t="s">
+      <c r="AR7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AS7" s="25" t="s">
+      <c r="AS7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AT7" s="25" t="s">
+      <c r="AT7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AU7" s="25" t="s">
+      <c r="AU7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AV7" s="25" t="s">
+      <c r="AV7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AW7" s="25" t="s">
+      <c r="AW7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AX7" s="25" t="s">
+      <c r="AX7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="AY7" s="25" t="s">
+      <c r="AY7" s="31" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="8" ht="67.5" spans="1:51">
-      <c r="A8" s="28"/>
-      <c r="B8" s="29" t="s">
+      <c r="A8" s="34"/>
+      <c r="B8" s="35" t="s">
         <v>173</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="36" t="s">
         <v>174</v>
       </c>
-      <c r="D8" s="30" t="s">
+      <c r="D8" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="E8" s="30" t="s">
+      <c r="E8" s="36" t="s">
         <v>176</v>
       </c>
-      <c r="F8" s="30" t="s">
+      <c r="F8" s="36" t="s">
         <v>177</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="36" t="s">
         <v>178</v>
       </c>
-      <c r="H8" s="30" t="s">
+      <c r="H8" s="36" t="s">
         <v>179</v>
       </c>
-      <c r="I8" s="30" t="s">
+      <c r="I8" s="36" t="s">
         <v>180</v>
       </c>
-      <c r="J8" s="30" t="s">
+      <c r="J8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="K8" s="30" t="s">
+      <c r="K8" s="36" t="s">
         <v>182</v>
       </c>
-      <c r="L8" s="30" t="s">
+      <c r="L8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="M8" s="30" t="s">
+      <c r="M8" s="36" t="s">
         <v>183</v>
       </c>
-      <c r="N8" s="30" t="s">
+      <c r="N8" s="36" t="s">
         <v>184</v>
       </c>
-      <c r="O8" s="30" t="s">
+      <c r="O8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="P8" s="30" t="s">
+      <c r="P8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="Q8" s="30" t="s">
+      <c r="Q8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="R8" s="30" t="s">
+      <c r="R8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="S8" s="30" t="s">
+      <c r="S8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="T8" s="30" t="s">
+      <c r="T8" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="U8" s="30" t="s">
+      <c r="U8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="V8" s="30" t="s">
+      <c r="V8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="W8" s="30" t="s">
+      <c r="W8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="X8" s="30" t="s">
+      <c r="X8" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="Y8" s="30" t="s">
+      <c r="Y8" s="36" t="s">
         <v>187</v>
       </c>
-      <c r="Z8" s="30" t="s">
+      <c r="Z8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AA8" s="30" t="s">
+      <c r="AA8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AB8" s="30" t="s">
+      <c r="AB8" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="AC8" s="30" t="s">
+      <c r="AC8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AD8" s="30" t="s">
+      <c r="AD8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AE8" s="30" t="s">
+      <c r="AE8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AF8" s="30" t="s">
+      <c r="AF8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AG8" s="30" t="s">
+      <c r="AG8" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="AH8" s="30" t="s">
+      <c r="AH8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AI8" s="30" t="s">
+      <c r="AI8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AJ8" s="30" t="s">
+      <c r="AJ8" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="AK8" s="30" t="s">
+      <c r="AK8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AL8" s="30" t="s">
+      <c r="AL8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AM8" s="30" t="s">
+      <c r="AM8" s="36" t="s">
         <v>191</v>
       </c>
-      <c r="AN8" s="30" t="s">
+      <c r="AN8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AO8" s="30" t="s">
+      <c r="AO8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AP8" s="30" t="s">
+      <c r="AP8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AQ8" s="30" t="s">
+      <c r="AQ8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AR8" s="30" t="s">
+      <c r="AR8" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="AS8" s="31" t="s">
+      <c r="AS8" s="37" t="s">
         <v>192</v>
       </c>
-      <c r="AT8" s="31" t="s">
+      <c r="AT8" s="37" t="s">
         <v>193</v>
       </c>
-      <c r="AU8" s="31" t="s">
+      <c r="AU8" s="37" t="s">
         <v>194</v>
       </c>
-      <c r="AV8" s="31" t="s">
+      <c r="AV8" s="37" t="s">
         <v>195</v>
       </c>
-      <c r="AW8" s="31" t="s">
+      <c r="AW8" s="37" t="s">
         <v>185</v>
       </c>
-      <c r="AX8" s="32" t="s">
+      <c r="AX8" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="AY8" s="32" t="s">
+      <c r="AY8" s="38" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="9" ht="40.5" spans="1:51">
-      <c r="A9" s="28"/>
-      <c r="B9" s="33" t="s">
+      <c r="A9" s="34"/>
+      <c r="B9" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31" t="s">
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37" t="s">
         <v>197</v>
       </c>
-      <c r="L9" s="31"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31" t="s">
+      <c r="L9" s="37"/>
+      <c r="M9" s="37"/>
+      <c r="N9" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="O9" s="31"/>
-      <c r="P9" s="31"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="31"/>
-      <c r="T9" s="31"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="31"/>
-      <c r="W9" s="31"/>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="31"/>
-      <c r="Z9" s="31"/>
-      <c r="AA9" s="31"/>
-      <c r="AB9" s="31"/>
-      <c r="AC9" s="31"/>
-      <c r="AD9" s="31"/>
-      <c r="AE9" s="31"/>
-      <c r="AF9" s="31"/>
-      <c r="AG9" s="31"/>
-      <c r="AH9" s="31"/>
-      <c r="AI9" s="31"/>
-      <c r="AJ9" s="31"/>
-      <c r="AK9" s="31"/>
-      <c r="AL9" s="31"/>
-      <c r="AM9" s="31"/>
-      <c r="AN9" s="31"/>
-      <c r="AO9" s="31"/>
-      <c r="AP9" s="31"/>
-      <c r="AQ9" s="31"/>
-      <c r="AR9" s="31"/>
-      <c r="AS9" s="31"/>
-      <c r="AT9" s="31"/>
-      <c r="AU9" s="31"/>
-      <c r="AV9" s="31"/>
-      <c r="AW9" s="31"/>
-      <c r="AX9" s="32"/>
-      <c r="AY9" s="32"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="37"/>
+      <c r="T9" s="37"/>
+      <c r="U9" s="37"/>
+      <c r="V9" s="37"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="37"/>
+      <c r="Y9" s="37"/>
+      <c r="Z9" s="37"/>
+      <c r="AA9" s="37"/>
+      <c r="AB9" s="37"/>
+      <c r="AC9" s="37"/>
+      <c r="AD9" s="37"/>
+      <c r="AE9" s="37"/>
+      <c r="AF9" s="37"/>
+      <c r="AG9" s="37"/>
+      <c r="AH9" s="37"/>
+      <c r="AI9" s="37"/>
+      <c r="AJ9" s="37"/>
+      <c r="AK9" s="37"/>
+      <c r="AL9" s="37"/>
+      <c r="AM9" s="37"/>
+      <c r="AN9" s="37"/>
+      <c r="AO9" s="37"/>
+      <c r="AP9" s="37"/>
+      <c r="AQ9" s="37"/>
+      <c r="AR9" s="37"/>
+      <c r="AS9" s="37"/>
+      <c r="AT9" s="37"/>
+      <c r="AU9" s="37"/>
+      <c r="AV9" s="37"/>
+      <c r="AW9" s="37"/>
+      <c r="AX9" s="38"/>
+      <c r="AY9" s="38"/>
     </row>
     <row r="10" ht="81" spans="1:51">
-      <c r="A10" s="34"/>
-      <c r="B10" s="33" t="s">
+      <c r="A10" s="40"/>
+      <c r="B10" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31" t="s">
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="37"/>
+      <c r="G10" s="37"/>
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="L10" s="31" t="s">
+      <c r="L10" s="37" t="s">
         <v>201</v>
       </c>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31" t="s">
+      <c r="M10" s="37"/>
+      <c r="N10" s="37" t="s">
         <v>202</v>
       </c>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="31"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="31"/>
-      <c r="W10" s="31"/>
-      <c r="X10" s="31"/>
-      <c r="Y10" s="31"/>
-      <c r="Z10" s="31"/>
-      <c r="AA10" s="31" t="s">
+      <c r="O10" s="37"/>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="37"/>
+      <c r="R10" s="37"/>
+      <c r="S10" s="37"/>
+      <c r="T10" s="37"/>
+      <c r="U10" s="37"/>
+      <c r="V10" s="37"/>
+      <c r="W10" s="37"/>
+      <c r="X10" s="37"/>
+      <c r="Y10" s="37"/>
+      <c r="Z10" s="37"/>
+      <c r="AA10" s="37" t="s">
         <v>203</v>
       </c>
-      <c r="AB10" s="31"/>
-      <c r="AC10" s="31"/>
-      <c r="AD10" s="31"/>
-      <c r="AE10" s="31"/>
-      <c r="AF10" s="31"/>
-      <c r="AG10" s="31"/>
-      <c r="AH10" s="31"/>
-      <c r="AI10" s="31"/>
-      <c r="AJ10" s="31" t="s">
+      <c r="AB10" s="37"/>
+      <c r="AC10" s="37"/>
+      <c r="AD10" s="37"/>
+      <c r="AE10" s="37"/>
+      <c r="AF10" s="37"/>
+      <c r="AG10" s="37"/>
+      <c r="AH10" s="37"/>
+      <c r="AI10" s="37"/>
+      <c r="AJ10" s="37" t="s">
         <v>204</v>
       </c>
-      <c r="AK10" s="31"/>
-      <c r="AL10" s="31"/>
-      <c r="AM10" s="31"/>
-      <c r="AN10" s="31"/>
-      <c r="AO10" s="31"/>
-      <c r="AP10" s="31"/>
-      <c r="AQ10" s="31"/>
-      <c r="AR10" s="31"/>
-      <c r="AS10" s="31"/>
-      <c r="AT10" s="31"/>
-      <c r="AU10" s="31"/>
-      <c r="AV10" s="31"/>
-      <c r="AW10" s="31"/>
-      <c r="AX10" s="32"/>
-      <c r="AY10" s="32"/>
+      <c r="AK10" s="37"/>
+      <c r="AL10" s="37"/>
+      <c r="AM10" s="37"/>
+      <c r="AN10" s="37"/>
+      <c r="AO10" s="37"/>
+      <c r="AP10" s="37"/>
+      <c r="AQ10" s="37"/>
+      <c r="AR10" s="37"/>
+      <c r="AS10" s="37"/>
+      <c r="AT10" s="37"/>
+      <c r="AU10" s="37"/>
+      <c r="AV10" s="37"/>
+      <c r="AW10" s="37"/>
+      <c r="AX10" s="38"/>
+      <c r="AY10" s="38"/>
     </row>
     <row r="11" spans="1:51">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="41" t="s">
         <v>205</v>
       </c>
-      <c r="B11" s="36" t="s">
+      <c r="B11" s="42" t="s">
         <v>206</v>
       </c>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="9"/>
-      <c r="R11" s="9"/>
-      <c r="S11" s="9"/>
-      <c r="T11" s="9"/>
-      <c r="U11" s="9"/>
-      <c r="V11" s="9"/>
-      <c r="W11" s="9"/>
-      <c r="X11" s="9"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="9"/>
-      <c r="AA11" s="9"/>
-      <c r="AB11" s="9"/>
-      <c r="AC11" s="9"/>
-      <c r="AD11" s="9"/>
-      <c r="AE11" s="9"/>
-      <c r="AF11" s="9"/>
-      <c r="AG11" s="9"/>
-      <c r="AH11" s="9"/>
-      <c r="AI11" s="9"/>
-      <c r="AJ11" s="9"/>
-      <c r="AK11" s="9"/>
-      <c r="AL11" s="9"/>
-      <c r="AM11" s="9"/>
-      <c r="AN11" s="9"/>
-      <c r="AO11" s="9"/>
-      <c r="AP11" s="9"/>
-      <c r="AQ11" s="9"/>
-      <c r="AR11" s="9"/>
-      <c r="AS11" s="9"/>
-      <c r="AT11" s="9"/>
-      <c r="AU11" s="9"/>
-      <c r="AV11" s="9"/>
-      <c r="AW11" s="9"/>
-      <c r="AX11" s="9"/>
-      <c r="AY11" s="9"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="15"/>
+      <c r="O11" s="15"/>
+      <c r="P11" s="15"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+      <c r="S11" s="15"/>
+      <c r="T11" s="15"/>
+      <c r="U11" s="15"/>
+      <c r="V11" s="15"/>
+      <c r="W11" s="15"/>
+      <c r="X11" s="15"/>
+      <c r="Y11" s="15"/>
+      <c r="Z11" s="15"/>
+      <c r="AA11" s="15"/>
+      <c r="AB11" s="15"/>
+      <c r="AC11" s="15"/>
+      <c r="AD11" s="15"/>
+      <c r="AE11" s="15"/>
+      <c r="AF11" s="15"/>
+      <c r="AG11" s="15"/>
+      <c r="AH11" s="15"/>
+      <c r="AI11" s="15"/>
+      <c r="AJ11" s="15"/>
+      <c r="AK11" s="15"/>
+      <c r="AL11" s="15"/>
+      <c r="AM11" s="15"/>
+      <c r="AN11" s="15"/>
+      <c r="AO11" s="15"/>
+      <c r="AP11" s="15"/>
+      <c r="AQ11" s="15"/>
+      <c r="AR11" s="15"/>
+      <c r="AS11" s="15"/>
+      <c r="AT11" s="15"/>
+      <c r="AU11" s="15"/>
+      <c r="AV11" s="15"/>
+      <c r="AW11" s="15"/>
+      <c r="AX11" s="15"/>
+      <c r="AY11" s="15"/>
     </row>
     <row r="12" spans="1:51">
-      <c r="A12" s="35" t="s">
+      <c r="A12" s="41" t="s">
         <v>207</v>
       </c>
-      <c r="B12" s="37" t="s">
+      <c r="B12" s="43" t="s">
         <v>208</v>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="9"/>
-      <c r="R12" s="9"/>
-      <c r="S12" s="9"/>
-      <c r="T12" s="9"/>
-      <c r="U12" s="9"/>
-      <c r="V12" s="9"/>
-      <c r="W12" s="9"/>
-      <c r="X12" s="9"/>
-      <c r="Y12" s="9"/>
-      <c r="Z12" s="9"/>
-      <c r="AA12" s="9"/>
-      <c r="AB12" s="9"/>
-      <c r="AC12" s="9"/>
-      <c r="AD12" s="9"/>
-      <c r="AE12" s="9"/>
-      <c r="AF12" s="9"/>
-      <c r="AG12" s="9"/>
-      <c r="AH12" s="9"/>
-      <c r="AI12" s="9"/>
-      <c r="AJ12" s="9"/>
-      <c r="AK12" s="9"/>
-      <c r="AL12" s="9"/>
-      <c r="AM12" s="9"/>
-      <c r="AN12" s="9"/>
-      <c r="AO12" s="9"/>
-      <c r="AP12" s="9"/>
-      <c r="AQ12" s="9"/>
-      <c r="AR12" s="9"/>
-      <c r="AS12" s="9"/>
-      <c r="AT12" s="9"/>
-      <c r="AU12" s="9"/>
-      <c r="AV12" s="9"/>
-      <c r="AW12" s="9"/>
-      <c r="AX12" s="9"/>
-      <c r="AY12" s="9"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15"/>
+      <c r="R12" s="15"/>
+      <c r="S12" s="15"/>
+      <c r="T12" s="15"/>
+      <c r="U12" s="15"/>
+      <c r="V12" s="15"/>
+      <c r="W12" s="15"/>
+      <c r="X12" s="15"/>
+      <c r="Y12" s="15"/>
+      <c r="Z12" s="15"/>
+      <c r="AA12" s="15"/>
+      <c r="AB12" s="15"/>
+      <c r="AC12" s="15"/>
+      <c r="AD12" s="15"/>
+      <c r="AE12" s="15"/>
+      <c r="AF12" s="15"/>
+      <c r="AG12" s="15"/>
+      <c r="AH12" s="15"/>
+      <c r="AI12" s="15"/>
+      <c r="AJ12" s="15"/>
+      <c r="AK12" s="15"/>
+      <c r="AL12" s="15"/>
+      <c r="AM12" s="15"/>
+      <c r="AN12" s="15"/>
+      <c r="AO12" s="15"/>
+      <c r="AP12" s="15"/>
+      <c r="AQ12" s="15"/>
+      <c r="AR12" s="15"/>
+      <c r="AS12" s="15"/>
+      <c r="AT12" s="15"/>
+      <c r="AU12" s="15"/>
+      <c r="AV12" s="15"/>
+      <c r="AW12" s="15"/>
+      <c r="AX12" s="15"/>
+      <c r="AY12" s="15"/>
     </row>
     <row r="14" ht="94.5" spans="1:51">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="B14" s="39" t="s">
+      <c r="B14" s="45" t="s">
         <v>210</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41" t="s">
+      <c r="C14" s="46"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47" t="s">
         <v>211</v>
       </c>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41" t="s">
+      <c r="G14" s="47"/>
+      <c r="H14" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="I14" s="41"/>
-      <c r="J14" s="41"/>
-      <c r="K14" s="41" t="s">
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47" t="s">
         <v>213</v>
       </c>
-      <c r="L14" s="41" t="s">
+      <c r="L14" s="47" t="s">
         <v>214</v>
       </c>
-      <c r="M14" s="41" t="s">
+      <c r="M14" s="47" t="s">
         <v>215</v>
       </c>
-      <c r="N14" s="41" t="s">
+      <c r="N14" s="47" t="s">
         <v>216</v>
       </c>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41" t="s">
+      <c r="O14" s="47"/>
+      <c r="P14" s="47"/>
+      <c r="Q14" s="47" t="s">
         <v>217</v>
       </c>
-      <c r="R14" s="41" t="s">
+      <c r="R14" s="47" t="s">
         <v>218</v>
       </c>
-      <c r="S14" s="41" t="s">
+      <c r="S14" s="47" t="s">
         <v>219</v>
       </c>
-      <c r="T14" s="41" t="s">
+      <c r="T14" s="47" t="s">
         <v>220</v>
       </c>
-      <c r="U14" s="41" t="s">
+      <c r="U14" s="47" t="s">
         <v>221</v>
       </c>
-      <c r="V14" s="41"/>
-      <c r="W14" s="41" t="s">
+      <c r="V14" s="47"/>
+      <c r="W14" s="47" t="s">
         <v>219</v>
       </c>
-      <c r="X14" s="41" t="s">
+      <c r="X14" s="47" t="s">
         <v>222</v>
       </c>
-      <c r="Y14" s="41" t="s">
+      <c r="Y14" s="47" t="s">
         <v>223</v>
       </c>
-      <c r="Z14" s="41" t="s">
+      <c r="Z14" s="47" t="s">
         <v>224</v>
       </c>
-      <c r="AA14" s="41" t="s">
+      <c r="AA14" s="47" t="s">
         <v>225</v>
       </c>
-      <c r="AB14" s="41" t="s">
+      <c r="AB14" s="47" t="s">
         <v>226</v>
       </c>
-      <c r="AC14" s="41" t="s">
+      <c r="AC14" s="47" t="s">
         <v>227</v>
       </c>
-      <c r="AD14" s="41" t="s">
+      <c r="AD14" s="47" t="s">
         <v>228</v>
       </c>
-      <c r="AE14" s="41" t="s">
+      <c r="AE14" s="47" t="s">
         <v>229</v>
       </c>
-      <c r="AF14" s="41" t="s">
+      <c r="AF14" s="47" t="s">
         <v>230</v>
       </c>
-      <c r="AG14" s="41"/>
-      <c r="AH14" s="41" t="s">
+      <c r="AG14" s="47"/>
+      <c r="AH14" s="47" t="s">
         <v>231</v>
       </c>
-      <c r="AI14" s="41" t="s">
+      <c r="AI14" s="47" t="s">
         <v>232</v>
       </c>
-      <c r="AJ14" s="41" t="s">
+      <c r="AJ14" s="47" t="s">
         <v>233</v>
       </c>
-      <c r="AK14" s="41"/>
-      <c r="AL14" s="41"/>
-      <c r="AM14" s="41" t="s">
+      <c r="AK14" s="47"/>
+      <c r="AL14" s="47"/>
+      <c r="AM14" s="47" t="s">
         <v>234</v>
       </c>
-      <c r="AN14" s="41" t="s">
+      <c r="AN14" s="47" t="s">
         <v>235</v>
       </c>
-      <c r="AO14" s="41" t="s">
+      <c r="AO14" s="47" t="s">
         <v>236</v>
       </c>
-      <c r="AP14" s="41" t="s">
+      <c r="AP14" s="47" t="s">
         <v>237</v>
       </c>
-      <c r="AQ14" s="41"/>
-      <c r="AR14" s="41" t="s">
+      <c r="AQ14" s="47"/>
+      <c r="AR14" s="47" t="s">
         <v>238</v>
       </c>
-      <c r="AS14" s="42" t="s">
+      <c r="AS14" s="48" t="s">
         <v>239</v>
       </c>
-      <c r="AT14" s="41" t="s">
+      <c r="AT14" s="47" t="s">
         <v>240</v>
       </c>
-      <c r="AU14" s="41" t="s">
+      <c r="AU14" s="47" t="s">
         <v>241</v>
       </c>
-      <c r="AV14" s="32"/>
-      <c r="AW14" s="32"/>
-      <c r="AX14" s="31" t="s">
+      <c r="AV14" s="38"/>
+      <c r="AW14" s="38"/>
+      <c r="AX14" s="37" t="s">
         <v>242</v>
       </c>
-      <c r="AY14" s="31"/>
+      <c r="AY14" s="37"/>
     </row>
     <row r="15" spans="1:51">
-      <c r="A15" s="43"/>
-      <c r="B15" s="44" t="s">
+      <c r="A15" s="49"/>
+      <c r="B15" s="50" t="s">
         <v>243</v>
       </c>
-      <c r="C15" s="45"/>
-      <c r="D15" s="37"/>
-      <c r="E15" s="37"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="37"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="37"/>
-      <c r="K15" s="37"/>
-      <c r="L15" s="37"/>
-      <c r="M15" s="37"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="37"/>
-      <c r="P15" s="37"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="37"/>
-      <c r="S15" s="37"/>
-      <c r="T15" s="37"/>
-      <c r="U15" s="37"/>
-      <c r="V15" s="37"/>
-      <c r="W15" s="37"/>
-      <c r="X15" s="37"/>
-      <c r="Y15" s="37"/>
-      <c r="Z15" s="37"/>
-      <c r="AA15" s="37"/>
-      <c r="AB15" s="37"/>
-      <c r="AC15" s="37"/>
-      <c r="AD15" s="37"/>
-      <c r="AE15" s="37"/>
-      <c r="AF15" s="37"/>
-      <c r="AG15" s="37"/>
-      <c r="AH15" s="37"/>
-      <c r="AI15" s="37"/>
-      <c r="AJ15" s="37"/>
-      <c r="AK15" s="37"/>
-      <c r="AL15" s="37"/>
-      <c r="AM15" s="37"/>
-      <c r="AN15" s="37"/>
-      <c r="AO15" s="37"/>
-      <c r="AP15" s="37"/>
-      <c r="AQ15" s="37"/>
-      <c r="AR15" s="37"/>
-      <c r="AS15" s="37"/>
-      <c r="AT15" s="37"/>
-      <c r="AU15" s="37"/>
-      <c r="AV15" s="37"/>
-      <c r="AW15" s="37"/>
-      <c r="AX15" s="37"/>
-      <c r="AY15" s="37"/>
+      <c r="C15" s="51"/>
+      <c r="D15" s="43"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="43"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="43"/>
+      <c r="K15" s="43"/>
+      <c r="L15" s="43"/>
+      <c r="M15" s="43"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="43"/>
+      <c r="U15" s="43"/>
+      <c r="V15" s="43"/>
+      <c r="W15" s="43"/>
+      <c r="X15" s="43"/>
+      <c r="Y15" s="43"/>
+      <c r="Z15" s="43"/>
+      <c r="AA15" s="43"/>
+      <c r="AB15" s="43"/>
+      <c r="AC15" s="43"/>
+      <c r="AD15" s="43"/>
+      <c r="AE15" s="43"/>
+      <c r="AF15" s="43"/>
+      <c r="AG15" s="43"/>
+      <c r="AH15" s="43"/>
+      <c r="AI15" s="43"/>
+      <c r="AJ15" s="43"/>
+      <c r="AK15" s="43"/>
+      <c r="AL15" s="43"/>
+      <c r="AM15" s="43"/>
+      <c r="AN15" s="43"/>
+      <c r="AO15" s="43"/>
+      <c r="AP15" s="43"/>
+      <c r="AQ15" s="43"/>
+      <c r="AR15" s="43"/>
+      <c r="AS15" s="43"/>
+      <c r="AT15" s="43"/>
+      <c r="AU15" s="43"/>
+      <c r="AV15" s="43"/>
+      <c r="AW15" s="43"/>
+      <c r="AX15" s="43"/>
+      <c r="AY15" s="43"/>
     </row>
     <row r="16" ht="67.5" spans="1:51">
-      <c r="A16" s="43"/>
-      <c r="B16" s="44" t="s">
+      <c r="A16" s="49"/>
+      <c r="B16" s="50" t="s">
         <v>244</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="52" t="s">
         <v>245</v>
       </c>
-      <c r="D16" s="47" t="s">
+      <c r="D16" s="53" t="s">
         <v>246</v>
       </c>
-      <c r="E16" s="37"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-      <c r="K16" s="47" t="s">
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="43"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="53" t="s">
         <v>247</v>
       </c>
-      <c r="L16" s="37"/>
-      <c r="M16" s="37"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="37"/>
-      <c r="P16" s="37"/>
-      <c r="Q16" s="37"/>
-      <c r="R16" s="37"/>
-      <c r="S16" s="37"/>
-      <c r="T16" s="37"/>
-      <c r="U16" s="37"/>
-      <c r="V16" s="37"/>
-      <c r="W16" s="37"/>
-      <c r="X16" s="37"/>
-      <c r="Y16" s="37"/>
-      <c r="Z16" s="47" t="s">
+      <c r="L16" s="43"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="43"/>
+      <c r="U16" s="43"/>
+      <c r="V16" s="43"/>
+      <c r="W16" s="43"/>
+      <c r="X16" s="43"/>
+      <c r="Y16" s="43"/>
+      <c r="Z16" s="53" t="s">
         <v>248</v>
       </c>
-      <c r="AA16" s="37" t="s">
+      <c r="AA16" s="43" t="s">
         <v>249</v>
       </c>
-      <c r="AB16" s="47" t="s">
+      <c r="AB16" s="53" t="s">
         <v>250</v>
       </c>
-      <c r="AC16" s="37"/>
-      <c r="AD16" s="37"/>
-      <c r="AE16" s="37"/>
-      <c r="AF16" s="37"/>
-      <c r="AG16" s="37"/>
-      <c r="AH16" s="37"/>
-      <c r="AI16" s="37"/>
-      <c r="AJ16" s="37"/>
-      <c r="AK16" s="37"/>
-      <c r="AL16" s="37"/>
-      <c r="AM16" s="47" t="s">
+      <c r="AC16" s="43"/>
+      <c r="AD16" s="43"/>
+      <c r="AE16" s="43"/>
+      <c r="AF16" s="43"/>
+      <c r="AG16" s="43"/>
+      <c r="AH16" s="43"/>
+      <c r="AI16" s="43"/>
+      <c r="AJ16" s="43"/>
+      <c r="AK16" s="43"/>
+      <c r="AL16" s="43"/>
+      <c r="AM16" s="53" t="s">
         <v>251</v>
       </c>
-      <c r="AN16" s="37"/>
-      <c r="AO16" s="37" t="s">
+      <c r="AN16" s="43"/>
+      <c r="AO16" s="43" t="s">
         <v>252</v>
       </c>
-      <c r="AP16" s="37" t="s">
+      <c r="AP16" s="43" t="s">
         <v>252</v>
       </c>
-      <c r="AQ16" s="37"/>
-      <c r="AR16" s="37"/>
-      <c r="AS16" s="37" t="s">
+      <c r="AQ16" s="43"/>
+      <c r="AR16" s="43"/>
+      <c r="AS16" s="43" t="s">
         <v>253</v>
       </c>
-      <c r="AT16" s="37"/>
-      <c r="AU16" s="37"/>
-      <c r="AV16" s="47" t="s">
+      <c r="AT16" s="43"/>
+      <c r="AU16" s="43"/>
+      <c r="AV16" s="53" t="s">
         <v>254</v>
       </c>
-      <c r="AW16" s="37"/>
-      <c r="AX16" s="37"/>
-      <c r="AY16" s="37"/>
+      <c r="AW16" s="43"/>
+      <c r="AX16" s="43"/>
+      <c r="AY16" s="43"/>
     </row>
     <row r="17" ht="81" spans="1:51">
-      <c r="A17" s="43"/>
-      <c r="B17" s="44" t="s">
+      <c r="A17" s="49"/>
+      <c r="B17" s="50" t="s">
         <v>255</v>
       </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="37"/>
-      <c r="E17" s="37"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="47" t="s">
+      <c r="C17" s="51"/>
+      <c r="D17" s="43"/>
+      <c r="E17" s="43"/>
+      <c r="F17" s="43"/>
+      <c r="G17" s="53" t="s">
         <v>256</v>
       </c>
-      <c r="H17" s="37"/>
-      <c r="I17" s="47" t="s">
+      <c r="H17" s="43"/>
+      <c r="I17" s="53" t="s">
         <v>257</v>
       </c>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37" t="s">
+      <c r="J17" s="43"/>
+      <c r="K17" s="43" t="s">
         <v>258</v>
       </c>
-      <c r="L17" s="37" t="s">
+      <c r="L17" s="43" t="s">
         <v>259</v>
       </c>
-      <c r="M17" s="37"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="47" t="s">
+      <c r="M17" s="43"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="53" t="s">
         <v>260</v>
       </c>
-      <c r="P17" s="37"/>
-      <c r="Q17" s="37"/>
-      <c r="R17" s="37"/>
-      <c r="S17" s="47" t="s">
+      <c r="P17" s="43"/>
+      <c r="Q17" s="43"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="53" t="s">
         <v>261</v>
       </c>
-      <c r="T17" s="47" t="s">
+      <c r="T17" s="53" t="s">
         <v>262</v>
       </c>
-      <c r="U17" s="47" t="s">
+      <c r="U17" s="53" t="s">
         <v>263</v>
       </c>
-      <c r="V17" s="37"/>
-      <c r="W17" s="47" t="s">
+      <c r="V17" s="43"/>
+      <c r="W17" s="53" t="s">
         <v>264</v>
       </c>
-      <c r="X17" s="37" t="s">
+      <c r="X17" s="43" t="s">
         <v>265</v>
       </c>
-      <c r="Y17" s="47" t="s">
+      <c r="Y17" s="53" t="s">
         <v>266</v>
       </c>
-      <c r="Z17" s="47" t="s">
+      <c r="Z17" s="53" t="s">
         <v>267</v>
       </c>
-      <c r="AA17" s="47" t="s">
+      <c r="AA17" s="53" t="s">
         <v>268</v>
       </c>
-      <c r="AB17" s="47" t="s">
+      <c r="AB17" s="53" t="s">
         <v>269</v>
       </c>
-      <c r="AC17" s="37"/>
-      <c r="AD17" s="37"/>
-      <c r="AE17" s="37"/>
-      <c r="AF17" s="37"/>
-      <c r="AG17" s="37"/>
-      <c r="AH17" s="47" t="s">
+      <c r="AC17" s="43"/>
+      <c r="AD17" s="43"/>
+      <c r="AE17" s="43"/>
+      <c r="AF17" s="43"/>
+      <c r="AG17" s="43"/>
+      <c r="AH17" s="53" t="s">
         <v>270</v>
       </c>
-      <c r="AI17" s="37"/>
-      <c r="AJ17" s="37"/>
-      <c r="AK17" s="37"/>
-      <c r="AL17" s="37" t="s">
+      <c r="AI17" s="43"/>
+      <c r="AJ17" s="43"/>
+      <c r="AK17" s="43"/>
+      <c r="AL17" s="43" t="s">
         <v>271</v>
       </c>
-      <c r="AM17" s="47" t="s">
+      <c r="AM17" s="53" t="s">
         <v>272</v>
       </c>
-      <c r="AN17" s="47" t="s">
+      <c r="AN17" s="53" t="s">
         <v>273</v>
       </c>
-      <c r="AO17" s="47" t="s">
+      <c r="AO17" s="53" t="s">
         <v>274</v>
       </c>
-      <c r="AP17" s="47" t="s">
+      <c r="AP17" s="53" t="s">
         <v>275</v>
       </c>
-      <c r="AQ17" s="37"/>
-      <c r="AR17" s="47" t="s">
+      <c r="AQ17" s="43"/>
+      <c r="AR17" s="53" t="s">
         <v>276</v>
       </c>
-      <c r="AS17" s="37" t="s">
+      <c r="AS17" s="43" t="s">
         <v>277</v>
       </c>
-      <c r="AT17" s="37" t="s">
+      <c r="AT17" s="43" t="s">
         <v>278</v>
       </c>
-      <c r="AU17" s="47" t="s">
+      <c r="AU17" s="53" t="s">
         <v>279</v>
       </c>
-      <c r="AV17" s="47" t="s">
+      <c r="AV17" s="53" t="s">
         <v>280</v>
       </c>
-      <c r="AW17" s="47" t="s">
+      <c r="AW17" s="53" t="s">
         <v>281</v>
       </c>
-      <c r="AX17" s="37"/>
-      <c r="AY17" s="47" t="s">
+      <c r="AX17" s="43"/>
+      <c r="AY17" s="53" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="18" ht="81" spans="1:51">
-      <c r="A18" s="43"/>
-      <c r="B18" s="44" t="s">
+      <c r="A18" s="49"/>
+      <c r="B18" s="50" t="s">
         <v>283</v>
       </c>
-      <c r="C18" s="45"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="37"/>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="47" t="s">
+      <c r="C18" s="51"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="43"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="43"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="43"/>
+      <c r="K18" s="53" t="s">
         <v>284</v>
       </c>
-      <c r="L18" s="37"/>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="37"/>
-      <c r="P18" s="37"/>
-      <c r="Q18" s="37"/>
-      <c r="R18" s="37"/>
-      <c r="S18" s="37"/>
-      <c r="T18" s="37"/>
-      <c r="U18" s="37"/>
-      <c r="V18" s="37"/>
-      <c r="W18" s="37"/>
-      <c r="X18" s="37"/>
-      <c r="Y18" s="37"/>
-      <c r="Z18" s="47" t="s">
+      <c r="L18" s="43"/>
+      <c r="M18" s="43"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="43"/>
+      <c r="Q18" s="43"/>
+      <c r="R18" s="43"/>
+      <c r="S18" s="43"/>
+      <c r="T18" s="43"/>
+      <c r="U18" s="43"/>
+      <c r="V18" s="43"/>
+      <c r="W18" s="43"/>
+      <c r="X18" s="43"/>
+      <c r="Y18" s="43"/>
+      <c r="Z18" s="53" t="s">
         <v>285</v>
       </c>
-      <c r="AA18" s="47" t="s">
+      <c r="AA18" s="53" t="s">
         <v>286</v>
       </c>
-      <c r="AB18" s="47" t="s">
+      <c r="AB18" s="53" t="s">
         <v>287</v>
       </c>
-      <c r="AC18" s="47" t="s">
+      <c r="AC18" s="53" t="s">
         <v>288</v>
       </c>
-      <c r="AD18" s="37"/>
-      <c r="AE18" s="37"/>
-      <c r="AF18" s="37"/>
-      <c r="AG18" s="37"/>
-      <c r="AH18" s="37"/>
-      <c r="AI18" s="37" t="s">
+      <c r="AD18" s="43"/>
+      <c r="AE18" s="43"/>
+      <c r="AF18" s="43"/>
+      <c r="AG18" s="43"/>
+      <c r="AH18" s="43"/>
+      <c r="AI18" s="43" t="s">
         <v>289</v>
       </c>
-      <c r="AJ18" s="37"/>
-      <c r="AK18" s="37" t="s">
+      <c r="AJ18" s="43"/>
+      <c r="AK18" s="43" t="s">
         <v>289</v>
       </c>
-      <c r="AL18" s="37"/>
-      <c r="AM18" s="37"/>
-      <c r="AN18" s="47" t="s">
+      <c r="AL18" s="43"/>
+      <c r="AM18" s="43"/>
+      <c r="AN18" s="53" t="s">
         <v>290</v>
       </c>
-      <c r="AO18" s="37"/>
-      <c r="AP18" s="37"/>
-      <c r="AQ18" s="37"/>
-      <c r="AR18" s="37"/>
-      <c r="AS18" s="37"/>
-      <c r="AT18" s="37"/>
-      <c r="AU18" s="37"/>
-      <c r="AV18" s="47" t="s">
+      <c r="AO18" s="43"/>
+      <c r="AP18" s="43"/>
+      <c r="AQ18" s="43"/>
+      <c r="AR18" s="43"/>
+      <c r="AS18" s="43"/>
+      <c r="AT18" s="43"/>
+      <c r="AU18" s="43"/>
+      <c r="AV18" s="53" t="s">
         <v>291</v>
       </c>
-      <c r="AW18" s="47" t="s">
+      <c r="AW18" s="53" t="s">
         <v>292</v>
       </c>
-      <c r="AX18" s="37"/>
-      <c r="AY18" s="47" t="s">
+      <c r="AX18" s="43"/>
+      <c r="AY18" s="53" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="19" ht="40.5" spans="1:51">
-      <c r="A19" s="43"/>
-      <c r="B19" s="44" t="s">
+      <c r="A19" s="49"/>
+      <c r="B19" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="C19" s="45"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="47" t="s">
+      <c r="C19" s="51"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="53" t="s">
         <v>294</v>
       </c>
-      <c r="I19" s="37"/>
-      <c r="J19" s="37"/>
-      <c r="K19" s="47" t="s">
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="53" t="s">
         <v>294</v>
       </c>
-      <c r="L19" s="37" t="s">
+      <c r="L19" s="43" t="s">
         <v>295</v>
       </c>
-      <c r="M19" s="37"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="37"/>
-      <c r="P19" s="37"/>
-      <c r="Q19" s="37"/>
-      <c r="R19" s="37"/>
-      <c r="S19" s="37"/>
-      <c r="T19" s="37"/>
-      <c r="U19" s="37"/>
-      <c r="V19" s="37"/>
-      <c r="W19" s="37"/>
-      <c r="X19" s="37"/>
-      <c r="Y19" s="37"/>
-      <c r="Z19" s="37"/>
-      <c r="AA19" s="37"/>
-      <c r="AB19" s="37"/>
-      <c r="AC19" s="37"/>
-      <c r="AD19" s="37"/>
-      <c r="AE19" s="37" t="s">
+      <c r="M19" s="43"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
+      <c r="P19" s="43"/>
+      <c r="Q19" s="43"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="43"/>
+      <c r="T19" s="43"/>
+      <c r="U19" s="43"/>
+      <c r="V19" s="43"/>
+      <c r="W19" s="43"/>
+      <c r="X19" s="43"/>
+      <c r="Y19" s="43"/>
+      <c r="Z19" s="43"/>
+      <c r="AA19" s="43"/>
+      <c r="AB19" s="43"/>
+      <c r="AC19" s="43"/>
+      <c r="AD19" s="43"/>
+      <c r="AE19" s="43" t="s">
         <v>295</v>
       </c>
-      <c r="AF19" s="37"/>
-      <c r="AG19" s="37"/>
-      <c r="AH19" s="37"/>
-      <c r="AI19" s="37"/>
-      <c r="AJ19" s="37"/>
-      <c r="AK19" s="37"/>
-      <c r="AL19" s="37"/>
-      <c r="AM19" s="37"/>
-      <c r="AN19" s="37"/>
-      <c r="AO19" s="37"/>
-      <c r="AP19" s="37" t="s">
+      <c r="AF19" s="43"/>
+      <c r="AG19" s="43"/>
+      <c r="AH19" s="43"/>
+      <c r="AI19" s="43"/>
+      <c r="AJ19" s="43"/>
+      <c r="AK19" s="43"/>
+      <c r="AL19" s="43"/>
+      <c r="AM19" s="43"/>
+      <c r="AN19" s="43"/>
+      <c r="AO19" s="43"/>
+      <c r="AP19" s="43" t="s">
         <v>295</v>
       </c>
-      <c r="AQ19" s="37"/>
-      <c r="AR19" s="37"/>
-      <c r="AS19" s="37"/>
-      <c r="AT19" s="37"/>
-      <c r="AU19" s="37"/>
-      <c r="AV19" s="47"/>
-      <c r="AW19" s="47"/>
-      <c r="AX19" s="37"/>
-      <c r="AY19" s="47" t="s">
+      <c r="AQ19" s="43"/>
+      <c r="AR19" s="43"/>
+      <c r="AS19" s="43"/>
+      <c r="AT19" s="43"/>
+      <c r="AU19" s="43"/>
+      <c r="AV19" s="53"/>
+      <c r="AW19" s="53"/>
+      <c r="AX19" s="43"/>
+      <c r="AY19" s="53" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="20" ht="54" spans="1:51">
-      <c r="A20" s="43"/>
-      <c r="B20" s="44" t="s">
+      <c r="A20" s="49"/>
+      <c r="B20" s="50" t="s">
         <v>297</v>
       </c>
-      <c r="C20" s="45"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="37"/>
-      <c r="H20" s="37"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="37"/>
-      <c r="K20" s="37"/>
-      <c r="L20" s="37"/>
-      <c r="M20" s="37"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="37"/>
-      <c r="P20" s="37"/>
-      <c r="Q20" s="37"/>
-      <c r="R20" s="37"/>
-      <c r="S20" s="37"/>
-      <c r="T20" s="37"/>
-      <c r="U20" s="37"/>
-      <c r="V20" s="37"/>
-      <c r="W20" s="37"/>
-      <c r="X20" s="37"/>
-      <c r="Y20" s="37"/>
-      <c r="Z20" s="37"/>
-      <c r="AA20" s="37"/>
-      <c r="AB20" s="37"/>
-      <c r="AC20" s="37"/>
-      <c r="AD20" s="37"/>
-      <c r="AE20" s="37"/>
-      <c r="AF20" s="37"/>
-      <c r="AG20" s="37"/>
-      <c r="AH20" s="37"/>
-      <c r="AI20" s="37"/>
-      <c r="AJ20" s="47" t="s">
+      <c r="C20" s="51"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="43"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="P20" s="43"/>
+      <c r="Q20" s="43"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="43"/>
+      <c r="T20" s="43"/>
+      <c r="U20" s="43"/>
+      <c r="V20" s="43"/>
+      <c r="W20" s="43"/>
+      <c r="X20" s="43"/>
+      <c r="Y20" s="43"/>
+      <c r="Z20" s="43"/>
+      <c r="AA20" s="43"/>
+      <c r="AB20" s="43"/>
+      <c r="AC20" s="43"/>
+      <c r="AD20" s="43"/>
+      <c r="AE20" s="43"/>
+      <c r="AF20" s="43"/>
+      <c r="AG20" s="43"/>
+      <c r="AH20" s="43"/>
+      <c r="AI20" s="43"/>
+      <c r="AJ20" s="53" t="s">
         <v>298</v>
       </c>
-      <c r="AK20" s="37"/>
-      <c r="AL20" s="37"/>
-      <c r="AM20" s="37"/>
-      <c r="AN20" s="37"/>
-      <c r="AO20" s="37"/>
-      <c r="AP20" s="37"/>
-      <c r="AQ20" s="37"/>
-      <c r="AR20" s="37"/>
-      <c r="AS20" s="37"/>
-      <c r="AT20" s="37"/>
-      <c r="AU20" s="37"/>
-      <c r="AV20" s="47"/>
-      <c r="AW20" s="47"/>
-      <c r="AX20" s="37"/>
-      <c r="AY20" s="37"/>
+      <c r="AK20" s="43"/>
+      <c r="AL20" s="43"/>
+      <c r="AM20" s="43"/>
+      <c r="AN20" s="43"/>
+      <c r="AO20" s="43"/>
+      <c r="AP20" s="43"/>
+      <c r="AQ20" s="43"/>
+      <c r="AR20" s="43"/>
+      <c r="AS20" s="43"/>
+      <c r="AT20" s="43"/>
+      <c r="AU20" s="43"/>
+      <c r="AV20" s="53"/>
+      <c r="AW20" s="53"/>
+      <c r="AX20" s="43"/>
+      <c r="AY20" s="43"/>
     </row>
     <row r="21" ht="81" spans="1:51">
-      <c r="A21" s="43"/>
-      <c r="B21" s="48" t="s">
+      <c r="A21" s="49"/>
+      <c r="B21" s="54" t="s">
         <v>299</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="52" t="s">
         <v>300</v>
       </c>
-      <c r="D21" s="46" t="s">
+      <c r="D21" s="52" t="s">
         <v>300</v>
       </c>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="47" t="s">
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="53" t="s">
         <v>301</v>
       </c>
-      <c r="L21" s="37" t="s">
+      <c r="L21" s="43" t="s">
         <v>302</v>
       </c>
-      <c r="M21" s="37"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="37"/>
-      <c r="P21" s="37"/>
-      <c r="Q21" s="37"/>
-      <c r="R21" s="37"/>
-      <c r="S21" s="37"/>
-      <c r="T21" s="37"/>
-      <c r="U21" s="37"/>
-      <c r="V21" s="37"/>
-      <c r="W21" s="37"/>
-      <c r="X21" s="37"/>
-      <c r="Y21" s="37"/>
-      <c r="Z21" s="37"/>
-      <c r="AA21" s="37"/>
-      <c r="AB21" s="37"/>
-      <c r="AC21" s="37"/>
-      <c r="AD21" s="37"/>
-      <c r="AE21" s="37" t="s">
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="43"/>
+      <c r="Q21" s="43"/>
+      <c r="R21" s="43"/>
+      <c r="S21" s="43"/>
+      <c r="T21" s="43"/>
+      <c r="U21" s="43"/>
+      <c r="V21" s="43"/>
+      <c r="W21" s="43"/>
+      <c r="X21" s="43"/>
+      <c r="Y21" s="43"/>
+      <c r="Z21" s="43"/>
+      <c r="AA21" s="43"/>
+      <c r="AB21" s="43"/>
+      <c r="AC21" s="43"/>
+      <c r="AD21" s="43"/>
+      <c r="AE21" s="43" t="s">
         <v>303</v>
       </c>
-      <c r="AF21" s="47" t="s">
+      <c r="AF21" s="53" t="s">
         <v>304</v>
       </c>
-      <c r="AG21" s="47" t="s">
+      <c r="AG21" s="53" t="s">
         <v>305</v>
       </c>
-      <c r="AH21" s="37"/>
-      <c r="AI21" s="47" t="s">
+      <c r="AH21" s="43"/>
+      <c r="AI21" s="53" t="s">
         <v>306</v>
       </c>
-      <c r="AJ21" s="47" t="s">
+      <c r="AJ21" s="53" t="s">
         <v>307</v>
       </c>
-      <c r="AK21" s="37"/>
-      <c r="AL21" s="37"/>
-      <c r="AM21" s="37"/>
-      <c r="AN21" s="37"/>
-      <c r="AO21" s="37" t="s">
+      <c r="AK21" s="43"/>
+      <c r="AL21" s="43"/>
+      <c r="AM21" s="43"/>
+      <c r="AN21" s="43"/>
+      <c r="AO21" s="43" t="s">
         <v>302</v>
       </c>
-      <c r="AP21" s="37" t="s">
+      <c r="AP21" s="43" t="s">
         <v>302</v>
       </c>
-      <c r="AQ21" s="37"/>
-      <c r="AR21" s="37"/>
-      <c r="AS21" s="37"/>
-      <c r="AT21" s="37" t="s">
+      <c r="AQ21" s="43"/>
+      <c r="AR21" s="43"/>
+      <c r="AS21" s="43"/>
+      <c r="AT21" s="43" t="s">
         <v>303</v>
       </c>
-      <c r="AU21" s="37"/>
-      <c r="AV21" s="37"/>
-      <c r="AW21" s="37"/>
-      <c r="AX21" s="47" t="s">
+      <c r="AU21" s="43"/>
+      <c r="AV21" s="43"/>
+      <c r="AW21" s="43"/>
+      <c r="AX21" s="53" t="s">
         <v>308</v>
       </c>
-      <c r="AY21" s="47" t="s">
+      <c r="AY21" s="53" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:51">
-      <c r="A22" s="49"/>
-      <c r="B22" s="44" t="s">
+      <c r="A22" s="55"/>
+      <c r="B22" s="50" t="s">
         <v>310</v>
       </c>
-      <c r="C22" s="45"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="37"/>
-      <c r="P22" s="37"/>
-      <c r="Q22" s="37"/>
-      <c r="R22" s="37"/>
-      <c r="S22" s="37"/>
-      <c r="T22" s="37"/>
-      <c r="U22" s="37"/>
-      <c r="V22" s="37"/>
-      <c r="W22" s="37"/>
-      <c r="X22" s="37"/>
-      <c r="Y22" s="37"/>
-      <c r="Z22" s="37"/>
-      <c r="AA22" s="37"/>
-      <c r="AB22" s="37"/>
-      <c r="AC22" s="37"/>
-      <c r="AD22" s="37"/>
-      <c r="AE22" s="37"/>
-      <c r="AF22" s="37"/>
-      <c r="AG22" s="37"/>
-      <c r="AH22" s="37"/>
-      <c r="AI22" s="37"/>
-      <c r="AJ22" s="37"/>
-      <c r="AK22" s="37"/>
-      <c r="AL22" s="37"/>
-      <c r="AM22" s="37"/>
-      <c r="AN22" s="37"/>
-      <c r="AO22" s="37"/>
-      <c r="AP22" s="37"/>
-      <c r="AQ22" s="37"/>
-      <c r="AR22" s="37"/>
-      <c r="AS22" s="37"/>
-      <c r="AT22" s="37"/>
-      <c r="AU22" s="37"/>
-      <c r="AV22" s="47"/>
-      <c r="AW22" s="47"/>
-      <c r="AX22" s="37"/>
-      <c r="AY22" s="37"/>
+      <c r="C22" s="51"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="43"/>
+      <c r="Q22" s="43"/>
+      <c r="R22" s="43"/>
+      <c r="S22" s="43"/>
+      <c r="T22" s="43"/>
+      <c r="U22" s="43"/>
+      <c r="V22" s="43"/>
+      <c r="W22" s="43"/>
+      <c r="X22" s="43"/>
+      <c r="Y22" s="43"/>
+      <c r="Z22" s="43"/>
+      <c r="AA22" s="43"/>
+      <c r="AB22" s="43"/>
+      <c r="AC22" s="43"/>
+      <c r="AD22" s="43"/>
+      <c r="AE22" s="43"/>
+      <c r="AF22" s="43"/>
+      <c r="AG22" s="43"/>
+      <c r="AH22" s="43"/>
+      <c r="AI22" s="43"/>
+      <c r="AJ22" s="43"/>
+      <c r="AK22" s="43"/>
+      <c r="AL22" s="43"/>
+      <c r="AM22" s="43"/>
+      <c r="AN22" s="43"/>
+      <c r="AO22" s="43"/>
+      <c r="AP22" s="43"/>
+      <c r="AQ22" s="43"/>
+      <c r="AR22" s="43"/>
+      <c r="AS22" s="43"/>
+      <c r="AT22" s="43"/>
+      <c r="AU22" s="43"/>
+      <c r="AV22" s="53"/>
+      <c r="AW22" s="53"/>
+      <c r="AX22" s="43"/>
+      <c r="AY22" s="43"/>
     </row>
     <row r="24" ht="108" spans="1:51">
-      <c r="A24" s="26" t="s">
+      <c r="A24" s="32" t="s">
         <v>311</v>
       </c>
-      <c r="B24" s="33" t="s">
+      <c r="B24" s="39" t="s">
         <v>312</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="37" t="s">
         <v>313</v>
       </c>
-      <c r="D24" s="31" t="s">
+      <c r="D24" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="E24" s="37" t="s">
         <v>314</v>
       </c>
-      <c r="F24" s="31" t="s">
+      <c r="F24" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="G24" s="31" t="s">
+      <c r="G24" s="37" t="s">
         <v>316</v>
       </c>
-      <c r="H24" s="31" t="s">
+      <c r="H24" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="I24" s="31" t="s">
+      <c r="I24" s="37" t="s">
         <v>318</v>
       </c>
-      <c r="J24" s="31" t="s">
+      <c r="J24" s="37" t="s">
         <v>319</v>
       </c>
-      <c r="K24" s="31" t="s">
+      <c r="K24" s="37" t="s">
         <v>320</v>
       </c>
-      <c r="L24" s="31" t="s">
+      <c r="L24" s="37" t="s">
         <v>321</v>
       </c>
-      <c r="M24" s="31" t="s">
+      <c r="M24" s="37" t="s">
         <v>322</v>
       </c>
-      <c r="N24" s="31" t="s">
+      <c r="N24" s="37" t="s">
         <v>323</v>
       </c>
-      <c r="O24" s="31" t="s">
+      <c r="O24" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="P24" s="31" t="s">
+      <c r="P24" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="Q24" s="31" t="s">
+      <c r="Q24" s="37" t="s">
         <v>325</v>
       </c>
-      <c r="R24" s="31" t="s">
+      <c r="R24" s="37" t="s">
         <v>326</v>
       </c>
-      <c r="S24" s="31" t="s">
+      <c r="S24" s="37" t="s">
         <v>327</v>
       </c>
-      <c r="T24" s="31" t="s">
+      <c r="T24" s="37" t="s">
         <v>328</v>
       </c>
-      <c r="U24" s="31" t="s">
+      <c r="U24" s="37" t="s">
         <v>329</v>
       </c>
-      <c r="V24" s="31" t="s">
+      <c r="V24" s="37" t="s">
         <v>330</v>
       </c>
-      <c r="W24" s="31" t="s">
+      <c r="W24" s="37" t="s">
         <v>331</v>
       </c>
-      <c r="X24" s="31" t="s">
+      <c r="X24" s="37" t="s">
         <v>332</v>
       </c>
-      <c r="Y24" s="31" t="s">
+      <c r="Y24" s="37" t="s">
         <v>333</v>
       </c>
-      <c r="Z24" s="31" t="s">
+      <c r="Z24" s="37" t="s">
         <v>334</v>
       </c>
-      <c r="AA24" s="31" t="s">
+      <c r="AA24" s="37" t="s">
         <v>335</v>
       </c>
-      <c r="AB24" s="31" t="s">
+      <c r="AB24" s="37" t="s">
         <v>336</v>
       </c>
-      <c r="AC24" s="31" t="s">
+      <c r="AC24" s="37" t="s">
         <v>337</v>
       </c>
-      <c r="AD24" s="31" t="s">
+      <c r="AD24" s="37" t="s">
         <v>338</v>
       </c>
-      <c r="AE24" s="31" t="s">
+      <c r="AE24" s="37" t="s">
         <v>339</v>
       </c>
-      <c r="AF24" s="31" t="s">
+      <c r="AF24" s="37" t="s">
         <v>340</v>
       </c>
-      <c r="AG24" s="31" t="s">
+      <c r="AG24" s="37" t="s">
         <v>341</v>
       </c>
-      <c r="AH24" s="31" t="s">
+      <c r="AH24" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="AI24" s="31" t="s">
+      <c r="AI24" s="37" t="s">
         <v>342</v>
       </c>
-      <c r="AJ24" s="31" t="s">
+      <c r="AJ24" s="37" t="s">
         <v>343</v>
       </c>
-      <c r="AK24" s="31" t="s">
+      <c r="AK24" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="AL24" s="31" t="s">
+      <c r="AL24" s="37" t="s">
         <v>344</v>
       </c>
-      <c r="AM24" s="31" t="s">
+      <c r="AM24" s="37" t="s">
         <v>345</v>
       </c>
-      <c r="AN24" s="31" t="s">
+      <c r="AN24" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="AO24" s="31" t="s">
+      <c r="AO24" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="AP24" s="31" t="s">
+      <c r="AP24" s="37" t="s">
         <v>341</v>
       </c>
-      <c r="AQ24" s="31" t="s">
+      <c r="AQ24" s="37" t="s">
         <v>341</v>
       </c>
-      <c r="AR24" s="31" t="s">
+      <c r="AR24" s="37" t="s">
         <v>181</v>
       </c>
-      <c r="AS24" s="31" t="s">
+      <c r="AS24" s="37" t="s">
         <v>346</v>
       </c>
-      <c r="AT24" s="31" t="s">
+      <c r="AT24" s="37" t="s">
         <v>347</v>
       </c>
-      <c r="AU24" s="31" t="s">
+      <c r="AU24" s="37" t="s">
         <v>348</v>
       </c>
-      <c r="AV24" s="31" t="s">
+      <c r="AV24" s="37" t="s">
         <v>349</v>
       </c>
-      <c r="AW24" s="32" t="s">
+      <c r="AW24" s="38" t="s">
         <v>350</v>
       </c>
-      <c r="AX24" s="32" t="s">
+      <c r="AX24" s="38" t="s">
         <v>341</v>
       </c>
-      <c r="AY24" s="32" t="s">
+      <c r="AY24" s="38" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:51">
-      <c r="A25" s="28"/>
-      <c r="B25" s="33" t="s">
+      <c r="A25" s="34"/>
+      <c r="B25" s="39" t="s">
         <v>351</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="31"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="31"/>
-      <c r="Q25" s="31"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="31"/>
-      <c r="T25" s="31"/>
-      <c r="U25" s="31"/>
-      <c r="V25" s="31"/>
-      <c r="W25" s="31"/>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="31"/>
-      <c r="Z25" s="31"/>
-      <c r="AA25" s="31"/>
-      <c r="AB25" s="31"/>
-      <c r="AC25" s="31"/>
-      <c r="AD25" s="31"/>
-      <c r="AE25" s="31"/>
-      <c r="AF25" s="31"/>
-      <c r="AG25" s="31"/>
-      <c r="AH25" s="31"/>
-      <c r="AI25" s="31"/>
-      <c r="AJ25" s="31"/>
-      <c r="AK25" s="31"/>
-      <c r="AL25" s="31"/>
-      <c r="AM25" s="31"/>
-      <c r="AN25" s="31"/>
-      <c r="AO25" s="31"/>
-      <c r="AP25" s="31"/>
-      <c r="AQ25" s="31"/>
-      <c r="AR25" s="31"/>
-      <c r="AS25" s="31"/>
-      <c r="AT25" s="31"/>
-      <c r="AU25" s="31"/>
-      <c r="AV25" s="31"/>
-      <c r="AW25" s="32"/>
-      <c r="AX25" s="32"/>
-      <c r="AY25" s="32"/>
+      <c r="C25" s="37"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="37"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="37"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="37"/>
+      <c r="P25" s="37"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="37"/>
+      <c r="S25" s="37"/>
+      <c r="T25" s="37"/>
+      <c r="U25" s="37"/>
+      <c r="V25" s="37"/>
+      <c r="W25" s="37"/>
+      <c r="X25" s="37"/>
+      <c r="Y25" s="37"/>
+      <c r="Z25" s="37"/>
+      <c r="AA25" s="37"/>
+      <c r="AB25" s="37"/>
+      <c r="AC25" s="37"/>
+      <c r="AD25" s="37"/>
+      <c r="AE25" s="37"/>
+      <c r="AF25" s="37"/>
+      <c r="AG25" s="37"/>
+      <c r="AH25" s="37"/>
+      <c r="AI25" s="37"/>
+      <c r="AJ25" s="37"/>
+      <c r="AK25" s="37"/>
+      <c r="AL25" s="37"/>
+      <c r="AM25" s="37"/>
+      <c r="AN25" s="37"/>
+      <c r="AO25" s="37"/>
+      <c r="AP25" s="37"/>
+      <c r="AQ25" s="37"/>
+      <c r="AR25" s="37"/>
+      <c r="AS25" s="37"/>
+      <c r="AT25" s="37"/>
+      <c r="AU25" s="37"/>
+      <c r="AV25" s="37"/>
+      <c r="AW25" s="38"/>
+      <c r="AX25" s="38"/>
+      <c r="AY25" s="38"/>
     </row>
     <row r="26" customFormat="1" ht="94.5" spans="1:51">
-      <c r="A26" s="34"/>
-      <c r="B26" s="33" t="s">
+      <c r="A26" s="40"/>
+      <c r="B26" s="39" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31" t="s">
+      <c r="C26" s="37"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="37"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="37" t="s">
         <v>353</v>
       </c>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31" t="s">
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="37"/>
+      <c r="M26" s="37" t="s">
         <v>354</v>
       </c>
-      <c r="N26" s="31" t="s">
+      <c r="N26" s="37" t="s">
         <v>355</v>
       </c>
-      <c r="O26" s="31"/>
-      <c r="P26" s="31"/>
-      <c r="Q26" s="31"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="31"/>
-      <c r="T26" s="31"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="31"/>
-      <c r="Z26" s="31"/>
-      <c r="AA26" s="31"/>
-      <c r="AB26" s="31"/>
-      <c r="AC26" s="31"/>
-      <c r="AD26" s="31"/>
-      <c r="AE26" s="31"/>
-      <c r="AF26" s="31"/>
-      <c r="AG26" s="31"/>
-      <c r="AH26" s="31"/>
-      <c r="AI26" s="31"/>
-      <c r="AJ26" s="31"/>
-      <c r="AK26" s="31"/>
-      <c r="AL26" s="31"/>
-      <c r="AM26" s="31"/>
-      <c r="AN26" s="31"/>
-      <c r="AO26" s="31" t="s">
+      <c r="O26" s="37"/>
+      <c r="P26" s="37"/>
+      <c r="Q26" s="37"/>
+      <c r="R26" s="37"/>
+      <c r="S26" s="37"/>
+      <c r="T26" s="37"/>
+      <c r="U26" s="37"/>
+      <c r="V26" s="37"/>
+      <c r="W26" s="37"/>
+      <c r="X26" s="37"/>
+      <c r="Y26" s="37"/>
+      <c r="Z26" s="37"/>
+      <c r="AA26" s="37"/>
+      <c r="AB26" s="37"/>
+      <c r="AC26" s="37"/>
+      <c r="AD26" s="37"/>
+      <c r="AE26" s="37"/>
+      <c r="AF26" s="37"/>
+      <c r="AG26" s="37"/>
+      <c r="AH26" s="37"/>
+      <c r="AI26" s="37"/>
+      <c r="AJ26" s="37"/>
+      <c r="AK26" s="37"/>
+      <c r="AL26" s="37"/>
+      <c r="AM26" s="37"/>
+      <c r="AN26" s="37"/>
+      <c r="AO26" s="37" t="s">
         <v>356</v>
       </c>
-      <c r="AP26" s="31" t="s">
+      <c r="AP26" s="37" t="s">
         <v>357</v>
       </c>
-      <c r="AQ26" s="31"/>
-      <c r="AR26" s="31"/>
-      <c r="AS26" s="31"/>
-      <c r="AT26" s="31"/>
-      <c r="AU26" s="31"/>
-      <c r="AV26" s="31"/>
-      <c r="AW26" s="32"/>
-      <c r="AX26" s="32"/>
-      <c r="AY26" s="32"/>
+      <c r="AQ26" s="37"/>
+      <c r="AR26" s="37"/>
+      <c r="AS26" s="37"/>
+      <c r="AT26" s="37"/>
+      <c r="AU26" s="37"/>
+      <c r="AV26" s="37"/>
+      <c r="AW26" s="38"/>
+      <c r="AX26" s="38"/>
+      <c r="AY26" s="38"/>
     </row>
-    <row r="27" s="9" customFormat="1" ht="27" spans="1:51">
-      <c r="A27" s="35" t="s">
+    <row r="27" s="15" customFormat="1" ht="27" spans="1:51">
+      <c r="A27" s="41" t="s">
         <v>358</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="53" t="s">
         <v>359</v>
       </c>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="50"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="50"/>
-      <c r="R27" s="50"/>
-      <c r="S27" s="50"/>
-      <c r="T27" s="50"/>
-      <c r="U27" s="50"/>
-      <c r="V27" s="50"/>
-      <c r="W27" s="50"/>
-      <c r="X27" s="50"/>
-      <c r="Y27" s="50"/>
-      <c r="Z27" s="50"/>
-      <c r="AA27" s="50"/>
-      <c r="AB27" s="50"/>
-      <c r="AC27" s="50"/>
-      <c r="AD27" s="50"/>
-      <c r="AE27" s="50"/>
-      <c r="AF27" s="50"/>
-      <c r="AG27" s="50"/>
-      <c r="AH27" s="50"/>
-      <c r="AI27" s="50"/>
-      <c r="AJ27" s="50"/>
-      <c r="AK27" s="50"/>
-      <c r="AL27" s="50"/>
-      <c r="AM27" s="50"/>
-      <c r="AN27" s="50"/>
-      <c r="AO27" s="50"/>
-      <c r="AP27" s="50"/>
-      <c r="AQ27" s="50"/>
-      <c r="AR27" s="50"/>
+      <c r="C27" s="56"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
+      <c r="I27" s="56"/>
+      <c r="J27" s="56"/>
+      <c r="K27" s="56"/>
+      <c r="L27" s="56"/>
+      <c r="M27" s="56"/>
+      <c r="N27" s="56"/>
+      <c r="O27" s="56"/>
+      <c r="P27" s="56"/>
+      <c r="Q27" s="56"/>
+      <c r="R27" s="56"/>
+      <c r="S27" s="56"/>
+      <c r="T27" s="56"/>
+      <c r="U27" s="56"/>
+      <c r="V27" s="56"/>
+      <c r="W27" s="56"/>
+      <c r="X27" s="56"/>
+      <c r="Y27" s="56"/>
+      <c r="Z27" s="56"/>
+      <c r="AA27" s="56"/>
+      <c r="AB27" s="56"/>
+      <c r="AC27" s="56"/>
+      <c r="AD27" s="56"/>
+      <c r="AE27" s="56"/>
+      <c r="AF27" s="56"/>
+      <c r="AG27" s="56"/>
+      <c r="AH27" s="56"/>
+      <c r="AI27" s="56"/>
+      <c r="AJ27" s="56"/>
+      <c r="AK27" s="56"/>
+      <c r="AL27" s="56"/>
+      <c r="AM27" s="56"/>
+      <c r="AN27" s="56"/>
+      <c r="AO27" s="56"/>
+      <c r="AP27" s="56"/>
+      <c r="AQ27" s="56"/>
+      <c r="AR27" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -8026,151 +8323,151 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="8"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="11" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="12"/>
+      <c r="B3" s="10"/>
+      <c r="C3" s="11" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5" t="s">
+      <c r="A4" s="12"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="11" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5" t="s">
+      <c r="A5" s="12"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="11" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="5"/>
+      <c r="A6" s="12"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="11"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="4" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="11" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5" t="s">
+      <c r="A8" s="12"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="11" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5" t="s">
+      <c r="A9" s="12"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5" t="s">
+      <c r="A10" s="12"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="5"/>
+      <c r="A11" s="12"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="11"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="4" t="s">
+      <c r="A12" s="12"/>
+      <c r="B12" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="11" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="5" t="s">
+      <c r="A13" s="12"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="11" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5" t="s">
+      <c r="A14" s="12"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="11" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5" t="s">
+      <c r="A15" s="12"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="11" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5" t="s">
+      <c r="A16" s="12"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="11" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="5"/>
+      <c r="A17" s="12"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="11"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="4" t="s">
+      <c r="A18" s="12"/>
+      <c r="B18" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="13" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="7" t="s">
+      <c r="A19" s="12"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="13" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="7" t="s">
+      <c r="A20" s="12"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="13" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="7" t="s">
+      <c r="A21" s="12"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="13" t="s">
         <v>381</v>
       </c>
     </row>
@@ -8190,9 +8487,169 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:D14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="21.25" customWidth="1"/>
+    <col min="4" max="4" width="77.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="4" ht="94.5" spans="1:4">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="5" ht="27" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="9" ht="27" spans="1:4">
+      <c r="A9" s="5"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="5"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="11" ht="40.5" spans="1:4">
+      <c r="A11" s="5"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="12" ht="27" spans="1:4">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="B8:B12"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="15360" windowHeight="4560"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="49过程输入输出工具" sheetId="1" r:id="rId1"/>
@@ -1207,14 +1207,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1226,19 +1218,95 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>是编写一份正式批准项目并授权项目经理在项目活动中使用组织资源的文件的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>编写</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>一份</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>正式批准</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>项目并</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>授权</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>项目经理在项目活动中使用组织资源的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>文件</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1250,19 +1318,53 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  是定义、准备和协调项目计划的所有组成部分，并把它们整合为一份综合项目管理计划的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t xml:space="preserve">  是定义、准备和</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>协调</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>项目计划的所有组成部分，并把它们</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>整合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>为一份综合项目管理计划的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1274,19 +1376,53 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  是为了实现项目目标而领导和执行项目管理计划中所确定的工作，并实施已批准的变更请求的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t xml:space="preserve">  是为了实现项目目标而</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>领导和执行</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>项目管理计划中所确定的工作，并</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>实施</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>已批准的变更请求的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -1298,19 +1434,95 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 是使用现有知识并生成新知识，以实现项目目标并且帮助组织学习的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t xml:space="preserve"> 是使用</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>现有知识</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>并生成</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>新知识</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，以实现项目</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>目标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>并且帮助组织</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>学习</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">定义： 
  </t>
     </r>
@@ -1322,19 +1534,53 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 是跟踪、审查和报告整体项目进展，以实现项目管理计划中确定的绩效目标的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t xml:space="preserve"> 是</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>跟踪、审查和报告</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>整体项目进展，以实现项目管理计划中确定的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>绩效目标</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1346,19 +1592,74 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>是审查所有变更请求、批准变更，管理对可交付成果、项目文件和项目管理计划的变更，并对变更处理结果进行沟通的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>审查</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>所有变更请求、批准变更，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>管理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>对可交付成果、项目文件和项目管理计划的变更，并对变更处理结果进行</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>沟通</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1370,7 +1671,28 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>是终结项目、阶段或合同的所有活动的过程</t>
+      <t>是</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>终结</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>项目、阶段或合同的所有活动的过程</t>
     </r>
   </si>
   <si>
@@ -1783,6 +2105,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -2375,14 +2705,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2394,21 +2716,85 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  1、明确项目与组织战略目标之间的直接联系
-  2、确定项目的正式地位
-  3、展示组织对项目的承诺</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t xml:space="preserve">  1、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>明确</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>项目与组织战略目标之间的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>直接联系</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  2、确定项目的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>正式地位</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  3、展示组织对项目的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>承诺</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">作用：
   </t>
     </r>
@@ -2420,19 +2806,64 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>生成一份综合文件，用于确定所有项目工作的基础及其执行方式</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t>生成一份综合文件，用于</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>确定</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>所有项目工作的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>基础</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>及其</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>执行方式</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2444,19 +2875,53 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  是对项目工作和可交付成果开展综合管理，以提高项目成功的可能性</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t xml:space="preserve">  是对项目工作和可交付成果开展</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>综合管理</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>，以</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>提高</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>项目成功的可能性</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2468,20 +2933,54 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  1、利用已有的组织知识来创造或改进项目成果
-  2、使当前项目创造的知识可用于支持组织运营和未来的项目或阶段</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t xml:space="preserve">  1、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>利用已有</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>的组织知识来创造或改进项目成果
+  2、使当前项目</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>创造的知识</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>可用于支持组织运营和未来的项目或阶段</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2493,20 +2992,138 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  1、让干系人了解项目的当前状态并认可为处理绩效问题而采取的行动
-  2、通过成本和进度预测，让干系人了解项目的未来状态</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t xml:space="preserve">  1、让干系人</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>了解</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>项目的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>当前</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>状态并</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>认可</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>为处理绩效问题而采取的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>行动</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+  2、通过成本和进度预测，让干系人</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>了解</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>项目的</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>未来</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>状态</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2518,19 +3135,22 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  确保对项目中已记录在案的变更做出综合评审</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t xml:space="preserve">  确保对项目中已记录在案的变更做出</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>综合评审</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -2542,8 +3162,50 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  1、存档项目或阶段信息，完成计划的工作
-  2、释放组织团队资源以开展新的工作</t>
+      <t xml:space="preserve">  1、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>存档</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>项目或阶段信息，完成计划的工作
+  2、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>释放</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>组织团队资源以开展新的工作</t>
     </r>
   </si>
   <si>
@@ -2957,6 +3619,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用：
 </t>
     </r>
@@ -5371,7 +6041,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -5405,13 +6075,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -5943,2328 +6607,2328 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:51">
-      <c r="A1" s="12"/>
-      <c r="B1" s="12"/>
-      <c r="C1" s="16" t="s">
+      <c r="A1" s="11"/>
+      <c r="B1" s="11"/>
+      <c r="C1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17" t="s">
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="15"/>
+      <c r="J1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17"/>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17" t="s">
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17"/>
-      <c r="V1" s="17" t="s">
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="15"/>
+      <c r="T1" s="15"/>
+      <c r="U1" s="15"/>
+      <c r="V1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="17"/>
-      <c r="X1" s="17"/>
-      <c r="Y1" s="17"/>
-      <c r="Z1" s="17" t="s">
+      <c r="W1" s="15"/>
+      <c r="X1" s="15"/>
+      <c r="Y1" s="15"/>
+      <c r="Z1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="17"/>
-      <c r="AB1" s="17"/>
-      <c r="AC1" s="17" t="s">
+      <c r="AA1" s="15"/>
+      <c r="AB1" s="15"/>
+      <c r="AC1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="17"/>
-      <c r="AE1" s="17"/>
-      <c r="AF1" s="17"/>
-      <c r="AG1" s="17"/>
-      <c r="AH1" s="17"/>
-      <c r="AI1" s="17" t="s">
+      <c r="AD1" s="15"/>
+      <c r="AE1" s="15"/>
+      <c r="AF1" s="15"/>
+      <c r="AG1" s="15"/>
+      <c r="AH1" s="15"/>
+      <c r="AI1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="AJ1" s="17"/>
-      <c r="AK1" s="17"/>
-      <c r="AL1" s="17" t="s">
+      <c r="AJ1" s="15"/>
+      <c r="AK1" s="15"/>
+      <c r="AL1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="AM1" s="17"/>
-      <c r="AN1" s="17"/>
-      <c r="AO1" s="17"/>
-      <c r="AP1" s="17"/>
-      <c r="AQ1" s="17"/>
-      <c r="AR1" s="17"/>
-      <c r="AS1" s="17" t="s">
+      <c r="AM1" s="15"/>
+      <c r="AN1" s="15"/>
+      <c r="AO1" s="15"/>
+      <c r="AP1" s="15"/>
+      <c r="AQ1" s="15"/>
+      <c r="AR1" s="15"/>
+      <c r="AS1" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="AT1" s="17"/>
-      <c r="AU1" s="17"/>
-      <c r="AV1" s="17" t="s">
+      <c r="AT1" s="15"/>
+      <c r="AU1" s="15"/>
+      <c r="AV1" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="AW1" s="17"/>
-      <c r="AX1" s="17"/>
-      <c r="AY1" s="17"/>
+      <c r="AW1" s="15"/>
+      <c r="AX1" s="15"/>
+      <c r="AY1" s="15"/>
     </row>
     <row r="2" customFormat="1" ht="58" customHeight="1" spans="1:51">
-      <c r="A2" s="12"/>
-      <c r="B2" s="12"/>
-      <c r="C2" s="18" t="s">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="20" t="s">
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="21"/>
-      <c r="L2" s="21"/>
-      <c r="M2" s="21"/>
-      <c r="N2" s="21"/>
-      <c r="O2" s="21"/>
-      <c r="P2" s="22" t="s">
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="21"/>
-      <c r="R2" s="21"/>
-      <c r="S2" s="21"/>
-      <c r="T2" s="21"/>
-      <c r="U2" s="23"/>
-      <c r="V2" s="22" t="s">
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
+      <c r="T2" s="19"/>
+      <c r="U2" s="21"/>
+      <c r="V2" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="W2" s="21"/>
-      <c r="X2" s="21"/>
-      <c r="Y2" s="23"/>
-      <c r="Z2" s="20" t="s">
+      <c r="W2" s="19"/>
+      <c r="X2" s="19"/>
+      <c r="Y2" s="21"/>
+      <c r="Z2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="21"/>
-      <c r="AB2" s="23"/>
-      <c r="AC2" s="22" t="s">
+      <c r="AA2" s="19"/>
+      <c r="AB2" s="21"/>
+      <c r="AC2" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="AD2" s="21"/>
-      <c r="AE2" s="21"/>
-      <c r="AF2" s="21"/>
-      <c r="AG2" s="21"/>
-      <c r="AH2" s="23"/>
-      <c r="AI2" s="22" t="s">
+      <c r="AD2" s="19"/>
+      <c r="AE2" s="19"/>
+      <c r="AF2" s="19"/>
+      <c r="AG2" s="19"/>
+      <c r="AH2" s="21"/>
+      <c r="AI2" s="20" t="s">
         <v>16</v>
       </c>
-      <c r="AJ2" s="21"/>
-      <c r="AK2" s="23"/>
-      <c r="AL2" s="22" t="s">
+      <c r="AJ2" s="19"/>
+      <c r="AK2" s="21"/>
+      <c r="AL2" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="AM2" s="21"/>
-      <c r="AN2" s="21"/>
-      <c r="AO2" s="21"/>
-      <c r="AP2" s="21"/>
-      <c r="AQ2" s="21"/>
-      <c r="AR2" s="23"/>
-      <c r="AS2" s="24" t="s">
+      <c r="AM2" s="19"/>
+      <c r="AN2" s="19"/>
+      <c r="AO2" s="19"/>
+      <c r="AP2" s="19"/>
+      <c r="AQ2" s="19"/>
+      <c r="AR2" s="21"/>
+      <c r="AS2" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="AT2" s="25"/>
-      <c r="AU2" s="26"/>
-      <c r="AV2" s="22" t="s">
+      <c r="AT2" s="23"/>
+      <c r="AU2" s="24"/>
+      <c r="AV2" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="AW2" s="21"/>
-      <c r="AX2" s="21"/>
-      <c r="AY2" s="23"/>
+      <c r="AW2" s="19"/>
+      <c r="AX2" s="19"/>
+      <c r="AY2" s="21"/>
     </row>
-    <row r="3" s="14" customFormat="1" spans="1:51">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="28" t="s">
+    <row r="3" s="12" customFormat="1" spans="1:51">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="28" t="s">
+      <c r="D3" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="28" t="s">
+      <c r="F3" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="28" t="s">
+      <c r="G3" s="26" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="28" t="s">
+      <c r="I3" s="26" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="29" t="s">
+      <c r="J3" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="29" t="s">
+      <c r="K3" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="29" t="s">
+      <c r="L3" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="29" t="s">
+      <c r="M3" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="29" t="s">
+      <c r="N3" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="29" t="s">
+      <c r="O3" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="29" t="s">
+      <c r="P3" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="29" t="s">
+      <c r="Q3" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="R3" s="29" t="s">
+      <c r="R3" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="29" t="s">
+      <c r="S3" s="27" t="s">
         <v>36</v>
       </c>
-      <c r="T3" s="29" t="s">
+      <c r="T3" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="29" t="s">
+      <c r="U3" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="V3" s="29" t="s">
+      <c r="V3" s="27" t="s">
         <v>39</v>
       </c>
-      <c r="W3" s="29" t="s">
+      <c r="W3" s="27" t="s">
         <v>40</v>
       </c>
-      <c r="X3" s="29" t="s">
+      <c r="X3" s="27" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="29" t="s">
+      <c r="Y3" s="27" t="s">
         <v>42</v>
       </c>
-      <c r="Z3" s="29" t="s">
+      <c r="Z3" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="AA3" s="29" t="s">
+      <c r="AA3" s="27" t="s">
         <v>44</v>
       </c>
-      <c r="AB3" s="29" t="s">
+      <c r="AB3" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="AC3" s="29" t="s">
+      <c r="AC3" s="27" t="s">
         <v>46</v>
       </c>
-      <c r="AD3" s="29" t="s">
+      <c r="AD3" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="AE3" s="29" t="s">
+      <c r="AE3" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="AF3" s="29" t="s">
+      <c r="AF3" s="27" t="s">
         <v>49</v>
       </c>
-      <c r="AG3" s="29" t="s">
+      <c r="AG3" s="27" t="s">
         <v>50</v>
       </c>
-      <c r="AH3" s="29" t="s">
+      <c r="AH3" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="AI3" s="29" t="s">
+      <c r="AI3" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="AJ3" s="29" t="s">
+      <c r="AJ3" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="AK3" s="29" t="s">
+      <c r="AK3" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="AL3" s="29" t="s">
+      <c r="AL3" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="AM3" s="29" t="s">
+      <c r="AM3" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="AN3" s="29" t="s">
+      <c r="AN3" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="AO3" s="29" t="s">
+      <c r="AO3" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="AP3" s="29" t="s">
+      <c r="AP3" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="AQ3" s="29" t="s">
+      <c r="AQ3" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="AR3" s="29" t="s">
+      <c r="AR3" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AS3" s="28" t="s">
+      <c r="AS3" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="AT3" s="28" t="s">
+      <c r="AT3" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="AU3" s="28" t="s">
+      <c r="AU3" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="AV3" s="28" t="s">
+      <c r="AV3" s="26" t="s">
         <v>65</v>
       </c>
-      <c r="AW3" s="28" t="s">
+      <c r="AW3" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="AX3" s="28" t="s">
+      <c r="AX3" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="AY3" s="28" t="s">
+      <c r="AY3" s="26" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" s="14" customFormat="1" ht="81" spans="1:51">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="30" t="s">
+    <row r="4" s="12" customFormat="1" ht="81" spans="1:51">
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="28" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="30" t="s">
+      <c r="H4" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="J4" s="28" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="30" t="s">
+      <c r="K4" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="30" t="s">
+      <c r="L4" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="30" t="s">
+      <c r="M4" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="N4" s="30" t="s">
+      <c r="N4" s="28" t="s">
         <v>80</v>
       </c>
-      <c r="O4" s="30" t="s">
+      <c r="O4" s="28" t="s">
         <v>81</v>
       </c>
-      <c r="P4" s="30" t="s">
+      <c r="P4" s="28" t="s">
         <v>82</v>
       </c>
-      <c r="Q4" s="30" t="s">
+      <c r="Q4" s="28" t="s">
         <v>83</v>
       </c>
-      <c r="R4" s="30" t="s">
+      <c r="R4" s="28" t="s">
         <v>84</v>
       </c>
-      <c r="S4" s="30" t="s">
+      <c r="S4" s="28" t="s">
         <v>85</v>
       </c>
-      <c r="T4" s="30" t="s">
+      <c r="T4" s="28" t="s">
         <v>86</v>
       </c>
-      <c r="U4" s="30" t="s">
+      <c r="U4" s="28" t="s">
         <v>87</v>
       </c>
-      <c r="V4" s="30" t="s">
+      <c r="V4" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="W4" s="30" t="s">
+      <c r="W4" s="28" t="s">
         <v>89</v>
       </c>
-      <c r="X4" s="30" t="s">
+      <c r="X4" s="28" t="s">
         <v>90</v>
       </c>
-      <c r="Y4" s="30" t="s">
+      <c r="Y4" s="28" t="s">
         <v>91</v>
       </c>
-      <c r="Z4" s="30" t="s">
+      <c r="Z4" s="28" t="s">
         <v>92</v>
       </c>
-      <c r="AA4" s="30" t="s">
+      <c r="AA4" s="28" t="s">
         <v>93</v>
       </c>
-      <c r="AB4" s="30" t="s">
+      <c r="AB4" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="AC4" s="30" t="s">
+      <c r="AC4" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="AD4" s="30" t="s">
+      <c r="AD4" s="28" t="s">
         <v>96</v>
       </c>
-      <c r="AE4" s="30" t="s">
+      <c r="AE4" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="AF4" s="30" t="s">
+      <c r="AF4" s="28" t="s">
         <v>98</v>
       </c>
-      <c r="AG4" s="30" t="s">
+      <c r="AG4" s="28" t="s">
         <v>99</v>
       </c>
-      <c r="AH4" s="30" t="s">
+      <c r="AH4" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="AI4" s="30" t="s">
+      <c r="AI4" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="AJ4" s="30" t="s">
+      <c r="AJ4" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="AK4" s="30" t="s">
+      <c r="AK4" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="AL4" s="30" t="s">
+      <c r="AL4" s="28" t="s">
         <v>104</v>
       </c>
-      <c r="AM4" s="30" t="s">
+      <c r="AM4" s="28" t="s">
         <v>105</v>
       </c>
-      <c r="AN4" s="30" t="s">
+      <c r="AN4" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="AO4" s="30" t="s">
+      <c r="AO4" s="28" t="s">
         <v>107</v>
       </c>
-      <c r="AP4" s="30" t="s">
+      <c r="AP4" s="28" t="s">
         <v>108</v>
       </c>
-      <c r="AQ4" s="30" t="s">
+      <c r="AQ4" s="28" t="s">
         <v>109</v>
       </c>
-      <c r="AR4" s="30" t="s">
+      <c r="AR4" s="28" t="s">
         <v>110</v>
       </c>
-      <c r="AS4" s="30" t="s">
+      <c r="AS4" s="28" t="s">
         <v>111</v>
       </c>
-      <c r="AT4" s="30" t="s">
+      <c r="AT4" s="28" t="s">
         <v>112</v>
       </c>
-      <c r="AU4" s="30" t="s">
+      <c r="AU4" s="28" t="s">
         <v>113</v>
       </c>
-      <c r="AV4" s="30" t="s">
+      <c r="AV4" s="28" t="s">
         <v>114</v>
       </c>
-      <c r="AW4" s="30" t="s">
+      <c r="AW4" s="28" t="s">
         <v>115</v>
       </c>
-      <c r="AX4" s="30" t="s">
+      <c r="AX4" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="AY4" s="30" t="s">
+      <c r="AY4" s="28" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" s="14" customFormat="1" ht="108" spans="1:51">
-      <c r="A5" s="27"/>
-      <c r="B5" s="27"/>
-      <c r="C5" s="30" t="s">
+    <row r="5" s="12" customFormat="1" ht="108" spans="1:51">
+      <c r="A5" s="25"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="D5" s="30" t="s">
+      <c r="D5" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="E5" s="30" t="s">
+      <c r="E5" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="F5" s="30" t="s">
+      <c r="F5" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="30" t="s">
+      <c r="G5" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="H5" s="30" t="s">
+      <c r="H5" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="I5" s="30" t="s">
+      <c r="I5" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="J5" s="30" t="s">
+      <c r="J5" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="K5" s="30" t="s">
+      <c r="K5" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="L5" s="30" t="s">
+      <c r="L5" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="M5" s="30" t="s">
+      <c r="M5" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="N5" s="30" t="s">
+      <c r="N5" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="O5" s="30" t="s">
+      <c r="O5" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="P5" s="30" t="s">
+      <c r="P5" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="Q5" s="30" t="s">
+      <c r="Q5" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="R5" s="30" t="s">
+      <c r="R5" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="S5" s="30" t="s">
+      <c r="S5" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="T5" s="30" t="s">
+      <c r="T5" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="U5" s="30" t="s">
+      <c r="U5" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="V5" s="30" t="s">
+      <c r="V5" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="W5" s="30" t="s">
+      <c r="W5" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="X5" s="30" t="s">
+      <c r="X5" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="Y5" s="30" t="s">
+      <c r="Y5" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="Z5" s="30" t="s">
+      <c r="Z5" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="AA5" s="30" t="s">
+      <c r="AA5" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="AB5" s="30" t="s">
+      <c r="AB5" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="AC5" s="30" t="s">
+      <c r="AC5" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="AD5" s="30" t="s">
+      <c r="AD5" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="AE5" s="30" t="s">
+      <c r="AE5" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="AF5" s="30" t="s">
+      <c r="AF5" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="AG5" s="30" t="s">
+      <c r="AG5" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="AH5" s="30" t="s">
+      <c r="AH5" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="AI5" s="30" t="s">
+      <c r="AI5" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="AJ5" s="30" t="s">
+      <c r="AJ5" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="AK5" s="30" t="s">
+      <c r="AK5" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="AL5" s="30" t="s">
+      <c r="AL5" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="AM5" s="30" t="s">
+      <c r="AM5" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="AN5" s="30" t="s">
+      <c r="AN5" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="AO5" s="30" t="s">
+      <c r="AO5" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="AP5" s="30" t="s">
+      <c r="AP5" s="28" t="s">
         <v>157</v>
       </c>
-      <c r="AQ5" s="30" t="s">
+      <c r="AQ5" s="28" t="s">
         <v>158</v>
       </c>
-      <c r="AR5" s="30" t="s">
+      <c r="AR5" s="28" t="s">
         <v>159</v>
       </c>
-      <c r="AS5" s="30" t="s">
+      <c r="AS5" s="28" t="s">
         <v>160</v>
       </c>
-      <c r="AT5" s="30" t="s">
+      <c r="AT5" s="28" t="s">
         <v>161</v>
       </c>
-      <c r="AU5" s="30" t="s">
+      <c r="AU5" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="AV5" s="30" t="s">
+      <c r="AV5" s="28" t="s">
         <v>163</v>
       </c>
-      <c r="AW5" s="30" t="s">
+      <c r="AW5" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="AX5" s="30" t="s">
+      <c r="AX5" s="28" t="s">
         <v>165</v>
       </c>
-      <c r="AY5" s="30" t="s">
+      <c r="AY5" s="28" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="6" s="14" customFormat="1" ht="27" spans="1:51">
-      <c r="A6" s="27"/>
-      <c r="B6" s="27"/>
-      <c r="C6" s="31" t="s">
+    <row r="6" s="12" customFormat="1" ht="27" spans="1:51">
+      <c r="A6" s="25"/>
+      <c r="B6" s="25"/>
+      <c r="C6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="D6" s="31" t="s">
+      <c r="D6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="E6" s="31" t="s">
+      <c r="E6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="F6" s="31" t="s">
+      <c r="F6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="H6" s="31" t="s">
+      <c r="H6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="I6" s="31" t="s">
+      <c r="I6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="J6" s="31" t="s">
+      <c r="J6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="K6" s="31" t="s">
+      <c r="K6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="L6" s="31" t="s">
+      <c r="L6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="M6" s="31" t="s">
+      <c r="M6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="N6" s="31" t="s">
+      <c r="N6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="O6" s="31" t="s">
+      <c r="O6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="P6" s="31" t="s">
+      <c r="P6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="Q6" s="31" t="s">
+      <c r="Q6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="R6" s="31" t="s">
+      <c r="R6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="S6" s="31" t="s">
+      <c r="S6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="T6" s="31" t="s">
+      <c r="T6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="U6" s="31" t="s">
+      <c r="U6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="V6" s="30" t="s">
+      <c r="V6" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="W6" s="31" t="s">
+      <c r="W6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="X6" s="31" t="s">
+      <c r="X6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="Y6" s="31" t="s">
+      <c r="Y6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="Z6" s="31" t="s">
+      <c r="Z6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AA6" s="31" t="s">
+      <c r="AA6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AB6" s="31" t="s">
+      <c r="AB6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AC6" s="31" t="s">
+      <c r="AC6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AD6" s="31" t="s">
+      <c r="AD6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AE6" s="31" t="s">
+      <c r="AE6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AF6" s="31" t="s">
+      <c r="AF6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AG6" s="31" t="s">
+      <c r="AG6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AH6" s="31" t="s">
+      <c r="AH6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AI6" s="31" t="s">
+      <c r="AI6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AJ6" s="31" t="s">
+      <c r="AJ6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AK6" s="31" t="s">
+      <c r="AK6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AL6" s="31" t="s">
+      <c r="AL6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AM6" s="31" t="s">
+      <c r="AM6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AN6" s="31" t="s">
+      <c r="AN6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AO6" s="31" t="s">
+      <c r="AO6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AP6" s="31" t="s">
+      <c r="AP6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AQ6" s="31" t="s">
+      <c r="AQ6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AR6" s="31" t="s">
+      <c r="AR6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AS6" s="31" t="s">
+      <c r="AS6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AT6" s="31" t="s">
+      <c r="AT6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AU6" s="31" t="s">
+      <c r="AU6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AV6" s="31" t="s">
+      <c r="AV6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AW6" s="31" t="s">
+      <c r="AW6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AX6" s="31" t="s">
+      <c r="AX6" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="AY6" s="31" t="s">
+      <c r="AY6" s="29" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="7" s="14" customFormat="1" ht="54" spans="1:51">
-      <c r="A7" s="32" t="s">
+    <row r="7" s="12" customFormat="1" ht="54" spans="1:51">
+      <c r="A7" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="C7" s="33" t="s">
+      <c r="C7" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="D7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="E7" s="31" t="s">
+      <c r="E7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="F7" s="31" t="s">
+      <c r="F7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="H7" s="31" t="s">
+      <c r="H7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="I7" s="31" t="s">
+      <c r="I7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="J7" s="31" t="s">
+      <c r="J7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="K7" s="31" t="s">
+      <c r="K7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="L7" s="31" t="s">
+      <c r="L7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="M7" s="31" t="s">
+      <c r="M7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="N7" s="31" t="s">
+      <c r="N7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="O7" s="31" t="s">
+      <c r="O7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="P7" s="31" t="s">
+      <c r="P7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="Q7" s="31" t="s">
+      <c r="Q7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="R7" s="31" t="s">
+      <c r="R7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="S7" s="31" t="s">
+      <c r="S7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="T7" s="31" t="s">
+      <c r="T7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="U7" s="31" t="s">
+      <c r="U7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="V7" s="30" t="s">
+      <c r="V7" s="28" t="s">
         <v>172</v>
       </c>
-      <c r="W7" s="31" t="s">
+      <c r="W7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="X7" s="31" t="s">
+      <c r="X7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="Y7" s="31" t="s">
+      <c r="Y7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="Z7" s="31" t="s">
+      <c r="Z7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AA7" s="31" t="s">
+      <c r="AA7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AB7" s="31" t="s">
+      <c r="AB7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AC7" s="31" t="s">
+      <c r="AC7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AD7" s="31" t="s">
+      <c r="AD7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AE7" s="31" t="s">
+      <c r="AE7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AF7" s="31" t="s">
+      <c r="AF7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AG7" s="31" t="s">
+      <c r="AG7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AH7" s="31" t="s">
+      <c r="AH7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AI7" s="31" t="s">
+      <c r="AI7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AJ7" s="31" t="s">
+      <c r="AJ7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AK7" s="31" t="s">
+      <c r="AK7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AL7" s="31" t="s">
+      <c r="AL7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AM7" s="31" t="s">
+      <c r="AM7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AN7" s="31" t="s">
+      <c r="AN7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AO7" s="31" t="s">
+      <c r="AO7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AP7" s="31" t="s">
+      <c r="AP7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AQ7" s="31" t="s">
+      <c r="AQ7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AR7" s="31" t="s">
+      <c r="AR7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AS7" s="31" t="s">
+      <c r="AS7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AT7" s="31" t="s">
+      <c r="AT7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AU7" s="31" t="s">
+      <c r="AU7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AV7" s="31" t="s">
+      <c r="AV7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AW7" s="31" t="s">
+      <c r="AW7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AX7" s="31" t="s">
+      <c r="AX7" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="AY7" s="31" t="s">
+      <c r="AY7" s="29" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="8" ht="67.5" spans="1:51">
-      <c r="A8" s="34"/>
-      <c r="B8" s="35" t="s">
+      <c r="A8" s="32"/>
+      <c r="B8" s="33" t="s">
         <v>173</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="C8" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="D8" s="36" t="s">
+      <c r="D8" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="E8" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="F8" s="36" t="s">
+      <c r="F8" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="G8" s="36" t="s">
+      <c r="G8" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="H8" s="36" t="s">
+      <c r="H8" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="I8" s="36" t="s">
+      <c r="I8" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="J8" s="36" t="s">
+      <c r="J8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="K8" s="36" t="s">
+      <c r="K8" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="L8" s="36" t="s">
+      <c r="L8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="M8" s="36" t="s">
+      <c r="M8" s="34" t="s">
         <v>183</v>
       </c>
-      <c r="N8" s="36" t="s">
+      <c r="N8" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="O8" s="36" t="s">
+      <c r="O8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="P8" s="36" t="s">
+      <c r="P8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="Q8" s="36" t="s">
+      <c r="Q8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="R8" s="36" t="s">
+      <c r="R8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="S8" s="36" t="s">
+      <c r="S8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="T8" s="36" t="s">
+      <c r="T8" s="34" t="s">
         <v>185</v>
       </c>
-      <c r="U8" s="36" t="s">
+      <c r="U8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="V8" s="36" t="s">
+      <c r="V8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="W8" s="36" t="s">
+      <c r="W8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="X8" s="36" t="s">
+      <c r="X8" s="34" t="s">
         <v>186</v>
       </c>
-      <c r="Y8" s="36" t="s">
+      <c r="Y8" s="34" t="s">
         <v>187</v>
       </c>
-      <c r="Z8" s="36" t="s">
+      <c r="Z8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AA8" s="36" t="s">
+      <c r="AA8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AB8" s="36" t="s">
+      <c r="AB8" s="34" t="s">
         <v>188</v>
       </c>
-      <c r="AC8" s="36" t="s">
+      <c r="AC8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AD8" s="36" t="s">
+      <c r="AD8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AE8" s="36" t="s">
+      <c r="AE8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AF8" s="36" t="s">
+      <c r="AF8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AG8" s="36" t="s">
+      <c r="AG8" s="34" t="s">
         <v>189</v>
       </c>
-      <c r="AH8" s="36" t="s">
+      <c r="AH8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AI8" s="36" t="s">
+      <c r="AI8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AJ8" s="36" t="s">
+      <c r="AJ8" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="AK8" s="36" t="s">
+      <c r="AK8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AL8" s="36" t="s">
+      <c r="AL8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AM8" s="36" t="s">
+      <c r="AM8" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="AN8" s="36" t="s">
+      <c r="AN8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AO8" s="36" t="s">
+      <c r="AO8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AP8" s="36" t="s">
+      <c r="AP8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AQ8" s="36" t="s">
+      <c r="AQ8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="AR8" s="36" t="s">
+      <c r="AR8" s="34" t="s">
         <v>190</v>
       </c>
-      <c r="AS8" s="37" t="s">
+      <c r="AS8" s="35" t="s">
         <v>192</v>
       </c>
-      <c r="AT8" s="37" t="s">
+      <c r="AT8" s="35" t="s">
         <v>193</v>
       </c>
-      <c r="AU8" s="37" t="s">
+      <c r="AU8" s="35" t="s">
         <v>194</v>
       </c>
-      <c r="AV8" s="37" t="s">
+      <c r="AV8" s="35" t="s">
         <v>195</v>
       </c>
-      <c r="AW8" s="37" t="s">
+      <c r="AW8" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="AX8" s="38" t="s">
+      <c r="AX8" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="AY8" s="38" t="s">
+      <c r="AY8" s="36" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="9" ht="40.5" spans="1:51">
-      <c r="A9" s="34"/>
-      <c r="B9" s="39" t="s">
+      <c r="A9" s="32"/>
+      <c r="B9" s="37" t="s">
         <v>196</v>
       </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37" t="s">
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
+      <c r="E9" s="35"/>
+      <c r="F9" s="35"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="35" t="s">
         <v>197</v>
       </c>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="37" t="s">
+      <c r="L9" s="35"/>
+      <c r="M9" s="35"/>
+      <c r="N9" s="35" t="s">
         <v>198</v>
       </c>
-      <c r="O9" s="37"/>
-      <c r="P9" s="37"/>
-      <c r="Q9" s="37"/>
-      <c r="R9" s="37"/>
-      <c r="S9" s="37"/>
-      <c r="T9" s="37"/>
-      <c r="U9" s="37"/>
-      <c r="V9" s="37"/>
-      <c r="W9" s="37"/>
-      <c r="X9" s="37"/>
-      <c r="Y9" s="37"/>
-      <c r="Z9" s="37"/>
-      <c r="AA9" s="37"/>
-      <c r="AB9" s="37"/>
-      <c r="AC9" s="37"/>
-      <c r="AD9" s="37"/>
-      <c r="AE9" s="37"/>
-      <c r="AF9" s="37"/>
-      <c r="AG9" s="37"/>
-      <c r="AH9" s="37"/>
-      <c r="AI9" s="37"/>
-      <c r="AJ9" s="37"/>
-      <c r="AK9" s="37"/>
-      <c r="AL9" s="37"/>
-      <c r="AM9" s="37"/>
-      <c r="AN9" s="37"/>
-      <c r="AO9" s="37"/>
-      <c r="AP9" s="37"/>
-      <c r="AQ9" s="37"/>
-      <c r="AR9" s="37"/>
-      <c r="AS9" s="37"/>
-      <c r="AT9" s="37"/>
-      <c r="AU9" s="37"/>
-      <c r="AV9" s="37"/>
-      <c r="AW9" s="37"/>
-      <c r="AX9" s="38"/>
-      <c r="AY9" s="38"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="35"/>
+      <c r="W9" s="35"/>
+      <c r="X9" s="35"/>
+      <c r="Y9" s="35"/>
+      <c r="Z9" s="35"/>
+      <c r="AA9" s="35"/>
+      <c r="AB9" s="35"/>
+      <c r="AC9" s="35"/>
+      <c r="AD9" s="35"/>
+      <c r="AE9" s="35"/>
+      <c r="AF9" s="35"/>
+      <c r="AG9" s="35"/>
+      <c r="AH9" s="35"/>
+      <c r="AI9" s="35"/>
+      <c r="AJ9" s="35"/>
+      <c r="AK9" s="35"/>
+      <c r="AL9" s="35"/>
+      <c r="AM9" s="35"/>
+      <c r="AN9" s="35"/>
+      <c r="AO9" s="35"/>
+      <c r="AP9" s="35"/>
+      <c r="AQ9" s="35"/>
+      <c r="AR9" s="35"/>
+      <c r="AS9" s="35"/>
+      <c r="AT9" s="35"/>
+      <c r="AU9" s="35"/>
+      <c r="AV9" s="35"/>
+      <c r="AW9" s="35"/>
+      <c r="AX9" s="36"/>
+      <c r="AY9" s="36"/>
     </row>
     <row r="10" ht="81" spans="1:51">
-      <c r="A10" s="40"/>
-      <c r="B10" s="39" t="s">
+      <c r="A10" s="38"/>
+      <c r="B10" s="37" t="s">
         <v>199</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="37"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="37"/>
-      <c r="I10" s="37"/>
-      <c r="J10" s="37"/>
-      <c r="K10" s="37" t="s">
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
+      <c r="E10" s="35"/>
+      <c r="F10" s="35"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="35"/>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="35" t="s">
         <v>200</v>
       </c>
-      <c r="L10" s="37" t="s">
+      <c r="L10" s="35" t="s">
         <v>201</v>
       </c>
-      <c r="M10" s="37"/>
-      <c r="N10" s="37" t="s">
+      <c r="M10" s="35"/>
+      <c r="N10" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="O10" s="37"/>
-      <c r="P10" s="37"/>
-      <c r="Q10" s="37"/>
-      <c r="R10" s="37"/>
-      <c r="S10" s="37"/>
-      <c r="T10" s="37"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="37"/>
-      <c r="W10" s="37"/>
-      <c r="X10" s="37"/>
-      <c r="Y10" s="37"/>
-      <c r="Z10" s="37"/>
-      <c r="AA10" s="37" t="s">
+      <c r="O10" s="35"/>
+      <c r="P10" s="35"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+      <c r="X10" s="35"/>
+      <c r="Y10" s="35"/>
+      <c r="Z10" s="35"/>
+      <c r="AA10" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="AB10" s="37"/>
-      <c r="AC10" s="37"/>
-      <c r="AD10" s="37"/>
-      <c r="AE10" s="37"/>
-      <c r="AF10" s="37"/>
-      <c r="AG10" s="37"/>
-      <c r="AH10" s="37"/>
-      <c r="AI10" s="37"/>
-      <c r="AJ10" s="37" t="s">
+      <c r="AB10" s="35"/>
+      <c r="AC10" s="35"/>
+      <c r="AD10" s="35"/>
+      <c r="AE10" s="35"/>
+      <c r="AF10" s="35"/>
+      <c r="AG10" s="35"/>
+      <c r="AH10" s="35"/>
+      <c r="AI10" s="35"/>
+      <c r="AJ10" s="35" t="s">
         <v>204</v>
       </c>
-      <c r="AK10" s="37"/>
-      <c r="AL10" s="37"/>
-      <c r="AM10" s="37"/>
-      <c r="AN10" s="37"/>
-      <c r="AO10" s="37"/>
-      <c r="AP10" s="37"/>
-      <c r="AQ10" s="37"/>
-      <c r="AR10" s="37"/>
-      <c r="AS10" s="37"/>
-      <c r="AT10" s="37"/>
-      <c r="AU10" s="37"/>
-      <c r="AV10" s="37"/>
-      <c r="AW10" s="37"/>
-      <c r="AX10" s="38"/>
-      <c r="AY10" s="38"/>
+      <c r="AK10" s="35"/>
+      <c r="AL10" s="35"/>
+      <c r="AM10" s="35"/>
+      <c r="AN10" s="35"/>
+      <c r="AO10" s="35"/>
+      <c r="AP10" s="35"/>
+      <c r="AQ10" s="35"/>
+      <c r="AR10" s="35"/>
+      <c r="AS10" s="35"/>
+      <c r="AT10" s="35"/>
+      <c r="AU10" s="35"/>
+      <c r="AV10" s="35"/>
+      <c r="AW10" s="35"/>
+      <c r="AX10" s="36"/>
+      <c r="AY10" s="36"/>
     </row>
     <row r="11" spans="1:51">
-      <c r="A11" s="41" t="s">
+      <c r="A11" s="39" t="s">
         <v>205</v>
       </c>
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="40" t="s">
         <v>206</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="15"/>
-      <c r="O11" s="15"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="15"/>
-      <c r="R11" s="15"/>
-      <c r="S11" s="15"/>
-      <c r="T11" s="15"/>
-      <c r="U11" s="15"/>
-      <c r="V11" s="15"/>
-      <c r="W11" s="15"/>
-      <c r="X11" s="15"/>
-      <c r="Y11" s="15"/>
-      <c r="Z11" s="15"/>
-      <c r="AA11" s="15"/>
-      <c r="AB11" s="15"/>
-      <c r="AC11" s="15"/>
-      <c r="AD11" s="15"/>
-      <c r="AE11" s="15"/>
-      <c r="AF11" s="15"/>
-      <c r="AG11" s="15"/>
-      <c r="AH11" s="15"/>
-      <c r="AI11" s="15"/>
-      <c r="AJ11" s="15"/>
-      <c r="AK11" s="15"/>
-      <c r="AL11" s="15"/>
-      <c r="AM11" s="15"/>
-      <c r="AN11" s="15"/>
-      <c r="AO11" s="15"/>
-      <c r="AP11" s="15"/>
-      <c r="AQ11" s="15"/>
-      <c r="AR11" s="15"/>
-      <c r="AS11" s="15"/>
-      <c r="AT11" s="15"/>
-      <c r="AU11" s="15"/>
-      <c r="AV11" s="15"/>
-      <c r="AW11" s="15"/>
-      <c r="AX11" s="15"/>
-      <c r="AY11" s="15"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="13"/>
+      <c r="AC11" s="13"/>
+      <c r="AD11" s="13"/>
+      <c r="AE11" s="13"/>
+      <c r="AF11" s="13"/>
+      <c r="AG11" s="13"/>
+      <c r="AH11" s="13"/>
+      <c r="AI11" s="13"/>
+      <c r="AJ11" s="13"/>
+      <c r="AK11" s="13"/>
+      <c r="AL11" s="13"/>
+      <c r="AM11" s="13"/>
+      <c r="AN11" s="13"/>
+      <c r="AO11" s="13"/>
+      <c r="AP11" s="13"/>
+      <c r="AQ11" s="13"/>
+      <c r="AR11" s="13"/>
+      <c r="AS11" s="13"/>
+      <c r="AT11" s="13"/>
+      <c r="AU11" s="13"/>
+      <c r="AV11" s="13"/>
+      <c r="AW11" s="13"/>
+      <c r="AX11" s="13"/>
+      <c r="AY11" s="13"/>
     </row>
     <row r="12" spans="1:51">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="41" t="s">
         <v>208</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
-      <c r="U12" s="15"/>
-      <c r="V12" s="15"/>
-      <c r="W12" s="15"/>
-      <c r="X12" s="15"/>
-      <c r="Y12" s="15"/>
-      <c r="Z12" s="15"/>
-      <c r="AA12" s="15"/>
-      <c r="AB12" s="15"/>
-      <c r="AC12" s="15"/>
-      <c r="AD12" s="15"/>
-      <c r="AE12" s="15"/>
-      <c r="AF12" s="15"/>
-      <c r="AG12" s="15"/>
-      <c r="AH12" s="15"/>
-      <c r="AI12" s="15"/>
-      <c r="AJ12" s="15"/>
-      <c r="AK12" s="15"/>
-      <c r="AL12" s="15"/>
-      <c r="AM12" s="15"/>
-      <c r="AN12" s="15"/>
-      <c r="AO12" s="15"/>
-      <c r="AP12" s="15"/>
-      <c r="AQ12" s="15"/>
-      <c r="AR12" s="15"/>
-      <c r="AS12" s="15"/>
-      <c r="AT12" s="15"/>
-      <c r="AU12" s="15"/>
-      <c r="AV12" s="15"/>
-      <c r="AW12" s="15"/>
-      <c r="AX12" s="15"/>
-      <c r="AY12" s="15"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="13"/>
+      <c r="M12" s="13"/>
+      <c r="N12" s="13"/>
+      <c r="O12" s="13"/>
+      <c r="P12" s="13"/>
+      <c r="Q12" s="13"/>
+      <c r="R12" s="13"/>
+      <c r="S12" s="13"/>
+      <c r="T12" s="13"/>
+      <c r="U12" s="13"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="13"/>
+      <c r="AB12" s="13"/>
+      <c r="AC12" s="13"/>
+      <c r="AD12" s="13"/>
+      <c r="AE12" s="13"/>
+      <c r="AF12" s="13"/>
+      <c r="AG12" s="13"/>
+      <c r="AH12" s="13"/>
+      <c r="AI12" s="13"/>
+      <c r="AJ12" s="13"/>
+      <c r="AK12" s="13"/>
+      <c r="AL12" s="13"/>
+      <c r="AM12" s="13"/>
+      <c r="AN12" s="13"/>
+      <c r="AO12" s="13"/>
+      <c r="AP12" s="13"/>
+      <c r="AQ12" s="13"/>
+      <c r="AR12" s="13"/>
+      <c r="AS12" s="13"/>
+      <c r="AT12" s="13"/>
+      <c r="AU12" s="13"/>
+      <c r="AV12" s="13"/>
+      <c r="AW12" s="13"/>
+      <c r="AX12" s="13"/>
+      <c r="AY12" s="13"/>
     </row>
     <row r="14" ht="94.5" spans="1:51">
-      <c r="A14" s="44" t="s">
+      <c r="A14" s="42" t="s">
         <v>209</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B14" s="43" t="s">
         <v>210</v>
       </c>
-      <c r="C14" s="46"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47" t="s">
+      <c r="C14" s="44"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="45"/>
+      <c r="F14" s="45" t="s">
         <v>211</v>
       </c>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47" t="s">
+      <c r="G14" s="45"/>
+      <c r="H14" s="45" t="s">
         <v>212</v>
       </c>
-      <c r="I14" s="47"/>
-      <c r="J14" s="47"/>
-      <c r="K14" s="47" t="s">
+      <c r="I14" s="45"/>
+      <c r="J14" s="45"/>
+      <c r="K14" s="45" t="s">
         <v>213</v>
       </c>
-      <c r="L14" s="47" t="s">
+      <c r="L14" s="45" t="s">
         <v>214</v>
       </c>
-      <c r="M14" s="47" t="s">
+      <c r="M14" s="45" t="s">
         <v>215</v>
       </c>
-      <c r="N14" s="47" t="s">
+      <c r="N14" s="45" t="s">
         <v>216</v>
       </c>
-      <c r="O14" s="47"/>
-      <c r="P14" s="47"/>
-      <c r="Q14" s="47" t="s">
+      <c r="O14" s="45"/>
+      <c r="P14" s="45"/>
+      <c r="Q14" s="45" t="s">
         <v>217</v>
       </c>
-      <c r="R14" s="47" t="s">
+      <c r="R14" s="45" t="s">
         <v>218</v>
       </c>
-      <c r="S14" s="47" t="s">
+      <c r="S14" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="T14" s="47" t="s">
+      <c r="T14" s="45" t="s">
         <v>220</v>
       </c>
-      <c r="U14" s="47" t="s">
+      <c r="U14" s="45" t="s">
         <v>221</v>
       </c>
-      <c r="V14" s="47"/>
-      <c r="W14" s="47" t="s">
+      <c r="V14" s="45"/>
+      <c r="W14" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="X14" s="47" t="s">
+      <c r="X14" s="45" t="s">
         <v>222</v>
       </c>
-      <c r="Y14" s="47" t="s">
+      <c r="Y14" s="45" t="s">
         <v>223</v>
       </c>
-      <c r="Z14" s="47" t="s">
+      <c r="Z14" s="45" t="s">
         <v>224</v>
       </c>
-      <c r="AA14" s="47" t="s">
+      <c r="AA14" s="45" t="s">
         <v>225</v>
       </c>
-      <c r="AB14" s="47" t="s">
+      <c r="AB14" s="45" t="s">
         <v>226</v>
       </c>
-      <c r="AC14" s="47" t="s">
+      <c r="AC14" s="45" t="s">
         <v>227</v>
       </c>
-      <c r="AD14" s="47" t="s">
+      <c r="AD14" s="45" t="s">
         <v>228</v>
       </c>
-      <c r="AE14" s="47" t="s">
+      <c r="AE14" s="45" t="s">
         <v>229</v>
       </c>
-      <c r="AF14" s="47" t="s">
+      <c r="AF14" s="45" t="s">
         <v>230</v>
       </c>
-      <c r="AG14" s="47"/>
-      <c r="AH14" s="47" t="s">
+      <c r="AG14" s="45"/>
+      <c r="AH14" s="45" t="s">
         <v>231</v>
       </c>
-      <c r="AI14" s="47" t="s">
+      <c r="AI14" s="45" t="s">
         <v>232</v>
       </c>
-      <c r="AJ14" s="47" t="s">
+      <c r="AJ14" s="45" t="s">
         <v>233</v>
       </c>
-      <c r="AK14" s="47"/>
-      <c r="AL14" s="47"/>
-      <c r="AM14" s="47" t="s">
+      <c r="AK14" s="45"/>
+      <c r="AL14" s="45"/>
+      <c r="AM14" s="45" t="s">
         <v>234</v>
       </c>
-      <c r="AN14" s="47" t="s">
+      <c r="AN14" s="45" t="s">
         <v>235</v>
       </c>
-      <c r="AO14" s="47" t="s">
+      <c r="AO14" s="45" t="s">
         <v>236</v>
       </c>
-      <c r="AP14" s="47" t="s">
+      <c r="AP14" s="45" t="s">
         <v>237</v>
       </c>
-      <c r="AQ14" s="47"/>
-      <c r="AR14" s="47" t="s">
+      <c r="AQ14" s="45"/>
+      <c r="AR14" s="45" t="s">
         <v>238</v>
       </c>
-      <c r="AS14" s="48" t="s">
+      <c r="AS14" s="46" t="s">
         <v>239</v>
       </c>
-      <c r="AT14" s="47" t="s">
+      <c r="AT14" s="45" t="s">
         <v>240</v>
       </c>
-      <c r="AU14" s="47" t="s">
+      <c r="AU14" s="45" t="s">
         <v>241</v>
       </c>
-      <c r="AV14" s="38"/>
-      <c r="AW14" s="38"/>
-      <c r="AX14" s="37" t="s">
+      <c r="AV14" s="36"/>
+      <c r="AW14" s="36"/>
+      <c r="AX14" s="35" t="s">
         <v>242</v>
       </c>
-      <c r="AY14" s="37"/>
+      <c r="AY14" s="35"/>
     </row>
     <row r="15" spans="1:51">
-      <c r="A15" s="49"/>
-      <c r="B15" s="50" t="s">
+      <c r="A15" s="47"/>
+      <c r="B15" s="48" t="s">
         <v>243</v>
       </c>
-      <c r="C15" s="51"/>
-      <c r="D15" s="43"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="43"/>
-      <c r="G15" s="43"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
-      <c r="J15" s="43"/>
-      <c r="K15" s="43"/>
-      <c r="L15" s="43"/>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="43"/>
-      <c r="P15" s="43"/>
-      <c r="Q15" s="43"/>
-      <c r="R15" s="43"/>
-      <c r="S15" s="43"/>
-      <c r="T15" s="43"/>
-      <c r="U15" s="43"/>
-      <c r="V15" s="43"/>
-      <c r="W15" s="43"/>
-      <c r="X15" s="43"/>
-      <c r="Y15" s="43"/>
-      <c r="Z15" s="43"/>
-      <c r="AA15" s="43"/>
-      <c r="AB15" s="43"/>
-      <c r="AC15" s="43"/>
-      <c r="AD15" s="43"/>
-      <c r="AE15" s="43"/>
-      <c r="AF15" s="43"/>
-      <c r="AG15" s="43"/>
-      <c r="AH15" s="43"/>
-      <c r="AI15" s="43"/>
-      <c r="AJ15" s="43"/>
-      <c r="AK15" s="43"/>
-      <c r="AL15" s="43"/>
-      <c r="AM15" s="43"/>
-      <c r="AN15" s="43"/>
-      <c r="AO15" s="43"/>
-      <c r="AP15" s="43"/>
-      <c r="AQ15" s="43"/>
-      <c r="AR15" s="43"/>
-      <c r="AS15" s="43"/>
-      <c r="AT15" s="43"/>
-      <c r="AU15" s="43"/>
-      <c r="AV15" s="43"/>
-      <c r="AW15" s="43"/>
-      <c r="AX15" s="43"/>
-      <c r="AY15" s="43"/>
+      <c r="C15" s="49"/>
+      <c r="D15" s="41"/>
+      <c r="E15" s="41"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="41"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="41"/>
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="41"/>
+      <c r="P15" s="41"/>
+      <c r="Q15" s="41"/>
+      <c r="R15" s="41"/>
+      <c r="S15" s="41"/>
+      <c r="T15" s="41"/>
+      <c r="U15" s="41"/>
+      <c r="V15" s="41"/>
+      <c r="W15" s="41"/>
+      <c r="X15" s="41"/>
+      <c r="Y15" s="41"/>
+      <c r="Z15" s="41"/>
+      <c r="AA15" s="41"/>
+      <c r="AB15" s="41"/>
+      <c r="AC15" s="41"/>
+      <c r="AD15" s="41"/>
+      <c r="AE15" s="41"/>
+      <c r="AF15" s="41"/>
+      <c r="AG15" s="41"/>
+      <c r="AH15" s="41"/>
+      <c r="AI15" s="41"/>
+      <c r="AJ15" s="41"/>
+      <c r="AK15" s="41"/>
+      <c r="AL15" s="41"/>
+      <c r="AM15" s="41"/>
+      <c r="AN15" s="41"/>
+      <c r="AO15" s="41"/>
+      <c r="AP15" s="41"/>
+      <c r="AQ15" s="41"/>
+      <c r="AR15" s="41"/>
+      <c r="AS15" s="41"/>
+      <c r="AT15" s="41"/>
+      <c r="AU15" s="41"/>
+      <c r="AV15" s="41"/>
+      <c r="AW15" s="41"/>
+      <c r="AX15" s="41"/>
+      <c r="AY15" s="41"/>
     </row>
     <row r="16" ht="67.5" spans="1:51">
-      <c r="A16" s="49"/>
-      <c r="B16" s="50" t="s">
+      <c r="A16" s="47"/>
+      <c r="B16" s="48" t="s">
         <v>244</v>
       </c>
-      <c r="C16" s="52" t="s">
+      <c r="C16" s="50" t="s">
         <v>245</v>
       </c>
-      <c r="D16" s="53" t="s">
+      <c r="D16" s="51" t="s">
         <v>246</v>
       </c>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="43"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="53" t="s">
+      <c r="E16" s="41"/>
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41"/>
+      <c r="J16" s="41"/>
+      <c r="K16" s="51" t="s">
         <v>247</v>
       </c>
-      <c r="L16" s="43"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="43"/>
-      <c r="Q16" s="43"/>
-      <c r="R16" s="43"/>
-      <c r="S16" s="43"/>
-      <c r="T16" s="43"/>
-      <c r="U16" s="43"/>
-      <c r="V16" s="43"/>
-      <c r="W16" s="43"/>
-      <c r="X16" s="43"/>
-      <c r="Y16" s="43"/>
-      <c r="Z16" s="53" t="s">
+      <c r="L16" s="41"/>
+      <c r="M16" s="41"/>
+      <c r="N16" s="41"/>
+      <c r="O16" s="41"/>
+      <c r="P16" s="41"/>
+      <c r="Q16" s="41"/>
+      <c r="R16" s="41"/>
+      <c r="S16" s="41"/>
+      <c r="T16" s="41"/>
+      <c r="U16" s="41"/>
+      <c r="V16" s="41"/>
+      <c r="W16" s="41"/>
+      <c r="X16" s="41"/>
+      <c r="Y16" s="41"/>
+      <c r="Z16" s="51" t="s">
         <v>248</v>
       </c>
-      <c r="AA16" s="43" t="s">
+      <c r="AA16" s="41" t="s">
         <v>249</v>
       </c>
-      <c r="AB16" s="53" t="s">
+      <c r="AB16" s="51" t="s">
         <v>250</v>
       </c>
-      <c r="AC16" s="43"/>
-      <c r="AD16" s="43"/>
-      <c r="AE16" s="43"/>
-      <c r="AF16" s="43"/>
-      <c r="AG16" s="43"/>
-      <c r="AH16" s="43"/>
-      <c r="AI16" s="43"/>
-      <c r="AJ16" s="43"/>
-      <c r="AK16" s="43"/>
-      <c r="AL16" s="43"/>
-      <c r="AM16" s="53" t="s">
+      <c r="AC16" s="41"/>
+      <c r="AD16" s="41"/>
+      <c r="AE16" s="41"/>
+      <c r="AF16" s="41"/>
+      <c r="AG16" s="41"/>
+      <c r="AH16" s="41"/>
+      <c r="AI16" s="41"/>
+      <c r="AJ16" s="41"/>
+      <c r="AK16" s="41"/>
+      <c r="AL16" s="41"/>
+      <c r="AM16" s="51" t="s">
         <v>251</v>
       </c>
-      <c r="AN16" s="43"/>
-      <c r="AO16" s="43" t="s">
+      <c r="AN16" s="41"/>
+      <c r="AO16" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="AP16" s="43" t="s">
+      <c r="AP16" s="41" t="s">
         <v>252</v>
       </c>
-      <c r="AQ16" s="43"/>
-      <c r="AR16" s="43"/>
-      <c r="AS16" s="43" t="s">
+      <c r="AQ16" s="41"/>
+      <c r="AR16" s="41"/>
+      <c r="AS16" s="41" t="s">
         <v>253</v>
       </c>
-      <c r="AT16" s="43"/>
-      <c r="AU16" s="43"/>
-      <c r="AV16" s="53" t="s">
+      <c r="AT16" s="41"/>
+      <c r="AU16" s="41"/>
+      <c r="AV16" s="51" t="s">
         <v>254</v>
       </c>
-      <c r="AW16" s="43"/>
-      <c r="AX16" s="43"/>
-      <c r="AY16" s="43"/>
+      <c r="AW16" s="41"/>
+      <c r="AX16" s="41"/>
+      <c r="AY16" s="41"/>
     </row>
     <row r="17" ht="81" spans="1:51">
-      <c r="A17" s="49"/>
-      <c r="B17" s="50" t="s">
+      <c r="A17" s="47"/>
+      <c r="B17" s="48" t="s">
         <v>255</v>
       </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="43"/>
-      <c r="E17" s="43"/>
-      <c r="F17" s="43"/>
-      <c r="G17" s="53" t="s">
+      <c r="C17" s="49"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="51" t="s">
         <v>256</v>
       </c>
-      <c r="H17" s="43"/>
-      <c r="I17" s="53" t="s">
+      <c r="H17" s="41"/>
+      <c r="I17" s="51" t="s">
         <v>257</v>
       </c>
-      <c r="J17" s="43"/>
-      <c r="K17" s="43" t="s">
+      <c r="J17" s="41"/>
+      <c r="K17" s="41" t="s">
         <v>258</v>
       </c>
-      <c r="L17" s="43" t="s">
+      <c r="L17" s="41" t="s">
         <v>259</v>
       </c>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="53" t="s">
+      <c r="M17" s="41"/>
+      <c r="N17" s="41"/>
+      <c r="O17" s="51" t="s">
         <v>260</v>
       </c>
-      <c r="P17" s="43"/>
-      <c r="Q17" s="43"/>
-      <c r="R17" s="43"/>
-      <c r="S17" s="53" t="s">
+      <c r="P17" s="41"/>
+      <c r="Q17" s="41"/>
+      <c r="R17" s="41"/>
+      <c r="S17" s="51" t="s">
         <v>261</v>
       </c>
-      <c r="T17" s="53" t="s">
+      <c r="T17" s="51" t="s">
         <v>262</v>
       </c>
-      <c r="U17" s="53" t="s">
+      <c r="U17" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="V17" s="43"/>
-      <c r="W17" s="53" t="s">
+      <c r="V17" s="41"/>
+      <c r="W17" s="51" t="s">
         <v>264</v>
       </c>
-      <c r="X17" s="43" t="s">
+      <c r="X17" s="41" t="s">
         <v>265</v>
       </c>
-      <c r="Y17" s="53" t="s">
+      <c r="Y17" s="51" t="s">
         <v>266</v>
       </c>
-      <c r="Z17" s="53" t="s">
+      <c r="Z17" s="51" t="s">
         <v>267</v>
       </c>
-      <c r="AA17" s="53" t="s">
+      <c r="AA17" s="51" t="s">
         <v>268</v>
       </c>
-      <c r="AB17" s="53" t="s">
+      <c r="AB17" s="51" t="s">
         <v>269</v>
       </c>
-      <c r="AC17" s="43"/>
-      <c r="AD17" s="43"/>
-      <c r="AE17" s="43"/>
-      <c r="AF17" s="43"/>
-      <c r="AG17" s="43"/>
-      <c r="AH17" s="53" t="s">
+      <c r="AC17" s="41"/>
+      <c r="AD17" s="41"/>
+      <c r="AE17" s="41"/>
+      <c r="AF17" s="41"/>
+      <c r="AG17" s="41"/>
+      <c r="AH17" s="51" t="s">
         <v>270</v>
       </c>
-      <c r="AI17" s="43"/>
-      <c r="AJ17" s="43"/>
-      <c r="AK17" s="43"/>
-      <c r="AL17" s="43" t="s">
+      <c r="AI17" s="41"/>
+      <c r="AJ17" s="41"/>
+      <c r="AK17" s="41"/>
+      <c r="AL17" s="41" t="s">
         <v>271</v>
       </c>
-      <c r="AM17" s="53" t="s">
+      <c r="AM17" s="51" t="s">
         <v>272</v>
       </c>
-      <c r="AN17" s="53" t="s">
+      <c r="AN17" s="51" t="s">
         <v>273</v>
       </c>
-      <c r="AO17" s="53" t="s">
+      <c r="AO17" s="51" t="s">
         <v>274</v>
       </c>
-      <c r="AP17" s="53" t="s">
+      <c r="AP17" s="51" t="s">
         <v>275</v>
       </c>
-      <c r="AQ17" s="43"/>
-      <c r="AR17" s="53" t="s">
+      <c r="AQ17" s="41"/>
+      <c r="AR17" s="51" t="s">
         <v>276</v>
       </c>
-      <c r="AS17" s="43" t="s">
+      <c r="AS17" s="41" t="s">
         <v>277</v>
       </c>
-      <c r="AT17" s="43" t="s">
+      <c r="AT17" s="41" t="s">
         <v>278</v>
       </c>
-      <c r="AU17" s="53" t="s">
+      <c r="AU17" s="51" t="s">
         <v>279</v>
       </c>
-      <c r="AV17" s="53" t="s">
+      <c r="AV17" s="51" t="s">
         <v>280</v>
       </c>
-      <c r="AW17" s="53" t="s">
+      <c r="AW17" s="51" t="s">
         <v>281</v>
       </c>
-      <c r="AX17" s="43"/>
-      <c r="AY17" s="53" t="s">
+      <c r="AX17" s="41"/>
+      <c r="AY17" s="51" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="18" ht="81" spans="1:51">
-      <c r="A18" s="49"/>
-      <c r="B18" s="50" t="s">
+      <c r="A18" s="47"/>
+      <c r="B18" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="C18" s="51"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="53" t="s">
+      <c r="C18" s="49"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="51" t="s">
         <v>284</v>
       </c>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-      <c r="P18" s="43"/>
-      <c r="Q18" s="43"/>
-      <c r="R18" s="43"/>
-      <c r="S18" s="43"/>
-      <c r="T18" s="43"/>
-      <c r="U18" s="43"/>
-      <c r="V18" s="43"/>
-      <c r="W18" s="43"/>
-      <c r="X18" s="43"/>
-      <c r="Y18" s="43"/>
-      <c r="Z18" s="53" t="s">
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="41"/>
+      <c r="P18" s="41"/>
+      <c r="Q18" s="41"/>
+      <c r="R18" s="41"/>
+      <c r="S18" s="41"/>
+      <c r="T18" s="41"/>
+      <c r="U18" s="41"/>
+      <c r="V18" s="41"/>
+      <c r="W18" s="41"/>
+      <c r="X18" s="41"/>
+      <c r="Y18" s="41"/>
+      <c r="Z18" s="51" t="s">
         <v>285</v>
       </c>
-      <c r="AA18" s="53" t="s">
+      <c r="AA18" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="AB18" s="53" t="s">
+      <c r="AB18" s="51" t="s">
         <v>287</v>
       </c>
-      <c r="AC18" s="53" t="s">
+      <c r="AC18" s="51" t="s">
         <v>288</v>
       </c>
-      <c r="AD18" s="43"/>
-      <c r="AE18" s="43"/>
-      <c r="AF18" s="43"/>
-      <c r="AG18" s="43"/>
-      <c r="AH18" s="43"/>
-      <c r="AI18" s="43" t="s">
+      <c r="AD18" s="41"/>
+      <c r="AE18" s="41"/>
+      <c r="AF18" s="41"/>
+      <c r="AG18" s="41"/>
+      <c r="AH18" s="41"/>
+      <c r="AI18" s="41" t="s">
         <v>289</v>
       </c>
-      <c r="AJ18" s="43"/>
-      <c r="AK18" s="43" t="s">
+      <c r="AJ18" s="41"/>
+      <c r="AK18" s="41" t="s">
         <v>289</v>
       </c>
-      <c r="AL18" s="43"/>
-      <c r="AM18" s="43"/>
-      <c r="AN18" s="53" t="s">
+      <c r="AL18" s="41"/>
+      <c r="AM18" s="41"/>
+      <c r="AN18" s="51" t="s">
         <v>290</v>
       </c>
-      <c r="AO18" s="43"/>
-      <c r="AP18" s="43"/>
-      <c r="AQ18" s="43"/>
-      <c r="AR18" s="43"/>
-      <c r="AS18" s="43"/>
-      <c r="AT18" s="43"/>
-      <c r="AU18" s="43"/>
-      <c r="AV18" s="53" t="s">
+      <c r="AO18" s="41"/>
+      <c r="AP18" s="41"/>
+      <c r="AQ18" s="41"/>
+      <c r="AR18" s="41"/>
+      <c r="AS18" s="41"/>
+      <c r="AT18" s="41"/>
+      <c r="AU18" s="41"/>
+      <c r="AV18" s="51" t="s">
         <v>291</v>
       </c>
-      <c r="AW18" s="53" t="s">
+      <c r="AW18" s="51" t="s">
         <v>292</v>
       </c>
-      <c r="AX18" s="43"/>
-      <c r="AY18" s="53" t="s">
+      <c r="AX18" s="41"/>
+      <c r="AY18" s="51" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="19" ht="40.5" spans="1:51">
-      <c r="A19" s="49"/>
-      <c r="B19" s="50" t="s">
+      <c r="A19" s="47"/>
+      <c r="B19" s="48" t="s">
         <v>293</v>
       </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="53" t="s">
+      <c r="C19" s="49"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="51" t="s">
         <v>294</v>
       </c>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="53" t="s">
+      <c r="I19" s="41"/>
+      <c r="J19" s="41"/>
+      <c r="K19" s="51" t="s">
         <v>294</v>
       </c>
-      <c r="L19" s="43" t="s">
+      <c r="L19" s="41" t="s">
         <v>295</v>
       </c>
-      <c r="M19" s="43"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="43"/>
-      <c r="P19" s="43"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="43"/>
-      <c r="T19" s="43"/>
-      <c r="U19" s="43"/>
-      <c r="V19" s="43"/>
-      <c r="W19" s="43"/>
-      <c r="X19" s="43"/>
-      <c r="Y19" s="43"/>
-      <c r="Z19" s="43"/>
-      <c r="AA19" s="43"/>
-      <c r="AB19" s="43"/>
-      <c r="AC19" s="43"/>
-      <c r="AD19" s="43"/>
-      <c r="AE19" s="43" t="s">
+      <c r="M19" s="41"/>
+      <c r="N19" s="41"/>
+      <c r="O19" s="41"/>
+      <c r="P19" s="41"/>
+      <c r="Q19" s="41"/>
+      <c r="R19" s="41"/>
+      <c r="S19" s="41"/>
+      <c r="T19" s="41"/>
+      <c r="U19" s="41"/>
+      <c r="V19" s="41"/>
+      <c r="W19" s="41"/>
+      <c r="X19" s="41"/>
+      <c r="Y19" s="41"/>
+      <c r="Z19" s="41"/>
+      <c r="AA19" s="41"/>
+      <c r="AB19" s="41"/>
+      <c r="AC19" s="41"/>
+      <c r="AD19" s="41"/>
+      <c r="AE19" s="41" t="s">
         <v>295</v>
       </c>
-      <c r="AF19" s="43"/>
-      <c r="AG19" s="43"/>
-      <c r="AH19" s="43"/>
-      <c r="AI19" s="43"/>
-      <c r="AJ19" s="43"/>
-      <c r="AK19" s="43"/>
-      <c r="AL19" s="43"/>
-      <c r="AM19" s="43"/>
-      <c r="AN19" s="43"/>
-      <c r="AO19" s="43"/>
-      <c r="AP19" s="43" t="s">
+      <c r="AF19" s="41"/>
+      <c r="AG19" s="41"/>
+      <c r="AH19" s="41"/>
+      <c r="AI19" s="41"/>
+      <c r="AJ19" s="41"/>
+      <c r="AK19" s="41"/>
+      <c r="AL19" s="41"/>
+      <c r="AM19" s="41"/>
+      <c r="AN19" s="41"/>
+      <c r="AO19" s="41"/>
+      <c r="AP19" s="41" t="s">
         <v>295</v>
       </c>
-      <c r="AQ19" s="43"/>
-      <c r="AR19" s="43"/>
-      <c r="AS19" s="43"/>
-      <c r="AT19" s="43"/>
-      <c r="AU19" s="43"/>
-      <c r="AV19" s="53"/>
-      <c r="AW19" s="53"/>
-      <c r="AX19" s="43"/>
-      <c r="AY19" s="53" t="s">
+      <c r="AQ19" s="41"/>
+      <c r="AR19" s="41"/>
+      <c r="AS19" s="41"/>
+      <c r="AT19" s="41"/>
+      <c r="AU19" s="41"/>
+      <c r="AV19" s="51"/>
+      <c r="AW19" s="51"/>
+      <c r="AX19" s="41"/>
+      <c r="AY19" s="51" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="20" ht="54" spans="1:51">
-      <c r="A20" s="49"/>
-      <c r="B20" s="50" t="s">
+      <c r="A20" s="47"/>
+      <c r="B20" s="48" t="s">
         <v>297</v>
       </c>
-      <c r="C20" s="51"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
-      <c r="G20" s="43"/>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="43"/>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="43"/>
-      <c r="P20" s="43"/>
-      <c r="Q20" s="43"/>
-      <c r="R20" s="43"/>
-      <c r="S20" s="43"/>
-      <c r="T20" s="43"/>
-      <c r="U20" s="43"/>
-      <c r="V20" s="43"/>
-      <c r="W20" s="43"/>
-      <c r="X20" s="43"/>
-      <c r="Y20" s="43"/>
-      <c r="Z20" s="43"/>
-      <c r="AA20" s="43"/>
-      <c r="AB20" s="43"/>
-      <c r="AC20" s="43"/>
-      <c r="AD20" s="43"/>
-      <c r="AE20" s="43"/>
-      <c r="AF20" s="43"/>
-      <c r="AG20" s="43"/>
-      <c r="AH20" s="43"/>
-      <c r="AI20" s="43"/>
-      <c r="AJ20" s="53" t="s">
+      <c r="C20" s="49"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="41"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="41"/>
+      <c r="R20" s="41"/>
+      <c r="S20" s="41"/>
+      <c r="T20" s="41"/>
+      <c r="U20" s="41"/>
+      <c r="V20" s="41"/>
+      <c r="W20" s="41"/>
+      <c r="X20" s="41"/>
+      <c r="Y20" s="41"/>
+      <c r="Z20" s="41"/>
+      <c r="AA20" s="41"/>
+      <c r="AB20" s="41"/>
+      <c r="AC20" s="41"/>
+      <c r="AD20" s="41"/>
+      <c r="AE20" s="41"/>
+      <c r="AF20" s="41"/>
+      <c r="AG20" s="41"/>
+      <c r="AH20" s="41"/>
+      <c r="AI20" s="41"/>
+      <c r="AJ20" s="51" t="s">
         <v>298</v>
       </c>
-      <c r="AK20" s="43"/>
-      <c r="AL20" s="43"/>
-      <c r="AM20" s="43"/>
-      <c r="AN20" s="43"/>
-      <c r="AO20" s="43"/>
-      <c r="AP20" s="43"/>
-      <c r="AQ20" s="43"/>
-      <c r="AR20" s="43"/>
-      <c r="AS20" s="43"/>
-      <c r="AT20" s="43"/>
-      <c r="AU20" s="43"/>
-      <c r="AV20" s="53"/>
-      <c r="AW20" s="53"/>
-      <c r="AX20" s="43"/>
-      <c r="AY20" s="43"/>
+      <c r="AK20" s="41"/>
+      <c r="AL20" s="41"/>
+      <c r="AM20" s="41"/>
+      <c r="AN20" s="41"/>
+      <c r="AO20" s="41"/>
+      <c r="AP20" s="41"/>
+      <c r="AQ20" s="41"/>
+      <c r="AR20" s="41"/>
+      <c r="AS20" s="41"/>
+      <c r="AT20" s="41"/>
+      <c r="AU20" s="41"/>
+      <c r="AV20" s="51"/>
+      <c r="AW20" s="51"/>
+      <c r="AX20" s="41"/>
+      <c r="AY20" s="41"/>
     </row>
     <row r="21" ht="81" spans="1:51">
-      <c r="A21" s="49"/>
-      <c r="B21" s="54" t="s">
+      <c r="A21" s="47"/>
+      <c r="B21" s="52" t="s">
         <v>299</v>
       </c>
-      <c r="C21" s="52" t="s">
+      <c r="C21" s="50" t="s">
         <v>300</v>
       </c>
-      <c r="D21" s="52" t="s">
+      <c r="D21" s="50" t="s">
         <v>300</v>
       </c>
-      <c r="E21" s="43"/>
-      <c r="F21" s="43"/>
-      <c r="G21" s="43"/>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="53" t="s">
+      <c r="E21" s="41"/>
+      <c r="F21" s="41"/>
+      <c r="G21" s="41"/>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41"/>
+      <c r="J21" s="41"/>
+      <c r="K21" s="51" t="s">
         <v>301</v>
       </c>
-      <c r="L21" s="43" t="s">
+      <c r="L21" s="41" t="s">
         <v>302</v>
       </c>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="43"/>
-      <c r="P21" s="43"/>
-      <c r="Q21" s="43"/>
-      <c r="R21" s="43"/>
-      <c r="S21" s="43"/>
-      <c r="T21" s="43"/>
-      <c r="U21" s="43"/>
-      <c r="V21" s="43"/>
-      <c r="W21" s="43"/>
-      <c r="X21" s="43"/>
-      <c r="Y21" s="43"/>
-      <c r="Z21" s="43"/>
-      <c r="AA21" s="43"/>
-      <c r="AB21" s="43"/>
-      <c r="AC21" s="43"/>
-      <c r="AD21" s="43"/>
-      <c r="AE21" s="43" t="s">
+      <c r="M21" s="41"/>
+      <c r="N21" s="41"/>
+      <c r="O21" s="41"/>
+      <c r="P21" s="41"/>
+      <c r="Q21" s="41"/>
+      <c r="R21" s="41"/>
+      <c r="S21" s="41"/>
+      <c r="T21" s="41"/>
+      <c r="U21" s="41"/>
+      <c r="V21" s="41"/>
+      <c r="W21" s="41"/>
+      <c r="X21" s="41"/>
+      <c r="Y21" s="41"/>
+      <c r="Z21" s="41"/>
+      <c r="AA21" s="41"/>
+      <c r="AB21" s="41"/>
+      <c r="AC21" s="41"/>
+      <c r="AD21" s="41"/>
+      <c r="AE21" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="AF21" s="53" t="s">
+      <c r="AF21" s="51" t="s">
         <v>304</v>
       </c>
-      <c r="AG21" s="53" t="s">
+      <c r="AG21" s="51" t="s">
         <v>305</v>
       </c>
-      <c r="AH21" s="43"/>
-      <c r="AI21" s="53" t="s">
+      <c r="AH21" s="41"/>
+      <c r="AI21" s="51" t="s">
         <v>306</v>
       </c>
-      <c r="AJ21" s="53" t="s">
+      <c r="AJ21" s="51" t="s">
         <v>307</v>
       </c>
-      <c r="AK21" s="43"/>
-      <c r="AL21" s="43"/>
-      <c r="AM21" s="43"/>
-      <c r="AN21" s="43"/>
-      <c r="AO21" s="43" t="s">
+      <c r="AK21" s="41"/>
+      <c r="AL21" s="41"/>
+      <c r="AM21" s="41"/>
+      <c r="AN21" s="41"/>
+      <c r="AO21" s="41" t="s">
         <v>302</v>
       </c>
-      <c r="AP21" s="43" t="s">
+      <c r="AP21" s="41" t="s">
         <v>302</v>
       </c>
-      <c r="AQ21" s="43"/>
-      <c r="AR21" s="43"/>
-      <c r="AS21" s="43"/>
-      <c r="AT21" s="43" t="s">
+      <c r="AQ21" s="41"/>
+      <c r="AR21" s="41"/>
+      <c r="AS21" s="41"/>
+      <c r="AT21" s="41" t="s">
         <v>303</v>
       </c>
-      <c r="AU21" s="43"/>
-      <c r="AV21" s="43"/>
-      <c r="AW21" s="43"/>
-      <c r="AX21" s="53" t="s">
+      <c r="AU21" s="41"/>
+      <c r="AV21" s="41"/>
+      <c r="AW21" s="41"/>
+      <c r="AX21" s="51" t="s">
         <v>308</v>
       </c>
-      <c r="AY21" s="53" t="s">
+      <c r="AY21" s="51" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:51">
-      <c r="A22" s="55"/>
-      <c r="B22" s="50" t="s">
+      <c r="A22" s="53"/>
+      <c r="B22" s="48" t="s">
         <v>310</v>
       </c>
-      <c r="C22" s="51"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="43"/>
-      <c r="F22" s="43"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="43"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="43"/>
-      <c r="P22" s="43"/>
-      <c r="Q22" s="43"/>
-      <c r="R22" s="43"/>
-      <c r="S22" s="43"/>
-      <c r="T22" s="43"/>
-      <c r="U22" s="43"/>
-      <c r="V22" s="43"/>
-      <c r="W22" s="43"/>
-      <c r="X22" s="43"/>
-      <c r="Y22" s="43"/>
-      <c r="Z22" s="43"/>
-      <c r="AA22" s="43"/>
-      <c r="AB22" s="43"/>
-      <c r="AC22" s="43"/>
-      <c r="AD22" s="43"/>
-      <c r="AE22" s="43"/>
-      <c r="AF22" s="43"/>
-      <c r="AG22" s="43"/>
-      <c r="AH22" s="43"/>
-      <c r="AI22" s="43"/>
-      <c r="AJ22" s="43"/>
-      <c r="AK22" s="43"/>
-      <c r="AL22" s="43"/>
-      <c r="AM22" s="43"/>
-      <c r="AN22" s="43"/>
-      <c r="AO22" s="43"/>
-      <c r="AP22" s="43"/>
-      <c r="AQ22" s="43"/>
-      <c r="AR22" s="43"/>
-      <c r="AS22" s="43"/>
-      <c r="AT22" s="43"/>
-      <c r="AU22" s="43"/>
-      <c r="AV22" s="53"/>
-      <c r="AW22" s="53"/>
-      <c r="AX22" s="43"/>
-      <c r="AY22" s="43"/>
+      <c r="C22" s="49"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="41"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41"/>
+      <c r="J22" s="41"/>
+      <c r="K22" s="41"/>
+      <c r="L22" s="41"/>
+      <c r="M22" s="41"/>
+      <c r="N22" s="41"/>
+      <c r="O22" s="41"/>
+      <c r="P22" s="41"/>
+      <c r="Q22" s="41"/>
+      <c r="R22" s="41"/>
+      <c r="S22" s="41"/>
+      <c r="T22" s="41"/>
+      <c r="U22" s="41"/>
+      <c r="V22" s="41"/>
+      <c r="W22" s="41"/>
+      <c r="X22" s="41"/>
+      <c r="Y22" s="41"/>
+      <c r="Z22" s="41"/>
+      <c r="AA22" s="41"/>
+      <c r="AB22" s="41"/>
+      <c r="AC22" s="41"/>
+      <c r="AD22" s="41"/>
+      <c r="AE22" s="41"/>
+      <c r="AF22" s="41"/>
+      <c r="AG22" s="41"/>
+      <c r="AH22" s="41"/>
+      <c r="AI22" s="41"/>
+      <c r="AJ22" s="41"/>
+      <c r="AK22" s="41"/>
+      <c r="AL22" s="41"/>
+      <c r="AM22" s="41"/>
+      <c r="AN22" s="41"/>
+      <c r="AO22" s="41"/>
+      <c r="AP22" s="41"/>
+      <c r="AQ22" s="41"/>
+      <c r="AR22" s="41"/>
+      <c r="AS22" s="41"/>
+      <c r="AT22" s="41"/>
+      <c r="AU22" s="41"/>
+      <c r="AV22" s="51"/>
+      <c r="AW22" s="51"/>
+      <c r="AX22" s="41"/>
+      <c r="AY22" s="41"/>
     </row>
     <row r="24" ht="108" spans="1:51">
-      <c r="A24" s="32" t="s">
+      <c r="A24" s="30" t="s">
         <v>311</v>
       </c>
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="C24" s="37" t="s">
+      <c r="C24" s="35" t="s">
         <v>313</v>
       </c>
-      <c r="D24" s="37" t="s">
+      <c r="D24" s="35" t="s">
         <v>196</v>
       </c>
-      <c r="E24" s="37" t="s">
+      <c r="E24" s="35" t="s">
         <v>314</v>
       </c>
-      <c r="F24" s="37" t="s">
+      <c r="F24" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="G24" s="37" t="s">
+      <c r="G24" s="35" t="s">
         <v>316</v>
       </c>
-      <c r="H24" s="37" t="s">
+      <c r="H24" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="I24" s="37" t="s">
+      <c r="I24" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="J24" s="37" t="s">
+      <c r="J24" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="K24" s="37" t="s">
+      <c r="K24" s="35" t="s">
         <v>320</v>
       </c>
-      <c r="L24" s="37" t="s">
+      <c r="L24" s="35" t="s">
         <v>321</v>
       </c>
-      <c r="M24" s="37" t="s">
+      <c r="M24" s="35" t="s">
         <v>322</v>
       </c>
-      <c r="N24" s="37" t="s">
+      <c r="N24" s="35" t="s">
         <v>323</v>
       </c>
-      <c r="O24" s="37" t="s">
+      <c r="O24" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="P24" s="37" t="s">
+      <c r="P24" s="35" t="s">
         <v>324</v>
       </c>
-      <c r="Q24" s="37" t="s">
+      <c r="Q24" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="R24" s="37" t="s">
+      <c r="R24" s="35" t="s">
         <v>326</v>
       </c>
-      <c r="S24" s="37" t="s">
+      <c r="S24" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="T24" s="37" t="s">
+      <c r="T24" s="35" t="s">
         <v>328</v>
       </c>
-      <c r="U24" s="37" t="s">
+      <c r="U24" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="V24" s="37" t="s">
+      <c r="V24" s="35" t="s">
         <v>330</v>
       </c>
-      <c r="W24" s="37" t="s">
+      <c r="W24" s="35" t="s">
         <v>331</v>
       </c>
-      <c r="X24" s="37" t="s">
+      <c r="X24" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="Y24" s="37" t="s">
+      <c r="Y24" s="35" t="s">
         <v>333</v>
       </c>
-      <c r="Z24" s="37" t="s">
+      <c r="Z24" s="35" t="s">
         <v>334</v>
       </c>
-      <c r="AA24" s="37" t="s">
+      <c r="AA24" s="35" t="s">
         <v>335</v>
       </c>
-      <c r="AB24" s="37" t="s">
+      <c r="AB24" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="AC24" s="37" t="s">
+      <c r="AC24" s="35" t="s">
         <v>337</v>
       </c>
-      <c r="AD24" s="37" t="s">
+      <c r="AD24" s="35" t="s">
         <v>338</v>
       </c>
-      <c r="AE24" s="37" t="s">
+      <c r="AE24" s="35" t="s">
         <v>339</v>
       </c>
-      <c r="AF24" s="37" t="s">
+      <c r="AF24" s="35" t="s">
         <v>340</v>
       </c>
-      <c r="AG24" s="37" t="s">
+      <c r="AG24" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="AH24" s="37" t="s">
+      <c r="AH24" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="AI24" s="37" t="s">
+      <c r="AI24" s="35" t="s">
         <v>342</v>
       </c>
-      <c r="AJ24" s="37" t="s">
+      <c r="AJ24" s="35" t="s">
         <v>343</v>
       </c>
-      <c r="AK24" s="37" t="s">
+      <c r="AK24" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="AL24" s="37" t="s">
+      <c r="AL24" s="35" t="s">
         <v>344</v>
       </c>
-      <c r="AM24" s="37" t="s">
+      <c r="AM24" s="35" t="s">
         <v>345</v>
       </c>
-      <c r="AN24" s="37" t="s">
+      <c r="AN24" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="AO24" s="37" t="s">
+      <c r="AO24" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="AP24" s="37" t="s">
+      <c r="AP24" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="AQ24" s="37" t="s">
+      <c r="AQ24" s="35" t="s">
         <v>341</v>
       </c>
-      <c r="AR24" s="37" t="s">
+      <c r="AR24" s="35" t="s">
         <v>181</v>
       </c>
-      <c r="AS24" s="37" t="s">
+      <c r="AS24" s="35" t="s">
         <v>346</v>
       </c>
-      <c r="AT24" s="37" t="s">
+      <c r="AT24" s="35" t="s">
         <v>347</v>
       </c>
-      <c r="AU24" s="37" t="s">
+      <c r="AU24" s="35" t="s">
         <v>348</v>
       </c>
-      <c r="AV24" s="37" t="s">
+      <c r="AV24" s="35" t="s">
         <v>349</v>
       </c>
-      <c r="AW24" s="38" t="s">
+      <c r="AW24" s="36" t="s">
         <v>350</v>
       </c>
-      <c r="AX24" s="38" t="s">
+      <c r="AX24" s="36" t="s">
         <v>341</v>
       </c>
-      <c r="AY24" s="38" t="s">
+      <c r="AY24" s="36" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:51">
-      <c r="A25" s="34"/>
-      <c r="B25" s="39" t="s">
+      <c r="A25" s="32"/>
+      <c r="B25" s="37" t="s">
         <v>351</v>
       </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="37"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="37"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="37"/>
-      <c r="K25" s="37"/>
-      <c r="L25" s="37"/>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="37"/>
-      <c r="P25" s="37"/>
-      <c r="Q25" s="37"/>
-      <c r="R25" s="37"/>
-      <c r="S25" s="37"/>
-      <c r="T25" s="37"/>
-      <c r="U25" s="37"/>
-      <c r="V25" s="37"/>
-      <c r="W25" s="37"/>
-      <c r="X25" s="37"/>
-      <c r="Y25" s="37"/>
-      <c r="Z25" s="37"/>
-      <c r="AA25" s="37"/>
-      <c r="AB25" s="37"/>
-      <c r="AC25" s="37"/>
-      <c r="AD25" s="37"/>
-      <c r="AE25" s="37"/>
-      <c r="AF25" s="37"/>
-      <c r="AG25" s="37"/>
-      <c r="AH25" s="37"/>
-      <c r="AI25" s="37"/>
-      <c r="AJ25" s="37"/>
-      <c r="AK25" s="37"/>
-      <c r="AL25" s="37"/>
-      <c r="AM25" s="37"/>
-      <c r="AN25" s="37"/>
-      <c r="AO25" s="37"/>
-      <c r="AP25" s="37"/>
-      <c r="AQ25" s="37"/>
-      <c r="AR25" s="37"/>
-      <c r="AS25" s="37"/>
-      <c r="AT25" s="37"/>
-      <c r="AU25" s="37"/>
-      <c r="AV25" s="37"/>
-      <c r="AW25" s="38"/>
-      <c r="AX25" s="38"/>
-      <c r="AY25" s="38"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="35"/>
+      <c r="E25" s="35"/>
+      <c r="F25" s="35"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
+      <c r="R25" s="35"/>
+      <c r="S25" s="35"/>
+      <c r="T25" s="35"/>
+      <c r="U25" s="35"/>
+      <c r="V25" s="35"/>
+      <c r="W25" s="35"/>
+      <c r="X25" s="35"/>
+      <c r="Y25" s="35"/>
+      <c r="Z25" s="35"/>
+      <c r="AA25" s="35"/>
+      <c r="AB25" s="35"/>
+      <c r="AC25" s="35"/>
+      <c r="AD25" s="35"/>
+      <c r="AE25" s="35"/>
+      <c r="AF25" s="35"/>
+      <c r="AG25" s="35"/>
+      <c r="AH25" s="35"/>
+      <c r="AI25" s="35"/>
+      <c r="AJ25" s="35"/>
+      <c r="AK25" s="35"/>
+      <c r="AL25" s="35"/>
+      <c r="AM25" s="35"/>
+      <c r="AN25" s="35"/>
+      <c r="AO25" s="35"/>
+      <c r="AP25" s="35"/>
+      <c r="AQ25" s="35"/>
+      <c r="AR25" s="35"/>
+      <c r="AS25" s="35"/>
+      <c r="AT25" s="35"/>
+      <c r="AU25" s="35"/>
+      <c r="AV25" s="35"/>
+      <c r="AW25" s="36"/>
+      <c r="AX25" s="36"/>
+      <c r="AY25" s="36"/>
     </row>
     <row r="26" customFormat="1" ht="94.5" spans="1:51">
-      <c r="A26" s="40"/>
-      <c r="B26" s="39" t="s">
+      <c r="A26" s="38"/>
+      <c r="B26" s="37" t="s">
         <v>352</v>
       </c>
-      <c r="C26" s="37"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="37"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="37" t="s">
+      <c r="C26" s="35"/>
+      <c r="D26" s="35"/>
+      <c r="E26" s="35"/>
+      <c r="F26" s="35"/>
+      <c r="G26" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="H26" s="37"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="37"/>
-      <c r="K26" s="37"/>
-      <c r="L26" s="37"/>
-      <c r="M26" s="37" t="s">
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35" t="s">
         <v>354</v>
       </c>
-      <c r="N26" s="37" t="s">
+      <c r="N26" s="35" t="s">
         <v>355</v>
       </c>
-      <c r="O26" s="37"/>
-      <c r="P26" s="37"/>
-      <c r="Q26" s="37"/>
-      <c r="R26" s="37"/>
-      <c r="S26" s="37"/>
-      <c r="T26" s="37"/>
-      <c r="U26" s="37"/>
-      <c r="V26" s="37"/>
-      <c r="W26" s="37"/>
-      <c r="X26" s="37"/>
-      <c r="Y26" s="37"/>
-      <c r="Z26" s="37"/>
-      <c r="AA26" s="37"/>
-      <c r="AB26" s="37"/>
-      <c r="AC26" s="37"/>
-      <c r="AD26" s="37"/>
-      <c r="AE26" s="37"/>
-      <c r="AF26" s="37"/>
-      <c r="AG26" s="37"/>
-      <c r="AH26" s="37"/>
-      <c r="AI26" s="37"/>
-      <c r="AJ26" s="37"/>
-      <c r="AK26" s="37"/>
-      <c r="AL26" s="37"/>
-      <c r="AM26" s="37"/>
-      <c r="AN26" s="37"/>
-      <c r="AO26" s="37" t="s">
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="35"/>
+      <c r="T26" s="35"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="35"/>
+      <c r="W26" s="35"/>
+      <c r="X26" s="35"/>
+      <c r="Y26" s="35"/>
+      <c r="Z26" s="35"/>
+      <c r="AA26" s="35"/>
+      <c r="AB26" s="35"/>
+      <c r="AC26" s="35"/>
+      <c r="AD26" s="35"/>
+      <c r="AE26" s="35"/>
+      <c r="AF26" s="35"/>
+      <c r="AG26" s="35"/>
+      <c r="AH26" s="35"/>
+      <c r="AI26" s="35"/>
+      <c r="AJ26" s="35"/>
+      <c r="AK26" s="35"/>
+      <c r="AL26" s="35"/>
+      <c r="AM26" s="35"/>
+      <c r="AN26" s="35"/>
+      <c r="AO26" s="35" t="s">
         <v>356</v>
       </c>
-      <c r="AP26" s="37" t="s">
+      <c r="AP26" s="35" t="s">
         <v>357</v>
       </c>
-      <c r="AQ26" s="37"/>
-      <c r="AR26" s="37"/>
-      <c r="AS26" s="37"/>
-      <c r="AT26" s="37"/>
-      <c r="AU26" s="37"/>
-      <c r="AV26" s="37"/>
-      <c r="AW26" s="38"/>
-      <c r="AX26" s="38"/>
-      <c r="AY26" s="38"/>
+      <c r="AQ26" s="35"/>
+      <c r="AR26" s="35"/>
+      <c r="AS26" s="35"/>
+      <c r="AT26" s="35"/>
+      <c r="AU26" s="35"/>
+      <c r="AV26" s="35"/>
+      <c r="AW26" s="36"/>
+      <c r="AX26" s="36"/>
+      <c r="AY26" s="36"/>
     </row>
-    <row r="27" s="15" customFormat="1" ht="27" spans="1:51">
-      <c r="A27" s="41" t="s">
+    <row r="27" s="13" customFormat="1" ht="27" spans="1:51">
+      <c r="A27" s="39" t="s">
         <v>358</v>
       </c>
-      <c r="B27" s="53" t="s">
+      <c r="B27" s="51" t="s">
         <v>359</v>
       </c>
-      <c r="C27" s="56"/>
-      <c r="D27" s="56"/>
-      <c r="E27" s="56"/>
-      <c r="F27" s="56"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="56"/>
-      <c r="J27" s="56"/>
-      <c r="K27" s="56"/>
-      <c r="L27" s="56"/>
-      <c r="M27" s="56"/>
-      <c r="N27" s="56"/>
-      <c r="O27" s="56"/>
-      <c r="P27" s="56"/>
-      <c r="Q27" s="56"/>
-      <c r="R27" s="56"/>
-      <c r="S27" s="56"/>
-      <c r="T27" s="56"/>
-      <c r="U27" s="56"/>
-      <c r="V27" s="56"/>
-      <c r="W27" s="56"/>
-      <c r="X27" s="56"/>
-      <c r="Y27" s="56"/>
-      <c r="Z27" s="56"/>
-      <c r="AA27" s="56"/>
-      <c r="AB27" s="56"/>
-      <c r="AC27" s="56"/>
-      <c r="AD27" s="56"/>
-      <c r="AE27" s="56"/>
-      <c r="AF27" s="56"/>
-      <c r="AG27" s="56"/>
-      <c r="AH27" s="56"/>
-      <c r="AI27" s="56"/>
-      <c r="AJ27" s="56"/>
-      <c r="AK27" s="56"/>
-      <c r="AL27" s="56"/>
-      <c r="AM27" s="56"/>
-      <c r="AN27" s="56"/>
-      <c r="AO27" s="56"/>
-      <c r="AP27" s="56"/>
-      <c r="AQ27" s="56"/>
-      <c r="AR27" s="56"/>
+      <c r="C27" s="54"/>
+      <c r="D27" s="54"/>
+      <c r="E27" s="54"/>
+      <c r="F27" s="54"/>
+      <c r="G27" s="54"/>
+      <c r="H27" s="54"/>
+      <c r="I27" s="54"/>
+      <c r="J27" s="54"/>
+      <c r="K27" s="54"/>
+      <c r="L27" s="54"/>
+      <c r="M27" s="54"/>
+      <c r="N27" s="54"/>
+      <c r="O27" s="54"/>
+      <c r="P27" s="54"/>
+      <c r="Q27" s="54"/>
+      <c r="R27" s="54"/>
+      <c r="S27" s="54"/>
+      <c r="T27" s="54"/>
+      <c r="U27" s="54"/>
+      <c r="V27" s="54"/>
+      <c r="W27" s="54"/>
+      <c r="X27" s="54"/>
+      <c r="Y27" s="54"/>
+      <c r="Z27" s="54"/>
+      <c r="AA27" s="54"/>
+      <c r="AB27" s="54"/>
+      <c r="AC27" s="54"/>
+      <c r="AD27" s="54"/>
+      <c r="AE27" s="54"/>
+      <c r="AF27" s="54"/>
+      <c r="AG27" s="54"/>
+      <c r="AH27" s="54"/>
+      <c r="AI27" s="54"/>
+      <c r="AJ27" s="54"/>
+      <c r="AK27" s="54"/>
+      <c r="AL27" s="54"/>
+      <c r="AM27" s="54"/>
+      <c r="AN27" s="54"/>
+      <c r="AO27" s="54"/>
+      <c r="AP27" s="54"/>
+      <c r="AQ27" s="54"/>
+      <c r="AR27" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -8334,140 +8998,140 @@
       <c r="B2" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="3" t="s">
         <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="12"/>
+      <c r="A3" s="11"/>
       <c r="B3" s="10"/>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="3" t="s">
         <v>363</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="12"/>
+      <c r="A4" s="11"/>
       <c r="B4" s="10"/>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="3" t="s">
         <v>364</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="12"/>
+      <c r="A5" s="11"/>
       <c r="B5" s="10"/>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="3" t="s">
         <v>365</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="11"/>
+      <c r="A6" s="11"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="3"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="12"/>
+      <c r="A7" s="11"/>
       <c r="B7" s="10" t="s">
         <v>366</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="3" t="s">
         <v>367</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="12"/>
+      <c r="A8" s="11"/>
       <c r="B8" s="10"/>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="3" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="12"/>
+      <c r="A9" s="11"/>
       <c r="B9" s="10"/>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="3" t="s">
         <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="12"/>
+      <c r="A10" s="11"/>
       <c r="B10" s="10"/>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="3" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="12"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="11"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="3"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="12"/>
+      <c r="A12" s="11"/>
       <c r="B12" s="10" t="s">
         <v>371</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="3" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="12"/>
+      <c r="A13" s="11"/>
       <c r="B13" s="10"/>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="3" t="s">
         <v>373</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="12"/>
+      <c r="A14" s="11"/>
       <c r="B14" s="10"/>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="3" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="12"/>
+      <c r="A15" s="11"/>
       <c r="B15" s="10"/>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="3" t="s">
         <v>375</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="12"/>
+      <c r="A16" s="11"/>
       <c r="B16" s="10"/>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="3" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="12"/>
-      <c r="B17" s="13"/>
-      <c r="C17" s="11"/>
+      <c r="A17" s="11"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="3"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="12"/>
+      <c r="A18" s="11"/>
       <c r="B18" s="10" t="s">
         <v>377</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" s="2" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="12"/>
+      <c r="A19" s="11"/>
       <c r="B19" s="10"/>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="2" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="12"/>
+      <c r="A20" s="11"/>
       <c r="B20" s="10"/>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="2" t="s">
         <v>380</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="12"/>
+      <c r="A21" s="11"/>
       <c r="B21" s="10"/>
-      <c r="C21" s="13" t="s">
+      <c r="C21" s="2" t="s">
         <v>381</v>
       </c>
     </row>
@@ -8487,7 +9151,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="31" customWidth="1"/>
@@ -8630,18 +9294,6 @@
       <c r="D12" s="3" t="s">
         <v>412</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2"/>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="404">
   <si>
     <t>项目整合管理</t>
   </si>
@@ -64,43 +64,11 @@
     <t xml:space="preserve">项目干系人管理 </t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>识别、定义、组合、统一和协调项目管理过程组的各个过程和项目管理管理活动</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
+    <t>识别、定义、统一协调项目管理各过程及活动，贯穿项目始终,具备建立联系和统一的性质</t>
+  </si>
+  <si>
+    <t xml:space="preserve">定义和控制项目内工作,确保项目做且只做所需的全部工作，包括产品范围和项目范围
 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>整合管理兼具统一、合并、沟通和建立联系的性质，项目整合管理贯穿项目始终</t>
-    </r>
-  </si>
-  <si>
-    <t>确保项目做且只做所需的全部工作，以成功完成项目
-定义和控制哪些工作应该包括在项目内，哪些不应该包括在项目内
-涉及产品范围和项目范围</t>
   </si>
   <si>
     <t>为了项目在批准的时间内完成，对进度进行规划、估算、管理和控制的过程</t>
@@ -1207,6 +1175,278 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">定义作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>制定一份正式批准项目、授权项目经理使用组织资源的文件，来明确项目正式地位，与组织战略目标联系，展示了组织对项目的承诺</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  制定一份识别、定义、统一协调项目计划的各部分的文件，来确定项目工作的基础和执行方式</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  执行项目管理计划中的工作，实施已批准的变更请求，来管理项目工作和可交付成果，提高项目成功可能性</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 使用已有知识、生成新知识，帮助组织学习并实现项目目标，已有知识用来创造和改进项目成果，新知识可用来支持组织运营和未来项目</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用： 
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 为实现项目管理计划中确定的绩效目标，而对项目进展进行跟踪、审查、报告，来让干系人了解项目当前状，通过成本和进度预测了解项目未来状态，并认可处理绩效问题的行动</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>管理、审查、批准可交付成果、项目文件、项目管理计划的变更，对变更处理结果进行沟通</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>终结项目、阶段的所有活动，存档项目、阶段信息，释放组织团队资源</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  制定一份定义、确认、控制项目范围的文件，为管理项目范围提供指南和方向</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  用来确定、记录、管理干系人需要和需求，是定义产品范围和项目范围的基础</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是制定项目和产品详细描述的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  创建工作分解结构WBS是把项目可交付成果和项目工作分解成较小、更易于管理的组件的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是正式验收已完成的项目可交付成果的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是监督项目和产品的范围状态，管理范围基准变更的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是为规划、编制、管理、执行和控制项目进度而制定政策、程序和文档的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1218,95 +1458,19 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>是</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>编写</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>一份</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>正式批准</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>项目并</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>授权</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>项目经理在项目活动中使用组织资源的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>文件</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t>是识别和记录为完成项目可交付成果而须采取的具体行动的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1318,53 +1482,19 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  是定义、准备和</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>协调</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>项目计划的所有组成部分，并把它们</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>整合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>为一份综合项目管理计划的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t xml:space="preserve">  是识别和记录项目活动之间关系的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1376,53 +1506,19 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  是为了实现项目目标而</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>领导和执行</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>项目管理计划中所确定的工作，并</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>实施</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>已批准的变更请求的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t xml:space="preserve">  是根据资源估算的结果，估算完成单项活动所需工作时段数的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
  </t>
     </r>
@@ -1434,96 +1530,44 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 是使用</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>现有知识</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>并生成</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>新知识</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>，以实现项目</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>目标</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>并且帮助组织</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>学习</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">定义： 
+      <t xml:space="preserve"> 是分析活动顺序、持续时间、资源需求和进度制约因素，创建进度模型，从而落实项目执行和监控的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是监督项目状态，以更新项目进度和管理进度基准变更的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
  </t>
     </r>
     <r>
@@ -1534,53 +1578,19 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 是</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>跟踪、审查和报告</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>整体项目进展，以实现项目管理计划中确定的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>绩效目标</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t xml:space="preserve"> 是确定如何估算、预算、管理、监督和控制项目成本的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1592,74 +1602,163 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>是</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>审查</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>所有变更请求、批准变更，</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>管理</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>对可交付成果、项目文件和项目管理计划的变更，并对变更处理结果进行</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>沟通</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
+      <t>是对完成项目工作所需资源成本进行近似估算的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是汇总所有单个活动或工作包的估算成本，建立一个经批准的成本基准的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是监督项目状态，以更新项目成本和管理成本基准变更的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是识别项目及其可交付成果的质量要求、标准，并书面描述项目将如何证明符合质量要求、标准的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是把组织的质量政策用于项目，并将质量管理计划转化为可执行的质量活动的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是为了评估绩效，确保项目输出完整、正确且满足客户期望，而监督和记录质量管理活动执行结果的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是定义如何估算、获取、管理和利用团队及其实物资源的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -1671,28 +1770,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>是</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>终结</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>项目、阶段或合同的所有活动的过程</t>
+      <t>是估算执行项目所需的团队资源，以及材料、设备和用品的类型和数量的过程</t>
     </r>
   </si>
   <si>
@@ -1716,7 +1794,55 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  是为了记录如何定义、确认和控制项目范围，而创建范围管理计划的过程</t>
+      <t xml:space="preserve">  是获取项目所需的团队成员、设施、设备、材料、用品和其他资源的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是提高工作能力，促进团队成员互动，改善团队整体氛围，以提高项目绩效的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是跟踪团队成员工作表现、提供反馈、解决问题并管理团队变更以优化项目绩效的过程</t>
     </r>
   </si>
   <si>
@@ -1740,7 +1866,151 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  是为了实现目标而确定、记录并管理干系人的需要和需求的过程</t>
+      <t xml:space="preserve">  是确保按计划为项目分配实物资源，以及根据资源使用计划监督资源实际使用情况，并采取必要纠正措施的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是基于每个干系人或干系人群体的信息需求、可用的组织资产，以及具体项目的需求，为项目沟通活动制定恰当的方法和计划的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是确保项目信息及时且恰当的收集、生成、发布、存储、检索、管理、监督和最终处置的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是确保满足项目及其干系人的信息需求的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是定义如何实施项目风险管理活动的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是识别单个项目风险以及整体项目风险的来源，并记录风险特征的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是通过评估单个项目风险发生的概率和影响及其他特征，对风险进行优先级排序，从而为后续分析或行动提供基础的过程</t>
     </r>
   </si>
   <si>
@@ -1764,7 +2034,55 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  是制定项目和产品详细描述的过程</t>
+      <t xml:space="preserve">  是就已识别的单个项目风险和不确定性的其他来源对整体项目目标的影响进行定量分析的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是为了应对项目风险，而制定可选方案、选择应对策略并商定应对行动的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是执行商定的风险应对计划的过程</t>
     </r>
   </si>
   <si>
@@ -1788,7 +2106,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  创建工作分解结构WBS是把项目可交付成果和项目工作分解成较小、更易于管理的组件的过程</t>
+      <t xml:space="preserve">  是在整个项目期间，监督风险应对计划的实施，并跟踪已识别风险、识别和分析新风险，以及评估风险管理有效性的过程</t>
     </r>
   </si>
   <si>
@@ -1812,7 +2130,79 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 是正式验收已完成的项目可交付成果的过程</t>
+      <t xml:space="preserve"> 是记录项目采购决策、明确采购方法，及识别潜在卖方的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是获取卖方应答、选择卖方并授予合同的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是管理采购关系、监督合同绩效、实施必要的变更和纠偏，以及关闭合同的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是定期识别项目干系人，分析和记录他们的利益、参与度、项目依赖性、影响力和对项目成功的潜在影响的过程</t>
     </r>
   </si>
   <si>
@@ -1836,7 +2226,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 是监督项目和产品的范围状态，管理范围基准变更的过程</t>
+      <t xml:space="preserve"> 是根据干系人的需求、期望、利益和对项目的潜在影响，制定项目干系人参与项目的方法的过程</t>
     </r>
   </si>
   <si>
@@ -1860,7 +2250,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  是为规划、编制、管理、执行和控制项目进度而制定政策、程序和文档的过程</t>
+      <t xml:space="preserve">  是通过与干系人进行沟通协作，以满足其需求与期望、处理问题，并促进干系人合理参与的过程</t>
     </r>
   </si>
   <si>
@@ -1884,1376 +2274,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>是识别和记录为完成项目可交付成果而须采取的具体行动的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是识别和记录项目活动之间关系的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是根据资源估算的结果，估算完成单项活动所需工作时段数的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 是分析活动顺序、持续时间、资源需求和进度制约因素，创建进度模型，从而落实项目执行和监控的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是监督项目状态，以更新项目进度和管理进度基准变更的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 是确定如何估算、预算、管理、监督和控制项目成本的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是对完成项目工作所需资源成本进行近似估算的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是汇总所有单个活动或工作包的估算成本，建立一个经批准的成本基准的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是监督项目状态，以更新项目成本和管理成本基准变更的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是识别项目及其可交付成果的质量要求、标准，并书面描述项目将如何证明符合质量要求、标准的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是把组织的质量政策用于项目，并将质量管理计划转化为可执行的质量活动的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是为了评估绩效，确保项目输出完整、正确且满足客户期望，而监督和记录质量管理活动执行结果的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是定义如何估算、获取、管理和利用团队及其实物资源的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是估算执行项目所需的团队资源，以及材料、设备和用品的类型和数量的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是获取项目所需的团队成员、设施、设备、材料、用品和其他资源的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是提高工作能力，促进团队成员互动，改善团队整体氛围，以提高项目绩效的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 是跟踪团队成员工作表现、提供反馈、解决问题并管理团队变更以优化项目绩效的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是确保按计划为项目分配实物资源，以及根据资源使用计划监督资源实际使用情况，并采取必要纠正措施的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是基于每个干系人或干系人群体的信息需求、可用的组织资产，以及具体项目的需求，为项目沟通活动制定恰当的方法和计划的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是确保项目信息及时且恰当的收集、生成、发布、存储、检索、管理、监督和最终处置的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是确保满足项目及其干系人的信息需求的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是定义如何实施项目风险管理活动的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是识别单个项目风险以及整体项目风险的来源，并记录风险特征的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是通过评估单个项目风险发生的概率和影响及其他特征，对风险进行优先级排序，从而为后续分析或行动提供基础的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是就已识别的单个项目风险和不确定性的其他来源对整体项目目标的影响进行定量分析的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 是为了应对项目风险，而制定可选方案、选择应对策略并商定应对行动的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是执行商定的风险应对计划的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是在整个项目期间，监督风险应对计划的实施，并跟踪已识别风险、识别和分析新风险，以及评估风险管理有效性的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 是记录项目采购决策、明确采购方法，及识别潜在卖方的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是获取卖方应答、选择卖方并授予合同的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是管理采购关系、监督合同绩效、实施必要的变更和纠偏，以及关闭合同的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是定期识别项目干系人，分析和记录他们的利益、参与度、项目依赖性、影响力和对项目成功的潜在影响的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 是根据干系人的需求、期望、利益和对项目的潜在影响，制定项目干系人参与项目的方法的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是通过与干系人进行沟通协作，以满足其需求与期望、处理问题，并促进干系人合理参与的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>是监督项目干系人的关系，并通过修订参与策略和计划来引导干系人合理参与项目的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  1、</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>明确</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>项目与组织战略目标之间的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>直接联系</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  2、确定项目的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>正式地位</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  3、展示组织对项目的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>承诺</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">作用：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>生成一份综合文件，用于</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>确定</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>所有项目工作的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>基础</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>及其</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>执行方式</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是对项目工作和可交付成果开展</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>综合管理</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>，以</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>提高</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>项目成功的可能性</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  1、</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>利用已有</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>的组织知识来创造或改进项目成果
-  2、使当前项目</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>创造的知识</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>可用于支持组织运营和未来的项目或阶段</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  1、让干系人</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>了解</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>项目的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>当前</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>状态并</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>认可</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>为处理绩效问题而采取的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>行动</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-  2、通过成本和进度预测，让干系人</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>了解</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>项目的</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>未来</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>状态</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  确保对项目中已记录在案的变更做出</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>综合评审</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  1、</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>存档</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>项目或阶段信息，完成计划的工作
-  2、</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>释放</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>组织团队资源以开展新的工作</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>在整个项目期间对如何管理范围提供指南和方向</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是为定义产品范围和项目范围奠定基础</t>
     </r>
   </si>
   <si>
@@ -6298,7 +5319,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2794000" y="17367250"/>
+          <a:off x="2794000" y="17538700"/>
           <a:ext cx="11544300" cy="6191250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6903,7 +5924,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" s="12" customFormat="1" ht="81" spans="1:51">
+    <row r="4" s="12" customFormat="1" ht="94.5" spans="1:51">
       <c r="A4" s="25"/>
       <c r="B4" s="25"/>
       <c r="C4" s="28" t="s">
@@ -7057,617 +6078,599 @@
     <row r="5" s="12" customFormat="1" ht="108" spans="1:51">
       <c r="A5" s="25"/>
       <c r="B5" s="25"/>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="D5" s="28" t="s">
+      <c r="M5" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="E5" s="28" t="s">
+      <c r="N5" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="F5" s="28" t="s">
+      <c r="O5" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="P5" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="H5" s="28" t="s">
+      <c r="Q5" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="I5" s="28" t="s">
+      <c r="R5" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="J5" s="28" t="s">
+      <c r="S5" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="K5" s="28" t="s">
+      <c r="T5" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="L5" s="28" t="s">
+      <c r="U5" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="M5" s="28" t="s">
+      <c r="V5" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="N5" s="28" t="s">
+      <c r="W5" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="O5" s="28" t="s">
+      <c r="X5" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="P5" s="28" t="s">
+      <c r="Y5" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="Q5" s="28" t="s">
+      <c r="Z5" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="R5" s="28" t="s">
+      <c r="AA5" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="S5" s="28" t="s">
+      <c r="AB5" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="T5" s="28" t="s">
+      <c r="AC5" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="U5" s="28" t="s">
+      <c r="AD5" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="V5" s="28" t="s">
+      <c r="AE5" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="W5" s="28" t="s">
+      <c r="AF5" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="X5" s="28" t="s">
+      <c r="AG5" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="Y5" s="28" t="s">
+      <c r="AH5" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="Z5" s="28" t="s">
+      <c r="AI5" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="AA5" s="28" t="s">
+      <c r="AJ5" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="AB5" s="28" t="s">
+      <c r="AK5" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="AC5" s="28" t="s">
+      <c r="AL5" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="AD5" s="28" t="s">
+      <c r="AM5" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="AE5" s="28" t="s">
+      <c r="AN5" s="28" t="s">
         <v>146</v>
       </c>
-      <c r="AF5" s="28" t="s">
+      <c r="AO5" s="28" t="s">
         <v>147</v>
       </c>
-      <c r="AG5" s="28" t="s">
+      <c r="AP5" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="AH5" s="28" t="s">
+      <c r="AQ5" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="AI5" s="28" t="s">
+      <c r="AR5" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="AJ5" s="28" t="s">
+      <c r="AS5" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="AK5" s="28" t="s">
+      <c r="AT5" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="AL5" s="28" t="s">
+      <c r="AU5" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="AM5" s="28" t="s">
+      <c r="AV5" s="28" t="s">
         <v>154</v>
       </c>
-      <c r="AN5" s="28" t="s">
+      <c r="AW5" s="28" t="s">
         <v>155</v>
       </c>
-      <c r="AO5" s="28" t="s">
+      <c r="AX5" s="28" t="s">
         <v>156</v>
       </c>
-      <c r="AP5" s="28" t="s">
+      <c r="AY5" s="28" t="s">
         <v>157</v>
-      </c>
-      <c r="AQ5" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="AR5" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="AS5" s="28" t="s">
-        <v>160</v>
-      </c>
-      <c r="AT5" s="28" t="s">
-        <v>161</v>
-      </c>
-      <c r="AU5" s="28" t="s">
-        <v>162</v>
-      </c>
-      <c r="AV5" s="28" t="s">
-        <v>163</v>
-      </c>
-      <c r="AW5" s="28" t="s">
-        <v>164</v>
-      </c>
-      <c r="AX5" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="AY5" s="28" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="6" s="12" customFormat="1" ht="27" spans="1:51">
       <c r="A6" s="25"/>
       <c r="B6" s="25"/>
       <c r="C6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="J6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="M6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="O6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="P6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="Q6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="R6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="S6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="T6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="U6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="V6" s="28" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="W6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="X6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="Y6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="Z6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AA6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AB6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AC6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AD6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AE6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AF6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AG6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AH6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AI6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AJ6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AL6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AM6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AN6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AO6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AP6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AQ6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AR6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AS6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AT6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AU6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AV6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AW6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AX6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="AY6" s="29" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
     </row>
     <row r="7" s="12" customFormat="1" ht="54" spans="1:51">
       <c r="A7" s="30" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="J7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="K7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="L7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="M7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="N7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="O7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="P7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="Q7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="R7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="S7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="T7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="U7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="V7" s="28" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="W7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="Y7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="Z7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AA7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AB7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AC7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AD7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AE7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AF7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AG7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AH7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AI7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AJ7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AK7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AL7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AM7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AN7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AO7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AP7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AQ7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AR7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AS7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AT7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AU7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AV7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AW7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AX7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="AY7" s="29" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" ht="67.5" spans="1:51">
       <c r="A8" s="32"/>
       <c r="B8" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="J8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="K8" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="L8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="M8" s="34" t="s">
         <v>174</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="N8" s="34" t="s">
         <v>175</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="O8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="P8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="R8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="S8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="T8" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="U8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="V8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="W8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="X8" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="G8" s="34" t="s">
+      <c r="Y8" s="34" t="s">
         <v>178</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="Z8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AA8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB8" s="34" t="s">
         <v>179</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="AC8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AD8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AE8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AF8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AG8" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="J8" s="34" t="s">
+      <c r="AH8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AI8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AJ8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="K8" s="34" t="s">
+      <c r="AK8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AL8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AM8" s="34" t="s">
         <v>182</v>
       </c>
-      <c r="L8" s="34" t="s">
+      <c r="AN8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AO8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AP8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AQ8" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="AR8" s="34" t="s">
         <v>181</v>
       </c>
-      <c r="M8" s="34" t="s">
+      <c r="AS8" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="N8" s="34" t="s">
+      <c r="AT8" s="35" t="s">
         <v>184</v>
       </c>
-      <c r="O8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="P8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="Q8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="R8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="S8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="T8" s="34" t="s">
+      <c r="AU8" s="35" t="s">
         <v>185</v>
       </c>
-      <c r="U8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="V8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="W8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="X8" s="34" t="s">
+      <c r="AV8" s="35" t="s">
         <v>186</v>
       </c>
-      <c r="Y8" s="34" t="s">
-        <v>187</v>
-      </c>
-      <c r="Z8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AA8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AB8" s="34" t="s">
-        <v>188</v>
-      </c>
-      <c r="AC8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AD8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AF8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AG8" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="AH8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AI8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AJ8" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="AK8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AL8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AM8" s="34" t="s">
-        <v>191</v>
-      </c>
-      <c r="AN8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AO8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AP8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AQ8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AR8" s="34" t="s">
-        <v>190</v>
-      </c>
-      <c r="AS8" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="AT8" s="35" t="s">
-        <v>193</v>
-      </c>
-      <c r="AU8" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="AV8" s="35" t="s">
-        <v>195</v>
-      </c>
       <c r="AW8" s="35" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="AX8" s="36" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="AY8" s="36" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
     </row>
     <row r="9" ht="40.5" spans="1:51">
       <c r="A9" s="32"/>
       <c r="B9" s="37" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C9" s="35"/>
       <c r="D9" s="35"/>
@@ -7678,12 +6681,12 @@
       <c r="I9" s="35"/>
       <c r="J9" s="35"/>
       <c r="K9" s="35" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="L9" s="35"/>
       <c r="M9" s="35"/>
       <c r="N9" s="35" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="O9" s="35"/>
       <c r="P9" s="35"/>
@@ -7726,7 +6729,7 @@
     <row r="10" ht="81" spans="1:51">
       <c r="A10" s="38"/>
       <c r="B10" s="37" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C10" s="35"/>
       <c r="D10" s="35"/>
@@ -7737,14 +6740,14 @@
       <c r="I10" s="35"/>
       <c r="J10" s="35"/>
       <c r="K10" s="35" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="L10" s="35" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="M10" s="35"/>
       <c r="N10" s="35" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="O10" s="35"/>
       <c r="P10" s="35"/>
@@ -7759,7 +6762,7 @@
       <c r="Y10" s="35"/>
       <c r="Z10" s="35"/>
       <c r="AA10" s="35" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="AB10" s="35"/>
       <c r="AC10" s="35"/>
@@ -7770,7 +6773,7 @@
       <c r="AH10" s="35"/>
       <c r="AI10" s="35"/>
       <c r="AJ10" s="35" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="AK10" s="35"/>
       <c r="AL10" s="35"/>
@@ -7790,10 +6793,10 @@
     </row>
     <row r="11" spans="1:51">
       <c r="A11" s="39" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
@@ -7847,10 +6850,10 @@
     </row>
     <row r="12" spans="1:51">
       <c r="A12" s="39" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
@@ -7904,131 +6907,131 @@
     </row>
     <row r="14" ht="94.5" spans="1:51">
       <c r="A14" s="42" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C14" s="44"/>
       <c r="D14" s="45"/>
       <c r="E14" s="45"/>
       <c r="F14" s="45" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="G14" s="45"/>
       <c r="H14" s="45" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="I14" s="45"/>
       <c r="J14" s="45"/>
       <c r="K14" s="45" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="L14" s="45" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="M14" s="45" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="N14" s="45" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="O14" s="45"/>
       <c r="P14" s="45"/>
       <c r="Q14" s="45" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="R14" s="45" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="S14" s="45" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="T14" s="45" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="U14" s="45" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="V14" s="45"/>
       <c r="W14" s="45" t="s">
+        <v>210</v>
+      </c>
+      <c r="X14" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="Y14" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z14" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA14" s="45" t="s">
+        <v>216</v>
+      </c>
+      <c r="AB14" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="AC14" s="45" t="s">
+        <v>218</v>
+      </c>
+      <c r="AD14" s="45" t="s">
         <v>219</v>
       </c>
-      <c r="X14" s="45" t="s">
-        <v>222</v>
-      </c>
-      <c r="Y14" s="45" t="s">
-        <v>223</v>
-      </c>
-      <c r="Z14" s="45" t="s">
-        <v>224</v>
-      </c>
-      <c r="AA14" s="45" t="s">
-        <v>225</v>
-      </c>
-      <c r="AB14" s="45" t="s">
-        <v>226</v>
-      </c>
-      <c r="AC14" s="45" t="s">
-        <v>227</v>
-      </c>
-      <c r="AD14" s="45" t="s">
-        <v>228</v>
-      </c>
       <c r="AE14" s="45" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="AF14" s="45" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="AG14" s="45"/>
       <c r="AH14" s="45" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="AI14" s="45" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="AJ14" s="45" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="AK14" s="45"/>
       <c r="AL14" s="45"/>
       <c r="AM14" s="45" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="AN14" s="45" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="AO14" s="45" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AP14" s="45" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="AQ14" s="45"/>
       <c r="AR14" s="45" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="AS14" s="46" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="AT14" s="45" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AU14" s="45" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="AV14" s="36"/>
       <c r="AW14" s="36"/>
       <c r="AX14" s="35" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="AY14" s="35"/>
     </row>
     <row r="15" spans="1:51">
       <c r="A15" s="47"/>
       <c r="B15" s="48" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C15" s="49"/>
       <c r="D15" s="41"/>
@@ -8083,13 +7086,13 @@
     <row r="16" ht="67.5" spans="1:51">
       <c r="A16" s="47"/>
       <c r="B16" s="48" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="E16" s="41"/>
       <c r="F16" s="41"/>
@@ -8098,7 +7101,7 @@
       <c r="I16" s="41"/>
       <c r="J16" s="41"/>
       <c r="K16" s="51" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="L16" s="41"/>
       <c r="M16" s="41"/>
@@ -8115,13 +7118,13 @@
       <c r="X16" s="41"/>
       <c r="Y16" s="41"/>
       <c r="Z16" s="51" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="AA16" s="41" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="AB16" s="51" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="AC16" s="41"/>
       <c r="AD16" s="41"/>
@@ -8134,24 +7137,24 @@
       <c r="AK16" s="41"/>
       <c r="AL16" s="41"/>
       <c r="AM16" s="51" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="AN16" s="41"/>
       <c r="AO16" s="41" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="AP16" s="41" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="AQ16" s="41"/>
       <c r="AR16" s="41"/>
       <c r="AS16" s="41" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="AT16" s="41"/>
       <c r="AU16" s="41"/>
       <c r="AV16" s="51" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="AW16" s="41"/>
       <c r="AX16" s="41"/>
@@ -8160,61 +7163,61 @@
     <row r="17" ht="81" spans="1:51">
       <c r="A17" s="47"/>
       <c r="B17" s="48" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="C17" s="49"/>
       <c r="D17" s="41"/>
       <c r="E17" s="41"/>
       <c r="F17" s="41"/>
       <c r="G17" s="51" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="H17" s="41"/>
       <c r="I17" s="51" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="J17" s="41"/>
       <c r="K17" s="41" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="L17" s="41" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="M17" s="41"/>
       <c r="N17" s="41"/>
       <c r="O17" s="51" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="P17" s="41"/>
       <c r="Q17" s="41"/>
       <c r="R17" s="41"/>
       <c r="S17" s="51" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="T17" s="51" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="U17" s="51" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="V17" s="41"/>
       <c r="W17" s="51" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="X17" s="41" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="Y17" s="51" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="Z17" s="51" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="AA17" s="51" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="AB17" s="51" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="AC17" s="41"/>
       <c r="AD17" s="41"/>
@@ -8222,54 +7225,54 @@
       <c r="AF17" s="41"/>
       <c r="AG17" s="41"/>
       <c r="AH17" s="51" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="AI17" s="41"/>
       <c r="AJ17" s="41"/>
       <c r="AK17" s="41"/>
       <c r="AL17" s="41" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="AM17" s="51" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="AN17" s="51" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="AO17" s="51" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="AP17" s="51" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="AQ17" s="41"/>
       <c r="AR17" s="51" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="AS17" s="41" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="AT17" s="41" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="AU17" s="51" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="AV17" s="51" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="AW17" s="51" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="AX17" s="41"/>
       <c r="AY17" s="51" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
     </row>
     <row r="18" ht="81" spans="1:51">
       <c r="A18" s="47"/>
       <c r="B18" s="48" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="C18" s="49"/>
       <c r="D18" s="41"/>
@@ -8280,7 +7283,7 @@
       <c r="I18" s="41"/>
       <c r="J18" s="41"/>
       <c r="K18" s="51" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="L18" s="41"/>
       <c r="M18" s="41"/>
@@ -8297,16 +7300,16 @@
       <c r="X18" s="41"/>
       <c r="Y18" s="41"/>
       <c r="Z18" s="51" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="AA18" s="51" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="AB18" s="51" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="AC18" s="51" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="AD18" s="41"/>
       <c r="AE18" s="41"/>
@@ -8314,16 +7317,16 @@
       <c r="AG18" s="41"/>
       <c r="AH18" s="41"/>
       <c r="AI18" s="41" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="AJ18" s="41"/>
       <c r="AK18" s="41" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="AL18" s="41"/>
       <c r="AM18" s="41"/>
       <c r="AN18" s="51" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="AO18" s="41"/>
       <c r="AP18" s="41"/>
@@ -8333,20 +7336,20 @@
       <c r="AT18" s="41"/>
       <c r="AU18" s="41"/>
       <c r="AV18" s="51" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="AW18" s="51" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="AX18" s="41"/>
       <c r="AY18" s="51" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" ht="40.5" spans="1:51">
       <c r="A19" s="47"/>
       <c r="B19" s="48" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="C19" s="49"/>
       <c r="D19" s="41"/>
@@ -8354,15 +7357,15 @@
       <c r="F19" s="41"/>
       <c r="G19" s="41"/>
       <c r="H19" s="51" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="I19" s="41"/>
       <c r="J19" s="41"/>
       <c r="K19" s="51" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="L19" s="41" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="M19" s="41"/>
       <c r="N19" s="41"/>
@@ -8383,7 +7386,7 @@
       <c r="AC19" s="41"/>
       <c r="AD19" s="41"/>
       <c r="AE19" s="41" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AF19" s="41"/>
       <c r="AG19" s="41"/>
@@ -8396,7 +7399,7 @@
       <c r="AN19" s="41"/>
       <c r="AO19" s="41"/>
       <c r="AP19" s="41" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="AQ19" s="41"/>
       <c r="AR19" s="41"/>
@@ -8407,13 +7410,13 @@
       <c r="AW19" s="51"/>
       <c r="AX19" s="41"/>
       <c r="AY19" s="51" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
     </row>
     <row r="20" ht="54" spans="1:51">
       <c r="A20" s="47"/>
       <c r="B20" s="48" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="C20" s="49"/>
       <c r="D20" s="41"/>
@@ -8449,7 +7452,7 @@
       <c r="AH20" s="41"/>
       <c r="AI20" s="41"/>
       <c r="AJ20" s="51" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="AK20" s="41"/>
       <c r="AL20" s="41"/>
@@ -8470,13 +7473,13 @@
     <row r="21" ht="81" spans="1:51">
       <c r="A21" s="47"/>
       <c r="B21" s="52" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="E21" s="41"/>
       <c r="F21" s="41"/>
@@ -8485,10 +7488,10 @@
       <c r="I21" s="41"/>
       <c r="J21" s="41"/>
       <c r="K21" s="51" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="L21" s="41" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="M21" s="41"/>
       <c r="N21" s="41"/>
@@ -8509,51 +7512,51 @@
       <c r="AC21" s="41"/>
       <c r="AD21" s="41"/>
       <c r="AE21" s="41" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="AF21" s="51" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="AG21" s="51" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="AH21" s="41"/>
       <c r="AI21" s="51" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="AJ21" s="51" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="AK21" s="41"/>
       <c r="AL21" s="41"/>
       <c r="AM21" s="41"/>
       <c r="AN21" s="41"/>
       <c r="AO21" s="41" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="AP21" s="41" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="AQ21" s="41"/>
       <c r="AR21" s="41"/>
       <c r="AS21" s="41"/>
       <c r="AT21" s="41" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="AU21" s="41"/>
       <c r="AV21" s="41"/>
       <c r="AW21" s="41"/>
       <c r="AX21" s="51" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="AY21" s="51" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:51">
       <c r="A22" s="53"/>
       <c r="B22" s="48" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="C22" s="49"/>
       <c r="D22" s="41"/>
@@ -8607,163 +7610,163 @@
     </row>
     <row r="24" ht="108" spans="1:51">
       <c r="A24" s="30" t="s">
+        <v>302</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>303</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>187</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>305</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>306</v>
+      </c>
+      <c r="G24" s="35" t="s">
+        <v>307</v>
+      </c>
+      <c r="H24" s="35" t="s">
+        <v>308</v>
+      </c>
+      <c r="I24" s="35" t="s">
+        <v>309</v>
+      </c>
+      <c r="J24" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="K24" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="L24" s="35" t="s">
         <v>312</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="M24" s="35" t="s">
         <v>313</v>
       </c>
-      <c r="D24" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="E24" s="35" t="s">
+      <c r="N24" s="35" t="s">
         <v>314</v>
       </c>
-      <c r="F24" s="35" t="s">
+      <c r="O24" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="P24" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="G24" s="35" t="s">
+      <c r="Q24" s="35" t="s">
         <v>316</v>
       </c>
-      <c r="H24" s="35" t="s">
+      <c r="R24" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="I24" s="35" t="s">
+      <c r="S24" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="J24" s="35" t="s">
+      <c r="T24" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="K24" s="35" t="s">
+      <c r="U24" s="35" t="s">
         <v>320</v>
       </c>
-      <c r="L24" s="35" t="s">
+      <c r="V24" s="35" t="s">
         <v>321</v>
       </c>
-      <c r="M24" s="35" t="s">
+      <c r="W24" s="35" t="s">
         <v>322</v>
       </c>
-      <c r="N24" s="35" t="s">
+      <c r="X24" s="35" t="s">
         <v>323</v>
       </c>
-      <c r="O24" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="P24" s="35" t="s">
+      <c r="Y24" s="35" t="s">
         <v>324</v>
       </c>
-      <c r="Q24" s="35" t="s">
+      <c r="Z24" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="R24" s="35" t="s">
+      <c r="AA24" s="35" t="s">
         <v>326</v>
       </c>
-      <c r="S24" s="35" t="s">
+      <c r="AB24" s="35" t="s">
         <v>327</v>
       </c>
-      <c r="T24" s="35" t="s">
+      <c r="AC24" s="35" t="s">
         <v>328</v>
       </c>
-      <c r="U24" s="35" t="s">
+      <c r="AD24" s="35" t="s">
         <v>329</v>
       </c>
-      <c r="V24" s="35" t="s">
+      <c r="AE24" s="35" t="s">
         <v>330</v>
       </c>
-      <c r="W24" s="35" t="s">
+      <c r="AF24" s="35" t="s">
         <v>331</v>
       </c>
-      <c r="X24" s="35" t="s">
+      <c r="AG24" s="35" t="s">
         <v>332</v>
       </c>
-      <c r="Y24" s="35" t="s">
+      <c r="AH24" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="AI24" s="35" t="s">
         <v>333</v>
       </c>
-      <c r="Z24" s="35" t="s">
+      <c r="AJ24" s="35" t="s">
         <v>334</v>
       </c>
-      <c r="AA24" s="35" t="s">
+      <c r="AK24" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="AL24" s="35" t="s">
         <v>335</v>
       </c>
-      <c r="AB24" s="35" t="s">
+      <c r="AM24" s="35" t="s">
         <v>336</v>
       </c>
-      <c r="AC24" s="35" t="s">
+      <c r="AN24" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="AO24" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="AP24" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="AQ24" s="35" t="s">
+        <v>332</v>
+      </c>
+      <c r="AR24" s="35" t="s">
+        <v>172</v>
+      </c>
+      <c r="AS24" s="35" t="s">
         <v>337</v>
       </c>
-      <c r="AD24" s="35" t="s">
+      <c r="AT24" s="35" t="s">
         <v>338</v>
       </c>
-      <c r="AE24" s="35" t="s">
+      <c r="AU24" s="35" t="s">
         <v>339</v>
       </c>
-      <c r="AF24" s="35" t="s">
+      <c r="AV24" s="35" t="s">
         <v>340</v>
       </c>
-      <c r="AG24" s="35" t="s">
+      <c r="AW24" s="36" t="s">
         <v>341</v>
       </c>
-      <c r="AH24" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="AI24" s="35" t="s">
-        <v>342</v>
-      </c>
-      <c r="AJ24" s="35" t="s">
-        <v>343</v>
-      </c>
-      <c r="AK24" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="AL24" s="35" t="s">
-        <v>344</v>
-      </c>
-      <c r="AM24" s="35" t="s">
-        <v>345</v>
-      </c>
-      <c r="AN24" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="AO24" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="AP24" s="35" t="s">
-        <v>341</v>
-      </c>
-      <c r="AQ24" s="35" t="s">
-        <v>341</v>
-      </c>
-      <c r="AR24" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="AS24" s="35" t="s">
-        <v>346</v>
-      </c>
-      <c r="AT24" s="35" t="s">
-        <v>347</v>
-      </c>
-      <c r="AU24" s="35" t="s">
-        <v>348</v>
-      </c>
-      <c r="AV24" s="35" t="s">
-        <v>349</v>
-      </c>
-      <c r="AW24" s="36" t="s">
-        <v>350</v>
-      </c>
       <c r="AX24" s="36" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="AY24" s="36" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:51">
       <c r="A25" s="32"/>
       <c r="B25" s="37" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="C25" s="35"/>
       <c r="D25" s="35"/>
@@ -8818,14 +7821,14 @@
     <row r="26" customFormat="1" ht="94.5" spans="1:51">
       <c r="A26" s="38"/>
       <c r="B26" s="37" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="C26" s="35"/>
       <c r="D26" s="35"/>
       <c r="E26" s="35"/>
       <c r="F26" s="35"/>
       <c r="G26" s="35" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="H26" s="35"/>
       <c r="I26" s="35"/>
@@ -8833,10 +7836,10 @@
       <c r="K26" s="35"/>
       <c r="L26" s="35"/>
       <c r="M26" s="35" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="N26" s="35" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="O26" s="35"/>
       <c r="P26" s="35"/>
@@ -8865,10 +7868,10 @@
       <c r="AM26" s="35"/>
       <c r="AN26" s="35"/>
       <c r="AO26" s="35" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="AP26" s="35" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="AQ26" s="35"/>
       <c r="AR26" s="35"/>
@@ -8882,10 +7885,10 @@
     </row>
     <row r="27" s="13" customFormat="1" ht="27" spans="1:51">
       <c r="A27" s="39" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="C27" s="54"/>
       <c r="D27" s="54"/>
@@ -8988,7 +7991,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="8"/>
@@ -8996,31 +7999,31 @@
     <row r="2" spans="1:3">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="11"/>
       <c r="B3" s="10"/>
       <c r="C3" s="3" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="11"/>
       <c r="B4" s="10"/>
       <c r="C4" s="3" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="11"/>
       <c r="B5" s="10"/>
       <c r="C5" s="3" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -9031,31 +8034,31 @@
     <row r="7" spans="1:3">
       <c r="A7" s="11"/>
       <c r="B7" s="10" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="11"/>
       <c r="B8" s="10"/>
       <c r="C8" s="3" t="s">
-        <v>368</v>
+        <v>359</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="11"/>
       <c r="B9" s="10"/>
       <c r="C9" s="3" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="11"/>
       <c r="B10" s="10"/>
       <c r="C10" s="3" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -9066,38 +8069,38 @@
     <row r="12" spans="1:3">
       <c r="A12" s="11"/>
       <c r="B12" s="10" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="11"/>
       <c r="B13" s="10"/>
       <c r="C13" s="3" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="11"/>
       <c r="B14" s="10"/>
       <c r="C14" s="3" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="11"/>
       <c r="B15" s="10"/>
       <c r="C15" s="3" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="11"/>
       <c r="B16" s="10"/>
       <c r="C16" s="3" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -9108,31 +8111,31 @@
     <row r="18" spans="1:3">
       <c r="A18" s="11"/>
       <c r="B18" s="10" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="11"/>
       <c r="B19" s="10"/>
       <c r="C19" s="2" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="11"/>
       <c r="B20" s="10"/>
       <c r="C20" s="2" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="11"/>
       <c r="B21" s="10"/>
       <c r="C21" s="2" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
     </row>
   </sheetData>
@@ -9161,138 +8164,138 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
     </row>
     <row r="4" ht="94.5" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="3" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
     </row>
     <row r="5" ht="27" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="4" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:4">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="2" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="2" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
     </row>
     <row r="11" ht="40.5" spans="1:4">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="2" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
     </row>
     <row r="12" ht="27" spans="1:4">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="2" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
     </row>
   </sheetData>

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -9,10 +9,11 @@
   <sheets>
     <sheet name="49过程输入输出工具" sheetId="1" r:id="rId1"/>
     <sheet name="49子过程图表实例（自己画的）" sheetId="2" r:id="rId2"/>
-    <sheet name="必背默写知识点" sheetId="3" r:id="rId3"/>
-    <sheet name="计算公式汇总" sheetId="4" r:id="rId4"/>
-    <sheet name="案例分析技巧汇总" sheetId="5" r:id="rId5"/>
-    <sheet name="完整论文" sheetId="6" r:id="rId6"/>
+    <sheet name="8大绩效域" sheetId="8" r:id="rId3"/>
+    <sheet name="必背默写知识点" sheetId="3" r:id="rId4"/>
+    <sheet name="计算公式汇总" sheetId="4" r:id="rId5"/>
+    <sheet name="案例分析技巧汇总" sheetId="5" r:id="rId6"/>
+    <sheet name="完整论文" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="387">
   <si>
     <t>项目整合管理</t>
   </si>
@@ -67,14 +68,13 @@
     <t>识别、定义、统一协调项目管理各过程及活动，贯穿项目始终,具备建立联系和统一的性质</t>
   </si>
   <si>
-    <t xml:space="preserve">定义和控制项目内工作,确保项目做且只做所需的全部工作，包括产品范围和项目范围
-</t>
+    <t>定义和控制项目和产品的范围,确保项目只做需要做的全部工作</t>
   </si>
   <si>
     <t>为了项目在批准的时间内完成，对进度进行规划、估算、管理和控制的过程</t>
   </si>
   <si>
-    <t>为了项目在批准的预算内完成，对成本进行规划、估算、预算、融资、筹资、管理和控制的过程</t>
+    <t>对成本进行规划、估算、预算、融资、筹资、管理和控制，使得项目在预算内完成</t>
   </si>
   <si>
     <t>确定质量方针、目标和职责，并通过质量体系中的质量规划、质量保证、质量控
@@ -1218,7 +1218,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  执行项目管理计划中的工作，实施已批准的变更请求，来管理项目工作和可交付成果，提高项目成功可能性</t>
+      <t xml:space="preserve">  执行项目管理计划中的工作、实施已批准的变更请求、管理项目工作和可交付成果，提高项目成功可能性</t>
     </r>
   </si>
   <si>
@@ -1250,7 +1250,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 为实现项目管理计划中确定的绩效目标，而对项目进展进行跟踪、审查、报告，来让干系人了解项目当前状，通过成本和进度预测了解项目未来状态，并认可处理绩效问题的行动</t>
+      <t xml:space="preserve"> 为实现项目管理计划中定的绩效目标，而对项目进展进行跟踪、审查、报告，来让干系人了解项目当前状，通过成本和进度预测了解项目未来状态，并认可处理绩效问题的行动</t>
     </r>
   </si>
   <si>
@@ -1266,7 +1266,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>管理、审查、批准可交付成果、项目文件、项目管理计划的变更，对变更处理结果进行沟通</t>
+      <t>管理、审查、批准可交付成果、项目文件、项目管理计划的变更，并沟通变更处理结果</t>
     </r>
   </si>
   <si>
@@ -1298,7 +1298,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  制定一份定义、确认、控制项目范围的文件，为管理项目范围提供指南和方向</t>
+      <t xml:space="preserve">  制定一份如何定义、确认、控制项目范围的文件，作为管理项目范围的指南和方向</t>
     </r>
   </si>
   <si>
@@ -1319,14 +1319,70 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t xml:space="preserve">定义作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  对项目产品、服务成果的边界和验收标准的详细描述</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>把项目可交付成果、工作分解成小且易管理的组件，形成交付内容架构</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 通过客观性的验收项目可交付成果，来提高最终产品、服务成果被验收的可能</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 为维护项目范围基准，监督项目和产品的范围状态，管理范围基准变更</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1338,19 +1394,171 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  是制定项目和产品详细描述的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+      <t xml:space="preserve">  制定一份如何规划、编制、管理、执行、控制项目进度的文件，作为管理项目进度的指南和方向</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>为完成项目可交付成果，将工作包分解为进度活动，是项目进度估算、规划、执行、监督和控制的基础</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">作用定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  识别记录项目活动之间逻辑关系，使项目在制约因素下获得最高的效率</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  估算完成单项活动所需花费的时间量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 分析活动顺序、持续时间、资源需求和进度制约因素，创建具有计划日期的进度模型，以便项目执行和监控</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  为维护进度基准，监督项目状态并更新项目进度，管理进度基准变更</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 制定一份如何估算、预算、管理、监督、控制项目成本的文件，作为管理项目成本的指南和方向</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>对项目所需资源成本进行近似估算， 确定项目所需的资金</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  汇总所有活动、工作包的估算成本来确定项目成本基准，方便监督和控制项目绩效</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  为维护成本基准，监督项目状态，更新项目成本，管理成本基准变更</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  制定一份是识别项目可交付成果的质量要求、标准，并描述如何证明</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1362,7 +1570,119 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  创建工作分解结构WBS是把项目可交付成果和项目工作分解成较小、更易于管理的组件的过程</t>
+      <t xml:space="preserve">  把质量政策用于项目，将质量管理计划转化质量活动，提高实现质量目标的可能性，识别无效过程和导致质量低劣的原因，使用质量控制数据结果，向干系人展示项目的质量状态</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">定义作用：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  监督和记录质量管理活动执行结果，确保项目输出满足规范标准要求和客户期望，核实项目可交付成果满足最终验收质量要求</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是定义如何估算、获取、管理和利用团队及其实物资源的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是估算执行项目所需的团队资源，以及材料、设备和用品的类型和数量的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是获取项目所需的团队成员、设施、设备、材料、用品和其他资源的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是提高工作能力，促进团队成员互动，改善团队整体氛围，以提高项目绩效的过程</t>
     </r>
   </si>
   <si>
@@ -1386,7 +1706,199 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 是正式验收已完成的项目可交付成果的过程</t>
+      <t xml:space="preserve"> 是跟踪团队成员工作表现、提供反馈、解决问题并管理团队变更以优化项目绩效的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是确保按计划为项目分配实物资源，以及根据资源使用计划监督资源实际使用情况，并采取必要纠正措施的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是基于每个干系人或干系人群体的信息需求、可用的组织资产，以及具体项目的需求，为项目沟通活动制定恰当的方法和计划的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是确保项目信息及时且恰当的收集、生成、发布、存储、检索、管理、监督和最终处置的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是确保满足项目及其干系人的信息需求的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是定义如何实施项目风险管理活动的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是识别单个项目风险以及整体项目风险的来源，并记录风险特征的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是通过评估单个项目风险发生的概率和影响及其他特征，对风险进行优先级排序，从而为后续分析或行动提供基础的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是就已识别的单个项目风险和不确定性的其他来源对整体项目目标的影响进行定量分析的过程</t>
     </r>
   </si>
   <si>
@@ -1410,7 +1922,31 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> 是监督项目和产品的范围状态，管理范围基准变更的过程</t>
+      <t xml:space="preserve"> 是为了应对项目风险，而制定可选方案、选择应对策略并商定应对行动的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是执行商定的风险应对计划的过程</t>
     </r>
   </si>
   <si>
@@ -1434,7 +1970,79 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  是为规划、编制、管理、执行和控制项目进度而制定政策、程序和文档的过程</t>
+      <t xml:space="preserve">  是在整个项目期间，监督风险应对计划的实施，并跟踪已识别风险、识别和分析新风险，以及评估风险管理有效性的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是记录项目采购决策、明确采购方法，及识别潜在卖方的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是获取卖方应答、选择卖方并授予合同的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是管理采购关系、监督合同绩效、实施必要的变更和纠偏，以及关闭合同的过程</t>
     </r>
   </si>
   <si>
@@ -1458,7 +2066,31 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>是识别和记录为完成项目可交付成果而须采取的具体行动的过程</t>
+      <t>是定期识别项目干系人，分析和记录他们的利益、参与度、项目依赖性、影响力和对项目成功的潜在影响的过程</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是根据干系人的需求、期望、利益和对项目的潜在影响，制定项目干系人参与项目的方法的过程</t>
     </r>
   </si>
   <si>
@@ -1482,103 +2114,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">  是识别和记录项目活动之间关系的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是根据资源估算的结果，估算完成单项活动所需工作时段数的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 是分析活动顺序、持续时间、资源需求和进度制约因素，创建进度模型，从而落实项目执行和监控的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是监督项目状态，以更新项目进度和管理进度基准变更的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 是确定如何估算、预算、管理、监督和控制项目成本的过程</t>
+      <t xml:space="preserve">  是通过与干系人进行沟通协作，以满足其需求与期望、处理问题，并促进干系人合理参与的过程</t>
     </r>
   </si>
   <si>
@@ -1602,1091 +2138,7 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>是对完成项目工作所需资源成本进行近似估算的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是汇总所有单个活动或工作包的估算成本，建立一个经批准的成本基准的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是监督项目状态，以更新项目成本和管理成本基准变更的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是识别项目及其可交付成果的质量要求、标准，并书面描述项目将如何证明符合质量要求、标准的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是把组织的质量政策用于项目，并将质量管理计划转化为可执行的质量活动的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是为了评估绩效，确保项目输出完整、正确且满足客户期望，而监督和记录质量管理活动执行结果的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是定义如何估算、获取、管理和利用团队及其实物资源的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是估算执行项目所需的团队资源，以及材料、设备和用品的类型和数量的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是获取项目所需的团队成员、设施、设备、材料、用品和其他资源的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是提高工作能力，促进团队成员互动，改善团队整体氛围，以提高项目绩效的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 是跟踪团队成员工作表现、提供反馈、解决问题并管理团队变更以优化项目绩效的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是确保按计划为项目分配实物资源，以及根据资源使用计划监督资源实际使用情况，并采取必要纠正措施的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是基于每个干系人或干系人群体的信息需求、可用的组织资产，以及具体项目的需求，为项目沟通活动制定恰当的方法和计划的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是确保项目信息及时且恰当的收集、生成、发布、存储、检索、管理、监督和最终处置的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是确保满足项目及其干系人的信息需求的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是定义如何实施项目风险管理活动的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是识别单个项目风险以及整体项目风险的来源，并记录风险特征的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是通过评估单个项目风险发生的概率和影响及其他特征，对风险进行优先级排序，从而为后续分析或行动提供基础的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是就已识别的单个项目风险和不确定性的其他来源对整体项目目标的影响进行定量分析的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 是为了应对项目风险，而制定可选方案、选择应对策略并商定应对行动的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是执行商定的风险应对计划的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是在整个项目期间，监督风险应对计划的实施，并跟踪已识别风险、识别和分析新风险，以及评估风险管理有效性的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 是记录项目采购决策、明确采购方法，及识别潜在卖方的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是获取卖方应答、选择卖方并授予合同的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是管理采购关系、监督合同绩效、实施必要的变更和纠偏，以及关闭合同的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是定期识别项目干系人，分析和记录他们的利益、参与度、项目依赖性、影响力和对项目成功的潜在影响的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 是根据干系人的需求、期望、利益和对项目的潜在影响，制定项目干系人参与项目的方法的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是通过与干系人进行沟通协作，以满足其需求与期望、处理问题，并促进干系人合理参与的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>是监督项目干系人的关系，并通过修订参与策略和计划来引导干系人合理参与项目的过程</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是描述产品、服务或成果的边界和验收标准</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>为所要交付的内容提供架构</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  1、使验收过程具有客观性
-  2、通过确认每个可交付成果来提高最终产品、服务或成果获得验收的可能性</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是在整个项目期间保持对范围基准的维护</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是为如何在整个项目期间管理项目进度提供指南和方向</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 将工作包分解为进度活动，作为对项目工作进行进度估算、规划、执行、监督和控制的基础</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  定义工作之间的逻辑顺序，以便在既定的所有项目制约因素下获得最高的效率</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是确定完成每个活动所需花费的时间量</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  为完成项目活动而制定具有计划日期的进度模型</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  在整个项目期间保持对进度基准的维护</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  在整个项目期间为如何管理项目成本提供指南和方向</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  确定项目所需的资金</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  确定可以依据其来进行监督和控制项目绩效的成本基准</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  在整个项目期间保持对成本基准的维护</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是为在整个项目期间如何管理和核实质量提供指南和方向</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  1、提高实现质量目标的可能性
-  2、识别无效过程和导致质量低劣的原因
-  3、使用控制质量过程的数据和结果向干系人展示项目的总体质量状态</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">作用：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  1、核实项目可交付成果和工作已经达到主要干系人的质量要求，可供最终验收
-  2、确定项目输出是否达到预期目的，这些输出需要满足所有适用标准、要求、法规和规范</t>
     </r>
   </si>
   <si>
@@ -5924,7 +5376,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" s="12" customFormat="1" ht="94.5" spans="1:51">
+    <row r="4" s="12" customFormat="1" ht="108" spans="1:51">
       <c r="A4" s="25"/>
       <c r="B4" s="25"/>
       <c r="C4" s="28" t="s">
@@ -6075,7 +5527,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" s="12" customFormat="1" ht="108" spans="1:51">
+    <row r="5" s="12" customFormat="1" ht="94.5" spans="1:51">
       <c r="A5" s="25"/>
       <c r="B5" s="25"/>
       <c r="C5" s="28"/>
@@ -6087,590 +5539,556 @@
       <c r="I5" s="28"/>
       <c r="J5" s="28"/>
       <c r="K5" s="28"/>
-      <c r="L5" s="28" t="s">
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
+      <c r="V5" s="28"/>
+      <c r="W5" s="28"/>
+      <c r="X5" s="28"/>
+      <c r="Y5" s="28"/>
+      <c r="Z5" s="28"/>
+      <c r="AA5" s="28"/>
+      <c r="AB5" s="28"/>
+      <c r="AC5" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="M5" s="28" t="s">
+      <c r="AD5" s="28" t="s">
         <v>119</v>
       </c>
-      <c r="N5" s="28" t="s">
+      <c r="AE5" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="O5" s="28" t="s">
+      <c r="AF5" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="P5" s="28" t="s">
+      <c r="AG5" s="28" t="s">
         <v>122</v>
       </c>
-      <c r="Q5" s="28" t="s">
+      <c r="AH5" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="R5" s="28" t="s">
+      <c r="AI5" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="S5" s="28" t="s">
+      <c r="AJ5" s="28" t="s">
         <v>125</v>
       </c>
-      <c r="T5" s="28" t="s">
+      <c r="AK5" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="U5" s="28" t="s">
+      <c r="AL5" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="V5" s="28" t="s">
+      <c r="AM5" s="28" t="s">
         <v>128</v>
       </c>
-      <c r="W5" s="28" t="s">
+      <c r="AN5" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="X5" s="28" t="s">
+      <c r="AO5" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="Y5" s="28" t="s">
+      <c r="AP5" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="Z5" s="28" t="s">
+      <c r="AQ5" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="AA5" s="28" t="s">
+      <c r="AR5" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="AB5" s="28" t="s">
+      <c r="AS5" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="AC5" s="28" t="s">
+      <c r="AT5" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="AD5" s="28" t="s">
+      <c r="AU5" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="AE5" s="28" t="s">
+      <c r="AV5" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="AF5" s="28" t="s">
+      <c r="AW5" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="AG5" s="28" t="s">
+      <c r="AX5" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="AH5" s="28" t="s">
+      <c r="AY5" s="28" t="s">
         <v>140</v>
-      </c>
-      <c r="AI5" s="28" t="s">
-        <v>141</v>
-      </c>
-      <c r="AJ5" s="28" t="s">
-        <v>142</v>
-      </c>
-      <c r="AK5" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="AL5" s="28" t="s">
-        <v>144</v>
-      </c>
-      <c r="AM5" s="28" t="s">
-        <v>145</v>
-      </c>
-      <c r="AN5" s="28" t="s">
-        <v>146</v>
-      </c>
-      <c r="AO5" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="AP5" s="28" t="s">
-        <v>148</v>
-      </c>
-      <c r="AQ5" s="28" t="s">
-        <v>149</v>
-      </c>
-      <c r="AR5" s="28" t="s">
-        <v>150</v>
-      </c>
-      <c r="AS5" s="28" t="s">
-        <v>151</v>
-      </c>
-      <c r="AT5" s="28" t="s">
-        <v>152</v>
-      </c>
-      <c r="AU5" s="28" t="s">
-        <v>153</v>
-      </c>
-      <c r="AV5" s="28" t="s">
-        <v>154</v>
-      </c>
-      <c r="AW5" s="28" t="s">
-        <v>155</v>
-      </c>
-      <c r="AX5" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="AY5" s="28" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="6" s="12" customFormat="1" ht="27" spans="1:51">
       <c r="A6" s="25"/>
       <c r="B6" s="25"/>
       <c r="C6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="H6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="I6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="J6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="K6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="L6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="M6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="N6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="O6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="P6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="Q6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="R6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="S6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="T6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="U6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="V6" s="28" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="W6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="X6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="Y6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="Z6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AA6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AB6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AC6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AD6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AE6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AF6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AG6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AH6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AI6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AJ6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AK6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AL6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AM6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AN6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AO6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AP6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AQ6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AR6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AS6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AT6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AU6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AV6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AW6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AX6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
       <c r="AY6" s="29" t="s">
-        <v>158</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" s="12" customFormat="1" ht="54" spans="1:51">
       <c r="A7" s="30" t="s">
-        <v>160</v>
+        <v>143</v>
       </c>
       <c r="B7" s="29" t="s">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="C7" s="31" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="G7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="H7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="I7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="J7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="K7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="L7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="M7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="N7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="O7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="P7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="Q7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="R7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="S7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="T7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="U7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="V7" s="28" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="W7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="X7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="Y7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="Z7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AA7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AB7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AC7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AD7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AE7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AF7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AG7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AH7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AI7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AJ7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AK7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AL7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AM7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AN7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AO7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AP7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AQ7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AR7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AS7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AT7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AU7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AV7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AW7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AX7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
       <c r="AY7" s="29" t="s">
-        <v>162</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" ht="67.5" spans="1:51">
       <c r="A8" s="32"/>
       <c r="B8" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="G8" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="I8" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="J8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="K8" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="L8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="M8" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="N8" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="O8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="P8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="R8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="S8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="T8" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="U8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="V8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="W8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="X8" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="Y8" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="Z8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AA8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AB8" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="AC8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AD8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AE8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AG8" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="AH8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AJ8" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="AK8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AL8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AM8" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="AN8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AO8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AQ8" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="AR8" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="AS8" s="35" t="s">
         <v>166</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="AT8" s="35" t="s">
         <v>167</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="AU8" s="35" t="s">
         <v>168</v>
       </c>
-      <c r="G8" s="34" t="s">
+      <c r="AV8" s="35" t="s">
         <v>169</v>
       </c>
-      <c r="H8" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="I8" s="34" t="s">
-        <v>171</v>
-      </c>
-      <c r="J8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="K8" s="34" t="s">
-        <v>173</v>
-      </c>
-      <c r="L8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="M8" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="N8" s="34" t="s">
-        <v>175</v>
-      </c>
-      <c r="O8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="P8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="Q8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="R8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="S8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="T8" s="34" t="s">
-        <v>176</v>
-      </c>
-      <c r="U8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="V8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="W8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="X8" s="34" t="s">
-        <v>177</v>
-      </c>
-      <c r="Y8" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="Z8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="AA8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="AB8" s="34" t="s">
-        <v>179</v>
-      </c>
-      <c r="AC8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="AD8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="AE8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="AF8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="AG8" s="34" t="s">
-        <v>180</v>
-      </c>
-      <c r="AH8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="AI8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="AJ8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AK8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="AL8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="AM8" s="34" t="s">
-        <v>182</v>
-      </c>
-      <c r="AN8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="AO8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="AP8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="AQ8" s="34" t="s">
-        <v>172</v>
-      </c>
-      <c r="AR8" s="34" t="s">
-        <v>181</v>
-      </c>
-      <c r="AS8" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="AT8" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="AU8" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="AV8" s="35" t="s">
-        <v>186</v>
-      </c>
       <c r="AW8" s="35" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="AX8" s="36" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="AY8" s="36" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" ht="40.5" spans="1:51">
       <c r="A9" s="32"/>
       <c r="B9" s="37" t="s">
-        <v>187</v>
+        <v>170</v>
       </c>
       <c r="C9" s="35"/>
       <c r="D9" s="35"/>
@@ -6681,12 +6099,12 @@
       <c r="I9" s="35"/>
       <c r="J9" s="35"/>
       <c r="K9" s="35" t="s">
-        <v>188</v>
+        <v>171</v>
       </c>
       <c r="L9" s="35"/>
       <c r="M9" s="35"/>
       <c r="N9" s="35" t="s">
-        <v>189</v>
+        <v>172</v>
       </c>
       <c r="O9" s="35"/>
       <c r="P9" s="35"/>
@@ -6729,7 +6147,7 @@
     <row r="10" ht="81" spans="1:51">
       <c r="A10" s="38"/>
       <c r="B10" s="37" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="C10" s="35"/>
       <c r="D10" s="35"/>
@@ -6740,14 +6158,14 @@
       <c r="I10" s="35"/>
       <c r="J10" s="35"/>
       <c r="K10" s="35" t="s">
-        <v>191</v>
+        <v>174</v>
       </c>
       <c r="L10" s="35" t="s">
-        <v>192</v>
+        <v>175</v>
       </c>
       <c r="M10" s="35"/>
       <c r="N10" s="35" t="s">
-        <v>193</v>
+        <v>176</v>
       </c>
       <c r="O10" s="35"/>
       <c r="P10" s="35"/>
@@ -6762,7 +6180,7 @@
       <c r="Y10" s="35"/>
       <c r="Z10" s="35"/>
       <c r="AA10" s="35" t="s">
-        <v>194</v>
+        <v>177</v>
       </c>
       <c r="AB10" s="35"/>
       <c r="AC10" s="35"/>
@@ -6773,7 +6191,7 @@
       <c r="AH10" s="35"/>
       <c r="AI10" s="35"/>
       <c r="AJ10" s="35" t="s">
-        <v>195</v>
+        <v>178</v>
       </c>
       <c r="AK10" s="35"/>
       <c r="AL10" s="35"/>
@@ -6793,10 +6211,10 @@
     </row>
     <row r="11" spans="1:51">
       <c r="A11" s="39" t="s">
-        <v>196</v>
+        <v>179</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>197</v>
+        <v>180</v>
       </c>
       <c r="C11" s="13"/>
       <c r="D11" s="13"/>
@@ -6850,10 +6268,10 @@
     </row>
     <row r="12" spans="1:51">
       <c r="A12" s="39" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="B12" s="41" t="s">
-        <v>199</v>
+        <v>182</v>
       </c>
       <c r="C12" s="13"/>
       <c r="D12" s="13"/>
@@ -6907,131 +6325,131 @@
     </row>
     <row r="14" ht="94.5" spans="1:51">
       <c r="A14" s="42" t="s">
-        <v>200</v>
+        <v>183</v>
       </c>
       <c r="B14" s="43" t="s">
-        <v>201</v>
+        <v>184</v>
       </c>
       <c r="C14" s="44"/>
       <c r="D14" s="45"/>
       <c r="E14" s="45"/>
       <c r="F14" s="45" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="G14" s="45"/>
       <c r="H14" s="45" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="I14" s="45"/>
       <c r="J14" s="45"/>
       <c r="K14" s="45" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="L14" s="45" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="M14" s="45" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="N14" s="45" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="O14" s="45"/>
       <c r="P14" s="45"/>
       <c r="Q14" s="45" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="R14" s="45" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="S14" s="45" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="T14" s="45" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="U14" s="45" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="V14" s="45"/>
       <c r="W14" s="45" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="X14" s="45" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="Y14" s="45" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="Z14" s="45" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="AA14" s="45" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="AB14" s="45" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="AC14" s="45" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="AD14" s="45" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="AE14" s="45" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="AF14" s="45" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="AG14" s="45"/>
       <c r="AH14" s="45" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="AI14" s="45" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="AJ14" s="45" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="AK14" s="45"/>
       <c r="AL14" s="45"/>
       <c r="AM14" s="45" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="AN14" s="45" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="AO14" s="45" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="AP14" s="45" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="AQ14" s="45"/>
       <c r="AR14" s="45" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="AS14" s="46" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="AT14" s="45" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="AU14" s="45" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="AV14" s="36"/>
       <c r="AW14" s="36"/>
       <c r="AX14" s="35" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="AY14" s="35"/>
     </row>
     <row r="15" spans="1:51">
       <c r="A15" s="47"/>
       <c r="B15" s="48" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="C15" s="49"/>
       <c r="D15" s="41"/>
@@ -7086,13 +6504,13 @@
     <row r="16" ht="67.5" spans="1:51">
       <c r="A16" s="47"/>
       <c r="B16" s="48" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="C16" s="50" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="D16" s="51" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="E16" s="41"/>
       <c r="F16" s="41"/>
@@ -7101,7 +6519,7 @@
       <c r="I16" s="41"/>
       <c r="J16" s="41"/>
       <c r="K16" s="51" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="L16" s="41"/>
       <c r="M16" s="41"/>
@@ -7118,13 +6536,13 @@
       <c r="X16" s="41"/>
       <c r="Y16" s="41"/>
       <c r="Z16" s="51" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="AA16" s="41" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="AB16" s="51" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="AC16" s="41"/>
       <c r="AD16" s="41"/>
@@ -7137,24 +6555,24 @@
       <c r="AK16" s="41"/>
       <c r="AL16" s="41"/>
       <c r="AM16" s="51" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="AN16" s="41"/>
       <c r="AO16" s="41" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="AP16" s="41" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="AQ16" s="41"/>
       <c r="AR16" s="41"/>
       <c r="AS16" s="41" t="s">
-        <v>244</v>
+        <v>227</v>
       </c>
       <c r="AT16" s="41"/>
       <c r="AU16" s="41"/>
       <c r="AV16" s="51" t="s">
-        <v>245</v>
+        <v>228</v>
       </c>
       <c r="AW16" s="41"/>
       <c r="AX16" s="41"/>
@@ -7163,61 +6581,61 @@
     <row r="17" ht="81" spans="1:51">
       <c r="A17" s="47"/>
       <c r="B17" s="48" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="C17" s="49"/>
       <c r="D17" s="41"/>
       <c r="E17" s="41"/>
       <c r="F17" s="41"/>
       <c r="G17" s="51" t="s">
-        <v>247</v>
+        <v>230</v>
       </c>
       <c r="H17" s="41"/>
       <c r="I17" s="51" t="s">
-        <v>248</v>
+        <v>231</v>
       </c>
       <c r="J17" s="41"/>
       <c r="K17" s="41" t="s">
-        <v>249</v>
+        <v>232</v>
       </c>
       <c r="L17" s="41" t="s">
-        <v>250</v>
+        <v>233</v>
       </c>
       <c r="M17" s="41"/>
       <c r="N17" s="41"/>
       <c r="O17" s="51" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="P17" s="41"/>
       <c r="Q17" s="41"/>
       <c r="R17" s="41"/>
       <c r="S17" s="51" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="T17" s="51" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="U17" s="51" t="s">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="V17" s="41"/>
       <c r="W17" s="51" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="X17" s="41" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="Y17" s="51" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="Z17" s="51" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="AA17" s="51" t="s">
-        <v>259</v>
+        <v>242</v>
       </c>
       <c r="AB17" s="51" t="s">
-        <v>260</v>
+        <v>243</v>
       </c>
       <c r="AC17" s="41"/>
       <c r="AD17" s="41"/>
@@ -7225,54 +6643,54 @@
       <c r="AF17" s="41"/>
       <c r="AG17" s="41"/>
       <c r="AH17" s="51" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
       <c r="AI17" s="41"/>
       <c r="AJ17" s="41"/>
       <c r="AK17" s="41"/>
       <c r="AL17" s="41" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="AM17" s="51" t="s">
-        <v>263</v>
+        <v>246</v>
       </c>
       <c r="AN17" s="51" t="s">
-        <v>264</v>
+        <v>247</v>
       </c>
       <c r="AO17" s="51" t="s">
-        <v>265</v>
+        <v>248</v>
       </c>
       <c r="AP17" s="51" t="s">
-        <v>266</v>
+        <v>249</v>
       </c>
       <c r="AQ17" s="41"/>
       <c r="AR17" s="51" t="s">
-        <v>267</v>
+        <v>250</v>
       </c>
       <c r="AS17" s="41" t="s">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="AT17" s="41" t="s">
-        <v>269</v>
+        <v>252</v>
       </c>
       <c r="AU17" s="51" t="s">
-        <v>270</v>
+        <v>253</v>
       </c>
       <c r="AV17" s="51" t="s">
-        <v>271</v>
+        <v>254</v>
       </c>
       <c r="AW17" s="51" t="s">
-        <v>272</v>
+        <v>255</v>
       </c>
       <c r="AX17" s="41"/>
       <c r="AY17" s="51" t="s">
-        <v>273</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" ht="81" spans="1:51">
       <c r="A18" s="47"/>
       <c r="B18" s="48" t="s">
-        <v>274</v>
+        <v>257</v>
       </c>
       <c r="C18" s="49"/>
       <c r="D18" s="41"/>
@@ -7283,7 +6701,7 @@
       <c r="I18" s="41"/>
       <c r="J18" s="41"/>
       <c r="K18" s="51" t="s">
-        <v>275</v>
+        <v>258</v>
       </c>
       <c r="L18" s="41"/>
       <c r="M18" s="41"/>
@@ -7300,16 +6718,16 @@
       <c r="X18" s="41"/>
       <c r="Y18" s="41"/>
       <c r="Z18" s="51" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="AA18" s="51" t="s">
-        <v>277</v>
+        <v>260</v>
       </c>
       <c r="AB18" s="51" t="s">
-        <v>278</v>
+        <v>261</v>
       </c>
       <c r="AC18" s="51" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="AD18" s="41"/>
       <c r="AE18" s="41"/>
@@ -7317,16 +6735,16 @@
       <c r="AG18" s="41"/>
       <c r="AH18" s="41"/>
       <c r="AI18" s="41" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="AJ18" s="41"/>
       <c r="AK18" s="41" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
       <c r="AL18" s="41"/>
       <c r="AM18" s="41"/>
       <c r="AN18" s="51" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="AO18" s="41"/>
       <c r="AP18" s="41"/>
@@ -7336,20 +6754,20 @@
       <c r="AT18" s="41"/>
       <c r="AU18" s="41"/>
       <c r="AV18" s="51" t="s">
-        <v>282</v>
+        <v>265</v>
       </c>
       <c r="AW18" s="51" t="s">
-        <v>283</v>
+        <v>266</v>
       </c>
       <c r="AX18" s="41"/>
       <c r="AY18" s="51" t="s">
-        <v>280</v>
+        <v>263</v>
       </c>
     </row>
     <row r="19" ht="40.5" spans="1:51">
       <c r="A19" s="47"/>
       <c r="B19" s="48" t="s">
-        <v>284</v>
+        <v>267</v>
       </c>
       <c r="C19" s="49"/>
       <c r="D19" s="41"/>
@@ -7357,15 +6775,15 @@
       <c r="F19" s="41"/>
       <c r="G19" s="41"/>
       <c r="H19" s="51" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="I19" s="41"/>
       <c r="J19" s="41"/>
       <c r="K19" s="51" t="s">
-        <v>285</v>
+        <v>268</v>
       </c>
       <c r="L19" s="41" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="M19" s="41"/>
       <c r="N19" s="41"/>
@@ -7386,7 +6804,7 @@
       <c r="AC19" s="41"/>
       <c r="AD19" s="41"/>
       <c r="AE19" s="41" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="AF19" s="41"/>
       <c r="AG19" s="41"/>
@@ -7399,7 +6817,7 @@
       <c r="AN19" s="41"/>
       <c r="AO19" s="41"/>
       <c r="AP19" s="41" t="s">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="AQ19" s="41"/>
       <c r="AR19" s="41"/>
@@ -7410,13 +6828,13 @@
       <c r="AW19" s="51"/>
       <c r="AX19" s="41"/>
       <c r="AY19" s="51" t="s">
-        <v>287</v>
+        <v>270</v>
       </c>
     </row>
     <row r="20" ht="54" spans="1:51">
       <c r="A20" s="47"/>
       <c r="B20" s="48" t="s">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="C20" s="49"/>
       <c r="D20" s="41"/>
@@ -7452,7 +6870,7 @@
       <c r="AH20" s="41"/>
       <c r="AI20" s="41"/>
       <c r="AJ20" s="51" t="s">
-        <v>289</v>
+        <v>272</v>
       </c>
       <c r="AK20" s="41"/>
       <c r="AL20" s="41"/>
@@ -7473,13 +6891,13 @@
     <row r="21" ht="81" spans="1:51">
       <c r="A21" s="47"/>
       <c r="B21" s="52" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="C21" s="50" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="D21" s="50" t="s">
-        <v>291</v>
+        <v>274</v>
       </c>
       <c r="E21" s="41"/>
       <c r="F21" s="41"/>
@@ -7488,10 +6906,10 @@
       <c r="I21" s="41"/>
       <c r="J21" s="41"/>
       <c r="K21" s="51" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="L21" s="41" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="M21" s="41"/>
       <c r="N21" s="41"/>
@@ -7512,51 +6930,51 @@
       <c r="AC21" s="41"/>
       <c r="AD21" s="41"/>
       <c r="AE21" s="41" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="AF21" s="51" t="s">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="AG21" s="51" t="s">
-        <v>296</v>
+        <v>279</v>
       </c>
       <c r="AH21" s="41"/>
       <c r="AI21" s="51" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="AJ21" s="51" t="s">
-        <v>298</v>
+        <v>281</v>
       </c>
       <c r="AK21" s="41"/>
       <c r="AL21" s="41"/>
       <c r="AM21" s="41"/>
       <c r="AN21" s="41"/>
       <c r="AO21" s="41" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="AP21" s="41" t="s">
-        <v>293</v>
+        <v>276</v>
       </c>
       <c r="AQ21" s="41"/>
       <c r="AR21" s="41"/>
       <c r="AS21" s="41"/>
       <c r="AT21" s="41" t="s">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="AU21" s="41"/>
       <c r="AV21" s="41"/>
       <c r="AW21" s="41"/>
       <c r="AX21" s="51" t="s">
-        <v>299</v>
+        <v>282</v>
       </c>
       <c r="AY21" s="51" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:51">
       <c r="A22" s="53"/>
       <c r="B22" s="48" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="C22" s="49"/>
       <c r="D22" s="41"/>
@@ -7610,163 +7028,163 @@
     </row>
     <row r="24" ht="108" spans="1:51">
       <c r="A24" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="B24" s="37" t="s">
+        <v>286</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>287</v>
+      </c>
+      <c r="D24" s="35" t="s">
+        <v>170</v>
+      </c>
+      <c r="E24" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="F24" s="35" t="s">
+        <v>289</v>
+      </c>
+      <c r="G24" s="35" t="s">
+        <v>290</v>
+      </c>
+      <c r="H24" s="35" t="s">
+        <v>291</v>
+      </c>
+      <c r="I24" s="35" t="s">
+        <v>292</v>
+      </c>
+      <c r="J24" s="35" t="s">
+        <v>293</v>
+      </c>
+      <c r="K24" s="35" t="s">
+        <v>294</v>
+      </c>
+      <c r="L24" s="35" t="s">
+        <v>295</v>
+      </c>
+      <c r="M24" s="35" t="s">
+        <v>296</v>
+      </c>
+      <c r="N24" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="O24" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="P24" s="35" t="s">
+        <v>298</v>
+      </c>
+      <c r="Q24" s="35" t="s">
+        <v>299</v>
+      </c>
+      <c r="R24" s="35" t="s">
+        <v>300</v>
+      </c>
+      <c r="S24" s="35" t="s">
+        <v>301</v>
+      </c>
+      <c r="T24" s="35" t="s">
         <v>302</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="U24" s="35" t="s">
         <v>303</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="V24" s="35" t="s">
         <v>304</v>
       </c>
-      <c r="D24" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="E24" s="35" t="s">
+      <c r="W24" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="F24" s="35" t="s">
+      <c r="X24" s="35" t="s">
         <v>306</v>
       </c>
-      <c r="G24" s="35" t="s">
+      <c r="Y24" s="35" t="s">
         <v>307</v>
       </c>
-      <c r="H24" s="35" t="s">
+      <c r="Z24" s="35" t="s">
         <v>308</v>
       </c>
-      <c r="I24" s="35" t="s">
+      <c r="AA24" s="35" t="s">
         <v>309</v>
       </c>
-      <c r="J24" s="35" t="s">
+      <c r="AB24" s="35" t="s">
         <v>310</v>
       </c>
-      <c r="K24" s="35" t="s">
+      <c r="AC24" s="35" t="s">
         <v>311</v>
       </c>
-      <c r="L24" s="35" t="s">
+      <c r="AD24" s="35" t="s">
         <v>312</v>
       </c>
-      <c r="M24" s="35" t="s">
+      <c r="AE24" s="35" t="s">
         <v>313</v>
       </c>
-      <c r="N24" s="35" t="s">
+      <c r="AF24" s="35" t="s">
         <v>314</v>
       </c>
-      <c r="O24" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="P24" s="35" t="s">
+      <c r="AG24" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="Q24" s="35" t="s">
+      <c r="AH24" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="AI24" s="35" t="s">
         <v>316</v>
       </c>
-      <c r="R24" s="35" t="s">
+      <c r="AJ24" s="35" t="s">
         <v>317</v>
       </c>
-      <c r="S24" s="35" t="s">
+      <c r="AK24" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="AL24" s="35" t="s">
         <v>318</v>
       </c>
-      <c r="T24" s="35" t="s">
+      <c r="AM24" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="U24" s="35" t="s">
+      <c r="AN24" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="AO24" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="AP24" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="AQ24" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="AR24" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="AS24" s="35" t="s">
         <v>320</v>
       </c>
-      <c r="V24" s="35" t="s">
+      <c r="AT24" s="35" t="s">
         <v>321</v>
       </c>
-      <c r="W24" s="35" t="s">
+      <c r="AU24" s="35" t="s">
         <v>322</v>
       </c>
-      <c r="X24" s="35" t="s">
+      <c r="AV24" s="35" t="s">
         <v>323</v>
       </c>
-      <c r="Y24" s="35" t="s">
+      <c r="AW24" s="36" t="s">
         <v>324</v>
       </c>
-      <c r="Z24" s="35" t="s">
-        <v>325</v>
-      </c>
-      <c r="AA24" s="35" t="s">
-        <v>326</v>
-      </c>
-      <c r="AB24" s="35" t="s">
-        <v>327</v>
-      </c>
-      <c r="AC24" s="35" t="s">
-        <v>328</v>
-      </c>
-      <c r="AD24" s="35" t="s">
-        <v>329</v>
-      </c>
-      <c r="AE24" s="35" t="s">
-        <v>330</v>
-      </c>
-      <c r="AF24" s="35" t="s">
-        <v>331</v>
-      </c>
-      <c r="AG24" s="35" t="s">
-        <v>332</v>
-      </c>
-      <c r="AH24" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="AI24" s="35" t="s">
-        <v>333</v>
-      </c>
-      <c r="AJ24" s="35" t="s">
-        <v>334</v>
-      </c>
-      <c r="AK24" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="AL24" s="35" t="s">
-        <v>335</v>
-      </c>
-      <c r="AM24" s="35" t="s">
-        <v>336</v>
-      </c>
-      <c r="AN24" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="AO24" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="AP24" s="35" t="s">
-        <v>332</v>
-      </c>
-      <c r="AQ24" s="35" t="s">
-        <v>332</v>
-      </c>
-      <c r="AR24" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="AS24" s="35" t="s">
-        <v>337</v>
-      </c>
-      <c r="AT24" s="35" t="s">
-        <v>338</v>
-      </c>
-      <c r="AU24" s="35" t="s">
-        <v>339</v>
-      </c>
-      <c r="AV24" s="35" t="s">
-        <v>340</v>
-      </c>
-      <c r="AW24" s="36" t="s">
-        <v>341</v>
-      </c>
       <c r="AX24" s="36" t="s">
-        <v>332</v>
+        <v>315</v>
       </c>
       <c r="AY24" s="36" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:51">
       <c r="A25" s="32"/>
       <c r="B25" s="37" t="s">
-        <v>342</v>
+        <v>325</v>
       </c>
       <c r="C25" s="35"/>
       <c r="D25" s="35"/>
@@ -7821,14 +7239,14 @@
     <row r="26" customFormat="1" ht="94.5" spans="1:51">
       <c r="A26" s="38"/>
       <c r="B26" s="37" t="s">
-        <v>343</v>
+        <v>326</v>
       </c>
       <c r="C26" s="35"/>
       <c r="D26" s="35"/>
       <c r="E26" s="35"/>
       <c r="F26" s="35"/>
       <c r="G26" s="35" t="s">
-        <v>344</v>
+        <v>327</v>
       </c>
       <c r="H26" s="35"/>
       <c r="I26" s="35"/>
@@ -7836,10 +7254,10 @@
       <c r="K26" s="35"/>
       <c r="L26" s="35"/>
       <c r="M26" s="35" t="s">
-        <v>345</v>
+        <v>328</v>
       </c>
       <c r="N26" s="35" t="s">
-        <v>346</v>
+        <v>329</v>
       </c>
       <c r="O26" s="35"/>
       <c r="P26" s="35"/>
@@ -7868,10 +7286,10 @@
       <c r="AM26" s="35"/>
       <c r="AN26" s="35"/>
       <c r="AO26" s="35" t="s">
-        <v>347</v>
+        <v>330</v>
       </c>
       <c r="AP26" s="35" t="s">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="AQ26" s="35"/>
       <c r="AR26" s="35"/>
@@ -7885,10 +7303,10 @@
     </row>
     <row r="27" s="13" customFormat="1" ht="27" spans="1:51">
       <c r="A27" s="39" t="s">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>350</v>
+        <v>333</v>
       </c>
       <c r="C27" s="54"/>
       <c r="D27" s="54"/>
@@ -7981,6 +7399,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
@@ -7991,7 +7420,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="8"/>
@@ -7999,31 +7428,31 @@
     <row r="2" spans="1:3">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
-        <v>352</v>
+        <v>335</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>353</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="11"/>
       <c r="B3" s="10"/>
       <c r="C3" s="3" t="s">
-        <v>354</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="11"/>
       <c r="B4" s="10"/>
       <c r="C4" s="3" t="s">
-        <v>355</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="11"/>
       <c r="B5" s="10"/>
       <c r="C5" s="3" t="s">
-        <v>356</v>
+        <v>339</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -8034,31 +7463,31 @@
     <row r="7" spans="1:3">
       <c r="A7" s="11"/>
       <c r="B7" s="10" t="s">
-        <v>357</v>
+        <v>340</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>358</v>
+        <v>341</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="11"/>
       <c r="B8" s="10"/>
       <c r="C8" s="3" t="s">
-        <v>359</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="11"/>
       <c r="B9" s="10"/>
       <c r="C9" s="3" t="s">
-        <v>360</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="11"/>
       <c r="B10" s="10"/>
       <c r="C10" s="3" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -8069,38 +7498,38 @@
     <row r="12" spans="1:3">
       <c r="A12" s="11"/>
       <c r="B12" s="10" t="s">
-        <v>362</v>
+        <v>345</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>363</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="11"/>
       <c r="B13" s="10"/>
       <c r="C13" s="3" t="s">
-        <v>364</v>
+        <v>347</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="11"/>
       <c r="B14" s="10"/>
       <c r="C14" s="3" t="s">
-        <v>365</v>
+        <v>348</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="11"/>
       <c r="B15" s="10"/>
       <c r="C15" s="3" t="s">
-        <v>366</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="11"/>
       <c r="B16" s="10"/>
       <c r="C16" s="3" t="s">
-        <v>367</v>
+        <v>350</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -8111,31 +7540,31 @@
     <row r="18" spans="1:3">
       <c r="A18" s="11"/>
       <c r="B18" s="10" t="s">
-        <v>368</v>
+        <v>351</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>369</v>
+        <v>352</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="11"/>
       <c r="B19" s="10"/>
       <c r="C19" s="2" t="s">
-        <v>370</v>
+        <v>353</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="11"/>
       <c r="B20" s="10"/>
       <c r="C20" s="2" t="s">
-        <v>371</v>
+        <v>354</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="11"/>
       <c r="B21" s="10"/>
       <c r="C21" s="2" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -8151,7 +7580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D12"/>
@@ -8164,138 +7593,138 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
-        <v>379</v>
+        <v>362</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>380</v>
+        <v>363</v>
       </c>
     </row>
     <row r="4" ht="94.5" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="3" t="s">
-        <v>381</v>
+        <v>364</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>382</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" ht="27" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>383</v>
+        <v>366</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>384</v>
+        <v>367</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>385</v>
+        <v>368</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>386</v>
+        <v>369</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>387</v>
+        <v>370</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>388</v>
+        <v>371</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>390</v>
+        <v>373</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>391</v>
+        <v>374</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>392</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="4" t="s">
-        <v>351</v>
+        <v>334</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>393</v>
+        <v>376</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>394</v>
+        <v>377</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>395</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:4">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="2" t="s">
-        <v>396</v>
+        <v>379</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>397</v>
+        <v>380</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="2" t="s">
-        <v>398</v>
+        <v>381</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>399</v>
+        <v>382</v>
       </c>
     </row>
     <row r="11" ht="40.5" spans="1:4">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="2" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>401</v>
+        <v>384</v>
       </c>
     </row>
     <row r="12" ht="27" spans="1:4">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="2" t="s">
-        <v>402</v>
+        <v>385</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>403</v>
+        <v>386</v>
       </c>
     </row>
   </sheetData>
@@ -8305,17 +7734,6 @@
     <mergeCell ref="B1:B4"/>
     <mergeCell ref="B8:B12"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -8330,4 +7748,15 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -4,16 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="29868" windowHeight="13500" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="49过程输入输出工具" sheetId="1" r:id="rId1"/>
-    <sheet name="49子过程图表实例（自己画的）" sheetId="2" r:id="rId2"/>
-    <sheet name="8大绩效域" sheetId="8" r:id="rId3"/>
-    <sheet name="必背默写知识点" sheetId="3" r:id="rId4"/>
-    <sheet name="计算公式汇总" sheetId="4" r:id="rId5"/>
-    <sheet name="案例分析技巧汇总" sheetId="5" r:id="rId6"/>
-    <sheet name="完整论文" sheetId="6" r:id="rId7"/>
+    <sheet name="49过程输入输出工具-横版" sheetId="1" r:id="rId1"/>
+    <sheet name="49过程输入输出工具-竖版" sheetId="9" r:id="rId2"/>
+    <sheet name="49子过程图表实例（自己画的）" sheetId="2" r:id="rId3"/>
+    <sheet name="8大绩效域" sheetId="8" r:id="rId4"/>
+    <sheet name="必背默写知识点" sheetId="3" r:id="rId5"/>
+    <sheet name="计算公式汇总" sheetId="4" r:id="rId6"/>
+    <sheet name="案例分析技巧汇总" sheetId="5" r:id="rId7"/>
+    <sheet name="完整论文" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="511">
   <si>
     <t>项目整合管理</t>
   </si>
@@ -1175,6 +1176,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
   </t>
     </r>
@@ -1191,6 +1200,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
 </t>
     </r>
@@ -1207,6 +1224,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
 </t>
     </r>
@@ -1223,6 +1248,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
  </t>
     </r>
@@ -1239,6 +1272,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用： 
  </t>
     </r>
@@ -1255,6 +1296,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
   </t>
     </r>
@@ -1271,6 +1320,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
   </t>
     </r>
@@ -1287,6 +1344,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
 </t>
     </r>
@@ -1303,6 +1368,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
 </t>
     </r>
@@ -1319,6 +1392,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
 </t>
     </r>
@@ -1335,6 +1416,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
 </t>
     </r>
@@ -1351,6 +1440,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
  </t>
     </r>
@@ -1367,6 +1464,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
  </t>
     </r>
@@ -1383,6 +1488,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1399,6 +1512,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
   </t>
     </r>
@@ -1415,6 +1536,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">作用定义：
 </t>
     </r>
@@ -1431,6 +1560,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
 </t>
     </r>
@@ -1447,6 +1584,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
  </t>
     </r>
@@ -1463,6 +1608,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
 </t>
     </r>
@@ -1479,6 +1632,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
  </t>
     </r>
@@ -1495,6 +1656,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
   </t>
     </r>
@@ -1511,6 +1680,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
 </t>
     </r>
@@ -1527,6 +1704,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
 </t>
     </r>
@@ -1543,6 +1728,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
 </t>
     </r>
@@ -1559,6 +1752,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义：
 </t>
     </r>
@@ -1575,6 +1776,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">定义作用：
 </t>
     </r>
@@ -3579,6 +3788,751 @@
   <si>
     <t>工作绩效信息
 变更请求</t>
+  </si>
+  <si>
+    <t>十大管理</t>
+  </si>
+  <si>
+    <t xml:space="preserve">工作内容
+</t>
+  </si>
+  <si>
+    <t>49个管理过程</t>
+  </si>
+  <si>
+    <t>工作内容</t>
+  </si>
+  <si>
+    <t>口语解释</t>
+  </si>
+  <si>
+    <t>写作思路</t>
+  </si>
+  <si>
+    <t>通用输入</t>
+  </si>
+  <si>
+    <t>通用工具技术</t>
+  </si>
+  <si>
+    <t>通用输出</t>
+  </si>
+  <si>
+    <t>事业环境因素
+组织过程资产</t>
+  </si>
+  <si>
+    <t>专家
+判断</t>
+  </si>
+  <si>
+    <t>项目管理
+信息系统</t>
+  </si>
+  <si>
+    <t>沟通技能
+/技术</t>
+  </si>
+  <si>
+    <t>人际关系
+与团队技能</t>
+  </si>
+  <si>
+    <t>工作内容：识别、协调项目管理各过程、活动，贯穿项目始终,具备建立联系和统一的性质</t>
+  </si>
+  <si>
+    <t>制定项目章程
+（启动过程组）</t>
+  </si>
+  <si>
+    <t>1明确项目正式地位
+2确认组织战略目标联系
+3展示组织对项目的承诺
+4正式批准项目
+5授权项目经理使用组织资源</t>
+  </si>
+  <si>
+    <t>制定项目管理计划（规划过程组）</t>
+  </si>
+  <si>
+    <t>1确定项目工作的基础和执行方式
+2识别、定义、统一协调项目计划的各部分</t>
+  </si>
+  <si>
+    <t>项目管理子计划</t>
+  </si>
+  <si>
+    <t>指导与管理项目工作（执行过程组）</t>
+  </si>
+  <si>
+    <t>1提高项目成功可能性
+2执行项目管理计划中的工作
+3实施已批准的变更请求
+4管理项目工作和可交付成果</t>
+  </si>
+  <si>
+    <t>可交付成果
+工作绩效数据
+问题日志
+变更请求</t>
+  </si>
+  <si>
+    <t>管理项目知识（执行过程组）</t>
+  </si>
+  <si>
+    <t>1已有知识用来创造和改进项目成果
+2新知识可用来支持组织运营和未来项目
+3使用已有知识
+4生成新知识
+5帮助组织学习并实现项目目标</t>
+  </si>
+  <si>
+    <t>监控项目工作（监控过程组）</t>
+  </si>
+  <si>
+    <t>1实现项目管理计划中定的绩效目标
+2让干系人了解项目当前状况
+3让干系人认可处理绩效问题的行动
+3对项目进展进行跟踪、审查、报告
+4通过成本和进度预测了解项目未来状态</t>
+  </si>
+  <si>
+    <t>工作绩效信息（非数据）
+协议</t>
+  </si>
+  <si>
+    <t>实施整体变更控制（监控过程组）</t>
+  </si>
+  <si>
+    <t>1管理、审查、批准可交付成果、项目文件、项目管理计划的变更
+2沟通变更处理结果</t>
+  </si>
+  <si>
+    <t>结束项目或阶段（收尾过程组）</t>
+  </si>
+  <si>
+    <t>1终结项目、阶段的所有活动
+2存档项目、阶段信息
+3释放组织团队资源</t>
+  </si>
+  <si>
+    <t>定义和控制项目、产品的范围,确保项目只做需要做的全部工作</t>
+  </si>
+  <si>
+    <t>规划范围管理（规划过程组）</t>
+  </si>
+  <si>
+    <t>1作为管理项目范围的指南和方向
+2定义、确认、控制项目范围</t>
+  </si>
+  <si>
+    <t>收集需求（规划过程组）</t>
+  </si>
+  <si>
+    <t>1是定义产品范围和项目范围的基础
+2确定、记录、管理干系人需要和需求</t>
+  </si>
+  <si>
+    <t>定义范围（规划过程组）</t>
+  </si>
+  <si>
+    <t>1对项目产品、服务成果的边界和验收标准的详细描述</t>
+  </si>
+  <si>
+    <t>创建WBS（规划过程组）</t>
+  </si>
+  <si>
+    <t>1确定进度基准
+2形成交付内容架构
+3把项目可交付成果、工作分解成小且易管理的组件</t>
+  </si>
+  <si>
+    <t>确认范围（监控过程组）</t>
+  </si>
+  <si>
+    <t>1提高最终产品、服务成果被验收的可能性
+2通过客观性的验收项目可交付成果</t>
+  </si>
+  <si>
+    <t>验收的可交付成果</t>
+  </si>
+  <si>
+    <t>控制范围（监控过程组）</t>
+  </si>
+  <si>
+    <t>1维护项目范围基准
+2监督项目和产品的范围状态
+3管理范围基准变更</t>
+  </si>
+  <si>
+    <t>规划进度管理（规划过程组）</t>
+  </si>
+  <si>
+    <t>1是管理项目进度的指南和方向
+2规划、编制、管理、执行、控制项目进度</t>
+  </si>
+  <si>
+    <t>定义活动（规划过程组）</t>
+  </si>
+  <si>
+    <t>1是项目进度估算、规划、执行、监督和控制的基础
+2为完成项目可交付成果，将工作包分解为进度活动，</t>
+  </si>
+  <si>
+    <t>排列活动顺序（规划过程组）</t>
+  </si>
+  <si>
+    <t>1使项目在制约因素下获得最高的效率
+2识别记录项目活动之间逻辑关系</t>
+  </si>
+  <si>
+    <t>估算活动持续时间（规划过程组）</t>
+  </si>
+  <si>
+    <t>1估算完成单项活动所需花费的时间量</t>
+  </si>
+  <si>
+    <t>制定进度计划（规划过程组）</t>
+  </si>
+  <si>
+    <t>1确定进度基准
+2创建具有计划日期的进度模型，以便项目执行和监控3分析活动顺序、持续时间、资源需求和进度制约因素，</t>
+  </si>
+  <si>
+    <t>控制进度（监控过程组）</t>
+  </si>
+  <si>
+    <t>1维护进度基准
+2监督项目状态
+3更新项目进度
+4管理进度基准变更</t>
+  </si>
+  <si>
+    <t>对成本进行规划、估算、预算、筹资、管理和控制，使得项目在预算内完成</t>
+  </si>
+  <si>
+    <t>规划成本管理（规划过程组）</t>
+  </si>
+  <si>
+    <t>1管理项目成本的指南和方向
+2估算、预算、管理、监督、控制项目成本</t>
+  </si>
+  <si>
+    <t>估算成本（规划过程组）</t>
+  </si>
+  <si>
+    <t>1确定项目所需的资金
+2对项目所需资源成本进行近似估算</t>
+  </si>
+  <si>
+    <t>制定预算（规划过程组）</t>
+  </si>
+  <si>
+    <t>1确定项目成本基准
+2方便监督和控制项目绩效
+3汇总所有活动、工作包的估算成本</t>
+  </si>
+  <si>
+    <t>控制成本（监控过程组）</t>
+  </si>
+  <si>
+    <t>1维护成本基准
+2监督项目状态
+3更新项目成本
+4管理成本基准变更</t>
+  </si>
+  <si>
+    <t>工作绩效信息
+成本预测</t>
+  </si>
+  <si>
+    <t>确定质量目标方针，并执行质量规划、保证、控
+制、改进的活动</t>
+  </si>
+  <si>
+    <t>规划质量管理（规划过程组）</t>
+  </si>
+  <si>
+    <t>1规划并证明，识别可交付成果质量的要求和标准</t>
+  </si>
+  <si>
+    <t>管理质量（执行过程组）</t>
+  </si>
+  <si>
+    <t>1使用质量控制数据结果，向干系人展示项目的质量状态
+把质量政策用于项目，将质量管理计划转化质量活动，提高实现质量目标的可能性，识别无效过程和导致质量低劣的原因，</t>
+  </si>
+  <si>
+    <t>控制质量（监控过程组）</t>
+  </si>
+  <si>
+    <t>监督和记录质量管理活动执行结果，确保项目输出满足规范标准要求和客户期望，核实项目可交付成果满足最终验收质量要求</t>
+  </si>
+  <si>
+    <t>规划资源管理（规划过程组）</t>
+  </si>
+  <si>
+    <t>定义：
+  是定义如何估算、获取、管理和利用团队及其实物资源的过程
+作用：
+  根据项目类型和复杂程度确定适用于项目资源的管理方法和管理程度</t>
+  </si>
+  <si>
+    <t>估算活动资源（规划过程组）</t>
+  </si>
+  <si>
+    <t>定义：
+  是估算执行项目所需的团队资源，以及材料、设备和用品的类型和数量的过程
+作用：
+  明确完成项目所需的资源种类、数量和特性</t>
+  </si>
+  <si>
+    <t>获取资源（执行过程组）</t>
+  </si>
+  <si>
+    <t>定义：
+  是获取项目所需的团队成员、设施、设备、材料、用品和其他资源的过程
+作用：
+  1、概述和指导资源的选择
+  2、将选择的资源分配给相应的活动</t>
+  </si>
+  <si>
+    <t>建设团队（执行过程组）</t>
+  </si>
+  <si>
+    <t>定义：
+  是提高工作能力，促进团队成员互动，改善团队整体氛围，以提高项目绩效的过程
+作用：
+  改进团队协作、增强人际关系技能、激励员工，减少摩擦以及提升整体项目绩效</t>
+  </si>
+  <si>
+    <t>管理团队（执行过程组）</t>
+  </si>
+  <si>
+    <t>定义：
+  是跟踪团队成员工作表现、提供反馈、解决问题并管理团队变更以优化项目绩效的过程
+作用：
+  影响团队行为、管理冲突以及解决问题</t>
+  </si>
+  <si>
+    <t>控制资源（监控过程组）</t>
+  </si>
+  <si>
+    <t>定义：
+  是确保按计划为项目分配实物资源，以及根据资源使用计划监督资源实际使用情况，并采取必要纠正措施的过程
+作用：
+  1、确保所分配的资源适时、适地可用于项目
+  2、资源在不再需要时被释放</t>
+  </si>
+  <si>
+    <t>规划沟通管理（规划过程组）</t>
+  </si>
+  <si>
+    <t>定义：
+  是基于每个干系人或干系人群体的信息需求、可用的组织资产，以及具体项目的需求，为项目沟通活动制定恰当的方法和计划的过程
+作用：
+  1、及时向干系人提供相关信息
+  2、引导干系人有效参与项目
+  3、编制书面沟通计划</t>
+  </si>
+  <si>
+    <t>沟通需求分析
+沟通模型
+沟通方法（互动、推式、拉式）</t>
+  </si>
+  <si>
+    <t>管理沟通（执行过程组）</t>
+  </si>
+  <si>
+    <t>定义：
+  是确保项目信息及时且恰当的收集、生成、发布、存储、检索、管理、监督和最终处置的过程
+作用：
+  促成项目团队与干系人之间的有效信息流动</t>
+  </si>
+  <si>
+    <t>监督沟通（监控过程组）</t>
+  </si>
+  <si>
+    <t>定义：
+  是确保满足项目及其干系人的信息需求的过程
+作用：
+  按沟通管理计划和干系人参与计划的要求优化信息传递流程</t>
+  </si>
+  <si>
+    <t>项目内对风险进行规划、识别、分析、管理和控制的过程</t>
+  </si>
+  <si>
+    <t>规划风险管理（规划过程组）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是定义如何实施项目风险管理活动的过程
+作用：
+  确保风险管理的水平、方法和可见度与项目风险程度相匹配，与对组织和其他干系人的重要程度相匹配</t>
+    </r>
+  </si>
+  <si>
+    <t>识别风险（规划过程组）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是识别单个项目风险以及整体项目风险的来源，并记录风险特征的过程
+作用：
+  1、记录现有的单个项目风险，以及整体项目风险的来源
+  2、汇总相关信息，以便项目团队能够恰当地应对已识别的风险</t>
+    </r>
+  </si>
+  <si>
+    <t>实施定性风险分析（规划过程组）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是通过评估单个项目风险发生的概率和影响及其他特征，对风险进行优先级排序，从而为后续分析或行动提供基础的过程
+作用：
+  是重点关注高优先级的风险</t>
+    </r>
+  </si>
+  <si>
+    <t>实施定量风险分析（规划过程组）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是就已识别的单个项目风险和不确定性的其他来源对整体项目目标的影响进行定量分析的过程
+作用：
+  1、量化整体项目风险最大可能性
+  2、提供额外的定量风险信息，以支持风险应对规划</t>
+    </r>
+  </si>
+  <si>
+    <t>规划风险应对（规划过程组）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是为了应对项目风险，而制定可选方案、选择应对策略并商定应对行动的过程
+作用：
+  1、制定应对整体项目风险和单个项目风险的适当方法
+  2、分配资源，并根据需要将相关活动添加进项目文件和项目管理计划中</t>
+    </r>
+  </si>
+  <si>
+    <t>实施风险应对（执行过程组）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是执行商定的风险应对计划的过程
+作用：
+  1、确保按计划执行商定的风险应对措施
+  2、管理整体项目风险入口、最小化单个项目威胁，以及最大化单个项目机会</t>
+    </r>
+  </si>
+  <si>
+    <t>监督风险（监控过程组）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是在整个项目期间，监督风险应对计划的实施，并跟踪已识别风险、识别和分析新风险，以及评估风险管理有效性的过程
+作用：
+  保证项目决策是在整体项目风险和单个项目风险当前信息的基础上运行</t>
+    </r>
+  </si>
+  <si>
+    <t>规划采购管理（规划过程组）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 是记录项目采购决策、明确采购方法，及识别潜在卖方的过程
+作用：
+  是确定是否从项目外部获取货物和服务，如果是，则还要确定将在什么时间、以什么方式获取什么货物和服务</t>
+    </r>
+  </si>
+  <si>
+    <t>实施采购（执行过程组）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是获取卖方应答、选择卖方并授予合同的过程
+作用：
+  选定合格卖方并签署关于货物或服务交付的法律协议</t>
+    </r>
+  </si>
+  <si>
+    <t>控制采购（监控过程组）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是管理采购关系、监督合同绩效、实施必要的变更和纠偏，以及关闭合同的过程
+作用：
+  确保买卖双方履行法律协议，满足项目需求</t>
+    </r>
+  </si>
+  <si>
+    <t>识别干系人（启动过程组）</t>
+  </si>
+  <si>
+    <t>定义：
+  是定期识别项目干系人，分析和记录他们的利益、参与度、项目依赖性、影响力和对项目成功的潜在影响的过程
+作用：
+  使项目团队能够建立对每个干系人或干系人群体的适度关注</t>
+  </si>
+  <si>
+    <t>规划干系人参与（规划过程组）</t>
+  </si>
+  <si>
+    <t>定义：
+  是根据干系人的需求、期望、利益和对项目的潜在影响，制定项目干系人参与项目的方法的过程
+作用：
+  提供与干系人进行有效互动的可行计划</t>
+  </si>
+  <si>
+    <t>管理干系人参与（执行过程组）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  是通过与干系人进行沟通协作，以满足其需求与期望、处理问题，并促进干系人合理参与的过程
+作用：
+  尽可能提高干系人的支持度，并降低干系人的抵制程度</t>
+    </r>
+  </si>
+  <si>
+    <t>基本规则</t>
+  </si>
+  <si>
+    <t>监督干系人参与（监控过程组）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">定义：
+  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>是监督项目干系人的关系，并通过修订参与策略和计划来引导干系人合理参与项目的过程
+作用：
+  随着项目进展和环境变化，维持或提升干系人参与会随着项目进展和环境变化，维持或提升干系人参与活动的效率和效果</t>
+    </r>
   </si>
   <si>
     <t>立项管理</t>
@@ -3936,7 +4890,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="38">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3951,7 +4905,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -4077,12 +5055,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -4142,7 +5114,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -4211,6 +5183,144 @@
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -4390,7 +5500,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="11">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="21">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
@@ -4402,55 +5512,43 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="14">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="24">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="15">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="25">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="14">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="24">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="16">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="26">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="18">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="28">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
@@ -4465,56 +5563,68 @@
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="37" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -4551,13 +5661,136 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4572,22 +5805,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -4600,34 +5833,28 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4635,46 +5862,46 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -4771,8 +5998,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2794000" y="17538700"/>
-          <a:ext cx="11544300" cy="6191250"/>
+          <a:off x="2514600" y="18841720"/>
+          <a:ext cx="10575290" cy="6602730"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -5039,2317 +6266,2317 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AY27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.1083333333333" customWidth="1"/>
-    <col min="2" max="2" width="22.5583333333333" customWidth="1"/>
-    <col min="3" max="3" width="29.375" customWidth="1"/>
+    <col min="1" max="1" width="14.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="22.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="29.3796296296296" customWidth="1"/>
     <col min="4" max="4" width="33.75" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="28.125" customWidth="1"/>
-    <col min="7" max="7" width="29.375" customWidth="1"/>
+    <col min="6" max="6" width="28.1296296296296" customWidth="1"/>
+    <col min="7" max="7" width="29.3796296296296" customWidth="1"/>
     <col min="8" max="8" width="33.75" customWidth="1"/>
     <col min="9" max="9" width="31.5" customWidth="1"/>
-    <col min="10" max="10" width="29.375" customWidth="1"/>
-    <col min="11" max="12" width="24.875" customWidth="1"/>
-    <col min="13" max="13" width="24.125" customWidth="1"/>
-    <col min="14" max="15" width="24.875" customWidth="1"/>
-    <col min="16" max="16" width="29.375" customWidth="1"/>
-    <col min="17" max="17" width="24.875" customWidth="1"/>
-    <col min="18" max="18" width="29.375" customWidth="1"/>
+    <col min="10" max="10" width="29.3796296296296" customWidth="1"/>
+    <col min="11" max="12" width="24.8796296296296" customWidth="1"/>
+    <col min="13" max="13" width="24.1296296296296" customWidth="1"/>
+    <col min="14" max="15" width="24.8796296296296" customWidth="1"/>
+    <col min="16" max="16" width="29.3796296296296" customWidth="1"/>
+    <col min="17" max="17" width="24.8796296296296" customWidth="1"/>
+    <col min="18" max="18" width="29.3796296296296" customWidth="1"/>
     <col min="19" max="19" width="32.5" customWidth="1"/>
-    <col min="20" max="20" width="29.375" customWidth="1"/>
-    <col min="21" max="21" width="24.875" customWidth="1"/>
-    <col min="22" max="22" width="29.375" customWidth="1"/>
-    <col min="23" max="25" width="24.875" customWidth="1"/>
-    <col min="26" max="26" width="29.375" customWidth="1"/>
-    <col min="27" max="28" width="24.875" customWidth="1"/>
-    <col min="29" max="30" width="29.375" customWidth="1"/>
-    <col min="31" max="34" width="24.875" customWidth="1"/>
-    <col min="35" max="35" width="29.375" customWidth="1"/>
-    <col min="36" max="37" width="24.875" customWidth="1"/>
-    <col min="38" max="38" width="29.375" customWidth="1"/>
-    <col min="39" max="39" width="24.875" customWidth="1"/>
+    <col min="20" max="20" width="29.3796296296296" customWidth="1"/>
+    <col min="21" max="21" width="24.8796296296296" customWidth="1"/>
+    <col min="22" max="22" width="29.3796296296296" customWidth="1"/>
+    <col min="23" max="25" width="24.8796296296296" customWidth="1"/>
+    <col min="26" max="26" width="29.3796296296296" customWidth="1"/>
+    <col min="27" max="28" width="24.8796296296296" customWidth="1"/>
+    <col min="29" max="30" width="29.3796296296296" customWidth="1"/>
+    <col min="31" max="34" width="24.8796296296296" customWidth="1"/>
+    <col min="35" max="35" width="29.3796296296296" customWidth="1"/>
+    <col min="36" max="37" width="24.8796296296296" customWidth="1"/>
+    <col min="38" max="38" width="29.3796296296296" customWidth="1"/>
+    <col min="39" max="39" width="24.8796296296296" customWidth="1"/>
     <col min="40" max="41" width="33.75" customWidth="1"/>
-    <col min="42" max="43" width="29.375" customWidth="1"/>
-    <col min="44" max="44" width="24.875" customWidth="1"/>
-    <col min="45" max="45" width="29.375" customWidth="1"/>
-    <col min="46" max="47" width="24.875" customWidth="1"/>
-    <col min="48" max="48" width="27.125" customWidth="1"/>
+    <col min="42" max="43" width="29.3796296296296" customWidth="1"/>
+    <col min="44" max="44" width="24.8796296296296" customWidth="1"/>
+    <col min="45" max="45" width="29.3796296296296" customWidth="1"/>
+    <col min="46" max="47" width="24.8796296296296" customWidth="1"/>
+    <col min="48" max="48" width="27.1296296296296" customWidth="1"/>
     <col min="49" max="51" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51">
       <c r="A1" s="11"/>
       <c r="B1" s="11"/>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15" t="s">
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15" t="s">
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15" t="s">
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15" t="s">
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="15"/>
-      <c r="AB1" s="15"/>
-      <c r="AC1" s="15" t="s">
+      <c r="AA1" s="56"/>
+      <c r="AB1" s="56"/>
+      <c r="AC1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="15"/>
-      <c r="AE1" s="15"/>
-      <c r="AF1" s="15"/>
-      <c r="AG1" s="15"/>
-      <c r="AH1" s="15"/>
-      <c r="AI1" s="15" t="s">
+      <c r="AD1" s="56"/>
+      <c r="AE1" s="56"/>
+      <c r="AF1" s="56"/>
+      <c r="AG1" s="56"/>
+      <c r="AH1" s="56"/>
+      <c r="AI1" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="AJ1" s="15"/>
-      <c r="AK1" s="15"/>
-      <c r="AL1" s="15" t="s">
+      <c r="AJ1" s="56"/>
+      <c r="AK1" s="56"/>
+      <c r="AL1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="AM1" s="15"/>
-      <c r="AN1" s="15"/>
-      <c r="AO1" s="15"/>
-      <c r="AP1" s="15"/>
-      <c r="AQ1" s="15"/>
-      <c r="AR1" s="15"/>
-      <c r="AS1" s="15" t="s">
+      <c r="AM1" s="56"/>
+      <c r="AN1" s="56"/>
+      <c r="AO1" s="56"/>
+      <c r="AP1" s="56"/>
+      <c r="AQ1" s="56"/>
+      <c r="AR1" s="56"/>
+      <c r="AS1" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="AT1" s="15"/>
-      <c r="AU1" s="15"/>
-      <c r="AV1" s="15" t="s">
+      <c r="AT1" s="56"/>
+      <c r="AU1" s="56"/>
+      <c r="AV1" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="AW1" s="15"/>
-      <c r="AX1" s="15"/>
-      <c r="AY1" s="15"/>
+      <c r="AW1" s="56"/>
+      <c r="AX1" s="56"/>
+      <c r="AY1" s="56"/>
     </row>
     <row r="2" customFormat="1" ht="58" customHeight="1" spans="1:51">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="18" t="s">
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="20" t="s">
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="19"/>
-      <c r="R2" s="19"/>
-      <c r="S2" s="19"/>
-      <c r="T2" s="19"/>
-      <c r="U2" s="21"/>
-      <c r="V2" s="20" t="s">
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="W2" s="19"/>
-      <c r="X2" s="19"/>
-      <c r="Y2" s="21"/>
-      <c r="Z2" s="18" t="s">
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="19"/>
-      <c r="AB2" s="21"/>
-      <c r="AC2" s="20" t="s">
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="62"/>
+      <c r="AC2" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="AD2" s="19"/>
-      <c r="AE2" s="19"/>
-      <c r="AF2" s="19"/>
-      <c r="AG2" s="19"/>
-      <c r="AH2" s="21"/>
-      <c r="AI2" s="20" t="s">
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="62"/>
+      <c r="AI2" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="AJ2" s="19"/>
-      <c r="AK2" s="21"/>
-      <c r="AL2" s="20" t="s">
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="62"/>
+      <c r="AL2" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="AM2" s="19"/>
-      <c r="AN2" s="19"/>
-      <c r="AO2" s="19"/>
-      <c r="AP2" s="19"/>
-      <c r="AQ2" s="19"/>
-      <c r="AR2" s="21"/>
-      <c r="AS2" s="22" t="s">
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
+      <c r="AR2" s="62"/>
+      <c r="AS2" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="AT2" s="23"/>
-      <c r="AU2" s="24"/>
-      <c r="AV2" s="20" t="s">
+      <c r="AT2" s="64"/>
+      <c r="AU2" s="65"/>
+      <c r="AV2" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="AW2" s="19"/>
-      <c r="AX2" s="19"/>
-      <c r="AY2" s="21"/>
+      <c r="AW2" s="60"/>
+      <c r="AX2" s="60"/>
+      <c r="AY2" s="62"/>
     </row>
-    <row r="3" s="12" customFormat="1" spans="1:51">
-      <c r="A3" s="25"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="26" t="s">
+    <row r="3" s="53" customFormat="1" spans="1:51">
+      <c r="A3" s="66"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="26" t="s">
+      <c r="E3" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="26" t="s">
+      <c r="F3" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="26" t="s">
+      <c r="G3" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="26" t="s">
+      <c r="I3" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="27" t="s">
+      <c r="J3" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="27" t="s">
+      <c r="N3" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="27" t="s">
+      <c r="O3" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="27" t="s">
+      <c r="P3" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="27" t="s">
+      <c r="Q3" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="R3" s="27" t="s">
+      <c r="R3" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="27" t="s">
+      <c r="S3" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="T3" s="27" t="s">
+      <c r="T3" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="27" t="s">
+      <c r="U3" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="V3" s="27" t="s">
+      <c r="V3" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="W3" s="27" t="s">
+      <c r="W3" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="X3" s="27" t="s">
+      <c r="X3" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="27" t="s">
+      <c r="Y3" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="Z3" s="27" t="s">
+      <c r="Z3" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="AA3" s="27" t="s">
+      <c r="AA3" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="AB3" s="27" t="s">
+      <c r="AB3" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="AC3" s="27" t="s">
+      <c r="AC3" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="AD3" s="27" t="s">
+      <c r="AD3" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="AE3" s="27" t="s">
+      <c r="AE3" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="AF3" s="27" t="s">
+      <c r="AF3" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="AG3" s="27" t="s">
+      <c r="AG3" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="AH3" s="27" t="s">
+      <c r="AH3" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="AI3" s="27" t="s">
+      <c r="AI3" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="AJ3" s="27" t="s">
+      <c r="AJ3" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="AK3" s="27" t="s">
+      <c r="AK3" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="AL3" s="27" t="s">
+      <c r="AL3" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="AM3" s="27" t="s">
+      <c r="AM3" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="AN3" s="27" t="s">
+      <c r="AN3" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="AO3" s="27" t="s">
+      <c r="AO3" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="AP3" s="27" t="s">
+      <c r="AP3" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="AQ3" s="27" t="s">
+      <c r="AQ3" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="AR3" s="27" t="s">
+      <c r="AR3" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="AS3" s="26" t="s">
+      <c r="AS3" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="AT3" s="26" t="s">
+      <c r="AT3" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="AU3" s="26" t="s">
+      <c r="AU3" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="AV3" s="26" t="s">
+      <c r="AV3" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="AW3" s="26" t="s">
+      <c r="AW3" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="AX3" s="26" t="s">
+      <c r="AX3" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="AY3" s="26" t="s">
+      <c r="AY3" s="67" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" s="12" customFormat="1" ht="108" spans="1:51">
-      <c r="A4" s="25"/>
-      <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+    <row r="4" s="53" customFormat="1" ht="115.2" spans="1:51">
+      <c r="A4" s="66"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="28" t="s">
+      <c r="D4" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="28" t="s">
+      <c r="G4" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="28" t="s">
+      <c r="J4" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="L4" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="N4" s="28" t="s">
+      <c r="N4" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="O4" s="28" t="s">
+      <c r="O4" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="P4" s="28" t="s">
+      <c r="P4" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="Q4" s="28" t="s">
+      <c r="Q4" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="R4" s="28" t="s">
+      <c r="R4" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="S4" s="28" t="s">
+      <c r="S4" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="T4" s="28" t="s">
+      <c r="T4" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="U4" s="28" t="s">
+      <c r="U4" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="V4" s="28" t="s">
+      <c r="V4" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="W4" s="28" t="s">
+      <c r="W4" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="X4" s="28" t="s">
+      <c r="X4" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="Y4" s="28" t="s">
+      <c r="Y4" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="Z4" s="28" t="s">
+      <c r="Z4" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="AA4" s="28" t="s">
+      <c r="AA4" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="AB4" s="28" t="s">
+      <c r="AB4" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="AC4" s="28" t="s">
+      <c r="AC4" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="AD4" s="28" t="s">
+      <c r="AD4" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="AE4" s="28" t="s">
+      <c r="AE4" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AF4" s="28" t="s">
+      <c r="AF4" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="AG4" s="28" t="s">
+      <c r="AG4" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="AH4" s="28" t="s">
+      <c r="AH4" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="AI4" s="28" t="s">
+      <c r="AI4" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="AJ4" s="28" t="s">
+      <c r="AJ4" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="AK4" s="28" t="s">
+      <c r="AK4" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="AL4" s="28" t="s">
+      <c r="AL4" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="AM4" s="28" t="s">
+      <c r="AM4" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="AN4" s="28" t="s">
+      <c r="AN4" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="AO4" s="28" t="s">
+      <c r="AO4" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="AP4" s="28" t="s">
+      <c r="AP4" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="AQ4" s="28" t="s">
+      <c r="AQ4" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="AR4" s="28" t="s">
+      <c r="AR4" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="AS4" s="28" t="s">
+      <c r="AS4" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="AT4" s="28" t="s">
+      <c r="AT4" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="AU4" s="28" t="s">
+      <c r="AU4" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="AV4" s="28" t="s">
+      <c r="AV4" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="AW4" s="28" t="s">
+      <c r="AW4" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="AX4" s="28" t="s">
+      <c r="AX4" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="AY4" s="28" t="s">
+      <c r="AY4" s="32" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" s="12" customFormat="1" ht="94.5" spans="1:51">
-      <c r="A5" s="25"/>
-      <c r="B5" s="25"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28"/>
-      <c r="P5" s="28"/>
-      <c r="Q5" s="28"/>
-      <c r="R5" s="28"/>
-      <c r="S5" s="28"/>
-      <c r="T5" s="28"/>
-      <c r="U5" s="28"/>
-      <c r="V5" s="28"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="28"/>
-      <c r="Y5" s="28"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="28"/>
-      <c r="AC5" s="28" t="s">
+    <row r="5" s="53" customFormat="1" ht="100.8" spans="1:51">
+      <c r="A5" s="66"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="32"/>
+      <c r="S5" s="32"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="32"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="32"/>
+      <c r="Z5" s="32"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="32"/>
+      <c r="AC5" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="28" t="s">
+      <c r="AD5" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="AE5" s="28" t="s">
+      <c r="AE5" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="AF5" s="28" t="s">
+      <c r="AF5" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AG5" s="28" t="s">
+      <c r="AG5" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="AH5" s="28" t="s">
+      <c r="AH5" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="AI5" s="28" t="s">
+      <c r="AI5" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="AJ5" s="28" t="s">
+      <c r="AJ5" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="AK5" s="28" t="s">
+      <c r="AK5" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="AL5" s="28" t="s">
+      <c r="AL5" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="AM5" s="28" t="s">
+      <c r="AM5" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="AN5" s="28" t="s">
+      <c r="AN5" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="AO5" s="28" t="s">
+      <c r="AO5" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="AP5" s="28" t="s">
+      <c r="AP5" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="AQ5" s="28" t="s">
+      <c r="AQ5" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="AR5" s="28" t="s">
+      <c r="AR5" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="AS5" s="28" t="s">
+      <c r="AS5" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="AT5" s="28" t="s">
+      <c r="AT5" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="AU5" s="28" t="s">
+      <c r="AU5" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="AV5" s="28" t="s">
+      <c r="AV5" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="AW5" s="28" t="s">
+      <c r="AW5" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="AX5" s="28" t="s">
+      <c r="AX5" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="AY5" s="28" t="s">
+      <c r="AY5" s="32" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="6" s="12" customFormat="1" ht="27" spans="1:51">
-      <c r="A6" s="25"/>
-      <c r="B6" s="25"/>
-      <c r="C6" s="29" t="s">
+    <row r="6" s="53" customFormat="1" ht="28.8" spans="1:51">
+      <c r="A6" s="66"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="29" t="s">
+      <c r="D6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="E6" s="29" t="s">
+      <c r="E6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="F6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="29" t="s">
+      <c r="G6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="H6" s="29" t="s">
+      <c r="H6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="I6" s="29" t="s">
+      <c r="I6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="J6" s="29" t="s">
+      <c r="J6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="K6" s="29" t="s">
+      <c r="K6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="L6" s="29" t="s">
+      <c r="L6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="M6" s="29" t="s">
+      <c r="M6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="N6" s="29" t="s">
+      <c r="N6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="O6" s="29" t="s">
+      <c r="O6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="P6" s="29" t="s">
+      <c r="P6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="Q6" s="29" t="s">
+      <c r="Q6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="R6" s="29" t="s">
+      <c r="R6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="S6" s="29" t="s">
+      <c r="S6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="T6" s="29" t="s">
+      <c r="T6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="U6" s="29" t="s">
+      <c r="U6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="V6" s="28" t="s">
+      <c r="V6" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="W6" s="29" t="s">
+      <c r="W6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="X6" s="29" t="s">
+      <c r="X6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="Y6" s="29" t="s">
+      <c r="Y6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="Z6" s="29" t="s">
+      <c r="Z6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AA6" s="29" t="s">
+      <c r="AA6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AB6" s="29" t="s">
+      <c r="AB6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AC6" s="29" t="s">
+      <c r="AC6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AD6" s="29" t="s">
+      <c r="AD6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AE6" s="29" t="s">
+      <c r="AE6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AF6" s="29" t="s">
+      <c r="AF6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AG6" s="29" t="s">
+      <c r="AG6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AH6" s="29" t="s">
+      <c r="AH6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AI6" s="29" t="s">
+      <c r="AI6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AJ6" s="29" t="s">
+      <c r="AJ6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AK6" s="29" t="s">
+      <c r="AK6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AL6" s="29" t="s">
+      <c r="AL6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AM6" s="29" t="s">
+      <c r="AM6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AN6" s="29" t="s">
+      <c r="AN6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AO6" s="29" t="s">
+      <c r="AO6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AP6" s="29" t="s">
+      <c r="AP6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AQ6" s="29" t="s">
+      <c r="AQ6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="29" t="s">
+      <c r="AR6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AS6" s="29" t="s">
+      <c r="AS6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AT6" s="29" t="s">
+      <c r="AT6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AU6" s="29" t="s">
+      <c r="AU6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AV6" s="29" t="s">
+      <c r="AV6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AW6" s="29" t="s">
+      <c r="AW6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AX6" s="29" t="s">
+      <c r="AX6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AY6" s="29" t="s">
+      <c r="AY6" s="69" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="7" s="12" customFormat="1" ht="54" spans="1:51">
-      <c r="A7" s="30" t="s">
+    <row r="7" s="53" customFormat="1" ht="57.6" spans="1:51">
+      <c r="A7" s="70" t="s">
         <v>143</v>
       </c>
-      <c r="B7" s="29" t="s">
+      <c r="B7" s="69" t="s">
         <v>144</v>
       </c>
-      <c r="C7" s="31" t="s">
+      <c r="C7" s="71" t="s">
         <v>145</v>
       </c>
-      <c r="D7" s="29" t="s">
+      <c r="D7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="H7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="J7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="K7" s="29" t="s">
+      <c r="K7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="L7" s="29" t="s">
+      <c r="L7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="M7" s="29" t="s">
+      <c r="M7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="N7" s="29" t="s">
+      <c r="N7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="O7" s="29" t="s">
+      <c r="O7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="P7" s="29" t="s">
+      <c r="P7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="Q7" s="29" t="s">
+      <c r="Q7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="R7" s="29" t="s">
+      <c r="R7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="S7" s="29" t="s">
+      <c r="S7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="T7" s="29" t="s">
+      <c r="T7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="U7" s="29" t="s">
+      <c r="U7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="V7" s="28" t="s">
+      <c r="V7" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="W7" s="29" t="s">
+      <c r="W7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="X7" s="29" t="s">
+      <c r="X7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="Y7" s="29" t="s">
+      <c r="Y7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="Z7" s="29" t="s">
+      <c r="Z7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AA7" s="29" t="s">
+      <c r="AA7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AB7" s="29" t="s">
+      <c r="AB7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AC7" s="29" t="s">
+      <c r="AC7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AD7" s="29" t="s">
+      <c r="AD7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AE7" s="29" t="s">
+      <c r="AE7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AF7" s="29" t="s">
+      <c r="AF7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AG7" s="29" t="s">
+      <c r="AG7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AH7" s="29" t="s">
+      <c r="AH7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AI7" s="29" t="s">
+      <c r="AI7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AJ7" s="29" t="s">
+      <c r="AJ7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AK7" s="29" t="s">
+      <c r="AK7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AL7" s="29" t="s">
+      <c r="AL7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AM7" s="29" t="s">
+      <c r="AM7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AN7" s="29" t="s">
+      <c r="AN7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AO7" s="29" t="s">
+      <c r="AO7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AP7" s="29" t="s">
+      <c r="AP7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AQ7" s="29" t="s">
+      <c r="AQ7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AR7" s="29" t="s">
+      <c r="AR7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AS7" s="29" t="s">
+      <c r="AS7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AT7" s="29" t="s">
+      <c r="AT7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AU7" s="29" t="s">
+      <c r="AU7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AV7" s="29" t="s">
+      <c r="AV7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AW7" s="29" t="s">
+      <c r="AW7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AX7" s="29" t="s">
+      <c r="AX7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AY7" s="29" t="s">
+      <c r="AY7" s="69" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="8" ht="67.5" spans="1:51">
-      <c r="A8" s="32"/>
-      <c r="B8" s="33" t="s">
+    <row r="8" ht="72" spans="1:51">
+      <c r="A8" s="72"/>
+      <c r="B8" s="73" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="74" t="s">
         <v>148</v>
       </c>
-      <c r="D8" s="34" t="s">
+      <c r="D8" s="74" t="s">
         <v>149</v>
       </c>
-      <c r="E8" s="34" t="s">
+      <c r="E8" s="74" t="s">
         <v>150</v>
       </c>
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="74" t="s">
         <v>151</v>
       </c>
-      <c r="G8" s="34" t="s">
+      <c r="G8" s="74" t="s">
         <v>152</v>
       </c>
-      <c r="H8" s="34" t="s">
+      <c r="H8" s="74" t="s">
         <v>153</v>
       </c>
-      <c r="I8" s="34" t="s">
+      <c r="I8" s="74" t="s">
         <v>154</v>
       </c>
-      <c r="J8" s="34" t="s">
+      <c r="J8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="K8" s="34" t="s">
+      <c r="K8" s="74" t="s">
         <v>156</v>
       </c>
-      <c r="L8" s="34" t="s">
+      <c r="L8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="M8" s="34" t="s">
+      <c r="M8" s="74" t="s">
         <v>157</v>
       </c>
-      <c r="N8" s="34" t="s">
+      <c r="N8" s="74" t="s">
         <v>158</v>
       </c>
-      <c r="O8" s="34" t="s">
+      <c r="O8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="P8" s="34" t="s">
+      <c r="P8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="Q8" s="34" t="s">
+      <c r="Q8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="R8" s="34" t="s">
+      <c r="R8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="S8" s="34" t="s">
+      <c r="S8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="T8" s="34" t="s">
+      <c r="T8" s="74" t="s">
         <v>159</v>
       </c>
-      <c r="U8" s="34" t="s">
+      <c r="U8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="V8" s="34" t="s">
+      <c r="V8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="W8" s="34" t="s">
+      <c r="W8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="X8" s="34" t="s">
+      <c r="X8" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="Y8" s="34" t="s">
+      <c r="Y8" s="74" t="s">
         <v>161</v>
       </c>
-      <c r="Z8" s="34" t="s">
+      <c r="Z8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AA8" s="34" t="s">
+      <c r="AA8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AB8" s="34" t="s">
+      <c r="AB8" s="74" t="s">
         <v>162</v>
       </c>
-      <c r="AC8" s="34" t="s">
+      <c r="AC8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AD8" s="34" t="s">
+      <c r="AD8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AE8" s="34" t="s">
+      <c r="AE8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AF8" s="34" t="s">
+      <c r="AF8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AG8" s="34" t="s">
+      <c r="AG8" s="74" t="s">
         <v>163</v>
       </c>
-      <c r="AH8" s="34" t="s">
+      <c r="AH8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AI8" s="34" t="s">
+      <c r="AI8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AJ8" s="34" t="s">
+      <c r="AJ8" s="74" t="s">
         <v>164</v>
       </c>
-      <c r="AK8" s="34" t="s">
+      <c r="AK8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AL8" s="34" t="s">
+      <c r="AL8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AM8" s="34" t="s">
+      <c r="AM8" s="74" t="s">
         <v>165</v>
       </c>
-      <c r="AN8" s="34" t="s">
+      <c r="AN8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AO8" s="34" t="s">
+      <c r="AO8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AP8" s="34" t="s">
+      <c r="AP8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AQ8" s="34" t="s">
+      <c r="AQ8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AR8" s="34" t="s">
+      <c r="AR8" s="74" t="s">
         <v>164</v>
       </c>
-      <c r="AS8" s="35" t="s">
+      <c r="AS8" s="75" t="s">
         <v>166</v>
       </c>
-      <c r="AT8" s="35" t="s">
+      <c r="AT8" s="75" t="s">
         <v>167</v>
       </c>
-      <c r="AU8" s="35" t="s">
+      <c r="AU8" s="75" t="s">
         <v>168</v>
       </c>
-      <c r="AV8" s="35" t="s">
+      <c r="AV8" s="75" t="s">
         <v>169</v>
       </c>
-      <c r="AW8" s="35" t="s">
+      <c r="AW8" s="75" t="s">
         <v>159</v>
       </c>
-      <c r="AX8" s="36" t="s">
+      <c r="AX8" s="76" t="s">
         <v>155</v>
       </c>
-      <c r="AY8" s="36" t="s">
+      <c r="AY8" s="76" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="9" ht="40.5" spans="1:51">
-      <c r="A9" s="32"/>
-      <c r="B9" s="37" t="s">
+    <row r="9" ht="43.2" spans="1:51">
+      <c r="A9" s="72"/>
+      <c r="B9" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="35"/>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="35" t="s">
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75" t="s">
         <v>171</v>
       </c>
-      <c r="L9" s="35"/>
-      <c r="M9" s="35"/>
-      <c r="N9" s="35" t="s">
+      <c r="L9" s="75"/>
+      <c r="M9" s="75"/>
+      <c r="N9" s="75" t="s">
         <v>172</v>
       </c>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35"/>
-      <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="35"/>
-      <c r="V9" s="35"/>
-      <c r="W9" s="35"/>
-      <c r="X9" s="35"/>
-      <c r="Y9" s="35"/>
-      <c r="Z9" s="35"/>
-      <c r="AA9" s="35"/>
-      <c r="AB9" s="35"/>
-      <c r="AC9" s="35"/>
-      <c r="AD9" s="35"/>
-      <c r="AE9" s="35"/>
-      <c r="AF9" s="35"/>
-      <c r="AG9" s="35"/>
-      <c r="AH9" s="35"/>
-      <c r="AI9" s="35"/>
-      <c r="AJ9" s="35"/>
-      <c r="AK9" s="35"/>
-      <c r="AL9" s="35"/>
-      <c r="AM9" s="35"/>
-      <c r="AN9" s="35"/>
-      <c r="AO9" s="35"/>
-      <c r="AP9" s="35"/>
-      <c r="AQ9" s="35"/>
-      <c r="AR9" s="35"/>
-      <c r="AS9" s="35"/>
-      <c r="AT9" s="35"/>
-      <c r="AU9" s="35"/>
-      <c r="AV9" s="35"/>
-      <c r="AW9" s="35"/>
-      <c r="AX9" s="36"/>
-      <c r="AY9" s="36"/>
+      <c r="O9" s="75"/>
+      <c r="P9" s="75"/>
+      <c r="Q9" s="75"/>
+      <c r="R9" s="75"/>
+      <c r="S9" s="75"/>
+      <c r="T9" s="75"/>
+      <c r="U9" s="75"/>
+      <c r="V9" s="75"/>
+      <c r="W9" s="75"/>
+      <c r="X9" s="75"/>
+      <c r="Y9" s="75"/>
+      <c r="Z9" s="75"/>
+      <c r="AA9" s="75"/>
+      <c r="AB9" s="75"/>
+      <c r="AC9" s="75"/>
+      <c r="AD9" s="75"/>
+      <c r="AE9" s="75"/>
+      <c r="AF9" s="75"/>
+      <c r="AG9" s="75"/>
+      <c r="AH9" s="75"/>
+      <c r="AI9" s="75"/>
+      <c r="AJ9" s="75"/>
+      <c r="AK9" s="75"/>
+      <c r="AL9" s="75"/>
+      <c r="AM9" s="75"/>
+      <c r="AN9" s="75"/>
+      <c r="AO9" s="75"/>
+      <c r="AP9" s="75"/>
+      <c r="AQ9" s="75"/>
+      <c r="AR9" s="75"/>
+      <c r="AS9" s="75"/>
+      <c r="AT9" s="75"/>
+      <c r="AU9" s="75"/>
+      <c r="AV9" s="75"/>
+      <c r="AW9" s="75"/>
+      <c r="AX9" s="76"/>
+      <c r="AY9" s="76"/>
     </row>
-    <row r="10" ht="81" spans="1:51">
-      <c r="A10" s="38"/>
-      <c r="B10" s="37" t="s">
+    <row r="10" ht="86.4" spans="1:51">
+      <c r="A10" s="77"/>
+      <c r="B10" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
-      <c r="E10" s="35"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="35"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="35" t="s">
+      <c r="C10" s="75"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="75"/>
+      <c r="K10" s="75" t="s">
         <v>174</v>
       </c>
-      <c r="L10" s="35" t="s">
+      <c r="L10" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="M10" s="35"/>
-      <c r="N10" s="35" t="s">
+      <c r="M10" s="75"/>
+      <c r="N10" s="75" t="s">
         <v>176</v>
       </c>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35"/>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="35"/>
-      <c r="W10" s="35"/>
-      <c r="X10" s="35"/>
-      <c r="Y10" s="35"/>
-      <c r="Z10" s="35"/>
-      <c r="AA10" s="35" t="s">
+      <c r="O10" s="75"/>
+      <c r="P10" s="75"/>
+      <c r="Q10" s="75"/>
+      <c r="R10" s="75"/>
+      <c r="S10" s="75"/>
+      <c r="T10" s="75"/>
+      <c r="U10" s="75"/>
+      <c r="V10" s="75"/>
+      <c r="W10" s="75"/>
+      <c r="X10" s="75"/>
+      <c r="Y10" s="75"/>
+      <c r="Z10" s="75"/>
+      <c r="AA10" s="75" t="s">
         <v>177</v>
       </c>
-      <c r="AB10" s="35"/>
-      <c r="AC10" s="35"/>
-      <c r="AD10" s="35"/>
-      <c r="AE10" s="35"/>
-      <c r="AF10" s="35"/>
-      <c r="AG10" s="35"/>
-      <c r="AH10" s="35"/>
-      <c r="AI10" s="35"/>
-      <c r="AJ10" s="35" t="s">
+      <c r="AB10" s="75"/>
+      <c r="AC10" s="75"/>
+      <c r="AD10" s="75"/>
+      <c r="AE10" s="75"/>
+      <c r="AF10" s="75"/>
+      <c r="AG10" s="75"/>
+      <c r="AH10" s="75"/>
+      <c r="AI10" s="75"/>
+      <c r="AJ10" s="75" t="s">
         <v>178</v>
       </c>
-      <c r="AK10" s="35"/>
-      <c r="AL10" s="35"/>
-      <c r="AM10" s="35"/>
-      <c r="AN10" s="35"/>
-      <c r="AO10" s="35"/>
-      <c r="AP10" s="35"/>
-      <c r="AQ10" s="35"/>
-      <c r="AR10" s="35"/>
-      <c r="AS10" s="35"/>
-      <c r="AT10" s="35"/>
-      <c r="AU10" s="35"/>
-      <c r="AV10" s="35"/>
-      <c r="AW10" s="35"/>
-      <c r="AX10" s="36"/>
-      <c r="AY10" s="36"/>
+      <c r="AK10" s="75"/>
+      <c r="AL10" s="75"/>
+      <c r="AM10" s="75"/>
+      <c r="AN10" s="75"/>
+      <c r="AO10" s="75"/>
+      <c r="AP10" s="75"/>
+      <c r="AQ10" s="75"/>
+      <c r="AR10" s="75"/>
+      <c r="AS10" s="75"/>
+      <c r="AT10" s="75"/>
+      <c r="AU10" s="75"/>
+      <c r="AV10" s="75"/>
+      <c r="AW10" s="75"/>
+      <c r="AX10" s="76"/>
+      <c r="AY10" s="76"/>
     </row>
     <row r="11" spans="1:51">
-      <c r="A11" s="39" t="s">
+      <c r="A11" s="78" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="13"/>
-      <c r="T11" s="13"/>
-      <c r="U11" s="13"/>
-      <c r="V11" s="13"/>
-      <c r="W11" s="13"/>
-      <c r="X11" s="13"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="13"/>
-      <c r="AA11" s="13"/>
-      <c r="AB11" s="13"/>
-      <c r="AC11" s="13"/>
-      <c r="AD11" s="13"/>
-      <c r="AE11" s="13"/>
-      <c r="AF11" s="13"/>
-      <c r="AG11" s="13"/>
-      <c r="AH11" s="13"/>
-      <c r="AI11" s="13"/>
-      <c r="AJ11" s="13"/>
-      <c r="AK11" s="13"/>
-      <c r="AL11" s="13"/>
-      <c r="AM11" s="13"/>
-      <c r="AN11" s="13"/>
-      <c r="AO11" s="13"/>
-      <c r="AP11" s="13"/>
-      <c r="AQ11" s="13"/>
-      <c r="AR11" s="13"/>
-      <c r="AS11" s="13"/>
-      <c r="AT11" s="13"/>
-      <c r="AU11" s="13"/>
-      <c r="AV11" s="13"/>
-      <c r="AW11" s="13"/>
-      <c r="AX11" s="13"/>
-      <c r="AY11" s="13"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
+      <c r="S11" s="54"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="54"/>
+      <c r="X11" s="54"/>
+      <c r="Y11" s="54"/>
+      <c r="Z11" s="54"/>
+      <c r="AA11" s="54"/>
+      <c r="AB11" s="54"/>
+      <c r="AC11" s="54"/>
+      <c r="AD11" s="54"/>
+      <c r="AE11" s="54"/>
+      <c r="AF11" s="54"/>
+      <c r="AG11" s="54"/>
+      <c r="AH11" s="54"/>
+      <c r="AI11" s="54"/>
+      <c r="AJ11" s="54"/>
+      <c r="AK11" s="54"/>
+      <c r="AL11" s="54"/>
+      <c r="AM11" s="54"/>
+      <c r="AN11" s="54"/>
+      <c r="AO11" s="54"/>
+      <c r="AP11" s="54"/>
+      <c r="AQ11" s="54"/>
+      <c r="AR11" s="54"/>
+      <c r="AS11" s="54"/>
+      <c r="AT11" s="54"/>
+      <c r="AU11" s="54"/>
+      <c r="AV11" s="54"/>
+      <c r="AW11" s="54"/>
+      <c r="AX11" s="54"/>
+      <c r="AY11" s="54"/>
     </row>
     <row r="12" spans="1:51">
-      <c r="A12" s="39" t="s">
+      <c r="A12" s="78" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="41" t="s">
+      <c r="B12" s="80" t="s">
         <v>182</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="13"/>
-      <c r="U12" s="13"/>
-      <c r="V12" s="13"/>
-      <c r="W12" s="13"/>
-      <c r="X12" s="13"/>
-      <c r="Y12" s="13"/>
-      <c r="Z12" s="13"/>
-      <c r="AA12" s="13"/>
-      <c r="AB12" s="13"/>
-      <c r="AC12" s="13"/>
-      <c r="AD12" s="13"/>
-      <c r="AE12" s="13"/>
-      <c r="AF12" s="13"/>
-      <c r="AG12" s="13"/>
-      <c r="AH12" s="13"/>
-      <c r="AI12" s="13"/>
-      <c r="AJ12" s="13"/>
-      <c r="AK12" s="13"/>
-      <c r="AL12" s="13"/>
-      <c r="AM12" s="13"/>
-      <c r="AN12" s="13"/>
-      <c r="AO12" s="13"/>
-      <c r="AP12" s="13"/>
-      <c r="AQ12" s="13"/>
-      <c r="AR12" s="13"/>
-      <c r="AS12" s="13"/>
-      <c r="AT12" s="13"/>
-      <c r="AU12" s="13"/>
-      <c r="AV12" s="13"/>
-      <c r="AW12" s="13"/>
-      <c r="AX12" s="13"/>
-      <c r="AY12" s="13"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
+      <c r="K12" s="54"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="54"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="54"/>
+      <c r="S12" s="54"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="54"/>
+      <c r="V12" s="54"/>
+      <c r="W12" s="54"/>
+      <c r="X12" s="54"/>
+      <c r="Y12" s="54"/>
+      <c r="Z12" s="54"/>
+      <c r="AA12" s="54"/>
+      <c r="AB12" s="54"/>
+      <c r="AC12" s="54"/>
+      <c r="AD12" s="54"/>
+      <c r="AE12" s="54"/>
+      <c r="AF12" s="54"/>
+      <c r="AG12" s="54"/>
+      <c r="AH12" s="54"/>
+      <c r="AI12" s="54"/>
+      <c r="AJ12" s="54"/>
+      <c r="AK12" s="54"/>
+      <c r="AL12" s="54"/>
+      <c r="AM12" s="54"/>
+      <c r="AN12" s="54"/>
+      <c r="AO12" s="54"/>
+      <c r="AP12" s="54"/>
+      <c r="AQ12" s="54"/>
+      <c r="AR12" s="54"/>
+      <c r="AS12" s="54"/>
+      <c r="AT12" s="54"/>
+      <c r="AU12" s="54"/>
+      <c r="AV12" s="54"/>
+      <c r="AW12" s="54"/>
+      <c r="AX12" s="54"/>
+      <c r="AY12" s="54"/>
     </row>
-    <row r="14" ht="94.5" spans="1:51">
-      <c r="A14" s="42" t="s">
+    <row r="14" ht="115.2" spans="1:51">
+      <c r="A14" s="81" t="s">
         <v>183</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="82" t="s">
         <v>184</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45" t="s">
+      <c r="C14" s="83"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84" t="s">
         <v>185</v>
       </c>
-      <c r="G14" s="45"/>
-      <c r="H14" s="45" t="s">
+      <c r="G14" s="84"/>
+      <c r="H14" s="84" t="s">
         <v>186</v>
       </c>
-      <c r="I14" s="45"/>
-      <c r="J14" s="45"/>
-      <c r="K14" s="45" t="s">
+      <c r="I14" s="84"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="84" t="s">
         <v>187</v>
       </c>
-      <c r="L14" s="45" t="s">
+      <c r="L14" s="84" t="s">
         <v>188</v>
       </c>
-      <c r="M14" s="45" t="s">
+      <c r="M14" s="84" t="s">
         <v>189</v>
       </c>
-      <c r="N14" s="45" t="s">
+      <c r="N14" s="84" t="s">
         <v>190</v>
       </c>
-      <c r="O14" s="45"/>
-      <c r="P14" s="45"/>
-      <c r="Q14" s="45" t="s">
+      <c r="O14" s="84"/>
+      <c r="P14" s="84"/>
+      <c r="Q14" s="84" t="s">
         <v>191</v>
       </c>
-      <c r="R14" s="45" t="s">
+      <c r="R14" s="84" t="s">
         <v>192</v>
       </c>
-      <c r="S14" s="45" t="s">
+      <c r="S14" s="84" t="s">
         <v>193</v>
       </c>
-      <c r="T14" s="45" t="s">
+      <c r="T14" s="84" t="s">
         <v>194</v>
       </c>
-      <c r="U14" s="45" t="s">
+      <c r="U14" s="84" t="s">
         <v>195</v>
       </c>
-      <c r="V14" s="45"/>
-      <c r="W14" s="45" t="s">
+      <c r="V14" s="84"/>
+      <c r="W14" s="84" t="s">
         <v>193</v>
       </c>
-      <c r="X14" s="45" t="s">
+      <c r="X14" s="84" t="s">
         <v>196</v>
       </c>
-      <c r="Y14" s="45" t="s">
+      <c r="Y14" s="84" t="s">
         <v>197</v>
       </c>
-      <c r="Z14" s="45" t="s">
+      <c r="Z14" s="84" t="s">
         <v>198</v>
       </c>
-      <c r="AA14" s="45" t="s">
+      <c r="AA14" s="84" t="s">
         <v>199</v>
       </c>
-      <c r="AB14" s="45" t="s">
+      <c r="AB14" s="84" t="s">
         <v>200</v>
       </c>
-      <c r="AC14" s="45" t="s">
+      <c r="AC14" s="84" t="s">
         <v>201</v>
       </c>
-      <c r="AD14" s="45" t="s">
+      <c r="AD14" s="84" t="s">
         <v>202</v>
       </c>
-      <c r="AE14" s="45" t="s">
+      <c r="AE14" s="84" t="s">
         <v>203</v>
       </c>
-      <c r="AF14" s="45" t="s">
+      <c r="AF14" s="84" t="s">
         <v>204</v>
       </c>
-      <c r="AG14" s="45"/>
-      <c r="AH14" s="45" t="s">
+      <c r="AG14" s="84"/>
+      <c r="AH14" s="84" t="s">
         <v>205</v>
       </c>
-      <c r="AI14" s="45" t="s">
+      <c r="AI14" s="84" t="s">
         <v>206</v>
       </c>
-      <c r="AJ14" s="45" t="s">
+      <c r="AJ14" s="84" t="s">
         <v>207</v>
       </c>
-      <c r="AK14" s="45"/>
-      <c r="AL14" s="45"/>
-      <c r="AM14" s="45" t="s">
+      <c r="AK14" s="84"/>
+      <c r="AL14" s="84"/>
+      <c r="AM14" s="84" t="s">
         <v>208</v>
       </c>
-      <c r="AN14" s="45" t="s">
+      <c r="AN14" s="84" t="s">
         <v>209</v>
       </c>
-      <c r="AO14" s="45" t="s">
+      <c r="AO14" s="84" t="s">
         <v>210</v>
       </c>
-      <c r="AP14" s="45" t="s">
+      <c r="AP14" s="84" t="s">
         <v>211</v>
       </c>
-      <c r="AQ14" s="45"/>
-      <c r="AR14" s="45" t="s">
+      <c r="AQ14" s="84"/>
+      <c r="AR14" s="84" t="s">
         <v>212</v>
       </c>
-      <c r="AS14" s="46" t="s">
+      <c r="AS14" s="85" t="s">
         <v>213</v>
       </c>
-      <c r="AT14" s="45" t="s">
+      <c r="AT14" s="84" t="s">
         <v>214</v>
       </c>
-      <c r="AU14" s="45" t="s">
+      <c r="AU14" s="84" t="s">
         <v>215</v>
       </c>
-      <c r="AV14" s="36"/>
-      <c r="AW14" s="36"/>
-      <c r="AX14" s="35" t="s">
+      <c r="AV14" s="76"/>
+      <c r="AW14" s="76"/>
+      <c r="AX14" s="75" t="s">
         <v>216</v>
       </c>
-      <c r="AY14" s="35"/>
+      <c r="AY14" s="75"/>
     </row>
     <row r="15" spans="1:51">
-      <c r="A15" s="47"/>
-      <c r="B15" s="48" t="s">
+      <c r="A15" s="86"/>
+      <c r="B15" s="87" t="s">
         <v>217</v>
       </c>
-      <c r="C15" s="49"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="41"/>
-      <c r="S15" s="41"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="41"/>
-      <c r="V15" s="41"/>
-      <c r="W15" s="41"/>
-      <c r="X15" s="41"/>
-      <c r="Y15" s="41"/>
-      <c r="Z15" s="41"/>
-      <c r="AA15" s="41"/>
-      <c r="AB15" s="41"/>
-      <c r="AC15" s="41"/>
-      <c r="AD15" s="41"/>
-      <c r="AE15" s="41"/>
-      <c r="AF15" s="41"/>
-      <c r="AG15" s="41"/>
-      <c r="AH15" s="41"/>
-      <c r="AI15" s="41"/>
-      <c r="AJ15" s="41"/>
-      <c r="AK15" s="41"/>
-      <c r="AL15" s="41"/>
-      <c r="AM15" s="41"/>
-      <c r="AN15" s="41"/>
-      <c r="AO15" s="41"/>
-      <c r="AP15" s="41"/>
-      <c r="AQ15" s="41"/>
-      <c r="AR15" s="41"/>
-      <c r="AS15" s="41"/>
-      <c r="AT15" s="41"/>
-      <c r="AU15" s="41"/>
-      <c r="AV15" s="41"/>
-      <c r="AW15" s="41"/>
-      <c r="AX15" s="41"/>
-      <c r="AY15" s="41"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="80"/>
+      <c r="R15" s="80"/>
+      <c r="S15" s="80"/>
+      <c r="T15" s="80"/>
+      <c r="U15" s="80"/>
+      <c r="V15" s="80"/>
+      <c r="W15" s="80"/>
+      <c r="X15" s="80"/>
+      <c r="Y15" s="80"/>
+      <c r="Z15" s="80"/>
+      <c r="AA15" s="80"/>
+      <c r="AB15" s="80"/>
+      <c r="AC15" s="80"/>
+      <c r="AD15" s="80"/>
+      <c r="AE15" s="80"/>
+      <c r="AF15" s="80"/>
+      <c r="AG15" s="80"/>
+      <c r="AH15" s="80"/>
+      <c r="AI15" s="80"/>
+      <c r="AJ15" s="80"/>
+      <c r="AK15" s="80"/>
+      <c r="AL15" s="80"/>
+      <c r="AM15" s="80"/>
+      <c r="AN15" s="80"/>
+      <c r="AO15" s="80"/>
+      <c r="AP15" s="80"/>
+      <c r="AQ15" s="80"/>
+      <c r="AR15" s="80"/>
+      <c r="AS15" s="80"/>
+      <c r="AT15" s="80"/>
+      <c r="AU15" s="80"/>
+      <c r="AV15" s="80"/>
+      <c r="AW15" s="80"/>
+      <c r="AX15" s="80"/>
+      <c r="AY15" s="80"/>
     </row>
-    <row r="16" ht="67.5" spans="1:51">
-      <c r="A16" s="47"/>
-      <c r="B16" s="48" t="s">
+    <row r="16" ht="72" spans="1:51">
+      <c r="A16" s="86"/>
+      <c r="B16" s="87" t="s">
         <v>218</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="89" t="s">
         <v>219</v>
       </c>
-      <c r="D16" s="51" t="s">
+      <c r="D16" s="90" t="s">
         <v>220</v>
       </c>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="51" t="s">
+      <c r="E16" s="80"/>
+      <c r="F16" s="80"/>
+      <c r="G16" s="80"/>
+      <c r="H16" s="80"/>
+      <c r="I16" s="80"/>
+      <c r="J16" s="80"/>
+      <c r="K16" s="90" t="s">
         <v>221</v>
       </c>
-      <c r="L16" s="41"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="41"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="41"/>
-      <c r="S16" s="41"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="41"/>
-      <c r="V16" s="41"/>
-      <c r="W16" s="41"/>
-      <c r="X16" s="41"/>
-      <c r="Y16" s="41"/>
-      <c r="Z16" s="51" t="s">
+      <c r="L16" s="80"/>
+      <c r="M16" s="80"/>
+      <c r="N16" s="80"/>
+      <c r="O16" s="80"/>
+      <c r="P16" s="80"/>
+      <c r="Q16" s="80"/>
+      <c r="R16" s="80"/>
+      <c r="S16" s="80"/>
+      <c r="T16" s="80"/>
+      <c r="U16" s="80"/>
+      <c r="V16" s="80"/>
+      <c r="W16" s="80"/>
+      <c r="X16" s="80"/>
+      <c r="Y16" s="80"/>
+      <c r="Z16" s="90" t="s">
         <v>222</v>
       </c>
-      <c r="AA16" s="41" t="s">
+      <c r="AA16" s="80" t="s">
         <v>223</v>
       </c>
-      <c r="AB16" s="51" t="s">
+      <c r="AB16" s="90" t="s">
         <v>224</v>
       </c>
-      <c r="AC16" s="41"/>
-      <c r="AD16" s="41"/>
-      <c r="AE16" s="41"/>
-      <c r="AF16" s="41"/>
-      <c r="AG16" s="41"/>
-      <c r="AH16" s="41"/>
-      <c r="AI16" s="41"/>
-      <c r="AJ16" s="41"/>
-      <c r="AK16" s="41"/>
-      <c r="AL16" s="41"/>
-      <c r="AM16" s="51" t="s">
+      <c r="AC16" s="80"/>
+      <c r="AD16" s="80"/>
+      <c r="AE16" s="80"/>
+      <c r="AF16" s="80"/>
+      <c r="AG16" s="80"/>
+      <c r="AH16" s="80"/>
+      <c r="AI16" s="80"/>
+      <c r="AJ16" s="80"/>
+      <c r="AK16" s="80"/>
+      <c r="AL16" s="80"/>
+      <c r="AM16" s="90" t="s">
         <v>225</v>
       </c>
-      <c r="AN16" s="41"/>
-      <c r="AO16" s="41" t="s">
+      <c r="AN16" s="80"/>
+      <c r="AO16" s="80" t="s">
         <v>226</v>
       </c>
-      <c r="AP16" s="41" t="s">
+      <c r="AP16" s="80" t="s">
         <v>226</v>
       </c>
-      <c r="AQ16" s="41"/>
-      <c r="AR16" s="41"/>
-      <c r="AS16" s="41" t="s">
+      <c r="AQ16" s="80"/>
+      <c r="AR16" s="80"/>
+      <c r="AS16" s="80" t="s">
         <v>227</v>
       </c>
-      <c r="AT16" s="41"/>
-      <c r="AU16" s="41"/>
-      <c r="AV16" s="51" t="s">
+      <c r="AT16" s="80"/>
+      <c r="AU16" s="80"/>
+      <c r="AV16" s="90" t="s">
         <v>228</v>
       </c>
-      <c r="AW16" s="41"/>
-      <c r="AX16" s="41"/>
-      <c r="AY16" s="41"/>
+      <c r="AW16" s="80"/>
+      <c r="AX16" s="80"/>
+      <c r="AY16" s="80"/>
     </row>
-    <row r="17" ht="81" spans="1:51">
-      <c r="A17" s="47"/>
-      <c r="B17" s="48" t="s">
+    <row r="17" ht="86.4" spans="1:51">
+      <c r="A17" s="86"/>
+      <c r="B17" s="87" t="s">
         <v>229</v>
       </c>
-      <c r="C17" s="49"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="51" t="s">
+      <c r="C17" s="88"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="90" t="s">
         <v>230</v>
       </c>
-      <c r="H17" s="41"/>
-      <c r="I17" s="51" t="s">
+      <c r="H17" s="80"/>
+      <c r="I17" s="90" t="s">
         <v>231</v>
       </c>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41" t="s">
+      <c r="J17" s="80"/>
+      <c r="K17" s="80" t="s">
         <v>232</v>
       </c>
-      <c r="L17" s="41" t="s">
+      <c r="L17" s="80" t="s">
         <v>233</v>
       </c>
-      <c r="M17" s="41"/>
-      <c r="N17" s="41"/>
-      <c r="O17" s="51" t="s">
+      <c r="M17" s="80"/>
+      <c r="N17" s="80"/>
+      <c r="O17" s="90" t="s">
         <v>234</v>
       </c>
-      <c r="P17" s="41"/>
-      <c r="Q17" s="41"/>
-      <c r="R17" s="41"/>
-      <c r="S17" s="51" t="s">
+      <c r="P17" s="80"/>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="80"/>
+      <c r="S17" s="90" t="s">
         <v>235</v>
       </c>
-      <c r="T17" s="51" t="s">
+      <c r="T17" s="90" t="s">
         <v>236</v>
       </c>
-      <c r="U17" s="51" t="s">
+      <c r="U17" s="90" t="s">
         <v>237</v>
       </c>
-      <c r="V17" s="41"/>
-      <c r="W17" s="51" t="s">
+      <c r="V17" s="80"/>
+      <c r="W17" s="90" t="s">
         <v>238</v>
       </c>
-      <c r="X17" s="41" t="s">
+      <c r="X17" s="80" t="s">
         <v>239</v>
       </c>
-      <c r="Y17" s="51" t="s">
+      <c r="Y17" s="90" t="s">
         <v>240</v>
       </c>
-      <c r="Z17" s="51" t="s">
+      <c r="Z17" s="90" t="s">
         <v>241</v>
       </c>
-      <c r="AA17" s="51" t="s">
+      <c r="AA17" s="90" t="s">
         <v>242</v>
       </c>
-      <c r="AB17" s="51" t="s">
+      <c r="AB17" s="90" t="s">
         <v>243</v>
       </c>
-      <c r="AC17" s="41"/>
-      <c r="AD17" s="41"/>
-      <c r="AE17" s="41"/>
-      <c r="AF17" s="41"/>
-      <c r="AG17" s="41"/>
-      <c r="AH17" s="51" t="s">
+      <c r="AC17" s="80"/>
+      <c r="AD17" s="80"/>
+      <c r="AE17" s="80"/>
+      <c r="AF17" s="80"/>
+      <c r="AG17" s="80"/>
+      <c r="AH17" s="90" t="s">
         <v>244</v>
       </c>
-      <c r="AI17" s="41"/>
-      <c r="AJ17" s="41"/>
-      <c r="AK17" s="41"/>
-      <c r="AL17" s="41" t="s">
+      <c r="AI17" s="80"/>
+      <c r="AJ17" s="80"/>
+      <c r="AK17" s="80"/>
+      <c r="AL17" s="80" t="s">
         <v>245</v>
       </c>
-      <c r="AM17" s="51" t="s">
+      <c r="AM17" s="90" t="s">
         <v>246</v>
       </c>
-      <c r="AN17" s="51" t="s">
+      <c r="AN17" s="90" t="s">
         <v>247</v>
       </c>
-      <c r="AO17" s="51" t="s">
+      <c r="AO17" s="90" t="s">
         <v>248</v>
       </c>
-      <c r="AP17" s="51" t="s">
+      <c r="AP17" s="90" t="s">
         <v>249</v>
       </c>
-      <c r="AQ17" s="41"/>
-      <c r="AR17" s="51" t="s">
+      <c r="AQ17" s="80"/>
+      <c r="AR17" s="90" t="s">
         <v>250</v>
       </c>
-      <c r="AS17" s="41" t="s">
+      <c r="AS17" s="80" t="s">
         <v>251</v>
       </c>
-      <c r="AT17" s="41" t="s">
+      <c r="AT17" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="AU17" s="51" t="s">
+      <c r="AU17" s="90" t="s">
         <v>253</v>
       </c>
-      <c r="AV17" s="51" t="s">
+      <c r="AV17" s="90" t="s">
         <v>254</v>
       </c>
-      <c r="AW17" s="51" t="s">
+      <c r="AW17" s="90" t="s">
         <v>255</v>
       </c>
-      <c r="AX17" s="41"/>
-      <c r="AY17" s="51" t="s">
+      <c r="AX17" s="80"/>
+      <c r="AY17" s="90" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="18" ht="81" spans="1:51">
-      <c r="A18" s="47"/>
-      <c r="B18" s="48" t="s">
+    <row r="18" ht="86.4" spans="1:51">
+      <c r="A18" s="86"/>
+      <c r="B18" s="87" t="s">
         <v>257</v>
       </c>
-      <c r="C18" s="49"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="41"/>
-      <c r="F18" s="41"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="41"/>
-      <c r="I18" s="41"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="51" t="s">
+      <c r="C18" s="88"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="80"/>
+      <c r="G18" s="80"/>
+      <c r="H18" s="80"/>
+      <c r="I18" s="80"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="90" t="s">
         <v>258</v>
       </c>
-      <c r="L18" s="41"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="41"/>
-      <c r="O18" s="41"/>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="41"/>
-      <c r="R18" s="41"/>
-      <c r="S18" s="41"/>
-      <c r="T18" s="41"/>
-      <c r="U18" s="41"/>
-      <c r="V18" s="41"/>
-      <c r="W18" s="41"/>
-      <c r="X18" s="41"/>
-      <c r="Y18" s="41"/>
-      <c r="Z18" s="51" t="s">
+      <c r="L18" s="80"/>
+      <c r="M18" s="80"/>
+      <c r="N18" s="80"/>
+      <c r="O18" s="80"/>
+      <c r="P18" s="80"/>
+      <c r="Q18" s="80"/>
+      <c r="R18" s="80"/>
+      <c r="S18" s="80"/>
+      <c r="T18" s="80"/>
+      <c r="U18" s="80"/>
+      <c r="V18" s="80"/>
+      <c r="W18" s="80"/>
+      <c r="X18" s="80"/>
+      <c r="Y18" s="80"/>
+      <c r="Z18" s="90" t="s">
         <v>259</v>
       </c>
-      <c r="AA18" s="51" t="s">
+      <c r="AA18" s="90" t="s">
         <v>260</v>
       </c>
-      <c r="AB18" s="51" t="s">
+      <c r="AB18" s="90" t="s">
         <v>261</v>
       </c>
-      <c r="AC18" s="51" t="s">
+      <c r="AC18" s="90" t="s">
         <v>262</v>
       </c>
-      <c r="AD18" s="41"/>
-      <c r="AE18" s="41"/>
-      <c r="AF18" s="41"/>
-      <c r="AG18" s="41"/>
-      <c r="AH18" s="41"/>
-      <c r="AI18" s="41" t="s">
+      <c r="AD18" s="80"/>
+      <c r="AE18" s="80"/>
+      <c r="AF18" s="80"/>
+      <c r="AG18" s="80"/>
+      <c r="AH18" s="80"/>
+      <c r="AI18" s="80" t="s">
         <v>263</v>
       </c>
-      <c r="AJ18" s="41"/>
-      <c r="AK18" s="41" t="s">
+      <c r="AJ18" s="80"/>
+      <c r="AK18" s="80" t="s">
         <v>263</v>
       </c>
-      <c r="AL18" s="41"/>
-      <c r="AM18" s="41"/>
-      <c r="AN18" s="51" t="s">
+      <c r="AL18" s="80"/>
+      <c r="AM18" s="80"/>
+      <c r="AN18" s="90" t="s">
         <v>264</v>
       </c>
-      <c r="AO18" s="41"/>
-      <c r="AP18" s="41"/>
-      <c r="AQ18" s="41"/>
-      <c r="AR18" s="41"/>
-      <c r="AS18" s="41"/>
-      <c r="AT18" s="41"/>
-      <c r="AU18" s="41"/>
-      <c r="AV18" s="51" t="s">
+      <c r="AO18" s="80"/>
+      <c r="AP18" s="80"/>
+      <c r="AQ18" s="80"/>
+      <c r="AR18" s="80"/>
+      <c r="AS18" s="80"/>
+      <c r="AT18" s="80"/>
+      <c r="AU18" s="80"/>
+      <c r="AV18" s="90" t="s">
         <v>265</v>
       </c>
-      <c r="AW18" s="51" t="s">
+      <c r="AW18" s="90" t="s">
         <v>266</v>
       </c>
-      <c r="AX18" s="41"/>
-      <c r="AY18" s="51" t="s">
+      <c r="AX18" s="80"/>
+      <c r="AY18" s="90" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="19" ht="40.5" spans="1:51">
-      <c r="A19" s="47"/>
-      <c r="B19" s="48" t="s">
+    <row r="19" ht="43.2" spans="1:51">
+      <c r="A19" s="86"/>
+      <c r="B19" s="87" t="s">
         <v>267</v>
       </c>
-      <c r="C19" s="49"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="41"/>
-      <c r="F19" s="41"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="51" t="s">
+      <c r="C19" s="88"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
+      <c r="G19" s="80"/>
+      <c r="H19" s="90" t="s">
         <v>268</v>
       </c>
-      <c r="I19" s="41"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="51" t="s">
+      <c r="I19" s="80"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="90" t="s">
         <v>268</v>
       </c>
-      <c r="L19" s="41" t="s">
+      <c r="L19" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="M19" s="41"/>
-      <c r="N19" s="41"/>
-      <c r="O19" s="41"/>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="41"/>
-      <c r="S19" s="41"/>
-      <c r="T19" s="41"/>
-      <c r="U19" s="41"/>
-      <c r="V19" s="41"/>
-      <c r="W19" s="41"/>
-      <c r="X19" s="41"/>
-      <c r="Y19" s="41"/>
-      <c r="Z19" s="41"/>
-      <c r="AA19" s="41"/>
-      <c r="AB19" s="41"/>
-      <c r="AC19" s="41"/>
-      <c r="AD19" s="41"/>
-      <c r="AE19" s="41" t="s">
+      <c r="M19" s="80"/>
+      <c r="N19" s="80"/>
+      <c r="O19" s="80"/>
+      <c r="P19" s="80"/>
+      <c r="Q19" s="80"/>
+      <c r="R19" s="80"/>
+      <c r="S19" s="80"/>
+      <c r="T19" s="80"/>
+      <c r="U19" s="80"/>
+      <c r="V19" s="80"/>
+      <c r="W19" s="80"/>
+      <c r="X19" s="80"/>
+      <c r="Y19" s="80"/>
+      <c r="Z19" s="80"/>
+      <c r="AA19" s="80"/>
+      <c r="AB19" s="80"/>
+      <c r="AC19" s="80"/>
+      <c r="AD19" s="80"/>
+      <c r="AE19" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="AF19" s="41"/>
-      <c r="AG19" s="41"/>
-      <c r="AH19" s="41"/>
-      <c r="AI19" s="41"/>
-      <c r="AJ19" s="41"/>
-      <c r="AK19" s="41"/>
-      <c r="AL19" s="41"/>
-      <c r="AM19" s="41"/>
-      <c r="AN19" s="41"/>
-      <c r="AO19" s="41"/>
-      <c r="AP19" s="41" t="s">
+      <c r="AF19" s="80"/>
+      <c r="AG19" s="80"/>
+      <c r="AH19" s="80"/>
+      <c r="AI19" s="80"/>
+      <c r="AJ19" s="80"/>
+      <c r="AK19" s="80"/>
+      <c r="AL19" s="80"/>
+      <c r="AM19" s="80"/>
+      <c r="AN19" s="80"/>
+      <c r="AO19" s="80"/>
+      <c r="AP19" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="AQ19" s="41"/>
-      <c r="AR19" s="41"/>
-      <c r="AS19" s="41"/>
-      <c r="AT19" s="41"/>
-      <c r="AU19" s="41"/>
-      <c r="AV19" s="51"/>
-      <c r="AW19" s="51"/>
-      <c r="AX19" s="41"/>
-      <c r="AY19" s="51" t="s">
+      <c r="AQ19" s="80"/>
+      <c r="AR19" s="80"/>
+      <c r="AS19" s="80"/>
+      <c r="AT19" s="80"/>
+      <c r="AU19" s="80"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="80"/>
+      <c r="AY19" s="90" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="20" ht="54" spans="1:51">
-      <c r="A20" s="47"/>
-      <c r="B20" s="48" t="s">
+    <row r="20" ht="57.6" spans="1:51">
+      <c r="A20" s="86"/>
+      <c r="B20" s="87" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="49"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="41"/>
-      <c r="I20" s="41"/>
-      <c r="J20" s="41"/>
-      <c r="K20" s="41"/>
-      <c r="L20" s="41"/>
-      <c r="M20" s="41"/>
-      <c r="N20" s="41"/>
-      <c r="O20" s="41"/>
-      <c r="P20" s="41"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="41"/>
-      <c r="S20" s="41"/>
-      <c r="T20" s="41"/>
-      <c r="U20" s="41"/>
-      <c r="V20" s="41"/>
-      <c r="W20" s="41"/>
-      <c r="X20" s="41"/>
-      <c r="Y20" s="41"/>
-      <c r="Z20" s="41"/>
-      <c r="AA20" s="41"/>
-      <c r="AB20" s="41"/>
-      <c r="AC20" s="41"/>
-      <c r="AD20" s="41"/>
-      <c r="AE20" s="41"/>
-      <c r="AF20" s="41"/>
-      <c r="AG20" s="41"/>
-      <c r="AH20" s="41"/>
-      <c r="AI20" s="41"/>
-      <c r="AJ20" s="51" t="s">
+      <c r="C20" s="88"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="80"/>
+      <c r="K20" s="80"/>
+      <c r="L20" s="80"/>
+      <c r="M20" s="80"/>
+      <c r="N20" s="80"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="80"/>
+      <c r="R20" s="80"/>
+      <c r="S20" s="80"/>
+      <c r="T20" s="80"/>
+      <c r="U20" s="80"/>
+      <c r="V20" s="80"/>
+      <c r="W20" s="80"/>
+      <c r="X20" s="80"/>
+      <c r="Y20" s="80"/>
+      <c r="Z20" s="80"/>
+      <c r="AA20" s="80"/>
+      <c r="AB20" s="80"/>
+      <c r="AC20" s="80"/>
+      <c r="AD20" s="80"/>
+      <c r="AE20" s="80"/>
+      <c r="AF20" s="80"/>
+      <c r="AG20" s="80"/>
+      <c r="AH20" s="80"/>
+      <c r="AI20" s="80"/>
+      <c r="AJ20" s="90" t="s">
         <v>272</v>
       </c>
-      <c r="AK20" s="41"/>
-      <c r="AL20" s="41"/>
-      <c r="AM20" s="41"/>
-      <c r="AN20" s="41"/>
-      <c r="AO20" s="41"/>
-      <c r="AP20" s="41"/>
-      <c r="AQ20" s="41"/>
-      <c r="AR20" s="41"/>
-      <c r="AS20" s="41"/>
-      <c r="AT20" s="41"/>
-      <c r="AU20" s="41"/>
-      <c r="AV20" s="51"/>
-      <c r="AW20" s="51"/>
-      <c r="AX20" s="41"/>
-      <c r="AY20" s="41"/>
+      <c r="AK20" s="80"/>
+      <c r="AL20" s="80"/>
+      <c r="AM20" s="80"/>
+      <c r="AN20" s="80"/>
+      <c r="AO20" s="80"/>
+      <c r="AP20" s="80"/>
+      <c r="AQ20" s="80"/>
+      <c r="AR20" s="80"/>
+      <c r="AS20" s="80"/>
+      <c r="AT20" s="80"/>
+      <c r="AU20" s="80"/>
+      <c r="AV20" s="90"/>
+      <c r="AW20" s="90"/>
+      <c r="AX20" s="80"/>
+      <c r="AY20" s="80"/>
     </row>
-    <row r="21" ht="81" spans="1:51">
-      <c r="A21" s="47"/>
-      <c r="B21" s="52" t="s">
+    <row r="21" ht="86.4" spans="1:51">
+      <c r="A21" s="86"/>
+      <c r="B21" s="91" t="s">
         <v>273</v>
       </c>
-      <c r="C21" s="50" t="s">
+      <c r="C21" s="89" t="s">
         <v>274</v>
       </c>
-      <c r="D21" s="50" t="s">
+      <c r="D21" s="89" t="s">
         <v>274</v>
       </c>
-      <c r="E21" s="41"/>
-      <c r="F21" s="41"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="51" t="s">
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="80"/>
+      <c r="K21" s="90" t="s">
         <v>275</v>
       </c>
-      <c r="L21" s="41" t="s">
+      <c r="L21" s="80" t="s">
         <v>276</v>
       </c>
-      <c r="M21" s="41"/>
-      <c r="N21" s="41"/>
-      <c r="O21" s="41"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="41"/>
-      <c r="S21" s="41"/>
-      <c r="T21" s="41"/>
-      <c r="U21" s="41"/>
-      <c r="V21" s="41"/>
-      <c r="W21" s="41"/>
-      <c r="X21" s="41"/>
-      <c r="Y21" s="41"/>
-      <c r="Z21" s="41"/>
-      <c r="AA21" s="41"/>
-      <c r="AB21" s="41"/>
-      <c r="AC21" s="41"/>
-      <c r="AD21" s="41"/>
-      <c r="AE21" s="41" t="s">
+      <c r="M21" s="80"/>
+      <c r="N21" s="80"/>
+      <c r="O21" s="80"/>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="80"/>
+      <c r="R21" s="80"/>
+      <c r="S21" s="80"/>
+      <c r="T21" s="80"/>
+      <c r="U21" s="80"/>
+      <c r="V21" s="80"/>
+      <c r="W21" s="80"/>
+      <c r="X21" s="80"/>
+      <c r="Y21" s="80"/>
+      <c r="Z21" s="80"/>
+      <c r="AA21" s="80"/>
+      <c r="AB21" s="80"/>
+      <c r="AC21" s="80"/>
+      <c r="AD21" s="80"/>
+      <c r="AE21" s="80" t="s">
         <v>277</v>
       </c>
-      <c r="AF21" s="51" t="s">
+      <c r="AF21" s="90" t="s">
         <v>278</v>
       </c>
-      <c r="AG21" s="51" t="s">
+      <c r="AG21" s="90" t="s">
         <v>279</v>
       </c>
-      <c r="AH21" s="41"/>
-      <c r="AI21" s="51" t="s">
+      <c r="AH21" s="80"/>
+      <c r="AI21" s="90" t="s">
         <v>280</v>
       </c>
-      <c r="AJ21" s="51" t="s">
+      <c r="AJ21" s="90" t="s">
         <v>281</v>
       </c>
-      <c r="AK21" s="41"/>
-      <c r="AL21" s="41"/>
-      <c r="AM21" s="41"/>
-      <c r="AN21" s="41"/>
-      <c r="AO21" s="41" t="s">
+      <c r="AK21" s="80"/>
+      <c r="AL21" s="80"/>
+      <c r="AM21" s="80"/>
+      <c r="AN21" s="80"/>
+      <c r="AO21" s="80" t="s">
         <v>276</v>
       </c>
-      <c r="AP21" s="41" t="s">
+      <c r="AP21" s="80" t="s">
         <v>276</v>
       </c>
-      <c r="AQ21" s="41"/>
-      <c r="AR21" s="41"/>
-      <c r="AS21" s="41"/>
-      <c r="AT21" s="41" t="s">
+      <c r="AQ21" s="80"/>
+      <c r="AR21" s="80"/>
+      <c r="AS21" s="80"/>
+      <c r="AT21" s="80" t="s">
         <v>277</v>
       </c>
-      <c r="AU21" s="41"/>
-      <c r="AV21" s="41"/>
-      <c r="AW21" s="41"/>
-      <c r="AX21" s="51" t="s">
+      <c r="AU21" s="80"/>
+      <c r="AV21" s="80"/>
+      <c r="AW21" s="80"/>
+      <c r="AX21" s="90" t="s">
         <v>282</v>
       </c>
-      <c r="AY21" s="51" t="s">
+      <c r="AY21" s="90" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:51">
-      <c r="A22" s="53"/>
-      <c r="B22" s="48" t="s">
+      <c r="A22" s="92"/>
+      <c r="B22" s="87" t="s">
         <v>284</v>
       </c>
-      <c r="C22" s="49"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="41"/>
-      <c r="K22" s="41"/>
-      <c r="L22" s="41"/>
-      <c r="M22" s="41"/>
-      <c r="N22" s="41"/>
-      <c r="O22" s="41"/>
-      <c r="P22" s="41"/>
-      <c r="Q22" s="41"/>
-      <c r="R22" s="41"/>
-      <c r="S22" s="41"/>
-      <c r="T22" s="41"/>
-      <c r="U22" s="41"/>
-      <c r="V22" s="41"/>
-      <c r="W22" s="41"/>
-      <c r="X22" s="41"/>
-      <c r="Y22" s="41"/>
-      <c r="Z22" s="41"/>
-      <c r="AA22" s="41"/>
-      <c r="AB22" s="41"/>
-      <c r="AC22" s="41"/>
-      <c r="AD22" s="41"/>
-      <c r="AE22" s="41"/>
-      <c r="AF22" s="41"/>
-      <c r="AG22" s="41"/>
-      <c r="AH22" s="41"/>
-      <c r="AI22" s="41"/>
-      <c r="AJ22" s="41"/>
-      <c r="AK22" s="41"/>
-      <c r="AL22" s="41"/>
-      <c r="AM22" s="41"/>
-      <c r="AN22" s="41"/>
-      <c r="AO22" s="41"/>
-      <c r="AP22" s="41"/>
-      <c r="AQ22" s="41"/>
-      <c r="AR22" s="41"/>
-      <c r="AS22" s="41"/>
-      <c r="AT22" s="41"/>
-      <c r="AU22" s="41"/>
-      <c r="AV22" s="51"/>
-      <c r="AW22" s="51"/>
-      <c r="AX22" s="41"/>
-      <c r="AY22" s="41"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="80"/>
+      <c r="K22" s="80"/>
+      <c r="L22" s="80"/>
+      <c r="M22" s="80"/>
+      <c r="N22" s="80"/>
+      <c r="O22" s="80"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="80"/>
+      <c r="R22" s="80"/>
+      <c r="S22" s="80"/>
+      <c r="T22" s="80"/>
+      <c r="U22" s="80"/>
+      <c r="V22" s="80"/>
+      <c r="W22" s="80"/>
+      <c r="X22" s="80"/>
+      <c r="Y22" s="80"/>
+      <c r="Z22" s="80"/>
+      <c r="AA22" s="80"/>
+      <c r="AB22" s="80"/>
+      <c r="AC22" s="80"/>
+      <c r="AD22" s="80"/>
+      <c r="AE22" s="80"/>
+      <c r="AF22" s="80"/>
+      <c r="AG22" s="80"/>
+      <c r="AH22" s="80"/>
+      <c r="AI22" s="80"/>
+      <c r="AJ22" s="80"/>
+      <c r="AK22" s="80"/>
+      <c r="AL22" s="80"/>
+      <c r="AM22" s="80"/>
+      <c r="AN22" s="80"/>
+      <c r="AO22" s="80"/>
+      <c r="AP22" s="80"/>
+      <c r="AQ22" s="80"/>
+      <c r="AR22" s="80"/>
+      <c r="AS22" s="80"/>
+      <c r="AT22" s="80"/>
+      <c r="AU22" s="80"/>
+      <c r="AV22" s="90"/>
+      <c r="AW22" s="90"/>
+      <c r="AX22" s="80"/>
+      <c r="AY22" s="80"/>
     </row>
-    <row r="24" ht="108" spans="1:51">
-      <c r="A24" s="30" t="s">
+    <row r="24" ht="115.2" spans="1:51">
+      <c r="A24" s="70" t="s">
         <v>285</v>
       </c>
-      <c r="B24" s="37" t="s">
+      <c r="B24" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="C24" s="75" t="s">
         <v>287</v>
       </c>
-      <c r="D24" s="35" t="s">
+      <c r="D24" s="75" t="s">
         <v>170</v>
       </c>
-      <c r="E24" s="35" t="s">
+      <c r="E24" s="75" t="s">
         <v>288</v>
       </c>
-      <c r="F24" s="35" t="s">
+      <c r="F24" s="75" t="s">
         <v>289</v>
       </c>
-      <c r="G24" s="35" t="s">
+      <c r="G24" s="75" t="s">
         <v>290</v>
       </c>
-      <c r="H24" s="35" t="s">
+      <c r="H24" s="75" t="s">
         <v>291</v>
       </c>
-      <c r="I24" s="35" t="s">
+      <c r="I24" s="75" t="s">
         <v>292</v>
       </c>
-      <c r="J24" s="35" t="s">
+      <c r="J24" s="75" t="s">
         <v>293</v>
       </c>
-      <c r="K24" s="35" t="s">
+      <c r="K24" s="75" t="s">
         <v>294</v>
       </c>
-      <c r="L24" s="35" t="s">
+      <c r="L24" s="75" t="s">
         <v>295</v>
       </c>
-      <c r="M24" s="35" t="s">
+      <c r="M24" s="75" t="s">
         <v>296</v>
       </c>
-      <c r="N24" s="35" t="s">
+      <c r="N24" s="75" t="s">
         <v>297</v>
       </c>
-      <c r="O24" s="35" t="s">
+      <c r="O24" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="P24" s="35" t="s">
+      <c r="P24" s="75" t="s">
         <v>298</v>
       </c>
-      <c r="Q24" s="35" t="s">
+      <c r="Q24" s="75" t="s">
         <v>299</v>
       </c>
-      <c r="R24" s="35" t="s">
+      <c r="R24" s="75" t="s">
         <v>300</v>
       </c>
-      <c r="S24" s="35" t="s">
+      <c r="S24" s="75" t="s">
         <v>301</v>
       </c>
-      <c r="T24" s="35" t="s">
+      <c r="T24" s="75" t="s">
         <v>302</v>
       </c>
-      <c r="U24" s="35" t="s">
+      <c r="U24" s="75" t="s">
         <v>303</v>
       </c>
-      <c r="V24" s="35" t="s">
+      <c r="V24" s="75" t="s">
         <v>304</v>
       </c>
-      <c r="W24" s="35" t="s">
+      <c r="W24" s="75" t="s">
         <v>305</v>
       </c>
-      <c r="X24" s="35" t="s">
+      <c r="X24" s="75" t="s">
         <v>306</v>
       </c>
-      <c r="Y24" s="35" t="s">
+      <c r="Y24" s="75" t="s">
         <v>307</v>
       </c>
-      <c r="Z24" s="35" t="s">
+      <c r="Z24" s="75" t="s">
         <v>308</v>
       </c>
-      <c r="AA24" s="35" t="s">
+      <c r="AA24" s="75" t="s">
         <v>309</v>
       </c>
-      <c r="AB24" s="35" t="s">
+      <c r="AB24" s="75" t="s">
         <v>310</v>
       </c>
-      <c r="AC24" s="35" t="s">
+      <c r="AC24" s="75" t="s">
         <v>311</v>
       </c>
-      <c r="AD24" s="35" t="s">
+      <c r="AD24" s="75" t="s">
         <v>312</v>
       </c>
-      <c r="AE24" s="35" t="s">
+      <c r="AE24" s="75" t="s">
         <v>313</v>
       </c>
-      <c r="AF24" s="35" t="s">
+      <c r="AF24" s="75" t="s">
         <v>314</v>
       </c>
-      <c r="AG24" s="35" t="s">
+      <c r="AG24" s="75" t="s">
         <v>315</v>
       </c>
-      <c r="AH24" s="35" t="s">
+      <c r="AH24" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AI24" s="35" t="s">
+      <c r="AI24" s="75" t="s">
         <v>316</v>
       </c>
-      <c r="AJ24" s="35" t="s">
+      <c r="AJ24" s="75" t="s">
         <v>317</v>
       </c>
-      <c r="AK24" s="35" t="s">
+      <c r="AK24" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AL24" s="35" t="s">
+      <c r="AL24" s="75" t="s">
         <v>318</v>
       </c>
-      <c r="AM24" s="35" t="s">
+      <c r="AM24" s="75" t="s">
         <v>319</v>
       </c>
-      <c r="AN24" s="35" t="s">
+      <c r="AN24" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AO24" s="35" t="s">
+      <c r="AO24" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AP24" s="35" t="s">
+      <c r="AP24" s="75" t="s">
         <v>315</v>
       </c>
-      <c r="AQ24" s="35" t="s">
+      <c r="AQ24" s="75" t="s">
         <v>315</v>
       </c>
-      <c r="AR24" s="35" t="s">
+      <c r="AR24" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AS24" s="35" t="s">
+      <c r="AS24" s="75" t="s">
         <v>320</v>
       </c>
-      <c r="AT24" s="35" t="s">
+      <c r="AT24" s="75" t="s">
         <v>321</v>
       </c>
-      <c r="AU24" s="35" t="s">
+      <c r="AU24" s="75" t="s">
         <v>322</v>
       </c>
-      <c r="AV24" s="35" t="s">
+      <c r="AV24" s="75" t="s">
         <v>323</v>
       </c>
-      <c r="AW24" s="36" t="s">
+      <c r="AW24" s="76" t="s">
         <v>324</v>
       </c>
-      <c r="AX24" s="36" t="s">
+      <c r="AX24" s="76" t="s">
         <v>315</v>
       </c>
-      <c r="AY24" s="36" t="s">
+      <c r="AY24" s="76" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:51">
-      <c r="A25" s="32"/>
-      <c r="B25" s="37" t="s">
+      <c r="A25" s="72"/>
+      <c r="B25" s="27" t="s">
         <v>325</v>
       </c>
-      <c r="C25" s="35"/>
-      <c r="D25" s="35"/>
-      <c r="E25" s="35"/>
-      <c r="F25" s="35"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="35"/>
-      <c r="I25" s="35"/>
-      <c r="J25" s="35"/>
-      <c r="K25" s="35"/>
-      <c r="L25" s="35"/>
-      <c r="M25" s="35"/>
-      <c r="N25" s="35"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35"/>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="35"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="35"/>
-      <c r="W25" s="35"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="35"/>
-      <c r="Z25" s="35"/>
-      <c r="AA25" s="35"/>
-      <c r="AB25" s="35"/>
-      <c r="AC25" s="35"/>
-      <c r="AD25" s="35"/>
-      <c r="AE25" s="35"/>
-      <c r="AF25" s="35"/>
-      <c r="AG25" s="35"/>
-      <c r="AH25" s="35"/>
-      <c r="AI25" s="35"/>
-      <c r="AJ25" s="35"/>
-      <c r="AK25" s="35"/>
-      <c r="AL25" s="35"/>
-      <c r="AM25" s="35"/>
-      <c r="AN25" s="35"/>
-      <c r="AO25" s="35"/>
-      <c r="AP25" s="35"/>
-      <c r="AQ25" s="35"/>
-      <c r="AR25" s="35"/>
-      <c r="AS25" s="35"/>
-      <c r="AT25" s="35"/>
-      <c r="AU25" s="35"/>
-      <c r="AV25" s="35"/>
-      <c r="AW25" s="36"/>
-      <c r="AX25" s="36"/>
-      <c r="AY25" s="36"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
+      <c r="J25" s="75"/>
+      <c r="K25" s="75"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="75"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="75"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="75"/>
+      <c r="R25" s="75"/>
+      <c r="S25" s="75"/>
+      <c r="T25" s="75"/>
+      <c r="U25" s="75"/>
+      <c r="V25" s="75"/>
+      <c r="W25" s="75"/>
+      <c r="X25" s="75"/>
+      <c r="Y25" s="75"/>
+      <c r="Z25" s="75"/>
+      <c r="AA25" s="75"/>
+      <c r="AB25" s="75"/>
+      <c r="AC25" s="75"/>
+      <c r="AD25" s="75"/>
+      <c r="AE25" s="75"/>
+      <c r="AF25" s="75"/>
+      <c r="AG25" s="75"/>
+      <c r="AH25" s="75"/>
+      <c r="AI25" s="75"/>
+      <c r="AJ25" s="75"/>
+      <c r="AK25" s="75"/>
+      <c r="AL25" s="75"/>
+      <c r="AM25" s="75"/>
+      <c r="AN25" s="75"/>
+      <c r="AO25" s="75"/>
+      <c r="AP25" s="75"/>
+      <c r="AQ25" s="75"/>
+      <c r="AR25" s="75"/>
+      <c r="AS25" s="75"/>
+      <c r="AT25" s="75"/>
+      <c r="AU25" s="75"/>
+      <c r="AV25" s="75"/>
+      <c r="AW25" s="76"/>
+      <c r="AX25" s="76"/>
+      <c r="AY25" s="76"/>
     </row>
-    <row r="26" customFormat="1" ht="94.5" spans="1:51">
-      <c r="A26" s="38"/>
-      <c r="B26" s="37" t="s">
+    <row r="26" customFormat="1" ht="100.8" spans="1:51">
+      <c r="A26" s="77"/>
+      <c r="B26" s="27" t="s">
         <v>326</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35"/>
-      <c r="G26" s="35" t="s">
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75" t="s">
         <v>327</v>
       </c>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="35"/>
-      <c r="M26" s="35" t="s">
+      <c r="H26" s="75"/>
+      <c r="I26" s="75"/>
+      <c r="J26" s="75"/>
+      <c r="K26" s="75"/>
+      <c r="L26" s="75"/>
+      <c r="M26" s="75" t="s">
         <v>328</v>
       </c>
-      <c r="N26" s="35" t="s">
+      <c r="N26" s="75" t="s">
         <v>329</v>
       </c>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35"/>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="35"/>
-      <c r="U26" s="35"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="35"/>
-      <c r="Z26" s="35"/>
-      <c r="AA26" s="35"/>
-      <c r="AB26" s="35"/>
-      <c r="AC26" s="35"/>
-      <c r="AD26" s="35"/>
-      <c r="AE26" s="35"/>
-      <c r="AF26" s="35"/>
-      <c r="AG26" s="35"/>
-      <c r="AH26" s="35"/>
-      <c r="AI26" s="35"/>
-      <c r="AJ26" s="35"/>
-      <c r="AK26" s="35"/>
-      <c r="AL26" s="35"/>
-      <c r="AM26" s="35"/>
-      <c r="AN26" s="35"/>
-      <c r="AO26" s="35" t="s">
+      <c r="O26" s="75"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="75"/>
+      <c r="R26" s="75"/>
+      <c r="S26" s="75"/>
+      <c r="T26" s="75"/>
+      <c r="U26" s="75"/>
+      <c r="V26" s="75"/>
+      <c r="W26" s="75"/>
+      <c r="X26" s="75"/>
+      <c r="Y26" s="75"/>
+      <c r="Z26" s="75"/>
+      <c r="AA26" s="75"/>
+      <c r="AB26" s="75"/>
+      <c r="AC26" s="75"/>
+      <c r="AD26" s="75"/>
+      <c r="AE26" s="75"/>
+      <c r="AF26" s="75"/>
+      <c r="AG26" s="75"/>
+      <c r="AH26" s="75"/>
+      <c r="AI26" s="75"/>
+      <c r="AJ26" s="75"/>
+      <c r="AK26" s="75"/>
+      <c r="AL26" s="75"/>
+      <c r="AM26" s="75"/>
+      <c r="AN26" s="75"/>
+      <c r="AO26" s="75" t="s">
         <v>330</v>
       </c>
-      <c r="AP26" s="35" t="s">
+      <c r="AP26" s="75" t="s">
         <v>331</v>
       </c>
-      <c r="AQ26" s="35"/>
-      <c r="AR26" s="35"/>
-      <c r="AS26" s="35"/>
-      <c r="AT26" s="35"/>
-      <c r="AU26" s="35"/>
-      <c r="AV26" s="35"/>
-      <c r="AW26" s="36"/>
-      <c r="AX26" s="36"/>
-      <c r="AY26" s="36"/>
+      <c r="AQ26" s="75"/>
+      <c r="AR26" s="75"/>
+      <c r="AS26" s="75"/>
+      <c r="AT26" s="75"/>
+      <c r="AU26" s="75"/>
+      <c r="AV26" s="75"/>
+      <c r="AW26" s="76"/>
+      <c r="AX26" s="76"/>
+      <c r="AY26" s="76"/>
     </row>
-    <row r="27" s="13" customFormat="1" ht="27" spans="1:51">
-      <c r="A27" s="39" t="s">
+    <row r="27" s="54" customFormat="1" ht="28.8" spans="1:51">
+      <c r="A27" s="78" t="s">
         <v>332</v>
       </c>
-      <c r="B27" s="51" t="s">
+      <c r="B27" s="90" t="s">
         <v>333</v>
       </c>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="54"/>
-      <c r="G27" s="54"/>
-      <c r="H27" s="54"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="54"/>
-      <c r="K27" s="54"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="54"/>
-      <c r="O27" s="54"/>
-      <c r="P27" s="54"/>
-      <c r="Q27" s="54"/>
-      <c r="R27" s="54"/>
-      <c r="S27" s="54"/>
-      <c r="T27" s="54"/>
-      <c r="U27" s="54"/>
-      <c r="V27" s="54"/>
-      <c r="W27" s="54"/>
-      <c r="X27" s="54"/>
-      <c r="Y27" s="54"/>
-      <c r="Z27" s="54"/>
-      <c r="AA27" s="54"/>
-      <c r="AB27" s="54"/>
-      <c r="AC27" s="54"/>
-      <c r="AD27" s="54"/>
-      <c r="AE27" s="54"/>
-      <c r="AF27" s="54"/>
-      <c r="AG27" s="54"/>
-      <c r="AH27" s="54"/>
-      <c r="AI27" s="54"/>
-      <c r="AJ27" s="54"/>
-      <c r="AK27" s="54"/>
-      <c r="AL27" s="54"/>
-      <c r="AM27" s="54"/>
-      <c r="AN27" s="54"/>
-      <c r="AO27" s="54"/>
-      <c r="AP27" s="54"/>
-      <c r="AQ27" s="54"/>
-      <c r="AR27" s="54"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="93"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="93"/>
+      <c r="K27" s="93"/>
+      <c r="L27" s="93"/>
+      <c r="M27" s="93"/>
+      <c r="N27" s="93"/>
+      <c r="O27" s="93"/>
+      <c r="P27" s="93"/>
+      <c r="Q27" s="93"/>
+      <c r="R27" s="93"/>
+      <c r="S27" s="93"/>
+      <c r="T27" s="93"/>
+      <c r="U27" s="93"/>
+      <c r="V27" s="93"/>
+      <c r="W27" s="93"/>
+      <c r="X27" s="93"/>
+      <c r="Y27" s="93"/>
+      <c r="Z27" s="93"/>
+      <c r="AA27" s="93"/>
+      <c r="AB27" s="93"/>
+      <c r="AC27" s="93"/>
+      <c r="AD27" s="93"/>
+      <c r="AE27" s="93"/>
+      <c r="AF27" s="93"/>
+      <c r="AG27" s="93"/>
+      <c r="AH27" s="93"/>
+      <c r="AI27" s="93"/>
+      <c r="AJ27" s="93"/>
+      <c r="AK27" s="93"/>
+      <c r="AL27" s="93"/>
+      <c r="AM27" s="93"/>
+      <c r="AN27" s="93"/>
+      <c r="AO27" s="93"/>
+      <c r="AP27" s="93"/>
+      <c r="AQ27" s="93"/>
+      <c r="AR27" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -7387,11 +8614,2293 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <dimension ref="A1:X52"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="13.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="4" max="4" width="13" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="14.8888888888889" customWidth="1"/>
+    <col min="8" max="8" width="13.1111111111111" customWidth="1"/>
+    <col min="9" max="9" width="13.2222222222222" customWidth="1"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="11" max="11" width="9.77777777777778" customWidth="1"/>
+    <col min="12" max="12" width="4.77777777777778" customWidth="1"/>
+    <col min="13" max="13" width="5.66666666666667" customWidth="1"/>
+    <col min="15" max="15" width="9.66666666666667" customWidth="1"/>
+    <col min="16" max="16" width="14.3333333333333" customWidth="1"/>
+    <col min="17" max="17" width="9.66666666666667" customWidth="1"/>
+    <col min="19" max="19" width="11.4444444444444" customWidth="1"/>
+    <col min="20" max="20" width="13.5555555555556" customWidth="1"/>
+    <col min="21" max="21" width="9.11111111111111" customWidth="1"/>
+    <col min="23" max="23" width="12.8888888888889" customWidth="1"/>
+    <col min="24" max="24" width="10.2222222222222" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:24">
+      <c r="A1" s="14" t="s">
+        <v>334</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>335</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>337</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>338</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>339</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+      <c r="L1" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="M1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="O1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="Q1" s="16"/>
+      <c r="R1" s="16"/>
+      <c r="S1" s="16"/>
+      <c r="T1" s="16"/>
+      <c r="U1" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="V1" s="16"/>
+      <c r="W1" s="16"/>
+      <c r="X1" s="18"/>
+    </row>
+    <row r="2" spans="1:24">
+      <c r="A2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="H2" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="I2" s="23" t="s">
+        <v>340</v>
+      </c>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
+      <c r="L2" s="24" t="s">
+        <v>341</v>
+      </c>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="22" t="s">
+        <v>332</v>
+      </c>
+      <c r="V2" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="W2" s="23"/>
+      <c r="X2" s="25"/>
+    </row>
+    <row r="3" ht="87.15" spans="1:24">
+      <c r="A3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="I3" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="J3" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="K3" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="L3" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="M3" s="29" t="s">
+        <v>217</v>
+      </c>
+      <c r="N3" s="28" t="s">
+        <v>345</v>
+      </c>
+      <c r="O3" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="P3" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="Q3" s="29" t="s">
+        <v>257</v>
+      </c>
+      <c r="R3" s="29" t="s">
+        <v>267</v>
+      </c>
+      <c r="S3" s="28" t="s">
+        <v>346</v>
+      </c>
+      <c r="T3" s="28" t="s">
+        <v>347</v>
+      </c>
+      <c r="U3" s="26" t="s">
+        <v>333</v>
+      </c>
+      <c r="V3" s="27" t="s">
+        <v>286</v>
+      </c>
+      <c r="W3" s="27" t="s">
+        <v>325</v>
+      </c>
+      <c r="X3" s="30" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="4" s="12" customFormat="1" ht="158.4" spans="1:24">
+      <c r="A4" s="19" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="31" t="s">
+        <v>348</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>349</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="E4" s="32"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="33" t="s">
+        <v>148</v>
+      </c>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="35" t="s">
+        <v>219</v>
+      </c>
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="U4" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="37"/>
+    </row>
+    <row r="5" ht="100.8" spans="1:24">
+      <c r="A5" s="19"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="32" t="s">
+        <v>351</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="E5" s="32"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="33" t="s">
+        <v>353</v>
+      </c>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="35" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="U5" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="V5" s="33"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="37"/>
+    </row>
+    <row r="6" ht="144" spans="1:24">
+      <c r="A6" s="19"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E6" s="32"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="V6" s="33"/>
+      <c r="W6" s="33"/>
+      <c r="X6" s="37"/>
+    </row>
+    <row r="7" ht="172.8" spans="1:24">
+      <c r="A7" s="19"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="32" t="s">
+        <v>357</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="E7" s="32"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="M7" s="39"/>
+      <c r="N7" s="39"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="33" t="s">
+        <v>289</v>
+      </c>
+      <c r="V7" s="33"/>
+      <c r="W7" s="33"/>
+      <c r="X7" s="37"/>
+    </row>
+    <row r="8" customFormat="1" ht="216" spans="1:24">
+      <c r="A8" s="19"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="32" t="s">
+        <v>359</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E8" s="32"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="33" t="s">
+        <v>361</v>
+      </c>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35" t="s">
+        <v>230</v>
+      </c>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="V8" s="33"/>
+      <c r="W8" s="33"/>
+      <c r="X8" s="40" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="9" customFormat="1" ht="100.8" spans="1:24">
+      <c r="A9" s="19"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="32" t="s">
+        <v>362</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="E9" s="32"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="39" t="s">
+        <v>186</v>
+      </c>
+      <c r="M9" s="39"/>
+      <c r="N9" s="39"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="S9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="33" t="s">
+        <v>291</v>
+      </c>
+      <c r="V9" s="33"/>
+      <c r="W9" s="33"/>
+      <c r="X9" s="37"/>
+    </row>
+    <row r="10" s="13" customFormat="1" ht="101.55" spans="1:24">
+      <c r="A10" s="19"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="E10" s="32"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="39"/>
+      <c r="M10" s="39"/>
+      <c r="N10" s="39"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="35" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="33" t="s">
+        <v>292</v>
+      </c>
+      <c r="V10" s="33"/>
+      <c r="W10" s="33"/>
+      <c r="X10" s="37"/>
+    </row>
+    <row r="11" s="12" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A11" s="19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="41" t="s">
+        <v>366</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="E11" s="32"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="33" t="s">
+        <v>293</v>
+      </c>
+      <c r="V11" s="33"/>
+      <c r="W11" s="33"/>
+      <c r="X11" s="37"/>
+    </row>
+    <row r="12" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A12" s="19"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="32" t="s">
+        <v>369</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="E12" s="32"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="42" t="s">
+        <v>171</v>
+      </c>
+      <c r="K12" s="42" t="s">
+        <v>174</v>
+      </c>
+      <c r="L12" s="39" t="s">
+        <v>187</v>
+      </c>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="P12" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="Q12" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="R12" s="35" t="s">
+        <v>268</v>
+      </c>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="U12" s="33" t="s">
+        <v>294</v>
+      </c>
+      <c r="V12" s="33"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="37"/>
+    </row>
+    <row r="13" customFormat="1" ht="57.6" spans="1:24">
+      <c r="A13" s="19"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="E13" s="32"/>
+      <c r="F13" s="38"/>
+      <c r="G13" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="42" t="s">
+        <v>175</v>
+      </c>
+      <c r="L13" s="39" t="s">
+        <v>188</v>
+      </c>
+      <c r="M13" s="39"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="S13" s="35"/>
+      <c r="T13" s="35" t="s">
+        <v>276</v>
+      </c>
+      <c r="U13" s="33" t="s">
+        <v>295</v>
+      </c>
+      <c r="V13" s="33"/>
+      <c r="W13" s="33"/>
+      <c r="X13" s="37"/>
+    </row>
+    <row r="14" customFormat="1" ht="115.2" spans="1:24">
+      <c r="A14" s="19"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="32" t="s">
+        <v>373</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="E14" s="32"/>
+      <c r="F14" s="38"/>
+      <c r="G14" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="39" t="s">
+        <v>189</v>
+      </c>
+      <c r="M14" s="39"/>
+      <c r="N14" s="39"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="33" t="s">
+        <v>296</v>
+      </c>
+      <c r="V14" s="33"/>
+      <c r="W14" s="33"/>
+      <c r="X14" s="40" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="100.8" spans="1:24">
+      <c r="A15" s="19"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="32" t="s">
+        <v>375</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="E15" s="32"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="33" t="s">
+        <v>158</v>
+      </c>
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="42" t="s">
+        <v>172</v>
+      </c>
+      <c r="K15" s="42" t="s">
+        <v>176</v>
+      </c>
+      <c r="L15" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="M15" s="39"/>
+      <c r="N15" s="39"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="33" t="s">
+        <v>377</v>
+      </c>
+      <c r="V15" s="33"/>
+      <c r="W15" s="33"/>
+      <c r="X15" s="40" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="16" s="13" customFormat="1" ht="101.55" spans="1:24">
+      <c r="A16" s="19"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="32" t="s">
+        <v>378</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="E16" s="32"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="37"/>
+    </row>
+    <row r="17" s="12" customFormat="1" ht="100.8" spans="1:24">
+      <c r="A17" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B17" s="41" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>380</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="E17" s="32"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="33" t="s">
+        <v>298</v>
+      </c>
+      <c r="V17" s="33"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="37"/>
+    </row>
+    <row r="18" customFormat="1" ht="115.2" spans="1:24">
+      <c r="A18" s="19"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="32" t="s">
+        <v>382</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="E18" s="32"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="M18" s="39"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="V18" s="33"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="37"/>
+    </row>
+    <row r="19" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A19" s="19"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="32" t="s">
+        <v>384</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="E19" s="32"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="M19" s="39"/>
+      <c r="N19" s="39"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="33" t="s">
+        <v>300</v>
+      </c>
+      <c r="V19" s="33"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="37"/>
+    </row>
+    <row r="20" customFormat="1" ht="57.6" spans="1:24">
+      <c r="A20" s="19"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="32" t="s">
+        <v>386</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E20" s="32"/>
+      <c r="F20" s="38"/>
+      <c r="G20" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="M20" s="39"/>
+      <c r="N20" s="39"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="V20" s="33"/>
+      <c r="W20" s="33"/>
+      <c r="X20" s="37"/>
+    </row>
+    <row r="21" customFormat="1" ht="158.4" spans="1:24">
+      <c r="A21" s="19"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="32" t="s">
+        <v>388</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="E21" s="32"/>
+      <c r="F21" s="38"/>
+      <c r="G21" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="33" t="s">
+        <v>302</v>
+      </c>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="37"/>
+    </row>
+    <row r="22" s="13" customFormat="1" ht="115.95" spans="1:24">
+      <c r="A22" s="19"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="32" t="s">
+        <v>390</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="E22" s="32"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="33" t="s">
+        <v>303</v>
+      </c>
+      <c r="V22" s="33"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="37"/>
+    </row>
+    <row r="23" s="12" customFormat="1" ht="100.8" spans="1:24">
+      <c r="A23" s="19" t="s">
+        <v>3</v>
+      </c>
+      <c r="B23" s="41" t="s">
+        <v>392</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>393</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="E23" s="32"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="33" t="s">
+        <v>304</v>
+      </c>
+      <c r="V23" s="33"/>
+      <c r="W23" s="33"/>
+      <c r="X23" s="37"/>
+    </row>
+    <row r="24" customFormat="1" ht="76" customHeight="1" spans="1:24">
+      <c r="A24" s="19"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="32" t="s">
+        <v>395</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="E24" s="32"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="M24" s="39"/>
+      <c r="N24" s="39"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="33" t="s">
+        <v>305</v>
+      </c>
+      <c r="V24" s="33"/>
+      <c r="W24" s="33"/>
+      <c r="X24" s="37"/>
+    </row>
+    <row r="25" customFormat="1" ht="100.8" spans="1:24">
+      <c r="A25" s="19"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="32" t="s">
+        <v>397</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="E25" s="32"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q25" s="35"/>
+      <c r="R25" s="35"/>
+      <c r="S25" s="35"/>
+      <c r="T25" s="35"/>
+      <c r="U25" s="33" t="s">
+        <v>306</v>
+      </c>
+      <c r="V25" s="33"/>
+      <c r="W25" s="33"/>
+      <c r="X25" s="37"/>
+    </row>
+    <row r="26" s="13" customFormat="1" ht="115.95" spans="1:24">
+      <c r="A26" s="19"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="32" t="s">
+        <v>399</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E26" s="32"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="35"/>
+      <c r="T26" s="35"/>
+      <c r="U26" s="33" t="s">
+        <v>401</v>
+      </c>
+      <c r="V26" s="33"/>
+      <c r="W26" s="33"/>
+      <c r="X26" s="37"/>
+    </row>
+    <row r="27" s="12" customFormat="1" ht="72" spans="1:24">
+      <c r="A27" s="19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="41" t="s">
+        <v>402</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>403</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="E27" s="32"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="P27" s="35" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q27" s="35" t="s">
+        <v>259</v>
+      </c>
+      <c r="R27" s="35"/>
+      <c r="S27" s="35"/>
+      <c r="T27" s="35"/>
+      <c r="U27" s="33" t="s">
+        <v>308</v>
+      </c>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="37"/>
+    </row>
+    <row r="28" customFormat="1" ht="216" spans="1:24">
+      <c r="A28" s="19"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="32" t="s">
+        <v>405</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="E28" s="32"/>
+      <c r="F28" s="38"/>
+      <c r="G28" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="42" t="s">
+        <v>177</v>
+      </c>
+      <c r="L28" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="M28" s="39"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="P28" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q28" s="35" t="s">
+        <v>260</v>
+      </c>
+      <c r="R28" s="35"/>
+      <c r="S28" s="35"/>
+      <c r="T28" s="35"/>
+      <c r="U28" s="33" t="s">
+        <v>309</v>
+      </c>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="37"/>
+    </row>
+    <row r="29" s="13" customFormat="1" ht="144.75" spans="1:24">
+      <c r="A29" s="19"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="32" t="s">
+        <v>407</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="E29" s="32"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="M29" s="39"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="35" t="s">
+        <v>224</v>
+      </c>
+      <c r="P29" s="35" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q29" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="R29" s="35"/>
+      <c r="S29" s="35"/>
+      <c r="T29" s="35"/>
+      <c r="U29" s="33" t="s">
+        <v>310</v>
+      </c>
+      <c r="V29" s="33"/>
+      <c r="W29" s="33"/>
+      <c r="X29" s="37"/>
+    </row>
+    <row r="30" s="12" customFormat="1" ht="187.2" spans="1:24">
+      <c r="A30" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="B30" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>409</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="E30" s="32"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="M30" s="39"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="35" t="s">
+        <v>262</v>
+      </c>
+      <c r="R30" s="35"/>
+      <c r="S30" s="35"/>
+      <c r="T30" s="35"/>
+      <c r="U30" s="33" t="s">
+        <v>311</v>
+      </c>
+      <c r="V30" s="33"/>
+      <c r="W30" s="33"/>
+      <c r="X30" s="37"/>
+    </row>
+    <row r="31" customFormat="1" ht="172.8" spans="1:24">
+      <c r="A31" s="19"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="32" t="s">
+        <v>411</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E31" s="32"/>
+      <c r="F31" s="38"/>
+      <c r="G31" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="M31" s="39"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="33" t="s">
+        <v>312</v>
+      </c>
+      <c r="V31" s="33"/>
+      <c r="W31" s="33"/>
+      <c r="X31" s="37"/>
+    </row>
+    <row r="32" customFormat="1" ht="201.6" spans="1:24">
+      <c r="A32" s="19"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="32" t="s">
+        <v>413</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="E32" s="32"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="M32" s="39"/>
+      <c r="N32" s="39"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
+      <c r="R32" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="S32" s="35"/>
+      <c r="T32" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="U32" s="33" t="s">
+        <v>313</v>
+      </c>
+      <c r="V32" s="33"/>
+      <c r="W32" s="33"/>
+      <c r="X32" s="37"/>
+    </row>
+    <row r="33" customFormat="1" ht="216" spans="1:24">
+      <c r="A33" s="19"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="32" t="s">
+        <v>415</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="E33" s="32"/>
+      <c r="F33" s="38"/>
+      <c r="G33" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="M33" s="39"/>
+      <c r="N33" s="39"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="35"/>
+      <c r="R33" s="35"/>
+      <c r="S33" s="35"/>
+      <c r="T33" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="U33" s="33" t="s">
+        <v>314</v>
+      </c>
+      <c r="V33" s="33"/>
+      <c r="W33" s="33"/>
+      <c r="X33" s="37"/>
+    </row>
+    <row r="34" customFormat="1" ht="172.8" spans="1:24">
+      <c r="A34" s="19"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="32" t="s">
+        <v>417</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="E34" s="32"/>
+      <c r="F34" s="38"/>
+      <c r="G34" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="39"/>
+      <c r="N34" s="39"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="35"/>
+      <c r="R34" s="35"/>
+      <c r="S34" s="35"/>
+      <c r="T34" s="35" t="s">
+        <v>279</v>
+      </c>
+      <c r="U34" s="43" t="s">
+        <v>315</v>
+      </c>
+      <c r="V34" s="43"/>
+      <c r="W34" s="43"/>
+      <c r="X34" s="44"/>
+    </row>
+    <row r="35" s="13" customFormat="1" ht="259.95" spans="1:24">
+      <c r="A35" s="19"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="32" t="s">
+        <v>419</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E35" s="32"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="39" t="s">
+        <v>205</v>
+      </c>
+      <c r="M35" s="39"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35" t="s">
+        <v>244</v>
+      </c>
+      <c r="Q35" s="35"/>
+      <c r="R35" s="35"/>
+      <c r="S35" s="35"/>
+      <c r="T35" s="35"/>
+      <c r="U35" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="V35" s="33"/>
+      <c r="W35" s="33"/>
+      <c r="X35" s="37"/>
+    </row>
+    <row r="36" s="12" customFormat="1" ht="288" spans="1:24">
+      <c r="A36" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B36" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="E36" s="32"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="39" t="s">
+        <v>423</v>
+      </c>
+      <c r="M36" s="39"/>
+      <c r="N36" s="39"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="35" t="s">
+        <v>263</v>
+      </c>
+      <c r="R36" s="35"/>
+      <c r="S36" s="35"/>
+      <c r="T36" s="35" t="s">
+        <v>280</v>
+      </c>
+      <c r="U36" s="33" t="s">
+        <v>316</v>
+      </c>
+      <c r="V36" s="33"/>
+      <c r="W36" s="33"/>
+      <c r="X36" s="37"/>
+    </row>
+    <row r="37" customFormat="1" ht="187.2" spans="1:24">
+      <c r="A37" s="19"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="32" t="s">
+        <v>424</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="E37" s="32"/>
+      <c r="F37" s="38"/>
+      <c r="G37" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="42" t="s">
+        <v>178</v>
+      </c>
+      <c r="L37" s="39" t="s">
+        <v>207</v>
+      </c>
+      <c r="M37" s="39"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="35"/>
+      <c r="P37" s="35"/>
+      <c r="Q37" s="35"/>
+      <c r="R37" s="35"/>
+      <c r="S37" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="T37" s="35" t="s">
+        <v>281</v>
+      </c>
+      <c r="U37" s="33" t="s">
+        <v>317</v>
+      </c>
+      <c r="V37" s="33"/>
+      <c r="W37" s="33"/>
+      <c r="X37" s="37"/>
+    </row>
+    <row r="38" s="13" customFormat="1" ht="159.15" spans="1:24">
+      <c r="A38" s="19"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="32" t="s">
+        <v>426</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="E38" s="32"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
+      <c r="L38" s="39"/>
+      <c r="M38" s="39"/>
+      <c r="N38" s="39"/>
+      <c r="O38" s="35"/>
+      <c r="P38" s="35"/>
+      <c r="Q38" s="35" t="s">
+        <v>263</v>
+      </c>
+      <c r="R38" s="35"/>
+      <c r="S38" s="35"/>
+      <c r="T38" s="35"/>
+      <c r="U38" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="V38" s="33"/>
+      <c r="W38" s="33"/>
+      <c r="X38" s="37"/>
+    </row>
+    <row r="39" s="12" customFormat="1" ht="201.6" spans="1:24">
+      <c r="A39" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="41" t="s">
+        <v>428</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>429</v>
+      </c>
+      <c r="D39" s="32" t="s">
+        <v>430</v>
+      </c>
+      <c r="E39" s="32"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="35"/>
+      <c r="P39" s="35" t="s">
+        <v>245</v>
+      </c>
+      <c r="Q39" s="35"/>
+      <c r="R39" s="35"/>
+      <c r="S39" s="35"/>
+      <c r="T39" s="35"/>
+      <c r="U39" s="33" t="s">
+        <v>318</v>
+      </c>
+      <c r="V39" s="33"/>
+      <c r="W39" s="33"/>
+      <c r="X39" s="37"/>
+    </row>
+    <row r="40" customFormat="1" ht="259.2" spans="1:24">
+      <c r="A40" s="19"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="32" t="s">
+        <v>431</v>
+      </c>
+      <c r="D40" s="32" t="s">
+        <v>432</v>
+      </c>
+      <c r="E40" s="32"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="33"/>
+      <c r="L40" s="39" t="s">
+        <v>208</v>
+      </c>
+      <c r="M40" s="39"/>
+      <c r="N40" s="39"/>
+      <c r="O40" s="35" t="s">
+        <v>225</v>
+      </c>
+      <c r="P40" s="35" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q40" s="35"/>
+      <c r="R40" s="35"/>
+      <c r="S40" s="35"/>
+      <c r="T40" s="35"/>
+      <c r="U40" s="33" t="s">
+        <v>319</v>
+      </c>
+      <c r="V40" s="33"/>
+      <c r="W40" s="33"/>
+      <c r="X40" s="37"/>
+    </row>
+    <row r="41" customFormat="1" ht="216" spans="1:24">
+      <c r="A41" s="19"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="32" t="s">
+        <v>433</v>
+      </c>
+      <c r="D41" s="32" t="s">
+        <v>434</v>
+      </c>
+      <c r="E41" s="32"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
+      <c r="L41" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="M41" s="39"/>
+      <c r="N41" s="39"/>
+      <c r="O41" s="35"/>
+      <c r="P41" s="35" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q41" s="35" t="s">
+        <v>264</v>
+      </c>
+      <c r="R41" s="35"/>
+      <c r="S41" s="35"/>
+      <c r="T41" s="35"/>
+      <c r="U41" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="V41" s="33"/>
+      <c r="W41" s="33"/>
+      <c r="X41" s="37"/>
+    </row>
+    <row r="42" customFormat="1" ht="230.4" spans="1:24">
+      <c r="A42" s="19"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="32" t="s">
+        <v>435</v>
+      </c>
+      <c r="D42" s="32" t="s">
+        <v>436</v>
+      </c>
+      <c r="E42" s="32"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="39" t="s">
+        <v>210</v>
+      </c>
+      <c r="M42" s="39"/>
+      <c r="N42" s="39"/>
+      <c r="O42" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="P42" s="35" t="s">
+        <v>248</v>
+      </c>
+      <c r="Q42" s="35"/>
+      <c r="R42" s="35"/>
+      <c r="S42" s="35"/>
+      <c r="T42" s="35" t="s">
+        <v>276</v>
+      </c>
+      <c r="U42" s="43" t="s">
+        <v>155</v>
+      </c>
+      <c r="V42" s="43"/>
+      <c r="W42" s="43"/>
+      <c r="X42" s="40" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="43" customFormat="1" ht="273.6" spans="1:24">
+      <c r="A43" s="19"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="32" t="s">
+        <v>437</v>
+      </c>
+      <c r="D43" s="32" t="s">
+        <v>438</v>
+      </c>
+      <c r="E43" s="32"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
+      <c r="J43" s="33"/>
+      <c r="K43" s="33"/>
+      <c r="L43" s="39" t="s">
+        <v>211</v>
+      </c>
+      <c r="M43" s="39"/>
+      <c r="N43" s="39"/>
+      <c r="O43" s="35" t="s">
+        <v>226</v>
+      </c>
+      <c r="P43" s="35" t="s">
+        <v>249</v>
+      </c>
+      <c r="Q43" s="35"/>
+      <c r="R43" s="35" t="s">
+        <v>269</v>
+      </c>
+      <c r="S43" s="35"/>
+      <c r="T43" s="35" t="s">
+        <v>276</v>
+      </c>
+      <c r="U43" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="V43" s="33"/>
+      <c r="W43" s="33"/>
+      <c r="X43" s="40" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="44" customFormat="1" ht="216" spans="1:24">
+      <c r="A44" s="19"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="32" t="s">
+        <v>439</v>
+      </c>
+      <c r="D44" s="32" t="s">
+        <v>440</v>
+      </c>
+      <c r="E44" s="32"/>
+      <c r="F44" s="38"/>
+      <c r="G44" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H44" s="33"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="33"/>
+      <c r="L44" s="39"/>
+      <c r="M44" s="39"/>
+      <c r="N44" s="39"/>
+      <c r="O44" s="35"/>
+      <c r="P44" s="35"/>
+      <c r="Q44" s="35"/>
+      <c r="R44" s="35"/>
+      <c r="S44" s="35"/>
+      <c r="T44" s="35"/>
+      <c r="U44" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="V44" s="33"/>
+      <c r="W44" s="33"/>
+      <c r="X44" s="37"/>
+    </row>
+    <row r="45" s="13" customFormat="1" ht="245.55" spans="1:24">
+      <c r="A45" s="19"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="32" t="s">
+        <v>441</v>
+      </c>
+      <c r="D45" s="32" t="s">
+        <v>442</v>
+      </c>
+      <c r="E45" s="32"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="H45" s="33"/>
+      <c r="I45" s="33"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
+      <c r="L45" s="39" t="s">
+        <v>212</v>
+      </c>
+      <c r="M45" s="39"/>
+      <c r="N45" s="39"/>
+      <c r="O45" s="35"/>
+      <c r="P45" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q45" s="35"/>
+      <c r="R45" s="35"/>
+      <c r="S45" s="35"/>
+      <c r="T45" s="35"/>
+      <c r="U45" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="V45" s="33"/>
+      <c r="W45" s="33"/>
+      <c r="X45" s="37"/>
+    </row>
+    <row r="46" s="12" customFormat="1" ht="230.4" spans="1:24">
+      <c r="A46" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="B46" s="41" t="s">
+        <v>18</v>
+      </c>
+      <c r="C46" s="32" t="s">
+        <v>443</v>
+      </c>
+      <c r="D46" s="32" t="s">
+        <v>444</v>
+      </c>
+      <c r="E46" s="32"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="33" t="s">
+        <v>166</v>
+      </c>
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="39" t="s">
+        <v>213</v>
+      </c>
+      <c r="M46" s="39"/>
+      <c r="N46" s="39"/>
+      <c r="O46" s="35" t="s">
+        <v>227</v>
+      </c>
+      <c r="P46" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q46" s="35"/>
+      <c r="R46" s="35"/>
+      <c r="S46" s="35"/>
+      <c r="T46" s="35"/>
+      <c r="U46" s="33" t="s">
+        <v>320</v>
+      </c>
+      <c r="V46" s="33"/>
+      <c r="W46" s="33"/>
+      <c r="X46" s="37"/>
+    </row>
+    <row r="47" customFormat="1" ht="144" spans="1:24">
+      <c r="A47" s="19"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="32" t="s">
+        <v>445</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>446</v>
+      </c>
+      <c r="E47" s="32"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="H47" s="33"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="39" t="s">
+        <v>214</v>
+      </c>
+      <c r="M47" s="39"/>
+      <c r="N47" s="39"/>
+      <c r="O47" s="35"/>
+      <c r="P47" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="Q47" s="35"/>
+      <c r="R47" s="35"/>
+      <c r="S47" s="35"/>
+      <c r="T47" s="35" t="s">
+        <v>277</v>
+      </c>
+      <c r="U47" s="33" t="s">
+        <v>321</v>
+      </c>
+      <c r="V47" s="33"/>
+      <c r="W47" s="33"/>
+      <c r="X47" s="37"/>
+    </row>
+    <row r="48" s="13" customFormat="1" ht="173.55" spans="1:24">
+      <c r="A48" s="19"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="32" t="s">
+        <v>447</v>
+      </c>
+      <c r="D48" s="32" t="s">
+        <v>448</v>
+      </c>
+      <c r="E48" s="32"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="H48" s="33"/>
+      <c r="I48" s="33"/>
+      <c r="J48" s="33"/>
+      <c r="K48" s="33"/>
+      <c r="L48" s="39" t="s">
+        <v>215</v>
+      </c>
+      <c r="M48" s="39"/>
+      <c r="N48" s="39"/>
+      <c r="O48" s="35"/>
+      <c r="P48" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q48" s="35"/>
+      <c r="R48" s="35"/>
+      <c r="S48" s="35"/>
+      <c r="T48" s="35"/>
+      <c r="U48" s="33" t="s">
+        <v>322</v>
+      </c>
+      <c r="V48" s="33"/>
+      <c r="W48" s="33"/>
+      <c r="X48" s="37"/>
+    </row>
+    <row r="49" s="12" customFormat="1" ht="230.4" spans="1:24">
+      <c r="A49" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" s="41" t="s">
+        <v>19</v>
+      </c>
+      <c r="C49" s="32" t="s">
+        <v>449</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="E49" s="32"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="H49" s="33"/>
+      <c r="I49" s="33"/>
+      <c r="J49" s="33"/>
+      <c r="K49" s="33"/>
+      <c r="L49" s="39"/>
+      <c r="M49" s="39"/>
+      <c r="N49" s="39"/>
+      <c r="O49" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="P49" s="35" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q49" s="35" t="s">
+        <v>265</v>
+      </c>
+      <c r="R49" s="35"/>
+      <c r="S49" s="35"/>
+      <c r="T49" s="35"/>
+      <c r="U49" s="33" t="s">
+        <v>323</v>
+      </c>
+      <c r="V49" s="33"/>
+      <c r="W49" s="33"/>
+      <c r="X49" s="37"/>
+    </row>
+    <row r="50" customFormat="1" ht="187.2" spans="1:24">
+      <c r="A50" s="19"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="32" t="s">
+        <v>451</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="E50" s="32"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="33" t="s">
+        <v>159</v>
+      </c>
+      <c r="H50" s="33"/>
+      <c r="I50" s="33"/>
+      <c r="J50" s="33"/>
+      <c r="K50" s="33"/>
+      <c r="L50" s="39"/>
+      <c r="M50" s="39"/>
+      <c r="N50" s="39"/>
+      <c r="O50" s="35"/>
+      <c r="P50" s="35" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q50" s="35" t="s">
+        <v>266</v>
+      </c>
+      <c r="R50" s="35"/>
+      <c r="S50" s="35"/>
+      <c r="T50" s="35"/>
+      <c r="U50" s="33" t="s">
+        <v>324</v>
+      </c>
+      <c r="V50" s="33"/>
+      <c r="W50" s="33"/>
+      <c r="X50" s="37"/>
+    </row>
+    <row r="51" customFormat="1" ht="216" spans="1:24">
+      <c r="A51" s="19"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="32" t="s">
+        <v>453</v>
+      </c>
+      <c r="D51" s="32" t="s">
+        <v>454</v>
+      </c>
+      <c r="E51" s="32"/>
+      <c r="F51" s="38"/>
+      <c r="G51" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="H51" s="33"/>
+      <c r="I51" s="33"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="39" t="s">
+        <v>455</v>
+      </c>
+      <c r="M51" s="39"/>
+      <c r="N51" s="39"/>
+      <c r="O51" s="35"/>
+      <c r="P51" s="35"/>
+      <c r="Q51" s="35"/>
+      <c r="R51" s="35"/>
+      <c r="S51" s="35"/>
+      <c r="T51" s="35" t="s">
+        <v>282</v>
+      </c>
+      <c r="U51" s="33" t="s">
+        <v>315</v>
+      </c>
+      <c r="V51" s="33"/>
+      <c r="W51" s="33"/>
+      <c r="X51" s="37"/>
+    </row>
+    <row r="52" s="13" customFormat="1" ht="274.35" spans="1:24">
+      <c r="A52" s="45"/>
+      <c r="B52" s="46"/>
+      <c r="C52" s="47" t="s">
+        <v>456</v>
+      </c>
+      <c r="D52" s="47" t="s">
+        <v>457</v>
+      </c>
+      <c r="E52" s="47"/>
+      <c r="F52" s="48"/>
+      <c r="G52" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="H52" s="49"/>
+      <c r="I52" s="49"/>
+      <c r="J52" s="49"/>
+      <c r="K52" s="49"/>
+      <c r="L52" s="50"/>
+      <c r="M52" s="50"/>
+      <c r="N52" s="50"/>
+      <c r="O52" s="51"/>
+      <c r="P52" s="51" t="s">
+        <v>256</v>
+      </c>
+      <c r="Q52" s="51" t="s">
+        <v>263</v>
+      </c>
+      <c r="R52" s="51" t="s">
+        <v>270</v>
+      </c>
+      <c r="S52" s="51"/>
+      <c r="T52" s="51" t="s">
+        <v>283</v>
+      </c>
+      <c r="U52" s="49" t="s">
+        <v>155</v>
+      </c>
+      <c r="V52" s="49"/>
+      <c r="W52" s="49"/>
+      <c r="X52" s="52"/>
+    </row>
+  </sheetData>
+  <mergeCells count="179">
+    <mergeCell ref="G1:K1"/>
+    <mergeCell ref="L1:T1"/>
+    <mergeCell ref="U1:X1"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:T2"/>
+    <mergeCell ref="V2:X2"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="U4:X4"/>
+    <mergeCell ref="G5:K5"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="U5:X5"/>
+    <mergeCell ref="G6:K6"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="U6:X6"/>
+    <mergeCell ref="G7:K7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="U7:X7"/>
+    <mergeCell ref="G8:K8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="U8:W8"/>
+    <mergeCell ref="G9:K9"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="U9:X9"/>
+    <mergeCell ref="G10:K10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="U10:X10"/>
+    <mergeCell ref="G11:K11"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="U11:X11"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="U12:X12"/>
+    <mergeCell ref="G13:J13"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="U13:X13"/>
+    <mergeCell ref="G14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="U14:W14"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="U15:W15"/>
+    <mergeCell ref="G16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="U16:X16"/>
+    <mergeCell ref="G17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="U17:X17"/>
+    <mergeCell ref="G18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="U18:X18"/>
+    <mergeCell ref="G19:K19"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="U19:X19"/>
+    <mergeCell ref="G20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="U20:X20"/>
+    <mergeCell ref="G21:K21"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="U21:X21"/>
+    <mergeCell ref="G22:K22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="U22:X22"/>
+    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="U23:X23"/>
+    <mergeCell ref="G24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="U24:X24"/>
+    <mergeCell ref="G25:K25"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="U25:X25"/>
+    <mergeCell ref="G26:K26"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="G27:K27"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="U27:X27"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="U28:X28"/>
+    <mergeCell ref="G29:K29"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="U29:X29"/>
+    <mergeCell ref="G30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="U30:X30"/>
+    <mergeCell ref="G31:K31"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="U31:X31"/>
+    <mergeCell ref="G32:K32"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="U32:X32"/>
+    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="G34:K34"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="U34:X34"/>
+    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="U35:X35"/>
+    <mergeCell ref="G36:K36"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="U36:X36"/>
+    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="U37:X37"/>
+    <mergeCell ref="G38:K38"/>
+    <mergeCell ref="L38:N38"/>
+    <mergeCell ref="U38:X38"/>
+    <mergeCell ref="G39:K39"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="U39:X39"/>
+    <mergeCell ref="G40:K40"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="U40:X40"/>
+    <mergeCell ref="G41:K41"/>
+    <mergeCell ref="L41:N41"/>
+    <mergeCell ref="U41:X41"/>
+    <mergeCell ref="G42:K42"/>
+    <mergeCell ref="L42:N42"/>
+    <mergeCell ref="U42:W42"/>
+    <mergeCell ref="G43:K43"/>
+    <mergeCell ref="L43:N43"/>
+    <mergeCell ref="U43:W43"/>
+    <mergeCell ref="G44:K44"/>
+    <mergeCell ref="L44:N44"/>
+    <mergeCell ref="U44:X44"/>
+    <mergeCell ref="G45:K45"/>
+    <mergeCell ref="L45:N45"/>
+    <mergeCell ref="U45:X45"/>
+    <mergeCell ref="G46:K46"/>
+    <mergeCell ref="L46:N46"/>
+    <mergeCell ref="U46:X46"/>
+    <mergeCell ref="G47:K47"/>
+    <mergeCell ref="L47:N47"/>
+    <mergeCell ref="U47:X47"/>
+    <mergeCell ref="G48:K48"/>
+    <mergeCell ref="L48:N48"/>
+    <mergeCell ref="U48:X48"/>
+    <mergeCell ref="G49:K49"/>
+    <mergeCell ref="L49:N49"/>
+    <mergeCell ref="U49:X49"/>
+    <mergeCell ref="G50:K50"/>
+    <mergeCell ref="L50:N50"/>
+    <mergeCell ref="U50:X50"/>
+    <mergeCell ref="G51:K51"/>
+    <mergeCell ref="L51:N51"/>
+    <mergeCell ref="U51:X51"/>
+    <mergeCell ref="G52:K52"/>
+    <mergeCell ref="L52:N52"/>
+    <mergeCell ref="U52:X52"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A11:A16"/>
+    <mergeCell ref="A17:A22"/>
+    <mergeCell ref="A23:A26"/>
+    <mergeCell ref="A27:A29"/>
+    <mergeCell ref="A30:A35"/>
+    <mergeCell ref="A36:A38"/>
+    <mergeCell ref="A39:A45"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="A49:A52"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="B4:B10"/>
+    <mergeCell ref="B11:B16"/>
+    <mergeCell ref="B17:B22"/>
+    <mergeCell ref="B23:B26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B30:B35"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="B39:B45"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="B49:B52"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
+    <mergeCell ref="F1:F3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -7400,9 +10909,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -7410,17 +10920,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="39.875" customWidth="1"/>
+    <col min="2" max="2" width="39.8796296296296" customWidth="1"/>
     <col min="3" max="3" width="63.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
-        <v>334</v>
+        <v>458</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="8"/>
@@ -7428,31 +10949,31 @@
     <row r="2" spans="1:3">
       <c r="A2" s="9"/>
       <c r="B2" s="10" t="s">
-        <v>335</v>
+        <v>459</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>336</v>
+        <v>460</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="11"/>
       <c r="B3" s="10"/>
       <c r="C3" s="3" t="s">
-        <v>337</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="11"/>
       <c r="B4" s="10"/>
       <c r="C4" s="3" t="s">
-        <v>338</v>
+        <v>462</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="11"/>
       <c r="B5" s="10"/>
       <c r="C5" s="3" t="s">
-        <v>339</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -7463,31 +10984,31 @@
     <row r="7" spans="1:3">
       <c r="A7" s="11"/>
       <c r="B7" s="10" t="s">
-        <v>340</v>
+        <v>464</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>341</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="11"/>
       <c r="B8" s="10"/>
       <c r="C8" s="3" t="s">
-        <v>342</v>
+        <v>466</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="11"/>
       <c r="B9" s="10"/>
       <c r="C9" s="3" t="s">
-        <v>343</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="11"/>
       <c r="B10" s="10"/>
       <c r="C10" s="3" t="s">
-        <v>344</v>
+        <v>468</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -7498,38 +11019,38 @@
     <row r="12" spans="1:3">
       <c r="A12" s="11"/>
       <c r="B12" s="10" t="s">
-        <v>345</v>
+        <v>469</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>346</v>
+        <v>470</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="11"/>
       <c r="B13" s="10"/>
       <c r="C13" s="3" t="s">
-        <v>347</v>
+        <v>471</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="11"/>
       <c r="B14" s="10"/>
       <c r="C14" s="3" t="s">
-        <v>348</v>
+        <v>472</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="11"/>
       <c r="B15" s="10"/>
       <c r="C15" s="3" t="s">
-        <v>349</v>
+        <v>473</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="11"/>
       <c r="B16" s="10"/>
       <c r="C16" s="3" t="s">
-        <v>350</v>
+        <v>474</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -7540,31 +11061,31 @@
     <row r="18" spans="1:3">
       <c r="A18" s="11"/>
       <c r="B18" s="10" t="s">
-        <v>351</v>
+        <v>475</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>352</v>
+        <v>476</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="11"/>
       <c r="B19" s="10"/>
       <c r="C19" s="2" t="s">
-        <v>353</v>
+        <v>477</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="11"/>
       <c r="B20" s="10"/>
       <c r="C20" s="2" t="s">
-        <v>354</v>
+        <v>478</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="11"/>
       <c r="B21" s="10"/>
       <c r="C21" s="2" t="s">
-        <v>355</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>
@@ -7580,151 +11101,151 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="21.25" customWidth="1"/>
-    <col min="4" max="4" width="77.125" customWidth="1"/>
+    <col min="4" max="4" width="77.1296296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>356</v>
+        <v>480</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>357</v>
+        <v>481</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>358</v>
+        <v>482</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>359</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="2" t="s">
-        <v>360</v>
+        <v>484</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>361</v>
+        <v>485</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="2" t="s">
-        <v>362</v>
+        <v>486</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>363</v>
+        <v>487</v>
       </c>
     </row>
-    <row r="4" ht="94.5" spans="1:4">
+    <row r="4" ht="100.8" spans="1:4">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="3" t="s">
-        <v>364</v>
+        <v>488</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>365</v>
+        <v>489</v>
       </c>
     </row>
-    <row r="5" ht="27" spans="1:4">
+    <row r="5" ht="28.8" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>366</v>
+        <v>490</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>367</v>
+        <v>491</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
-        <v>368</v>
+        <v>492</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>369</v>
+        <v>493</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>370</v>
+        <v>494</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>371</v>
+        <v>495</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
-        <v>372</v>
+        <v>496</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>373</v>
+        <v>497</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>374</v>
+        <v>498</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>375</v>
+        <v>499</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="4" t="s">
-        <v>334</v>
+        <v>458</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>376</v>
+        <v>500</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>377</v>
+        <v>501</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>378</v>
+        <v>502</v>
       </c>
     </row>
-    <row r="9" ht="27" spans="1:4">
+    <row r="9" ht="28.8" spans="1:4">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="2" t="s">
-        <v>379</v>
+        <v>503</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>380</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="5"/>
       <c r="B10" s="5"/>
       <c r="C10" s="2" t="s">
-        <v>381</v>
+        <v>505</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>382</v>
+        <v>506</v>
       </c>
     </row>
-    <row r="11" ht="40.5" spans="1:4">
+    <row r="11" ht="43.2" spans="1:4">
       <c r="A11" s="5"/>
       <c r="B11" s="5"/>
       <c r="C11" s="2" t="s">
-        <v>383</v>
+        <v>507</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>384</v>
+        <v>508</v>
       </c>
     </row>
-    <row r="12" ht="27" spans="1:4">
+    <row r="12" ht="28.8" spans="1:4">
       <c r="A12" s="6"/>
       <c r="B12" s="6"/>
       <c r="C12" s="2" t="s">
-        <v>385</v>
+        <v>509</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>386</v>
+        <v>510</v>
       </c>
     </row>
   </sheetData>
@@ -7739,22 +11260,22 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -4059,81 +4059,72 @@
     <t>管理质量（执行过程组）</t>
   </si>
   <si>
-    <t>1使用质量控制数据结果，向干系人展示项目的质量状态
-把质量政策用于项目，将质量管理计划转化质量活动，提高实现质量目标的可能性，识别无效过程和导致质量低劣的原因，</t>
+    <t>1将质量管理计划转化质量活动
+2把质量政策用于项目
+3使用质量控制数据结果，向干系人展示项目的质量状态
+4提高实现质量目标的可能性
+5识别无效过程和导致质量低劣的原因</t>
   </si>
   <si>
     <t>控制质量（监控过程组）</t>
   </si>
   <si>
-    <t>监督和记录质量管理活动执行结果，确保项目输出满足规范标准要求和客户期望，核实项目可交付成果满足最终验收质量要求</t>
+    <t>1核实项目可交付成果满足最终验收质量要求
+2监督和记录质量管理活动执行结果
+3确保项目输出满足规范标准要求和客户期望</t>
   </si>
   <si>
     <t>规划资源管理（规划过程组）</t>
   </si>
   <si>
-    <t>定义：
-  是定义如何估算、获取、管理和利用团队及其实物资源的过程
-作用：
-  根据项目类型和复杂程度确定适用于项目资源的管理方法和管理程度</t>
+    <t>1确定适用于项目资源的管理方法和管理程度
+2估算、获取、管理和利用团队及其实物资源</t>
   </si>
   <si>
     <t>估算活动资源（规划过程组）</t>
   </si>
   <si>
-    <t>定义：
-  是估算执行项目所需的团队资源，以及材料、设备和用品的类型和数量的过程
-作用：
-  明确完成项目所需的资源种类、数量和特性</t>
+    <t>1明确完成项目所需的资源种类、数量和特性
+2估算执行项目所需的团队资源和实物资源如：材料、设备的类型和数量</t>
   </si>
   <si>
     <t>获取资源（执行过程组）</t>
   </si>
   <si>
-    <t>定义：
-  是获取项目所需的团队成员、设施、设备、材料、用品和其他资源的过程
-作用：
-  1、概述和指导资源的选择
-  2、将选择的资源分配给相应的活动</t>
+    <t>1概述和指导资源的选择
+2将资源分配给相应的活动
+3获取项目所需的团队资源和实物资源</t>
   </si>
   <si>
     <t>建设团队（执行过程组）</t>
   </si>
   <si>
-    <t>定义：
-  是提高工作能力，促进团队成员互动，改善团队整体氛围，以提高项目绩效的过程
-作用：
-  改进团队协作、增强人际关系技能、激励员工，减少摩擦以及提升整体项目绩效</t>
+    <t>1改进团队协作、人际关系、激励员工，减少摩擦、提升项目绩效
+2提高工作能力，促进团队成员互动，改善团队整体氛围，以提高项目绩效的过程</t>
   </si>
   <si>
     <t>管理团队（执行过程组）</t>
   </si>
   <si>
-    <t>定义：
-  是跟踪团队成员工作表现、提供反馈、解决问题并管理团队变更以优化项目绩效的过程
-作用：
-  影响团队行为、管理冲突以及解决问题</t>
+    <t>1影响团队行为、管理冲突、解决问题
+2跟踪团队成员工作表现、提供反馈、解决问题并管理团队变更以优化项目绩效的过程</t>
   </si>
   <si>
     <t>控制资源（监控过程组）</t>
   </si>
   <si>
-    <t>定义：
-  是确保按计划为项目分配实物资源，以及根据资源使用计划监督资源实际使用情况，并采取必要纠正措施的过程
-作用：
-  1、确保所分配的资源适时、适地可用于项目
-  2、资源在不再需要时被释放</t>
+    <t>1确保按计划为项目分配实物资源
+2根据资源使用计划监督资源实际使用情况，并采取纠正措施
+3确保资源适时、适地用于项目
+3资源释放</t>
   </si>
   <si>
     <t>规划沟通管理（规划过程组）</t>
   </si>
   <si>
-    <t>定义：
-  是基于每个干系人或干系人群体的信息需求、可用的组织资产，以及具体项目的需求，为项目沟通活动制定恰当的方法和计划的过程
-作用：
-  1、及时向干系人提供相关信息
-  2、引导干系人有效参与项目
-  3、编制书面沟通计划</t>
+    <t>1基于每个干系人的息需求、组织资产、项目的需求编制书面沟通计划
+2及时向干系人提供信息
+3引导干系人有效参与项目</t>
   </si>
   <si>
     <t>沟通需求分析
@@ -4144,19 +4135,15 @@
     <t>管理沟通（执行过程组）</t>
   </si>
   <si>
-    <t>定义：
-  是确保项目信息及时且恰当的收集、生成、发布、存储、检索、管理、监督和最终处置的过程
-作用：
-  促成项目团队与干系人之间的有效信息流动</t>
+    <t>1促成干系人之间的有效信息流动
+2确保项目信息及时且恰当的收集、生成、发布、存储、检索、管理、监督和最终处置</t>
   </si>
   <si>
     <t>监督沟通（监控过程组）</t>
   </si>
   <si>
-    <t>定义：
-  是确保满足项目及其干系人的信息需求的过程
-作用：
-  按沟通管理计划和干系人参与计划的要求优化信息传递流程</t>
+    <t>1按沟通管理计划和干系人参与计划的要求优化信息传递流程
+2确保满足项目和干系人的信息需求</t>
   </si>
   <si>
     <t>项目内对风险进行规划、识别、分析、管理和控制的过程</t>
@@ -4165,15 +4152,14 @@
     <t>规划风险管理（规划过程组）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
+    <t>1定义如何实施项目风险管理活动
+2确保风险管理的水平、方法和可见度与项目风险程度和对组织干系人重要重读相匹配</t>
+  </si>
+  <si>
+    <t>识别风险（规划过程组）</t>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">定义：
   </t>
     </r>
@@ -4185,39 +4171,10 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </rPr>
-      <t>是定义如何实施项目风险管理活动的过程
-作用：
-  确保风险管理的水平、方法和可见度与项目风险程度相匹配，与对组织和其他干系人的重要程度相匹配</t>
-    </r>
-  </si>
-  <si>
-    <t>识别风险（规划过程组）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>是识别单个项目风险以及整体项目风险的来源，并记录风险特征的过程
 作用：
-  1、记录现有的单个项目风险，以及整体项目风险的来源
-  2、汇总相关信息，以便项目团队能够恰当地应对已识别的风险</t>
+1记录单个项目风险和整体项目风险来源
+2汇总相关信息，以便项目团队能够恰当地应对已识别的风险</t>
     </r>
   </si>
   <si>
@@ -5624,7 +5581,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -5676,9 +5633,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5688,9 +5642,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5739,18 +5690,12 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -5759,6 +5704,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6309,2274 +6257,2274 @@
     <row r="1" spans="1:51">
       <c r="A1" s="11"/>
       <c r="B1" s="11"/>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56" t="s">
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="53"/>
+      <c r="J1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56" t="s">
+      <c r="K1" s="53"/>
+      <c r="L1" s="53"/>
+      <c r="M1" s="53"/>
+      <c r="N1" s="53"/>
+      <c r="O1" s="53"/>
+      <c r="P1" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56" t="s">
+      <c r="Q1" s="53"/>
+      <c r="R1" s="53"/>
+      <c r="S1" s="53"/>
+      <c r="T1" s="53"/>
+      <c r="U1" s="53"/>
+      <c r="V1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56" t="s">
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="53"/>
+      <c r="Z1" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="56"/>
-      <c r="AB1" s="56"/>
-      <c r="AC1" s="56" t="s">
+      <c r="AA1" s="53"/>
+      <c r="AB1" s="53"/>
+      <c r="AC1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="56"/>
-      <c r="AE1" s="56"/>
-      <c r="AF1" s="56"/>
-      <c r="AG1" s="56"/>
-      <c r="AH1" s="56"/>
-      <c r="AI1" s="56" t="s">
+      <c r="AD1" s="53"/>
+      <c r="AE1" s="53"/>
+      <c r="AF1" s="53"/>
+      <c r="AG1" s="53"/>
+      <c r="AH1" s="53"/>
+      <c r="AI1" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="AJ1" s="56"/>
-      <c r="AK1" s="56"/>
-      <c r="AL1" s="56" t="s">
+      <c r="AJ1" s="53"/>
+      <c r="AK1" s="53"/>
+      <c r="AL1" s="53" t="s">
         <v>7</v>
       </c>
-      <c r="AM1" s="56"/>
-      <c r="AN1" s="56"/>
-      <c r="AO1" s="56"/>
-      <c r="AP1" s="56"/>
-      <c r="AQ1" s="56"/>
-      <c r="AR1" s="56"/>
-      <c r="AS1" s="56" t="s">
+      <c r="AM1" s="53"/>
+      <c r="AN1" s="53"/>
+      <c r="AO1" s="53"/>
+      <c r="AP1" s="53"/>
+      <c r="AQ1" s="53"/>
+      <c r="AR1" s="53"/>
+      <c r="AS1" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="AT1" s="56"/>
-      <c r="AU1" s="56"/>
-      <c r="AV1" s="56" t="s">
+      <c r="AT1" s="53"/>
+      <c r="AU1" s="53"/>
+      <c r="AV1" s="53" t="s">
         <v>9</v>
       </c>
-      <c r="AW1" s="56"/>
-      <c r="AX1" s="56"/>
-      <c r="AY1" s="56"/>
+      <c r="AW1" s="53"/>
+      <c r="AX1" s="53"/>
+      <c r="AY1" s="53"/>
     </row>
     <row r="2" customFormat="1" ht="58" customHeight="1" spans="1:51">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="59" t="s">
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="61" t="s">
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
+      <c r="M2" s="57"/>
+      <c r="N2" s="57"/>
+      <c r="O2" s="57"/>
+      <c r="P2" s="58" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="61" t="s">
+      <c r="Q2" s="57"/>
+      <c r="R2" s="57"/>
+      <c r="S2" s="57"/>
+      <c r="T2" s="57"/>
+      <c r="U2" s="59"/>
+      <c r="V2" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="W2" s="60"/>
-      <c r="X2" s="60"/>
-      <c r="Y2" s="62"/>
-      <c r="Z2" s="59" t="s">
+      <c r="W2" s="57"/>
+      <c r="X2" s="57"/>
+      <c r="Y2" s="59"/>
+      <c r="Z2" s="56" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="60"/>
-      <c r="AB2" s="62"/>
-      <c r="AC2" s="61" t="s">
+      <c r="AA2" s="57"/>
+      <c r="AB2" s="59"/>
+      <c r="AC2" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="AD2" s="60"/>
-      <c r="AE2" s="60"/>
-      <c r="AF2" s="60"/>
-      <c r="AG2" s="60"/>
-      <c r="AH2" s="62"/>
-      <c r="AI2" s="61" t="s">
+      <c r="AD2" s="57"/>
+      <c r="AE2" s="57"/>
+      <c r="AF2" s="57"/>
+      <c r="AG2" s="57"/>
+      <c r="AH2" s="59"/>
+      <c r="AI2" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="AJ2" s="60"/>
-      <c r="AK2" s="62"/>
-      <c r="AL2" s="61" t="s">
+      <c r="AJ2" s="57"/>
+      <c r="AK2" s="59"/>
+      <c r="AL2" s="58" t="s">
         <v>17</v>
       </c>
-      <c r="AM2" s="60"/>
-      <c r="AN2" s="60"/>
-      <c r="AO2" s="60"/>
-      <c r="AP2" s="60"/>
-      <c r="AQ2" s="60"/>
-      <c r="AR2" s="62"/>
-      <c r="AS2" s="63" t="s">
+      <c r="AM2" s="57"/>
+      <c r="AN2" s="57"/>
+      <c r="AO2" s="57"/>
+      <c r="AP2" s="57"/>
+      <c r="AQ2" s="57"/>
+      <c r="AR2" s="59"/>
+      <c r="AS2" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="AT2" s="64"/>
-      <c r="AU2" s="65"/>
-      <c r="AV2" s="61" t="s">
+      <c r="AT2" s="61"/>
+      <c r="AU2" s="62"/>
+      <c r="AV2" s="58" t="s">
         <v>19</v>
       </c>
-      <c r="AW2" s="60"/>
-      <c r="AX2" s="60"/>
-      <c r="AY2" s="62"/>
+      <c r="AW2" s="57"/>
+      <c r="AX2" s="57"/>
+      <c r="AY2" s="59"/>
     </row>
-    <row r="3" s="53" customFormat="1" spans="1:51">
-      <c r="A3" s="66"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="67" t="s">
+    <row r="3" s="50" customFormat="1" spans="1:51">
+      <c r="A3" s="63"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="67" t="s">
+      <c r="D3" s="64" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="E3" s="64" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="67" t="s">
+      <c r="F3" s="64" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="67" t="s">
+      <c r="G3" s="64" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="67" t="s">
+      <c r="H3" s="64" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="67" t="s">
+      <c r="I3" s="64" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="68" t="s">
+      <c r="J3" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="68" t="s">
+      <c r="K3" s="65" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="68" t="s">
+      <c r="L3" s="65" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="68" t="s">
+      <c r="M3" s="65" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="68" t="s">
+      <c r="N3" s="65" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="68" t="s">
+      <c r="O3" s="65" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="68" t="s">
+      <c r="P3" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="68" t="s">
+      <c r="Q3" s="65" t="s">
         <v>34</v>
       </c>
-      <c r="R3" s="68" t="s">
+      <c r="R3" s="65" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="68" t="s">
+      <c r="S3" s="65" t="s">
         <v>36</v>
       </c>
-      <c r="T3" s="68" t="s">
+      <c r="T3" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="68" t="s">
+      <c r="U3" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="V3" s="68" t="s">
+      <c r="V3" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="W3" s="68" t="s">
+      <c r="W3" s="65" t="s">
         <v>40</v>
       </c>
-      <c r="X3" s="68" t="s">
+      <c r="X3" s="65" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="68" t="s">
+      <c r="Y3" s="65" t="s">
         <v>42</v>
       </c>
-      <c r="Z3" s="68" t="s">
+      <c r="Z3" s="65" t="s">
         <v>43</v>
       </c>
-      <c r="AA3" s="68" t="s">
+      <c r="AA3" s="65" t="s">
         <v>44</v>
       </c>
-      <c r="AB3" s="68" t="s">
+      <c r="AB3" s="65" t="s">
         <v>45</v>
       </c>
-      <c r="AC3" s="68" t="s">
+      <c r="AC3" s="65" t="s">
         <v>46</v>
       </c>
-      <c r="AD3" s="68" t="s">
+      <c r="AD3" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="AE3" s="68" t="s">
+      <c r="AE3" s="65" t="s">
         <v>48</v>
       </c>
-      <c r="AF3" s="68" t="s">
+      <c r="AF3" s="65" t="s">
         <v>49</v>
       </c>
-      <c r="AG3" s="68" t="s">
+      <c r="AG3" s="65" t="s">
         <v>50</v>
       </c>
-      <c r="AH3" s="68" t="s">
+      <c r="AH3" s="65" t="s">
         <v>51</v>
       </c>
-      <c r="AI3" s="68" t="s">
+      <c r="AI3" s="65" t="s">
         <v>52</v>
       </c>
-      <c r="AJ3" s="68" t="s">
+      <c r="AJ3" s="65" t="s">
         <v>53</v>
       </c>
-      <c r="AK3" s="68" t="s">
+      <c r="AK3" s="65" t="s">
         <v>54</v>
       </c>
-      <c r="AL3" s="68" t="s">
+      <c r="AL3" s="65" t="s">
         <v>55</v>
       </c>
-      <c r="AM3" s="68" t="s">
+      <c r="AM3" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="AN3" s="68" t="s">
+      <c r="AN3" s="65" t="s">
         <v>57</v>
       </c>
-      <c r="AO3" s="68" t="s">
+      <c r="AO3" s="65" t="s">
         <v>58</v>
       </c>
-      <c r="AP3" s="68" t="s">
+      <c r="AP3" s="65" t="s">
         <v>59</v>
       </c>
-      <c r="AQ3" s="68" t="s">
+      <c r="AQ3" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="AR3" s="68" t="s">
+      <c r="AR3" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="AS3" s="67" t="s">
+      <c r="AS3" s="64" t="s">
         <v>62</v>
       </c>
-      <c r="AT3" s="67" t="s">
+      <c r="AT3" s="64" t="s">
         <v>63</v>
       </c>
-      <c r="AU3" s="67" t="s">
+      <c r="AU3" s="64" t="s">
         <v>64</v>
       </c>
-      <c r="AV3" s="67" t="s">
+      <c r="AV3" s="64" t="s">
         <v>65</v>
       </c>
-      <c r="AW3" s="67" t="s">
+      <c r="AW3" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="AX3" s="67" t="s">
+      <c r="AX3" s="64" t="s">
         <v>67</v>
       </c>
-      <c r="AY3" s="67" t="s">
+      <c r="AY3" s="64" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" s="53" customFormat="1" ht="115.2" spans="1:51">
-      <c r="A4" s="66"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="32" t="s">
+    <row r="4" s="50" customFormat="1" ht="115.2" spans="1:51">
+      <c r="A4" s="63"/>
+      <c r="B4" s="63"/>
+      <c r="C4" s="30" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="30" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="30" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="30" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="30" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="32" t="s">
+      <c r="I4" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="30" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="K4" s="30" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="32" t="s">
+      <c r="L4" s="30" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="32" t="s">
+      <c r="M4" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="N4" s="32" t="s">
+      <c r="N4" s="30" t="s">
         <v>80</v>
       </c>
-      <c r="O4" s="32" t="s">
+      <c r="O4" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="P4" s="32" t="s">
+      <c r="P4" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="Q4" s="32" t="s">
+      <c r="Q4" s="30" t="s">
         <v>83</v>
       </c>
-      <c r="R4" s="32" t="s">
+      <c r="R4" s="30" t="s">
         <v>84</v>
       </c>
-      <c r="S4" s="32" t="s">
+      <c r="S4" s="30" t="s">
         <v>85</v>
       </c>
-      <c r="T4" s="32" t="s">
+      <c r="T4" s="30" t="s">
         <v>86</v>
       </c>
-      <c r="U4" s="32" t="s">
+      <c r="U4" s="30" t="s">
         <v>87</v>
       </c>
-      <c r="V4" s="32" t="s">
+      <c r="V4" s="30" t="s">
         <v>88</v>
       </c>
-      <c r="W4" s="32" t="s">
+      <c r="W4" s="30" t="s">
         <v>89</v>
       </c>
-      <c r="X4" s="32" t="s">
+      <c r="X4" s="30" t="s">
         <v>90</v>
       </c>
-      <c r="Y4" s="32" t="s">
+      <c r="Y4" s="30" t="s">
         <v>91</v>
       </c>
-      <c r="Z4" s="32" t="s">
+      <c r="Z4" s="30" t="s">
         <v>92</v>
       </c>
-      <c r="AA4" s="32" t="s">
+      <c r="AA4" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="AB4" s="32" t="s">
+      <c r="AB4" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="AC4" s="32" t="s">
+      <c r="AC4" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="AD4" s="32" t="s">
+      <c r="AD4" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="AE4" s="32" t="s">
+      <c r="AE4" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="AF4" s="32" t="s">
+      <c r="AF4" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="AG4" s="32" t="s">
+      <c r="AG4" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="AH4" s="32" t="s">
+      <c r="AH4" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="AI4" s="32" t="s">
+      <c r="AI4" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="AJ4" s="32" t="s">
+      <c r="AJ4" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="AK4" s="32" t="s">
+      <c r="AK4" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="AL4" s="32" t="s">
+      <c r="AL4" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="AM4" s="32" t="s">
+      <c r="AM4" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="AN4" s="32" t="s">
+      <c r="AN4" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="AO4" s="32" t="s">
+      <c r="AO4" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="AP4" s="32" t="s">
+      <c r="AP4" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="AQ4" s="32" t="s">
+      <c r="AQ4" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="AR4" s="32" t="s">
+      <c r="AR4" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="AS4" s="32" t="s">
+      <c r="AS4" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="AT4" s="32" t="s">
+      <c r="AT4" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="AU4" s="32" t="s">
+      <c r="AU4" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="AV4" s="32" t="s">
+      <c r="AV4" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="AW4" s="32" t="s">
+      <c r="AW4" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="AX4" s="32" t="s">
+      <c r="AX4" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="AY4" s="32" t="s">
+      <c r="AY4" s="30" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" s="53" customFormat="1" ht="100.8" spans="1:51">
-      <c r="A5" s="66"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="32"/>
-      <c r="S5" s="32"/>
-      <c r="T5" s="32"/>
-      <c r="U5" s="32"/>
-      <c r="V5" s="32"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="32"/>
-      <c r="Y5" s="32"/>
-      <c r="Z5" s="32"/>
-      <c r="AA5" s="32"/>
-      <c r="AB5" s="32"/>
-      <c r="AC5" s="32" t="s">
+    <row r="5" s="50" customFormat="1" ht="100.8" spans="1:51">
+      <c r="A5" s="63"/>
+      <c r="B5" s="63"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="30"/>
+      <c r="L5" s="30"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="30"/>
+      <c r="O5" s="30"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="30"/>
+      <c r="R5" s="30"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="30"/>
+      <c r="U5" s="30"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="30"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="30"/>
+      <c r="AA5" s="30"/>
+      <c r="AB5" s="30"/>
+      <c r="AC5" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="32" t="s">
+      <c r="AD5" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AE5" s="32" t="s">
+      <c r="AE5" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="AF5" s="32" t="s">
+      <c r="AF5" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="AG5" s="32" t="s">
+      <c r="AG5" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="AH5" s="32" t="s">
+      <c r="AH5" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="AI5" s="32" t="s">
+      <c r="AI5" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="AJ5" s="32" t="s">
+      <c r="AJ5" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="AK5" s="32" t="s">
+      <c r="AK5" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="AL5" s="32" t="s">
+      <c r="AL5" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="AM5" s="32" t="s">
+      <c r="AM5" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="AN5" s="32" t="s">
+      <c r="AN5" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="AO5" s="32" t="s">
+      <c r="AO5" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="AP5" s="32" t="s">
+      <c r="AP5" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="AQ5" s="32" t="s">
+      <c r="AQ5" s="30" t="s">
         <v>132</v>
       </c>
-      <c r="AR5" s="32" t="s">
+      <c r="AR5" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="AS5" s="32" t="s">
+      <c r="AS5" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="AT5" s="32" t="s">
+      <c r="AT5" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="AU5" s="32" t="s">
+      <c r="AU5" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="AV5" s="32" t="s">
+      <c r="AV5" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="AW5" s="32" t="s">
+      <c r="AW5" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="AX5" s="32" t="s">
+      <c r="AX5" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="AY5" s="32" t="s">
+      <c r="AY5" s="30" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="6" s="53" customFormat="1" ht="28.8" spans="1:51">
-      <c r="A6" s="66"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="69" t="s">
+    <row r="6" s="50" customFormat="1" ht="28.8" spans="1:51">
+      <c r="A6" s="63"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="E6" s="69" t="s">
+      <c r="E6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="F6" s="69" t="s">
+      <c r="F6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="H6" s="69" t="s">
+      <c r="H6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="J6" s="69" t="s">
+      <c r="J6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="K6" s="69" t="s">
+      <c r="K6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="L6" s="69" t="s">
+      <c r="L6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="M6" s="69" t="s">
+      <c r="M6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="N6" s="69" t="s">
+      <c r="N6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="O6" s="69" t="s">
+      <c r="O6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="Q6" s="69" t="s">
+      <c r="Q6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="R6" s="69" t="s">
+      <c r="R6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="S6" s="69" t="s">
+      <c r="S6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="T6" s="69" t="s">
+      <c r="T6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="U6" s="69" t="s">
+      <c r="U6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="V6" s="32" t="s">
+      <c r="V6" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="W6" s="69" t="s">
+      <c r="W6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="X6" s="69" t="s">
+      <c r="X6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="Y6" s="69" t="s">
+      <c r="Y6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="Z6" s="69" t="s">
+      <c r="Z6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AA6" s="69" t="s">
+      <c r="AA6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AB6" s="69" t="s">
+      <c r="AB6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AC6" s="69" t="s">
+      <c r="AC6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AD6" s="69" t="s">
+      <c r="AD6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AE6" s="69" t="s">
+      <c r="AE6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AF6" s="69" t="s">
+      <c r="AF6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AG6" s="69" t="s">
+      <c r="AG6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AH6" s="69" t="s">
+      <c r="AH6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AI6" s="69" t="s">
+      <c r="AI6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AJ6" s="69" t="s">
+      <c r="AJ6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AK6" s="69" t="s">
+      <c r="AK6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AL6" s="69" t="s">
+      <c r="AL6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AM6" s="69" t="s">
+      <c r="AM6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AN6" s="69" t="s">
+      <c r="AN6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AO6" s="69" t="s">
+      <c r="AO6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AP6" s="69" t="s">
+      <c r="AP6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AQ6" s="69" t="s">
+      <c r="AQ6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="69" t="s">
+      <c r="AR6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AS6" s="69" t="s">
+      <c r="AS6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AT6" s="69" t="s">
+      <c r="AT6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AU6" s="69" t="s">
+      <c r="AU6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AV6" s="69" t="s">
+      <c r="AV6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AW6" s="69" t="s">
+      <c r="AW6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AX6" s="69" t="s">
+      <c r="AX6" s="66" t="s">
         <v>141</v>
       </c>
-      <c r="AY6" s="69" t="s">
+      <c r="AY6" s="66" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="7" s="53" customFormat="1" ht="57.6" spans="1:51">
-      <c r="A7" s="70" t="s">
+    <row r="7" s="50" customFormat="1" ht="57.6" spans="1:51">
+      <c r="A7" s="67" t="s">
         <v>143</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="66" t="s">
         <v>144</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="D7" s="69" t="s">
+      <c r="D7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="E7" s="69" t="s">
+      <c r="E7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="F7" s="69" t="s">
+      <c r="F7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="G7" s="69" t="s">
+      <c r="G7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="H7" s="69" t="s">
+      <c r="H7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="I7" s="69" t="s">
+      <c r="I7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="J7" s="69" t="s">
+      <c r="J7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="K7" s="69" t="s">
+      <c r="K7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="L7" s="69" t="s">
+      <c r="L7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="M7" s="69" t="s">
+      <c r="M7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="N7" s="69" t="s">
+      <c r="N7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="O7" s="69" t="s">
+      <c r="O7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="P7" s="69" t="s">
+      <c r="P7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="Q7" s="69" t="s">
+      <c r="Q7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="R7" s="69" t="s">
+      <c r="R7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="S7" s="69" t="s">
+      <c r="S7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="T7" s="69" t="s">
+      <c r="T7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="U7" s="69" t="s">
+      <c r="U7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="V7" s="32" t="s">
+      <c r="V7" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="W7" s="69" t="s">
+      <c r="W7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="X7" s="69" t="s">
+      <c r="X7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="Y7" s="69" t="s">
+      <c r="Y7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="Z7" s="69" t="s">
+      <c r="Z7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AA7" s="69" t="s">
+      <c r="AA7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AB7" s="69" t="s">
+      <c r="AB7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AC7" s="69" t="s">
+      <c r="AC7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AD7" s="69" t="s">
+      <c r="AD7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AE7" s="69" t="s">
+      <c r="AE7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AF7" s="69" t="s">
+      <c r="AF7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AG7" s="69" t="s">
+      <c r="AG7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AH7" s="69" t="s">
+      <c r="AH7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AI7" s="69" t="s">
+      <c r="AI7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AJ7" s="69" t="s">
+      <c r="AJ7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AK7" s="69" t="s">
+      <c r="AK7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AL7" s="69" t="s">
+      <c r="AL7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AM7" s="69" t="s">
+      <c r="AM7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AN7" s="69" t="s">
+      <c r="AN7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AO7" s="69" t="s">
+      <c r="AO7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AP7" s="69" t="s">
+      <c r="AP7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AQ7" s="69" t="s">
+      <c r="AQ7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AR7" s="69" t="s">
+      <c r="AR7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AS7" s="69" t="s">
+      <c r="AS7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AT7" s="69" t="s">
+      <c r="AT7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AU7" s="69" t="s">
+      <c r="AU7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AV7" s="69" t="s">
+      <c r="AV7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AW7" s="69" t="s">
+      <c r="AW7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AX7" s="69" t="s">
+      <c r="AX7" s="66" t="s">
         <v>145</v>
       </c>
-      <c r="AY7" s="69" t="s">
+      <c r="AY7" s="66" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="8" ht="72" spans="1:51">
-      <c r="A8" s="72"/>
-      <c r="B8" s="73" t="s">
+      <c r="A8" s="69"/>
+      <c r="B8" s="70" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="74" t="s">
+      <c r="C8" s="71" t="s">
         <v>148</v>
       </c>
-      <c r="D8" s="74" t="s">
+      <c r="D8" s="71" t="s">
         <v>149</v>
       </c>
-      <c r="E8" s="74" t="s">
+      <c r="E8" s="71" t="s">
         <v>150</v>
       </c>
-      <c r="F8" s="74" t="s">
+      <c r="F8" s="71" t="s">
         <v>151</v>
       </c>
-      <c r="G8" s="74" t="s">
+      <c r="G8" s="71" t="s">
         <v>152</v>
       </c>
-      <c r="H8" s="74" t="s">
+      <c r="H8" s="71" t="s">
         <v>153</v>
       </c>
-      <c r="I8" s="74" t="s">
+      <c r="I8" s="71" t="s">
         <v>154</v>
       </c>
-      <c r="J8" s="74" t="s">
+      <c r="J8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="K8" s="74" t="s">
+      <c r="K8" s="71" t="s">
         <v>156</v>
       </c>
-      <c r="L8" s="74" t="s">
+      <c r="L8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="M8" s="74" t="s">
+      <c r="M8" s="71" t="s">
         <v>157</v>
       </c>
-      <c r="N8" s="74" t="s">
+      <c r="N8" s="71" t="s">
         <v>158</v>
       </c>
-      <c r="O8" s="74" t="s">
+      <c r="O8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="P8" s="74" t="s">
+      <c r="P8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="Q8" s="74" t="s">
+      <c r="Q8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="R8" s="74" t="s">
+      <c r="R8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="S8" s="74" t="s">
+      <c r="S8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="T8" s="74" t="s">
+      <c r="T8" s="71" t="s">
         <v>159</v>
       </c>
-      <c r="U8" s="74" t="s">
+      <c r="U8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="V8" s="74" t="s">
+      <c r="V8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="W8" s="74" t="s">
+      <c r="W8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="X8" s="74" t="s">
+      <c r="X8" s="71" t="s">
         <v>160</v>
       </c>
-      <c r="Y8" s="74" t="s">
+      <c r="Y8" s="71" t="s">
         <v>161</v>
       </c>
-      <c r="Z8" s="74" t="s">
+      <c r="Z8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AA8" s="74" t="s">
+      <c r="AA8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AB8" s="74" t="s">
+      <c r="AB8" s="71" t="s">
         <v>162</v>
       </c>
-      <c r="AC8" s="74" t="s">
+      <c r="AC8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AD8" s="74" t="s">
+      <c r="AD8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AE8" s="74" t="s">
+      <c r="AE8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AF8" s="74" t="s">
+      <c r="AF8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AG8" s="74" t="s">
+      <c r="AG8" s="71" t="s">
         <v>163</v>
       </c>
-      <c r="AH8" s="74" t="s">
+      <c r="AH8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AI8" s="74" t="s">
+      <c r="AI8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AJ8" s="74" t="s">
+      <c r="AJ8" s="71" t="s">
         <v>164</v>
       </c>
-      <c r="AK8" s="74" t="s">
+      <c r="AK8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AL8" s="74" t="s">
+      <c r="AL8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AM8" s="74" t="s">
+      <c r="AM8" s="71" t="s">
         <v>165</v>
       </c>
-      <c r="AN8" s="74" t="s">
+      <c r="AN8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AO8" s="74" t="s">
+      <c r="AO8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AP8" s="74" t="s">
+      <c r="AP8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AQ8" s="74" t="s">
+      <c r="AQ8" s="71" t="s">
         <v>155</v>
       </c>
-      <c r="AR8" s="74" t="s">
+      <c r="AR8" s="71" t="s">
         <v>164</v>
       </c>
-      <c r="AS8" s="75" t="s">
+      <c r="AS8" s="72" t="s">
         <v>166</v>
       </c>
-      <c r="AT8" s="75" t="s">
+      <c r="AT8" s="72" t="s">
         <v>167</v>
       </c>
-      <c r="AU8" s="75" t="s">
+      <c r="AU8" s="72" t="s">
         <v>168</v>
       </c>
-      <c r="AV8" s="75" t="s">
+      <c r="AV8" s="72" t="s">
         <v>169</v>
       </c>
-      <c r="AW8" s="75" t="s">
+      <c r="AW8" s="72" t="s">
         <v>159</v>
       </c>
-      <c r="AX8" s="76" t="s">
+      <c r="AX8" s="73" t="s">
         <v>155</v>
       </c>
-      <c r="AY8" s="76" t="s">
+      <c r="AY8" s="73" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="9" ht="43.2" spans="1:51">
-      <c r="A9" s="72"/>
-      <c r="B9" s="27" t="s">
+      <c r="A9" s="69"/>
+      <c r="B9" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="C9" s="75"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
-      <c r="J9" s="75"/>
-      <c r="K9" s="75" t="s">
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="72"/>
+      <c r="F9" s="72"/>
+      <c r="G9" s="72"/>
+      <c r="H9" s="72"/>
+      <c r="I9" s="72"/>
+      <c r="J9" s="72"/>
+      <c r="K9" s="72" t="s">
         <v>171</v>
       </c>
-      <c r="L9" s="75"/>
-      <c r="M9" s="75"/>
-      <c r="N9" s="75" t="s">
+      <c r="L9" s="72"/>
+      <c r="M9" s="72"/>
+      <c r="N9" s="72" t="s">
         <v>172</v>
       </c>
-      <c r="O9" s="75"/>
-      <c r="P9" s="75"/>
-      <c r="Q9" s="75"/>
-      <c r="R9" s="75"/>
-      <c r="S9" s="75"/>
-      <c r="T9" s="75"/>
-      <c r="U9" s="75"/>
-      <c r="V9" s="75"/>
-      <c r="W9" s="75"/>
-      <c r="X9" s="75"/>
-      <c r="Y9" s="75"/>
-      <c r="Z9" s="75"/>
-      <c r="AA9" s="75"/>
-      <c r="AB9" s="75"/>
-      <c r="AC9" s="75"/>
-      <c r="AD9" s="75"/>
-      <c r="AE9" s="75"/>
-      <c r="AF9" s="75"/>
-      <c r="AG9" s="75"/>
-      <c r="AH9" s="75"/>
-      <c r="AI9" s="75"/>
-      <c r="AJ9" s="75"/>
-      <c r="AK9" s="75"/>
-      <c r="AL9" s="75"/>
-      <c r="AM9" s="75"/>
-      <c r="AN9" s="75"/>
-      <c r="AO9" s="75"/>
-      <c r="AP9" s="75"/>
-      <c r="AQ9" s="75"/>
-      <c r="AR9" s="75"/>
-      <c r="AS9" s="75"/>
-      <c r="AT9" s="75"/>
-      <c r="AU9" s="75"/>
-      <c r="AV9" s="75"/>
-      <c r="AW9" s="75"/>
-      <c r="AX9" s="76"/>
-      <c r="AY9" s="76"/>
+      <c r="O9" s="72"/>
+      <c r="P9" s="72"/>
+      <c r="Q9" s="72"/>
+      <c r="R9" s="72"/>
+      <c r="S9" s="72"/>
+      <c r="T9" s="72"/>
+      <c r="U9" s="72"/>
+      <c r="V9" s="72"/>
+      <c r="W9" s="72"/>
+      <c r="X9" s="72"/>
+      <c r="Y9" s="72"/>
+      <c r="Z9" s="72"/>
+      <c r="AA9" s="72"/>
+      <c r="AB9" s="72"/>
+      <c r="AC9" s="72"/>
+      <c r="AD9" s="72"/>
+      <c r="AE9" s="72"/>
+      <c r="AF9" s="72"/>
+      <c r="AG9" s="72"/>
+      <c r="AH9" s="72"/>
+      <c r="AI9" s="72"/>
+      <c r="AJ9" s="72"/>
+      <c r="AK9" s="72"/>
+      <c r="AL9" s="72"/>
+      <c r="AM9" s="72"/>
+      <c r="AN9" s="72"/>
+      <c r="AO9" s="72"/>
+      <c r="AP9" s="72"/>
+      <c r="AQ9" s="72"/>
+      <c r="AR9" s="72"/>
+      <c r="AS9" s="72"/>
+      <c r="AT9" s="72"/>
+      <c r="AU9" s="72"/>
+      <c r="AV9" s="72"/>
+      <c r="AW9" s="72"/>
+      <c r="AX9" s="73"/>
+      <c r="AY9" s="73"/>
     </row>
     <row r="10" ht="86.4" spans="1:51">
-      <c r="A10" s="77"/>
-      <c r="B10" s="27" t="s">
+      <c r="A10" s="74"/>
+      <c r="B10" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
-      <c r="J10" s="75"/>
-      <c r="K10" s="75" t="s">
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="72"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
+      <c r="J10" s="72"/>
+      <c r="K10" s="72" t="s">
         <v>174</v>
       </c>
-      <c r="L10" s="75" t="s">
+      <c r="L10" s="72" t="s">
         <v>175</v>
       </c>
-      <c r="M10" s="75"/>
-      <c r="N10" s="75" t="s">
+      <c r="M10" s="72"/>
+      <c r="N10" s="72" t="s">
         <v>176</v>
       </c>
-      <c r="O10" s="75"/>
-      <c r="P10" s="75"/>
-      <c r="Q10" s="75"/>
-      <c r="R10" s="75"/>
-      <c r="S10" s="75"/>
-      <c r="T10" s="75"/>
-      <c r="U10" s="75"/>
-      <c r="V10" s="75"/>
-      <c r="W10" s="75"/>
-      <c r="X10" s="75"/>
-      <c r="Y10" s="75"/>
-      <c r="Z10" s="75"/>
-      <c r="AA10" s="75" t="s">
+      <c r="O10" s="72"/>
+      <c r="P10" s="72"/>
+      <c r="Q10" s="72"/>
+      <c r="R10" s="72"/>
+      <c r="S10" s="72"/>
+      <c r="T10" s="72"/>
+      <c r="U10" s="72"/>
+      <c r="V10" s="72"/>
+      <c r="W10" s="72"/>
+      <c r="X10" s="72"/>
+      <c r="Y10" s="72"/>
+      <c r="Z10" s="72"/>
+      <c r="AA10" s="72" t="s">
         <v>177</v>
       </c>
-      <c r="AB10" s="75"/>
-      <c r="AC10" s="75"/>
-      <c r="AD10" s="75"/>
-      <c r="AE10" s="75"/>
-      <c r="AF10" s="75"/>
-      <c r="AG10" s="75"/>
-      <c r="AH10" s="75"/>
-      <c r="AI10" s="75"/>
-      <c r="AJ10" s="75" t="s">
+      <c r="AB10" s="72"/>
+      <c r="AC10" s="72"/>
+      <c r="AD10" s="72"/>
+      <c r="AE10" s="72"/>
+      <c r="AF10" s="72"/>
+      <c r="AG10" s="72"/>
+      <c r="AH10" s="72"/>
+      <c r="AI10" s="72"/>
+      <c r="AJ10" s="72" t="s">
         <v>178</v>
       </c>
-      <c r="AK10" s="75"/>
-      <c r="AL10" s="75"/>
-      <c r="AM10" s="75"/>
-      <c r="AN10" s="75"/>
-      <c r="AO10" s="75"/>
-      <c r="AP10" s="75"/>
-      <c r="AQ10" s="75"/>
-      <c r="AR10" s="75"/>
-      <c r="AS10" s="75"/>
-      <c r="AT10" s="75"/>
-      <c r="AU10" s="75"/>
-      <c r="AV10" s="75"/>
-      <c r="AW10" s="75"/>
-      <c r="AX10" s="76"/>
-      <c r="AY10" s="76"/>
+      <c r="AK10" s="72"/>
+      <c r="AL10" s="72"/>
+      <c r="AM10" s="72"/>
+      <c r="AN10" s="72"/>
+      <c r="AO10" s="72"/>
+      <c r="AP10" s="72"/>
+      <c r="AQ10" s="72"/>
+      <c r="AR10" s="72"/>
+      <c r="AS10" s="72"/>
+      <c r="AT10" s="72"/>
+      <c r="AU10" s="72"/>
+      <c r="AV10" s="72"/>
+      <c r="AW10" s="72"/>
+      <c r="AX10" s="73"/>
+      <c r="AY10" s="73"/>
     </row>
     <row r="11" spans="1:51">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="75" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="79" t="s">
+      <c r="B11" s="76" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
-      <c r="S11" s="54"/>
-      <c r="T11" s="54"/>
-      <c r="U11" s="54"/>
-      <c r="V11" s="54"/>
-      <c r="W11" s="54"/>
-      <c r="X11" s="54"/>
-      <c r="Y11" s="54"/>
-      <c r="Z11" s="54"/>
-      <c r="AA11" s="54"/>
-      <c r="AB11" s="54"/>
-      <c r="AC11" s="54"/>
-      <c r="AD11" s="54"/>
-      <c r="AE11" s="54"/>
-      <c r="AF11" s="54"/>
-      <c r="AG11" s="54"/>
-      <c r="AH11" s="54"/>
-      <c r="AI11" s="54"/>
-      <c r="AJ11" s="54"/>
-      <c r="AK11" s="54"/>
-      <c r="AL11" s="54"/>
-      <c r="AM11" s="54"/>
-      <c r="AN11" s="54"/>
-      <c r="AO11" s="54"/>
-      <c r="AP11" s="54"/>
-      <c r="AQ11" s="54"/>
-      <c r="AR11" s="54"/>
-      <c r="AS11" s="54"/>
-      <c r="AT11" s="54"/>
-      <c r="AU11" s="54"/>
-      <c r="AV11" s="54"/>
-      <c r="AW11" s="54"/>
-      <c r="AX11" s="54"/>
-      <c r="AY11" s="54"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="51"/>
+      <c r="E11" s="51"/>
+      <c r="F11" s="51"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="51"/>
+      <c r="I11" s="51"/>
+      <c r="J11" s="51"/>
+      <c r="K11" s="51"/>
+      <c r="L11" s="51"/>
+      <c r="M11" s="51"/>
+      <c r="N11" s="51"/>
+      <c r="O11" s="51"/>
+      <c r="P11" s="51"/>
+      <c r="Q11" s="51"/>
+      <c r="R11" s="51"/>
+      <c r="S11" s="51"/>
+      <c r="T11" s="51"/>
+      <c r="U11" s="51"/>
+      <c r="V11" s="51"/>
+      <c r="W11" s="51"/>
+      <c r="X11" s="51"/>
+      <c r="Y11" s="51"/>
+      <c r="Z11" s="51"/>
+      <c r="AA11" s="51"/>
+      <c r="AB11" s="51"/>
+      <c r="AC11" s="51"/>
+      <c r="AD11" s="51"/>
+      <c r="AE11" s="51"/>
+      <c r="AF11" s="51"/>
+      <c r="AG11" s="51"/>
+      <c r="AH11" s="51"/>
+      <c r="AI11" s="51"/>
+      <c r="AJ11" s="51"/>
+      <c r="AK11" s="51"/>
+      <c r="AL11" s="51"/>
+      <c r="AM11" s="51"/>
+      <c r="AN11" s="51"/>
+      <c r="AO11" s="51"/>
+      <c r="AP11" s="51"/>
+      <c r="AQ11" s="51"/>
+      <c r="AR11" s="51"/>
+      <c r="AS11" s="51"/>
+      <c r="AT11" s="51"/>
+      <c r="AU11" s="51"/>
+      <c r="AV11" s="51"/>
+      <c r="AW11" s="51"/>
+      <c r="AX11" s="51"/>
+      <c r="AY11" s="51"/>
     </row>
     <row r="12" spans="1:51">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="75" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="80" t="s">
+      <c r="B12" s="77" t="s">
         <v>182</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="54"/>
-      <c r="K12" s="54"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="54"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="54"/>
-      <c r="Q12" s="54"/>
-      <c r="R12" s="54"/>
-      <c r="S12" s="54"/>
-      <c r="T12" s="54"/>
-      <c r="U12" s="54"/>
-      <c r="V12" s="54"/>
-      <c r="W12" s="54"/>
-      <c r="X12" s="54"/>
-      <c r="Y12" s="54"/>
-      <c r="Z12" s="54"/>
-      <c r="AA12" s="54"/>
-      <c r="AB12" s="54"/>
-      <c r="AC12" s="54"/>
-      <c r="AD12" s="54"/>
-      <c r="AE12" s="54"/>
-      <c r="AF12" s="54"/>
-      <c r="AG12" s="54"/>
-      <c r="AH12" s="54"/>
-      <c r="AI12" s="54"/>
-      <c r="AJ12" s="54"/>
-      <c r="AK12" s="54"/>
-      <c r="AL12" s="54"/>
-      <c r="AM12" s="54"/>
-      <c r="AN12" s="54"/>
-      <c r="AO12" s="54"/>
-      <c r="AP12" s="54"/>
-      <c r="AQ12" s="54"/>
-      <c r="AR12" s="54"/>
-      <c r="AS12" s="54"/>
-      <c r="AT12" s="54"/>
-      <c r="AU12" s="54"/>
-      <c r="AV12" s="54"/>
-      <c r="AW12" s="54"/>
-      <c r="AX12" s="54"/>
-      <c r="AY12" s="54"/>
+      <c r="C12" s="51"/>
+      <c r="D12" s="51"/>
+      <c r="E12" s="51"/>
+      <c r="F12" s="51"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="51"/>
+      <c r="I12" s="51"/>
+      <c r="J12" s="51"/>
+      <c r="K12" s="51"/>
+      <c r="L12" s="51"/>
+      <c r="M12" s="51"/>
+      <c r="N12" s="51"/>
+      <c r="O12" s="51"/>
+      <c r="P12" s="51"/>
+      <c r="Q12" s="51"/>
+      <c r="R12" s="51"/>
+      <c r="S12" s="51"/>
+      <c r="T12" s="51"/>
+      <c r="U12" s="51"/>
+      <c r="V12" s="51"/>
+      <c r="W12" s="51"/>
+      <c r="X12" s="51"/>
+      <c r="Y12" s="51"/>
+      <c r="Z12" s="51"/>
+      <c r="AA12" s="51"/>
+      <c r="AB12" s="51"/>
+      <c r="AC12" s="51"/>
+      <c r="AD12" s="51"/>
+      <c r="AE12" s="51"/>
+      <c r="AF12" s="51"/>
+      <c r="AG12" s="51"/>
+      <c r="AH12" s="51"/>
+      <c r="AI12" s="51"/>
+      <c r="AJ12" s="51"/>
+      <c r="AK12" s="51"/>
+      <c r="AL12" s="51"/>
+      <c r="AM12" s="51"/>
+      <c r="AN12" s="51"/>
+      <c r="AO12" s="51"/>
+      <c r="AP12" s="51"/>
+      <c r="AQ12" s="51"/>
+      <c r="AR12" s="51"/>
+      <c r="AS12" s="51"/>
+      <c r="AT12" s="51"/>
+      <c r="AU12" s="51"/>
+      <c r="AV12" s="51"/>
+      <c r="AW12" s="51"/>
+      <c r="AX12" s="51"/>
+      <c r="AY12" s="51"/>
     </row>
     <row r="14" ht="115.2" spans="1:51">
-      <c r="A14" s="81" t="s">
+      <c r="A14" s="78" t="s">
         <v>183</v>
       </c>
-      <c r="B14" s="82" t="s">
+      <c r="B14" s="79" t="s">
         <v>184</v>
       </c>
-      <c r="C14" s="83"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="84" t="s">
+      <c r="C14" s="80"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81" t="s">
         <v>185</v>
       </c>
-      <c r="G14" s="84"/>
-      <c r="H14" s="84" t="s">
+      <c r="G14" s="81"/>
+      <c r="H14" s="81" t="s">
         <v>186</v>
       </c>
-      <c r="I14" s="84"/>
-      <c r="J14" s="84"/>
-      <c r="K14" s="84" t="s">
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="81" t="s">
         <v>187</v>
       </c>
-      <c r="L14" s="84" t="s">
+      <c r="L14" s="81" t="s">
         <v>188</v>
       </c>
-      <c r="M14" s="84" t="s">
+      <c r="M14" s="81" t="s">
         <v>189</v>
       </c>
-      <c r="N14" s="84" t="s">
+      <c r="N14" s="81" t="s">
         <v>190</v>
       </c>
-      <c r="O14" s="84"/>
-      <c r="P14" s="84"/>
-      <c r="Q14" s="84" t="s">
+      <c r="O14" s="81"/>
+      <c r="P14" s="81"/>
+      <c r="Q14" s="81" t="s">
         <v>191</v>
       </c>
-      <c r="R14" s="84" t="s">
+      <c r="R14" s="81" t="s">
         <v>192</v>
       </c>
-      <c r="S14" s="84" t="s">
+      <c r="S14" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="T14" s="84" t="s">
+      <c r="T14" s="81" t="s">
         <v>194</v>
       </c>
-      <c r="U14" s="84" t="s">
+      <c r="U14" s="81" t="s">
         <v>195</v>
       </c>
-      <c r="V14" s="84"/>
-      <c r="W14" s="84" t="s">
+      <c r="V14" s="81"/>
+      <c r="W14" s="81" t="s">
         <v>193</v>
       </c>
-      <c r="X14" s="84" t="s">
+      <c r="X14" s="81" t="s">
         <v>196</v>
       </c>
-      <c r="Y14" s="84" t="s">
+      <c r="Y14" s="81" t="s">
         <v>197</v>
       </c>
-      <c r="Z14" s="84" t="s">
+      <c r="Z14" s="81" t="s">
         <v>198</v>
       </c>
-      <c r="AA14" s="84" t="s">
+      <c r="AA14" s="81" t="s">
         <v>199</v>
       </c>
-      <c r="AB14" s="84" t="s">
+      <c r="AB14" s="81" t="s">
         <v>200</v>
       </c>
-      <c r="AC14" s="84" t="s">
+      <c r="AC14" s="81" t="s">
         <v>201</v>
       </c>
-      <c r="AD14" s="84" t="s">
+      <c r="AD14" s="81" t="s">
         <v>202</v>
       </c>
-      <c r="AE14" s="84" t="s">
+      <c r="AE14" s="81" t="s">
         <v>203</v>
       </c>
-      <c r="AF14" s="84" t="s">
+      <c r="AF14" s="81" t="s">
         <v>204</v>
       </c>
-      <c r="AG14" s="84"/>
-      <c r="AH14" s="84" t="s">
+      <c r="AG14" s="81"/>
+      <c r="AH14" s="81" t="s">
         <v>205</v>
       </c>
-      <c r="AI14" s="84" t="s">
+      <c r="AI14" s="81" t="s">
         <v>206</v>
       </c>
-      <c r="AJ14" s="84" t="s">
+      <c r="AJ14" s="81" t="s">
         <v>207</v>
       </c>
-      <c r="AK14" s="84"/>
-      <c r="AL14" s="84"/>
-      <c r="AM14" s="84" t="s">
+      <c r="AK14" s="81"/>
+      <c r="AL14" s="81"/>
+      <c r="AM14" s="81" t="s">
         <v>208</v>
       </c>
-      <c r="AN14" s="84" t="s">
+      <c r="AN14" s="81" t="s">
         <v>209</v>
       </c>
-      <c r="AO14" s="84" t="s">
+      <c r="AO14" s="81" t="s">
         <v>210</v>
       </c>
-      <c r="AP14" s="84" t="s">
+      <c r="AP14" s="81" t="s">
         <v>211</v>
       </c>
-      <c r="AQ14" s="84"/>
-      <c r="AR14" s="84" t="s">
+      <c r="AQ14" s="81"/>
+      <c r="AR14" s="81" t="s">
         <v>212</v>
       </c>
-      <c r="AS14" s="85" t="s">
+      <c r="AS14" s="82" t="s">
         <v>213</v>
       </c>
-      <c r="AT14" s="84" t="s">
+      <c r="AT14" s="81" t="s">
         <v>214</v>
       </c>
-      <c r="AU14" s="84" t="s">
+      <c r="AU14" s="81" t="s">
         <v>215</v>
       </c>
-      <c r="AV14" s="76"/>
-      <c r="AW14" s="76"/>
-      <c r="AX14" s="75" t="s">
+      <c r="AV14" s="73"/>
+      <c r="AW14" s="73"/>
+      <c r="AX14" s="72" t="s">
         <v>216</v>
       </c>
-      <c r="AY14" s="75"/>
+      <c r="AY14" s="72"/>
     </row>
     <row r="15" spans="1:51">
-      <c r="A15" s="86"/>
-      <c r="B15" s="87" t="s">
+      <c r="A15" s="83"/>
+      <c r="B15" s="84" t="s">
         <v>217</v>
       </c>
-      <c r="C15" s="88"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="80"/>
-      <c r="L15" s="80"/>
-      <c r="M15" s="80"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="80"/>
-      <c r="Q15" s="80"/>
-      <c r="R15" s="80"/>
-      <c r="S15" s="80"/>
-      <c r="T15" s="80"/>
-      <c r="U15" s="80"/>
-      <c r="V15" s="80"/>
-      <c r="W15" s="80"/>
-      <c r="X15" s="80"/>
-      <c r="Y15" s="80"/>
-      <c r="Z15" s="80"/>
-      <c r="AA15" s="80"/>
-      <c r="AB15" s="80"/>
-      <c r="AC15" s="80"/>
-      <c r="AD15" s="80"/>
-      <c r="AE15" s="80"/>
-      <c r="AF15" s="80"/>
-      <c r="AG15" s="80"/>
-      <c r="AH15" s="80"/>
-      <c r="AI15" s="80"/>
-      <c r="AJ15" s="80"/>
-      <c r="AK15" s="80"/>
-      <c r="AL15" s="80"/>
-      <c r="AM15" s="80"/>
-      <c r="AN15" s="80"/>
-      <c r="AO15" s="80"/>
-      <c r="AP15" s="80"/>
-      <c r="AQ15" s="80"/>
-      <c r="AR15" s="80"/>
-      <c r="AS15" s="80"/>
-      <c r="AT15" s="80"/>
-      <c r="AU15" s="80"/>
-      <c r="AV15" s="80"/>
-      <c r="AW15" s="80"/>
-      <c r="AX15" s="80"/>
-      <c r="AY15" s="80"/>
+      <c r="C15" s="85"/>
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77"/>
+      <c r="G15" s="77"/>
+      <c r="H15" s="77"/>
+      <c r="I15" s="77"/>
+      <c r="J15" s="77"/>
+      <c r="K15" s="77"/>
+      <c r="L15" s="77"/>
+      <c r="M15" s="77"/>
+      <c r="N15" s="77"/>
+      <c r="O15" s="77"/>
+      <c r="P15" s="77"/>
+      <c r="Q15" s="77"/>
+      <c r="R15" s="77"/>
+      <c r="S15" s="77"/>
+      <c r="T15" s="77"/>
+      <c r="U15" s="77"/>
+      <c r="V15" s="77"/>
+      <c r="W15" s="77"/>
+      <c r="X15" s="77"/>
+      <c r="Y15" s="77"/>
+      <c r="Z15" s="77"/>
+      <c r="AA15" s="77"/>
+      <c r="AB15" s="77"/>
+      <c r="AC15" s="77"/>
+      <c r="AD15" s="77"/>
+      <c r="AE15" s="77"/>
+      <c r="AF15" s="77"/>
+      <c r="AG15" s="77"/>
+      <c r="AH15" s="77"/>
+      <c r="AI15" s="77"/>
+      <c r="AJ15" s="77"/>
+      <c r="AK15" s="77"/>
+      <c r="AL15" s="77"/>
+      <c r="AM15" s="77"/>
+      <c r="AN15" s="77"/>
+      <c r="AO15" s="77"/>
+      <c r="AP15" s="77"/>
+      <c r="AQ15" s="77"/>
+      <c r="AR15" s="77"/>
+      <c r="AS15" s="77"/>
+      <c r="AT15" s="77"/>
+      <c r="AU15" s="77"/>
+      <c r="AV15" s="77"/>
+      <c r="AW15" s="77"/>
+      <c r="AX15" s="77"/>
+      <c r="AY15" s="77"/>
     </row>
     <row r="16" ht="72" spans="1:51">
-      <c r="A16" s="86"/>
-      <c r="B16" s="87" t="s">
+      <c r="A16" s="83"/>
+      <c r="B16" s="84" t="s">
         <v>218</v>
       </c>
-      <c r="C16" s="89" t="s">
+      <c r="C16" s="86" t="s">
         <v>219</v>
       </c>
-      <c r="D16" s="90" t="s">
+      <c r="D16" s="87" t="s">
         <v>220</v>
       </c>
-      <c r="E16" s="80"/>
-      <c r="F16" s="80"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="80"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="80"/>
-      <c r="K16" s="90" t="s">
+      <c r="E16" s="77"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
+      <c r="H16" s="77"/>
+      <c r="I16" s="77"/>
+      <c r="J16" s="77"/>
+      <c r="K16" s="87" t="s">
         <v>221</v>
       </c>
-      <c r="L16" s="80"/>
-      <c r="M16" s="80"/>
-      <c r="N16" s="80"/>
-      <c r="O16" s="80"/>
-      <c r="P16" s="80"/>
-      <c r="Q16" s="80"/>
-      <c r="R16" s="80"/>
-      <c r="S16" s="80"/>
-      <c r="T16" s="80"/>
-      <c r="U16" s="80"/>
-      <c r="V16" s="80"/>
-      <c r="W16" s="80"/>
-      <c r="X16" s="80"/>
-      <c r="Y16" s="80"/>
-      <c r="Z16" s="90" t="s">
+      <c r="L16" s="77"/>
+      <c r="M16" s="77"/>
+      <c r="N16" s="77"/>
+      <c r="O16" s="77"/>
+      <c r="P16" s="77"/>
+      <c r="Q16" s="77"/>
+      <c r="R16" s="77"/>
+      <c r="S16" s="77"/>
+      <c r="T16" s="77"/>
+      <c r="U16" s="77"/>
+      <c r="V16" s="77"/>
+      <c r="W16" s="77"/>
+      <c r="X16" s="77"/>
+      <c r="Y16" s="77"/>
+      <c r="Z16" s="87" t="s">
         <v>222</v>
       </c>
-      <c r="AA16" s="80" t="s">
+      <c r="AA16" s="77" t="s">
         <v>223</v>
       </c>
-      <c r="AB16" s="90" t="s">
+      <c r="AB16" s="87" t="s">
         <v>224</v>
       </c>
-      <c r="AC16" s="80"/>
-      <c r="AD16" s="80"/>
-      <c r="AE16" s="80"/>
-      <c r="AF16" s="80"/>
-      <c r="AG16" s="80"/>
-      <c r="AH16" s="80"/>
-      <c r="AI16" s="80"/>
-      <c r="AJ16" s="80"/>
-      <c r="AK16" s="80"/>
-      <c r="AL16" s="80"/>
-      <c r="AM16" s="90" t="s">
+      <c r="AC16" s="77"/>
+      <c r="AD16" s="77"/>
+      <c r="AE16" s="77"/>
+      <c r="AF16" s="77"/>
+      <c r="AG16" s="77"/>
+      <c r="AH16" s="77"/>
+      <c r="AI16" s="77"/>
+      <c r="AJ16" s="77"/>
+      <c r="AK16" s="77"/>
+      <c r="AL16" s="77"/>
+      <c r="AM16" s="87" t="s">
         <v>225</v>
       </c>
-      <c r="AN16" s="80"/>
-      <c r="AO16" s="80" t="s">
+      <c r="AN16" s="77"/>
+      <c r="AO16" s="77" t="s">
         <v>226</v>
       </c>
-      <c r="AP16" s="80" t="s">
+      <c r="AP16" s="77" t="s">
         <v>226</v>
       </c>
-      <c r="AQ16" s="80"/>
-      <c r="AR16" s="80"/>
-      <c r="AS16" s="80" t="s">
+      <c r="AQ16" s="77"/>
+      <c r="AR16" s="77"/>
+      <c r="AS16" s="77" t="s">
         <v>227</v>
       </c>
-      <c r="AT16" s="80"/>
-      <c r="AU16" s="80"/>
-      <c r="AV16" s="90" t="s">
+      <c r="AT16" s="77"/>
+      <c r="AU16" s="77"/>
+      <c r="AV16" s="87" t="s">
         <v>228</v>
       </c>
-      <c r="AW16" s="80"/>
-      <c r="AX16" s="80"/>
-      <c r="AY16" s="80"/>
+      <c r="AW16" s="77"/>
+      <c r="AX16" s="77"/>
+      <c r="AY16" s="77"/>
     </row>
     <row r="17" ht="86.4" spans="1:51">
-      <c r="A17" s="86"/>
-      <c r="B17" s="87" t="s">
+      <c r="A17" s="83"/>
+      <c r="B17" s="84" t="s">
         <v>229</v>
       </c>
-      <c r="C17" s="88"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="90" t="s">
+      <c r="C17" s="85"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="87" t="s">
         <v>230</v>
       </c>
-      <c r="H17" s="80"/>
-      <c r="I17" s="90" t="s">
+      <c r="H17" s="77"/>
+      <c r="I17" s="87" t="s">
         <v>231</v>
       </c>
-      <c r="J17" s="80"/>
-      <c r="K17" s="80" t="s">
+      <c r="J17" s="77"/>
+      <c r="K17" s="77" t="s">
         <v>232</v>
       </c>
-      <c r="L17" s="80" t="s">
+      <c r="L17" s="77" t="s">
         <v>233</v>
       </c>
-      <c r="M17" s="80"/>
-      <c r="N17" s="80"/>
-      <c r="O17" s="90" t="s">
+      <c r="M17" s="77"/>
+      <c r="N17" s="77"/>
+      <c r="O17" s="87" t="s">
         <v>234</v>
       </c>
-      <c r="P17" s="80"/>
-      <c r="Q17" s="80"/>
-      <c r="R17" s="80"/>
-      <c r="S17" s="90" t="s">
+      <c r="P17" s="77"/>
+      <c r="Q17" s="77"/>
+      <c r="R17" s="77"/>
+      <c r="S17" s="87" t="s">
         <v>235</v>
       </c>
-      <c r="T17" s="90" t="s">
+      <c r="T17" s="87" t="s">
         <v>236</v>
       </c>
-      <c r="U17" s="90" t="s">
+      <c r="U17" s="87" t="s">
         <v>237</v>
       </c>
-      <c r="V17" s="80"/>
-      <c r="W17" s="90" t="s">
+      <c r="V17" s="77"/>
+      <c r="W17" s="87" t="s">
         <v>238</v>
       </c>
-      <c r="X17" s="80" t="s">
+      <c r="X17" s="77" t="s">
         <v>239</v>
       </c>
-      <c r="Y17" s="90" t="s">
+      <c r="Y17" s="87" t="s">
         <v>240</v>
       </c>
-      <c r="Z17" s="90" t="s">
+      <c r="Z17" s="87" t="s">
         <v>241</v>
       </c>
-      <c r="AA17" s="90" t="s">
+      <c r="AA17" s="87" t="s">
         <v>242</v>
       </c>
-      <c r="AB17" s="90" t="s">
+      <c r="AB17" s="87" t="s">
         <v>243</v>
       </c>
-      <c r="AC17" s="80"/>
-      <c r="AD17" s="80"/>
-      <c r="AE17" s="80"/>
-      <c r="AF17" s="80"/>
-      <c r="AG17" s="80"/>
-      <c r="AH17" s="90" t="s">
+      <c r="AC17" s="77"/>
+      <c r="AD17" s="77"/>
+      <c r="AE17" s="77"/>
+      <c r="AF17" s="77"/>
+      <c r="AG17" s="77"/>
+      <c r="AH17" s="87" t="s">
         <v>244</v>
       </c>
-      <c r="AI17" s="80"/>
-      <c r="AJ17" s="80"/>
-      <c r="AK17" s="80"/>
-      <c r="AL17" s="80" t="s">
+      <c r="AI17" s="77"/>
+      <c r="AJ17" s="77"/>
+      <c r="AK17" s="77"/>
+      <c r="AL17" s="77" t="s">
         <v>245</v>
       </c>
-      <c r="AM17" s="90" t="s">
+      <c r="AM17" s="87" t="s">
         <v>246</v>
       </c>
-      <c r="AN17" s="90" t="s">
+      <c r="AN17" s="87" t="s">
         <v>247</v>
       </c>
-      <c r="AO17" s="90" t="s">
+      <c r="AO17" s="87" t="s">
         <v>248</v>
       </c>
-      <c r="AP17" s="90" t="s">
+      <c r="AP17" s="87" t="s">
         <v>249</v>
       </c>
-      <c r="AQ17" s="80"/>
-      <c r="AR17" s="90" t="s">
+      <c r="AQ17" s="77"/>
+      <c r="AR17" s="87" t="s">
         <v>250</v>
       </c>
-      <c r="AS17" s="80" t="s">
+      <c r="AS17" s="77" t="s">
         <v>251</v>
       </c>
-      <c r="AT17" s="80" t="s">
+      <c r="AT17" s="77" t="s">
         <v>252</v>
       </c>
-      <c r="AU17" s="90" t="s">
+      <c r="AU17" s="87" t="s">
         <v>253</v>
       </c>
-      <c r="AV17" s="90" t="s">
+      <c r="AV17" s="87" t="s">
         <v>254</v>
       </c>
-      <c r="AW17" s="90" t="s">
+      <c r="AW17" s="87" t="s">
         <v>255</v>
       </c>
-      <c r="AX17" s="80"/>
-      <c r="AY17" s="90" t="s">
+      <c r="AX17" s="77"/>
+      <c r="AY17" s="87" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="18" ht="86.4" spans="1:51">
-      <c r="A18" s="86"/>
-      <c r="B18" s="87" t="s">
+      <c r="A18" s="83"/>
+      <c r="B18" s="84" t="s">
         <v>257</v>
       </c>
-      <c r="C18" s="88"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="80"/>
-      <c r="G18" s="80"/>
-      <c r="H18" s="80"/>
-      <c r="I18" s="80"/>
-      <c r="J18" s="80"/>
-      <c r="K18" s="90" t="s">
+      <c r="C18" s="85"/>
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="77"/>
+      <c r="J18" s="77"/>
+      <c r="K18" s="87" t="s">
         <v>258</v>
       </c>
-      <c r="L18" s="80"/>
-      <c r="M18" s="80"/>
-      <c r="N18" s="80"/>
-      <c r="O18" s="80"/>
-      <c r="P18" s="80"/>
-      <c r="Q18" s="80"/>
-      <c r="R18" s="80"/>
-      <c r="S18" s="80"/>
-      <c r="T18" s="80"/>
-      <c r="U18" s="80"/>
-      <c r="V18" s="80"/>
-      <c r="W18" s="80"/>
-      <c r="X18" s="80"/>
-      <c r="Y18" s="80"/>
-      <c r="Z18" s="90" t="s">
+      <c r="L18" s="77"/>
+      <c r="M18" s="77"/>
+      <c r="N18" s="77"/>
+      <c r="O18" s="77"/>
+      <c r="P18" s="77"/>
+      <c r="Q18" s="77"/>
+      <c r="R18" s="77"/>
+      <c r="S18" s="77"/>
+      <c r="T18" s="77"/>
+      <c r="U18" s="77"/>
+      <c r="V18" s="77"/>
+      <c r="W18" s="77"/>
+      <c r="X18" s="77"/>
+      <c r="Y18" s="77"/>
+      <c r="Z18" s="87" t="s">
         <v>259</v>
       </c>
-      <c r="AA18" s="90" t="s">
+      <c r="AA18" s="87" t="s">
         <v>260</v>
       </c>
-      <c r="AB18" s="90" t="s">
+      <c r="AB18" s="87" t="s">
         <v>261</v>
       </c>
-      <c r="AC18" s="90" t="s">
+      <c r="AC18" s="87" t="s">
         <v>262</v>
       </c>
-      <c r="AD18" s="80"/>
-      <c r="AE18" s="80"/>
-      <c r="AF18" s="80"/>
-      <c r="AG18" s="80"/>
-      <c r="AH18" s="80"/>
-      <c r="AI18" s="80" t="s">
+      <c r="AD18" s="77"/>
+      <c r="AE18" s="77"/>
+      <c r="AF18" s="77"/>
+      <c r="AG18" s="77"/>
+      <c r="AH18" s="77"/>
+      <c r="AI18" s="77" t="s">
         <v>263</v>
       </c>
-      <c r="AJ18" s="80"/>
-      <c r="AK18" s="80" t="s">
+      <c r="AJ18" s="77"/>
+      <c r="AK18" s="77" t="s">
         <v>263</v>
       </c>
-      <c r="AL18" s="80"/>
-      <c r="AM18" s="80"/>
-      <c r="AN18" s="90" t="s">
+      <c r="AL18" s="77"/>
+      <c r="AM18" s="77"/>
+      <c r="AN18" s="87" t="s">
         <v>264</v>
       </c>
-      <c r="AO18" s="80"/>
-      <c r="AP18" s="80"/>
-      <c r="AQ18" s="80"/>
-      <c r="AR18" s="80"/>
-      <c r="AS18" s="80"/>
-      <c r="AT18" s="80"/>
-      <c r="AU18" s="80"/>
-      <c r="AV18" s="90" t="s">
+      <c r="AO18" s="77"/>
+      <c r="AP18" s="77"/>
+      <c r="AQ18" s="77"/>
+      <c r="AR18" s="77"/>
+      <c r="AS18" s="77"/>
+      <c r="AT18" s="77"/>
+      <c r="AU18" s="77"/>
+      <c r="AV18" s="87" t="s">
         <v>265</v>
       </c>
-      <c r="AW18" s="90" t="s">
+      <c r="AW18" s="87" t="s">
         <v>266</v>
       </c>
-      <c r="AX18" s="80"/>
-      <c r="AY18" s="90" t="s">
+      <c r="AX18" s="77"/>
+      <c r="AY18" s="87" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="19" ht="43.2" spans="1:51">
-      <c r="A19" s="86"/>
-      <c r="B19" s="87" t="s">
+      <c r="A19" s="83"/>
+      <c r="B19" s="84" t="s">
         <v>267</v>
       </c>
-      <c r="C19" s="88"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
-      <c r="G19" s="80"/>
-      <c r="H19" s="90" t="s">
+      <c r="C19" s="85"/>
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="87" t="s">
         <v>268</v>
       </c>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="90" t="s">
+      <c r="I19" s="77"/>
+      <c r="J19" s="77"/>
+      <c r="K19" s="87" t="s">
         <v>268</v>
       </c>
-      <c r="L19" s="80" t="s">
+      <c r="L19" s="77" t="s">
         <v>269</v>
       </c>
-      <c r="M19" s="80"/>
-      <c r="N19" s="80"/>
-      <c r="O19" s="80"/>
-      <c r="P19" s="80"/>
-      <c r="Q19" s="80"/>
-      <c r="R19" s="80"/>
-      <c r="S19" s="80"/>
-      <c r="T19" s="80"/>
-      <c r="U19" s="80"/>
-      <c r="V19" s="80"/>
-      <c r="W19" s="80"/>
-      <c r="X19" s="80"/>
-      <c r="Y19" s="80"/>
-      <c r="Z19" s="80"/>
-      <c r="AA19" s="80"/>
-      <c r="AB19" s="80"/>
-      <c r="AC19" s="80"/>
-      <c r="AD19" s="80"/>
-      <c r="AE19" s="80" t="s">
+      <c r="M19" s="77"/>
+      <c r="N19" s="77"/>
+      <c r="O19" s="77"/>
+      <c r="P19" s="77"/>
+      <c r="Q19" s="77"/>
+      <c r="R19" s="77"/>
+      <c r="S19" s="77"/>
+      <c r="T19" s="77"/>
+      <c r="U19" s="77"/>
+      <c r="V19" s="77"/>
+      <c r="W19" s="77"/>
+      <c r="X19" s="77"/>
+      <c r="Y19" s="77"/>
+      <c r="Z19" s="77"/>
+      <c r="AA19" s="77"/>
+      <c r="AB19" s="77"/>
+      <c r="AC19" s="77"/>
+      <c r="AD19" s="77"/>
+      <c r="AE19" s="77" t="s">
         <v>269</v>
       </c>
-      <c r="AF19" s="80"/>
-      <c r="AG19" s="80"/>
-      <c r="AH19" s="80"/>
-      <c r="AI19" s="80"/>
-      <c r="AJ19" s="80"/>
-      <c r="AK19" s="80"/>
-      <c r="AL19" s="80"/>
-      <c r="AM19" s="80"/>
-      <c r="AN19" s="80"/>
-      <c r="AO19" s="80"/>
-      <c r="AP19" s="80" t="s">
+      <c r="AF19" s="77"/>
+      <c r="AG19" s="77"/>
+      <c r="AH19" s="77"/>
+      <c r="AI19" s="77"/>
+      <c r="AJ19" s="77"/>
+      <c r="AK19" s="77"/>
+      <c r="AL19" s="77"/>
+      <c r="AM19" s="77"/>
+      <c r="AN19" s="77"/>
+      <c r="AO19" s="77"/>
+      <c r="AP19" s="77" t="s">
         <v>269</v>
       </c>
-      <c r="AQ19" s="80"/>
-      <c r="AR19" s="80"/>
-      <c r="AS19" s="80"/>
-      <c r="AT19" s="80"/>
-      <c r="AU19" s="80"/>
-      <c r="AV19" s="90"/>
-      <c r="AW19" s="90"/>
-      <c r="AX19" s="80"/>
-      <c r="AY19" s="90" t="s">
+      <c r="AQ19" s="77"/>
+      <c r="AR19" s="77"/>
+      <c r="AS19" s="77"/>
+      <c r="AT19" s="77"/>
+      <c r="AU19" s="77"/>
+      <c r="AV19" s="87"/>
+      <c r="AW19" s="87"/>
+      <c r="AX19" s="77"/>
+      <c r="AY19" s="87" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="20" ht="57.6" spans="1:51">
-      <c r="A20" s="86"/>
-      <c r="B20" s="87" t="s">
+      <c r="A20" s="83"/>
+      <c r="B20" s="84" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="88"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="80"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="80"/>
-      <c r="L20" s="80"/>
-      <c r="M20" s="80"/>
-      <c r="N20" s="80"/>
-      <c r="O20" s="80"/>
-      <c r="P20" s="80"/>
-      <c r="Q20" s="80"/>
-      <c r="R20" s="80"/>
-      <c r="S20" s="80"/>
-      <c r="T20" s="80"/>
-      <c r="U20" s="80"/>
-      <c r="V20" s="80"/>
-      <c r="W20" s="80"/>
-      <c r="X20" s="80"/>
-      <c r="Y20" s="80"/>
-      <c r="Z20" s="80"/>
-      <c r="AA20" s="80"/>
-      <c r="AB20" s="80"/>
-      <c r="AC20" s="80"/>
-      <c r="AD20" s="80"/>
-      <c r="AE20" s="80"/>
-      <c r="AF20" s="80"/>
-      <c r="AG20" s="80"/>
-      <c r="AH20" s="80"/>
-      <c r="AI20" s="80"/>
-      <c r="AJ20" s="90" t="s">
+      <c r="C20" s="85"/>
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="77"/>
+      <c r="G20" s="77"/>
+      <c r="H20" s="77"/>
+      <c r="I20" s="77"/>
+      <c r="J20" s="77"/>
+      <c r="K20" s="77"/>
+      <c r="L20" s="77"/>
+      <c r="M20" s="77"/>
+      <c r="N20" s="77"/>
+      <c r="O20" s="77"/>
+      <c r="P20" s="77"/>
+      <c r="Q20" s="77"/>
+      <c r="R20" s="77"/>
+      <c r="S20" s="77"/>
+      <c r="T20" s="77"/>
+      <c r="U20" s="77"/>
+      <c r="V20" s="77"/>
+      <c r="W20" s="77"/>
+      <c r="X20" s="77"/>
+      <c r="Y20" s="77"/>
+      <c r="Z20" s="77"/>
+      <c r="AA20" s="77"/>
+      <c r="AB20" s="77"/>
+      <c r="AC20" s="77"/>
+      <c r="AD20" s="77"/>
+      <c r="AE20" s="77"/>
+      <c r="AF20" s="77"/>
+      <c r="AG20" s="77"/>
+      <c r="AH20" s="77"/>
+      <c r="AI20" s="77"/>
+      <c r="AJ20" s="87" t="s">
         <v>272</v>
       </c>
-      <c r="AK20" s="80"/>
-      <c r="AL20" s="80"/>
-      <c r="AM20" s="80"/>
-      <c r="AN20" s="80"/>
-      <c r="AO20" s="80"/>
-      <c r="AP20" s="80"/>
-      <c r="AQ20" s="80"/>
-      <c r="AR20" s="80"/>
-      <c r="AS20" s="80"/>
-      <c r="AT20" s="80"/>
-      <c r="AU20" s="80"/>
-      <c r="AV20" s="90"/>
-      <c r="AW20" s="90"/>
-      <c r="AX20" s="80"/>
-      <c r="AY20" s="80"/>
+      <c r="AK20" s="77"/>
+      <c r="AL20" s="77"/>
+      <c r="AM20" s="77"/>
+      <c r="AN20" s="77"/>
+      <c r="AO20" s="77"/>
+      <c r="AP20" s="77"/>
+      <c r="AQ20" s="77"/>
+      <c r="AR20" s="77"/>
+      <c r="AS20" s="77"/>
+      <c r="AT20" s="77"/>
+      <c r="AU20" s="77"/>
+      <c r="AV20" s="87"/>
+      <c r="AW20" s="87"/>
+      <c r="AX20" s="77"/>
+      <c r="AY20" s="77"/>
     </row>
     <row r="21" ht="86.4" spans="1:51">
-      <c r="A21" s="86"/>
-      <c r="B21" s="91" t="s">
+      <c r="A21" s="83"/>
+      <c r="B21" s="88" t="s">
         <v>273</v>
       </c>
-      <c r="C21" s="89" t="s">
+      <c r="C21" s="86" t="s">
         <v>274</v>
       </c>
-      <c r="D21" s="89" t="s">
+      <c r="D21" s="86" t="s">
         <v>274</v>
       </c>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="80"/>
-      <c r="K21" s="90" t="s">
+      <c r="E21" s="77"/>
+      <c r="F21" s="77"/>
+      <c r="G21" s="77"/>
+      <c r="H21" s="77"/>
+      <c r="I21" s="77"/>
+      <c r="J21" s="77"/>
+      <c r="K21" s="87" t="s">
         <v>275</v>
       </c>
-      <c r="L21" s="80" t="s">
+      <c r="L21" s="77" t="s">
         <v>276</v>
       </c>
-      <c r="M21" s="80"/>
-      <c r="N21" s="80"/>
-      <c r="O21" s="80"/>
-      <c r="P21" s="80"/>
-      <c r="Q21" s="80"/>
-      <c r="R21" s="80"/>
-      <c r="S21" s="80"/>
-      <c r="T21" s="80"/>
-      <c r="U21" s="80"/>
-      <c r="V21" s="80"/>
-      <c r="W21" s="80"/>
-      <c r="X21" s="80"/>
-      <c r="Y21" s="80"/>
-      <c r="Z21" s="80"/>
-      <c r="AA21" s="80"/>
-      <c r="AB21" s="80"/>
-      <c r="AC21" s="80"/>
-      <c r="AD21" s="80"/>
-      <c r="AE21" s="80" t="s">
+      <c r="M21" s="77"/>
+      <c r="N21" s="77"/>
+      <c r="O21" s="77"/>
+      <c r="P21" s="77"/>
+      <c r="Q21" s="77"/>
+      <c r="R21" s="77"/>
+      <c r="S21" s="77"/>
+      <c r="T21" s="77"/>
+      <c r="U21" s="77"/>
+      <c r="V21" s="77"/>
+      <c r="W21" s="77"/>
+      <c r="X21" s="77"/>
+      <c r="Y21" s="77"/>
+      <c r="Z21" s="77"/>
+      <c r="AA21" s="77"/>
+      <c r="AB21" s="77"/>
+      <c r="AC21" s="77"/>
+      <c r="AD21" s="77"/>
+      <c r="AE21" s="77" t="s">
         <v>277</v>
       </c>
-      <c r="AF21" s="90" t="s">
+      <c r="AF21" s="87" t="s">
         <v>278</v>
       </c>
-      <c r="AG21" s="90" t="s">
+      <c r="AG21" s="87" t="s">
         <v>279</v>
       </c>
-      <c r="AH21" s="80"/>
-      <c r="AI21" s="90" t="s">
+      <c r="AH21" s="77"/>
+      <c r="AI21" s="87" t="s">
         <v>280</v>
       </c>
-      <c r="AJ21" s="90" t="s">
+      <c r="AJ21" s="87" t="s">
         <v>281</v>
       </c>
-      <c r="AK21" s="80"/>
-      <c r="AL21" s="80"/>
-      <c r="AM21" s="80"/>
-      <c r="AN21" s="80"/>
-      <c r="AO21" s="80" t="s">
+      <c r="AK21" s="77"/>
+      <c r="AL21" s="77"/>
+      <c r="AM21" s="77"/>
+      <c r="AN21" s="77"/>
+      <c r="AO21" s="77" t="s">
         <v>276</v>
       </c>
-      <c r="AP21" s="80" t="s">
+      <c r="AP21" s="77" t="s">
         <v>276</v>
       </c>
-      <c r="AQ21" s="80"/>
-      <c r="AR21" s="80"/>
-      <c r="AS21" s="80"/>
-      <c r="AT21" s="80" t="s">
+      <c r="AQ21" s="77"/>
+      <c r="AR21" s="77"/>
+      <c r="AS21" s="77"/>
+      <c r="AT21" s="77" t="s">
         <v>277</v>
       </c>
-      <c r="AU21" s="80"/>
-      <c r="AV21" s="80"/>
-      <c r="AW21" s="80"/>
-      <c r="AX21" s="90" t="s">
+      <c r="AU21" s="77"/>
+      <c r="AV21" s="77"/>
+      <c r="AW21" s="77"/>
+      <c r="AX21" s="87" t="s">
         <v>282</v>
       </c>
-      <c r="AY21" s="90" t="s">
+      <c r="AY21" s="87" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:51">
-      <c r="A22" s="92"/>
-      <c r="B22" s="87" t="s">
+      <c r="A22" s="89"/>
+      <c r="B22" s="84" t="s">
         <v>284</v>
       </c>
-      <c r="C22" s="88"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="80"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="80"/>
-      <c r="J22" s="80"/>
-      <c r="K22" s="80"/>
-      <c r="L22" s="80"/>
-      <c r="M22" s="80"/>
-      <c r="N22" s="80"/>
-      <c r="O22" s="80"/>
-      <c r="P22" s="80"/>
-      <c r="Q22" s="80"/>
-      <c r="R22" s="80"/>
-      <c r="S22" s="80"/>
-      <c r="T22" s="80"/>
-      <c r="U22" s="80"/>
-      <c r="V22" s="80"/>
-      <c r="W22" s="80"/>
-      <c r="X22" s="80"/>
-      <c r="Y22" s="80"/>
-      <c r="Z22" s="80"/>
-      <c r="AA22" s="80"/>
-      <c r="AB22" s="80"/>
-      <c r="AC22" s="80"/>
-      <c r="AD22" s="80"/>
-      <c r="AE22" s="80"/>
-      <c r="AF22" s="80"/>
-      <c r="AG22" s="80"/>
-      <c r="AH22" s="80"/>
-      <c r="AI22" s="80"/>
-      <c r="AJ22" s="80"/>
-      <c r="AK22" s="80"/>
-      <c r="AL22" s="80"/>
-      <c r="AM22" s="80"/>
-      <c r="AN22" s="80"/>
-      <c r="AO22" s="80"/>
-      <c r="AP22" s="80"/>
-      <c r="AQ22" s="80"/>
-      <c r="AR22" s="80"/>
-      <c r="AS22" s="80"/>
-      <c r="AT22" s="80"/>
-      <c r="AU22" s="80"/>
-      <c r="AV22" s="90"/>
-      <c r="AW22" s="90"/>
-      <c r="AX22" s="80"/>
-      <c r="AY22" s="80"/>
+      <c r="C22" s="85"/>
+      <c r="D22" s="77"/>
+      <c r="E22" s="77"/>
+      <c r="F22" s="77"/>
+      <c r="G22" s="77"/>
+      <c r="H22" s="77"/>
+      <c r="I22" s="77"/>
+      <c r="J22" s="77"/>
+      <c r="K22" s="77"/>
+      <c r="L22" s="77"/>
+      <c r="M22" s="77"/>
+      <c r="N22" s="77"/>
+      <c r="O22" s="77"/>
+      <c r="P22" s="77"/>
+      <c r="Q22" s="77"/>
+      <c r="R22" s="77"/>
+      <c r="S22" s="77"/>
+      <c r="T22" s="77"/>
+      <c r="U22" s="77"/>
+      <c r="V22" s="77"/>
+      <c r="W22" s="77"/>
+      <c r="X22" s="77"/>
+      <c r="Y22" s="77"/>
+      <c r="Z22" s="77"/>
+      <c r="AA22" s="77"/>
+      <c r="AB22" s="77"/>
+      <c r="AC22" s="77"/>
+      <c r="AD22" s="77"/>
+      <c r="AE22" s="77"/>
+      <c r="AF22" s="77"/>
+      <c r="AG22" s="77"/>
+      <c r="AH22" s="77"/>
+      <c r="AI22" s="77"/>
+      <c r="AJ22" s="77"/>
+      <c r="AK22" s="77"/>
+      <c r="AL22" s="77"/>
+      <c r="AM22" s="77"/>
+      <c r="AN22" s="77"/>
+      <c r="AO22" s="77"/>
+      <c r="AP22" s="77"/>
+      <c r="AQ22" s="77"/>
+      <c r="AR22" s="77"/>
+      <c r="AS22" s="77"/>
+      <c r="AT22" s="77"/>
+      <c r="AU22" s="77"/>
+      <c r="AV22" s="87"/>
+      <c r="AW22" s="87"/>
+      <c r="AX22" s="77"/>
+      <c r="AY22" s="77"/>
     </row>
     <row r="24" ht="115.2" spans="1:51">
-      <c r="A24" s="70" t="s">
+      <c r="A24" s="67" t="s">
         <v>285</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="25" t="s">
         <v>286</v>
       </c>
-      <c r="C24" s="75" t="s">
+      <c r="C24" s="72" t="s">
         <v>287</v>
       </c>
-      <c r="D24" s="75" t="s">
+      <c r="D24" s="72" t="s">
         <v>170</v>
       </c>
-      <c r="E24" s="75" t="s">
+      <c r="E24" s="72" t="s">
         <v>288</v>
       </c>
-      <c r="F24" s="75" t="s">
+      <c r="F24" s="72" t="s">
         <v>289</v>
       </c>
-      <c r="G24" s="75" t="s">
+      <c r="G24" s="72" t="s">
         <v>290</v>
       </c>
-      <c r="H24" s="75" t="s">
+      <c r="H24" s="72" t="s">
         <v>291</v>
       </c>
-      <c r="I24" s="75" t="s">
+      <c r="I24" s="72" t="s">
         <v>292</v>
       </c>
-      <c r="J24" s="75" t="s">
+      <c r="J24" s="72" t="s">
         <v>293</v>
       </c>
-      <c r="K24" s="75" t="s">
+      <c r="K24" s="72" t="s">
         <v>294</v>
       </c>
-      <c r="L24" s="75" t="s">
+      <c r="L24" s="72" t="s">
         <v>295</v>
       </c>
-      <c r="M24" s="75" t="s">
+      <c r="M24" s="72" t="s">
         <v>296</v>
       </c>
-      <c r="N24" s="75" t="s">
+      <c r="N24" s="72" t="s">
         <v>297</v>
       </c>
-      <c r="O24" s="75" t="s">
+      <c r="O24" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="P24" s="75" t="s">
+      <c r="P24" s="72" t="s">
         <v>298</v>
       </c>
-      <c r="Q24" s="75" t="s">
+      <c r="Q24" s="72" t="s">
         <v>299</v>
       </c>
-      <c r="R24" s="75" t="s">
+      <c r="R24" s="72" t="s">
         <v>300</v>
       </c>
-      <c r="S24" s="75" t="s">
+      <c r="S24" s="72" t="s">
         <v>301</v>
       </c>
-      <c r="T24" s="75" t="s">
+      <c r="T24" s="72" t="s">
         <v>302</v>
       </c>
-      <c r="U24" s="75" t="s">
+      <c r="U24" s="72" t="s">
         <v>303</v>
       </c>
-      <c r="V24" s="75" t="s">
+      <c r="V24" s="72" t="s">
         <v>304</v>
       </c>
-      <c r="W24" s="75" t="s">
+      <c r="W24" s="72" t="s">
         <v>305</v>
       </c>
-      <c r="X24" s="75" t="s">
+      <c r="X24" s="72" t="s">
         <v>306</v>
       </c>
-      <c r="Y24" s="75" t="s">
+      <c r="Y24" s="72" t="s">
         <v>307</v>
       </c>
-      <c r="Z24" s="75" t="s">
+      <c r="Z24" s="72" t="s">
         <v>308</v>
       </c>
-      <c r="AA24" s="75" t="s">
+      <c r="AA24" s="72" t="s">
         <v>309</v>
       </c>
-      <c r="AB24" s="75" t="s">
+      <c r="AB24" s="72" t="s">
         <v>310</v>
       </c>
-      <c r="AC24" s="75" t="s">
+      <c r="AC24" s="72" t="s">
         <v>311</v>
       </c>
-      <c r="AD24" s="75" t="s">
+      <c r="AD24" s="72" t="s">
         <v>312</v>
       </c>
-      <c r="AE24" s="75" t="s">
+      <c r="AE24" s="72" t="s">
         <v>313</v>
       </c>
-      <c r="AF24" s="75" t="s">
+      <c r="AF24" s="72" t="s">
         <v>314</v>
       </c>
-      <c r="AG24" s="75" t="s">
+      <c r="AG24" s="72" t="s">
         <v>315</v>
       </c>
-      <c r="AH24" s="75" t="s">
+      <c r="AH24" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AI24" s="75" t="s">
+      <c r="AI24" s="72" t="s">
         <v>316</v>
       </c>
-      <c r="AJ24" s="75" t="s">
+      <c r="AJ24" s="72" t="s">
         <v>317</v>
       </c>
-      <c r="AK24" s="75" t="s">
+      <c r="AK24" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AL24" s="75" t="s">
+      <c r="AL24" s="72" t="s">
         <v>318</v>
       </c>
-      <c r="AM24" s="75" t="s">
+      <c r="AM24" s="72" t="s">
         <v>319</v>
       </c>
-      <c r="AN24" s="75" t="s">
+      <c r="AN24" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AO24" s="75" t="s">
+      <c r="AO24" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AP24" s="75" t="s">
+      <c r="AP24" s="72" t="s">
         <v>315</v>
       </c>
-      <c r="AQ24" s="75" t="s">
+      <c r="AQ24" s="72" t="s">
         <v>315</v>
       </c>
-      <c r="AR24" s="75" t="s">
+      <c r="AR24" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AS24" s="75" t="s">
+      <c r="AS24" s="72" t="s">
         <v>320</v>
       </c>
-      <c r="AT24" s="75" t="s">
+      <c r="AT24" s="72" t="s">
         <v>321</v>
       </c>
-      <c r="AU24" s="75" t="s">
+      <c r="AU24" s="72" t="s">
         <v>322</v>
       </c>
-      <c r="AV24" s="75" t="s">
+      <c r="AV24" s="72" t="s">
         <v>323</v>
       </c>
-      <c r="AW24" s="76" t="s">
+      <c r="AW24" s="73" t="s">
         <v>324</v>
       </c>
-      <c r="AX24" s="76" t="s">
+      <c r="AX24" s="73" t="s">
         <v>315</v>
       </c>
-      <c r="AY24" s="76" t="s">
+      <c r="AY24" s="73" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:51">
-      <c r="A25" s="72"/>
-      <c r="B25" s="27" t="s">
+      <c r="A25" s="69"/>
+      <c r="B25" s="25" t="s">
         <v>325</v>
       </c>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="E25" s="75"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="75"/>
-      <c r="J25" s="75"/>
-      <c r="K25" s="75"/>
-      <c r="L25" s="75"/>
-      <c r="M25" s="75"/>
-      <c r="N25" s="75"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="75"/>
-      <c r="S25" s="75"/>
-      <c r="T25" s="75"/>
-      <c r="U25" s="75"/>
-      <c r="V25" s="75"/>
-      <c r="W25" s="75"/>
-      <c r="X25" s="75"/>
-      <c r="Y25" s="75"/>
-      <c r="Z25" s="75"/>
-      <c r="AA25" s="75"/>
-      <c r="AB25" s="75"/>
-      <c r="AC25" s="75"/>
-      <c r="AD25" s="75"/>
-      <c r="AE25" s="75"/>
-      <c r="AF25" s="75"/>
-      <c r="AG25" s="75"/>
-      <c r="AH25" s="75"/>
-      <c r="AI25" s="75"/>
-      <c r="AJ25" s="75"/>
-      <c r="AK25" s="75"/>
-      <c r="AL25" s="75"/>
-      <c r="AM25" s="75"/>
-      <c r="AN25" s="75"/>
-      <c r="AO25" s="75"/>
-      <c r="AP25" s="75"/>
-      <c r="AQ25" s="75"/>
-      <c r="AR25" s="75"/>
-      <c r="AS25" s="75"/>
-      <c r="AT25" s="75"/>
-      <c r="AU25" s="75"/>
-      <c r="AV25" s="75"/>
-      <c r="AW25" s="76"/>
-      <c r="AX25" s="76"/>
-      <c r="AY25" s="76"/>
+      <c r="C25" s="72"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="72"/>
+      <c r="G25" s="72"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="72"/>
+      <c r="J25" s="72"/>
+      <c r="K25" s="72"/>
+      <c r="L25" s="72"/>
+      <c r="M25" s="72"/>
+      <c r="N25" s="72"/>
+      <c r="O25" s="72"/>
+      <c r="P25" s="72"/>
+      <c r="Q25" s="72"/>
+      <c r="R25" s="72"/>
+      <c r="S25" s="72"/>
+      <c r="T25" s="72"/>
+      <c r="U25" s="72"/>
+      <c r="V25" s="72"/>
+      <c r="W25" s="72"/>
+      <c r="X25" s="72"/>
+      <c r="Y25" s="72"/>
+      <c r="Z25" s="72"/>
+      <c r="AA25" s="72"/>
+      <c r="AB25" s="72"/>
+      <c r="AC25" s="72"/>
+      <c r="AD25" s="72"/>
+      <c r="AE25" s="72"/>
+      <c r="AF25" s="72"/>
+      <c r="AG25" s="72"/>
+      <c r="AH25" s="72"/>
+      <c r="AI25" s="72"/>
+      <c r="AJ25" s="72"/>
+      <c r="AK25" s="72"/>
+      <c r="AL25" s="72"/>
+      <c r="AM25" s="72"/>
+      <c r="AN25" s="72"/>
+      <c r="AO25" s="72"/>
+      <c r="AP25" s="72"/>
+      <c r="AQ25" s="72"/>
+      <c r="AR25" s="72"/>
+      <c r="AS25" s="72"/>
+      <c r="AT25" s="72"/>
+      <c r="AU25" s="72"/>
+      <c r="AV25" s="72"/>
+      <c r="AW25" s="73"/>
+      <c r="AX25" s="73"/>
+      <c r="AY25" s="73"/>
     </row>
     <row r="26" customFormat="1" ht="100.8" spans="1:51">
-      <c r="A26" s="77"/>
-      <c r="B26" s="27" t="s">
+      <c r="A26" s="74"/>
+      <c r="B26" s="25" t="s">
         <v>326</v>
       </c>
-      <c r="C26" s="75"/>
-      <c r="D26" s="75"/>
-      <c r="E26" s="75"/>
-      <c r="F26" s="75"/>
-      <c r="G26" s="75" t="s">
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="72"/>
+      <c r="G26" s="72" t="s">
         <v>327</v>
       </c>
-      <c r="H26" s="75"/>
-      <c r="I26" s="75"/>
-      <c r="J26" s="75"/>
-      <c r="K26" s="75"/>
-      <c r="L26" s="75"/>
-      <c r="M26" s="75" t="s">
+      <c r="H26" s="72"/>
+      <c r="I26" s="72"/>
+      <c r="J26" s="72"/>
+      <c r="K26" s="72"/>
+      <c r="L26" s="72"/>
+      <c r="M26" s="72" t="s">
         <v>328</v>
       </c>
-      <c r="N26" s="75" t="s">
+      <c r="N26" s="72" t="s">
         <v>329</v>
       </c>
-      <c r="O26" s="75"/>
-      <c r="P26" s="75"/>
-      <c r="Q26" s="75"/>
-      <c r="R26" s="75"/>
-      <c r="S26" s="75"/>
-      <c r="T26" s="75"/>
-      <c r="U26" s="75"/>
-      <c r="V26" s="75"/>
-      <c r="W26" s="75"/>
-      <c r="X26" s="75"/>
-      <c r="Y26" s="75"/>
-      <c r="Z26" s="75"/>
-      <c r="AA26" s="75"/>
-      <c r="AB26" s="75"/>
-      <c r="AC26" s="75"/>
-      <c r="AD26" s="75"/>
-      <c r="AE26" s="75"/>
-      <c r="AF26" s="75"/>
-      <c r="AG26" s="75"/>
-      <c r="AH26" s="75"/>
-      <c r="AI26" s="75"/>
-      <c r="AJ26" s="75"/>
-      <c r="AK26" s="75"/>
-      <c r="AL26" s="75"/>
-      <c r="AM26" s="75"/>
-      <c r="AN26" s="75"/>
-      <c r="AO26" s="75" t="s">
+      <c r="O26" s="72"/>
+      <c r="P26" s="72"/>
+      <c r="Q26" s="72"/>
+      <c r="R26" s="72"/>
+      <c r="S26" s="72"/>
+      <c r="T26" s="72"/>
+      <c r="U26" s="72"/>
+      <c r="V26" s="72"/>
+      <c r="W26" s="72"/>
+      <c r="X26" s="72"/>
+      <c r="Y26" s="72"/>
+      <c r="Z26" s="72"/>
+      <c r="AA26" s="72"/>
+      <c r="AB26" s="72"/>
+      <c r="AC26" s="72"/>
+      <c r="AD26" s="72"/>
+      <c r="AE26" s="72"/>
+      <c r="AF26" s="72"/>
+      <c r="AG26" s="72"/>
+      <c r="AH26" s="72"/>
+      <c r="AI26" s="72"/>
+      <c r="AJ26" s="72"/>
+      <c r="AK26" s="72"/>
+      <c r="AL26" s="72"/>
+      <c r="AM26" s="72"/>
+      <c r="AN26" s="72"/>
+      <c r="AO26" s="72" t="s">
         <v>330</v>
       </c>
-      <c r="AP26" s="75" t="s">
+      <c r="AP26" s="72" t="s">
         <v>331</v>
       </c>
-      <c r="AQ26" s="75"/>
-      <c r="AR26" s="75"/>
-      <c r="AS26" s="75"/>
-      <c r="AT26" s="75"/>
-      <c r="AU26" s="75"/>
-      <c r="AV26" s="75"/>
-      <c r="AW26" s="76"/>
-      <c r="AX26" s="76"/>
-      <c r="AY26" s="76"/>
+      <c r="AQ26" s="72"/>
+      <c r="AR26" s="72"/>
+      <c r="AS26" s="72"/>
+      <c r="AT26" s="72"/>
+      <c r="AU26" s="72"/>
+      <c r="AV26" s="72"/>
+      <c r="AW26" s="73"/>
+      <c r="AX26" s="73"/>
+      <c r="AY26" s="73"/>
     </row>
-    <row r="27" s="54" customFormat="1" ht="28.8" spans="1:51">
-      <c r="A27" s="78" t="s">
+    <row r="27" s="51" customFormat="1" ht="28.8" spans="1:51">
+      <c r="A27" s="75" t="s">
         <v>332</v>
       </c>
-      <c r="B27" s="90" t="s">
+      <c r="B27" s="87" t="s">
         <v>333</v>
       </c>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
-      <c r="H27" s="93"/>
-      <c r="I27" s="93"/>
-      <c r="J27" s="93"/>
-      <c r="K27" s="93"/>
-      <c r="L27" s="93"/>
-      <c r="M27" s="93"/>
-      <c r="N27" s="93"/>
-      <c r="O27" s="93"/>
-      <c r="P27" s="93"/>
-      <c r="Q27" s="93"/>
-      <c r="R27" s="93"/>
-      <c r="S27" s="93"/>
-      <c r="T27" s="93"/>
-      <c r="U27" s="93"/>
-      <c r="V27" s="93"/>
-      <c r="W27" s="93"/>
-      <c r="X27" s="93"/>
-      <c r="Y27" s="93"/>
-      <c r="Z27" s="93"/>
-      <c r="AA27" s="93"/>
-      <c r="AB27" s="93"/>
-      <c r="AC27" s="93"/>
-      <c r="AD27" s="93"/>
-      <c r="AE27" s="93"/>
-      <c r="AF27" s="93"/>
-      <c r="AG27" s="93"/>
-      <c r="AH27" s="93"/>
-      <c r="AI27" s="93"/>
-      <c r="AJ27" s="93"/>
-      <c r="AK27" s="93"/>
-      <c r="AL27" s="93"/>
-      <c r="AM27" s="93"/>
-      <c r="AN27" s="93"/>
-      <c r="AO27" s="93"/>
-      <c r="AP27" s="93"/>
-      <c r="AQ27" s="93"/>
-      <c r="AR27" s="93"/>
+      <c r="C27" s="90"/>
+      <c r="D27" s="90"/>
+      <c r="E27" s="90"/>
+      <c r="F27" s="90"/>
+      <c r="G27" s="90"/>
+      <c r="H27" s="90"/>
+      <c r="I27" s="90"/>
+      <c r="J27" s="90"/>
+      <c r="K27" s="90"/>
+      <c r="L27" s="90"/>
+      <c r="M27" s="90"/>
+      <c r="N27" s="90"/>
+      <c r="O27" s="90"/>
+      <c r="P27" s="90"/>
+      <c r="Q27" s="90"/>
+      <c r="R27" s="90"/>
+      <c r="S27" s="90"/>
+      <c r="T27" s="90"/>
+      <c r="U27" s="90"/>
+      <c r="V27" s="90"/>
+      <c r="W27" s="90"/>
+      <c r="X27" s="90"/>
+      <c r="Y27" s="90"/>
+      <c r="Z27" s="90"/>
+      <c r="AA27" s="90"/>
+      <c r="AB27" s="90"/>
+      <c r="AC27" s="90"/>
+      <c r="AD27" s="90"/>
+      <c r="AE27" s="90"/>
+      <c r="AF27" s="90"/>
+      <c r="AG27" s="90"/>
+      <c r="AH27" s="90"/>
+      <c r="AI27" s="90"/>
+      <c r="AJ27" s="90"/>
+      <c r="AK27" s="90"/>
+      <c r="AL27" s="90"/>
+      <c r="AM27" s="90"/>
+      <c r="AN27" s="90"/>
+      <c r="AO27" s="90"/>
+      <c r="AP27" s="90"/>
+      <c r="AQ27" s="90"/>
+      <c r="AR27" s="90"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -8651,10 +8599,10 @@
       <c r="D1" s="16" t="s">
         <v>337</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>338</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="16" t="s">
         <v>339</v>
       </c>
       <c r="G1" s="16" t="s">
@@ -8680,2043 +8628,2043 @@
       </c>
       <c r="V1" s="16"/>
       <c r="W1" s="16"/>
-      <c r="X1" s="18"/>
+      <c r="X1" s="17"/>
     </row>
     <row r="2" spans="1:24">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="22" t="s">
+      <c r="A2" s="18"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
-      <c r="L2" s="24" t="s">
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="22" t="s">
         <v>341</v>
       </c>
-      <c r="M2" s="24"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="24"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="24"/>
-      <c r="R2" s="24"/>
-      <c r="S2" s="24"/>
-      <c r="T2" s="24"/>
-      <c r="U2" s="22" t="s">
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="V2" s="23" t="s">
+      <c r="V2" s="21" t="s">
         <v>342</v>
       </c>
-      <c r="W2" s="23"/>
-      <c r="X2" s="25"/>
+      <c r="W2" s="21"/>
+      <c r="X2" s="23"/>
     </row>
     <row r="3" ht="87.15" spans="1:24">
-      <c r="A3" s="19"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="26" t="s">
+      <c r="A3" s="18"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="24" t="s">
         <v>180</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="I3" s="27" t="s">
+      <c r="I3" s="25" t="s">
         <v>343</v>
       </c>
-      <c r="J3" s="27" t="s">
+      <c r="J3" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="K3" s="27" t="s">
+      <c r="K3" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="L3" s="28" t="s">
+      <c r="L3" s="26" t="s">
         <v>344</v>
       </c>
-      <c r="M3" s="29" t="s">
+      <c r="M3" s="27" t="s">
         <v>217</v>
       </c>
-      <c r="N3" s="28" t="s">
+      <c r="N3" s="26" t="s">
         <v>345</v>
       </c>
-      <c r="O3" s="29" t="s">
+      <c r="O3" s="27" t="s">
         <v>218</v>
       </c>
-      <c r="P3" s="29" t="s">
+      <c r="P3" s="27" t="s">
         <v>229</v>
       </c>
-      <c r="Q3" s="29" t="s">
+      <c r="Q3" s="27" t="s">
         <v>257</v>
       </c>
-      <c r="R3" s="29" t="s">
+      <c r="R3" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="S3" s="28" t="s">
+      <c r="S3" s="26" t="s">
         <v>346</v>
       </c>
-      <c r="T3" s="28" t="s">
+      <c r="T3" s="26" t="s">
         <v>347</v>
       </c>
-      <c r="U3" s="26" t="s">
+      <c r="U3" s="24" t="s">
         <v>333</v>
       </c>
-      <c r="V3" s="27" t="s">
+      <c r="V3" s="25" t="s">
         <v>286</v>
       </c>
-      <c r="W3" s="27" t="s">
+      <c r="W3" s="25" t="s">
         <v>325</v>
       </c>
-      <c r="X3" s="30" t="s">
+      <c r="X3" s="28" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="4" s="12" customFormat="1" ht="158.4" spans="1:24">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="29" t="s">
         <v>348</v>
       </c>
-      <c r="C4" s="32" t="s">
+      <c r="C4" s="30" t="s">
         <v>349</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="E4" s="32"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="33" t="s">
+      <c r="G4" s="31" t="s">
         <v>148</v>
       </c>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="35" t="s">
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="33" t="s">
         <v>219</v>
       </c>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="35" t="s">
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="T4" s="33" t="s">
         <v>274</v>
       </c>
-      <c r="U4" s="33" t="s">
+      <c r="U4" s="31" t="s">
         <v>287</v>
       </c>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="37"/>
+      <c r="V4" s="31"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="35"/>
     </row>
     <row r="5" ht="100.8" spans="1:24">
-      <c r="A5" s="19"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="32" t="s">
+      <c r="A5" s="18"/>
+      <c r="B5" s="29"/>
+      <c r="C5" s="30" t="s">
         <v>351</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="E5" s="32"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="33" t="s">
+      <c r="E5" s="30"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="31" t="s">
         <v>353</v>
       </c>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="35" t="s">
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="31"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="33" t="s">
         <v>220</v>
       </c>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="35" t="s">
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34"/>
+      <c r="S5" s="34"/>
+      <c r="T5" s="33" t="s">
         <v>274</v>
       </c>
-      <c r="U5" s="33" t="s">
+      <c r="U5" s="31" t="s">
         <v>170</v>
       </c>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="37"/>
+      <c r="V5" s="31"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="35"/>
     </row>
     <row r="6" ht="144" spans="1:24">
-      <c r="A6" s="19"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="32" t="s">
+      <c r="A6" s="18"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="30" t="s">
         <v>354</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E6" s="32"/>
-      <c r="F6" s="38"/>
-      <c r="G6" s="33" t="s">
+      <c r="E6" s="30"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="31" t="s">
         <v>150</v>
       </c>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="33" t="s">
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="33"/>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="34"/>
+      <c r="S6" s="34"/>
+      <c r="T6" s="33"/>
+      <c r="U6" s="31" t="s">
         <v>356</v>
       </c>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="37"/>
+      <c r="V6" s="31"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="35"/>
     </row>
     <row r="7" ht="172.8" spans="1:24">
-      <c r="A7" s="19"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="32" t="s">
+      <c r="A7" s="18"/>
+      <c r="B7" s="29"/>
+      <c r="C7" s="30" t="s">
         <v>357</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E7" s="32"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="33" t="s">
+      <c r="E7" s="30"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="31" t="s">
         <v>151</v>
       </c>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="39" t="s">
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
-      <c r="S7" s="35"/>
-      <c r="T7" s="35"/>
-      <c r="U7" s="33" t="s">
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="33"/>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="33"/>
+      <c r="R7" s="33"/>
+      <c r="S7" s="33"/>
+      <c r="T7" s="33"/>
+      <c r="U7" s="31" t="s">
         <v>289</v>
       </c>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="37"/>
+      <c r="V7" s="31"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="35"/>
     </row>
     <row r="8" customFormat="1" ht="216" spans="1:24">
-      <c r="A8" s="19"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="32" t="s">
+      <c r="A8" s="18"/>
+      <c r="B8" s="29"/>
+      <c r="C8" s="30" t="s">
         <v>359</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="38"/>
-      <c r="G8" s="33" t="s">
+      <c r="E8" s="30"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="31" t="s">
         <v>361</v>
       </c>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="39"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="35" t="s">
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="31"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="36"/>
+      <c r="M8" s="36"/>
+      <c r="N8" s="36"/>
+      <c r="O8" s="33"/>
+      <c r="P8" s="33" t="s">
         <v>230</v>
       </c>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="35"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="33" t="s">
+      <c r="Q8" s="33"/>
+      <c r="R8" s="33"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="31" t="s">
         <v>290</v>
       </c>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="40" t="s">
+      <c r="V8" s="31"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="37" t="s">
         <v>327</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="100.8" spans="1:24">
-      <c r="A9" s="19"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="32" t="s">
+      <c r="A9" s="18"/>
+      <c r="B9" s="29"/>
+      <c r="C9" s="30" t="s">
         <v>362</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="38"/>
-      <c r="G9" s="33" t="s">
+      <c r="E9" s="30"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="39" t="s">
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="36" t="s">
         <v>186</v>
       </c>
-      <c r="M9" s="39"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35" t="s">
+      <c r="M9" s="36"/>
+      <c r="N9" s="36"/>
+      <c r="O9" s="33"/>
+      <c r="P9" s="33"/>
+      <c r="Q9" s="33"/>
+      <c r="R9" s="33" t="s">
         <v>268</v>
       </c>
-      <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="33" t="s">
+      <c r="S9" s="33"/>
+      <c r="T9" s="33"/>
+      <c r="U9" s="31" t="s">
         <v>291</v>
       </c>
-      <c r="V9" s="33"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="37"/>
+      <c r="V9" s="31"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="35"/>
     </row>
     <row r="10" s="13" customFormat="1" ht="101.55" spans="1:24">
-      <c r="A10" s="19"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="32" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="29"/>
+      <c r="C10" s="30" t="s">
         <v>364</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="E10" s="32"/>
+      <c r="E10" s="30"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="33" t="s">
+      <c r="G10" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="39"/>
-      <c r="M10" s="39"/>
-      <c r="N10" s="39"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35" t="s">
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="31"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="33"/>
+      <c r="P10" s="33" t="s">
         <v>231</v>
       </c>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="33" t="s">
+      <c r="Q10" s="33"/>
+      <c r="R10" s="33"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="31" t="s">
         <v>292</v>
       </c>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="37"/>
+      <c r="V10" s="31"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="35"/>
     </row>
     <row r="11" s="12" customFormat="1" ht="86.4" spans="1:24">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="41" t="s">
+      <c r="B11" s="29" t="s">
         <v>366</v>
       </c>
-      <c r="C11" s="32" t="s">
+      <c r="C11" s="30" t="s">
         <v>367</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="E11" s="32"/>
+      <c r="E11" s="30"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="33" t="s">
+      <c r="G11" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="39"/>
-      <c r="M11" s="39"/>
-      <c r="N11" s="39"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="33" t="s">
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="31"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" s="36"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="33"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="33"/>
+      <c r="U11" s="31" t="s">
         <v>293</v>
       </c>
-      <c r="V11" s="33"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="37"/>
+      <c r="V11" s="31"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="35"/>
     </row>
     <row r="12" customFormat="1" ht="86.4" spans="1:24">
-      <c r="A12" s="19"/>
-      <c r="B12" s="41"/>
-      <c r="C12" s="32" t="s">
+      <c r="A12" s="18"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="30" t="s">
         <v>369</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="E12" s="32"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="33" t="s">
+      <c r="E12" s="30"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="31" t="s">
         <v>156</v>
       </c>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="42" t="s">
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="38" t="s">
         <v>171</v>
       </c>
-      <c r="K12" s="42" t="s">
+      <c r="K12" s="38" t="s">
         <v>174</v>
       </c>
-      <c r="L12" s="39" t="s">
+      <c r="L12" s="36" t="s">
         <v>187</v>
       </c>
-      <c r="M12" s="39"/>
-      <c r="N12" s="39"/>
-      <c r="O12" s="35" t="s">
+      <c r="M12" s="36"/>
+      <c r="N12" s="36"/>
+      <c r="O12" s="33" t="s">
         <v>221</v>
       </c>
-      <c r="P12" s="35" t="s">
+      <c r="P12" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="Q12" s="35" t="s">
+      <c r="Q12" s="33" t="s">
         <v>258</v>
       </c>
-      <c r="R12" s="35" t="s">
+      <c r="R12" s="33" t="s">
         <v>268</v>
       </c>
-      <c r="S12" s="35"/>
-      <c r="T12" s="35" t="s">
+      <c r="S12" s="33"/>
+      <c r="T12" s="33" t="s">
         <v>275</v>
       </c>
-      <c r="U12" s="33" t="s">
+      <c r="U12" s="31" t="s">
         <v>294</v>
       </c>
-      <c r="V12" s="33"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="37"/>
+      <c r="V12" s="31"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="35"/>
     </row>
     <row r="13" customFormat="1" ht="57.6" spans="1:24">
-      <c r="A13" s="19"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="32" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="29"/>
+      <c r="C13" s="30" t="s">
         <v>371</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="38"/>
-      <c r="G13" s="33" t="s">
+      <c r="E13" s="30"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="42" t="s">
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="31"/>
+      <c r="K13" s="38" t="s">
         <v>175</v>
       </c>
-      <c r="L13" s="39" t="s">
+      <c r="L13" s="36" t="s">
         <v>188</v>
       </c>
-      <c r="M13" s="39"/>
-      <c r="N13" s="39"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35" t="s">
+      <c r="M13" s="36"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="33"/>
+      <c r="P13" s="33" t="s">
         <v>233</v>
       </c>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35" t="s">
+      <c r="Q13" s="33"/>
+      <c r="R13" s="33" t="s">
         <v>269</v>
       </c>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35" t="s">
+      <c r="S13" s="33"/>
+      <c r="T13" s="33" t="s">
         <v>276</v>
       </c>
-      <c r="U13" s="33" t="s">
+      <c r="U13" s="31" t="s">
         <v>295</v>
       </c>
-      <c r="V13" s="33"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="37"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="35"/>
     </row>
     <row r="14" customFormat="1" ht="115.2" spans="1:24">
-      <c r="A14" s="19"/>
-      <c r="B14" s="41"/>
-      <c r="C14" s="32" t="s">
+      <c r="A14" s="18"/>
+      <c r="B14" s="29"/>
+      <c r="C14" s="30" t="s">
         <v>373</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="38"/>
-      <c r="G14" s="33" t="s">
+      <c r="E14" s="30"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="31" t="s">
         <v>157</v>
       </c>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="39" t="s">
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="M14" s="39"/>
-      <c r="N14" s="39"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="33" t="s">
+      <c r="M14" s="36"/>
+      <c r="N14" s="36"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="33"/>
+      <c r="S14" s="33"/>
+      <c r="T14" s="33"/>
+      <c r="U14" s="31" t="s">
         <v>296</v>
       </c>
-      <c r="V14" s="33"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="40" t="s">
+      <c r="V14" s="31"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="37" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="15" customFormat="1" ht="100.8" spans="1:24">
-      <c r="A15" s="19"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="32" t="s">
+      <c r="A15" s="18"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="30" t="s">
         <v>375</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="E15" s="32"/>
-      <c r="F15" s="38"/>
-      <c r="G15" s="33" t="s">
+      <c r="E15" s="30"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="31" t="s">
         <v>158</v>
       </c>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="42" t="s">
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="38" t="s">
         <v>172</v>
       </c>
-      <c r="K15" s="42" t="s">
+      <c r="K15" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="L15" s="39" t="s">
+      <c r="L15" s="36" t="s">
         <v>190</v>
       </c>
-      <c r="M15" s="39"/>
-      <c r="N15" s="39"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="33" t="s">
+      <c r="M15" s="36"/>
+      <c r="N15" s="36"/>
+      <c r="O15" s="33"/>
+      <c r="P15" s="33"/>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="33"/>
+      <c r="S15" s="33"/>
+      <c r="T15" s="33"/>
+      <c r="U15" s="31" t="s">
         <v>377</v>
       </c>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="40" t="s">
+      <c r="V15" s="31"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="37" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="16" s="13" customFormat="1" ht="101.55" spans="1:24">
-      <c r="A16" s="19"/>
-      <c r="B16" s="41"/>
-      <c r="C16" s="32" t="s">
+      <c r="A16" s="18"/>
+      <c r="B16" s="29"/>
+      <c r="C16" s="30" t="s">
         <v>378</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="E16" s="32"/>
+      <c r="E16" s="30"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="39"/>
-      <c r="M16" s="39"/>
-      <c r="N16" s="39"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35" t="s">
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="31"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="33"/>
+      <c r="P16" s="33" t="s">
         <v>234</v>
       </c>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="33" t="s">
+      <c r="Q16" s="33"/>
+      <c r="R16" s="33"/>
+      <c r="S16" s="33"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="V16" s="33"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="37"/>
+      <c r="V16" s="31"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="35"/>
     </row>
     <row r="17" s="12" customFormat="1" ht="100.8" spans="1:24">
-      <c r="A17" s="19" t="s">
+      <c r="A17" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="41" t="s">
+      <c r="B17" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="32" t="s">
+      <c r="C17" s="30" t="s">
         <v>380</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="E17" s="32"/>
+      <c r="E17" s="30"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="39"/>
-      <c r="M17" s="39"/>
-      <c r="N17" s="39"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="33" t="s">
+      <c r="H17" s="31"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="31"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="36"/>
+      <c r="O17" s="33"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="33"/>
+      <c r="S17" s="33"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="31" t="s">
         <v>298</v>
       </c>
-      <c r="V17" s="33"/>
-      <c r="W17" s="33"/>
-      <c r="X17" s="37"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="35"/>
     </row>
     <row r="18" customFormat="1" ht="115.2" spans="1:24">
-      <c r="A18" s="19"/>
-      <c r="B18" s="41"/>
-      <c r="C18" s="32" t="s">
+      <c r="A18" s="18"/>
+      <c r="B18" s="29"/>
+      <c r="C18" s="30" t="s">
         <v>382</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="E18" s="32"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="33" t="s">
+      <c r="E18" s="30"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="39" t="s">
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="36" t="s">
         <v>191</v>
       </c>
-      <c r="M18" s="39"/>
-      <c r="N18" s="39"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="33" t="s">
+      <c r="M18" s="36"/>
+      <c r="N18" s="36"/>
+      <c r="O18" s="33"/>
+      <c r="P18" s="33"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="33"/>
+      <c r="S18" s="33"/>
+      <c r="T18" s="33"/>
+      <c r="U18" s="31" t="s">
         <v>299</v>
       </c>
-      <c r="V18" s="33"/>
-      <c r="W18" s="33"/>
-      <c r="X18" s="37"/>
+      <c r="V18" s="31"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="35"/>
     </row>
     <row r="19" customFormat="1" ht="86.4" spans="1:24">
-      <c r="A19" s="19"/>
-      <c r="B19" s="41"/>
-      <c r="C19" s="32" t="s">
+      <c r="A19" s="18"/>
+      <c r="B19" s="29"/>
+      <c r="C19" s="30" t="s">
         <v>384</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="E19" s="32"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="33" t="s">
+      <c r="E19" s="30"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="39" t="s">
+      <c r="H19" s="31"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="31"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="36" t="s">
         <v>192</v>
       </c>
-      <c r="M19" s="39"/>
-      <c r="N19" s="39"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="35"/>
-      <c r="U19" s="33" t="s">
+      <c r="M19" s="36"/>
+      <c r="N19" s="36"/>
+      <c r="O19" s="33"/>
+      <c r="P19" s="33"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="33"/>
+      <c r="S19" s="33"/>
+      <c r="T19" s="33"/>
+      <c r="U19" s="31" t="s">
         <v>300</v>
       </c>
-      <c r="V19" s="33"/>
-      <c r="W19" s="33"/>
-      <c r="X19" s="37"/>
+      <c r="V19" s="31"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="35"/>
     </row>
     <row r="20" customFormat="1" ht="57.6" spans="1:24">
-      <c r="A20" s="19"/>
-      <c r="B20" s="41"/>
-      <c r="C20" s="32" t="s">
+      <c r="A20" s="18"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="30" t="s">
         <v>386</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="E20" s="32"/>
-      <c r="F20" s="38"/>
-      <c r="G20" s="33" t="s">
+      <c r="E20" s="30"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="39" t="s">
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="M20" s="39"/>
-      <c r="N20" s="39"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="35" t="s">
+      <c r="M20" s="36"/>
+      <c r="N20" s="36"/>
+      <c r="O20" s="33"/>
+      <c r="P20" s="33" t="s">
         <v>235</v>
       </c>
-      <c r="Q20" s="35"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="35"/>
-      <c r="T20" s="35"/>
-      <c r="U20" s="33" t="s">
+      <c r="Q20" s="33"/>
+      <c r="R20" s="33"/>
+      <c r="S20" s="33"/>
+      <c r="T20" s="33"/>
+      <c r="U20" s="31" t="s">
         <v>301</v>
       </c>
-      <c r="V20" s="33"/>
-      <c r="W20" s="33"/>
-      <c r="X20" s="37"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="35"/>
     </row>
     <row r="21" customFormat="1" ht="158.4" spans="1:24">
-      <c r="A21" s="19"/>
-      <c r="B21" s="41"/>
-      <c r="C21" s="32" t="s">
+      <c r="A21" s="18"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="30" t="s">
         <v>388</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="E21" s="32"/>
-      <c r="F21" s="38"/>
-      <c r="G21" s="33" t="s">
+      <c r="E21" s="30"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="39" t="s">
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="31"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="36" t="s">
         <v>194</v>
       </c>
-      <c r="M21" s="39"/>
-      <c r="N21" s="39"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="35" t="s">
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="33" t="s">
         <v>236</v>
       </c>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="35"/>
-      <c r="U21" s="33" t="s">
+      <c r="Q21" s="33"/>
+      <c r="R21" s="33"/>
+      <c r="S21" s="33"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="31" t="s">
         <v>302</v>
       </c>
-      <c r="V21" s="33"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="37"/>
+      <c r="V21" s="31"/>
+      <c r="W21" s="31"/>
+      <c r="X21" s="35"/>
     </row>
     <row r="22" s="13" customFormat="1" ht="115.95" spans="1:24">
-      <c r="A22" s="19"/>
-      <c r="B22" s="41"/>
-      <c r="C22" s="32" t="s">
+      <c r="A22" s="18"/>
+      <c r="B22" s="29"/>
+      <c r="C22" s="30" t="s">
         <v>390</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="E22" s="32"/>
+      <c r="E22" s="30"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="33" t="s">
+      <c r="G22" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="39" t="s">
+      <c r="H22" s="31"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="31"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="36" t="s">
         <v>195</v>
       </c>
-      <c r="M22" s="39"/>
-      <c r="N22" s="39"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35" t="s">
+      <c r="M22" s="36"/>
+      <c r="N22" s="36"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="33" t="s">
         <v>237</v>
       </c>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="35"/>
-      <c r="U22" s="33" t="s">
+      <c r="Q22" s="33"/>
+      <c r="R22" s="33"/>
+      <c r="S22" s="33"/>
+      <c r="T22" s="33"/>
+      <c r="U22" s="31" t="s">
         <v>303</v>
       </c>
-      <c r="V22" s="33"/>
-      <c r="W22" s="33"/>
-      <c r="X22" s="37"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="31"/>
+      <c r="X22" s="35"/>
     </row>
     <row r="23" s="12" customFormat="1" ht="100.8" spans="1:24">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="29" t="s">
         <v>392</v>
       </c>
-      <c r="C23" s="32" t="s">
+      <c r="C23" s="30" t="s">
         <v>393</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="E23" s="32"/>
+      <c r="E23" s="30"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="33" t="s">
+      <c r="G23" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
-      <c r="T23" s="35"/>
-      <c r="U23" s="33" t="s">
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="36"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="36"/>
+      <c r="O23" s="33"/>
+      <c r="P23" s="33"/>
+      <c r="Q23" s="33"/>
+      <c r="R23" s="33"/>
+      <c r="S23" s="33"/>
+      <c r="T23" s="33"/>
+      <c r="U23" s="31" t="s">
         <v>304</v>
       </c>
-      <c r="V23" s="33"/>
-      <c r="W23" s="33"/>
-      <c r="X23" s="37"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="35"/>
     </row>
     <row r="24" customFormat="1" ht="76" customHeight="1" spans="1:24">
-      <c r="A24" s="19"/>
-      <c r="B24" s="41"/>
-      <c r="C24" s="32" t="s">
+      <c r="A24" s="18"/>
+      <c r="B24" s="29"/>
+      <c r="C24" s="30" t="s">
         <v>395</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="E24" s="32"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="33" t="s">
+      <c r="E24" s="30"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="39" t="s">
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="36" t="s">
         <v>193</v>
       </c>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35" t="s">
+      <c r="M24" s="36"/>
+      <c r="N24" s="36"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="33" t="s">
         <v>238</v>
       </c>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="35"/>
-      <c r="T24" s="35"/>
-      <c r="U24" s="33" t="s">
+      <c r="Q24" s="33"/>
+      <c r="R24" s="33"/>
+      <c r="S24" s="33"/>
+      <c r="T24" s="33"/>
+      <c r="U24" s="31" t="s">
         <v>305</v>
       </c>
-      <c r="V24" s="33"/>
-      <c r="W24" s="33"/>
-      <c r="X24" s="37"/>
+      <c r="V24" s="31"/>
+      <c r="W24" s="31"/>
+      <c r="X24" s="35"/>
     </row>
     <row r="25" customFormat="1" ht="100.8" spans="1:24">
-      <c r="A25" s="19"/>
-      <c r="B25" s="41"/>
-      <c r="C25" s="32" t="s">
+      <c r="A25" s="18"/>
+      <c r="B25" s="29"/>
+      <c r="C25" s="30" t="s">
         <v>397</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="E25" s="32"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="33" t="s">
+      <c r="E25" s="30"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="31" t="s">
         <v>160</v>
       </c>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="39" t="s">
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="31"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="36" t="s">
         <v>196</v>
       </c>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35" t="s">
+      <c r="M25" s="36"/>
+      <c r="N25" s="36"/>
+      <c r="O25" s="33"/>
+      <c r="P25" s="33" t="s">
         <v>239</v>
       </c>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="35"/>
-      <c r="U25" s="33" t="s">
+      <c r="Q25" s="33"/>
+      <c r="R25" s="33"/>
+      <c r="S25" s="33"/>
+      <c r="T25" s="33"/>
+      <c r="U25" s="31" t="s">
         <v>306</v>
       </c>
-      <c r="V25" s="33"/>
-      <c r="W25" s="33"/>
-      <c r="X25" s="37"/>
+      <c r="V25" s="31"/>
+      <c r="W25" s="31"/>
+      <c r="X25" s="35"/>
     </row>
     <row r="26" s="13" customFormat="1" ht="115.95" spans="1:24">
-      <c r="A26" s="19"/>
-      <c r="B26" s="41"/>
-      <c r="C26" s="32" t="s">
+      <c r="A26" s="18"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="30" t="s">
         <v>399</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="E26" s="32"/>
+      <c r="E26" s="30"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="33" t="s">
+      <c r="G26" s="31" t="s">
         <v>161</v>
       </c>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="39" t="s">
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="36" t="s">
         <v>197</v>
       </c>
-      <c r="M26" s="39"/>
-      <c r="N26" s="39"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35" t="s">
+      <c r="M26" s="36"/>
+      <c r="N26" s="36"/>
+      <c r="O26" s="33"/>
+      <c r="P26" s="33" t="s">
         <v>240</v>
       </c>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="35"/>
-      <c r="U26" s="33" t="s">
+      <c r="Q26" s="33"/>
+      <c r="R26" s="33"/>
+      <c r="S26" s="33"/>
+      <c r="T26" s="33"/>
+      <c r="U26" s="31" t="s">
         <v>401</v>
       </c>
-      <c r="V26" s="33"/>
-      <c r="W26" s="33"/>
-      <c r="X26" s="37"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="35"/>
     </row>
     <row r="27" s="12" customFormat="1" ht="72" spans="1:24">
-      <c r="A27" s="19" t="s">
+      <c r="A27" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="41" t="s">
+      <c r="B27" s="29" t="s">
         <v>402</v>
       </c>
-      <c r="C27" s="32" t="s">
+      <c r="C27" s="30" t="s">
         <v>403</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="E27" s="32"/>
+      <c r="E27" s="30"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="33" t="s">
+      <c r="G27" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="39" t="s">
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="36" t="s">
         <v>198</v>
       </c>
-      <c r="M27" s="39"/>
-      <c r="N27" s="39"/>
-      <c r="O27" s="35" t="s">
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="33" t="s">
         <v>222</v>
       </c>
-      <c r="P27" s="35" t="s">
+      <c r="P27" s="33" t="s">
         <v>241</v>
       </c>
-      <c r="Q27" s="35" t="s">
+      <c r="Q27" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="R27" s="35"/>
-      <c r="S27" s="35"/>
-      <c r="T27" s="35"/>
-      <c r="U27" s="33" t="s">
+      <c r="R27" s="33"/>
+      <c r="S27" s="33"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="31" t="s">
         <v>308</v>
       </c>
-      <c r="V27" s="33"/>
-      <c r="W27" s="33"/>
-      <c r="X27" s="37"/>
+      <c r="V27" s="31"/>
+      <c r="W27" s="31"/>
+      <c r="X27" s="35"/>
     </row>
-    <row r="28" customFormat="1" ht="216" spans="1:24">
-      <c r="A28" s="19"/>
-      <c r="B28" s="41"/>
-      <c r="C28" s="32" t="s">
+    <row r="28" customFormat="1" ht="230.4" spans="1:24">
+      <c r="A28" s="18"/>
+      <c r="B28" s="29"/>
+      <c r="C28" s="30" t="s">
         <v>405</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="E28" s="32"/>
-      <c r="F28" s="38"/>
-      <c r="G28" s="33" t="s">
+      <c r="E28" s="30"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="42" t="s">
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="38" t="s">
         <v>177</v>
       </c>
-      <c r="L28" s="39" t="s">
+      <c r="L28" s="36" t="s">
         <v>199</v>
       </c>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39"/>
-      <c r="O28" s="35" t="s">
+      <c r="M28" s="36"/>
+      <c r="N28" s="36"/>
+      <c r="O28" s="33" t="s">
         <v>223</v>
       </c>
-      <c r="P28" s="35" t="s">
+      <c r="P28" s="33" t="s">
         <v>242</v>
       </c>
-      <c r="Q28" s="35" t="s">
+      <c r="Q28" s="33" t="s">
         <v>260</v>
       </c>
-      <c r="R28" s="35"/>
-      <c r="S28" s="35"/>
-      <c r="T28" s="35"/>
-      <c r="U28" s="33" t="s">
+      <c r="R28" s="33"/>
+      <c r="S28" s="33"/>
+      <c r="T28" s="33"/>
+      <c r="U28" s="31" t="s">
         <v>309</v>
       </c>
-      <c r="V28" s="33"/>
-      <c r="W28" s="33"/>
-      <c r="X28" s="37"/>
+      <c r="V28" s="31"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="35"/>
     </row>
-    <row r="29" s="13" customFormat="1" ht="144.75" spans="1:24">
-      <c r="A29" s="19"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="32" t="s">
+    <row r="29" s="13" customFormat="1" ht="159.15" spans="1:24">
+      <c r="A29" s="18"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="30" t="s">
         <v>407</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="E29" s="32"/>
+      <c r="E29" s="30"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="33" t="s">
+      <c r="G29" s="31" t="s">
         <v>162</v>
       </c>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="39" t="s">
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="36" t="s">
         <v>200</v>
       </c>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="35" t="s">
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
+      <c r="O29" s="33" t="s">
         <v>224</v>
       </c>
-      <c r="P29" s="35" t="s">
+      <c r="P29" s="33" t="s">
         <v>243</v>
       </c>
-      <c r="Q29" s="35" t="s">
+      <c r="Q29" s="33" t="s">
         <v>261</v>
       </c>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
-      <c r="T29" s="35"/>
-      <c r="U29" s="33" t="s">
+      <c r="R29" s="33"/>
+      <c r="S29" s="33"/>
+      <c r="T29" s="33"/>
+      <c r="U29" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="V29" s="33"/>
-      <c r="W29" s="33"/>
-      <c r="X29" s="37"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="35"/>
     </row>
-    <row r="30" s="12" customFormat="1" ht="187.2" spans="1:24">
-      <c r="A30" s="19" t="s">
+    <row r="30" s="12" customFormat="1" ht="115.2" spans="1:24">
+      <c r="A30" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B30" s="41" t="s">
+      <c r="B30" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="32" t="s">
+      <c r="C30" s="30" t="s">
         <v>409</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="E30" s="32"/>
+      <c r="E30" s="30"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="33" t="s">
+      <c r="G30" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="39" t="s">
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
+      <c r="J30" s="31"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="36" t="s">
         <v>201</v>
       </c>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35" t="s">
+      <c r="M30" s="36"/>
+      <c r="N30" s="36"/>
+      <c r="O30" s="33"/>
+      <c r="P30" s="33"/>
+      <c r="Q30" s="33" t="s">
         <v>262</v>
       </c>
-      <c r="R30" s="35"/>
-      <c r="S30" s="35"/>
-      <c r="T30" s="35"/>
-      <c r="U30" s="33" t="s">
+      <c r="R30" s="33"/>
+      <c r="S30" s="33"/>
+      <c r="T30" s="33"/>
+      <c r="U30" s="31" t="s">
         <v>311</v>
       </c>
-      <c r="V30" s="33"/>
-      <c r="W30" s="33"/>
-      <c r="X30" s="37"/>
+      <c r="V30" s="31"/>
+      <c r="W30" s="31"/>
+      <c r="X30" s="35"/>
     </row>
-    <row r="31" customFormat="1" ht="172.8" spans="1:24">
-      <c r="A31" s="19"/>
-      <c r="B31" s="41"/>
-      <c r="C31" s="32" t="s">
+    <row r="31" customFormat="1" ht="144" spans="1:24">
+      <c r="A31" s="18"/>
+      <c r="B31" s="29"/>
+      <c r="C31" s="30" t="s">
         <v>411</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="E31" s="32"/>
-      <c r="F31" s="38"/>
-      <c r="G31" s="33" t="s">
+      <c r="E31" s="30"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="39" t="s">
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
+      <c r="J31" s="31"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="36" t="s">
         <v>202</v>
       </c>
-      <c r="M31" s="39"/>
-      <c r="N31" s="39"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="33" t="s">
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
+      <c r="O31" s="33"/>
+      <c r="P31" s="33"/>
+      <c r="Q31" s="33"/>
+      <c r="R31" s="33"/>
+      <c r="S31" s="33"/>
+      <c r="T31" s="33"/>
+      <c r="U31" s="31" t="s">
         <v>312</v>
       </c>
-      <c r="V31" s="33"/>
-      <c r="W31" s="33"/>
-      <c r="X31" s="37"/>
+      <c r="V31" s="31"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="35"/>
     </row>
-    <row r="32" customFormat="1" ht="201.6" spans="1:24">
-      <c r="A32" s="19"/>
-      <c r="B32" s="41"/>
-      <c r="C32" s="32" t="s">
+    <row r="32" customFormat="1" ht="100.8" spans="1:24">
+      <c r="A32" s="18"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="30" t="s">
         <v>413</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="E32" s="32"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="33" t="s">
+      <c r="E32" s="30"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="39" t="s">
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="36" t="s">
         <v>203</v>
       </c>
-      <c r="M32" s="39"/>
-      <c r="N32" s="39"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
-      <c r="R32" s="35" t="s">
+      <c r="M32" s="36"/>
+      <c r="N32" s="36"/>
+      <c r="O32" s="33"/>
+      <c r="P32" s="33"/>
+      <c r="Q32" s="33"/>
+      <c r="R32" s="33" t="s">
         <v>269</v>
       </c>
-      <c r="S32" s="35"/>
-      <c r="T32" s="35" t="s">
+      <c r="S32" s="33"/>
+      <c r="T32" s="33" t="s">
         <v>277</v>
       </c>
-      <c r="U32" s="33" t="s">
+      <c r="U32" s="31" t="s">
         <v>313</v>
       </c>
-      <c r="V32" s="33"/>
-      <c r="W32" s="33"/>
-      <c r="X32" s="37"/>
+      <c r="V32" s="31"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="35"/>
     </row>
-    <row r="33" customFormat="1" ht="216" spans="1:24">
-      <c r="A33" s="19"/>
-      <c r="B33" s="41"/>
-      <c r="C33" s="32" t="s">
+    <row r="33" customFormat="1" ht="158.4" spans="1:24">
+      <c r="A33" s="18"/>
+      <c r="B33" s="29"/>
+      <c r="C33" s="30" t="s">
         <v>415</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="E33" s="32"/>
-      <c r="F33" s="38"/>
-      <c r="G33" s="33" t="s">
+      <c r="E33" s="30"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="39" t="s">
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="36" t="s">
         <v>204</v>
       </c>
-      <c r="M33" s="39"/>
-      <c r="N33" s="39"/>
-      <c r="O33" s="35"/>
-      <c r="P33" s="35"/>
-      <c r="Q33" s="35"/>
-      <c r="R33" s="35"/>
-      <c r="S33" s="35"/>
-      <c r="T33" s="35" t="s">
+      <c r="M33" s="36"/>
+      <c r="N33" s="36"/>
+      <c r="O33" s="33"/>
+      <c r="P33" s="33"/>
+      <c r="Q33" s="33"/>
+      <c r="R33" s="33"/>
+      <c r="S33" s="33"/>
+      <c r="T33" s="33" t="s">
         <v>278</v>
       </c>
-      <c r="U33" s="33" t="s">
+      <c r="U33" s="31" t="s">
         <v>314</v>
       </c>
-      <c r="V33" s="33"/>
-      <c r="W33" s="33"/>
-      <c r="X33" s="37"/>
+      <c r="V33" s="31"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="35"/>
     </row>
-    <row r="34" customFormat="1" ht="172.8" spans="1:24">
-      <c r="A34" s="19"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="32" t="s">
+    <row r="34" customFormat="1" ht="144" spans="1:24">
+      <c r="A34" s="18"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="30" t="s">
         <v>417</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="E34" s="32"/>
-      <c r="F34" s="38"/>
-      <c r="G34" s="33" t="s">
+      <c r="E34" s="30"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="31" t="s">
         <v>163</v>
       </c>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="39"/>
-      <c r="M34" s="39"/>
-      <c r="N34" s="39"/>
-      <c r="O34" s="35"/>
-      <c r="P34" s="35"/>
-      <c r="Q34" s="35"/>
-      <c r="R34" s="35"/>
-      <c r="S34" s="35"/>
-      <c r="T34" s="35" t="s">
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="36"/>
+      <c r="M34" s="36"/>
+      <c r="N34" s="36"/>
+      <c r="O34" s="33"/>
+      <c r="P34" s="33"/>
+      <c r="Q34" s="33"/>
+      <c r="R34" s="33"/>
+      <c r="S34" s="33"/>
+      <c r="T34" s="33" t="s">
         <v>279</v>
       </c>
-      <c r="U34" s="43" t="s">
+      <c r="U34" s="39" t="s">
         <v>315</v>
       </c>
-      <c r="V34" s="43"/>
-      <c r="W34" s="43"/>
-      <c r="X34" s="44"/>
+      <c r="V34" s="39"/>
+      <c r="W34" s="39"/>
+      <c r="X34" s="40"/>
     </row>
-    <row r="35" s="13" customFormat="1" ht="259.95" spans="1:24">
-      <c r="A35" s="19"/>
-      <c r="B35" s="41"/>
-      <c r="C35" s="32" t="s">
+    <row r="35" s="13" customFormat="1" ht="173.55" spans="1:24">
+      <c r="A35" s="18"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="30" t="s">
         <v>419</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="E35" s="32"/>
+      <c r="E35" s="30"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="33" t="s">
+      <c r="G35" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H35" s="33"/>
-      <c r="I35" s="33"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="33"/>
-      <c r="L35" s="39" t="s">
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
+      <c r="J35" s="31"/>
+      <c r="K35" s="31"/>
+      <c r="L35" s="36" t="s">
         <v>205</v>
       </c>
-      <c r="M35" s="39"/>
-      <c r="N35" s="39"/>
-      <c r="O35" s="35"/>
-      <c r="P35" s="35" t="s">
+      <c r="M35" s="36"/>
+      <c r="N35" s="36"/>
+      <c r="O35" s="33"/>
+      <c r="P35" s="33" t="s">
         <v>244</v>
       </c>
-      <c r="Q35" s="35"/>
-      <c r="R35" s="35"/>
-      <c r="S35" s="35"/>
-      <c r="T35" s="35"/>
-      <c r="U35" s="33" t="s">
+      <c r="Q35" s="33"/>
+      <c r="R35" s="33"/>
+      <c r="S35" s="33"/>
+      <c r="T35" s="33"/>
+      <c r="U35" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="V35" s="33"/>
-      <c r="W35" s="33"/>
-      <c r="X35" s="37"/>
+      <c r="V35" s="31"/>
+      <c r="W35" s="31"/>
+      <c r="X35" s="35"/>
     </row>
-    <row r="36" s="12" customFormat="1" ht="288" spans="1:24">
-      <c r="A36" s="19" t="s">
+    <row r="36" s="12" customFormat="1" ht="144" spans="1:24">
+      <c r="A36" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="B36" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="32" t="s">
+      <c r="C36" s="30" t="s">
         <v>421</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="E36" s="32"/>
+      <c r="E36" s="30"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="33" t="s">
+      <c r="G36" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="39" t="s">
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
+      <c r="J36" s="31"/>
+      <c r="K36" s="31"/>
+      <c r="L36" s="36" t="s">
         <v>423</v>
       </c>
-      <c r="M36" s="39"/>
-      <c r="N36" s="39"/>
-      <c r="O36" s="35"/>
-      <c r="P36" s="35"/>
-      <c r="Q36" s="35" t="s">
+      <c r="M36" s="36"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="33"/>
+      <c r="P36" s="33"/>
+      <c r="Q36" s="33" t="s">
         <v>263</v>
       </c>
-      <c r="R36" s="35"/>
-      <c r="S36" s="35"/>
-      <c r="T36" s="35" t="s">
+      <c r="R36" s="33"/>
+      <c r="S36" s="33"/>
+      <c r="T36" s="33" t="s">
         <v>280</v>
       </c>
-      <c r="U36" s="33" t="s">
+      <c r="U36" s="31" t="s">
         <v>316</v>
       </c>
-      <c r="V36" s="33"/>
-      <c r="W36" s="33"/>
-      <c r="X36" s="37"/>
+      <c r="V36" s="31"/>
+      <c r="W36" s="31"/>
+      <c r="X36" s="35"/>
     </row>
-    <row r="37" customFormat="1" ht="187.2" spans="1:24">
-      <c r="A37" s="19"/>
-      <c r="B37" s="41"/>
-      <c r="C37" s="32" t="s">
+    <row r="37" customFormat="1" ht="144" spans="1:24">
+      <c r="A37" s="18"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="30" t="s">
         <v>424</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="E37" s="32"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="33" t="s">
+      <c r="E37" s="30"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="42" t="s">
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="38" t="s">
         <v>178</v>
       </c>
-      <c r="L37" s="39" t="s">
+      <c r="L37" s="36" t="s">
         <v>207</v>
       </c>
-      <c r="M37" s="39"/>
-      <c r="N37" s="39"/>
-      <c r="O37" s="35"/>
-      <c r="P37" s="35"/>
-      <c r="Q37" s="35"/>
-      <c r="R37" s="35"/>
-      <c r="S37" s="35" t="s">
+      <c r="M37" s="36"/>
+      <c r="N37" s="36"/>
+      <c r="O37" s="33"/>
+      <c r="P37" s="33"/>
+      <c r="Q37" s="33"/>
+      <c r="R37" s="33"/>
+      <c r="S37" s="33" t="s">
         <v>272</v>
       </c>
-      <c r="T37" s="35" t="s">
+      <c r="T37" s="33" t="s">
         <v>281</v>
       </c>
-      <c r="U37" s="33" t="s">
+      <c r="U37" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="V37" s="33"/>
-      <c r="W37" s="33"/>
-      <c r="X37" s="37"/>
+      <c r="V37" s="31"/>
+      <c r="W37" s="31"/>
+      <c r="X37" s="35"/>
     </row>
-    <row r="38" s="13" customFormat="1" ht="159.15" spans="1:24">
-      <c r="A38" s="19"/>
-      <c r="B38" s="41"/>
-      <c r="C38" s="32" t="s">
+    <row r="38" s="13" customFormat="1" ht="115.95" spans="1:24">
+      <c r="A38" s="18"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="30" t="s">
         <v>426</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="E38" s="32"/>
+      <c r="E38" s="30"/>
       <c r="F38" s="2"/>
-      <c r="G38" s="33" t="s">
+      <c r="G38" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="33"/>
-      <c r="L38" s="39"/>
-      <c r="M38" s="39"/>
-      <c r="N38" s="39"/>
-      <c r="O38" s="35"/>
-      <c r="P38" s="35"/>
-      <c r="Q38" s="35" t="s">
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="31"/>
+      <c r="L38" s="36"/>
+      <c r="M38" s="36"/>
+      <c r="N38" s="36"/>
+      <c r="O38" s="33"/>
+      <c r="P38" s="33"/>
+      <c r="Q38" s="33" t="s">
         <v>263</v>
       </c>
-      <c r="R38" s="35"/>
-      <c r="S38" s="35"/>
-      <c r="T38" s="35"/>
-      <c r="U38" s="33" t="s">
+      <c r="R38" s="33"/>
+      <c r="S38" s="33"/>
+      <c r="T38" s="33"/>
+      <c r="U38" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="V38" s="33"/>
-      <c r="W38" s="33"/>
-      <c r="X38" s="37"/>
+      <c r="V38" s="31"/>
+      <c r="W38" s="31"/>
+      <c r="X38" s="35"/>
     </row>
-    <row r="39" s="12" customFormat="1" ht="201.6" spans="1:24">
-      <c r="A39" s="19" t="s">
+    <row r="39" s="12" customFormat="1" ht="144" spans="1:24">
+      <c r="A39" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B39" s="41" t="s">
+      <c r="B39" s="29" t="s">
         <v>428</v>
       </c>
-      <c r="C39" s="32" t="s">
+      <c r="C39" s="30" t="s">
         <v>429</v>
       </c>
-      <c r="D39" s="32" t="s">
+      <c r="D39" s="41" t="s">
         <v>430</v>
       </c>
-      <c r="E39" s="32"/>
+      <c r="E39" s="30"/>
       <c r="F39" s="2"/>
-      <c r="G39" s="33" t="s">
+      <c r="G39" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="39"/>
-      <c r="M39" s="39"/>
-      <c r="N39" s="39"/>
-      <c r="O39" s="35"/>
-      <c r="P39" s="35" t="s">
+      <c r="H39" s="31"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="31"/>
+      <c r="K39" s="31"/>
+      <c r="L39" s="36"/>
+      <c r="M39" s="36"/>
+      <c r="N39" s="36"/>
+      <c r="O39" s="33"/>
+      <c r="P39" s="33" t="s">
         <v>245</v>
       </c>
-      <c r="Q39" s="35"/>
-      <c r="R39" s="35"/>
-      <c r="S39" s="35"/>
-      <c r="T39" s="35"/>
-      <c r="U39" s="33" t="s">
+      <c r="Q39" s="33"/>
+      <c r="R39" s="33"/>
+      <c r="S39" s="33"/>
+      <c r="T39" s="33"/>
+      <c r="U39" s="31" t="s">
         <v>318</v>
       </c>
-      <c r="V39" s="33"/>
-      <c r="W39" s="33"/>
-      <c r="X39" s="37"/>
+      <c r="V39" s="31"/>
+      <c r="W39" s="31"/>
+      <c r="X39" s="35"/>
     </row>
-    <row r="40" customFormat="1" ht="259.2" spans="1:24">
-      <c r="A40" s="19"/>
-      <c r="B40" s="41"/>
-      <c r="C40" s="32" t="s">
+    <row r="40" customFormat="1" ht="230.4" spans="1:24">
+      <c r="A40" s="18"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="30" t="s">
         <v>431</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="30" t="s">
         <v>432</v>
       </c>
-      <c r="E40" s="32"/>
-      <c r="F40" s="38"/>
-      <c r="G40" s="33" t="s">
+      <c r="E40" s="30"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="33"/>
-      <c r="L40" s="39" t="s">
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="36" t="s">
         <v>208</v>
       </c>
-      <c r="M40" s="39"/>
-      <c r="N40" s="39"/>
-      <c r="O40" s="35" t="s">
+      <c r="M40" s="36"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="33" t="s">
         <v>225</v>
       </c>
-      <c r="P40" s="35" t="s">
+      <c r="P40" s="33" t="s">
         <v>246</v>
       </c>
-      <c r="Q40" s="35"/>
-      <c r="R40" s="35"/>
-      <c r="S40" s="35"/>
-      <c r="T40" s="35"/>
-      <c r="U40" s="33" t="s">
+      <c r="Q40" s="33"/>
+      <c r="R40" s="33"/>
+      <c r="S40" s="33"/>
+      <c r="T40" s="33"/>
+      <c r="U40" s="31" t="s">
         <v>319</v>
       </c>
-      <c r="V40" s="33"/>
-      <c r="W40" s="33"/>
-      <c r="X40" s="37"/>
+      <c r="V40" s="31"/>
+      <c r="W40" s="31"/>
+      <c r="X40" s="35"/>
     </row>
     <row r="41" customFormat="1" ht="216" spans="1:24">
-      <c r="A41" s="19"/>
-      <c r="B41" s="41"/>
-      <c r="C41" s="32" t="s">
+      <c r="A41" s="18"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="30" t="s">
         <v>433</v>
       </c>
-      <c r="D41" s="32" t="s">
+      <c r="D41" s="30" t="s">
         <v>434</v>
       </c>
-      <c r="E41" s="32"/>
-      <c r="F41" s="38"/>
-      <c r="G41" s="33" t="s">
+      <c r="E41" s="30"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="39" t="s">
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+      <c r="K41" s="31"/>
+      <c r="L41" s="36" t="s">
         <v>209</v>
       </c>
-      <c r="M41" s="39"/>
-      <c r="N41" s="39"/>
-      <c r="O41" s="35"/>
-      <c r="P41" s="35" t="s">
+      <c r="M41" s="36"/>
+      <c r="N41" s="36"/>
+      <c r="O41" s="33"/>
+      <c r="P41" s="33" t="s">
         <v>247</v>
       </c>
-      <c r="Q41" s="35" t="s">
+      <c r="Q41" s="33" t="s">
         <v>264</v>
       </c>
-      <c r="R41" s="35"/>
-      <c r="S41" s="35"/>
-      <c r="T41" s="35"/>
-      <c r="U41" s="33" t="s">
+      <c r="R41" s="33"/>
+      <c r="S41" s="33"/>
+      <c r="T41" s="33"/>
+      <c r="U41" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="V41" s="33"/>
-      <c r="W41" s="33"/>
-      <c r="X41" s="37"/>
+      <c r="V41" s="31"/>
+      <c r="W41" s="31"/>
+      <c r="X41" s="35"/>
     </row>
     <row r="42" customFormat="1" ht="230.4" spans="1:24">
-      <c r="A42" s="19"/>
-      <c r="B42" s="41"/>
-      <c r="C42" s="32" t="s">
+      <c r="A42" s="18"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="30" t="s">
         <v>435</v>
       </c>
-      <c r="D42" s="32" t="s">
+      <c r="D42" s="30" t="s">
         <v>436</v>
       </c>
-      <c r="E42" s="32"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="33" t="s">
+      <c r="E42" s="30"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="39" t="s">
+      <c r="H42" s="31"/>
+      <c r="I42" s="31"/>
+      <c r="J42" s="31"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="36" t="s">
         <v>210</v>
       </c>
-      <c r="M42" s="39"/>
-      <c r="N42" s="39"/>
-      <c r="O42" s="35" t="s">
+      <c r="M42" s="36"/>
+      <c r="N42" s="36"/>
+      <c r="O42" s="33" t="s">
         <v>226</v>
       </c>
-      <c r="P42" s="35" t="s">
+      <c r="P42" s="33" t="s">
         <v>248</v>
       </c>
-      <c r="Q42" s="35"/>
-      <c r="R42" s="35"/>
-      <c r="S42" s="35"/>
-      <c r="T42" s="35" t="s">
+      <c r="Q42" s="33"/>
+      <c r="R42" s="33"/>
+      <c r="S42" s="33"/>
+      <c r="T42" s="33" t="s">
         <v>276</v>
       </c>
-      <c r="U42" s="43" t="s">
+      <c r="U42" s="39" t="s">
         <v>155</v>
       </c>
-      <c r="V42" s="43"/>
-      <c r="W42" s="43"/>
-      <c r="X42" s="40" t="s">
+      <c r="V42" s="39"/>
+      <c r="W42" s="39"/>
+      <c r="X42" s="37" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="43" customFormat="1" ht="273.6" spans="1:24">
-      <c r="A43" s="19"/>
-      <c r="B43" s="41"/>
-      <c r="C43" s="32" t="s">
+      <c r="A43" s="18"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="30" t="s">
         <v>437</v>
       </c>
-      <c r="D43" s="32" t="s">
+      <c r="D43" s="30" t="s">
         <v>438</v>
       </c>
-      <c r="E43" s="32"/>
-      <c r="F43" s="38"/>
-      <c r="G43" s="33" t="s">
+      <c r="E43" s="30"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="39" t="s">
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="36" t="s">
         <v>211</v>
       </c>
-      <c r="M43" s="39"/>
-      <c r="N43" s="39"/>
-      <c r="O43" s="35" t="s">
+      <c r="M43" s="36"/>
+      <c r="N43" s="36"/>
+      <c r="O43" s="33" t="s">
         <v>226</v>
       </c>
-      <c r="P43" s="35" t="s">
+      <c r="P43" s="33" t="s">
         <v>249</v>
       </c>
-      <c r="Q43" s="35"/>
-      <c r="R43" s="35" t="s">
+      <c r="Q43" s="33"/>
+      <c r="R43" s="33" t="s">
         <v>269</v>
       </c>
-      <c r="S43" s="35"/>
-      <c r="T43" s="35" t="s">
+      <c r="S43" s="33"/>
+      <c r="T43" s="33" t="s">
         <v>276</v>
       </c>
-      <c r="U43" s="33" t="s">
+      <c r="U43" s="31" t="s">
         <v>315</v>
       </c>
-      <c r="V43" s="33"/>
-      <c r="W43" s="33"/>
-      <c r="X43" s="40" t="s">
+      <c r="V43" s="31"/>
+      <c r="W43" s="31"/>
+      <c r="X43" s="37" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="44" customFormat="1" ht="216" spans="1:24">
-      <c r="A44" s="19"/>
-      <c r="B44" s="41"/>
-      <c r="C44" s="32" t="s">
+      <c r="A44" s="18"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="30" t="s">
         <v>439</v>
       </c>
-      <c r="D44" s="32" t="s">
+      <c r="D44" s="30" t="s">
         <v>440</v>
       </c>
-      <c r="E44" s="32"/>
-      <c r="F44" s="38"/>
-      <c r="G44" s="33" t="s">
+      <c r="E44" s="30"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
-      <c r="L44" s="39"/>
-      <c r="M44" s="39"/>
-      <c r="N44" s="39"/>
-      <c r="O44" s="35"/>
-      <c r="P44" s="35"/>
-      <c r="Q44" s="35"/>
-      <c r="R44" s="35"/>
-      <c r="S44" s="35"/>
-      <c r="T44" s="35"/>
-      <c r="U44" s="33" t="s">
+      <c r="H44" s="31"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="31"/>
+      <c r="K44" s="31"/>
+      <c r="L44" s="36"/>
+      <c r="M44" s="36"/>
+      <c r="N44" s="36"/>
+      <c r="O44" s="33"/>
+      <c r="P44" s="33"/>
+      <c r="Q44" s="33"/>
+      <c r="R44" s="33"/>
+      <c r="S44" s="33"/>
+      <c r="T44" s="33"/>
+      <c r="U44" s="31" t="s">
         <v>315</v>
       </c>
-      <c r="V44" s="33"/>
-      <c r="W44" s="33"/>
-      <c r="X44" s="37"/>
+      <c r="V44" s="31"/>
+      <c r="W44" s="31"/>
+      <c r="X44" s="35"/>
     </row>
     <row r="45" s="13" customFormat="1" ht="245.55" spans="1:24">
-      <c r="A45" s="19"/>
-      <c r="B45" s="41"/>
-      <c r="C45" s="32" t="s">
+      <c r="A45" s="18"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="30" t="s">
         <v>441</v>
       </c>
-      <c r="D45" s="32" t="s">
+      <c r="D45" s="30" t="s">
         <v>442</v>
       </c>
-      <c r="E45" s="32"/>
+      <c r="E45" s="30"/>
       <c r="F45" s="2"/>
-      <c r="G45" s="33" t="s">
+      <c r="G45" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="33"/>
-      <c r="L45" s="39" t="s">
+      <c r="H45" s="31"/>
+      <c r="I45" s="31"/>
+      <c r="J45" s="31"/>
+      <c r="K45" s="31"/>
+      <c r="L45" s="36" t="s">
         <v>212</v>
       </c>
-      <c r="M45" s="39"/>
-      <c r="N45" s="39"/>
-      <c r="O45" s="35"/>
-      <c r="P45" s="35" t="s">
+      <c r="M45" s="36"/>
+      <c r="N45" s="36"/>
+      <c r="O45" s="33"/>
+      <c r="P45" s="33" t="s">
         <v>250</v>
       </c>
-      <c r="Q45" s="35"/>
-      <c r="R45" s="35"/>
-      <c r="S45" s="35"/>
-      <c r="T45" s="35"/>
-      <c r="U45" s="33" t="s">
+      <c r="Q45" s="33"/>
+      <c r="R45" s="33"/>
+      <c r="S45" s="33"/>
+      <c r="T45" s="33"/>
+      <c r="U45" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="V45" s="33"/>
-      <c r="W45" s="33"/>
-      <c r="X45" s="37"/>
+      <c r="V45" s="31"/>
+      <c r="W45" s="31"/>
+      <c r="X45" s="35"/>
     </row>
     <row r="46" s="12" customFormat="1" ht="230.4" spans="1:24">
-      <c r="A46" s="19" t="s">
+      <c r="A46" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="B46" s="41" t="s">
+      <c r="B46" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C46" s="32" t="s">
+      <c r="C46" s="30" t="s">
         <v>443</v>
       </c>
-      <c r="D46" s="32" t="s">
+      <c r="D46" s="30" t="s">
         <v>444</v>
       </c>
-      <c r="E46" s="32"/>
+      <c r="E46" s="30"/>
       <c r="F46" s="2"/>
-      <c r="G46" s="33" t="s">
+      <c r="G46" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="33"/>
-      <c r="L46" s="39" t="s">
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="31"/>
+      <c r="L46" s="36" t="s">
         <v>213</v>
       </c>
-      <c r="M46" s="39"/>
-      <c r="N46" s="39"/>
-      <c r="O46" s="35" t="s">
+      <c r="M46" s="36"/>
+      <c r="N46" s="36"/>
+      <c r="O46" s="33" t="s">
         <v>227</v>
       </c>
-      <c r="P46" s="35" t="s">
+      <c r="P46" s="33" t="s">
         <v>251</v>
       </c>
-      <c r="Q46" s="35"/>
-      <c r="R46" s="35"/>
-      <c r="S46" s="35"/>
-      <c r="T46" s="35"/>
-      <c r="U46" s="33" t="s">
+      <c r="Q46" s="33"/>
+      <c r="R46" s="33"/>
+      <c r="S46" s="33"/>
+      <c r="T46" s="33"/>
+      <c r="U46" s="31" t="s">
         <v>320</v>
       </c>
-      <c r="V46" s="33"/>
-      <c r="W46" s="33"/>
-      <c r="X46" s="37"/>
+      <c r="V46" s="31"/>
+      <c r="W46" s="31"/>
+      <c r="X46" s="35"/>
     </row>
     <row r="47" customFormat="1" ht="144" spans="1:24">
-      <c r="A47" s="19"/>
-      <c r="B47" s="41"/>
-      <c r="C47" s="32" t="s">
+      <c r="A47" s="18"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="30" t="s">
         <v>445</v>
       </c>
-      <c r="D47" s="32" t="s">
+      <c r="D47" s="30" t="s">
         <v>446</v>
       </c>
-      <c r="E47" s="32"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="33" t="s">
+      <c r="E47" s="30"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="31" t="s">
         <v>167</v>
       </c>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="39" t="s">
+      <c r="H47" s="31"/>
+      <c r="I47" s="31"/>
+      <c r="J47" s="31"/>
+      <c r="K47" s="31"/>
+      <c r="L47" s="36" t="s">
         <v>214</v>
       </c>
-      <c r="M47" s="39"/>
-      <c r="N47" s="39"/>
-      <c r="O47" s="35"/>
-      <c r="P47" s="35" t="s">
+      <c r="M47" s="36"/>
+      <c r="N47" s="36"/>
+      <c r="O47" s="33"/>
+      <c r="P47" s="33" t="s">
         <v>252</v>
       </c>
-      <c r="Q47" s="35"/>
-      <c r="R47" s="35"/>
-      <c r="S47" s="35"/>
-      <c r="T47" s="35" t="s">
+      <c r="Q47" s="33"/>
+      <c r="R47" s="33"/>
+      <c r="S47" s="33"/>
+      <c r="T47" s="33" t="s">
         <v>277</v>
       </c>
-      <c r="U47" s="33" t="s">
+      <c r="U47" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="V47" s="33"/>
-      <c r="W47" s="33"/>
-      <c r="X47" s="37"/>
+      <c r="V47" s="31"/>
+      <c r="W47" s="31"/>
+      <c r="X47" s="35"/>
     </row>
     <row r="48" s="13" customFormat="1" ht="173.55" spans="1:24">
-      <c r="A48" s="19"/>
-      <c r="B48" s="41"/>
-      <c r="C48" s="32" t="s">
+      <c r="A48" s="18"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="30" t="s">
         <v>447</v>
       </c>
-      <c r="D48" s="32" t="s">
+      <c r="D48" s="30" t="s">
         <v>448</v>
       </c>
-      <c r="E48" s="32"/>
+      <c r="E48" s="30"/>
       <c r="F48" s="2"/>
-      <c r="G48" s="33" t="s">
+      <c r="G48" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="33"/>
-      <c r="L48" s="39" t="s">
+      <c r="H48" s="31"/>
+      <c r="I48" s="31"/>
+      <c r="J48" s="31"/>
+      <c r="K48" s="31"/>
+      <c r="L48" s="36" t="s">
         <v>215</v>
       </c>
-      <c r="M48" s="39"/>
-      <c r="N48" s="39"/>
-      <c r="O48" s="35"/>
-      <c r="P48" s="35" t="s">
+      <c r="M48" s="36"/>
+      <c r="N48" s="36"/>
+      <c r="O48" s="33"/>
+      <c r="P48" s="33" t="s">
         <v>253</v>
       </c>
-      <c r="Q48" s="35"/>
-      <c r="R48" s="35"/>
-      <c r="S48" s="35"/>
-      <c r="T48" s="35"/>
-      <c r="U48" s="33" t="s">
+      <c r="Q48" s="33"/>
+      <c r="R48" s="33"/>
+      <c r="S48" s="33"/>
+      <c r="T48" s="33"/>
+      <c r="U48" s="31" t="s">
         <v>322</v>
       </c>
-      <c r="V48" s="33"/>
-      <c r="W48" s="33"/>
-      <c r="X48" s="37"/>
+      <c r="V48" s="31"/>
+      <c r="W48" s="31"/>
+      <c r="X48" s="35"/>
     </row>
     <row r="49" s="12" customFormat="1" ht="230.4" spans="1:24">
-      <c r="A49" s="19" t="s">
+      <c r="A49" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B49" s="41" t="s">
+      <c r="B49" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="32" t="s">
+      <c r="C49" s="30" t="s">
         <v>449</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="E49" s="32"/>
+      <c r="E49" s="30"/>
       <c r="F49" s="2"/>
-      <c r="G49" s="33" t="s">
+      <c r="G49" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="H49" s="33"/>
-      <c r="I49" s="33"/>
-      <c r="J49" s="33"/>
-      <c r="K49" s="33"/>
-      <c r="L49" s="39"/>
-      <c r="M49" s="39"/>
-      <c r="N49" s="39"/>
-      <c r="O49" s="35" t="s">
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="31"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="36"/>
+      <c r="M49" s="36"/>
+      <c r="N49" s="36"/>
+      <c r="O49" s="33" t="s">
         <v>228</v>
       </c>
-      <c r="P49" s="35" t="s">
+      <c r="P49" s="33" t="s">
         <v>254</v>
       </c>
-      <c r="Q49" s="35" t="s">
+      <c r="Q49" s="33" t="s">
         <v>265</v>
       </c>
-      <c r="R49" s="35"/>
-      <c r="S49" s="35"/>
-      <c r="T49" s="35"/>
-      <c r="U49" s="33" t="s">
+      <c r="R49" s="33"/>
+      <c r="S49" s="33"/>
+      <c r="T49" s="33"/>
+      <c r="U49" s="31" t="s">
         <v>323</v>
       </c>
-      <c r="V49" s="33"/>
-      <c r="W49" s="33"/>
-      <c r="X49" s="37"/>
+      <c r="V49" s="31"/>
+      <c r="W49" s="31"/>
+      <c r="X49" s="35"/>
     </row>
     <row r="50" customFormat="1" ht="187.2" spans="1:24">
-      <c r="A50" s="19"/>
-      <c r="B50" s="41"/>
-      <c r="C50" s="32" t="s">
+      <c r="A50" s="18"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="30" t="s">
         <v>451</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="E50" s="32"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="33" t="s">
+      <c r="E50" s="30"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="H50" s="33"/>
-      <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="33"/>
-      <c r="L50" s="39"/>
-      <c r="M50" s="39"/>
-      <c r="N50" s="39"/>
-      <c r="O50" s="35"/>
-      <c r="P50" s="35" t="s">
+      <c r="H50" s="31"/>
+      <c r="I50" s="31"/>
+      <c r="J50" s="31"/>
+      <c r="K50" s="31"/>
+      <c r="L50" s="36"/>
+      <c r="M50" s="36"/>
+      <c r="N50" s="36"/>
+      <c r="O50" s="33"/>
+      <c r="P50" s="33" t="s">
         <v>255</v>
       </c>
-      <c r="Q50" s="35" t="s">
+      <c r="Q50" s="33" t="s">
         <v>266</v>
       </c>
-      <c r="R50" s="35"/>
-      <c r="S50" s="35"/>
-      <c r="T50" s="35"/>
-      <c r="U50" s="33" t="s">
+      <c r="R50" s="33"/>
+      <c r="S50" s="33"/>
+      <c r="T50" s="33"/>
+      <c r="U50" s="31" t="s">
         <v>324</v>
       </c>
-      <c r="V50" s="33"/>
-      <c r="W50" s="33"/>
-      <c r="X50" s="37"/>
+      <c r="V50" s="31"/>
+      <c r="W50" s="31"/>
+      <c r="X50" s="35"/>
     </row>
     <row r="51" customFormat="1" ht="216" spans="1:24">
-      <c r="A51" s="19"/>
-      <c r="B51" s="41"/>
-      <c r="C51" s="32" t="s">
+      <c r="A51" s="18"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="30" t="s">
         <v>453</v>
       </c>
-      <c r="D51" s="32" t="s">
+      <c r="D51" s="30" t="s">
         <v>454</v>
       </c>
-      <c r="E51" s="32"/>
-      <c r="F51" s="38"/>
-      <c r="G51" s="33" t="s">
+      <c r="E51" s="30"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="H51" s="33"/>
-      <c r="I51" s="33"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="33"/>
-      <c r="L51" s="39" t="s">
+      <c r="H51" s="31"/>
+      <c r="I51" s="31"/>
+      <c r="J51" s="31"/>
+      <c r="K51" s="31"/>
+      <c r="L51" s="36" t="s">
         <v>455</v>
       </c>
-      <c r="M51" s="39"/>
-      <c r="N51" s="39"/>
-      <c r="O51" s="35"/>
-      <c r="P51" s="35"/>
-      <c r="Q51" s="35"/>
-      <c r="R51" s="35"/>
-      <c r="S51" s="35"/>
-      <c r="T51" s="35" t="s">
+      <c r="M51" s="36"/>
+      <c r="N51" s="36"/>
+      <c r="O51" s="33"/>
+      <c r="P51" s="33"/>
+      <c r="Q51" s="33"/>
+      <c r="R51" s="33"/>
+      <c r="S51" s="33"/>
+      <c r="T51" s="33" t="s">
         <v>282</v>
       </c>
-      <c r="U51" s="33" t="s">
+      <c r="U51" s="31" t="s">
         <v>315</v>
       </c>
-      <c r="V51" s="33"/>
-      <c r="W51" s="33"/>
-      <c r="X51" s="37"/>
+      <c r="V51" s="31"/>
+      <c r="W51" s="31"/>
+      <c r="X51" s="35"/>
     </row>
     <row r="52" s="13" customFormat="1" ht="274.35" spans="1:24">
-      <c r="A52" s="45"/>
-      <c r="B52" s="46"/>
-      <c r="C52" s="47" t="s">
+      <c r="A52" s="42"/>
+      <c r="B52" s="43"/>
+      <c r="C52" s="44" t="s">
         <v>456</v>
       </c>
-      <c r="D52" s="47" t="s">
+      <c r="D52" s="44" t="s">
         <v>457</v>
       </c>
-      <c r="E52" s="47"/>
-      <c r="F52" s="48"/>
-      <c r="G52" s="49" t="s">
+      <c r="E52" s="44"/>
+      <c r="F52" s="45"/>
+      <c r="G52" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="H52" s="49"/>
-      <c r="I52" s="49"/>
-      <c r="J52" s="49"/>
-      <c r="K52" s="49"/>
-      <c r="L52" s="50"/>
-      <c r="M52" s="50"/>
-      <c r="N52" s="50"/>
-      <c r="O52" s="51"/>
-      <c r="P52" s="51" t="s">
+      <c r="H52" s="46"/>
+      <c r="I52" s="46"/>
+      <c r="J52" s="46"/>
+      <c r="K52" s="46"/>
+      <c r="L52" s="47"/>
+      <c r="M52" s="47"/>
+      <c r="N52" s="47"/>
+      <c r="O52" s="48"/>
+      <c r="P52" s="48" t="s">
         <v>256</v>
       </c>
-      <c r="Q52" s="51" t="s">
+      <c r="Q52" s="48" t="s">
         <v>263</v>
       </c>
-      <c r="R52" s="51" t="s">
+      <c r="R52" s="48" t="s">
         <v>270</v>
       </c>
-      <c r="S52" s="51"/>
-      <c r="T52" s="51" t="s">
+      <c r="S52" s="48"/>
+      <c r="T52" s="48" t="s">
         <v>283</v>
       </c>
-      <c r="U52" s="49" t="s">
+      <c r="U52" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="V52" s="49"/>
-      <c r="W52" s="49"/>
-      <c r="X52" s="52"/>
+      <c r="V52" s="46"/>
+      <c r="W52" s="46"/>
+      <c r="X52" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="179">

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -3951,7 +3951,7 @@
   </si>
   <si>
     <t>1提高最终产品、服务成果被验收的可能性
-2通过客观性的验收项目可交付成果</t>
+2客观性的验收项目可交付成果</t>
   </si>
   <si>
     <t>验收的可交付成果</t>
@@ -3960,8 +3960,8 @@
     <t>控制范围（监控过程组）</t>
   </si>
   <si>
-    <t>1维护项目范围基准
-2监督项目和产品的范围状态
+    <t>1监督项目和产品的范围
+2维护项目范围基准
 3管理范围基准变更</t>
   </si>
   <si>
@@ -3975,15 +3975,15 @@
     <t>定义活动（规划过程组）</t>
   </si>
   <si>
-    <t>1是项目进度估算、规划、执行、监督和控制的基础
-2为完成项目可交付成果，将工作包分解为进度活动，</t>
+    <t>1为完成项目可交付成果，将工作包分解为进度活动
+2是项目进度估算、规划、执行、监督和控制的基础</t>
   </si>
   <si>
     <t>排列活动顺序（规划过程组）</t>
   </si>
   <si>
-    <t>1使项目在制约因素下获得最高的效率
-2识别记录项目活动之间逻辑关系</t>
+    <t>1识别记录项目活动之间逻辑关系
+2使项目在制约因素下获得最高的效率</t>
   </si>
   <si>
     <t>估算活动持续时间（规划过程组）</t>
@@ -4160,304 +4160,127 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是识别单个项目风险以及整体项目风险的来源，并记录风险特征的过程
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">1记录单个项目风险和整体项目风险来源
+2汇总相关信息，以便项目团队能够恰当地应对已识别的风险  </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3识别单个项目风险以及整体项目风险的来源，并记录风险特征的过程</t>
+    </r>
+  </si>
+  <si>
+    <t>实施定性风险分析（规划过程组）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1重点关注高优先级的风险
+2通过评估单个项目风险发生的概率和影响及其他特征，对风险进行优先级排序
+</t>
+  </si>
+  <si>
+    <t>实施定量风险分析（规划过程组）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1量化整体项目风险最大可能性
+2提供额外的定量风险信息，以支持风险应对规划
+3就单个项目风险对整体项目目标的影响进行定量分析
+</t>
+  </si>
+  <si>
+    <t>规划风险应对（规划过程组）</t>
+  </si>
+  <si>
+    <t>1应对项目风险，而制定可选方案、应对策略并商定应对行动
+2制定整体项目风险和单个项目风险的应对方法
+3分配资源
+4根据需要将相关活动添加进项目文件和项目管理计划中</t>
+  </si>
+  <si>
+    <t>实施风险应对（执行过程组）</t>
+  </si>
+  <si>
+    <t>1执行商定的风险应对计划的过程
 作用：
-1记录单个项目风险和整体项目风险来源
-2汇总相关信息，以便项目团队能够恰当地应对已识别的风险</t>
-    </r>
-  </si>
-  <si>
-    <t>实施定性风险分析（规划过程组）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是通过评估单个项目风险发生的概率和影响及其他特征，对风险进行优先级排序，从而为后续分析或行动提供基础的过程
-作用：
-  是重点关注高优先级的风险</t>
-    </r>
-  </si>
-  <si>
-    <t>实施定量风险分析（规划过程组）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是就已识别的单个项目风险和不确定性的其他来源对整体项目目标的影响进行定量分析的过程
-作用：
-  1、量化整体项目风险最大可能性
-  2、提供额外的定量风险信息，以支持风险应对规划</t>
-    </r>
-  </si>
-  <si>
-    <t>规划风险应对（规划过程组）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 是为了应对项目风险，而制定可选方案、选择应对策略并商定应对行动的过程
-作用：
-  1、制定应对整体项目风险和单个项目风险的适当方法
-  2、分配资源，并根据需要将相关活动添加进项目文件和项目管理计划中</t>
-    </r>
-  </si>
-  <si>
-    <t>实施风险应对（执行过程组）</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是执行商定的风险应对计划的过程
-作用：
-  1、确保按计划执行商定的风险应对措施
-  2、管理整体项目风险入口、最小化单个项目威胁，以及最大化单个项目机会</t>
-    </r>
+2确保按计划执行商定的风险应对措施
+3管理整体项目风险入口、最小化单个项目威胁，以及最大化单个项目机会</t>
   </si>
   <si>
     <t>监督风险（监控过程组）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是在整个项目期间，监督风险应对计划的实施，并跟踪已识别风险、识别和分析新风险，以及评估风险管理有效性的过程
-作用：
-  保证项目决策是在整体项目风险和单个项目风险当前信息的基础上运行</t>
-    </r>
+    <t xml:space="preserve">
+1保证项目决策是在整体项目风险和单个项目风险当前信息的基础上运行
+2监督风险应对计划的实施3跟踪已识别风险、识别和分析新风险，4评估风险管理有效性的过程</t>
   </si>
   <si>
     <t>规划采购管理（规划过程组）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
- </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 是记录项目采购决策、明确采购方法，及识别潜在卖方的过程
-作用：
-  是确定是否从项目外部获取货物和服务，如果是，则还要确定将在什么时间、以什么方式获取什么货物和服务</t>
-    </r>
+    <t>1确定是否从项目外部获取货物和服务，2确定将在什么时间、以什么方式获取什么货物和服务
+3记录项目采购决策、明确采购方法，及识别潜在卖方</t>
   </si>
   <si>
     <t>实施采购（执行过程组）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是获取卖方应答、选择卖方并授予合同的过程
-作用：
-  选定合格卖方并签署关于货物或服务交付的法律协议</t>
-    </r>
+    <t>1选定合格卖方并签署关于货物或服务交付的法律协议
+2获取卖方应答、选择卖方并授予合同</t>
   </si>
   <si>
     <t>控制采购（监控过程组）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是管理采购关系、监督合同绩效、实施必要的变更和纠偏，以及关闭合同的过程
-作用：
-  确保买卖双方履行法律协议，满足项目需求</t>
-    </r>
+    <t>1确保买卖双方履行法律协议，满足项目需求
+2管理采购关系、监督合同绩效、实施必要的变更和纠偏，以及关闭合同</t>
   </si>
   <si>
     <t>识别干系人（启动过程组）</t>
   </si>
   <si>
-    <t>定义：
-  是定期识别项目干系人，分析和记录他们的利益、参与度、项目依赖性、影响力和对项目成功的潜在影响的过程
-作用：
-  使项目团队能够建立对每个干系人或干系人群体的适度关注</t>
+    <t>1使项目团队能够建立对每个干系人或干系人群体的适度关注
+2定期识别项目干系人，分析和记录他们的利益、参与度、项目依赖性、影响力和对项目成功的潜在影响</t>
   </si>
   <si>
     <t>规划干系人参与（规划过程组）</t>
   </si>
   <si>
-    <t>定义：
-  是根据干系人的需求、期望、利益和对项目的潜在影响，制定项目干系人参与项目的方法的过程
-作用：
-  提供与干系人进行有效互动的可行计划</t>
+    <t>1提供与干系人进行有效互动的可行计划
+2根据干系人的需求、期望、利益和对项目的潜在影响，制定项目干系人参与项目的方法</t>
   </si>
   <si>
     <t>管理干系人参与（执行过程组）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">  是通过与干系人进行沟通协作，以满足其需求与期望、处理问题，并促进干系人合理参与的过程
-作用：
-  尽可能提高干系人的支持度，并降低干系人的抵制程度</t>
-    </r>
+    <t>1尽可能提高干系人的支持度，并降低干系人的抵制程度
+2通过与干系人进行沟通协作，以满足其需求与期望、处理问题，并促进干系人合理参与</t>
   </si>
   <si>
     <t>基本规则</t>
@@ -4466,30 +4289,8 @@
     <t>监督干系人参与（监控过程组）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">定义：
-  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>是监督项目干系人的关系，并通过修订参与策略和计划来引导干系人合理参与项目的过程
-作用：
-  随着项目进展和环境变化，维持或提升干系人参与会随着项目进展和环境变化，维持或提升干系人参与活动的效率和效果</t>
-    </r>
+    <t>1维持或提升干系人参与活动的效率和效果
+2监督项目干系人的关系，并通过修订参与策略和计划来引导干系人合理参与项目</t>
   </si>
   <si>
     <t>立项管理</t>
@@ -5581,7 +5382,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -5715,6 +5516,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
@@ -6257,303 +6061,303 @@
     <row r="1" spans="1:51">
       <c r="A1" s="11"/>
       <c r="B1" s="11"/>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="53"/>
-      <c r="E1" s="53"/>
-      <c r="F1" s="53"/>
-      <c r="G1" s="53"/>
-      <c r="H1" s="53"/>
-      <c r="I1" s="53"/>
-      <c r="J1" s="53" t="s">
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
+      <c r="I1" s="54"/>
+      <c r="J1" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="53"/>
-      <c r="L1" s="53"/>
-      <c r="M1" s="53"/>
-      <c r="N1" s="53"/>
-      <c r="O1" s="53"/>
-      <c r="P1" s="53" t="s">
+      <c r="K1" s="54"/>
+      <c r="L1" s="54"/>
+      <c r="M1" s="54"/>
+      <c r="N1" s="54"/>
+      <c r="O1" s="54"/>
+      <c r="P1" s="54" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="53"/>
-      <c r="R1" s="53"/>
-      <c r="S1" s="53"/>
-      <c r="T1" s="53"/>
-      <c r="U1" s="53"/>
-      <c r="V1" s="53" t="s">
+      <c r="Q1" s="54"/>
+      <c r="R1" s="54"/>
+      <c r="S1" s="54"/>
+      <c r="T1" s="54"/>
+      <c r="U1" s="54"/>
+      <c r="V1" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="53" t="s">
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="53"/>
-      <c r="AB1" s="53"/>
-      <c r="AC1" s="53" t="s">
+      <c r="AA1" s="54"/>
+      <c r="AB1" s="54"/>
+      <c r="AC1" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="53"/>
-      <c r="AE1" s="53"/>
-      <c r="AF1" s="53"/>
-      <c r="AG1" s="53"/>
-      <c r="AH1" s="53"/>
-      <c r="AI1" s="53" t="s">
+      <c r="AD1" s="54"/>
+      <c r="AE1" s="54"/>
+      <c r="AF1" s="54"/>
+      <c r="AG1" s="54"/>
+      <c r="AH1" s="54"/>
+      <c r="AI1" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="AJ1" s="53"/>
-      <c r="AK1" s="53"/>
-      <c r="AL1" s="53" t="s">
+      <c r="AJ1" s="54"/>
+      <c r="AK1" s="54"/>
+      <c r="AL1" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="AM1" s="53"/>
-      <c r="AN1" s="53"/>
-      <c r="AO1" s="53"/>
-      <c r="AP1" s="53"/>
-      <c r="AQ1" s="53"/>
-      <c r="AR1" s="53"/>
-      <c r="AS1" s="53" t="s">
+      <c r="AM1" s="54"/>
+      <c r="AN1" s="54"/>
+      <c r="AO1" s="54"/>
+      <c r="AP1" s="54"/>
+      <c r="AQ1" s="54"/>
+      <c r="AR1" s="54"/>
+      <c r="AS1" s="54" t="s">
         <v>8</v>
       </c>
-      <c r="AT1" s="53"/>
-      <c r="AU1" s="53"/>
-      <c r="AV1" s="53" t="s">
+      <c r="AT1" s="54"/>
+      <c r="AU1" s="54"/>
+      <c r="AV1" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="AW1" s="53"/>
-      <c r="AX1" s="53"/>
-      <c r="AY1" s="53"/>
+      <c r="AW1" s="54"/>
+      <c r="AX1" s="54"/>
+      <c r="AY1" s="54"/>
     </row>
     <row r="2" customFormat="1" ht="58" customHeight="1" spans="1:51">
       <c r="A2" s="11"/>
       <c r="B2" s="11"/>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="55" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="56" t="s">
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="56"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+      <c r="J2" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="57"/>
-      <c r="L2" s="57"/>
-      <c r="M2" s="57"/>
-      <c r="N2" s="57"/>
-      <c r="O2" s="57"/>
-      <c r="P2" s="58" t="s">
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+      <c r="O2" s="58"/>
+      <c r="P2" s="59" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="57"/>
-      <c r="R2" s="57"/>
-      <c r="S2" s="57"/>
-      <c r="T2" s="57"/>
-      <c r="U2" s="59"/>
-      <c r="V2" s="58" t="s">
+      <c r="Q2" s="58"/>
+      <c r="R2" s="58"/>
+      <c r="S2" s="58"/>
+      <c r="T2" s="58"/>
+      <c r="U2" s="60"/>
+      <c r="V2" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="W2" s="57"/>
-      <c r="X2" s="57"/>
-      <c r="Y2" s="59"/>
-      <c r="Z2" s="56" t="s">
+      <c r="W2" s="58"/>
+      <c r="X2" s="58"/>
+      <c r="Y2" s="60"/>
+      <c r="Z2" s="57" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="57"/>
-      <c r="AB2" s="59"/>
-      <c r="AC2" s="58" t="s">
+      <c r="AA2" s="58"/>
+      <c r="AB2" s="60"/>
+      <c r="AC2" s="59" t="s">
         <v>15</v>
       </c>
-      <c r="AD2" s="57"/>
-      <c r="AE2" s="57"/>
-      <c r="AF2" s="57"/>
-      <c r="AG2" s="57"/>
-      <c r="AH2" s="59"/>
-      <c r="AI2" s="58" t="s">
+      <c r="AD2" s="58"/>
+      <c r="AE2" s="58"/>
+      <c r="AF2" s="58"/>
+      <c r="AG2" s="58"/>
+      <c r="AH2" s="60"/>
+      <c r="AI2" s="59" t="s">
         <v>16</v>
       </c>
-      <c r="AJ2" s="57"/>
-      <c r="AK2" s="59"/>
-      <c r="AL2" s="58" t="s">
+      <c r="AJ2" s="58"/>
+      <c r="AK2" s="60"/>
+      <c r="AL2" s="59" t="s">
         <v>17</v>
       </c>
-      <c r="AM2" s="57"/>
-      <c r="AN2" s="57"/>
-      <c r="AO2" s="57"/>
-      <c r="AP2" s="57"/>
-      <c r="AQ2" s="57"/>
-      <c r="AR2" s="59"/>
-      <c r="AS2" s="60" t="s">
+      <c r="AM2" s="58"/>
+      <c r="AN2" s="58"/>
+      <c r="AO2" s="58"/>
+      <c r="AP2" s="58"/>
+      <c r="AQ2" s="58"/>
+      <c r="AR2" s="60"/>
+      <c r="AS2" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="AT2" s="61"/>
-      <c r="AU2" s="62"/>
-      <c r="AV2" s="58" t="s">
+      <c r="AT2" s="62"/>
+      <c r="AU2" s="63"/>
+      <c r="AV2" s="59" t="s">
         <v>19</v>
       </c>
-      <c r="AW2" s="57"/>
-      <c r="AX2" s="57"/>
-      <c r="AY2" s="59"/>
+      <c r="AW2" s="58"/>
+      <c r="AX2" s="58"/>
+      <c r="AY2" s="60"/>
     </row>
-    <row r="3" s="50" customFormat="1" spans="1:51">
-      <c r="A3" s="63"/>
-      <c r="B3" s="63"/>
-      <c r="C3" s="64" t="s">
+    <row r="3" s="51" customFormat="1" spans="1:51">
+      <c r="A3" s="64"/>
+      <c r="B3" s="64"/>
+      <c r="C3" s="65" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="64" t="s">
+      <c r="D3" s="65" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="64" t="s">
+      <c r="E3" s="65" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="64" t="s">
+      <c r="F3" s="65" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="64" t="s">
+      <c r="G3" s="65" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="64" t="s">
+      <c r="H3" s="65" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="64" t="s">
+      <c r="I3" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="65" t="s">
+      <c r="J3" s="66" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="65" t="s">
+      <c r="K3" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="65" t="s">
+      <c r="L3" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="65" t="s">
+      <c r="M3" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="65" t="s">
+      <c r="N3" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="65" t="s">
+      <c r="O3" s="66" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="65" t="s">
+      <c r="P3" s="66" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="65" t="s">
+      <c r="Q3" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="R3" s="65" t="s">
+      <c r="R3" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="65" t="s">
+      <c r="S3" s="66" t="s">
         <v>36</v>
       </c>
-      <c r="T3" s="65" t="s">
+      <c r="T3" s="66" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="65" t="s">
+      <c r="U3" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="V3" s="65" t="s">
+      <c r="V3" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="W3" s="65" t="s">
+      <c r="W3" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="X3" s="65" t="s">
+      <c r="X3" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="65" t="s">
+      <c r="Y3" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="Z3" s="65" t="s">
+      <c r="Z3" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="AA3" s="65" t="s">
+      <c r="AA3" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="AB3" s="65" t="s">
+      <c r="AB3" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="AC3" s="65" t="s">
+      <c r="AC3" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="AD3" s="65" t="s">
+      <c r="AD3" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="AE3" s="65" t="s">
+      <c r="AE3" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="AF3" s="65" t="s">
+      <c r="AF3" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="AG3" s="65" t="s">
+      <c r="AG3" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="AH3" s="65" t="s">
+      <c r="AH3" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="AI3" s="65" t="s">
+      <c r="AI3" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="AJ3" s="65" t="s">
+      <c r="AJ3" s="66" t="s">
         <v>53</v>
       </c>
-      <c r="AK3" s="65" t="s">
+      <c r="AK3" s="66" t="s">
         <v>54</v>
       </c>
-      <c r="AL3" s="65" t="s">
+      <c r="AL3" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="AM3" s="65" t="s">
+      <c r="AM3" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="AN3" s="65" t="s">
+      <c r="AN3" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="AO3" s="65" t="s">
+      <c r="AO3" s="66" t="s">
         <v>58</v>
       </c>
-      <c r="AP3" s="65" t="s">
+      <c r="AP3" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="AQ3" s="65" t="s">
+      <c r="AQ3" s="66" t="s">
         <v>60</v>
       </c>
-      <c r="AR3" s="65" t="s">
+      <c r="AR3" s="66" t="s">
         <v>61</v>
       </c>
-      <c r="AS3" s="64" t="s">
+      <c r="AS3" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="AT3" s="64" t="s">
+      <c r="AT3" s="65" t="s">
         <v>63</v>
       </c>
-      <c r="AU3" s="64" t="s">
+      <c r="AU3" s="65" t="s">
         <v>64</v>
       </c>
-      <c r="AV3" s="64" t="s">
+      <c r="AV3" s="65" t="s">
         <v>65</v>
       </c>
-      <c r="AW3" s="64" t="s">
+      <c r="AW3" s="65" t="s">
         <v>66</v>
       </c>
-      <c r="AX3" s="64" t="s">
+      <c r="AX3" s="65" t="s">
         <v>67</v>
       </c>
-      <c r="AY3" s="64" t="s">
+      <c r="AY3" s="65" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" s="50" customFormat="1" ht="115.2" spans="1:51">
-      <c r="A4" s="63"/>
-      <c r="B4" s="63"/>
+    <row r="4" s="51" customFormat="1" ht="115.2" spans="1:51">
+      <c r="A4" s="64"/>
+      <c r="B4" s="64"/>
       <c r="C4" s="30" t="s">
         <v>69</v>
       </c>
@@ -6702,9 +6506,9 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" s="50" customFormat="1" ht="100.8" spans="1:51">
-      <c r="A5" s="63"/>
-      <c r="B5" s="63"/>
+    <row r="5" s="51" customFormat="1" ht="100.8" spans="1:51">
+      <c r="A5" s="64"/>
+      <c r="B5" s="64"/>
       <c r="C5" s="30"/>
       <c r="D5" s="30"/>
       <c r="E5" s="30"/>
@@ -6801,1730 +6605,1730 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" s="50" customFormat="1" ht="28.8" spans="1:51">
-      <c r="A6" s="63"/>
-      <c r="B6" s="63"/>
-      <c r="C6" s="66" t="s">
+    <row r="6" s="51" customFormat="1" ht="28.8" spans="1:51">
+      <c r="A6" s="64"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="66" t="s">
+      <c r="D6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="E6" s="66" t="s">
+      <c r="E6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="F6" s="66" t="s">
+      <c r="F6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="66" t="s">
+      <c r="G6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="H6" s="66" t="s">
+      <c r="H6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="I6" s="66" t="s">
+      <c r="I6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="J6" s="66" t="s">
+      <c r="J6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="K6" s="66" t="s">
+      <c r="K6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="L6" s="66" t="s">
+      <c r="L6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="M6" s="66" t="s">
+      <c r="M6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="N6" s="66" t="s">
+      <c r="N6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="O6" s="66" t="s">
+      <c r="O6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="P6" s="66" t="s">
+      <c r="P6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="Q6" s="66" t="s">
+      <c r="Q6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="R6" s="66" t="s">
+      <c r="R6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="S6" s="66" t="s">
+      <c r="S6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="T6" s="66" t="s">
+      <c r="T6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="U6" s="66" t="s">
+      <c r="U6" s="67" t="s">
         <v>141</v>
       </c>
       <c r="V6" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="W6" s="66" t="s">
+      <c r="W6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="X6" s="66" t="s">
+      <c r="X6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="Y6" s="66" t="s">
+      <c r="Y6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="Z6" s="66" t="s">
+      <c r="Z6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AA6" s="66" t="s">
+      <c r="AA6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AB6" s="66" t="s">
+      <c r="AB6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AC6" s="66" t="s">
+      <c r="AC6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AD6" s="66" t="s">
+      <c r="AD6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AE6" s="66" t="s">
+      <c r="AE6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AF6" s="66" t="s">
+      <c r="AF6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AG6" s="66" t="s">
+      <c r="AG6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AH6" s="66" t="s">
+      <c r="AH6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AI6" s="66" t="s">
+      <c r="AI6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AJ6" s="66" t="s">
+      <c r="AJ6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AK6" s="66" t="s">
+      <c r="AK6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AL6" s="66" t="s">
+      <c r="AL6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AM6" s="66" t="s">
+      <c r="AM6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AN6" s="66" t="s">
+      <c r="AN6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AO6" s="66" t="s">
+      <c r="AO6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AP6" s="66" t="s">
+      <c r="AP6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AQ6" s="66" t="s">
+      <c r="AQ6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="66" t="s">
+      <c r="AR6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AS6" s="66" t="s">
+      <c r="AS6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AT6" s="66" t="s">
+      <c r="AT6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AU6" s="66" t="s">
+      <c r="AU6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AV6" s="66" t="s">
+      <c r="AV6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AW6" s="66" t="s">
+      <c r="AW6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AX6" s="66" t="s">
+      <c r="AX6" s="67" t="s">
         <v>141</v>
       </c>
-      <c r="AY6" s="66" t="s">
+      <c r="AY6" s="67" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="7" s="50" customFormat="1" ht="57.6" spans="1:51">
-      <c r="A7" s="67" t="s">
+    <row r="7" s="51" customFormat="1" ht="57.6" spans="1:51">
+      <c r="A7" s="68" t="s">
         <v>143</v>
       </c>
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="67" t="s">
         <v>144</v>
       </c>
-      <c r="C7" s="68" t="s">
+      <c r="C7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="D7" s="66" t="s">
+      <c r="D7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="E7" s="66" t="s">
+      <c r="E7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="F7" s="66" t="s">
+      <c r="F7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="G7" s="66" t="s">
+      <c r="G7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="H7" s="66" t="s">
+      <c r="H7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="I7" s="66" t="s">
+      <c r="I7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="J7" s="66" t="s">
+      <c r="J7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="K7" s="66" t="s">
+      <c r="K7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="L7" s="66" t="s">
+      <c r="L7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="M7" s="66" t="s">
+      <c r="M7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="N7" s="66" t="s">
+      <c r="N7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="O7" s="66" t="s">
+      <c r="O7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="P7" s="66" t="s">
+      <c r="P7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="Q7" s="66" t="s">
+      <c r="Q7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="R7" s="66" t="s">
+      <c r="R7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="S7" s="66" t="s">
+      <c r="S7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="T7" s="66" t="s">
+      <c r="T7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="U7" s="66" t="s">
+      <c r="U7" s="67" t="s">
         <v>145</v>
       </c>
       <c r="V7" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="W7" s="66" t="s">
+      <c r="W7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="X7" s="66" t="s">
+      <c r="X7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="Y7" s="66" t="s">
+      <c r="Y7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="Z7" s="66" t="s">
+      <c r="Z7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AA7" s="66" t="s">
+      <c r="AA7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AB7" s="66" t="s">
+      <c r="AB7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AC7" s="66" t="s">
+      <c r="AC7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AD7" s="66" t="s">
+      <c r="AD7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AE7" s="66" t="s">
+      <c r="AE7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AF7" s="66" t="s">
+      <c r="AF7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AG7" s="66" t="s">
+      <c r="AG7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AH7" s="66" t="s">
+      <c r="AH7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AI7" s="66" t="s">
+      <c r="AI7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AJ7" s="66" t="s">
+      <c r="AJ7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AK7" s="66" t="s">
+      <c r="AK7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AL7" s="66" t="s">
+      <c r="AL7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AM7" s="66" t="s">
+      <c r="AM7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AN7" s="66" t="s">
+      <c r="AN7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AO7" s="66" t="s">
+      <c r="AO7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AP7" s="66" t="s">
+      <c r="AP7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AQ7" s="66" t="s">
+      <c r="AQ7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AR7" s="66" t="s">
+      <c r="AR7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AS7" s="66" t="s">
+      <c r="AS7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AT7" s="66" t="s">
+      <c r="AT7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AU7" s="66" t="s">
+      <c r="AU7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AV7" s="66" t="s">
+      <c r="AV7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AW7" s="66" t="s">
+      <c r="AW7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AX7" s="66" t="s">
+      <c r="AX7" s="67" t="s">
         <v>145</v>
       </c>
-      <c r="AY7" s="66" t="s">
+      <c r="AY7" s="67" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="8" ht="72" spans="1:51">
-      <c r="A8" s="69"/>
-      <c r="B8" s="70" t="s">
+      <c r="A8" s="70"/>
+      <c r="B8" s="71" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="71" t="s">
+      <c r="C8" s="72" t="s">
         <v>148</v>
       </c>
-      <c r="D8" s="71" t="s">
+      <c r="D8" s="72" t="s">
         <v>149</v>
       </c>
-      <c r="E8" s="71" t="s">
+      <c r="E8" s="72" t="s">
         <v>150</v>
       </c>
-      <c r="F8" s="71" t="s">
+      <c r="F8" s="72" t="s">
         <v>151</v>
       </c>
-      <c r="G8" s="71" t="s">
+      <c r="G8" s="72" t="s">
         <v>152</v>
       </c>
-      <c r="H8" s="71" t="s">
+      <c r="H8" s="72" t="s">
         <v>153</v>
       </c>
-      <c r="I8" s="71" t="s">
+      <c r="I8" s="72" t="s">
         <v>154</v>
       </c>
-      <c r="J8" s="71" t="s">
+      <c r="J8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="K8" s="71" t="s">
+      <c r="K8" s="72" t="s">
         <v>156</v>
       </c>
-      <c r="L8" s="71" t="s">
+      <c r="L8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="M8" s="71" t="s">
+      <c r="M8" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="N8" s="71" t="s">
+      <c r="N8" s="72" t="s">
         <v>158</v>
       </c>
-      <c r="O8" s="71" t="s">
+      <c r="O8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="P8" s="71" t="s">
+      <c r="P8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="Q8" s="71" t="s">
+      <c r="Q8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="R8" s="71" t="s">
+      <c r="R8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="S8" s="71" t="s">
+      <c r="S8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="T8" s="71" t="s">
+      <c r="T8" s="72" t="s">
         <v>159</v>
       </c>
-      <c r="U8" s="71" t="s">
+      <c r="U8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="V8" s="71" t="s">
+      <c r="V8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="W8" s="71" t="s">
+      <c r="W8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="X8" s="71" t="s">
+      <c r="X8" s="72" t="s">
         <v>160</v>
       </c>
-      <c r="Y8" s="71" t="s">
+      <c r="Y8" s="72" t="s">
         <v>161</v>
       </c>
-      <c r="Z8" s="71" t="s">
+      <c r="Z8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AA8" s="71" t="s">
+      <c r="AA8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AB8" s="71" t="s">
+      <c r="AB8" s="72" t="s">
         <v>162</v>
       </c>
-      <c r="AC8" s="71" t="s">
+      <c r="AC8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AD8" s="71" t="s">
+      <c r="AD8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AE8" s="71" t="s">
+      <c r="AE8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AF8" s="71" t="s">
+      <c r="AF8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AG8" s="71" t="s">
+      <c r="AG8" s="72" t="s">
         <v>163</v>
       </c>
-      <c r="AH8" s="71" t="s">
+      <c r="AH8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AI8" s="71" t="s">
+      <c r="AI8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AJ8" s="71" t="s">
+      <c r="AJ8" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="AK8" s="71" t="s">
+      <c r="AK8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AL8" s="71" t="s">
+      <c r="AL8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AM8" s="71" t="s">
+      <c r="AM8" s="72" t="s">
         <v>165</v>
       </c>
-      <c r="AN8" s="71" t="s">
+      <c r="AN8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AO8" s="71" t="s">
+      <c r="AO8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AP8" s="71" t="s">
+      <c r="AP8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AQ8" s="71" t="s">
+      <c r="AQ8" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="AR8" s="71" t="s">
+      <c r="AR8" s="72" t="s">
         <v>164</v>
       </c>
-      <c r="AS8" s="72" t="s">
+      <c r="AS8" s="73" t="s">
         <v>166</v>
       </c>
-      <c r="AT8" s="72" t="s">
+      <c r="AT8" s="73" t="s">
         <v>167</v>
       </c>
-      <c r="AU8" s="72" t="s">
+      <c r="AU8" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="AV8" s="72" t="s">
+      <c r="AV8" s="73" t="s">
         <v>169</v>
       </c>
-      <c r="AW8" s="72" t="s">
+      <c r="AW8" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="AX8" s="73" t="s">
+      <c r="AX8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AY8" s="73" t="s">
+      <c r="AY8" s="74" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="9" ht="43.2" spans="1:51">
-      <c r="A9" s="69"/>
+      <c r="A9" s="70"/>
       <c r="B9" s="25" t="s">
         <v>170</v>
       </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="72"/>
-      <c r="F9" s="72"/>
-      <c r="G9" s="72"/>
-      <c r="H9" s="72"/>
-      <c r="I9" s="72"/>
-      <c r="J9" s="72"/>
-      <c r="K9" s="72" t="s">
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
+      <c r="J9" s="73"/>
+      <c r="K9" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="L9" s="72"/>
-      <c r="M9" s="72"/>
-      <c r="N9" s="72" t="s">
+      <c r="L9" s="73"/>
+      <c r="M9" s="73"/>
+      <c r="N9" s="73" t="s">
         <v>172</v>
       </c>
-      <c r="O9" s="72"/>
-      <c r="P9" s="72"/>
-      <c r="Q9" s="72"/>
-      <c r="R9" s="72"/>
-      <c r="S9" s="72"/>
-      <c r="T9" s="72"/>
-      <c r="U9" s="72"/>
-      <c r="V9" s="72"/>
-      <c r="W9" s="72"/>
-      <c r="X9" s="72"/>
-      <c r="Y9" s="72"/>
-      <c r="Z9" s="72"/>
-      <c r="AA9" s="72"/>
-      <c r="AB9" s="72"/>
-      <c r="AC9" s="72"/>
-      <c r="AD9" s="72"/>
-      <c r="AE9" s="72"/>
-      <c r="AF9" s="72"/>
-      <c r="AG9" s="72"/>
-      <c r="AH9" s="72"/>
-      <c r="AI9" s="72"/>
-      <c r="AJ9" s="72"/>
-      <c r="AK9" s="72"/>
-      <c r="AL9" s="72"/>
-      <c r="AM9" s="72"/>
-      <c r="AN9" s="72"/>
-      <c r="AO9" s="72"/>
-      <c r="AP9" s="72"/>
-      <c r="AQ9" s="72"/>
-      <c r="AR9" s="72"/>
-      <c r="AS9" s="72"/>
-      <c r="AT9" s="72"/>
-      <c r="AU9" s="72"/>
-      <c r="AV9" s="72"/>
-      <c r="AW9" s="72"/>
-      <c r="AX9" s="73"/>
-      <c r="AY9" s="73"/>
+      <c r="O9" s="73"/>
+      <c r="P9" s="73"/>
+      <c r="Q9" s="73"/>
+      <c r="R9" s="73"/>
+      <c r="S9" s="73"/>
+      <c r="T9" s="73"/>
+      <c r="U9" s="73"/>
+      <c r="V9" s="73"/>
+      <c r="W9" s="73"/>
+      <c r="X9" s="73"/>
+      <c r="Y9" s="73"/>
+      <c r="Z9" s="73"/>
+      <c r="AA9" s="73"/>
+      <c r="AB9" s="73"/>
+      <c r="AC9" s="73"/>
+      <c r="AD9" s="73"/>
+      <c r="AE9" s="73"/>
+      <c r="AF9" s="73"/>
+      <c r="AG9" s="73"/>
+      <c r="AH9" s="73"/>
+      <c r="AI9" s="73"/>
+      <c r="AJ9" s="73"/>
+      <c r="AK9" s="73"/>
+      <c r="AL9" s="73"/>
+      <c r="AM9" s="73"/>
+      <c r="AN9" s="73"/>
+      <c r="AO9" s="73"/>
+      <c r="AP9" s="73"/>
+      <c r="AQ9" s="73"/>
+      <c r="AR9" s="73"/>
+      <c r="AS9" s="73"/>
+      <c r="AT9" s="73"/>
+      <c r="AU9" s="73"/>
+      <c r="AV9" s="73"/>
+      <c r="AW9" s="73"/>
+      <c r="AX9" s="74"/>
+      <c r="AY9" s="74"/>
     </row>
     <row r="10" ht="86.4" spans="1:51">
-      <c r="A10" s="74"/>
+      <c r="A10" s="75"/>
       <c r="B10" s="25" t="s">
         <v>173</v>
       </c>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72" t="s">
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+      <c r="J10" s="73"/>
+      <c r="K10" s="73" t="s">
         <v>174</v>
       </c>
-      <c r="L10" s="72" t="s">
+      <c r="L10" s="73" t="s">
         <v>175</v>
       </c>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72" t="s">
+      <c r="M10" s="73"/>
+      <c r="N10" s="73" t="s">
         <v>176</v>
       </c>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="72"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="72"/>
-      <c r="V10" s="72"/>
-      <c r="W10" s="72"/>
-      <c r="X10" s="72"/>
-      <c r="Y10" s="72"/>
-      <c r="Z10" s="72"/>
-      <c r="AA10" s="72" t="s">
+      <c r="O10" s="73"/>
+      <c r="P10" s="73"/>
+      <c r="Q10" s="73"/>
+      <c r="R10" s="73"/>
+      <c r="S10" s="73"/>
+      <c r="T10" s="73"/>
+      <c r="U10" s="73"/>
+      <c r="V10" s="73"/>
+      <c r="W10" s="73"/>
+      <c r="X10" s="73"/>
+      <c r="Y10" s="73"/>
+      <c r="Z10" s="73"/>
+      <c r="AA10" s="73" t="s">
         <v>177</v>
       </c>
-      <c r="AB10" s="72"/>
-      <c r="AC10" s="72"/>
-      <c r="AD10" s="72"/>
-      <c r="AE10" s="72"/>
-      <c r="AF10" s="72"/>
-      <c r="AG10" s="72"/>
-      <c r="AH10" s="72"/>
-      <c r="AI10" s="72"/>
-      <c r="AJ10" s="72" t="s">
+      <c r="AB10" s="73"/>
+      <c r="AC10" s="73"/>
+      <c r="AD10" s="73"/>
+      <c r="AE10" s="73"/>
+      <c r="AF10" s="73"/>
+      <c r="AG10" s="73"/>
+      <c r="AH10" s="73"/>
+      <c r="AI10" s="73"/>
+      <c r="AJ10" s="73" t="s">
         <v>178</v>
       </c>
-      <c r="AK10" s="72"/>
-      <c r="AL10" s="72"/>
-      <c r="AM10" s="72"/>
-      <c r="AN10" s="72"/>
-      <c r="AO10" s="72"/>
-      <c r="AP10" s="72"/>
-      <c r="AQ10" s="72"/>
-      <c r="AR10" s="72"/>
-      <c r="AS10" s="72"/>
-      <c r="AT10" s="72"/>
-      <c r="AU10" s="72"/>
-      <c r="AV10" s="72"/>
-      <c r="AW10" s="72"/>
-      <c r="AX10" s="73"/>
-      <c r="AY10" s="73"/>
+      <c r="AK10" s="73"/>
+      <c r="AL10" s="73"/>
+      <c r="AM10" s="73"/>
+      <c r="AN10" s="73"/>
+      <c r="AO10" s="73"/>
+      <c r="AP10" s="73"/>
+      <c r="AQ10" s="73"/>
+      <c r="AR10" s="73"/>
+      <c r="AS10" s="73"/>
+      <c r="AT10" s="73"/>
+      <c r="AU10" s="73"/>
+      <c r="AV10" s="73"/>
+      <c r="AW10" s="73"/>
+      <c r="AX10" s="74"/>
+      <c r="AY10" s="74"/>
     </row>
     <row r="11" spans="1:51">
-      <c r="A11" s="75" t="s">
+      <c r="A11" s="76" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="76" t="s">
+      <c r="B11" s="77" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="51"/>
-      <c r="E11" s="51"/>
-      <c r="F11" s="51"/>
-      <c r="G11" s="51"/>
-      <c r="H11" s="51"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="51"/>
-      <c r="K11" s="51"/>
-      <c r="L11" s="51"/>
-      <c r="M11" s="51"/>
-      <c r="N11" s="51"/>
-      <c r="O11" s="51"/>
-      <c r="P11" s="51"/>
-      <c r="Q11" s="51"/>
-      <c r="R11" s="51"/>
-      <c r="S11" s="51"/>
-      <c r="T11" s="51"/>
-      <c r="U11" s="51"/>
-      <c r="V11" s="51"/>
-      <c r="W11" s="51"/>
-      <c r="X11" s="51"/>
-      <c r="Y11" s="51"/>
-      <c r="Z11" s="51"/>
-      <c r="AA11" s="51"/>
-      <c r="AB11" s="51"/>
-      <c r="AC11" s="51"/>
-      <c r="AD11" s="51"/>
-      <c r="AE11" s="51"/>
-      <c r="AF11" s="51"/>
-      <c r="AG11" s="51"/>
-      <c r="AH11" s="51"/>
-      <c r="AI11" s="51"/>
-      <c r="AJ11" s="51"/>
-      <c r="AK11" s="51"/>
-      <c r="AL11" s="51"/>
-      <c r="AM11" s="51"/>
-      <c r="AN11" s="51"/>
-      <c r="AO11" s="51"/>
-      <c r="AP11" s="51"/>
-      <c r="AQ11" s="51"/>
-      <c r="AR11" s="51"/>
-      <c r="AS11" s="51"/>
-      <c r="AT11" s="51"/>
-      <c r="AU11" s="51"/>
-      <c r="AV11" s="51"/>
-      <c r="AW11" s="51"/>
-      <c r="AX11" s="51"/>
-      <c r="AY11" s="51"/>
+      <c r="C11" s="52"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="52"/>
+      <c r="K11" s="52"/>
+      <c r="L11" s="52"/>
+      <c r="M11" s="52"/>
+      <c r="N11" s="52"/>
+      <c r="O11" s="52"/>
+      <c r="P11" s="52"/>
+      <c r="Q11" s="52"/>
+      <c r="R11" s="52"/>
+      <c r="S11" s="52"/>
+      <c r="T11" s="52"/>
+      <c r="U11" s="52"/>
+      <c r="V11" s="52"/>
+      <c r="W11" s="52"/>
+      <c r="X11" s="52"/>
+      <c r="Y11" s="52"/>
+      <c r="Z11" s="52"/>
+      <c r="AA11" s="52"/>
+      <c r="AB11" s="52"/>
+      <c r="AC11" s="52"/>
+      <c r="AD11" s="52"/>
+      <c r="AE11" s="52"/>
+      <c r="AF11" s="52"/>
+      <c r="AG11" s="52"/>
+      <c r="AH11" s="52"/>
+      <c r="AI11" s="52"/>
+      <c r="AJ11" s="52"/>
+      <c r="AK11" s="52"/>
+      <c r="AL11" s="52"/>
+      <c r="AM11" s="52"/>
+      <c r="AN11" s="52"/>
+      <c r="AO11" s="52"/>
+      <c r="AP11" s="52"/>
+      <c r="AQ11" s="52"/>
+      <c r="AR11" s="52"/>
+      <c r="AS11" s="52"/>
+      <c r="AT11" s="52"/>
+      <c r="AU11" s="52"/>
+      <c r="AV11" s="52"/>
+      <c r="AW11" s="52"/>
+      <c r="AX11" s="52"/>
+      <c r="AY11" s="52"/>
     </row>
     <row r="12" spans="1:51">
-      <c r="A12" s="75" t="s">
+      <c r="A12" s="76" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="77" t="s">
+      <c r="B12" s="78" t="s">
         <v>182</v>
       </c>
-      <c r="C12" s="51"/>
-      <c r="D12" s="51"/>
-      <c r="E12" s="51"/>
-      <c r="F12" s="51"/>
-      <c r="G12" s="51"/>
-      <c r="H12" s="51"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="51"/>
-      <c r="K12" s="51"/>
-      <c r="L12" s="51"/>
-      <c r="M12" s="51"/>
-      <c r="N12" s="51"/>
-      <c r="O12" s="51"/>
-      <c r="P12" s="51"/>
-      <c r="Q12" s="51"/>
-      <c r="R12" s="51"/>
-      <c r="S12" s="51"/>
-      <c r="T12" s="51"/>
-      <c r="U12" s="51"/>
-      <c r="V12" s="51"/>
-      <c r="W12" s="51"/>
-      <c r="X12" s="51"/>
-      <c r="Y12" s="51"/>
-      <c r="Z12" s="51"/>
-      <c r="AA12" s="51"/>
-      <c r="AB12" s="51"/>
-      <c r="AC12" s="51"/>
-      <c r="AD12" s="51"/>
-      <c r="AE12" s="51"/>
-      <c r="AF12" s="51"/>
-      <c r="AG12" s="51"/>
-      <c r="AH12" s="51"/>
-      <c r="AI12" s="51"/>
-      <c r="AJ12" s="51"/>
-      <c r="AK12" s="51"/>
-      <c r="AL12" s="51"/>
-      <c r="AM12" s="51"/>
-      <c r="AN12" s="51"/>
-      <c r="AO12" s="51"/>
-      <c r="AP12" s="51"/>
-      <c r="AQ12" s="51"/>
-      <c r="AR12" s="51"/>
-      <c r="AS12" s="51"/>
-      <c r="AT12" s="51"/>
-      <c r="AU12" s="51"/>
-      <c r="AV12" s="51"/>
-      <c r="AW12" s="51"/>
-      <c r="AX12" s="51"/>
-      <c r="AY12" s="51"/>
+      <c r="C12" s="52"/>
+      <c r="D12" s="52"/>
+      <c r="E12" s="52"/>
+      <c r="F12" s="52"/>
+      <c r="G12" s="52"/>
+      <c r="H12" s="52"/>
+      <c r="I12" s="52"/>
+      <c r="J12" s="52"/>
+      <c r="K12" s="52"/>
+      <c r="L12" s="52"/>
+      <c r="M12" s="52"/>
+      <c r="N12" s="52"/>
+      <c r="O12" s="52"/>
+      <c r="P12" s="52"/>
+      <c r="Q12" s="52"/>
+      <c r="R12" s="52"/>
+      <c r="S12" s="52"/>
+      <c r="T12" s="52"/>
+      <c r="U12" s="52"/>
+      <c r="V12" s="52"/>
+      <c r="W12" s="52"/>
+      <c r="X12" s="52"/>
+      <c r="Y12" s="52"/>
+      <c r="Z12" s="52"/>
+      <c r="AA12" s="52"/>
+      <c r="AB12" s="52"/>
+      <c r="AC12" s="52"/>
+      <c r="AD12" s="52"/>
+      <c r="AE12" s="52"/>
+      <c r="AF12" s="52"/>
+      <c r="AG12" s="52"/>
+      <c r="AH12" s="52"/>
+      <c r="AI12" s="52"/>
+      <c r="AJ12" s="52"/>
+      <c r="AK12" s="52"/>
+      <c r="AL12" s="52"/>
+      <c r="AM12" s="52"/>
+      <c r="AN12" s="52"/>
+      <c r="AO12" s="52"/>
+      <c r="AP12" s="52"/>
+      <c r="AQ12" s="52"/>
+      <c r="AR12" s="52"/>
+      <c r="AS12" s="52"/>
+      <c r="AT12" s="52"/>
+      <c r="AU12" s="52"/>
+      <c r="AV12" s="52"/>
+      <c r="AW12" s="52"/>
+      <c r="AX12" s="52"/>
+      <c r="AY12" s="52"/>
     </row>
     <row r="14" ht="115.2" spans="1:51">
-      <c r="A14" s="78" t="s">
+      <c r="A14" s="79" t="s">
         <v>183</v>
       </c>
-      <c r="B14" s="79" t="s">
+      <c r="B14" s="80" t="s">
         <v>184</v>
       </c>
-      <c r="C14" s="80"/>
-      <c r="D14" s="81"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="81" t="s">
+      <c r="C14" s="81"/>
+      <c r="D14" s="82"/>
+      <c r="E14" s="82"/>
+      <c r="F14" s="82" t="s">
         <v>185</v>
       </c>
-      <c r="G14" s="81"/>
-      <c r="H14" s="81" t="s">
+      <c r="G14" s="82"/>
+      <c r="H14" s="82" t="s">
         <v>186</v>
       </c>
-      <c r="I14" s="81"/>
-      <c r="J14" s="81"/>
-      <c r="K14" s="81" t="s">
+      <c r="I14" s="82"/>
+      <c r="J14" s="82"/>
+      <c r="K14" s="82" t="s">
         <v>187</v>
       </c>
-      <c r="L14" s="81" t="s">
+      <c r="L14" s="82" t="s">
         <v>188</v>
       </c>
-      <c r="M14" s="81" t="s">
+      <c r="M14" s="82" t="s">
         <v>189</v>
       </c>
-      <c r="N14" s="81" t="s">
+      <c r="N14" s="82" t="s">
         <v>190</v>
       </c>
-      <c r="O14" s="81"/>
-      <c r="P14" s="81"/>
-      <c r="Q14" s="81" t="s">
+      <c r="O14" s="82"/>
+      <c r="P14" s="82"/>
+      <c r="Q14" s="82" t="s">
         <v>191</v>
       </c>
-      <c r="R14" s="81" t="s">
+      <c r="R14" s="82" t="s">
         <v>192</v>
       </c>
-      <c r="S14" s="81" t="s">
+      <c r="S14" s="82" t="s">
         <v>193</v>
       </c>
-      <c r="T14" s="81" t="s">
+      <c r="T14" s="82" t="s">
         <v>194</v>
       </c>
-      <c r="U14" s="81" t="s">
+      <c r="U14" s="82" t="s">
         <v>195</v>
       </c>
-      <c r="V14" s="81"/>
-      <c r="W14" s="81" t="s">
+      <c r="V14" s="82"/>
+      <c r="W14" s="82" t="s">
         <v>193</v>
       </c>
-      <c r="X14" s="81" t="s">
+      <c r="X14" s="82" t="s">
         <v>196</v>
       </c>
-      <c r="Y14" s="81" t="s">
+      <c r="Y14" s="82" t="s">
         <v>197</v>
       </c>
-      <c r="Z14" s="81" t="s">
+      <c r="Z14" s="82" t="s">
         <v>198</v>
       </c>
-      <c r="AA14" s="81" t="s">
+      <c r="AA14" s="82" t="s">
         <v>199</v>
       </c>
-      <c r="AB14" s="81" t="s">
+      <c r="AB14" s="82" t="s">
         <v>200</v>
       </c>
-      <c r="AC14" s="81" t="s">
+      <c r="AC14" s="82" t="s">
         <v>201</v>
       </c>
-      <c r="AD14" s="81" t="s">
+      <c r="AD14" s="82" t="s">
         <v>202</v>
       </c>
-      <c r="AE14" s="81" t="s">
+      <c r="AE14" s="82" t="s">
         <v>203</v>
       </c>
-      <c r="AF14" s="81" t="s">
+      <c r="AF14" s="82" t="s">
         <v>204</v>
       </c>
-      <c r="AG14" s="81"/>
-      <c r="AH14" s="81" t="s">
+      <c r="AG14" s="82"/>
+      <c r="AH14" s="82" t="s">
         <v>205</v>
       </c>
-      <c r="AI14" s="81" t="s">
+      <c r="AI14" s="82" t="s">
         <v>206</v>
       </c>
-      <c r="AJ14" s="81" t="s">
+      <c r="AJ14" s="82" t="s">
         <v>207</v>
       </c>
-      <c r="AK14" s="81"/>
-      <c r="AL14" s="81"/>
-      <c r="AM14" s="81" t="s">
+      <c r="AK14" s="82"/>
+      <c r="AL14" s="82"/>
+      <c r="AM14" s="82" t="s">
         <v>208</v>
       </c>
-      <c r="AN14" s="81" t="s">
+      <c r="AN14" s="82" t="s">
         <v>209</v>
       </c>
-      <c r="AO14" s="81" t="s">
+      <c r="AO14" s="82" t="s">
         <v>210</v>
       </c>
-      <c r="AP14" s="81" t="s">
+      <c r="AP14" s="82" t="s">
         <v>211</v>
       </c>
-      <c r="AQ14" s="81"/>
-      <c r="AR14" s="81" t="s">
+      <c r="AQ14" s="82"/>
+      <c r="AR14" s="82" t="s">
         <v>212</v>
       </c>
-      <c r="AS14" s="82" t="s">
+      <c r="AS14" s="83" t="s">
         <v>213</v>
       </c>
-      <c r="AT14" s="81" t="s">
+      <c r="AT14" s="82" t="s">
         <v>214</v>
       </c>
-      <c r="AU14" s="81" t="s">
+      <c r="AU14" s="82" t="s">
         <v>215</v>
       </c>
-      <c r="AV14" s="73"/>
-      <c r="AW14" s="73"/>
-      <c r="AX14" s="72" t="s">
+      <c r="AV14" s="74"/>
+      <c r="AW14" s="74"/>
+      <c r="AX14" s="73" t="s">
         <v>216</v>
       </c>
-      <c r="AY14" s="72"/>
+      <c r="AY14" s="73"/>
     </row>
     <row r="15" spans="1:51">
-      <c r="A15" s="83"/>
-      <c r="B15" s="84" t="s">
+      <c r="A15" s="84"/>
+      <c r="B15" s="85" t="s">
         <v>217</v>
       </c>
-      <c r="C15" s="85"/>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77"/>
-      <c r="G15" s="77"/>
-      <c r="H15" s="77"/>
-      <c r="I15" s="77"/>
-      <c r="J15" s="77"/>
-      <c r="K15" s="77"/>
-      <c r="L15" s="77"/>
-      <c r="M15" s="77"/>
-      <c r="N15" s="77"/>
-      <c r="O15" s="77"/>
-      <c r="P15" s="77"/>
-      <c r="Q15" s="77"/>
-      <c r="R15" s="77"/>
-      <c r="S15" s="77"/>
-      <c r="T15" s="77"/>
-      <c r="U15" s="77"/>
-      <c r="V15" s="77"/>
-      <c r="W15" s="77"/>
-      <c r="X15" s="77"/>
-      <c r="Y15" s="77"/>
-      <c r="Z15" s="77"/>
-      <c r="AA15" s="77"/>
-      <c r="AB15" s="77"/>
-      <c r="AC15" s="77"/>
-      <c r="AD15" s="77"/>
-      <c r="AE15" s="77"/>
-      <c r="AF15" s="77"/>
-      <c r="AG15" s="77"/>
-      <c r="AH15" s="77"/>
-      <c r="AI15" s="77"/>
-      <c r="AJ15" s="77"/>
-      <c r="AK15" s="77"/>
-      <c r="AL15" s="77"/>
-      <c r="AM15" s="77"/>
-      <c r="AN15" s="77"/>
-      <c r="AO15" s="77"/>
-      <c r="AP15" s="77"/>
-      <c r="AQ15" s="77"/>
-      <c r="AR15" s="77"/>
-      <c r="AS15" s="77"/>
-      <c r="AT15" s="77"/>
-      <c r="AU15" s="77"/>
-      <c r="AV15" s="77"/>
-      <c r="AW15" s="77"/>
-      <c r="AX15" s="77"/>
-      <c r="AY15" s="77"/>
+      <c r="C15" s="86"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="78"/>
+      <c r="F15" s="78"/>
+      <c r="G15" s="78"/>
+      <c r="H15" s="78"/>
+      <c r="I15" s="78"/>
+      <c r="J15" s="78"/>
+      <c r="K15" s="78"/>
+      <c r="L15" s="78"/>
+      <c r="M15" s="78"/>
+      <c r="N15" s="78"/>
+      <c r="O15" s="78"/>
+      <c r="P15" s="78"/>
+      <c r="Q15" s="78"/>
+      <c r="R15" s="78"/>
+      <c r="S15" s="78"/>
+      <c r="T15" s="78"/>
+      <c r="U15" s="78"/>
+      <c r="V15" s="78"/>
+      <c r="W15" s="78"/>
+      <c r="X15" s="78"/>
+      <c r="Y15" s="78"/>
+      <c r="Z15" s="78"/>
+      <c r="AA15" s="78"/>
+      <c r="AB15" s="78"/>
+      <c r="AC15" s="78"/>
+      <c r="AD15" s="78"/>
+      <c r="AE15" s="78"/>
+      <c r="AF15" s="78"/>
+      <c r="AG15" s="78"/>
+      <c r="AH15" s="78"/>
+      <c r="AI15" s="78"/>
+      <c r="AJ15" s="78"/>
+      <c r="AK15" s="78"/>
+      <c r="AL15" s="78"/>
+      <c r="AM15" s="78"/>
+      <c r="AN15" s="78"/>
+      <c r="AO15" s="78"/>
+      <c r="AP15" s="78"/>
+      <c r="AQ15" s="78"/>
+      <c r="AR15" s="78"/>
+      <c r="AS15" s="78"/>
+      <c r="AT15" s="78"/>
+      <c r="AU15" s="78"/>
+      <c r="AV15" s="78"/>
+      <c r="AW15" s="78"/>
+      <c r="AX15" s="78"/>
+      <c r="AY15" s="78"/>
     </row>
     <row r="16" ht="72" spans="1:51">
-      <c r="A16" s="83"/>
-      <c r="B16" s="84" t="s">
+      <c r="A16" s="84"/>
+      <c r="B16" s="85" t="s">
         <v>218</v>
       </c>
-      <c r="C16" s="86" t="s">
+      <c r="C16" s="87" t="s">
         <v>219</v>
       </c>
-      <c r="D16" s="87" t="s">
+      <c r="D16" s="88" t="s">
         <v>220</v>
       </c>
-      <c r="E16" s="77"/>
-      <c r="F16" s="77"/>
-      <c r="G16" s="77"/>
-      <c r="H16" s="77"/>
-      <c r="I16" s="77"/>
-      <c r="J16" s="77"/>
-      <c r="K16" s="87" t="s">
+      <c r="E16" s="78"/>
+      <c r="F16" s="78"/>
+      <c r="G16" s="78"/>
+      <c r="H16" s="78"/>
+      <c r="I16" s="78"/>
+      <c r="J16" s="78"/>
+      <c r="K16" s="88" t="s">
         <v>221</v>
       </c>
-      <c r="L16" s="77"/>
-      <c r="M16" s="77"/>
-      <c r="N16" s="77"/>
-      <c r="O16" s="77"/>
-      <c r="P16" s="77"/>
-      <c r="Q16" s="77"/>
-      <c r="R16" s="77"/>
-      <c r="S16" s="77"/>
-      <c r="T16" s="77"/>
-      <c r="U16" s="77"/>
-      <c r="V16" s="77"/>
-      <c r="W16" s="77"/>
-      <c r="X16" s="77"/>
-      <c r="Y16" s="77"/>
-      <c r="Z16" s="87" t="s">
+      <c r="L16" s="78"/>
+      <c r="M16" s="78"/>
+      <c r="N16" s="78"/>
+      <c r="O16" s="78"/>
+      <c r="P16" s="78"/>
+      <c r="Q16" s="78"/>
+      <c r="R16" s="78"/>
+      <c r="S16" s="78"/>
+      <c r="T16" s="78"/>
+      <c r="U16" s="78"/>
+      <c r="V16" s="78"/>
+      <c r="W16" s="78"/>
+      <c r="X16" s="78"/>
+      <c r="Y16" s="78"/>
+      <c r="Z16" s="88" t="s">
         <v>222</v>
       </c>
-      <c r="AA16" s="77" t="s">
+      <c r="AA16" s="78" t="s">
         <v>223</v>
       </c>
-      <c r="AB16" s="87" t="s">
+      <c r="AB16" s="88" t="s">
         <v>224</v>
       </c>
-      <c r="AC16" s="77"/>
-      <c r="AD16" s="77"/>
-      <c r="AE16" s="77"/>
-      <c r="AF16" s="77"/>
-      <c r="AG16" s="77"/>
-      <c r="AH16" s="77"/>
-      <c r="AI16" s="77"/>
-      <c r="AJ16" s="77"/>
-      <c r="AK16" s="77"/>
-      <c r="AL16" s="77"/>
-      <c r="AM16" s="87" t="s">
+      <c r="AC16" s="78"/>
+      <c r="AD16" s="78"/>
+      <c r="AE16" s="78"/>
+      <c r="AF16" s="78"/>
+      <c r="AG16" s="78"/>
+      <c r="AH16" s="78"/>
+      <c r="AI16" s="78"/>
+      <c r="AJ16" s="78"/>
+      <c r="AK16" s="78"/>
+      <c r="AL16" s="78"/>
+      <c r="AM16" s="88" t="s">
         <v>225</v>
       </c>
-      <c r="AN16" s="77"/>
-      <c r="AO16" s="77" t="s">
+      <c r="AN16" s="78"/>
+      <c r="AO16" s="78" t="s">
         <v>226</v>
       </c>
-      <c r="AP16" s="77" t="s">
+      <c r="AP16" s="78" t="s">
         <v>226</v>
       </c>
-      <c r="AQ16" s="77"/>
-      <c r="AR16" s="77"/>
-      <c r="AS16" s="77" t="s">
+      <c r="AQ16" s="78"/>
+      <c r="AR16" s="78"/>
+      <c r="AS16" s="78" t="s">
         <v>227</v>
       </c>
-      <c r="AT16" s="77"/>
-      <c r="AU16" s="77"/>
-      <c r="AV16" s="87" t="s">
+      <c r="AT16" s="78"/>
+      <c r="AU16" s="78"/>
+      <c r="AV16" s="88" t="s">
         <v>228</v>
       </c>
-      <c r="AW16" s="77"/>
-      <c r="AX16" s="77"/>
-      <c r="AY16" s="77"/>
+      <c r="AW16" s="78"/>
+      <c r="AX16" s="78"/>
+      <c r="AY16" s="78"/>
     </row>
     <row r="17" ht="86.4" spans="1:51">
-      <c r="A17" s="83"/>
-      <c r="B17" s="84" t="s">
+      <c r="A17" s="84"/>
+      <c r="B17" s="85" t="s">
         <v>229</v>
       </c>
-      <c r="C17" s="85"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="77"/>
-      <c r="G17" s="87" t="s">
+      <c r="C17" s="86"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="78"/>
+      <c r="F17" s="78"/>
+      <c r="G17" s="88" t="s">
         <v>230</v>
       </c>
-      <c r="H17" s="77"/>
-      <c r="I17" s="87" t="s">
+      <c r="H17" s="78"/>
+      <c r="I17" s="88" t="s">
         <v>231</v>
       </c>
-      <c r="J17" s="77"/>
-      <c r="K17" s="77" t="s">
+      <c r="J17" s="78"/>
+      <c r="K17" s="78" t="s">
         <v>232</v>
       </c>
-      <c r="L17" s="77" t="s">
+      <c r="L17" s="78" t="s">
         <v>233</v>
       </c>
-      <c r="M17" s="77"/>
-      <c r="N17" s="77"/>
-      <c r="O17" s="87" t="s">
+      <c r="M17" s="78"/>
+      <c r="N17" s="78"/>
+      <c r="O17" s="88" t="s">
         <v>234</v>
       </c>
-      <c r="P17" s="77"/>
-      <c r="Q17" s="77"/>
-      <c r="R17" s="77"/>
-      <c r="S17" s="87" t="s">
+      <c r="P17" s="78"/>
+      <c r="Q17" s="78"/>
+      <c r="R17" s="78"/>
+      <c r="S17" s="88" t="s">
         <v>235</v>
       </c>
-      <c r="T17" s="87" t="s">
+      <c r="T17" s="88" t="s">
         <v>236</v>
       </c>
-      <c r="U17" s="87" t="s">
+      <c r="U17" s="88" t="s">
         <v>237</v>
       </c>
-      <c r="V17" s="77"/>
-      <c r="W17" s="87" t="s">
+      <c r="V17" s="78"/>
+      <c r="W17" s="88" t="s">
         <v>238</v>
       </c>
-      <c r="X17" s="77" t="s">
+      <c r="X17" s="78" t="s">
         <v>239</v>
       </c>
-      <c r="Y17" s="87" t="s">
+      <c r="Y17" s="88" t="s">
         <v>240</v>
       </c>
-      <c r="Z17" s="87" t="s">
+      <c r="Z17" s="88" t="s">
         <v>241</v>
       </c>
-      <c r="AA17" s="87" t="s">
+      <c r="AA17" s="88" t="s">
         <v>242</v>
       </c>
-      <c r="AB17" s="87" t="s">
+      <c r="AB17" s="88" t="s">
         <v>243</v>
       </c>
-      <c r="AC17" s="77"/>
-      <c r="AD17" s="77"/>
-      <c r="AE17" s="77"/>
-      <c r="AF17" s="77"/>
-      <c r="AG17" s="77"/>
-      <c r="AH17" s="87" t="s">
+      <c r="AC17" s="78"/>
+      <c r="AD17" s="78"/>
+      <c r="AE17" s="78"/>
+      <c r="AF17" s="78"/>
+      <c r="AG17" s="78"/>
+      <c r="AH17" s="88" t="s">
         <v>244</v>
       </c>
-      <c r="AI17" s="77"/>
-      <c r="AJ17" s="77"/>
-      <c r="AK17" s="77"/>
-      <c r="AL17" s="77" t="s">
+      <c r="AI17" s="78"/>
+      <c r="AJ17" s="78"/>
+      <c r="AK17" s="78"/>
+      <c r="AL17" s="78" t="s">
         <v>245</v>
       </c>
-      <c r="AM17" s="87" t="s">
+      <c r="AM17" s="88" t="s">
         <v>246</v>
       </c>
-      <c r="AN17" s="87" t="s">
+      <c r="AN17" s="88" t="s">
         <v>247</v>
       </c>
-      <c r="AO17" s="87" t="s">
+      <c r="AO17" s="88" t="s">
         <v>248</v>
       </c>
-      <c r="AP17" s="87" t="s">
+      <c r="AP17" s="88" t="s">
         <v>249</v>
       </c>
-      <c r="AQ17" s="77"/>
-      <c r="AR17" s="87" t="s">
+      <c r="AQ17" s="78"/>
+      <c r="AR17" s="88" t="s">
         <v>250</v>
       </c>
-      <c r="AS17" s="77" t="s">
+      <c r="AS17" s="78" t="s">
         <v>251</v>
       </c>
-      <c r="AT17" s="77" t="s">
+      <c r="AT17" s="78" t="s">
         <v>252</v>
       </c>
-      <c r="AU17" s="87" t="s">
+      <c r="AU17" s="88" t="s">
         <v>253</v>
       </c>
-      <c r="AV17" s="87" t="s">
+      <c r="AV17" s="88" t="s">
         <v>254</v>
       </c>
-      <c r="AW17" s="87" t="s">
+      <c r="AW17" s="88" t="s">
         <v>255</v>
       </c>
-      <c r="AX17" s="77"/>
-      <c r="AY17" s="87" t="s">
+      <c r="AX17" s="78"/>
+      <c r="AY17" s="88" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="18" ht="86.4" spans="1:51">
-      <c r="A18" s="83"/>
-      <c r="B18" s="84" t="s">
+      <c r="A18" s="84"/>
+      <c r="B18" s="85" t="s">
         <v>257</v>
       </c>
-      <c r="C18" s="85"/>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77"/>
-      <c r="G18" s="77"/>
-      <c r="H18" s="77"/>
-      <c r="I18" s="77"/>
-      <c r="J18" s="77"/>
-      <c r="K18" s="87" t="s">
+      <c r="C18" s="86"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="78"/>
+      <c r="F18" s="78"/>
+      <c r="G18" s="78"/>
+      <c r="H18" s="78"/>
+      <c r="I18" s="78"/>
+      <c r="J18" s="78"/>
+      <c r="K18" s="88" t="s">
         <v>258</v>
       </c>
-      <c r="L18" s="77"/>
-      <c r="M18" s="77"/>
-      <c r="N18" s="77"/>
-      <c r="O18" s="77"/>
-      <c r="P18" s="77"/>
-      <c r="Q18" s="77"/>
-      <c r="R18" s="77"/>
-      <c r="S18" s="77"/>
-      <c r="T18" s="77"/>
-      <c r="U18" s="77"/>
-      <c r="V18" s="77"/>
-      <c r="W18" s="77"/>
-      <c r="X18" s="77"/>
-      <c r="Y18" s="77"/>
-      <c r="Z18" s="87" t="s">
+      <c r="L18" s="78"/>
+      <c r="M18" s="78"/>
+      <c r="N18" s="78"/>
+      <c r="O18" s="78"/>
+      <c r="P18" s="78"/>
+      <c r="Q18" s="78"/>
+      <c r="R18" s="78"/>
+      <c r="S18" s="78"/>
+      <c r="T18" s="78"/>
+      <c r="U18" s="78"/>
+      <c r="V18" s="78"/>
+      <c r="W18" s="78"/>
+      <c r="X18" s="78"/>
+      <c r="Y18" s="78"/>
+      <c r="Z18" s="88" t="s">
         <v>259</v>
       </c>
-      <c r="AA18" s="87" t="s">
+      <c r="AA18" s="88" t="s">
         <v>260</v>
       </c>
-      <c r="AB18" s="87" t="s">
+      <c r="AB18" s="88" t="s">
         <v>261</v>
       </c>
-      <c r="AC18" s="87" t="s">
+      <c r="AC18" s="88" t="s">
         <v>262</v>
       </c>
-      <c r="AD18" s="77"/>
-      <c r="AE18" s="77"/>
-      <c r="AF18" s="77"/>
-      <c r="AG18" s="77"/>
-      <c r="AH18" s="77"/>
-      <c r="AI18" s="77" t="s">
+      <c r="AD18" s="78"/>
+      <c r="AE18" s="78"/>
+      <c r="AF18" s="78"/>
+      <c r="AG18" s="78"/>
+      <c r="AH18" s="78"/>
+      <c r="AI18" s="78" t="s">
         <v>263</v>
       </c>
-      <c r="AJ18" s="77"/>
-      <c r="AK18" s="77" t="s">
+      <c r="AJ18" s="78"/>
+      <c r="AK18" s="78" t="s">
         <v>263</v>
       </c>
-      <c r="AL18" s="77"/>
-      <c r="AM18" s="77"/>
-      <c r="AN18" s="87" t="s">
+      <c r="AL18" s="78"/>
+      <c r="AM18" s="78"/>
+      <c r="AN18" s="88" t="s">
         <v>264</v>
       </c>
-      <c r="AO18" s="77"/>
-      <c r="AP18" s="77"/>
-      <c r="AQ18" s="77"/>
-      <c r="AR18" s="77"/>
-      <c r="AS18" s="77"/>
-      <c r="AT18" s="77"/>
-      <c r="AU18" s="77"/>
-      <c r="AV18" s="87" t="s">
+      <c r="AO18" s="78"/>
+      <c r="AP18" s="78"/>
+      <c r="AQ18" s="78"/>
+      <c r="AR18" s="78"/>
+      <c r="AS18" s="78"/>
+      <c r="AT18" s="78"/>
+      <c r="AU18" s="78"/>
+      <c r="AV18" s="88" t="s">
         <v>265</v>
       </c>
-      <c r="AW18" s="87" t="s">
+      <c r="AW18" s="88" t="s">
         <v>266</v>
       </c>
-      <c r="AX18" s="77"/>
-      <c r="AY18" s="87" t="s">
+      <c r="AX18" s="78"/>
+      <c r="AY18" s="88" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="19" ht="43.2" spans="1:51">
-      <c r="A19" s="83"/>
-      <c r="B19" s="84" t="s">
+      <c r="A19" s="84"/>
+      <c r="B19" s="85" t="s">
         <v>267</v>
       </c>
-      <c r="C19" s="85"/>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="77"/>
-      <c r="G19" s="77"/>
-      <c r="H19" s="87" t="s">
+      <c r="C19" s="86"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="78"/>
+      <c r="F19" s="78"/>
+      <c r="G19" s="78"/>
+      <c r="H19" s="88" t="s">
         <v>268</v>
       </c>
-      <c r="I19" s="77"/>
-      <c r="J19" s="77"/>
-      <c r="K19" s="87" t="s">
+      <c r="I19" s="78"/>
+      <c r="J19" s="78"/>
+      <c r="K19" s="88" t="s">
         <v>268</v>
       </c>
-      <c r="L19" s="77" t="s">
+      <c r="L19" s="78" t="s">
         <v>269</v>
       </c>
-      <c r="M19" s="77"/>
-      <c r="N19" s="77"/>
-      <c r="O19" s="77"/>
-      <c r="P19" s="77"/>
-      <c r="Q19" s="77"/>
-      <c r="R19" s="77"/>
-      <c r="S19" s="77"/>
-      <c r="T19" s="77"/>
-      <c r="U19" s="77"/>
-      <c r="V19" s="77"/>
-      <c r="W19" s="77"/>
-      <c r="X19" s="77"/>
-      <c r="Y19" s="77"/>
-      <c r="Z19" s="77"/>
-      <c r="AA19" s="77"/>
-      <c r="AB19" s="77"/>
-      <c r="AC19" s="77"/>
-      <c r="AD19" s="77"/>
-      <c r="AE19" s="77" t="s">
+      <c r="M19" s="78"/>
+      <c r="N19" s="78"/>
+      <c r="O19" s="78"/>
+      <c r="P19" s="78"/>
+      <c r="Q19" s="78"/>
+      <c r="R19" s="78"/>
+      <c r="S19" s="78"/>
+      <c r="T19" s="78"/>
+      <c r="U19" s="78"/>
+      <c r="V19" s="78"/>
+      <c r="W19" s="78"/>
+      <c r="X19" s="78"/>
+      <c r="Y19" s="78"/>
+      <c r="Z19" s="78"/>
+      <c r="AA19" s="78"/>
+      <c r="AB19" s="78"/>
+      <c r="AC19" s="78"/>
+      <c r="AD19" s="78"/>
+      <c r="AE19" s="78" t="s">
         <v>269</v>
       </c>
-      <c r="AF19" s="77"/>
-      <c r="AG19" s="77"/>
-      <c r="AH19" s="77"/>
-      <c r="AI19" s="77"/>
-      <c r="AJ19" s="77"/>
-      <c r="AK19" s="77"/>
-      <c r="AL19" s="77"/>
-      <c r="AM19" s="77"/>
-      <c r="AN19" s="77"/>
-      <c r="AO19" s="77"/>
-      <c r="AP19" s="77" t="s">
+      <c r="AF19" s="78"/>
+      <c r="AG19" s="78"/>
+      <c r="AH19" s="78"/>
+      <c r="AI19" s="78"/>
+      <c r="AJ19" s="78"/>
+      <c r="AK19" s="78"/>
+      <c r="AL19" s="78"/>
+      <c r="AM19" s="78"/>
+      <c r="AN19" s="78"/>
+      <c r="AO19" s="78"/>
+      <c r="AP19" s="78" t="s">
         <v>269</v>
       </c>
-      <c r="AQ19" s="77"/>
-      <c r="AR19" s="77"/>
-      <c r="AS19" s="77"/>
-      <c r="AT19" s="77"/>
-      <c r="AU19" s="77"/>
-      <c r="AV19" s="87"/>
-      <c r="AW19" s="87"/>
-      <c r="AX19" s="77"/>
-      <c r="AY19" s="87" t="s">
+      <c r="AQ19" s="78"/>
+      <c r="AR19" s="78"/>
+      <c r="AS19" s="78"/>
+      <c r="AT19" s="78"/>
+      <c r="AU19" s="78"/>
+      <c r="AV19" s="88"/>
+      <c r="AW19" s="88"/>
+      <c r="AX19" s="78"/>
+      <c r="AY19" s="88" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="20" ht="57.6" spans="1:51">
-      <c r="A20" s="83"/>
-      <c r="B20" s="84" t="s">
+      <c r="A20" s="84"/>
+      <c r="B20" s="85" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="85"/>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="77"/>
-      <c r="G20" s="77"/>
-      <c r="H20" s="77"/>
-      <c r="I20" s="77"/>
-      <c r="J20" s="77"/>
-      <c r="K20" s="77"/>
-      <c r="L20" s="77"/>
-      <c r="M20" s="77"/>
-      <c r="N20" s="77"/>
-      <c r="O20" s="77"/>
-      <c r="P20" s="77"/>
-      <c r="Q20" s="77"/>
-      <c r="R20" s="77"/>
-      <c r="S20" s="77"/>
-      <c r="T20" s="77"/>
-      <c r="U20" s="77"/>
-      <c r="V20" s="77"/>
-      <c r="W20" s="77"/>
-      <c r="X20" s="77"/>
-      <c r="Y20" s="77"/>
-      <c r="Z20" s="77"/>
-      <c r="AA20" s="77"/>
-      <c r="AB20" s="77"/>
-      <c r="AC20" s="77"/>
-      <c r="AD20" s="77"/>
-      <c r="AE20" s="77"/>
-      <c r="AF20" s="77"/>
-      <c r="AG20" s="77"/>
-      <c r="AH20" s="77"/>
-      <c r="AI20" s="77"/>
-      <c r="AJ20" s="87" t="s">
+      <c r="C20" s="86"/>
+      <c r="D20" s="78"/>
+      <c r="E20" s="78"/>
+      <c r="F20" s="78"/>
+      <c r="G20" s="78"/>
+      <c r="H20" s="78"/>
+      <c r="I20" s="78"/>
+      <c r="J20" s="78"/>
+      <c r="K20" s="78"/>
+      <c r="L20" s="78"/>
+      <c r="M20" s="78"/>
+      <c r="N20" s="78"/>
+      <c r="O20" s="78"/>
+      <c r="P20" s="78"/>
+      <c r="Q20" s="78"/>
+      <c r="R20" s="78"/>
+      <c r="S20" s="78"/>
+      <c r="T20" s="78"/>
+      <c r="U20" s="78"/>
+      <c r="V20" s="78"/>
+      <c r="W20" s="78"/>
+      <c r="X20" s="78"/>
+      <c r="Y20" s="78"/>
+      <c r="Z20" s="78"/>
+      <c r="AA20" s="78"/>
+      <c r="AB20" s="78"/>
+      <c r="AC20" s="78"/>
+      <c r="AD20" s="78"/>
+      <c r="AE20" s="78"/>
+      <c r="AF20" s="78"/>
+      <c r="AG20" s="78"/>
+      <c r="AH20" s="78"/>
+      <c r="AI20" s="78"/>
+      <c r="AJ20" s="88" t="s">
         <v>272</v>
       </c>
-      <c r="AK20" s="77"/>
-      <c r="AL20" s="77"/>
-      <c r="AM20" s="77"/>
-      <c r="AN20" s="77"/>
-      <c r="AO20" s="77"/>
-      <c r="AP20" s="77"/>
-      <c r="AQ20" s="77"/>
-      <c r="AR20" s="77"/>
-      <c r="AS20" s="77"/>
-      <c r="AT20" s="77"/>
-      <c r="AU20" s="77"/>
-      <c r="AV20" s="87"/>
-      <c r="AW20" s="87"/>
-      <c r="AX20" s="77"/>
-      <c r="AY20" s="77"/>
+      <c r="AK20" s="78"/>
+      <c r="AL20" s="78"/>
+      <c r="AM20" s="78"/>
+      <c r="AN20" s="78"/>
+      <c r="AO20" s="78"/>
+      <c r="AP20" s="78"/>
+      <c r="AQ20" s="78"/>
+      <c r="AR20" s="78"/>
+      <c r="AS20" s="78"/>
+      <c r="AT20" s="78"/>
+      <c r="AU20" s="78"/>
+      <c r="AV20" s="88"/>
+      <c r="AW20" s="88"/>
+      <c r="AX20" s="78"/>
+      <c r="AY20" s="78"/>
     </row>
     <row r="21" ht="86.4" spans="1:51">
-      <c r="A21" s="83"/>
-      <c r="B21" s="88" t="s">
+      <c r="A21" s="84"/>
+      <c r="B21" s="89" t="s">
         <v>273</v>
       </c>
-      <c r="C21" s="86" t="s">
+      <c r="C21" s="87" t="s">
         <v>274</v>
       </c>
-      <c r="D21" s="86" t="s">
+      <c r="D21" s="87" t="s">
         <v>274</v>
       </c>
-      <c r="E21" s="77"/>
-      <c r="F21" s="77"/>
-      <c r="G21" s="77"/>
-      <c r="H21" s="77"/>
-      <c r="I21" s="77"/>
-      <c r="J21" s="77"/>
-      <c r="K21" s="87" t="s">
+      <c r="E21" s="78"/>
+      <c r="F21" s="78"/>
+      <c r="G21" s="78"/>
+      <c r="H21" s="78"/>
+      <c r="I21" s="78"/>
+      <c r="J21" s="78"/>
+      <c r="K21" s="88" t="s">
         <v>275</v>
       </c>
-      <c r="L21" s="77" t="s">
+      <c r="L21" s="78" t="s">
         <v>276</v>
       </c>
-      <c r="M21" s="77"/>
-      <c r="N21" s="77"/>
-      <c r="O21" s="77"/>
-      <c r="P21" s="77"/>
-      <c r="Q21" s="77"/>
-      <c r="R21" s="77"/>
-      <c r="S21" s="77"/>
-      <c r="T21" s="77"/>
-      <c r="U21" s="77"/>
-      <c r="V21" s="77"/>
-      <c r="W21" s="77"/>
-      <c r="X21" s="77"/>
-      <c r="Y21" s="77"/>
-      <c r="Z21" s="77"/>
-      <c r="AA21" s="77"/>
-      <c r="AB21" s="77"/>
-      <c r="AC21" s="77"/>
-      <c r="AD21" s="77"/>
-      <c r="AE21" s="77" t="s">
+      <c r="M21" s="78"/>
+      <c r="N21" s="78"/>
+      <c r="O21" s="78"/>
+      <c r="P21" s="78"/>
+      <c r="Q21" s="78"/>
+      <c r="R21" s="78"/>
+      <c r="S21" s="78"/>
+      <c r="T21" s="78"/>
+      <c r="U21" s="78"/>
+      <c r="V21" s="78"/>
+      <c r="W21" s="78"/>
+      <c r="X21" s="78"/>
+      <c r="Y21" s="78"/>
+      <c r="Z21" s="78"/>
+      <c r="AA21" s="78"/>
+      <c r="AB21" s="78"/>
+      <c r="AC21" s="78"/>
+      <c r="AD21" s="78"/>
+      <c r="AE21" s="78" t="s">
         <v>277</v>
       </c>
-      <c r="AF21" s="87" t="s">
+      <c r="AF21" s="88" t="s">
         <v>278</v>
       </c>
-      <c r="AG21" s="87" t="s">
+      <c r="AG21" s="88" t="s">
         <v>279</v>
       </c>
-      <c r="AH21" s="77"/>
-      <c r="AI21" s="87" t="s">
+      <c r="AH21" s="78"/>
+      <c r="AI21" s="88" t="s">
         <v>280</v>
       </c>
-      <c r="AJ21" s="87" t="s">
+      <c r="AJ21" s="88" t="s">
         <v>281</v>
       </c>
-      <c r="AK21" s="77"/>
-      <c r="AL21" s="77"/>
-      <c r="AM21" s="77"/>
-      <c r="AN21" s="77"/>
-      <c r="AO21" s="77" t="s">
+      <c r="AK21" s="78"/>
+      <c r="AL21" s="78"/>
+      <c r="AM21" s="78"/>
+      <c r="AN21" s="78"/>
+      <c r="AO21" s="78" t="s">
         <v>276</v>
       </c>
-      <c r="AP21" s="77" t="s">
+      <c r="AP21" s="78" t="s">
         <v>276</v>
       </c>
-      <c r="AQ21" s="77"/>
-      <c r="AR21" s="77"/>
-      <c r="AS21" s="77"/>
-      <c r="AT21" s="77" t="s">
+      <c r="AQ21" s="78"/>
+      <c r="AR21" s="78"/>
+      <c r="AS21" s="78"/>
+      <c r="AT21" s="78" t="s">
         <v>277</v>
       </c>
-      <c r="AU21" s="77"/>
-      <c r="AV21" s="77"/>
-      <c r="AW21" s="77"/>
-      <c r="AX21" s="87" t="s">
+      <c r="AU21" s="78"/>
+      <c r="AV21" s="78"/>
+      <c r="AW21" s="78"/>
+      <c r="AX21" s="88" t="s">
         <v>282</v>
       </c>
-      <c r="AY21" s="87" t="s">
+      <c r="AY21" s="88" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:51">
-      <c r="A22" s="89"/>
-      <c r="B22" s="84" t="s">
+      <c r="A22" s="90"/>
+      <c r="B22" s="85" t="s">
         <v>284</v>
       </c>
-      <c r="C22" s="85"/>
-      <c r="D22" s="77"/>
-      <c r="E22" s="77"/>
-      <c r="F22" s="77"/>
-      <c r="G22" s="77"/>
-      <c r="H22" s="77"/>
-      <c r="I22" s="77"/>
-      <c r="J22" s="77"/>
-      <c r="K22" s="77"/>
-      <c r="L22" s="77"/>
-      <c r="M22" s="77"/>
-      <c r="N22" s="77"/>
-      <c r="O22" s="77"/>
-      <c r="P22" s="77"/>
-      <c r="Q22" s="77"/>
-      <c r="R22" s="77"/>
-      <c r="S22" s="77"/>
-      <c r="T22" s="77"/>
-      <c r="U22" s="77"/>
-      <c r="V22" s="77"/>
-      <c r="W22" s="77"/>
-      <c r="X22" s="77"/>
-      <c r="Y22" s="77"/>
-      <c r="Z22" s="77"/>
-      <c r="AA22" s="77"/>
-      <c r="AB22" s="77"/>
-      <c r="AC22" s="77"/>
-      <c r="AD22" s="77"/>
-      <c r="AE22" s="77"/>
-      <c r="AF22" s="77"/>
-      <c r="AG22" s="77"/>
-      <c r="AH22" s="77"/>
-      <c r="AI22" s="77"/>
-      <c r="AJ22" s="77"/>
-      <c r="AK22" s="77"/>
-      <c r="AL22" s="77"/>
-      <c r="AM22" s="77"/>
-      <c r="AN22" s="77"/>
-      <c r="AO22" s="77"/>
-      <c r="AP22" s="77"/>
-      <c r="AQ22" s="77"/>
-      <c r="AR22" s="77"/>
-      <c r="AS22" s="77"/>
-      <c r="AT22" s="77"/>
-      <c r="AU22" s="77"/>
-      <c r="AV22" s="87"/>
-      <c r="AW22" s="87"/>
-      <c r="AX22" s="77"/>
-      <c r="AY22" s="77"/>
+      <c r="C22" s="86"/>
+      <c r="D22" s="78"/>
+      <c r="E22" s="78"/>
+      <c r="F22" s="78"/>
+      <c r="G22" s="78"/>
+      <c r="H22" s="78"/>
+      <c r="I22" s="78"/>
+      <c r="J22" s="78"/>
+      <c r="K22" s="78"/>
+      <c r="L22" s="78"/>
+      <c r="M22" s="78"/>
+      <c r="N22" s="78"/>
+      <c r="O22" s="78"/>
+      <c r="P22" s="78"/>
+      <c r="Q22" s="78"/>
+      <c r="R22" s="78"/>
+      <c r="S22" s="78"/>
+      <c r="T22" s="78"/>
+      <c r="U22" s="78"/>
+      <c r="V22" s="78"/>
+      <c r="W22" s="78"/>
+      <c r="X22" s="78"/>
+      <c r="Y22" s="78"/>
+      <c r="Z22" s="78"/>
+      <c r="AA22" s="78"/>
+      <c r="AB22" s="78"/>
+      <c r="AC22" s="78"/>
+      <c r="AD22" s="78"/>
+      <c r="AE22" s="78"/>
+      <c r="AF22" s="78"/>
+      <c r="AG22" s="78"/>
+      <c r="AH22" s="78"/>
+      <c r="AI22" s="78"/>
+      <c r="AJ22" s="78"/>
+      <c r="AK22" s="78"/>
+      <c r="AL22" s="78"/>
+      <c r="AM22" s="78"/>
+      <c r="AN22" s="78"/>
+      <c r="AO22" s="78"/>
+      <c r="AP22" s="78"/>
+      <c r="AQ22" s="78"/>
+      <c r="AR22" s="78"/>
+      <c r="AS22" s="78"/>
+      <c r="AT22" s="78"/>
+      <c r="AU22" s="78"/>
+      <c r="AV22" s="88"/>
+      <c r="AW22" s="88"/>
+      <c r="AX22" s="78"/>
+      <c r="AY22" s="78"/>
     </row>
     <row r="24" ht="115.2" spans="1:51">
-      <c r="A24" s="67" t="s">
+      <c r="A24" s="68" t="s">
         <v>285</v>
       </c>
       <c r="B24" s="25" t="s">
         <v>286</v>
       </c>
-      <c r="C24" s="72" t="s">
+      <c r="C24" s="73" t="s">
         <v>287</v>
       </c>
-      <c r="D24" s="72" t="s">
+      <c r="D24" s="73" t="s">
         <v>170</v>
       </c>
-      <c r="E24" s="72" t="s">
+      <c r="E24" s="73" t="s">
         <v>288</v>
       </c>
-      <c r="F24" s="72" t="s">
+      <c r="F24" s="73" t="s">
         <v>289</v>
       </c>
-      <c r="G24" s="72" t="s">
+      <c r="G24" s="73" t="s">
         <v>290</v>
       </c>
-      <c r="H24" s="72" t="s">
+      <c r="H24" s="73" t="s">
         <v>291</v>
       </c>
-      <c r="I24" s="72" t="s">
+      <c r="I24" s="73" t="s">
         <v>292</v>
       </c>
-      <c r="J24" s="72" t="s">
+      <c r="J24" s="73" t="s">
         <v>293</v>
       </c>
-      <c r="K24" s="72" t="s">
+      <c r="K24" s="73" t="s">
         <v>294</v>
       </c>
-      <c r="L24" s="72" t="s">
+      <c r="L24" s="73" t="s">
         <v>295</v>
       </c>
-      <c r="M24" s="72" t="s">
+      <c r="M24" s="73" t="s">
         <v>296</v>
       </c>
-      <c r="N24" s="72" t="s">
+      <c r="N24" s="73" t="s">
         <v>297</v>
       </c>
-      <c r="O24" s="72" t="s">
+      <c r="O24" s="73" t="s">
         <v>155</v>
       </c>
-      <c r="P24" s="72" t="s">
+      <c r="P24" s="73" t="s">
         <v>298</v>
       </c>
-      <c r="Q24" s="72" t="s">
+      <c r="Q24" s="73" t="s">
         <v>299</v>
       </c>
-      <c r="R24" s="72" t="s">
+      <c r="R24" s="73" t="s">
         <v>300</v>
       </c>
-      <c r="S24" s="72" t="s">
+      <c r="S24" s="73" t="s">
         <v>301</v>
       </c>
-      <c r="T24" s="72" t="s">
+      <c r="T24" s="73" t="s">
         <v>302</v>
       </c>
-      <c r="U24" s="72" t="s">
+      <c r="U24" s="73" t="s">
         <v>303</v>
       </c>
-      <c r="V24" s="72" t="s">
+      <c r="V24" s="73" t="s">
         <v>304</v>
       </c>
-      <c r="W24" s="72" t="s">
+      <c r="W24" s="73" t="s">
         <v>305</v>
       </c>
-      <c r="X24" s="72" t="s">
+      <c r="X24" s="73" t="s">
         <v>306</v>
       </c>
-      <c r="Y24" s="72" t="s">
+      <c r="Y24" s="73" t="s">
         <v>307</v>
       </c>
-      <c r="Z24" s="72" t="s">
+      <c r="Z24" s="73" t="s">
         <v>308</v>
       </c>
-      <c r="AA24" s="72" t="s">
+      <c r="AA24" s="73" t="s">
         <v>309</v>
       </c>
-      <c r="AB24" s="72" t="s">
+      <c r="AB24" s="73" t="s">
         <v>310</v>
       </c>
-      <c r="AC24" s="72" t="s">
+      <c r="AC24" s="73" t="s">
         <v>311</v>
       </c>
-      <c r="AD24" s="72" t="s">
+      <c r="AD24" s="73" t="s">
         <v>312</v>
       </c>
-      <c r="AE24" s="72" t="s">
+      <c r="AE24" s="73" t="s">
         <v>313</v>
       </c>
-      <c r="AF24" s="72" t="s">
+      <c r="AF24" s="73" t="s">
         <v>314</v>
       </c>
-      <c r="AG24" s="72" t="s">
+      <c r="AG24" s="73" t="s">
         <v>315</v>
       </c>
-      <c r="AH24" s="72" t="s">
+      <c r="AH24" s="73" t="s">
         <v>155</v>
       </c>
-      <c r="AI24" s="72" t="s">
+      <c r="AI24" s="73" t="s">
         <v>316</v>
       </c>
-      <c r="AJ24" s="72" t="s">
+      <c r="AJ24" s="73" t="s">
         <v>317</v>
       </c>
-      <c r="AK24" s="72" t="s">
+      <c r="AK24" s="73" t="s">
         <v>155</v>
       </c>
-      <c r="AL24" s="72" t="s">
+      <c r="AL24" s="73" t="s">
         <v>318</v>
       </c>
-      <c r="AM24" s="72" t="s">
+      <c r="AM24" s="73" t="s">
         <v>319</v>
       </c>
-      <c r="AN24" s="72" t="s">
+      <c r="AN24" s="73" t="s">
         <v>155</v>
       </c>
-      <c r="AO24" s="72" t="s">
+      <c r="AO24" s="73" t="s">
         <v>155</v>
       </c>
-      <c r="AP24" s="72" t="s">
+      <c r="AP24" s="73" t="s">
         <v>315</v>
       </c>
-      <c r="AQ24" s="72" t="s">
+      <c r="AQ24" s="73" t="s">
         <v>315</v>
       </c>
-      <c r="AR24" s="72" t="s">
+      <c r="AR24" s="73" t="s">
         <v>155</v>
       </c>
-      <c r="AS24" s="72" t="s">
+      <c r="AS24" s="73" t="s">
         <v>320</v>
       </c>
-      <c r="AT24" s="72" t="s">
+      <c r="AT24" s="73" t="s">
         <v>321</v>
       </c>
-      <c r="AU24" s="72" t="s">
+      <c r="AU24" s="73" t="s">
         <v>322</v>
       </c>
-      <c r="AV24" s="72" t="s">
+      <c r="AV24" s="73" t="s">
         <v>323</v>
       </c>
-      <c r="AW24" s="73" t="s">
+      <c r="AW24" s="74" t="s">
         <v>324</v>
       </c>
-      <c r="AX24" s="73" t="s">
+      <c r="AX24" s="74" t="s">
         <v>315</v>
       </c>
-      <c r="AY24" s="73" t="s">
+      <c r="AY24" s="74" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:51">
-      <c r="A25" s="69"/>
+      <c r="A25" s="70"/>
       <c r="B25" s="25" t="s">
         <v>325</v>
       </c>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="72"/>
-      <c r="F25" s="72"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="72"/>
-      <c r="I25" s="72"/>
-      <c r="J25" s="72"/>
-      <c r="K25" s="72"/>
-      <c r="L25" s="72"/>
-      <c r="M25" s="72"/>
-      <c r="N25" s="72"/>
-      <c r="O25" s="72"/>
-      <c r="P25" s="72"/>
-      <c r="Q25" s="72"/>
-      <c r="R25" s="72"/>
-      <c r="S25" s="72"/>
-      <c r="T25" s="72"/>
-      <c r="U25" s="72"/>
-      <c r="V25" s="72"/>
-      <c r="W25" s="72"/>
-      <c r="X25" s="72"/>
-      <c r="Y25" s="72"/>
-      <c r="Z25" s="72"/>
-      <c r="AA25" s="72"/>
-      <c r="AB25" s="72"/>
-      <c r="AC25" s="72"/>
-      <c r="AD25" s="72"/>
-      <c r="AE25" s="72"/>
-      <c r="AF25" s="72"/>
-      <c r="AG25" s="72"/>
-      <c r="AH25" s="72"/>
-      <c r="AI25" s="72"/>
-      <c r="AJ25" s="72"/>
-      <c r="AK25" s="72"/>
-      <c r="AL25" s="72"/>
-      <c r="AM25" s="72"/>
-      <c r="AN25" s="72"/>
-      <c r="AO25" s="72"/>
-      <c r="AP25" s="72"/>
-      <c r="AQ25" s="72"/>
-      <c r="AR25" s="72"/>
-      <c r="AS25" s="72"/>
-      <c r="AT25" s="72"/>
-      <c r="AU25" s="72"/>
-      <c r="AV25" s="72"/>
-      <c r="AW25" s="73"/>
-      <c r="AX25" s="73"/>
-      <c r="AY25" s="73"/>
+      <c r="C25" s="73"/>
+      <c r="D25" s="73"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73"/>
+      <c r="J25" s="73"/>
+      <c r="K25" s="73"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="73"/>
+      <c r="N25" s="73"/>
+      <c r="O25" s="73"/>
+      <c r="P25" s="73"/>
+      <c r="Q25" s="73"/>
+      <c r="R25" s="73"/>
+      <c r="S25" s="73"/>
+      <c r="T25" s="73"/>
+      <c r="U25" s="73"/>
+      <c r="V25" s="73"/>
+      <c r="W25" s="73"/>
+      <c r="X25" s="73"/>
+      <c r="Y25" s="73"/>
+      <c r="Z25" s="73"/>
+      <c r="AA25" s="73"/>
+      <c r="AB25" s="73"/>
+      <c r="AC25" s="73"/>
+      <c r="AD25" s="73"/>
+      <c r="AE25" s="73"/>
+      <c r="AF25" s="73"/>
+      <c r="AG25" s="73"/>
+      <c r="AH25" s="73"/>
+      <c r="AI25" s="73"/>
+      <c r="AJ25" s="73"/>
+      <c r="AK25" s="73"/>
+      <c r="AL25" s="73"/>
+      <c r="AM25" s="73"/>
+      <c r="AN25" s="73"/>
+      <c r="AO25" s="73"/>
+      <c r="AP25" s="73"/>
+      <c r="AQ25" s="73"/>
+      <c r="AR25" s="73"/>
+      <c r="AS25" s="73"/>
+      <c r="AT25" s="73"/>
+      <c r="AU25" s="73"/>
+      <c r="AV25" s="73"/>
+      <c r="AW25" s="74"/>
+      <c r="AX25" s="74"/>
+      <c r="AY25" s="74"/>
     </row>
     <row r="26" customFormat="1" ht="100.8" spans="1:51">
-      <c r="A26" s="74"/>
+      <c r="A26" s="75"/>
       <c r="B26" s="25" t="s">
         <v>326</v>
       </c>
-      <c r="C26" s="72"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="72"/>
-      <c r="F26" s="72"/>
-      <c r="G26" s="72" t="s">
+      <c r="C26" s="73"/>
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="73" t="s">
         <v>327</v>
       </c>
-      <c r="H26" s="72"/>
-      <c r="I26" s="72"/>
-      <c r="J26" s="72"/>
-      <c r="K26" s="72"/>
-      <c r="L26" s="72"/>
-      <c r="M26" s="72" t="s">
+      <c r="H26" s="73"/>
+      <c r="I26" s="73"/>
+      <c r="J26" s="73"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="73"/>
+      <c r="M26" s="73" t="s">
         <v>328</v>
       </c>
-      <c r="N26" s="72" t="s">
+      <c r="N26" s="73" t="s">
         <v>329</v>
       </c>
-      <c r="O26" s="72"/>
-      <c r="P26" s="72"/>
-      <c r="Q26" s="72"/>
-      <c r="R26" s="72"/>
-      <c r="S26" s="72"/>
-      <c r="T26" s="72"/>
-      <c r="U26" s="72"/>
-      <c r="V26" s="72"/>
-      <c r="W26" s="72"/>
-      <c r="X26" s="72"/>
-      <c r="Y26" s="72"/>
-      <c r="Z26" s="72"/>
-      <c r="AA26" s="72"/>
-      <c r="AB26" s="72"/>
-      <c r="AC26" s="72"/>
-      <c r="AD26" s="72"/>
-      <c r="AE26" s="72"/>
-      <c r="AF26" s="72"/>
-      <c r="AG26" s="72"/>
-      <c r="AH26" s="72"/>
-      <c r="AI26" s="72"/>
-      <c r="AJ26" s="72"/>
-      <c r="AK26" s="72"/>
-      <c r="AL26" s="72"/>
-      <c r="AM26" s="72"/>
-      <c r="AN26" s="72"/>
-      <c r="AO26" s="72" t="s">
+      <c r="O26" s="73"/>
+      <c r="P26" s="73"/>
+      <c r="Q26" s="73"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="73"/>
+      <c r="T26" s="73"/>
+      <c r="U26" s="73"/>
+      <c r="V26" s="73"/>
+      <c r="W26" s="73"/>
+      <c r="X26" s="73"/>
+      <c r="Y26" s="73"/>
+      <c r="Z26" s="73"/>
+      <c r="AA26" s="73"/>
+      <c r="AB26" s="73"/>
+      <c r="AC26" s="73"/>
+      <c r="AD26" s="73"/>
+      <c r="AE26" s="73"/>
+      <c r="AF26" s="73"/>
+      <c r="AG26" s="73"/>
+      <c r="AH26" s="73"/>
+      <c r="AI26" s="73"/>
+      <c r="AJ26" s="73"/>
+      <c r="AK26" s="73"/>
+      <c r="AL26" s="73"/>
+      <c r="AM26" s="73"/>
+      <c r="AN26" s="73"/>
+      <c r="AO26" s="73" t="s">
         <v>330</v>
       </c>
-      <c r="AP26" s="72" t="s">
+      <c r="AP26" s="73" t="s">
         <v>331</v>
       </c>
-      <c r="AQ26" s="72"/>
-      <c r="AR26" s="72"/>
-      <c r="AS26" s="72"/>
-      <c r="AT26" s="72"/>
-      <c r="AU26" s="72"/>
-      <c r="AV26" s="72"/>
-      <c r="AW26" s="73"/>
-      <c r="AX26" s="73"/>
-      <c r="AY26" s="73"/>
+      <c r="AQ26" s="73"/>
+      <c r="AR26" s="73"/>
+      <c r="AS26" s="73"/>
+      <c r="AT26" s="73"/>
+      <c r="AU26" s="73"/>
+      <c r="AV26" s="73"/>
+      <c r="AW26" s="74"/>
+      <c r="AX26" s="74"/>
+      <c r="AY26" s="74"/>
     </row>
-    <row r="27" s="51" customFormat="1" ht="28.8" spans="1:51">
-      <c r="A27" s="75" t="s">
+    <row r="27" s="52" customFormat="1" ht="28.8" spans="1:51">
+      <c r="A27" s="76" t="s">
         <v>332</v>
       </c>
-      <c r="B27" s="87" t="s">
+      <c r="B27" s="88" t="s">
         <v>333</v>
       </c>
-      <c r="C27" s="90"/>
-      <c r="D27" s="90"/>
-      <c r="E27" s="90"/>
-      <c r="F27" s="90"/>
-      <c r="G27" s="90"/>
-      <c r="H27" s="90"/>
-      <c r="I27" s="90"/>
-      <c r="J27" s="90"/>
-      <c r="K27" s="90"/>
-      <c r="L27" s="90"/>
-      <c r="M27" s="90"/>
-      <c r="N27" s="90"/>
-      <c r="O27" s="90"/>
-      <c r="P27" s="90"/>
-      <c r="Q27" s="90"/>
-      <c r="R27" s="90"/>
-      <c r="S27" s="90"/>
-      <c r="T27" s="90"/>
-      <c r="U27" s="90"/>
-      <c r="V27" s="90"/>
-      <c r="W27" s="90"/>
-      <c r="X27" s="90"/>
-      <c r="Y27" s="90"/>
-      <c r="Z27" s="90"/>
-      <c r="AA27" s="90"/>
-      <c r="AB27" s="90"/>
-      <c r="AC27" s="90"/>
-      <c r="AD27" s="90"/>
-      <c r="AE27" s="90"/>
-      <c r="AF27" s="90"/>
-      <c r="AG27" s="90"/>
-      <c r="AH27" s="90"/>
-      <c r="AI27" s="90"/>
-      <c r="AJ27" s="90"/>
-      <c r="AK27" s="90"/>
-      <c r="AL27" s="90"/>
-      <c r="AM27" s="90"/>
-      <c r="AN27" s="90"/>
-      <c r="AO27" s="90"/>
-      <c r="AP27" s="90"/>
-      <c r="AQ27" s="90"/>
-      <c r="AR27" s="90"/>
+      <c r="C27" s="91"/>
+      <c r="D27" s="91"/>
+      <c r="E27" s="91"/>
+      <c r="F27" s="91"/>
+      <c r="G27" s="91"/>
+      <c r="H27" s="91"/>
+      <c r="I27" s="91"/>
+      <c r="J27" s="91"/>
+      <c r="K27" s="91"/>
+      <c r="L27" s="91"/>
+      <c r="M27" s="91"/>
+      <c r="N27" s="91"/>
+      <c r="O27" s="91"/>
+      <c r="P27" s="91"/>
+      <c r="Q27" s="91"/>
+      <c r="R27" s="91"/>
+      <c r="S27" s="91"/>
+      <c r="T27" s="91"/>
+      <c r="U27" s="91"/>
+      <c r="V27" s="91"/>
+      <c r="W27" s="91"/>
+      <c r="X27" s="91"/>
+      <c r="Y27" s="91"/>
+      <c r="Z27" s="91"/>
+      <c r="AA27" s="91"/>
+      <c r="AB27" s="91"/>
+      <c r="AC27" s="91"/>
+      <c r="AD27" s="91"/>
+      <c r="AE27" s="91"/>
+      <c r="AF27" s="91"/>
+      <c r="AG27" s="91"/>
+      <c r="AH27" s="91"/>
+      <c r="AI27" s="91"/>
+      <c r="AJ27" s="91"/>
+      <c r="AK27" s="91"/>
+      <c r="AL27" s="91"/>
+      <c r="AM27" s="91"/>
+      <c r="AN27" s="91"/>
+      <c r="AO27" s="91"/>
+      <c r="AP27" s="91"/>
+      <c r="AQ27" s="91"/>
+      <c r="AR27" s="91"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -9204,7 +9008,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="16" s="13" customFormat="1" ht="101.55" spans="1:24">
+    <row r="16" s="13" customFormat="1" ht="87.15" spans="1:24">
       <c r="A16" s="18"/>
       <c r="B16" s="29"/>
       <c r="C16" s="30" t="s">
@@ -10140,7 +9944,7 @@
       <c r="W39" s="31"/>
       <c r="X39" s="35"/>
     </row>
-    <row r="40" customFormat="1" ht="230.4" spans="1:24">
+    <row r="40" customFormat="1" ht="216" spans="1:24">
       <c r="A40" s="18"/>
       <c r="B40" s="29"/>
       <c r="C40" s="30" t="s">
@@ -10180,13 +9984,13 @@
       <c r="W40" s="31"/>
       <c r="X40" s="35"/>
     </row>
-    <row r="41" customFormat="1" ht="216" spans="1:24">
+    <row r="41" customFormat="1" ht="129.6" spans="1:24">
       <c r="A41" s="18"/>
       <c r="B41" s="29"/>
       <c r="C41" s="30" t="s">
         <v>433</v>
       </c>
-      <c r="D41" s="30" t="s">
+      <c r="D41" s="41" t="s">
         <v>434</v>
       </c>
       <c r="E41" s="30"/>
@@ -10220,13 +10024,13 @@
       <c r="W41" s="31"/>
       <c r="X41" s="35"/>
     </row>
-    <row r="42" customFormat="1" ht="230.4" spans="1:24">
+    <row r="42" customFormat="1" ht="172.8" spans="1:24">
       <c r="A42" s="18"/>
       <c r="B42" s="29"/>
       <c r="C42" s="30" t="s">
         <v>435</v>
       </c>
-      <c r="D42" s="30" t="s">
+      <c r="D42" s="41" t="s">
         <v>436</v>
       </c>
       <c r="E42" s="30"/>
@@ -10264,13 +10068,13 @@
         <v>330</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="273.6" spans="1:24">
+    <row r="43" customFormat="1" ht="216" spans="1:24">
       <c r="A43" s="18"/>
       <c r="B43" s="29"/>
       <c r="C43" s="30" t="s">
         <v>437</v>
       </c>
-      <c r="D43" s="30" t="s">
+      <c r="D43" s="41" t="s">
         <v>438</v>
       </c>
       <c r="E43" s="30"/>
@@ -10310,13 +10114,13 @@
         <v>331</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="216" spans="1:24">
+    <row r="44" customFormat="1" ht="187.2" spans="1:24">
       <c r="A44" s="18"/>
       <c r="B44" s="29"/>
       <c r="C44" s="30" t="s">
         <v>439</v>
       </c>
-      <c r="D44" s="30" t="s">
+      <c r="D44" s="41" t="s">
         <v>440</v>
       </c>
       <c r="E44" s="30"/>
@@ -10344,13 +10148,13 @@
       <c r="W44" s="31"/>
       <c r="X44" s="35"/>
     </row>
-    <row r="45" s="13" customFormat="1" ht="245.55" spans="1:24">
+    <row r="45" s="13" customFormat="1" ht="216.75" spans="1:24">
       <c r="A45" s="18"/>
       <c r="B45" s="29"/>
       <c r="C45" s="30" t="s">
         <v>441</v>
       </c>
-      <c r="D45" s="30" t="s">
+      <c r="D45" s="41" t="s">
         <v>442</v>
       </c>
       <c r="E45" s="30"/>
@@ -10382,7 +10186,7 @@
       <c r="W45" s="31"/>
       <c r="X45" s="35"/>
     </row>
-    <row r="46" s="12" customFormat="1" ht="230.4" spans="1:24">
+    <row r="46" s="12" customFormat="1" ht="158.4" spans="1:24">
       <c r="A46" s="18" t="s">
         <v>8</v>
       </c>
@@ -10392,7 +10196,7 @@
       <c r="C46" s="30" t="s">
         <v>443</v>
       </c>
-      <c r="D46" s="30" t="s">
+      <c r="D46" s="41" t="s">
         <v>444</v>
       </c>
       <c r="E46" s="30"/>
@@ -10426,13 +10230,13 @@
       <c r="W46" s="31"/>
       <c r="X46" s="35"/>
     </row>
-    <row r="47" customFormat="1" ht="144" spans="1:24">
+    <row r="47" customFormat="1" ht="100.8" spans="1:24">
       <c r="A47" s="18"/>
       <c r="B47" s="29"/>
       <c r="C47" s="30" t="s">
         <v>445</v>
       </c>
-      <c r="D47" s="30" t="s">
+      <c r="D47" s="41" t="s">
         <v>446</v>
       </c>
       <c r="E47" s="30"/>
@@ -10466,13 +10270,13 @@
       <c r="W47" s="31"/>
       <c r="X47" s="35"/>
     </row>
-    <row r="48" s="13" customFormat="1" ht="173.55" spans="1:24">
+    <row r="48" s="13" customFormat="1" ht="144.75" spans="1:24">
       <c r="A48" s="18"/>
       <c r="B48" s="29"/>
       <c r="C48" s="30" t="s">
         <v>447</v>
       </c>
-      <c r="D48" s="30" t="s">
+      <c r="D48" s="41" t="s">
         <v>448</v>
       </c>
       <c r="E48" s="30"/>
@@ -10504,7 +10308,7 @@
       <c r="W48" s="31"/>
       <c r="X48" s="35"/>
     </row>
-    <row r="49" s="12" customFormat="1" ht="230.4" spans="1:24">
+    <row r="49" s="12" customFormat="1" ht="187.2" spans="1:24">
       <c r="A49" s="18" t="s">
         <v>9</v>
       </c>
@@ -10548,7 +10352,7 @@
       <c r="W49" s="31"/>
       <c r="X49" s="35"/>
     </row>
-    <row r="50" customFormat="1" ht="187.2" spans="1:24">
+    <row r="50" customFormat="1" ht="144" spans="1:24">
       <c r="A50" s="18"/>
       <c r="B50" s="29"/>
       <c r="C50" s="30" t="s">
@@ -10586,13 +10390,13 @@
       <c r="W50" s="31"/>
       <c r="X50" s="35"/>
     </row>
-    <row r="51" customFormat="1" ht="216" spans="1:24">
+    <row r="51" customFormat="1" ht="172.8" spans="1:24">
       <c r="A51" s="18"/>
       <c r="B51" s="29"/>
       <c r="C51" s="30" t="s">
         <v>453</v>
       </c>
-      <c r="D51" s="30" t="s">
+      <c r="D51" s="41" t="s">
         <v>454</v>
       </c>
       <c r="E51" s="30"/>
@@ -10624,47 +10428,47 @@
       <c r="W51" s="31"/>
       <c r="X51" s="35"/>
     </row>
-    <row r="52" s="13" customFormat="1" ht="274.35" spans="1:24">
+    <row r="52" s="13" customFormat="1" ht="144.75" spans="1:24">
       <c r="A52" s="42"/>
       <c r="B52" s="43"/>
       <c r="C52" s="44" t="s">
         <v>456</v>
       </c>
-      <c r="D52" s="44" t="s">
+      <c r="D52" s="45" t="s">
         <v>457</v>
       </c>
       <c r="E52" s="44"/>
-      <c r="F52" s="45"/>
-      <c r="G52" s="46" t="s">
+      <c r="F52" s="46"/>
+      <c r="G52" s="47" t="s">
         <v>155</v>
       </c>
-      <c r="H52" s="46"/>
-      <c r="I52" s="46"/>
-      <c r="J52" s="46"/>
-      <c r="K52" s="46"/>
-      <c r="L52" s="47"/>
-      <c r="M52" s="47"/>
-      <c r="N52" s="47"/>
-      <c r="O52" s="48"/>
-      <c r="P52" s="48" t="s">
+      <c r="H52" s="47"/>
+      <c r="I52" s="47"/>
+      <c r="J52" s="47"/>
+      <c r="K52" s="47"/>
+      <c r="L52" s="48"/>
+      <c r="M52" s="48"/>
+      <c r="N52" s="48"/>
+      <c r="O52" s="49"/>
+      <c r="P52" s="49" t="s">
         <v>256</v>
       </c>
-      <c r="Q52" s="48" t="s">
+      <c r="Q52" s="49" t="s">
         <v>263</v>
       </c>
-      <c r="R52" s="48" t="s">
+      <c r="R52" s="49" t="s">
         <v>270</v>
       </c>
-      <c r="S52" s="48"/>
-      <c r="T52" s="48" t="s">
+      <c r="S52" s="49"/>
+      <c r="T52" s="49" t="s">
         <v>283</v>
       </c>
-      <c r="U52" s="46" t="s">
+      <c r="U52" s="47" t="s">
         <v>155</v>
       </c>
-      <c r="V52" s="46"/>
-      <c r="W52" s="46"/>
-      <c r="X52" s="49"/>
+      <c r="V52" s="47"/>
+      <c r="W52" s="47"/>
+      <c r="X52" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="179">

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -4,17 +4,17 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13500" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="49过程输入输出工具-横版" sheetId="1" r:id="rId1"/>
-    <sheet name="49过程输入输出工具-竖版" sheetId="9" r:id="rId2"/>
-    <sheet name="49子过程图表实例（自己画的）" sheetId="2" r:id="rId3"/>
+    <sheet name="49过程输入输出工具-横版" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="十大管理输入输出工具" sheetId="9" r:id="rId2"/>
+    <sheet name="49过程图表汇总" sheetId="2" r:id="rId3"/>
     <sheet name="8大绩效域" sheetId="8" r:id="rId4"/>
-    <sheet name="必背默写知识点" sheetId="3" r:id="rId5"/>
-    <sheet name="计算公式汇总" sheetId="4" r:id="rId6"/>
-    <sheet name="案例分析技巧汇总" sheetId="5" r:id="rId7"/>
-    <sheet name="完整论文" sheetId="6" r:id="rId8"/>
+    <sheet name="计算公式汇总" sheetId="4" r:id="rId5"/>
+    <sheet name="背默知识汇总" sheetId="3" r:id="rId6"/>
+    <sheet name="案例答题技巧" sheetId="5" r:id="rId7"/>
+    <sheet name="论文套路技巧" sheetId="6" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="521">
   <si>
     <t>项目整合管理</t>
   </si>
@@ -3838,6 +3838,10 @@
 与团队技能</t>
   </si>
   <si>
+    <t>项目整合
+管理</t>
+  </si>
+  <si>
     <t>工作内容：识别、协调项目管理各过程、活动，贯穿项目始终,具备建立联系和统一的性质</t>
   </si>
   <si>
@@ -3916,6 +3920,10 @@
 3释放组织团队资源</t>
   </si>
   <si>
+    <t>项目范围
+管理</t>
+  </si>
+  <si>
     <t>定义和控制项目、产品的范围,确保项目只做需要做的全部工作</t>
   </si>
   <si>
@@ -3963,6 +3971,10 @@
     <t>1监督项目和产品的范围
 2维护项目范围基准
 3管理范围基准变更</t>
+  </si>
+  <si>
+    <t>项目进度
+管理</t>
   </si>
   <si>
     <t>规划进度管理（规划过程组）</t>
@@ -4008,6 +4020,10 @@
 4管理进度基准变更</t>
   </si>
   <si>
+    <t>项目成本
+管理</t>
+  </si>
+  <si>
     <t>对成本进行规划、估算、预算、筹资、管理和控制，使得项目在预算内完成</t>
   </si>
   <si>
@@ -4044,6 +4060,10 @@
   <si>
     <t>工作绩效信息
 成本预测</t>
+  </si>
+  <si>
+    <t>项目质量
+管理</t>
   </si>
   <si>
     <t>确定质量目标方针，并执行质量规划、保证、控
@@ -4074,6 +4094,10 @@
 3确保项目输出满足规范标准要求和客户期望</t>
   </si>
   <si>
+    <t>项目资源
+管理</t>
+  </si>
+  <si>
     <t>规划资源管理（规划过程组）</t>
   </si>
   <si>
@@ -4119,6 +4143,10 @@
 3资源释放</t>
   </si>
   <si>
+    <t>项目沟通
+管理</t>
+  </si>
+  <si>
     <t>规划沟通管理（规划过程组）</t>
   </si>
   <si>
@@ -4146,6 +4174,10 @@
 2确保满足项目和干系人的信息需求</t>
   </si>
   <si>
+    <t>项目风险
+管理</t>
+  </si>
+  <si>
     <t>项目内对风险进行规划、识别、分析、管理和控制的过程</t>
   </si>
   <si>
@@ -4160,6 +4192,14 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t xml:space="preserve">
 </t>
     </r>
@@ -4241,6 +4281,10 @@
 2监督风险应对计划的实施3跟踪已识别风险、识别和分析新风险，4评估风险管理有效性的过程</t>
   </si>
   <si>
+    <t>项目采购
+管理</t>
+  </si>
+  <si>
     <t>规划采购管理（规划过程组）</t>
   </si>
   <si>
@@ -4262,6 +4306,10 @@
 2管理采购关系、监督合同绩效、实施必要的变更和纠偏，以及关闭合同</t>
   </si>
   <si>
+    <t xml:space="preserve">项目干系
+人管理 </t>
+  </si>
+  <si>
     <t>识别干系人（启动过程组）</t>
   </si>
   <si>
@@ -4291,72 +4339,6 @@
   <si>
     <t>1维持或提升干系人参与活动的效率和效果
 2监督项目干系人的关系，并通过修订参与策略和计划来引导干系人合理参与项目</t>
-  </si>
-  <si>
-    <t>立项管理</t>
-  </si>
-  <si>
-    <t>项目投资前四个阶段</t>
-  </si>
-  <si>
-    <t>1）项目建议与立项申请</t>
-  </si>
-  <si>
-    <t>2）初步可行性研究</t>
-  </si>
-  <si>
-    <t>3）详细可行性研究</t>
-  </si>
-  <si>
-    <t>4）评估与决策</t>
-  </si>
-  <si>
-    <t>项目建议书内容【简述-两必两预测】</t>
-  </si>
-  <si>
-    <t>1）项目的必要性</t>
-  </si>
-  <si>
-    <t>2）项目的市场预测</t>
-  </si>
-  <si>
-    <t>3）项目预期成果的市场预测</t>
-  </si>
-  <si>
-    <t>4）项目建设的必要条件</t>
-  </si>
-  <si>
-    <t>可行性研究的内容【可研-鸡精摄晕他】</t>
-  </si>
-  <si>
-    <t>1）技术可行性分析</t>
-  </si>
-  <si>
-    <t>2）经济可行性分析</t>
-  </si>
-  <si>
-    <t>3）社会效益可行性分析</t>
-  </si>
-  <si>
-    <t>4）运行环境可行性分析</t>
-  </si>
-  <si>
-    <t>5）其他方面可行性分析</t>
-  </si>
-  <si>
-    <t>技术可行性分析内容【饥渴-嫌小能用】</t>
-  </si>
-  <si>
-    <t>1）进行项目开发的风险</t>
-  </si>
-  <si>
-    <t>2）人力资源的有效性</t>
-  </si>
-  <si>
-    <t>3）技术能力的可能性</t>
-  </si>
-  <si>
-    <t>4）物资（产品）的可用性</t>
   </si>
   <si>
     <t>进度管理</t>
@@ -4426,6 +4408,9 @@
     <t>q1x(f11+f21+..+fn1)/n+q2x(f12+f22+..+fn2)/n+...+qnx(f1n+f2n+..+fnn)/n</t>
   </si>
   <si>
+    <t>立项管理</t>
+  </si>
+  <si>
     <t>净现值分析、投资收益率分析</t>
   </si>
   <si>
@@ -4461,6 +4446,128 @@
   <si>
     <t>题目是按年如2014、2015等，则投产年按第0年开始计算
 题目指出第一年是投产年的，则投产年按第1年开始计算</t>
+  </si>
+  <si>
+    <t>项目投资前四个阶段</t>
+  </si>
+  <si>
+    <t>1）项目建议与立项申请</t>
+  </si>
+  <si>
+    <t>2）初步可行性研究</t>
+  </si>
+  <si>
+    <t>3）详细可行性研究</t>
+  </si>
+  <si>
+    <t>4）评估与决策</t>
+  </si>
+  <si>
+    <r>
+      <t>项目建议书内容</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>【简述-两必两预测】</t>
+    </r>
+  </si>
+  <si>
+    <t>1）项目的必要性</t>
+  </si>
+  <si>
+    <t>2）项目的市场预测</t>
+  </si>
+  <si>
+    <t>3）项目预期成果的市场预测</t>
+  </si>
+  <si>
+    <t>4）项目建设的必要条件</t>
+  </si>
+  <si>
+    <r>
+      <t>可行性研究的内容【</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>科研-技精社运塌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>】</t>
+    </r>
+  </si>
+  <si>
+    <t>1）技术可行性分析</t>
+  </si>
+  <si>
+    <t>2）经济可行性分析</t>
+  </si>
+  <si>
+    <t>3）社会效益可行性分析</t>
+  </si>
+  <si>
+    <t>4）运行环境可行性分析</t>
+  </si>
+  <si>
+    <t>5）其他方面可行性分析</t>
+  </si>
+  <si>
+    <r>
+      <t>技术可行性分析内容【</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>饥渴-嫌小能用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>】</t>
+    </r>
+  </si>
+  <si>
+    <t>1）进行项目开发的风险</t>
+  </si>
+  <si>
+    <t>2）人力资源的有效性</t>
+  </si>
+  <si>
+    <t>3）技术能力的可能性</t>
+  </si>
+  <si>
+    <t>4）物资（产品）的可用性</t>
   </si>
 </sst>
 </file>
@@ -4899,6 +5006,17 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -4930,17 +5048,6 @@
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -5382,42 +5489,45 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5470,6 +5580,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -5554,19 +5667,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5581,25 +5694,25 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5608,37 +5721,37 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5650,7 +5763,7 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -5750,8 +5863,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2514600" y="18841720"/>
-          <a:ext cx="10575290" cy="6602730"/>
+          <a:off x="2794000" y="17538700"/>
+          <a:ext cx="11545570" cy="6191250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6018,2317 +6131,2317 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AY27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="22.5555555555556" customWidth="1"/>
-    <col min="3" max="3" width="29.3796296296296" customWidth="1"/>
+    <col min="1" max="1" width="14.1083333333333" customWidth="1"/>
+    <col min="2" max="2" width="22.5583333333333" customWidth="1"/>
+    <col min="3" max="3" width="29.3833333333333" customWidth="1"/>
     <col min="4" max="4" width="33.75" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="28.1296296296296" customWidth="1"/>
-    <col min="7" max="7" width="29.3796296296296" customWidth="1"/>
+    <col min="6" max="6" width="28.1333333333333" customWidth="1"/>
+    <col min="7" max="7" width="29.3833333333333" customWidth="1"/>
     <col min="8" max="8" width="33.75" customWidth="1"/>
     <col min="9" max="9" width="31.5" customWidth="1"/>
-    <col min="10" max="10" width="29.3796296296296" customWidth="1"/>
-    <col min="11" max="12" width="24.8796296296296" customWidth="1"/>
-    <col min="13" max="13" width="24.1296296296296" customWidth="1"/>
-    <col min="14" max="15" width="24.8796296296296" customWidth="1"/>
-    <col min="16" max="16" width="29.3796296296296" customWidth="1"/>
-    <col min="17" max="17" width="24.8796296296296" customWidth="1"/>
-    <col min="18" max="18" width="29.3796296296296" customWidth="1"/>
+    <col min="10" max="10" width="29.3833333333333" customWidth="1"/>
+    <col min="11" max="12" width="24.8833333333333" customWidth="1"/>
+    <col min="13" max="13" width="24.1333333333333" customWidth="1"/>
+    <col min="14" max="15" width="24.8833333333333" customWidth="1"/>
+    <col min="16" max="16" width="29.3833333333333" customWidth="1"/>
+    <col min="17" max="17" width="24.8833333333333" customWidth="1"/>
+    <col min="18" max="18" width="29.3833333333333" customWidth="1"/>
     <col min="19" max="19" width="32.5" customWidth="1"/>
-    <col min="20" max="20" width="29.3796296296296" customWidth="1"/>
-    <col min="21" max="21" width="24.8796296296296" customWidth="1"/>
-    <col min="22" max="22" width="29.3796296296296" customWidth="1"/>
-    <col min="23" max="25" width="24.8796296296296" customWidth="1"/>
-    <col min="26" max="26" width="29.3796296296296" customWidth="1"/>
-    <col min="27" max="28" width="24.8796296296296" customWidth="1"/>
-    <col min="29" max="30" width="29.3796296296296" customWidth="1"/>
-    <col min="31" max="34" width="24.8796296296296" customWidth="1"/>
-    <col min="35" max="35" width="29.3796296296296" customWidth="1"/>
-    <col min="36" max="37" width="24.8796296296296" customWidth="1"/>
-    <col min="38" max="38" width="29.3796296296296" customWidth="1"/>
-    <col min="39" max="39" width="24.8796296296296" customWidth="1"/>
+    <col min="20" max="20" width="29.3833333333333" customWidth="1"/>
+    <col min="21" max="21" width="24.8833333333333" customWidth="1"/>
+    <col min="22" max="22" width="29.3833333333333" customWidth="1"/>
+    <col min="23" max="25" width="24.8833333333333" customWidth="1"/>
+    <col min="26" max="26" width="29.3833333333333" customWidth="1"/>
+    <col min="27" max="28" width="24.8833333333333" customWidth="1"/>
+    <col min="29" max="30" width="29.3833333333333" customWidth="1"/>
+    <col min="31" max="34" width="24.8833333333333" customWidth="1"/>
+    <col min="35" max="35" width="29.3833333333333" customWidth="1"/>
+    <col min="36" max="37" width="24.8833333333333" customWidth="1"/>
+    <col min="38" max="38" width="29.3833333333333" customWidth="1"/>
+    <col min="39" max="39" width="24.8833333333333" customWidth="1"/>
     <col min="40" max="41" width="33.75" customWidth="1"/>
-    <col min="42" max="43" width="29.3796296296296" customWidth="1"/>
-    <col min="44" max="44" width="24.8796296296296" customWidth="1"/>
-    <col min="45" max="45" width="29.3796296296296" customWidth="1"/>
-    <col min="46" max="47" width="24.8796296296296" customWidth="1"/>
-    <col min="48" max="48" width="27.1296296296296" customWidth="1"/>
+    <col min="42" max="43" width="29.3833333333333" customWidth="1"/>
+    <col min="44" max="44" width="24.8833333333333" customWidth="1"/>
+    <col min="45" max="45" width="29.3833333333333" customWidth="1"/>
+    <col min="46" max="47" width="24.8833333333333" customWidth="1"/>
+    <col min="48" max="48" width="27.1333333333333" customWidth="1"/>
     <col min="49" max="51" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51">
-      <c r="A1" s="11"/>
-      <c r="B1" s="11"/>
-      <c r="C1" s="53" t="s">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+      <c r="C1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="54"/>
-      <c r="J1" s="54" t="s">
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="54"/>
-      <c r="L1" s="54"/>
-      <c r="M1" s="54"/>
-      <c r="N1" s="54"/>
-      <c r="O1" s="54"/>
-      <c r="P1" s="54" t="s">
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="54"/>
-      <c r="R1" s="54"/>
-      <c r="S1" s="54"/>
-      <c r="T1" s="54"/>
-      <c r="U1" s="54"/>
-      <c r="V1" s="54" t="s">
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="56"/>
+      <c r="V1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="54"/>
-      <c r="X1" s="54"/>
-      <c r="Y1" s="54"/>
-      <c r="Z1" s="54" t="s">
+      <c r="W1" s="56"/>
+      <c r="X1" s="56"/>
+      <c r="Y1" s="56"/>
+      <c r="Z1" s="56" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="54"/>
-      <c r="AB1" s="54"/>
-      <c r="AC1" s="54" t="s">
+      <c r="AA1" s="56"/>
+      <c r="AB1" s="56"/>
+      <c r="AC1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="54"/>
-      <c r="AE1" s="54"/>
-      <c r="AF1" s="54"/>
-      <c r="AG1" s="54"/>
-      <c r="AH1" s="54"/>
-      <c r="AI1" s="54" t="s">
+      <c r="AD1" s="56"/>
+      <c r="AE1" s="56"/>
+      <c r="AF1" s="56"/>
+      <c r="AG1" s="56"/>
+      <c r="AH1" s="56"/>
+      <c r="AI1" s="56" t="s">
         <v>6</v>
       </c>
-      <c r="AJ1" s="54"/>
-      <c r="AK1" s="54"/>
-      <c r="AL1" s="54" t="s">
+      <c r="AJ1" s="56"/>
+      <c r="AK1" s="56"/>
+      <c r="AL1" s="56" t="s">
         <v>7</v>
       </c>
-      <c r="AM1" s="54"/>
-      <c r="AN1" s="54"/>
-      <c r="AO1" s="54"/>
-      <c r="AP1" s="54"/>
-      <c r="AQ1" s="54"/>
-      <c r="AR1" s="54"/>
-      <c r="AS1" s="54" t="s">
+      <c r="AM1" s="56"/>
+      <c r="AN1" s="56"/>
+      <c r="AO1" s="56"/>
+      <c r="AP1" s="56"/>
+      <c r="AQ1" s="56"/>
+      <c r="AR1" s="56"/>
+      <c r="AS1" s="56" t="s">
         <v>8</v>
       </c>
-      <c r="AT1" s="54"/>
-      <c r="AU1" s="54"/>
-      <c r="AV1" s="54" t="s">
+      <c r="AT1" s="56"/>
+      <c r="AU1" s="56"/>
+      <c r="AV1" s="56" t="s">
         <v>9</v>
       </c>
-      <c r="AW1" s="54"/>
-      <c r="AX1" s="54"/>
-      <c r="AY1" s="54"/>
+      <c r="AW1" s="56"/>
+      <c r="AX1" s="56"/>
+      <c r="AY1" s="56"/>
     </row>
     <row r="2" customFormat="1" ht="58" customHeight="1" spans="1:51">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="55" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="57" t="s">
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="59" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="59" t="s">
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="M2" s="60"/>
+      <c r="N2" s="60"/>
+      <c r="O2" s="60"/>
+      <c r="P2" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="60"/>
-      <c r="V2" s="59" t="s">
+      <c r="Q2" s="60"/>
+      <c r="R2" s="60"/>
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="U2" s="62"/>
+      <c r="V2" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
-      <c r="Y2" s="60"/>
-      <c r="Z2" s="57" t="s">
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
+      <c r="Y2" s="62"/>
+      <c r="Z2" s="59" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="58"/>
-      <c r="AB2" s="60"/>
-      <c r="AC2" s="59" t="s">
+      <c r="AA2" s="60"/>
+      <c r="AB2" s="62"/>
+      <c r="AC2" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="AD2" s="58"/>
-      <c r="AE2" s="58"/>
-      <c r="AF2" s="58"/>
-      <c r="AG2" s="58"/>
-      <c r="AH2" s="60"/>
-      <c r="AI2" s="59" t="s">
+      <c r="AD2" s="60"/>
+      <c r="AE2" s="60"/>
+      <c r="AF2" s="60"/>
+      <c r="AG2" s="60"/>
+      <c r="AH2" s="62"/>
+      <c r="AI2" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="AJ2" s="58"/>
-      <c r="AK2" s="60"/>
-      <c r="AL2" s="59" t="s">
+      <c r="AJ2" s="60"/>
+      <c r="AK2" s="62"/>
+      <c r="AL2" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="AM2" s="58"/>
-      <c r="AN2" s="58"/>
-      <c r="AO2" s="58"/>
-      <c r="AP2" s="58"/>
-      <c r="AQ2" s="58"/>
-      <c r="AR2" s="60"/>
-      <c r="AS2" s="61" t="s">
+      <c r="AM2" s="60"/>
+      <c r="AN2" s="60"/>
+      <c r="AO2" s="60"/>
+      <c r="AP2" s="60"/>
+      <c r="AQ2" s="60"/>
+      <c r="AR2" s="62"/>
+      <c r="AS2" s="63" t="s">
         <v>18</v>
       </c>
-      <c r="AT2" s="62"/>
-      <c r="AU2" s="63"/>
-      <c r="AV2" s="59" t="s">
+      <c r="AT2" s="64"/>
+      <c r="AU2" s="65"/>
+      <c r="AV2" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="AW2" s="58"/>
-      <c r="AX2" s="58"/>
-      <c r="AY2" s="60"/>
+      <c r="AW2" s="60"/>
+      <c r="AX2" s="60"/>
+      <c r="AY2" s="62"/>
     </row>
-    <row r="3" s="51" customFormat="1" spans="1:51">
-      <c r="A3" s="64"/>
-      <c r="B3" s="64"/>
-      <c r="C3" s="65" t="s">
+    <row r="3" s="53" customFormat="1" spans="1:51">
+      <c r="A3" s="66"/>
+      <c r="B3" s="66"/>
+      <c r="C3" s="67" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="65" t="s">
+      <c r="D3" s="67" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="65" t="s">
+      <c r="E3" s="67" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="65" t="s">
+      <c r="F3" s="67" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="65" t="s">
+      <c r="G3" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="65" t="s">
+      <c r="H3" s="67" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="65" t="s">
+      <c r="I3" s="67" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="66" t="s">
+      <c r="J3" s="68" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="66" t="s">
+      <c r="K3" s="68" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="66" t="s">
+      <c r="L3" s="68" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="66" t="s">
+      <c r="M3" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="66" t="s">
+      <c r="N3" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="66" t="s">
+      <c r="O3" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="66" t="s">
+      <c r="P3" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="66" t="s">
+      <c r="Q3" s="68" t="s">
         <v>34</v>
       </c>
-      <c r="R3" s="66" t="s">
+      <c r="R3" s="68" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="66" t="s">
+      <c r="S3" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="T3" s="66" t="s">
+      <c r="T3" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="66" t="s">
+      <c r="U3" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="V3" s="66" t="s">
+      <c r="V3" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="W3" s="66" t="s">
+      <c r="W3" s="68" t="s">
         <v>40</v>
       </c>
-      <c r="X3" s="66" t="s">
+      <c r="X3" s="68" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="66" t="s">
+      <c r="Y3" s="68" t="s">
         <v>42</v>
       </c>
-      <c r="Z3" s="66" t="s">
+      <c r="Z3" s="68" t="s">
         <v>43</v>
       </c>
-      <c r="AA3" s="66" t="s">
+      <c r="AA3" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="AB3" s="66" t="s">
+      <c r="AB3" s="68" t="s">
         <v>45</v>
       </c>
-      <c r="AC3" s="66" t="s">
+      <c r="AC3" s="68" t="s">
         <v>46</v>
       </c>
-      <c r="AD3" s="66" t="s">
+      <c r="AD3" s="68" t="s">
         <v>47</v>
       </c>
-      <c r="AE3" s="66" t="s">
+      <c r="AE3" s="68" t="s">
         <v>48</v>
       </c>
-      <c r="AF3" s="66" t="s">
+      <c r="AF3" s="68" t="s">
         <v>49</v>
       </c>
-      <c r="AG3" s="66" t="s">
+      <c r="AG3" s="68" t="s">
         <v>50</v>
       </c>
-      <c r="AH3" s="66" t="s">
+      <c r="AH3" s="68" t="s">
         <v>51</v>
       </c>
-      <c r="AI3" s="66" t="s">
+      <c r="AI3" s="68" t="s">
         <v>52</v>
       </c>
-      <c r="AJ3" s="66" t="s">
+      <c r="AJ3" s="68" t="s">
         <v>53</v>
       </c>
-      <c r="AK3" s="66" t="s">
+      <c r="AK3" s="68" t="s">
         <v>54</v>
       </c>
-      <c r="AL3" s="66" t="s">
+      <c r="AL3" s="68" t="s">
         <v>55</v>
       </c>
-      <c r="AM3" s="66" t="s">
+      <c r="AM3" s="68" t="s">
         <v>56</v>
       </c>
-      <c r="AN3" s="66" t="s">
+      <c r="AN3" s="68" t="s">
         <v>57</v>
       </c>
-      <c r="AO3" s="66" t="s">
+      <c r="AO3" s="68" t="s">
         <v>58</v>
       </c>
-      <c r="AP3" s="66" t="s">
+      <c r="AP3" s="68" t="s">
         <v>59</v>
       </c>
-      <c r="AQ3" s="66" t="s">
+      <c r="AQ3" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="AR3" s="66" t="s">
+      <c r="AR3" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="AS3" s="65" t="s">
+      <c r="AS3" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="AT3" s="65" t="s">
+      <c r="AT3" s="67" t="s">
         <v>63</v>
       </c>
-      <c r="AU3" s="65" t="s">
+      <c r="AU3" s="67" t="s">
         <v>64</v>
       </c>
-      <c r="AV3" s="65" t="s">
+      <c r="AV3" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="AW3" s="65" t="s">
+      <c r="AW3" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="AX3" s="65" t="s">
+      <c r="AX3" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="AY3" s="65" t="s">
+      <c r="AY3" s="67" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" s="51" customFormat="1" ht="115.2" spans="1:51">
-      <c r="A4" s="64"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="30" t="s">
+    <row r="4" s="53" customFormat="1" ht="108" spans="1:51">
+      <c r="A4" s="66"/>
+      <c r="B4" s="66"/>
+      <c r="C4" s="32" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="30" t="s">
+      <c r="D4" s="32" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="30" t="s">
+      <c r="F4" s="32" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="30" t="s">
+      <c r="H4" s="32" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="30" t="s">
+      <c r="J4" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="30" t="s">
+      <c r="K4" s="32" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="30" t="s">
+      <c r="L4" s="32" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="30" t="s">
+      <c r="M4" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="N4" s="30" t="s">
+      <c r="N4" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="O4" s="30" t="s">
+      <c r="O4" s="32" t="s">
         <v>81</v>
       </c>
-      <c r="P4" s="30" t="s">
+      <c r="P4" s="32" t="s">
         <v>82</v>
       </c>
-      <c r="Q4" s="30" t="s">
+      <c r="Q4" s="32" t="s">
         <v>83</v>
       </c>
-      <c r="R4" s="30" t="s">
+      <c r="R4" s="32" t="s">
         <v>84</v>
       </c>
-      <c r="S4" s="30" t="s">
+      <c r="S4" s="32" t="s">
         <v>85</v>
       </c>
-      <c r="T4" s="30" t="s">
+      <c r="T4" s="32" t="s">
         <v>86</v>
       </c>
-      <c r="U4" s="30" t="s">
+      <c r="U4" s="32" t="s">
         <v>87</v>
       </c>
-      <c r="V4" s="30" t="s">
+      <c r="V4" s="32" t="s">
         <v>88</v>
       </c>
-      <c r="W4" s="30" t="s">
+      <c r="W4" s="32" t="s">
         <v>89</v>
       </c>
-      <c r="X4" s="30" t="s">
+      <c r="X4" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="Y4" s="30" t="s">
+      <c r="Y4" s="32" t="s">
         <v>91</v>
       </c>
-      <c r="Z4" s="30" t="s">
+      <c r="Z4" s="32" t="s">
         <v>92</v>
       </c>
-      <c r="AA4" s="30" t="s">
+      <c r="AA4" s="32" t="s">
         <v>93</v>
       </c>
-      <c r="AB4" s="30" t="s">
+      <c r="AB4" s="32" t="s">
         <v>94</v>
       </c>
-      <c r="AC4" s="30" t="s">
+      <c r="AC4" s="32" t="s">
         <v>95</v>
       </c>
-      <c r="AD4" s="30" t="s">
+      <c r="AD4" s="32" t="s">
         <v>96</v>
       </c>
-      <c r="AE4" s="30" t="s">
+      <c r="AE4" s="32" t="s">
         <v>97</v>
       </c>
-      <c r="AF4" s="30" t="s">
+      <c r="AF4" s="32" t="s">
         <v>98</v>
       </c>
-      <c r="AG4" s="30" t="s">
+      <c r="AG4" s="32" t="s">
         <v>99</v>
       </c>
-      <c r="AH4" s="30" t="s">
+      <c r="AH4" s="32" t="s">
         <v>100</v>
       </c>
-      <c r="AI4" s="30" t="s">
+      <c r="AI4" s="32" t="s">
         <v>101</v>
       </c>
-      <c r="AJ4" s="30" t="s">
+      <c r="AJ4" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="AK4" s="30" t="s">
+      <c r="AK4" s="32" t="s">
         <v>103</v>
       </c>
-      <c r="AL4" s="30" t="s">
+      <c r="AL4" s="32" t="s">
         <v>104</v>
       </c>
-      <c r="AM4" s="30" t="s">
+      <c r="AM4" s="32" t="s">
         <v>105</v>
       </c>
-      <c r="AN4" s="30" t="s">
+      <c r="AN4" s="32" t="s">
         <v>106</v>
       </c>
-      <c r="AO4" s="30" t="s">
+      <c r="AO4" s="32" t="s">
         <v>107</v>
       </c>
-      <c r="AP4" s="30" t="s">
+      <c r="AP4" s="32" t="s">
         <v>108</v>
       </c>
-      <c r="AQ4" s="30" t="s">
+      <c r="AQ4" s="32" t="s">
         <v>109</v>
       </c>
-      <c r="AR4" s="30" t="s">
+      <c r="AR4" s="32" t="s">
         <v>110</v>
       </c>
-      <c r="AS4" s="30" t="s">
+      <c r="AS4" s="32" t="s">
         <v>111</v>
       </c>
-      <c r="AT4" s="30" t="s">
+      <c r="AT4" s="32" t="s">
         <v>112</v>
       </c>
-      <c r="AU4" s="30" t="s">
+      <c r="AU4" s="32" t="s">
         <v>113</v>
       </c>
-      <c r="AV4" s="30" t="s">
+      <c r="AV4" s="32" t="s">
         <v>114</v>
       </c>
-      <c r="AW4" s="30" t="s">
+      <c r="AW4" s="32" t="s">
         <v>115</v>
       </c>
-      <c r="AX4" s="30" t="s">
+      <c r="AX4" s="32" t="s">
         <v>116</v>
       </c>
-      <c r="AY4" s="30" t="s">
+      <c r="AY4" s="32" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" s="51" customFormat="1" ht="100.8" spans="1:51">
-      <c r="A5" s="64"/>
-      <c r="B5" s="64"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="30"/>
-      <c r="K5" s="30"/>
-      <c r="L5" s="30"/>
-      <c r="M5" s="30"/>
-      <c r="N5" s="30"/>
-      <c r="O5" s="30"/>
-      <c r="P5" s="30"/>
-      <c r="Q5" s="30"/>
-      <c r="R5" s="30"/>
-      <c r="S5" s="30"/>
-      <c r="T5" s="30"/>
-      <c r="U5" s="30"/>
-      <c r="V5" s="30"/>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
-      <c r="Z5" s="30"/>
-      <c r="AA5" s="30"/>
-      <c r="AB5" s="30"/>
-      <c r="AC5" s="30" t="s">
+    <row r="5" s="53" customFormat="1" ht="94.5" spans="1:51">
+      <c r="A5" s="66"/>
+      <c r="B5" s="66"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="32"/>
+      <c r="S5" s="32"/>
+      <c r="T5" s="32"/>
+      <c r="U5" s="32"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="32"/>
+      <c r="Y5" s="32"/>
+      <c r="Z5" s="32"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="32"/>
+      <c r="AC5" s="32" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="30" t="s">
+      <c r="AD5" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="AE5" s="30" t="s">
+      <c r="AE5" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="AF5" s="30" t="s">
+      <c r="AF5" s="32" t="s">
         <v>121</v>
       </c>
-      <c r="AG5" s="30" t="s">
+      <c r="AG5" s="32" t="s">
         <v>122</v>
       </c>
-      <c r="AH5" s="30" t="s">
+      <c r="AH5" s="32" t="s">
         <v>123</v>
       </c>
-      <c r="AI5" s="30" t="s">
+      <c r="AI5" s="32" t="s">
         <v>124</v>
       </c>
-      <c r="AJ5" s="30" t="s">
+      <c r="AJ5" s="32" t="s">
         <v>125</v>
       </c>
-      <c r="AK5" s="30" t="s">
+      <c r="AK5" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="AL5" s="30" t="s">
+      <c r="AL5" s="32" t="s">
         <v>127</v>
       </c>
-      <c r="AM5" s="30" t="s">
+      <c r="AM5" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="AN5" s="30" t="s">
+      <c r="AN5" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="AO5" s="30" t="s">
+      <c r="AO5" s="32" t="s">
         <v>130</v>
       </c>
-      <c r="AP5" s="30" t="s">
+      <c r="AP5" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="AQ5" s="30" t="s">
+      <c r="AQ5" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="AR5" s="30" t="s">
+      <c r="AR5" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="AS5" s="30" t="s">
+      <c r="AS5" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="AT5" s="30" t="s">
+      <c r="AT5" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="AU5" s="30" t="s">
+      <c r="AU5" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="AV5" s="30" t="s">
+      <c r="AV5" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="AW5" s="30" t="s">
+      <c r="AW5" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="AX5" s="30" t="s">
+      <c r="AX5" s="32" t="s">
         <v>139</v>
       </c>
-      <c r="AY5" s="30" t="s">
+      <c r="AY5" s="32" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="6" s="51" customFormat="1" ht="28.8" spans="1:51">
-      <c r="A6" s="64"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="67" t="s">
+    <row r="6" s="53" customFormat="1" ht="27" spans="1:51">
+      <c r="A6" s="66"/>
+      <c r="B6" s="66"/>
+      <c r="C6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="67" t="s">
+      <c r="D6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="F6" s="67" t="s">
+      <c r="F6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="67" t="s">
+      <c r="G6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="H6" s="67" t="s">
+      <c r="H6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="I6" s="67" t="s">
+      <c r="I6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="J6" s="67" t="s">
+      <c r="J6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="K6" s="67" t="s">
+      <c r="K6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="L6" s="67" t="s">
+      <c r="L6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="M6" s="67" t="s">
+      <c r="M6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="N6" s="67" t="s">
+      <c r="N6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="O6" s="67" t="s">
+      <c r="O6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="P6" s="67" t="s">
+      <c r="P6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="Q6" s="67" t="s">
+      <c r="Q6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="R6" s="67" t="s">
+      <c r="R6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="S6" s="67" t="s">
+      <c r="S6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="T6" s="67" t="s">
+      <c r="T6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="U6" s="67" t="s">
+      <c r="U6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="V6" s="30" t="s">
+      <c r="V6" s="32" t="s">
         <v>142</v>
       </c>
-      <c r="W6" s="67" t="s">
+      <c r="W6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="X6" s="67" t="s">
+      <c r="X6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="Y6" s="67" t="s">
+      <c r="Y6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="Z6" s="67" t="s">
+      <c r="Z6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AA6" s="67" t="s">
+      <c r="AA6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AB6" s="67" t="s">
+      <c r="AB6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AC6" s="67" t="s">
+      <c r="AC6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AD6" s="67" t="s">
+      <c r="AD6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AE6" s="67" t="s">
+      <c r="AE6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AF6" s="67" t="s">
+      <c r="AF6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AG6" s="67" t="s">
+      <c r="AG6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AH6" s="67" t="s">
+      <c r="AH6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AI6" s="67" t="s">
+      <c r="AI6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AJ6" s="67" t="s">
+      <c r="AJ6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AK6" s="67" t="s">
+      <c r="AK6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AL6" s="67" t="s">
+      <c r="AL6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AM6" s="67" t="s">
+      <c r="AM6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AN6" s="67" t="s">
+      <c r="AN6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AO6" s="67" t="s">
+      <c r="AO6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AP6" s="67" t="s">
+      <c r="AP6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AQ6" s="67" t="s">
+      <c r="AQ6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="67" t="s">
+      <c r="AR6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AS6" s="67" t="s">
+      <c r="AS6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AT6" s="67" t="s">
+      <c r="AT6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AU6" s="67" t="s">
+      <c r="AU6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AV6" s="67" t="s">
+      <c r="AV6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AW6" s="67" t="s">
+      <c r="AW6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AX6" s="67" t="s">
+      <c r="AX6" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="AY6" s="67" t="s">
+      <c r="AY6" s="69" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="7" s="51" customFormat="1" ht="57.6" spans="1:51">
-      <c r="A7" s="68" t="s">
+    <row r="7" s="53" customFormat="1" ht="54" spans="1:51">
+      <c r="A7" s="70" t="s">
         <v>143</v>
       </c>
-      <c r="B7" s="67" t="s">
+      <c r="B7" s="69" t="s">
         <v>144</v>
       </c>
-      <c r="C7" s="69" t="s">
+      <c r="C7" s="71" t="s">
         <v>145</v>
       </c>
-      <c r="D7" s="67" t="s">
+      <c r="D7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="E7" s="67" t="s">
+      <c r="E7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="F7" s="67" t="s">
+      <c r="F7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="G7" s="67" t="s">
+      <c r="G7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="H7" s="67" t="s">
+      <c r="H7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="I7" s="67" t="s">
+      <c r="I7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="J7" s="67" t="s">
+      <c r="J7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="K7" s="67" t="s">
+      <c r="K7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="L7" s="67" t="s">
+      <c r="L7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="M7" s="67" t="s">
+      <c r="M7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="N7" s="67" t="s">
+      <c r="N7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="O7" s="67" t="s">
+      <c r="O7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="P7" s="67" t="s">
+      <c r="P7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="Q7" s="67" t="s">
+      <c r="Q7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="R7" s="67" t="s">
+      <c r="R7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="S7" s="67" t="s">
+      <c r="S7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="T7" s="67" t="s">
+      <c r="T7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="U7" s="67" t="s">
+      <c r="U7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="V7" s="30" t="s">
+      <c r="V7" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="W7" s="67" t="s">
+      <c r="W7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="X7" s="67" t="s">
+      <c r="X7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="Y7" s="67" t="s">
+      <c r="Y7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="Z7" s="67" t="s">
+      <c r="Z7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AA7" s="67" t="s">
+      <c r="AA7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AB7" s="67" t="s">
+      <c r="AB7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AC7" s="67" t="s">
+      <c r="AC7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AD7" s="67" t="s">
+      <c r="AD7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AE7" s="67" t="s">
+      <c r="AE7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AF7" s="67" t="s">
+      <c r="AF7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AG7" s="67" t="s">
+      <c r="AG7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AH7" s="67" t="s">
+      <c r="AH7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AI7" s="67" t="s">
+      <c r="AI7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AJ7" s="67" t="s">
+      <c r="AJ7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AK7" s="67" t="s">
+      <c r="AK7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AL7" s="67" t="s">
+      <c r="AL7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AM7" s="67" t="s">
+      <c r="AM7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AN7" s="67" t="s">
+      <c r="AN7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AO7" s="67" t="s">
+      <c r="AO7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AP7" s="67" t="s">
+      <c r="AP7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AQ7" s="67" t="s">
+      <c r="AQ7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AR7" s="67" t="s">
+      <c r="AR7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AS7" s="67" t="s">
+      <c r="AS7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AT7" s="67" t="s">
+      <c r="AT7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AU7" s="67" t="s">
+      <c r="AU7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AV7" s="67" t="s">
+      <c r="AV7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AW7" s="67" t="s">
+      <c r="AW7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AX7" s="67" t="s">
+      <c r="AX7" s="69" t="s">
         <v>145</v>
       </c>
-      <c r="AY7" s="67" t="s">
+      <c r="AY7" s="69" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="8" ht="72" spans="1:51">
-      <c r="A8" s="70"/>
-      <c r="B8" s="71" t="s">
+    <row r="8" ht="67.5" spans="1:51">
+      <c r="A8" s="72"/>
+      <c r="B8" s="73" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="72" t="s">
+      <c r="C8" s="74" t="s">
         <v>148</v>
       </c>
-      <c r="D8" s="72" t="s">
+      <c r="D8" s="74" t="s">
         <v>149</v>
       </c>
-      <c r="E8" s="72" t="s">
+      <c r="E8" s="74" t="s">
         <v>150</v>
       </c>
-      <c r="F8" s="72" t="s">
+      <c r="F8" s="74" t="s">
         <v>151</v>
       </c>
-      <c r="G8" s="72" t="s">
+      <c r="G8" s="74" t="s">
         <v>152</v>
       </c>
-      <c r="H8" s="72" t="s">
+      <c r="H8" s="74" t="s">
         <v>153</v>
       </c>
-      <c r="I8" s="72" t="s">
+      <c r="I8" s="74" t="s">
         <v>154</v>
       </c>
-      <c r="J8" s="72" t="s">
+      <c r="J8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="K8" s="72" t="s">
+      <c r="K8" s="74" t="s">
         <v>156</v>
       </c>
-      <c r="L8" s="72" t="s">
+      <c r="L8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="M8" s="72" t="s">
+      <c r="M8" s="74" t="s">
         <v>157</v>
       </c>
-      <c r="N8" s="72" t="s">
+      <c r="N8" s="74" t="s">
         <v>158</v>
       </c>
-      <c r="O8" s="72" t="s">
+      <c r="O8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="P8" s="72" t="s">
+      <c r="P8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="Q8" s="72" t="s">
+      <c r="Q8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="R8" s="72" t="s">
+      <c r="R8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="S8" s="72" t="s">
+      <c r="S8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="T8" s="72" t="s">
+      <c r="T8" s="74" t="s">
         <v>159</v>
       </c>
-      <c r="U8" s="72" t="s">
+      <c r="U8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="V8" s="72" t="s">
+      <c r="V8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="W8" s="72" t="s">
+      <c r="W8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="X8" s="72" t="s">
+      <c r="X8" s="74" t="s">
         <v>160</v>
       </c>
-      <c r="Y8" s="72" t="s">
+      <c r="Y8" s="74" t="s">
         <v>161</v>
       </c>
-      <c r="Z8" s="72" t="s">
+      <c r="Z8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AA8" s="72" t="s">
+      <c r="AA8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AB8" s="72" t="s">
+      <c r="AB8" s="74" t="s">
         <v>162</v>
       </c>
-      <c r="AC8" s="72" t="s">
+      <c r="AC8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AD8" s="72" t="s">
+      <c r="AD8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AE8" s="72" t="s">
+      <c r="AE8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AF8" s="72" t="s">
+      <c r="AF8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AG8" s="72" t="s">
+      <c r="AG8" s="74" t="s">
         <v>163</v>
       </c>
-      <c r="AH8" s="72" t="s">
+      <c r="AH8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AI8" s="72" t="s">
+      <c r="AI8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AJ8" s="72" t="s">
+      <c r="AJ8" s="74" t="s">
         <v>164</v>
       </c>
-      <c r="AK8" s="72" t="s">
+      <c r="AK8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AL8" s="72" t="s">
+      <c r="AL8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AM8" s="72" t="s">
+      <c r="AM8" s="74" t="s">
         <v>165</v>
       </c>
-      <c r="AN8" s="72" t="s">
+      <c r="AN8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AO8" s="72" t="s">
+      <c r="AO8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AP8" s="72" t="s">
+      <c r="AP8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AQ8" s="72" t="s">
+      <c r="AQ8" s="74" t="s">
         <v>155</v>
       </c>
-      <c r="AR8" s="72" t="s">
+      <c r="AR8" s="74" t="s">
         <v>164</v>
       </c>
-      <c r="AS8" s="73" t="s">
+      <c r="AS8" s="75" t="s">
         <v>166</v>
       </c>
-      <c r="AT8" s="73" t="s">
+      <c r="AT8" s="75" t="s">
         <v>167</v>
       </c>
-      <c r="AU8" s="73" t="s">
+      <c r="AU8" s="75" t="s">
         <v>168</v>
       </c>
-      <c r="AV8" s="73" t="s">
+      <c r="AV8" s="75" t="s">
         <v>169</v>
       </c>
-      <c r="AW8" s="73" t="s">
+      <c r="AW8" s="75" t="s">
         <v>159</v>
       </c>
-      <c r="AX8" s="74" t="s">
+      <c r="AX8" s="76" t="s">
         <v>155</v>
       </c>
-      <c r="AY8" s="74" t="s">
+      <c r="AY8" s="76" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="9" ht="43.2" spans="1:51">
-      <c r="A9" s="70"/>
-      <c r="B9" s="25" t="s">
+    <row r="9" ht="40.5" spans="1:51">
+      <c r="A9" s="72"/>
+      <c r="B9" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-      <c r="J9" s="73"/>
-      <c r="K9" s="73" t="s">
+      <c r="C9" s="75"/>
+      <c r="D9" s="75"/>
+      <c r="E9" s="75"/>
+      <c r="F9" s="75"/>
+      <c r="G9" s="75"/>
+      <c r="H9" s="75"/>
+      <c r="I9" s="75"/>
+      <c r="J9" s="75"/>
+      <c r="K9" s="75" t="s">
         <v>171</v>
       </c>
-      <c r="L9" s="73"/>
-      <c r="M9" s="73"/>
-      <c r="N9" s="73" t="s">
+      <c r="L9" s="75"/>
+      <c r="M9" s="75"/>
+      <c r="N9" s="75" t="s">
         <v>172</v>
       </c>
-      <c r="O9" s="73"/>
-      <c r="P9" s="73"/>
-      <c r="Q9" s="73"/>
-      <c r="R9" s="73"/>
-      <c r="S9" s="73"/>
-      <c r="T9" s="73"/>
-      <c r="U9" s="73"/>
-      <c r="V9" s="73"/>
-      <c r="W9" s="73"/>
-      <c r="X9" s="73"/>
-      <c r="Y9" s="73"/>
-      <c r="Z9" s="73"/>
-      <c r="AA9" s="73"/>
-      <c r="AB9" s="73"/>
-      <c r="AC9" s="73"/>
-      <c r="AD9" s="73"/>
-      <c r="AE9" s="73"/>
-      <c r="AF9" s="73"/>
-      <c r="AG9" s="73"/>
-      <c r="AH9" s="73"/>
-      <c r="AI9" s="73"/>
-      <c r="AJ9" s="73"/>
-      <c r="AK9" s="73"/>
-      <c r="AL9" s="73"/>
-      <c r="AM9" s="73"/>
-      <c r="AN9" s="73"/>
-      <c r="AO9" s="73"/>
-      <c r="AP9" s="73"/>
-      <c r="AQ9" s="73"/>
-      <c r="AR9" s="73"/>
-      <c r="AS9" s="73"/>
-      <c r="AT9" s="73"/>
-      <c r="AU9" s="73"/>
-      <c r="AV9" s="73"/>
-      <c r="AW9" s="73"/>
-      <c r="AX9" s="74"/>
-      <c r="AY9" s="74"/>
+      <c r="O9" s="75"/>
+      <c r="P9" s="75"/>
+      <c r="Q9" s="75"/>
+      <c r="R9" s="75"/>
+      <c r="S9" s="75"/>
+      <c r="T9" s="75"/>
+      <c r="U9" s="75"/>
+      <c r="V9" s="75"/>
+      <c r="W9" s="75"/>
+      <c r="X9" s="75"/>
+      <c r="Y9" s="75"/>
+      <c r="Z9" s="75"/>
+      <c r="AA9" s="75"/>
+      <c r="AB9" s="75"/>
+      <c r="AC9" s="75"/>
+      <c r="AD9" s="75"/>
+      <c r="AE9" s="75"/>
+      <c r="AF9" s="75"/>
+      <c r="AG9" s="75"/>
+      <c r="AH9" s="75"/>
+      <c r="AI9" s="75"/>
+      <c r="AJ9" s="75"/>
+      <c r="AK9" s="75"/>
+      <c r="AL9" s="75"/>
+      <c r="AM9" s="75"/>
+      <c r="AN9" s="75"/>
+      <c r="AO9" s="75"/>
+      <c r="AP9" s="75"/>
+      <c r="AQ9" s="75"/>
+      <c r="AR9" s="75"/>
+      <c r="AS9" s="75"/>
+      <c r="AT9" s="75"/>
+      <c r="AU9" s="75"/>
+      <c r="AV9" s="75"/>
+      <c r="AW9" s="75"/>
+      <c r="AX9" s="76"/>
+      <c r="AY9" s="76"/>
     </row>
-    <row r="10" ht="86.4" spans="1:51">
-      <c r="A10" s="75"/>
-      <c r="B10" s="25" t="s">
+    <row r="10" ht="81" spans="1:51">
+      <c r="A10" s="77"/>
+      <c r="B10" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73"/>
-      <c r="J10" s="73"/>
-      <c r="K10" s="73" t="s">
+      <c r="C10" s="75"/>
+      <c r="D10" s="75"/>
+      <c r="E10" s="75"/>
+      <c r="F10" s="75"/>
+      <c r="G10" s="75"/>
+      <c r="H10" s="75"/>
+      <c r="I10" s="75"/>
+      <c r="J10" s="75"/>
+      <c r="K10" s="75" t="s">
         <v>174</v>
       </c>
-      <c r="L10" s="73" t="s">
+      <c r="L10" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="M10" s="73"/>
-      <c r="N10" s="73" t="s">
+      <c r="M10" s="75"/>
+      <c r="N10" s="75" t="s">
         <v>176</v>
       </c>
-      <c r="O10" s="73"/>
-      <c r="P10" s="73"/>
-      <c r="Q10" s="73"/>
-      <c r="R10" s="73"/>
-      <c r="S10" s="73"/>
-      <c r="T10" s="73"/>
-      <c r="U10" s="73"/>
-      <c r="V10" s="73"/>
-      <c r="W10" s="73"/>
-      <c r="X10" s="73"/>
-      <c r="Y10" s="73"/>
-      <c r="Z10" s="73"/>
-      <c r="AA10" s="73" t="s">
+      <c r="O10" s="75"/>
+      <c r="P10" s="75"/>
+      <c r="Q10" s="75"/>
+      <c r="R10" s="75"/>
+      <c r="S10" s="75"/>
+      <c r="T10" s="75"/>
+      <c r="U10" s="75"/>
+      <c r="V10" s="75"/>
+      <c r="W10" s="75"/>
+      <c r="X10" s="75"/>
+      <c r="Y10" s="75"/>
+      <c r="Z10" s="75"/>
+      <c r="AA10" s="75" t="s">
         <v>177</v>
       </c>
-      <c r="AB10" s="73"/>
-      <c r="AC10" s="73"/>
-      <c r="AD10" s="73"/>
-      <c r="AE10" s="73"/>
-      <c r="AF10" s="73"/>
-      <c r="AG10" s="73"/>
-      <c r="AH10" s="73"/>
-      <c r="AI10" s="73"/>
-      <c r="AJ10" s="73" t="s">
+      <c r="AB10" s="75"/>
+      <c r="AC10" s="75"/>
+      <c r="AD10" s="75"/>
+      <c r="AE10" s="75"/>
+      <c r="AF10" s="75"/>
+      <c r="AG10" s="75"/>
+      <c r="AH10" s="75"/>
+      <c r="AI10" s="75"/>
+      <c r="AJ10" s="75" t="s">
         <v>178</v>
       </c>
-      <c r="AK10" s="73"/>
-      <c r="AL10" s="73"/>
-      <c r="AM10" s="73"/>
-      <c r="AN10" s="73"/>
-      <c r="AO10" s="73"/>
-      <c r="AP10" s="73"/>
-      <c r="AQ10" s="73"/>
-      <c r="AR10" s="73"/>
-      <c r="AS10" s="73"/>
-      <c r="AT10" s="73"/>
-      <c r="AU10" s="73"/>
-      <c r="AV10" s="73"/>
-      <c r="AW10" s="73"/>
-      <c r="AX10" s="74"/>
-      <c r="AY10" s="74"/>
+      <c r="AK10" s="75"/>
+      <c r="AL10" s="75"/>
+      <c r="AM10" s="75"/>
+      <c r="AN10" s="75"/>
+      <c r="AO10" s="75"/>
+      <c r="AP10" s="75"/>
+      <c r="AQ10" s="75"/>
+      <c r="AR10" s="75"/>
+      <c r="AS10" s="75"/>
+      <c r="AT10" s="75"/>
+      <c r="AU10" s="75"/>
+      <c r="AV10" s="75"/>
+      <c r="AW10" s="75"/>
+      <c r="AX10" s="76"/>
+      <c r="AY10" s="76"/>
     </row>
     <row r="11" spans="1:51">
-      <c r="A11" s="76" t="s">
+      <c r="A11" s="78" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="77" t="s">
+      <c r="B11" s="79" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="52"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="52"/>
-      <c r="K11" s="52"/>
-      <c r="L11" s="52"/>
-      <c r="M11" s="52"/>
-      <c r="N11" s="52"/>
-      <c r="O11" s="52"/>
-      <c r="P11" s="52"/>
-      <c r="Q11" s="52"/>
-      <c r="R11" s="52"/>
-      <c r="S11" s="52"/>
-      <c r="T11" s="52"/>
-      <c r="U11" s="52"/>
-      <c r="V11" s="52"/>
-      <c r="W11" s="52"/>
-      <c r="X11" s="52"/>
-      <c r="Y11" s="52"/>
-      <c r="Z11" s="52"/>
-      <c r="AA11" s="52"/>
-      <c r="AB11" s="52"/>
-      <c r="AC11" s="52"/>
-      <c r="AD11" s="52"/>
-      <c r="AE11" s="52"/>
-      <c r="AF11" s="52"/>
-      <c r="AG11" s="52"/>
-      <c r="AH11" s="52"/>
-      <c r="AI11" s="52"/>
-      <c r="AJ11" s="52"/>
-      <c r="AK11" s="52"/>
-      <c r="AL11" s="52"/>
-      <c r="AM11" s="52"/>
-      <c r="AN11" s="52"/>
-      <c r="AO11" s="52"/>
-      <c r="AP11" s="52"/>
-      <c r="AQ11" s="52"/>
-      <c r="AR11" s="52"/>
-      <c r="AS11" s="52"/>
-      <c r="AT11" s="52"/>
-      <c r="AU11" s="52"/>
-      <c r="AV11" s="52"/>
-      <c r="AW11" s="52"/>
-      <c r="AX11" s="52"/>
-      <c r="AY11" s="52"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
+      <c r="K11" s="54"/>
+      <c r="L11" s="54"/>
+      <c r="M11" s="54"/>
+      <c r="N11" s="54"/>
+      <c r="O11" s="54"/>
+      <c r="P11" s="54"/>
+      <c r="Q11" s="54"/>
+      <c r="R11" s="54"/>
+      <c r="S11" s="54"/>
+      <c r="T11" s="54"/>
+      <c r="U11" s="54"/>
+      <c r="V11" s="54"/>
+      <c r="W11" s="54"/>
+      <c r="X11" s="54"/>
+      <c r="Y11" s="54"/>
+      <c r="Z11" s="54"/>
+      <c r="AA11" s="54"/>
+      <c r="AB11" s="54"/>
+      <c r="AC11" s="54"/>
+      <c r="AD11" s="54"/>
+      <c r="AE11" s="54"/>
+      <c r="AF11" s="54"/>
+      <c r="AG11" s="54"/>
+      <c r="AH11" s="54"/>
+      <c r="AI11" s="54"/>
+      <c r="AJ11" s="54"/>
+      <c r="AK11" s="54"/>
+      <c r="AL11" s="54"/>
+      <c r="AM11" s="54"/>
+      <c r="AN11" s="54"/>
+      <c r="AO11" s="54"/>
+      <c r="AP11" s="54"/>
+      <c r="AQ11" s="54"/>
+      <c r="AR11" s="54"/>
+      <c r="AS11" s="54"/>
+      <c r="AT11" s="54"/>
+      <c r="AU11" s="54"/>
+      <c r="AV11" s="54"/>
+      <c r="AW11" s="54"/>
+      <c r="AX11" s="54"/>
+      <c r="AY11" s="54"/>
     </row>
     <row r="12" spans="1:51">
-      <c r="A12" s="76" t="s">
+      <c r="A12" s="78" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="78" t="s">
+      <c r="B12" s="80" t="s">
         <v>182</v>
       </c>
-      <c r="C12" s="52"/>
-      <c r="D12" s="52"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="52"/>
-      <c r="G12" s="52"/>
-      <c r="H12" s="52"/>
-      <c r="I12" s="52"/>
-      <c r="J12" s="52"/>
-      <c r="K12" s="52"/>
-      <c r="L12" s="52"/>
-      <c r="M12" s="52"/>
-      <c r="N12" s="52"/>
-      <c r="O12" s="52"/>
-      <c r="P12" s="52"/>
-      <c r="Q12" s="52"/>
-      <c r="R12" s="52"/>
-      <c r="S12" s="52"/>
-      <c r="T12" s="52"/>
-      <c r="U12" s="52"/>
-      <c r="V12" s="52"/>
-      <c r="W12" s="52"/>
-      <c r="X12" s="52"/>
-      <c r="Y12" s="52"/>
-      <c r="Z12" s="52"/>
-      <c r="AA12" s="52"/>
-      <c r="AB12" s="52"/>
-      <c r="AC12" s="52"/>
-      <c r="AD12" s="52"/>
-      <c r="AE12" s="52"/>
-      <c r="AF12" s="52"/>
-      <c r="AG12" s="52"/>
-      <c r="AH12" s="52"/>
-      <c r="AI12" s="52"/>
-      <c r="AJ12" s="52"/>
-      <c r="AK12" s="52"/>
-      <c r="AL12" s="52"/>
-      <c r="AM12" s="52"/>
-      <c r="AN12" s="52"/>
-      <c r="AO12" s="52"/>
-      <c r="AP12" s="52"/>
-      <c r="AQ12" s="52"/>
-      <c r="AR12" s="52"/>
-      <c r="AS12" s="52"/>
-      <c r="AT12" s="52"/>
-      <c r="AU12" s="52"/>
-      <c r="AV12" s="52"/>
-      <c r="AW12" s="52"/>
-      <c r="AX12" s="52"/>
-      <c r="AY12" s="52"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
+      <c r="K12" s="54"/>
+      <c r="L12" s="54"/>
+      <c r="M12" s="54"/>
+      <c r="N12" s="54"/>
+      <c r="O12" s="54"/>
+      <c r="P12" s="54"/>
+      <c r="Q12" s="54"/>
+      <c r="R12" s="54"/>
+      <c r="S12" s="54"/>
+      <c r="T12" s="54"/>
+      <c r="U12" s="54"/>
+      <c r="V12" s="54"/>
+      <c r="W12" s="54"/>
+      <c r="X12" s="54"/>
+      <c r="Y12" s="54"/>
+      <c r="Z12" s="54"/>
+      <c r="AA12" s="54"/>
+      <c r="AB12" s="54"/>
+      <c r="AC12" s="54"/>
+      <c r="AD12" s="54"/>
+      <c r="AE12" s="54"/>
+      <c r="AF12" s="54"/>
+      <c r="AG12" s="54"/>
+      <c r="AH12" s="54"/>
+      <c r="AI12" s="54"/>
+      <c r="AJ12" s="54"/>
+      <c r="AK12" s="54"/>
+      <c r="AL12" s="54"/>
+      <c r="AM12" s="54"/>
+      <c r="AN12" s="54"/>
+      <c r="AO12" s="54"/>
+      <c r="AP12" s="54"/>
+      <c r="AQ12" s="54"/>
+      <c r="AR12" s="54"/>
+      <c r="AS12" s="54"/>
+      <c r="AT12" s="54"/>
+      <c r="AU12" s="54"/>
+      <c r="AV12" s="54"/>
+      <c r="AW12" s="54"/>
+      <c r="AX12" s="54"/>
+      <c r="AY12" s="54"/>
     </row>
-    <row r="14" ht="115.2" spans="1:51">
-      <c r="A14" s="79" t="s">
+    <row r="14" ht="94.5" spans="1:51">
+      <c r="A14" s="81" t="s">
         <v>183</v>
       </c>
-      <c r="B14" s="80" t="s">
+      <c r="B14" s="82" t="s">
         <v>184</v>
       </c>
-      <c r="C14" s="81"/>
-      <c r="D14" s="82"/>
-      <c r="E14" s="82"/>
-      <c r="F14" s="82" t="s">
+      <c r="C14" s="83"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84" t="s">
         <v>185</v>
       </c>
-      <c r="G14" s="82"/>
-      <c r="H14" s="82" t="s">
+      <c r="G14" s="84"/>
+      <c r="H14" s="84" t="s">
         <v>186</v>
       </c>
-      <c r="I14" s="82"/>
-      <c r="J14" s="82"/>
-      <c r="K14" s="82" t="s">
+      <c r="I14" s="84"/>
+      <c r="J14" s="84"/>
+      <c r="K14" s="84" t="s">
         <v>187</v>
       </c>
-      <c r="L14" s="82" t="s">
+      <c r="L14" s="84" t="s">
         <v>188</v>
       </c>
-      <c r="M14" s="82" t="s">
+      <c r="M14" s="84" t="s">
         <v>189</v>
       </c>
-      <c r="N14" s="82" t="s">
+      <c r="N14" s="84" t="s">
         <v>190</v>
       </c>
-      <c r="O14" s="82"/>
-      <c r="P14" s="82"/>
-      <c r="Q14" s="82" t="s">
+      <c r="O14" s="84"/>
+      <c r="P14" s="84"/>
+      <c r="Q14" s="84" t="s">
         <v>191</v>
       </c>
-      <c r="R14" s="82" t="s">
+      <c r="R14" s="84" t="s">
         <v>192</v>
       </c>
-      <c r="S14" s="82" t="s">
+      <c r="S14" s="84" t="s">
         <v>193</v>
       </c>
-      <c r="T14" s="82" t="s">
+      <c r="T14" s="84" t="s">
         <v>194</v>
       </c>
-      <c r="U14" s="82" t="s">
+      <c r="U14" s="84" t="s">
         <v>195</v>
       </c>
-      <c r="V14" s="82"/>
-      <c r="W14" s="82" t="s">
+      <c r="V14" s="84"/>
+      <c r="W14" s="84" t="s">
         <v>193</v>
       </c>
-      <c r="X14" s="82" t="s">
+      <c r="X14" s="84" t="s">
         <v>196</v>
       </c>
-      <c r="Y14" s="82" t="s">
+      <c r="Y14" s="84" t="s">
         <v>197</v>
       </c>
-      <c r="Z14" s="82" t="s">
+      <c r="Z14" s="84" t="s">
         <v>198</v>
       </c>
-      <c r="AA14" s="82" t="s">
+      <c r="AA14" s="84" t="s">
         <v>199</v>
       </c>
-      <c r="AB14" s="82" t="s">
+      <c r="AB14" s="84" t="s">
         <v>200</v>
       </c>
-      <c r="AC14" s="82" t="s">
+      <c r="AC14" s="84" t="s">
         <v>201</v>
       </c>
-      <c r="AD14" s="82" t="s">
+      <c r="AD14" s="84" t="s">
         <v>202</v>
       </c>
-      <c r="AE14" s="82" t="s">
+      <c r="AE14" s="84" t="s">
         <v>203</v>
       </c>
-      <c r="AF14" s="82" t="s">
+      <c r="AF14" s="84" t="s">
         <v>204</v>
       </c>
-      <c r="AG14" s="82"/>
-      <c r="AH14" s="82" t="s">
+      <c r="AG14" s="84"/>
+      <c r="AH14" s="84" t="s">
         <v>205</v>
       </c>
-      <c r="AI14" s="82" t="s">
+      <c r="AI14" s="84" t="s">
         <v>206</v>
       </c>
-      <c r="AJ14" s="82" t="s">
+      <c r="AJ14" s="84" t="s">
         <v>207</v>
       </c>
-      <c r="AK14" s="82"/>
-      <c r="AL14" s="82"/>
-      <c r="AM14" s="82" t="s">
+      <c r="AK14" s="84"/>
+      <c r="AL14" s="84"/>
+      <c r="AM14" s="84" t="s">
         <v>208</v>
       </c>
-      <c r="AN14" s="82" t="s">
+      <c r="AN14" s="84" t="s">
         <v>209</v>
       </c>
-      <c r="AO14" s="82" t="s">
+      <c r="AO14" s="84" t="s">
         <v>210</v>
       </c>
-      <c r="AP14" s="82" t="s">
+      <c r="AP14" s="84" t="s">
         <v>211</v>
       </c>
-      <c r="AQ14" s="82"/>
-      <c r="AR14" s="82" t="s">
+      <c r="AQ14" s="84"/>
+      <c r="AR14" s="84" t="s">
         <v>212</v>
       </c>
-      <c r="AS14" s="83" t="s">
+      <c r="AS14" s="85" t="s">
         <v>213</v>
       </c>
-      <c r="AT14" s="82" t="s">
+      <c r="AT14" s="84" t="s">
         <v>214</v>
       </c>
-      <c r="AU14" s="82" t="s">
+      <c r="AU14" s="84" t="s">
         <v>215</v>
       </c>
-      <c r="AV14" s="74"/>
-      <c r="AW14" s="74"/>
-      <c r="AX14" s="73" t="s">
+      <c r="AV14" s="76"/>
+      <c r="AW14" s="76"/>
+      <c r="AX14" s="75" t="s">
         <v>216</v>
       </c>
-      <c r="AY14" s="73"/>
+      <c r="AY14" s="75"/>
     </row>
     <row r="15" spans="1:51">
-      <c r="A15" s="84"/>
-      <c r="B15" s="85" t="s">
+      <c r="A15" s="86"/>
+      <c r="B15" s="87" t="s">
         <v>217</v>
       </c>
-      <c r="C15" s="86"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-      <c r="F15" s="78"/>
-      <c r="G15" s="78"/>
-      <c r="H15" s="78"/>
-      <c r="I15" s="78"/>
-      <c r="J15" s="78"/>
-      <c r="K15" s="78"/>
-      <c r="L15" s="78"/>
-      <c r="M15" s="78"/>
-      <c r="N15" s="78"/>
-      <c r="O15" s="78"/>
-      <c r="P15" s="78"/>
-      <c r="Q15" s="78"/>
-      <c r="R15" s="78"/>
-      <c r="S15" s="78"/>
-      <c r="T15" s="78"/>
-      <c r="U15" s="78"/>
-      <c r="V15" s="78"/>
-      <c r="W15" s="78"/>
-      <c r="X15" s="78"/>
-      <c r="Y15" s="78"/>
-      <c r="Z15" s="78"/>
-      <c r="AA15" s="78"/>
-      <c r="AB15" s="78"/>
-      <c r="AC15" s="78"/>
-      <c r="AD15" s="78"/>
-      <c r="AE15" s="78"/>
-      <c r="AF15" s="78"/>
-      <c r="AG15" s="78"/>
-      <c r="AH15" s="78"/>
-      <c r="AI15" s="78"/>
-      <c r="AJ15" s="78"/>
-      <c r="AK15" s="78"/>
-      <c r="AL15" s="78"/>
-      <c r="AM15" s="78"/>
-      <c r="AN15" s="78"/>
-      <c r="AO15" s="78"/>
-      <c r="AP15" s="78"/>
-      <c r="AQ15" s="78"/>
-      <c r="AR15" s="78"/>
-      <c r="AS15" s="78"/>
-      <c r="AT15" s="78"/>
-      <c r="AU15" s="78"/>
-      <c r="AV15" s="78"/>
-      <c r="AW15" s="78"/>
-      <c r="AX15" s="78"/>
-      <c r="AY15" s="78"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="80"/>
+      <c r="F15" s="80"/>
+      <c r="G15" s="80"/>
+      <c r="H15" s="80"/>
+      <c r="I15" s="80"/>
+      <c r="J15" s="80"/>
+      <c r="K15" s="80"/>
+      <c r="L15" s="80"/>
+      <c r="M15" s="80"/>
+      <c r="N15" s="80"/>
+      <c r="O15" s="80"/>
+      <c r="P15" s="80"/>
+      <c r="Q15" s="80"/>
+      <c r="R15" s="80"/>
+      <c r="S15" s="80"/>
+      <c r="T15" s="80"/>
+      <c r="U15" s="80"/>
+      <c r="V15" s="80"/>
+      <c r="W15" s="80"/>
+      <c r="X15" s="80"/>
+      <c r="Y15" s="80"/>
+      <c r="Z15" s="80"/>
+      <c r="AA15" s="80"/>
+      <c r="AB15" s="80"/>
+      <c r="AC15" s="80"/>
+      <c r="AD15" s="80"/>
+      <c r="AE15" s="80"/>
+      <c r="AF15" s="80"/>
+      <c r="AG15" s="80"/>
+      <c r="AH15" s="80"/>
+      <c r="AI15" s="80"/>
+      <c r="AJ15" s="80"/>
+      <c r="AK15" s="80"/>
+      <c r="AL15" s="80"/>
+      <c r="AM15" s="80"/>
+      <c r="AN15" s="80"/>
+      <c r="AO15" s="80"/>
+      <c r="AP15" s="80"/>
+      <c r="AQ15" s="80"/>
+      <c r="AR15" s="80"/>
+      <c r="AS15" s="80"/>
+      <c r="AT15" s="80"/>
+      <c r="AU15" s="80"/>
+      <c r="AV15" s="80"/>
+      <c r="AW15" s="80"/>
+      <c r="AX15" s="80"/>
+      <c r="AY15" s="80"/>
     </row>
-    <row r="16" ht="72" spans="1:51">
-      <c r="A16" s="84"/>
-      <c r="B16" s="85" t="s">
+    <row r="16" ht="67.5" spans="1:51">
+      <c r="A16" s="86"/>
+      <c r="B16" s="87" t="s">
         <v>218</v>
       </c>
-      <c r="C16" s="87" t="s">
+      <c r="C16" s="89" t="s">
         <v>219</v>
       </c>
-      <c r="D16" s="88" t="s">
+      <c r="D16" s="90" t="s">
         <v>220</v>
       </c>
-      <c r="E16" s="78"/>
-      <c r="F16" s="78"/>
-      <c r="G16" s="78"/>
-      <c r="H16" s="78"/>
-      <c r="I16" s="78"/>
-      <c r="J16" s="78"/>
-      <c r="K16" s="88" t="s">
+      <c r="E16" s="80"/>
+      <c r="F16" s="80"/>
+      <c r="G16" s="80"/>
+      <c r="H16" s="80"/>
+      <c r="I16" s="80"/>
+      <c r="J16" s="80"/>
+      <c r="K16" s="90" t="s">
         <v>221</v>
       </c>
-      <c r="L16" s="78"/>
-      <c r="M16" s="78"/>
-      <c r="N16" s="78"/>
-      <c r="O16" s="78"/>
-      <c r="P16" s="78"/>
-      <c r="Q16" s="78"/>
-      <c r="R16" s="78"/>
-      <c r="S16" s="78"/>
-      <c r="T16" s="78"/>
-      <c r="U16" s="78"/>
-      <c r="V16" s="78"/>
-      <c r="W16" s="78"/>
-      <c r="X16" s="78"/>
-      <c r="Y16" s="78"/>
-      <c r="Z16" s="88" t="s">
+      <c r="L16" s="80"/>
+      <c r="M16" s="80"/>
+      <c r="N16" s="80"/>
+      <c r="O16" s="80"/>
+      <c r="P16" s="80"/>
+      <c r="Q16" s="80"/>
+      <c r="R16" s="80"/>
+      <c r="S16" s="80"/>
+      <c r="T16" s="80"/>
+      <c r="U16" s="80"/>
+      <c r="V16" s="80"/>
+      <c r="W16" s="80"/>
+      <c r="X16" s="80"/>
+      <c r="Y16" s="80"/>
+      <c r="Z16" s="90" t="s">
         <v>222</v>
       </c>
-      <c r="AA16" s="78" t="s">
+      <c r="AA16" s="80" t="s">
         <v>223</v>
       </c>
-      <c r="AB16" s="88" t="s">
+      <c r="AB16" s="90" t="s">
         <v>224</v>
       </c>
-      <c r="AC16" s="78"/>
-      <c r="AD16" s="78"/>
-      <c r="AE16" s="78"/>
-      <c r="AF16" s="78"/>
-      <c r="AG16" s="78"/>
-      <c r="AH16" s="78"/>
-      <c r="AI16" s="78"/>
-      <c r="AJ16" s="78"/>
-      <c r="AK16" s="78"/>
-      <c r="AL16" s="78"/>
-      <c r="AM16" s="88" t="s">
+      <c r="AC16" s="80"/>
+      <c r="AD16" s="80"/>
+      <c r="AE16" s="80"/>
+      <c r="AF16" s="80"/>
+      <c r="AG16" s="80"/>
+      <c r="AH16" s="80"/>
+      <c r="AI16" s="80"/>
+      <c r="AJ16" s="80"/>
+      <c r="AK16" s="80"/>
+      <c r="AL16" s="80"/>
+      <c r="AM16" s="90" t="s">
         <v>225</v>
       </c>
-      <c r="AN16" s="78"/>
-      <c r="AO16" s="78" t="s">
+      <c r="AN16" s="80"/>
+      <c r="AO16" s="80" t="s">
         <v>226</v>
       </c>
-      <c r="AP16" s="78" t="s">
+      <c r="AP16" s="80" t="s">
         <v>226</v>
       </c>
-      <c r="AQ16" s="78"/>
-      <c r="AR16" s="78"/>
-      <c r="AS16" s="78" t="s">
+      <c r="AQ16" s="80"/>
+      <c r="AR16" s="80"/>
+      <c r="AS16" s="80" t="s">
         <v>227</v>
       </c>
-      <c r="AT16" s="78"/>
-      <c r="AU16" s="78"/>
-      <c r="AV16" s="88" t="s">
+      <c r="AT16" s="80"/>
+      <c r="AU16" s="80"/>
+      <c r="AV16" s="90" t="s">
         <v>228</v>
       </c>
-      <c r="AW16" s="78"/>
-      <c r="AX16" s="78"/>
-      <c r="AY16" s="78"/>
+      <c r="AW16" s="80"/>
+      <c r="AX16" s="80"/>
+      <c r="AY16" s="80"/>
     </row>
-    <row r="17" ht="86.4" spans="1:51">
-      <c r="A17" s="84"/>
-      <c r="B17" s="85" t="s">
+    <row r="17" ht="81" spans="1:51">
+      <c r="A17" s="86"/>
+      <c r="B17" s="87" t="s">
         <v>229</v>
       </c>
-      <c r="C17" s="86"/>
-      <c r="D17" s="78"/>
-      <c r="E17" s="78"/>
-      <c r="F17" s="78"/>
-      <c r="G17" s="88" t="s">
+      <c r="C17" s="88"/>
+      <c r="D17" s="80"/>
+      <c r="E17" s="80"/>
+      <c r="F17" s="80"/>
+      <c r="G17" s="90" t="s">
         <v>230</v>
       </c>
-      <c r="H17" s="78"/>
-      <c r="I17" s="88" t="s">
+      <c r="H17" s="80"/>
+      <c r="I17" s="90" t="s">
         <v>231</v>
       </c>
-      <c r="J17" s="78"/>
-      <c r="K17" s="78" t="s">
+      <c r="J17" s="80"/>
+      <c r="K17" s="80" t="s">
         <v>232</v>
       </c>
-      <c r="L17" s="78" t="s">
+      <c r="L17" s="80" t="s">
         <v>233</v>
       </c>
-      <c r="M17" s="78"/>
-      <c r="N17" s="78"/>
-      <c r="O17" s="88" t="s">
+      <c r="M17" s="80"/>
+      <c r="N17" s="80"/>
+      <c r="O17" s="90" t="s">
         <v>234</v>
       </c>
-      <c r="P17" s="78"/>
-      <c r="Q17" s="78"/>
-      <c r="R17" s="78"/>
-      <c r="S17" s="88" t="s">
+      <c r="P17" s="80"/>
+      <c r="Q17" s="80"/>
+      <c r="R17" s="80"/>
+      <c r="S17" s="90" t="s">
         <v>235</v>
       </c>
-      <c r="T17" s="88" t="s">
+      <c r="T17" s="90" t="s">
         <v>236</v>
       </c>
-      <c r="U17" s="88" t="s">
+      <c r="U17" s="90" t="s">
         <v>237</v>
       </c>
-      <c r="V17" s="78"/>
-      <c r="W17" s="88" t="s">
+      <c r="V17" s="80"/>
+      <c r="W17" s="90" t="s">
         <v>238</v>
       </c>
-      <c r="X17" s="78" t="s">
+      <c r="X17" s="80" t="s">
         <v>239</v>
       </c>
-      <c r="Y17" s="88" t="s">
+      <c r="Y17" s="90" t="s">
         <v>240</v>
       </c>
-      <c r="Z17" s="88" t="s">
+      <c r="Z17" s="90" t="s">
         <v>241</v>
       </c>
-      <c r="AA17" s="88" t="s">
+      <c r="AA17" s="90" t="s">
         <v>242</v>
       </c>
-      <c r="AB17" s="88" t="s">
+      <c r="AB17" s="90" t="s">
         <v>243</v>
       </c>
-      <c r="AC17" s="78"/>
-      <c r="AD17" s="78"/>
-      <c r="AE17" s="78"/>
-      <c r="AF17" s="78"/>
-      <c r="AG17" s="78"/>
-      <c r="AH17" s="88" t="s">
+      <c r="AC17" s="80"/>
+      <c r="AD17" s="80"/>
+      <c r="AE17" s="80"/>
+      <c r="AF17" s="80"/>
+      <c r="AG17" s="80"/>
+      <c r="AH17" s="90" t="s">
         <v>244</v>
       </c>
-      <c r="AI17" s="78"/>
-      <c r="AJ17" s="78"/>
-      <c r="AK17" s="78"/>
-      <c r="AL17" s="78" t="s">
+      <c r="AI17" s="80"/>
+      <c r="AJ17" s="80"/>
+      <c r="AK17" s="80"/>
+      <c r="AL17" s="80" t="s">
         <v>245</v>
       </c>
-      <c r="AM17" s="88" t="s">
+      <c r="AM17" s="90" t="s">
         <v>246</v>
       </c>
-      <c r="AN17" s="88" t="s">
+      <c r="AN17" s="90" t="s">
         <v>247</v>
       </c>
-      <c r="AO17" s="88" t="s">
+      <c r="AO17" s="90" t="s">
         <v>248</v>
       </c>
-      <c r="AP17" s="88" t="s">
+      <c r="AP17" s="90" t="s">
         <v>249</v>
       </c>
-      <c r="AQ17" s="78"/>
-      <c r="AR17" s="88" t="s">
+      <c r="AQ17" s="80"/>
+      <c r="AR17" s="90" t="s">
         <v>250</v>
       </c>
-      <c r="AS17" s="78" t="s">
+      <c r="AS17" s="80" t="s">
         <v>251</v>
       </c>
-      <c r="AT17" s="78" t="s">
+      <c r="AT17" s="80" t="s">
         <v>252</v>
       </c>
-      <c r="AU17" s="88" t="s">
+      <c r="AU17" s="90" t="s">
         <v>253</v>
       </c>
-      <c r="AV17" s="88" t="s">
+      <c r="AV17" s="90" t="s">
         <v>254</v>
       </c>
-      <c r="AW17" s="88" t="s">
+      <c r="AW17" s="90" t="s">
         <v>255</v>
       </c>
-      <c r="AX17" s="78"/>
-      <c r="AY17" s="88" t="s">
+      <c r="AX17" s="80"/>
+      <c r="AY17" s="90" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="18" ht="86.4" spans="1:51">
-      <c r="A18" s="84"/>
-      <c r="B18" s="85" t="s">
+    <row r="18" ht="81" spans="1:51">
+      <c r="A18" s="86"/>
+      <c r="B18" s="87" t="s">
         <v>257</v>
       </c>
-      <c r="C18" s="86"/>
-      <c r="D18" s="78"/>
-      <c r="E18" s="78"/>
-      <c r="F18" s="78"/>
-      <c r="G18" s="78"/>
-      <c r="H18" s="78"/>
-      <c r="I18" s="78"/>
-      <c r="J18" s="78"/>
-      <c r="K18" s="88" t="s">
+      <c r="C18" s="88"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="80"/>
+      <c r="F18" s="80"/>
+      <c r="G18" s="80"/>
+      <c r="H18" s="80"/>
+      <c r="I18" s="80"/>
+      <c r="J18" s="80"/>
+      <c r="K18" s="90" t="s">
         <v>258</v>
       </c>
-      <c r="L18" s="78"/>
-      <c r="M18" s="78"/>
-      <c r="N18" s="78"/>
-      <c r="O18" s="78"/>
-      <c r="P18" s="78"/>
-      <c r="Q18" s="78"/>
-      <c r="R18" s="78"/>
-      <c r="S18" s="78"/>
-      <c r="T18" s="78"/>
-      <c r="U18" s="78"/>
-      <c r="V18" s="78"/>
-      <c r="W18" s="78"/>
-      <c r="X18" s="78"/>
-      <c r="Y18" s="78"/>
-      <c r="Z18" s="88" t="s">
+      <c r="L18" s="80"/>
+      <c r="M18" s="80"/>
+      <c r="N18" s="80"/>
+      <c r="O18" s="80"/>
+      <c r="P18" s="80"/>
+      <c r="Q18" s="80"/>
+      <c r="R18" s="80"/>
+      <c r="S18" s="80"/>
+      <c r="T18" s="80"/>
+      <c r="U18" s="80"/>
+      <c r="V18" s="80"/>
+      <c r="W18" s="80"/>
+      <c r="X18" s="80"/>
+      <c r="Y18" s="80"/>
+      <c r="Z18" s="90" t="s">
         <v>259</v>
       </c>
-      <c r="AA18" s="88" t="s">
+      <c r="AA18" s="90" t="s">
         <v>260</v>
       </c>
-      <c r="AB18" s="88" t="s">
+      <c r="AB18" s="90" t="s">
         <v>261</v>
       </c>
-      <c r="AC18" s="88" t="s">
+      <c r="AC18" s="90" t="s">
         <v>262</v>
       </c>
-      <c r="AD18" s="78"/>
-      <c r="AE18" s="78"/>
-      <c r="AF18" s="78"/>
-      <c r="AG18" s="78"/>
-      <c r="AH18" s="78"/>
-      <c r="AI18" s="78" t="s">
+      <c r="AD18" s="80"/>
+      <c r="AE18" s="80"/>
+      <c r="AF18" s="80"/>
+      <c r="AG18" s="80"/>
+      <c r="AH18" s="80"/>
+      <c r="AI18" s="80" t="s">
         <v>263</v>
       </c>
-      <c r="AJ18" s="78"/>
-      <c r="AK18" s="78" t="s">
+      <c r="AJ18" s="80"/>
+      <c r="AK18" s="80" t="s">
         <v>263</v>
       </c>
-      <c r="AL18" s="78"/>
-      <c r="AM18" s="78"/>
-      <c r="AN18" s="88" t="s">
+      <c r="AL18" s="80"/>
+      <c r="AM18" s="80"/>
+      <c r="AN18" s="90" t="s">
         <v>264</v>
       </c>
-      <c r="AO18" s="78"/>
-      <c r="AP18" s="78"/>
-      <c r="AQ18" s="78"/>
-      <c r="AR18" s="78"/>
-      <c r="AS18" s="78"/>
-      <c r="AT18" s="78"/>
-      <c r="AU18" s="78"/>
-      <c r="AV18" s="88" t="s">
+      <c r="AO18" s="80"/>
+      <c r="AP18" s="80"/>
+      <c r="AQ18" s="80"/>
+      <c r="AR18" s="80"/>
+      <c r="AS18" s="80"/>
+      <c r="AT18" s="80"/>
+      <c r="AU18" s="80"/>
+      <c r="AV18" s="90" t="s">
         <v>265</v>
       </c>
-      <c r="AW18" s="88" t="s">
+      <c r="AW18" s="90" t="s">
         <v>266</v>
       </c>
-      <c r="AX18" s="78"/>
-      <c r="AY18" s="88" t="s">
+      <c r="AX18" s="80"/>
+      <c r="AY18" s="90" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="19" ht="43.2" spans="1:51">
-      <c r="A19" s="84"/>
-      <c r="B19" s="85" t="s">
+    <row r="19" ht="40.5" spans="1:51">
+      <c r="A19" s="86"/>
+      <c r="B19" s="87" t="s">
         <v>267</v>
       </c>
-      <c r="C19" s="86"/>
-      <c r="D19" s="78"/>
-      <c r="E19" s="78"/>
-      <c r="F19" s="78"/>
-      <c r="G19" s="78"/>
-      <c r="H19" s="88" t="s">
+      <c r="C19" s="88"/>
+      <c r="D19" s="80"/>
+      <c r="E19" s="80"/>
+      <c r="F19" s="80"/>
+      <c r="G19" s="80"/>
+      <c r="H19" s="90" t="s">
         <v>268</v>
       </c>
-      <c r="I19" s="78"/>
-      <c r="J19" s="78"/>
-      <c r="K19" s="88" t="s">
+      <c r="I19" s="80"/>
+      <c r="J19" s="80"/>
+      <c r="K19" s="90" t="s">
         <v>268</v>
       </c>
-      <c r="L19" s="78" t="s">
+      <c r="L19" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="M19" s="78"/>
-      <c r="N19" s="78"/>
-      <c r="O19" s="78"/>
-      <c r="P19" s="78"/>
-      <c r="Q19" s="78"/>
-      <c r="R19" s="78"/>
-      <c r="S19" s="78"/>
-      <c r="T19" s="78"/>
-      <c r="U19" s="78"/>
-      <c r="V19" s="78"/>
-      <c r="W19" s="78"/>
-      <c r="X19" s="78"/>
-      <c r="Y19" s="78"/>
-      <c r="Z19" s="78"/>
-      <c r="AA19" s="78"/>
-      <c r="AB19" s="78"/>
-      <c r="AC19" s="78"/>
-      <c r="AD19" s="78"/>
-      <c r="AE19" s="78" t="s">
+      <c r="M19" s="80"/>
+      <c r="N19" s="80"/>
+      <c r="O19" s="80"/>
+      <c r="P19" s="80"/>
+      <c r="Q19" s="80"/>
+      <c r="R19" s="80"/>
+      <c r="S19" s="80"/>
+      <c r="T19" s="80"/>
+      <c r="U19" s="80"/>
+      <c r="V19" s="80"/>
+      <c r="W19" s="80"/>
+      <c r="X19" s="80"/>
+      <c r="Y19" s="80"/>
+      <c r="Z19" s="80"/>
+      <c r="AA19" s="80"/>
+      <c r="AB19" s="80"/>
+      <c r="AC19" s="80"/>
+      <c r="AD19" s="80"/>
+      <c r="AE19" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="AF19" s="78"/>
-      <c r="AG19" s="78"/>
-      <c r="AH19" s="78"/>
-      <c r="AI19" s="78"/>
-      <c r="AJ19" s="78"/>
-      <c r="AK19" s="78"/>
-      <c r="AL19" s="78"/>
-      <c r="AM19" s="78"/>
-      <c r="AN19" s="78"/>
-      <c r="AO19" s="78"/>
-      <c r="AP19" s="78" t="s">
+      <c r="AF19" s="80"/>
+      <c r="AG19" s="80"/>
+      <c r="AH19" s="80"/>
+      <c r="AI19" s="80"/>
+      <c r="AJ19" s="80"/>
+      <c r="AK19" s="80"/>
+      <c r="AL19" s="80"/>
+      <c r="AM19" s="80"/>
+      <c r="AN19" s="80"/>
+      <c r="AO19" s="80"/>
+      <c r="AP19" s="80" t="s">
         <v>269</v>
       </c>
-      <c r="AQ19" s="78"/>
-      <c r="AR19" s="78"/>
-      <c r="AS19" s="78"/>
-      <c r="AT19" s="78"/>
-      <c r="AU19" s="78"/>
-      <c r="AV19" s="88"/>
-      <c r="AW19" s="88"/>
-      <c r="AX19" s="78"/>
-      <c r="AY19" s="88" t="s">
+      <c r="AQ19" s="80"/>
+      <c r="AR19" s="80"/>
+      <c r="AS19" s="80"/>
+      <c r="AT19" s="80"/>
+      <c r="AU19" s="80"/>
+      <c r="AV19" s="90"/>
+      <c r="AW19" s="90"/>
+      <c r="AX19" s="80"/>
+      <c r="AY19" s="90" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="20" ht="57.6" spans="1:51">
-      <c r="A20" s="84"/>
-      <c r="B20" s="85" t="s">
+    <row r="20" ht="54" spans="1:51">
+      <c r="A20" s="86"/>
+      <c r="B20" s="87" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="86"/>
-      <c r="D20" s="78"/>
-      <c r="E20" s="78"/>
-      <c r="F20" s="78"/>
-      <c r="G20" s="78"/>
-      <c r="H20" s="78"/>
-      <c r="I20" s="78"/>
-      <c r="J20" s="78"/>
-      <c r="K20" s="78"/>
-      <c r="L20" s="78"/>
-      <c r="M20" s="78"/>
-      <c r="N20" s="78"/>
-      <c r="O20" s="78"/>
-      <c r="P20" s="78"/>
-      <c r="Q20" s="78"/>
-      <c r="R20" s="78"/>
-      <c r="S20" s="78"/>
-      <c r="T20" s="78"/>
-      <c r="U20" s="78"/>
-      <c r="V20" s="78"/>
-      <c r="W20" s="78"/>
-      <c r="X20" s="78"/>
-      <c r="Y20" s="78"/>
-      <c r="Z20" s="78"/>
-      <c r="AA20" s="78"/>
-      <c r="AB20" s="78"/>
-      <c r="AC20" s="78"/>
-      <c r="AD20" s="78"/>
-      <c r="AE20" s="78"/>
-      <c r="AF20" s="78"/>
-      <c r="AG20" s="78"/>
-      <c r="AH20" s="78"/>
-      <c r="AI20" s="78"/>
-      <c r="AJ20" s="88" t="s">
+      <c r="C20" s="88"/>
+      <c r="D20" s="80"/>
+      <c r="E20" s="80"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="80"/>
+      <c r="K20" s="80"/>
+      <c r="L20" s="80"/>
+      <c r="M20" s="80"/>
+      <c r="N20" s="80"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="80"/>
+      <c r="R20" s="80"/>
+      <c r="S20" s="80"/>
+      <c r="T20" s="80"/>
+      <c r="U20" s="80"/>
+      <c r="V20" s="80"/>
+      <c r="W20" s="80"/>
+      <c r="X20" s="80"/>
+      <c r="Y20" s="80"/>
+      <c r="Z20" s="80"/>
+      <c r="AA20" s="80"/>
+      <c r="AB20" s="80"/>
+      <c r="AC20" s="80"/>
+      <c r="AD20" s="80"/>
+      <c r="AE20" s="80"/>
+      <c r="AF20" s="80"/>
+      <c r="AG20" s="80"/>
+      <c r="AH20" s="80"/>
+      <c r="AI20" s="80"/>
+      <c r="AJ20" s="90" t="s">
         <v>272</v>
       </c>
-      <c r="AK20" s="78"/>
-      <c r="AL20" s="78"/>
-      <c r="AM20" s="78"/>
-      <c r="AN20" s="78"/>
-      <c r="AO20" s="78"/>
-      <c r="AP20" s="78"/>
-      <c r="AQ20" s="78"/>
-      <c r="AR20" s="78"/>
-      <c r="AS20" s="78"/>
-      <c r="AT20" s="78"/>
-      <c r="AU20" s="78"/>
-      <c r="AV20" s="88"/>
-      <c r="AW20" s="88"/>
-      <c r="AX20" s="78"/>
-      <c r="AY20" s="78"/>
+      <c r="AK20" s="80"/>
+      <c r="AL20" s="80"/>
+      <c r="AM20" s="80"/>
+      <c r="AN20" s="80"/>
+      <c r="AO20" s="80"/>
+      <c r="AP20" s="80"/>
+      <c r="AQ20" s="80"/>
+      <c r="AR20" s="80"/>
+      <c r="AS20" s="80"/>
+      <c r="AT20" s="80"/>
+      <c r="AU20" s="80"/>
+      <c r="AV20" s="90"/>
+      <c r="AW20" s="90"/>
+      <c r="AX20" s="80"/>
+      <c r="AY20" s="80"/>
     </row>
-    <row r="21" ht="86.4" spans="1:51">
-      <c r="A21" s="84"/>
-      <c r="B21" s="89" t="s">
+    <row r="21" ht="81" spans="1:51">
+      <c r="A21" s="86"/>
+      <c r="B21" s="91" t="s">
         <v>273</v>
       </c>
-      <c r="C21" s="87" t="s">
+      <c r="C21" s="89" t="s">
         <v>274</v>
       </c>
-      <c r="D21" s="87" t="s">
+      <c r="D21" s="89" t="s">
         <v>274</v>
       </c>
-      <c r="E21" s="78"/>
-      <c r="F21" s="78"/>
-      <c r="G21" s="78"/>
-      <c r="H21" s="78"/>
-      <c r="I21" s="78"/>
-      <c r="J21" s="78"/>
-      <c r="K21" s="88" t="s">
+      <c r="E21" s="80"/>
+      <c r="F21" s="80"/>
+      <c r="G21" s="80"/>
+      <c r="H21" s="80"/>
+      <c r="I21" s="80"/>
+      <c r="J21" s="80"/>
+      <c r="K21" s="90" t="s">
         <v>275</v>
       </c>
-      <c r="L21" s="78" t="s">
+      <c r="L21" s="80" t="s">
         <v>276</v>
       </c>
-      <c r="M21" s="78"/>
-      <c r="N21" s="78"/>
-      <c r="O21" s="78"/>
-      <c r="P21" s="78"/>
-      <c r="Q21" s="78"/>
-      <c r="R21" s="78"/>
-      <c r="S21" s="78"/>
-      <c r="T21" s="78"/>
-      <c r="U21" s="78"/>
-      <c r="V21" s="78"/>
-      <c r="W21" s="78"/>
-      <c r="X21" s="78"/>
-      <c r="Y21" s="78"/>
-      <c r="Z21" s="78"/>
-      <c r="AA21" s="78"/>
-      <c r="AB21" s="78"/>
-      <c r="AC21" s="78"/>
-      <c r="AD21" s="78"/>
-      <c r="AE21" s="78" t="s">
+      <c r="M21" s="80"/>
+      <c r="N21" s="80"/>
+      <c r="O21" s="80"/>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="80"/>
+      <c r="R21" s="80"/>
+      <c r="S21" s="80"/>
+      <c r="T21" s="80"/>
+      <c r="U21" s="80"/>
+      <c r="V21" s="80"/>
+      <c r="W21" s="80"/>
+      <c r="X21" s="80"/>
+      <c r="Y21" s="80"/>
+      <c r="Z21" s="80"/>
+      <c r="AA21" s="80"/>
+      <c r="AB21" s="80"/>
+      <c r="AC21" s="80"/>
+      <c r="AD21" s="80"/>
+      <c r="AE21" s="80" t="s">
         <v>277</v>
       </c>
-      <c r="AF21" s="88" t="s">
+      <c r="AF21" s="90" t="s">
         <v>278</v>
       </c>
-      <c r="AG21" s="88" t="s">
+      <c r="AG21" s="90" t="s">
         <v>279</v>
       </c>
-      <c r="AH21" s="78"/>
-      <c r="AI21" s="88" t="s">
+      <c r="AH21" s="80"/>
+      <c r="AI21" s="90" t="s">
         <v>280</v>
       </c>
-      <c r="AJ21" s="88" t="s">
+      <c r="AJ21" s="90" t="s">
         <v>281</v>
       </c>
-      <c r="AK21" s="78"/>
-      <c r="AL21" s="78"/>
-      <c r="AM21" s="78"/>
-      <c r="AN21" s="78"/>
-      <c r="AO21" s="78" t="s">
+      <c r="AK21" s="80"/>
+      <c r="AL21" s="80"/>
+      <c r="AM21" s="80"/>
+      <c r="AN21" s="80"/>
+      <c r="AO21" s="80" t="s">
         <v>276</v>
       </c>
-      <c r="AP21" s="78" t="s">
+      <c r="AP21" s="80" t="s">
         <v>276</v>
       </c>
-      <c r="AQ21" s="78"/>
-      <c r="AR21" s="78"/>
-      <c r="AS21" s="78"/>
-      <c r="AT21" s="78" t="s">
+      <c r="AQ21" s="80"/>
+      <c r="AR21" s="80"/>
+      <c r="AS21" s="80"/>
+      <c r="AT21" s="80" t="s">
         <v>277</v>
       </c>
-      <c r="AU21" s="78"/>
-      <c r="AV21" s="78"/>
-      <c r="AW21" s="78"/>
-      <c r="AX21" s="88" t="s">
+      <c r="AU21" s="80"/>
+      <c r="AV21" s="80"/>
+      <c r="AW21" s="80"/>
+      <c r="AX21" s="90" t="s">
         <v>282</v>
       </c>
-      <c r="AY21" s="88" t="s">
+      <c r="AY21" s="90" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:51">
-      <c r="A22" s="90"/>
-      <c r="B22" s="85" t="s">
+      <c r="A22" s="92"/>
+      <c r="B22" s="87" t="s">
         <v>284</v>
       </c>
-      <c r="C22" s="86"/>
-      <c r="D22" s="78"/>
-      <c r="E22" s="78"/>
-      <c r="F22" s="78"/>
-      <c r="G22" s="78"/>
-      <c r="H22" s="78"/>
-      <c r="I22" s="78"/>
-      <c r="J22" s="78"/>
-      <c r="K22" s="78"/>
-      <c r="L22" s="78"/>
-      <c r="M22" s="78"/>
-      <c r="N22" s="78"/>
-      <c r="O22" s="78"/>
-      <c r="P22" s="78"/>
-      <c r="Q22" s="78"/>
-      <c r="R22" s="78"/>
-      <c r="S22" s="78"/>
-      <c r="T22" s="78"/>
-      <c r="U22" s="78"/>
-      <c r="V22" s="78"/>
-      <c r="W22" s="78"/>
-      <c r="X22" s="78"/>
-      <c r="Y22" s="78"/>
-      <c r="Z22" s="78"/>
-      <c r="AA22" s="78"/>
-      <c r="AB22" s="78"/>
-      <c r="AC22" s="78"/>
-      <c r="AD22" s="78"/>
-      <c r="AE22" s="78"/>
-      <c r="AF22" s="78"/>
-      <c r="AG22" s="78"/>
-      <c r="AH22" s="78"/>
-      <c r="AI22" s="78"/>
-      <c r="AJ22" s="78"/>
-      <c r="AK22" s="78"/>
-      <c r="AL22" s="78"/>
-      <c r="AM22" s="78"/>
-      <c r="AN22" s="78"/>
-      <c r="AO22" s="78"/>
-      <c r="AP22" s="78"/>
-      <c r="AQ22" s="78"/>
-      <c r="AR22" s="78"/>
-      <c r="AS22" s="78"/>
-      <c r="AT22" s="78"/>
-      <c r="AU22" s="78"/>
-      <c r="AV22" s="88"/>
-      <c r="AW22" s="88"/>
-      <c r="AX22" s="78"/>
-      <c r="AY22" s="78"/>
+      <c r="C22" s="88"/>
+      <c r="D22" s="80"/>
+      <c r="E22" s="80"/>
+      <c r="F22" s="80"/>
+      <c r="G22" s="80"/>
+      <c r="H22" s="80"/>
+      <c r="I22" s="80"/>
+      <c r="J22" s="80"/>
+      <c r="K22" s="80"/>
+      <c r="L22" s="80"/>
+      <c r="M22" s="80"/>
+      <c r="N22" s="80"/>
+      <c r="O22" s="80"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="80"/>
+      <c r="R22" s="80"/>
+      <c r="S22" s="80"/>
+      <c r="T22" s="80"/>
+      <c r="U22" s="80"/>
+      <c r="V22" s="80"/>
+      <c r="W22" s="80"/>
+      <c r="X22" s="80"/>
+      <c r="Y22" s="80"/>
+      <c r="Z22" s="80"/>
+      <c r="AA22" s="80"/>
+      <c r="AB22" s="80"/>
+      <c r="AC22" s="80"/>
+      <c r="AD22" s="80"/>
+      <c r="AE22" s="80"/>
+      <c r="AF22" s="80"/>
+      <c r="AG22" s="80"/>
+      <c r="AH22" s="80"/>
+      <c r="AI22" s="80"/>
+      <c r="AJ22" s="80"/>
+      <c r="AK22" s="80"/>
+      <c r="AL22" s="80"/>
+      <c r="AM22" s="80"/>
+      <c r="AN22" s="80"/>
+      <c r="AO22" s="80"/>
+      <c r="AP22" s="80"/>
+      <c r="AQ22" s="80"/>
+      <c r="AR22" s="80"/>
+      <c r="AS22" s="80"/>
+      <c r="AT22" s="80"/>
+      <c r="AU22" s="80"/>
+      <c r="AV22" s="90"/>
+      <c r="AW22" s="90"/>
+      <c r="AX22" s="80"/>
+      <c r="AY22" s="80"/>
     </row>
-    <row r="24" ht="115.2" spans="1:51">
-      <c r="A24" s="68" t="s">
+    <row r="24" ht="108" spans="1:51">
+      <c r="A24" s="70" t="s">
         <v>285</v>
       </c>
-      <c r="B24" s="25" t="s">
+      <c r="B24" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="C24" s="73" t="s">
+      <c r="C24" s="75" t="s">
         <v>287</v>
       </c>
-      <c r="D24" s="73" t="s">
+      <c r="D24" s="75" t="s">
         <v>170</v>
       </c>
-      <c r="E24" s="73" t="s">
+      <c r="E24" s="75" t="s">
         <v>288</v>
       </c>
-      <c r="F24" s="73" t="s">
+      <c r="F24" s="75" t="s">
         <v>289</v>
       </c>
-      <c r="G24" s="73" t="s">
+      <c r="G24" s="75" t="s">
         <v>290</v>
       </c>
-      <c r="H24" s="73" t="s">
+      <c r="H24" s="75" t="s">
         <v>291</v>
       </c>
-      <c r="I24" s="73" t="s">
+      <c r="I24" s="75" t="s">
         <v>292</v>
       </c>
-      <c r="J24" s="73" t="s">
+      <c r="J24" s="75" t="s">
         <v>293</v>
       </c>
-      <c r="K24" s="73" t="s">
+      <c r="K24" s="75" t="s">
         <v>294</v>
       </c>
-      <c r="L24" s="73" t="s">
+      <c r="L24" s="75" t="s">
         <v>295</v>
       </c>
-      <c r="M24" s="73" t="s">
+      <c r="M24" s="75" t="s">
         <v>296</v>
       </c>
-      <c r="N24" s="73" t="s">
+      <c r="N24" s="75" t="s">
         <v>297</v>
       </c>
-      <c r="O24" s="73" t="s">
+      <c r="O24" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="P24" s="73" t="s">
+      <c r="P24" s="75" t="s">
         <v>298</v>
       </c>
-      <c r="Q24" s="73" t="s">
+      <c r="Q24" s="75" t="s">
         <v>299</v>
       </c>
-      <c r="R24" s="73" t="s">
+      <c r="R24" s="75" t="s">
         <v>300</v>
       </c>
-      <c r="S24" s="73" t="s">
+      <c r="S24" s="75" t="s">
         <v>301</v>
       </c>
-      <c r="T24" s="73" t="s">
+      <c r="T24" s="75" t="s">
         <v>302</v>
       </c>
-      <c r="U24" s="73" t="s">
+      <c r="U24" s="75" t="s">
         <v>303</v>
       </c>
-      <c r="V24" s="73" t="s">
+      <c r="V24" s="75" t="s">
         <v>304</v>
       </c>
-      <c r="W24" s="73" t="s">
+      <c r="W24" s="75" t="s">
         <v>305</v>
       </c>
-      <c r="X24" s="73" t="s">
+      <c r="X24" s="75" t="s">
         <v>306</v>
       </c>
-      <c r="Y24" s="73" t="s">
+      <c r="Y24" s="75" t="s">
         <v>307</v>
       </c>
-      <c r="Z24" s="73" t="s">
+      <c r="Z24" s="75" t="s">
         <v>308</v>
       </c>
-      <c r="AA24" s="73" t="s">
+      <c r="AA24" s="75" t="s">
         <v>309</v>
       </c>
-      <c r="AB24" s="73" t="s">
+      <c r="AB24" s="75" t="s">
         <v>310</v>
       </c>
-      <c r="AC24" s="73" t="s">
+      <c r="AC24" s="75" t="s">
         <v>311</v>
       </c>
-      <c r="AD24" s="73" t="s">
+      <c r="AD24" s="75" t="s">
         <v>312</v>
       </c>
-      <c r="AE24" s="73" t="s">
+      <c r="AE24" s="75" t="s">
         <v>313</v>
       </c>
-      <c r="AF24" s="73" t="s">
+      <c r="AF24" s="75" t="s">
         <v>314</v>
       </c>
-      <c r="AG24" s="73" t="s">
+      <c r="AG24" s="75" t="s">
         <v>315</v>
       </c>
-      <c r="AH24" s="73" t="s">
+      <c r="AH24" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AI24" s="73" t="s">
+      <c r="AI24" s="75" t="s">
         <v>316</v>
       </c>
-      <c r="AJ24" s="73" t="s">
+      <c r="AJ24" s="75" t="s">
         <v>317</v>
       </c>
-      <c r="AK24" s="73" t="s">
+      <c r="AK24" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AL24" s="73" t="s">
+      <c r="AL24" s="75" t="s">
         <v>318</v>
       </c>
-      <c r="AM24" s="73" t="s">
+      <c r="AM24" s="75" t="s">
         <v>319</v>
       </c>
-      <c r="AN24" s="73" t="s">
+      <c r="AN24" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AO24" s="73" t="s">
+      <c r="AO24" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AP24" s="73" t="s">
+      <c r="AP24" s="75" t="s">
         <v>315</v>
       </c>
-      <c r="AQ24" s="73" t="s">
+      <c r="AQ24" s="75" t="s">
         <v>315</v>
       </c>
-      <c r="AR24" s="73" t="s">
+      <c r="AR24" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AS24" s="73" t="s">
+      <c r="AS24" s="75" t="s">
         <v>320</v>
       </c>
-      <c r="AT24" s="73" t="s">
+      <c r="AT24" s="75" t="s">
         <v>321</v>
       </c>
-      <c r="AU24" s="73" t="s">
+      <c r="AU24" s="75" t="s">
         <v>322</v>
       </c>
-      <c r="AV24" s="73" t="s">
+      <c r="AV24" s="75" t="s">
         <v>323</v>
       </c>
-      <c r="AW24" s="74" t="s">
+      <c r="AW24" s="76" t="s">
         <v>324</v>
       </c>
-      <c r="AX24" s="74" t="s">
+      <c r="AX24" s="76" t="s">
         <v>315</v>
       </c>
-      <c r="AY24" s="74" t="s">
+      <c r="AY24" s="76" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:51">
-      <c r="A25" s="70"/>
-      <c r="B25" s="25" t="s">
+      <c r="A25" s="72"/>
+      <c r="B25" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="C25" s="73"/>
-      <c r="D25" s="73"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="73"/>
-      <c r="J25" s="73"/>
-      <c r="K25" s="73"/>
-      <c r="L25" s="73"/>
-      <c r="M25" s="73"/>
-      <c r="N25" s="73"/>
-      <c r="O25" s="73"/>
-      <c r="P25" s="73"/>
-      <c r="Q25" s="73"/>
-      <c r="R25" s="73"/>
-      <c r="S25" s="73"/>
-      <c r="T25" s="73"/>
-      <c r="U25" s="73"/>
-      <c r="V25" s="73"/>
-      <c r="W25" s="73"/>
-      <c r="X25" s="73"/>
-      <c r="Y25" s="73"/>
-      <c r="Z25" s="73"/>
-      <c r="AA25" s="73"/>
-      <c r="AB25" s="73"/>
-      <c r="AC25" s="73"/>
-      <c r="AD25" s="73"/>
-      <c r="AE25" s="73"/>
-      <c r="AF25" s="73"/>
-      <c r="AG25" s="73"/>
-      <c r="AH25" s="73"/>
-      <c r="AI25" s="73"/>
-      <c r="AJ25" s="73"/>
-      <c r="AK25" s="73"/>
-      <c r="AL25" s="73"/>
-      <c r="AM25" s="73"/>
-      <c r="AN25" s="73"/>
-      <c r="AO25" s="73"/>
-      <c r="AP25" s="73"/>
-      <c r="AQ25" s="73"/>
-      <c r="AR25" s="73"/>
-      <c r="AS25" s="73"/>
-      <c r="AT25" s="73"/>
-      <c r="AU25" s="73"/>
-      <c r="AV25" s="73"/>
-      <c r="AW25" s="74"/>
-      <c r="AX25" s="74"/>
-      <c r="AY25" s="74"/>
+      <c r="C25" s="75"/>
+      <c r="D25" s="75"/>
+      <c r="E25" s="75"/>
+      <c r="F25" s="75"/>
+      <c r="G25" s="75"/>
+      <c r="H25" s="75"/>
+      <c r="I25" s="75"/>
+      <c r="J25" s="75"/>
+      <c r="K25" s="75"/>
+      <c r="L25" s="75"/>
+      <c r="M25" s="75"/>
+      <c r="N25" s="75"/>
+      <c r="O25" s="75"/>
+      <c r="P25" s="75"/>
+      <c r="Q25" s="75"/>
+      <c r="R25" s="75"/>
+      <c r="S25" s="75"/>
+      <c r="T25" s="75"/>
+      <c r="U25" s="75"/>
+      <c r="V25" s="75"/>
+      <c r="W25" s="75"/>
+      <c r="X25" s="75"/>
+      <c r="Y25" s="75"/>
+      <c r="Z25" s="75"/>
+      <c r="AA25" s="75"/>
+      <c r="AB25" s="75"/>
+      <c r="AC25" s="75"/>
+      <c r="AD25" s="75"/>
+      <c r="AE25" s="75"/>
+      <c r="AF25" s="75"/>
+      <c r="AG25" s="75"/>
+      <c r="AH25" s="75"/>
+      <c r="AI25" s="75"/>
+      <c r="AJ25" s="75"/>
+      <c r="AK25" s="75"/>
+      <c r="AL25" s="75"/>
+      <c r="AM25" s="75"/>
+      <c r="AN25" s="75"/>
+      <c r="AO25" s="75"/>
+      <c r="AP25" s="75"/>
+      <c r="AQ25" s="75"/>
+      <c r="AR25" s="75"/>
+      <c r="AS25" s="75"/>
+      <c r="AT25" s="75"/>
+      <c r="AU25" s="75"/>
+      <c r="AV25" s="75"/>
+      <c r="AW25" s="76"/>
+      <c r="AX25" s="76"/>
+      <c r="AY25" s="76"/>
     </row>
-    <row r="26" customFormat="1" ht="100.8" spans="1:51">
-      <c r="A26" s="75"/>
-      <c r="B26" s="25" t="s">
+    <row r="26" customFormat="1" ht="94.5" spans="1:51">
+      <c r="A26" s="77"/>
+      <c r="B26" s="26" t="s">
         <v>326</v>
       </c>
-      <c r="C26" s="73"/>
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="73" t="s">
+      <c r="C26" s="75"/>
+      <c r="D26" s="75"/>
+      <c r="E26" s="75"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="75" t="s">
         <v>327</v>
       </c>
-      <c r="H26" s="73"/>
-      <c r="I26" s="73"/>
-      <c r="J26" s="73"/>
-      <c r="K26" s="73"/>
-      <c r="L26" s="73"/>
-      <c r="M26" s="73" t="s">
+      <c r="H26" s="75"/>
+      <c r="I26" s="75"/>
+      <c r="J26" s="75"/>
+      <c r="K26" s="75"/>
+      <c r="L26" s="75"/>
+      <c r="M26" s="75" t="s">
         <v>328</v>
       </c>
-      <c r="N26" s="73" t="s">
+      <c r="N26" s="75" t="s">
         <v>329</v>
       </c>
-      <c r="O26" s="73"/>
-      <c r="P26" s="73"/>
-      <c r="Q26" s="73"/>
-      <c r="R26" s="73"/>
-      <c r="S26" s="73"/>
-      <c r="T26" s="73"/>
-      <c r="U26" s="73"/>
-      <c r="V26" s="73"/>
-      <c r="W26" s="73"/>
-      <c r="X26" s="73"/>
-      <c r="Y26" s="73"/>
-      <c r="Z26" s="73"/>
-      <c r="AA26" s="73"/>
-      <c r="AB26" s="73"/>
-      <c r="AC26" s="73"/>
-      <c r="AD26" s="73"/>
-      <c r="AE26" s="73"/>
-      <c r="AF26" s="73"/>
-      <c r="AG26" s="73"/>
-      <c r="AH26" s="73"/>
-      <c r="AI26" s="73"/>
-      <c r="AJ26" s="73"/>
-      <c r="AK26" s="73"/>
-      <c r="AL26" s="73"/>
-      <c r="AM26" s="73"/>
-      <c r="AN26" s="73"/>
-      <c r="AO26" s="73" t="s">
+      <c r="O26" s="75"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="75"/>
+      <c r="R26" s="75"/>
+      <c r="S26" s="75"/>
+      <c r="T26" s="75"/>
+      <c r="U26" s="75"/>
+      <c r="V26" s="75"/>
+      <c r="W26" s="75"/>
+      <c r="X26" s="75"/>
+      <c r="Y26" s="75"/>
+      <c r="Z26" s="75"/>
+      <c r="AA26" s="75"/>
+      <c r="AB26" s="75"/>
+      <c r="AC26" s="75"/>
+      <c r="AD26" s="75"/>
+      <c r="AE26" s="75"/>
+      <c r="AF26" s="75"/>
+      <c r="AG26" s="75"/>
+      <c r="AH26" s="75"/>
+      <c r="AI26" s="75"/>
+      <c r="AJ26" s="75"/>
+      <c r="AK26" s="75"/>
+      <c r="AL26" s="75"/>
+      <c r="AM26" s="75"/>
+      <c r="AN26" s="75"/>
+      <c r="AO26" s="75" t="s">
         <v>330</v>
       </c>
-      <c r="AP26" s="73" t="s">
+      <c r="AP26" s="75" t="s">
         <v>331</v>
       </c>
-      <c r="AQ26" s="73"/>
-      <c r="AR26" s="73"/>
-      <c r="AS26" s="73"/>
-      <c r="AT26" s="73"/>
-      <c r="AU26" s="73"/>
-      <c r="AV26" s="73"/>
-      <c r="AW26" s="74"/>
-      <c r="AX26" s="74"/>
-      <c r="AY26" s="74"/>
+      <c r="AQ26" s="75"/>
+      <c r="AR26" s="75"/>
+      <c r="AS26" s="75"/>
+      <c r="AT26" s="75"/>
+      <c r="AU26" s="75"/>
+      <c r="AV26" s="75"/>
+      <c r="AW26" s="76"/>
+      <c r="AX26" s="76"/>
+      <c r="AY26" s="76"/>
     </row>
-    <row r="27" s="52" customFormat="1" ht="28.8" spans="1:51">
-      <c r="A27" s="76" t="s">
+    <row r="27" s="54" customFormat="1" ht="27" spans="1:51">
+      <c r="A27" s="78" t="s">
         <v>332</v>
       </c>
-      <c r="B27" s="88" t="s">
+      <c r="B27" s="90" t="s">
         <v>333</v>
       </c>
-      <c r="C27" s="91"/>
-      <c r="D27" s="91"/>
-      <c r="E27" s="91"/>
-      <c r="F27" s="91"/>
-      <c r="G27" s="91"/>
-      <c r="H27" s="91"/>
-      <c r="I27" s="91"/>
-      <c r="J27" s="91"/>
-      <c r="K27" s="91"/>
-      <c r="L27" s="91"/>
-      <c r="M27" s="91"/>
-      <c r="N27" s="91"/>
-      <c r="O27" s="91"/>
-      <c r="P27" s="91"/>
-      <c r="Q27" s="91"/>
-      <c r="R27" s="91"/>
-      <c r="S27" s="91"/>
-      <c r="T27" s="91"/>
-      <c r="U27" s="91"/>
-      <c r="V27" s="91"/>
-      <c r="W27" s="91"/>
-      <c r="X27" s="91"/>
-      <c r="Y27" s="91"/>
-      <c r="Z27" s="91"/>
-      <c r="AA27" s="91"/>
-      <c r="AB27" s="91"/>
-      <c r="AC27" s="91"/>
-      <c r="AD27" s="91"/>
-      <c r="AE27" s="91"/>
-      <c r="AF27" s="91"/>
-      <c r="AG27" s="91"/>
-      <c r="AH27" s="91"/>
-      <c r="AI27" s="91"/>
-      <c r="AJ27" s="91"/>
-      <c r="AK27" s="91"/>
-      <c r="AL27" s="91"/>
-      <c r="AM27" s="91"/>
-      <c r="AN27" s="91"/>
-      <c r="AO27" s="91"/>
-      <c r="AP27" s="91"/>
-      <c r="AQ27" s="91"/>
-      <c r="AR27" s="91"/>
+      <c r="C27" s="93"/>
+      <c r="D27" s="93"/>
+      <c r="E27" s="93"/>
+      <c r="F27" s="93"/>
+      <c r="G27" s="93"/>
+      <c r="H27" s="93"/>
+      <c r="I27" s="93"/>
+      <c r="J27" s="93"/>
+      <c r="K27" s="93"/>
+      <c r="L27" s="93"/>
+      <c r="M27" s="93"/>
+      <c r="N27" s="93"/>
+      <c r="O27" s="93"/>
+      <c r="P27" s="93"/>
+      <c r="Q27" s="93"/>
+      <c r="R27" s="93"/>
+      <c r="S27" s="93"/>
+      <c r="T27" s="93"/>
+      <c r="U27" s="93"/>
+      <c r="V27" s="93"/>
+      <c r="W27" s="93"/>
+      <c r="X27" s="93"/>
+      <c r="Y27" s="93"/>
+      <c r="Z27" s="93"/>
+      <c r="AA27" s="93"/>
+      <c r="AB27" s="93"/>
+      <c r="AC27" s="93"/>
+      <c r="AD27" s="93"/>
+      <c r="AE27" s="93"/>
+      <c r="AF27" s="93"/>
+      <c r="AG27" s="93"/>
+      <c r="AH27" s="93"/>
+      <c r="AI27" s="93"/>
+      <c r="AJ27" s="93"/>
+      <c r="AK27" s="93"/>
+      <c r="AL27" s="93"/>
+      <c r="AM27" s="93"/>
+      <c r="AN27" s="93"/>
+      <c r="AO27" s="93"/>
+      <c r="AP27" s="93"/>
+      <c r="AQ27" s="93"/>
+      <c r="AR27" s="93"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -8367,2108 +8480,2108 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:X52"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="13.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="13.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="14.8888888888889" customWidth="1"/>
-    <col min="8" max="8" width="13.1111111111111" customWidth="1"/>
-    <col min="9" max="9" width="13.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="14.8916666666667" customWidth="1"/>
+    <col min="8" max="8" width="13.1083333333333" customWidth="1"/>
+    <col min="9" max="9" width="13.225" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="9.77777777777778" customWidth="1"/>
-    <col min="12" max="12" width="4.77777777777778" customWidth="1"/>
+    <col min="11" max="11" width="9.775" customWidth="1"/>
+    <col min="12" max="12" width="4.775" customWidth="1"/>
     <col min="13" max="13" width="5.66666666666667" customWidth="1"/>
     <col min="15" max="15" width="9.66666666666667" customWidth="1"/>
     <col min="16" max="16" width="14.3333333333333" customWidth="1"/>
     <col min="17" max="17" width="9.66666666666667" customWidth="1"/>
-    <col min="19" max="19" width="11.4444444444444" customWidth="1"/>
-    <col min="20" max="20" width="13.5555555555556" customWidth="1"/>
-    <col min="21" max="21" width="9.11111111111111" customWidth="1"/>
-    <col min="23" max="23" width="12.8888888888889" customWidth="1"/>
-    <col min="24" max="24" width="10.2222222222222" customWidth="1"/>
+    <col min="19" max="19" width="11.4416666666667" customWidth="1"/>
+    <col min="20" max="20" width="13.5583333333333" customWidth="1"/>
+    <col min="21" max="21" width="9.10833333333333" customWidth="1"/>
+    <col min="23" max="23" width="12.8916666666667" customWidth="1"/>
+    <col min="24" max="24" width="10.225" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="17" t="s">
         <v>337</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="17" t="s">
         <v>338</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="F1" s="17" t="s">
         <v>339</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="17" t="s">
         <v>143</v>
       </c>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16" t="s">
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16" t="s">
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+      <c r="P1" s="17"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
+      <c r="S1" s="17"/>
+      <c r="T1" s="17"/>
+      <c r="U1" s="17" t="s">
         <v>285</v>
       </c>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="17"/>
+      <c r="V1" s="17"/>
+      <c r="W1" s="17"/>
+      <c r="X1" s="18"/>
     </row>
     <row r="2" spans="1:24">
-      <c r="A2" s="18"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="20" t="s">
+      <c r="A2" s="19"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="I2" s="21" t="s">
+      <c r="I2" s="22" t="s">
         <v>340</v>
       </c>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
-      <c r="L2" s="22" t="s">
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
+      <c r="L2" s="23" t="s">
         <v>341</v>
       </c>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="20" t="s">
+      <c r="M2" s="23"/>
+      <c r="N2" s="23"/>
+      <c r="O2" s="23"/>
+      <c r="P2" s="23"/>
+      <c r="Q2" s="23"/>
+      <c r="R2" s="23"/>
+      <c r="S2" s="23"/>
+      <c r="T2" s="23"/>
+      <c r="U2" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="V2" s="21" t="s">
+      <c r="V2" s="22" t="s">
         <v>342</v>
       </c>
-      <c r="W2" s="21"/>
-      <c r="X2" s="23"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="24"/>
     </row>
-    <row r="3" ht="87.15" spans="1:24">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="24" t="s">
+    <row r="3" ht="81.75" spans="1:24">
+      <c r="A3" s="19"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="25" t="s">
         <v>182</v>
       </c>
-      <c r="I3" s="25" t="s">
+      <c r="I3" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="J3" s="25" t="s">
+      <c r="J3" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="K3" s="25" t="s">
+      <c r="K3" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="L3" s="26" t="s">
+      <c r="L3" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="N3" s="26" t="s">
+      <c r="N3" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="O3" s="27" t="s">
+      <c r="O3" s="28" t="s">
         <v>218</v>
       </c>
-      <c r="P3" s="27" t="s">
+      <c r="P3" s="28" t="s">
         <v>229</v>
       </c>
-      <c r="Q3" s="27" t="s">
+      <c r="Q3" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="R3" s="27" t="s">
+      <c r="R3" s="28" t="s">
         <v>267</v>
       </c>
-      <c r="S3" s="26" t="s">
+      <c r="S3" s="27" t="s">
         <v>346</v>
       </c>
-      <c r="T3" s="26" t="s">
+      <c r="T3" s="27" t="s">
         <v>347</v>
       </c>
-      <c r="U3" s="24" t="s">
+      <c r="U3" s="25" t="s">
         <v>333</v>
       </c>
-      <c r="V3" s="25" t="s">
+      <c r="V3" s="26" t="s">
         <v>286</v>
       </c>
-      <c r="W3" s="25" t="s">
+      <c r="W3" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="X3" s="28" t="s">
+      <c r="X3" s="29" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="4" s="12" customFormat="1" ht="158.4" spans="1:24">
-      <c r="A4" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="29" t="s">
+    <row r="4" s="13" customFormat="1" ht="121.5" spans="1:24">
+      <c r="A4" s="30" t="s">
         <v>348</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="B4" s="31" t="s">
         <v>349</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="C4" s="32" t="s">
         <v>350</v>
       </c>
-      <c r="E4" s="30"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="31" t="s">
+      <c r="D4" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="E4" s="32"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
-      <c r="J4" s="31"/>
-      <c r="K4" s="31"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="32"/>
-      <c r="O4" s="33" t="s">
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="35" t="s">
         <v>219</v>
       </c>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="S4" s="34"/>
-      <c r="T4" s="33" t="s">
+      <c r="P4" s="36"/>
+      <c r="Q4" s="36"/>
+      <c r="R4" s="36"/>
+      <c r="S4" s="36"/>
+      <c r="T4" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="U4" s="31" t="s">
+      <c r="U4" s="33" t="s">
         <v>287</v>
       </c>
-      <c r="V4" s="31"/>
-      <c r="W4" s="31"/>
-      <c r="X4" s="35"/>
+      <c r="V4" s="33"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="37"/>
     </row>
-    <row r="5" ht="100.8" spans="1:24">
-      <c r="A5" s="18"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="30" t="s">
-        <v>351</v>
-      </c>
-      <c r="D5" s="3" t="s">
+    <row r="5" ht="81" spans="1:24">
+      <c r="A5" s="19"/>
+      <c r="B5" s="31"/>
+      <c r="C5" s="32" t="s">
         <v>352</v>
       </c>
-      <c r="E5" s="30"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="31" t="s">
+      <c r="D5" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="31"/>
-      <c r="K5" s="31"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="33" t="s">
+      <c r="E5" s="32"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="35" t="s">
         <v>220</v>
       </c>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="34"/>
-      <c r="R5" s="34"/>
-      <c r="S5" s="34"/>
-      <c r="T5" s="33" t="s">
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="35" t="s">
         <v>274</v>
       </c>
-      <c r="U5" s="31" t="s">
+      <c r="U5" s="33" t="s">
         <v>170</v>
       </c>
-      <c r="V5" s="31"/>
-      <c r="W5" s="31"/>
-      <c r="X5" s="35"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="37"/>
     </row>
-    <row r="6" ht="144" spans="1:24">
-      <c r="A6" s="18"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="30" t="s">
-        <v>354</v>
-      </c>
-      <c r="D6" s="3" t="s">
+    <row r="6" ht="108" spans="1:24">
+      <c r="A6" s="19"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="32" t="s">
         <v>355</v>
       </c>
-      <c r="E6" s="30"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="31" t="s">
+      <c r="D6" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="E6" s="32"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="33" t="s">
         <v>150</v>
       </c>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="32"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
-      <c r="O6" s="33"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="34"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="31" t="s">
-        <v>356</v>
-      </c>
-      <c r="V6" s="31"/>
-      <c r="W6" s="31"/>
-      <c r="X6" s="35"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="33" t="s">
+        <v>357</v>
+      </c>
+      <c r="V6" s="33"/>
+      <c r="W6" s="33"/>
+      <c r="X6" s="37"/>
     </row>
-    <row r="7" ht="172.8" spans="1:24">
-      <c r="A7" s="18"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="30" t="s">
-        <v>357</v>
-      </c>
-      <c r="D7" s="3" t="s">
+    <row r="7" ht="148.5" spans="1:24">
+      <c r="A7" s="19"/>
+      <c r="B7" s="31"/>
+      <c r="C7" s="32" t="s">
         <v>358</v>
       </c>
-      <c r="E7" s="30"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="31" t="s">
+      <c r="D7" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="E7" s="32"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="33" t="s">
         <v>151</v>
       </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="31"/>
-      <c r="K7" s="31"/>
-      <c r="L7" s="36" t="s">
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="38" t="s">
         <v>185</v>
       </c>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="33"/>
-      <c r="P7" s="33"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="33"/>
-      <c r="S7" s="33"/>
-      <c r="T7" s="33"/>
-      <c r="U7" s="31" t="s">
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="33" t="s">
         <v>289</v>
       </c>
-      <c r="V7" s="31"/>
-      <c r="W7" s="31"/>
-      <c r="X7" s="35"/>
+      <c r="V7" s="33"/>
+      <c r="W7" s="33"/>
+      <c r="X7" s="37"/>
     </row>
-    <row r="8" customFormat="1" ht="216" spans="1:24">
-      <c r="A8" s="18"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="30" t="s">
-        <v>359</v>
-      </c>
-      <c r="D8" s="3" t="s">
+    <row r="8" customFormat="1" ht="189" spans="1:24">
+      <c r="A8" s="19"/>
+      <c r="B8" s="31"/>
+      <c r="C8" s="32" t="s">
         <v>360</v>
       </c>
-      <c r="E8" s="30"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="31" t="s">
+      <c r="D8" s="5" t="s">
         <v>361</v>
       </c>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="31"/>
-      <c r="K8" s="31"/>
-      <c r="L8" s="36"/>
-      <c r="M8" s="36"/>
-      <c r="N8" s="36"/>
-      <c r="O8" s="33"/>
-      <c r="P8" s="33" t="s">
+      <c r="E8" s="32"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="33" t="s">
+        <v>362</v>
+      </c>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="38"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35" t="s">
         <v>230</v>
       </c>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="33"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="31" t="s">
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="33" t="s">
         <v>290</v>
       </c>
-      <c r="V8" s="31"/>
-      <c r="W8" s="31"/>
-      <c r="X8" s="37" t="s">
+      <c r="V8" s="33"/>
+      <c r="W8" s="33"/>
+      <c r="X8" s="39" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="100.8" spans="1:24">
-      <c r="A9" s="18"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="30" t="s">
-        <v>362</v>
-      </c>
-      <c r="D9" s="3" t="s">
+    <row r="9" customFormat="1" ht="94.5" spans="1:24">
+      <c r="A9" s="19"/>
+      <c r="B9" s="31"/>
+      <c r="C9" s="32" t="s">
         <v>363</v>
       </c>
-      <c r="E9" s="30"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="31" t="s">
+      <c r="D9" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="E9" s="32"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="31"/>
-      <c r="K9" s="31"/>
-      <c r="L9" s="36" t="s">
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="38" t="s">
         <v>186</v>
       </c>
-      <c r="M9" s="36"/>
-      <c r="N9" s="36"/>
-      <c r="O9" s="33"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="33" t="s">
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="35"/>
+      <c r="P9" s="35"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="S9" s="33"/>
-      <c r="T9" s="33"/>
-      <c r="U9" s="31" t="s">
+      <c r="S9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="33" t="s">
         <v>291</v>
       </c>
-      <c r="V9" s="31"/>
-      <c r="W9" s="31"/>
-      <c r="X9" s="35"/>
+      <c r="V9" s="33"/>
+      <c r="W9" s="33"/>
+      <c r="X9" s="37"/>
     </row>
-    <row r="10" s="13" customFormat="1" ht="101.55" spans="1:24">
-      <c r="A10" s="18"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="30" t="s">
-        <v>364</v>
-      </c>
-      <c r="D10" s="3" t="s">
+    <row r="10" s="14" customFormat="1" ht="81.75" spans="1:24">
+      <c r="A10" s="19"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="32" t="s">
         <v>365</v>
       </c>
-      <c r="E10" s="30"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="31" t="s">
+      <c r="D10" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="E10" s="32"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="33" t="s">
         <v>154</v>
       </c>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="31"/>
-      <c r="K10" s="31"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="33"/>
-      <c r="P10" s="33" t="s">
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="38"/>
+      <c r="M10" s="38"/>
+      <c r="N10" s="38"/>
+      <c r="O10" s="35"/>
+      <c r="P10" s="35" t="s">
         <v>231</v>
       </c>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="33"/>
-      <c r="S10" s="33"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="31" t="s">
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="33" t="s">
         <v>292</v>
       </c>
-      <c r="V10" s="31"/>
-      <c r="W10" s="31"/>
-      <c r="X10" s="35"/>
+      <c r="V10" s="33"/>
+      <c r="W10" s="33"/>
+      <c r="X10" s="37"/>
     </row>
-    <row r="11" s="12" customFormat="1" ht="86.4" spans="1:24">
-      <c r="A11" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>366</v>
-      </c>
-      <c r="C11" s="30" t="s">
+    <row r="11" s="13" customFormat="1" ht="67.5" spans="1:24">
+      <c r="A11" s="30" t="s">
         <v>367</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="B11" s="31" t="s">
         <v>368</v>
       </c>
-      <c r="E11" s="30"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="31" t="s">
+      <c r="C11" s="32" t="s">
+        <v>369</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="E11" s="32"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="31"/>
-      <c r="K11" s="31"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="33"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="33"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="31" t="s">
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="38"/>
+      <c r="M11" s="38"/>
+      <c r="N11" s="38"/>
+      <c r="O11" s="35"/>
+      <c r="P11" s="35"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="V11" s="31"/>
-      <c r="W11" s="31"/>
-      <c r="X11" s="35"/>
+      <c r="V11" s="33"/>
+      <c r="W11" s="33"/>
+      <c r="X11" s="37"/>
     </row>
-    <row r="12" customFormat="1" ht="86.4" spans="1:24">
-      <c r="A12" s="18"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="30" t="s">
-        <v>369</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="E12" s="30"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="31" t="s">
+    <row r="12" customFormat="1" ht="81" spans="1:24">
+      <c r="A12" s="19"/>
+      <c r="B12" s="31"/>
+      <c r="C12" s="32" t="s">
+        <v>371</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="E12" s="32"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="33" t="s">
         <v>156</v>
       </c>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="38" t="s">
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="40" t="s">
         <v>171</v>
       </c>
-      <c r="K12" s="38" t="s">
+      <c r="K12" s="40" t="s">
         <v>174</v>
       </c>
-      <c r="L12" s="36" t="s">
+      <c r="L12" s="38" t="s">
         <v>187</v>
       </c>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="33" t="s">
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="35" t="s">
         <v>221</v>
       </c>
-      <c r="P12" s="33" t="s">
+      <c r="P12" s="35" t="s">
         <v>232</v>
       </c>
-      <c r="Q12" s="33" t="s">
+      <c r="Q12" s="35" t="s">
         <v>258</v>
       </c>
-      <c r="R12" s="33" t="s">
+      <c r="R12" s="35" t="s">
         <v>268</v>
       </c>
-      <c r="S12" s="33"/>
-      <c r="T12" s="33" t="s">
+      <c r="S12" s="35"/>
+      <c r="T12" s="35" t="s">
         <v>275</v>
       </c>
-      <c r="U12" s="31" t="s">
+      <c r="U12" s="33" t="s">
         <v>294</v>
       </c>
-      <c r="V12" s="31"/>
-      <c r="W12" s="31"/>
-      <c r="X12" s="35"/>
+      <c r="V12" s="33"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="37"/>
     </row>
-    <row r="13" customFormat="1" ht="57.6" spans="1:24">
-      <c r="A13" s="18"/>
-      <c r="B13" s="29"/>
-      <c r="C13" s="30" t="s">
-        <v>371</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="E13" s="30"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="31" t="s">
+    <row r="13" customFormat="1" ht="54" spans="1:24">
+      <c r="A13" s="19"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="32" t="s">
+        <v>373</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>374</v>
+      </c>
+      <c r="E13" s="32"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="31"/>
-      <c r="K13" s="38" t="s">
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="33"/>
+      <c r="K13" s="40" t="s">
         <v>175</v>
       </c>
-      <c r="L13" s="36" t="s">
+      <c r="L13" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="M13" s="36"/>
-      <c r="N13" s="36"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33" t="s">
+      <c r="M13" s="38"/>
+      <c r="N13" s="38"/>
+      <c r="O13" s="35"/>
+      <c r="P13" s="35" t="s">
         <v>233</v>
       </c>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33" t="s">
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33" t="s">
+      <c r="S13" s="35"/>
+      <c r="T13" s="35" t="s">
         <v>276</v>
       </c>
-      <c r="U13" s="31" t="s">
+      <c r="U13" s="33" t="s">
         <v>295</v>
       </c>
-      <c r="V13" s="31"/>
-      <c r="W13" s="31"/>
-      <c r="X13" s="35"/>
+      <c r="V13" s="33"/>
+      <c r="W13" s="33"/>
+      <c r="X13" s="37"/>
     </row>
-    <row r="14" customFormat="1" ht="115.2" spans="1:24">
-      <c r="A14" s="18"/>
-      <c r="B14" s="29"/>
-      <c r="C14" s="30" t="s">
-        <v>373</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="E14" s="30"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="31" t="s">
+    <row r="14" customFormat="1" ht="94.5" spans="1:24">
+      <c r="A14" s="19"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="32" t="s">
+        <v>375</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="E14" s="32"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="31"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="36" t="s">
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="38" t="s">
         <v>189</v>
       </c>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="33"/>
-      <c r="P14" s="33"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="33"/>
-      <c r="S14" s="33"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="31" t="s">
+      <c r="M14" s="38"/>
+      <c r="N14" s="38"/>
+      <c r="O14" s="35"/>
+      <c r="P14" s="35"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="V14" s="31"/>
-      <c r="W14" s="31"/>
-      <c r="X14" s="37" t="s">
+      <c r="V14" s="33"/>
+      <c r="W14" s="33"/>
+      <c r="X14" s="39" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="100.8" spans="1:24">
-      <c r="A15" s="18"/>
-      <c r="B15" s="29"/>
-      <c r="C15" s="30" t="s">
-        <v>375</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="E15" s="30"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="31" t="s">
+    <row r="15" customFormat="1" ht="81" spans="1:24">
+      <c r="A15" s="19"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="32" t="s">
+        <v>377</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="E15" s="32"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="38" t="s">
+      <c r="H15" s="33"/>
+      <c r="I15" s="33"/>
+      <c r="J15" s="40" t="s">
         <v>172</v>
       </c>
-      <c r="K15" s="38" t="s">
+      <c r="K15" s="40" t="s">
         <v>176</v>
       </c>
-      <c r="L15" s="36" t="s">
+      <c r="L15" s="38" t="s">
         <v>190</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="36"/>
-      <c r="O15" s="33"/>
-      <c r="P15" s="33"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="33"/>
-      <c r="S15" s="33"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="31" t="s">
-        <v>377</v>
-      </c>
-      <c r="V15" s="31"/>
-      <c r="W15" s="31"/>
-      <c r="X15" s="37" t="s">
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="35"/>
+      <c r="P15" s="35"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="33" t="s">
+        <v>379</v>
+      </c>
+      <c r="V15" s="33"/>
+      <c r="W15" s="33"/>
+      <c r="X15" s="39" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="16" s="13" customFormat="1" ht="87.15" spans="1:24">
-      <c r="A16" s="18"/>
-      <c r="B16" s="29"/>
-      <c r="C16" s="30" t="s">
-        <v>378</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="E16" s="30"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="31" t="s">
+    <row r="16" s="14" customFormat="1" ht="81.75" spans="1:24">
+      <c r="A16" s="19"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="32" t="s">
+        <v>380</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="E16" s="32"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H16" s="31"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36"/>
-      <c r="N16" s="36"/>
-      <c r="O16" s="33"/>
-      <c r="P16" s="33" t="s">
+      <c r="H16" s="33"/>
+      <c r="I16" s="33"/>
+      <c r="J16" s="33"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="38"/>
+      <c r="M16" s="38"/>
+      <c r="N16" s="38"/>
+      <c r="O16" s="35"/>
+      <c r="P16" s="35" t="s">
         <v>234</v>
       </c>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="31" t="s">
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="V16" s="31"/>
-      <c r="W16" s="31"/>
-      <c r="X16" s="35"/>
+      <c r="V16" s="33"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="37"/>
     </row>
-    <row r="17" s="12" customFormat="1" ht="100.8" spans="1:24">
-      <c r="A17" s="18" t="s">
-        <v>2</v>
-      </c>
-      <c r="B17" s="29" t="s">
+    <row r="17" s="13" customFormat="1" ht="81" spans="1:24">
+      <c r="A17" s="30" t="s">
+        <v>382</v>
+      </c>
+      <c r="B17" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="30" t="s">
-        <v>380</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="E17" s="30"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="31" t="s">
+      <c r="C17" s="32" t="s">
+        <v>383</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>384</v>
+      </c>
+      <c r="E17" s="32"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H17" s="31"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="31"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="33"/>
-      <c r="P17" s="33"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="31" t="s">
+      <c r="H17" s="33"/>
+      <c r="I17" s="33"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="38"/>
+      <c r="M17" s="38"/>
+      <c r="N17" s="38"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="33" t="s">
         <v>298</v>
       </c>
-      <c r="V17" s="31"/>
-      <c r="W17" s="31"/>
-      <c r="X17" s="35"/>
+      <c r="V17" s="33"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="37"/>
     </row>
-    <row r="18" customFormat="1" ht="115.2" spans="1:24">
-      <c r="A18" s="18"/>
-      <c r="B18" s="29"/>
-      <c r="C18" s="30" t="s">
-        <v>382</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="E18" s="30"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="31" t="s">
+    <row r="18" customFormat="1" ht="108" spans="1:24">
+      <c r="A18" s="19"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>386</v>
+      </c>
+      <c r="E18" s="32"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H18" s="31"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="31"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="36" t="s">
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="38" t="s">
         <v>191</v>
       </c>
-      <c r="M18" s="36"/>
-      <c r="N18" s="36"/>
-      <c r="O18" s="33"/>
-      <c r="P18" s="33"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="31" t="s">
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="33" t="s">
         <v>299</v>
       </c>
-      <c r="V18" s="31"/>
-      <c r="W18" s="31"/>
-      <c r="X18" s="35"/>
+      <c r="V18" s="33"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="37"/>
     </row>
-    <row r="19" customFormat="1" ht="86.4" spans="1:24">
-      <c r="A19" s="18"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="30" t="s">
-        <v>384</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="E19" s="30"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="31" t="s">
+    <row r="19" customFormat="1" ht="81" spans="1:24">
+      <c r="A19" s="19"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="32" t="s">
+        <v>387</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="E19" s="32"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H19" s="31"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="31"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="36" t="s">
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="38" t="s">
         <v>192</v>
       </c>
-      <c r="M19" s="36"/>
-      <c r="N19" s="36"/>
-      <c r="O19" s="33"/>
-      <c r="P19" s="33"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
-      <c r="T19" s="33"/>
-      <c r="U19" s="31" t="s">
+      <c r="M19" s="38"/>
+      <c r="N19" s="38"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="33" t="s">
         <v>300</v>
       </c>
-      <c r="V19" s="31"/>
-      <c r="W19" s="31"/>
-      <c r="X19" s="35"/>
+      <c r="V19" s="33"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="37"/>
     </row>
-    <row r="20" customFormat="1" ht="57.6" spans="1:24">
-      <c r="A20" s="18"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="30" t="s">
-        <v>386</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="E20" s="30"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="31" t="s">
+    <row r="20" customFormat="1" ht="54" spans="1:24">
+      <c r="A20" s="19"/>
+      <c r="B20" s="31"/>
+      <c r="C20" s="32" t="s">
+        <v>389</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>390</v>
+      </c>
+      <c r="E20" s="32"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="36" t="s">
+      <c r="H20" s="33"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="33"/>
+      <c r="K20" s="33"/>
+      <c r="L20" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="M20" s="36"/>
-      <c r="N20" s="36"/>
-      <c r="O20" s="33"/>
-      <c r="P20" s="33" t="s">
+      <c r="M20" s="38"/>
+      <c r="N20" s="38"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35" t="s">
         <v>235</v>
       </c>
-      <c r="Q20" s="33"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="33"/>
-      <c r="U20" s="31" t="s">
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="33" t="s">
         <v>301</v>
       </c>
-      <c r="V20" s="31"/>
-      <c r="W20" s="31"/>
-      <c r="X20" s="35"/>
+      <c r="V20" s="33"/>
+      <c r="W20" s="33"/>
+      <c r="X20" s="37"/>
     </row>
-    <row r="21" customFormat="1" ht="158.4" spans="1:24">
-      <c r="A21" s="18"/>
-      <c r="B21" s="29"/>
-      <c r="C21" s="30" t="s">
-        <v>388</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="E21" s="30"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="31" t="s">
+    <row r="21" customFormat="1" ht="121.5" spans="1:24">
+      <c r="A21" s="19"/>
+      <c r="B21" s="31"/>
+      <c r="C21" s="32" t="s">
+        <v>391</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="E21" s="32"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="36" t="s">
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="38" t="s">
         <v>194</v>
       </c>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="33" t="s">
+      <c r="M21" s="38"/>
+      <c r="N21" s="38"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35" t="s">
         <v>236</v>
       </c>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="31" t="s">
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="V21" s="31"/>
-      <c r="W21" s="31"/>
-      <c r="X21" s="35"/>
+      <c r="V21" s="33"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="37"/>
     </row>
-    <row r="22" s="13" customFormat="1" ht="115.95" spans="1:24">
-      <c r="A22" s="18"/>
-      <c r="B22" s="29"/>
-      <c r="C22" s="30" t="s">
-        <v>390</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="E22" s="30"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="31" t="s">
+    <row r="22" s="14" customFormat="1" ht="81.75" spans="1:24">
+      <c r="A22" s="19"/>
+      <c r="B22" s="31"/>
+      <c r="C22" s="32" t="s">
+        <v>393</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="E22" s="32"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H22" s="31"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="31"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="36" t="s">
+      <c r="H22" s="33"/>
+      <c r="I22" s="33"/>
+      <c r="J22" s="33"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="38" t="s">
         <v>195</v>
       </c>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="33" t="s">
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35" t="s">
         <v>237</v>
       </c>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="33"/>
-      <c r="U22" s="31" t="s">
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="33" t="s">
         <v>303</v>
       </c>
-      <c r="V22" s="31"/>
-      <c r="W22" s="31"/>
-      <c r="X22" s="35"/>
+      <c r="V22" s="33"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="37"/>
     </row>
-    <row r="23" s="12" customFormat="1" ht="100.8" spans="1:24">
-      <c r="A23" s="18" t="s">
-        <v>3</v>
-      </c>
-      <c r="B23" s="29" t="s">
-        <v>392</v>
-      </c>
-      <c r="C23" s="30" t="s">
-        <v>393</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E23" s="30"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="31" t="s">
+    <row r="23" s="13" customFormat="1" ht="67.5" spans="1:24">
+      <c r="A23" s="30" t="s">
+        <v>395</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>396</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>397</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="E23" s="32"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H23" s="31"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="33"/>
-      <c r="P23" s="33"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="33"/>
-      <c r="T23" s="33"/>
-      <c r="U23" s="31" t="s">
+      <c r="H23" s="33"/>
+      <c r="I23" s="33"/>
+      <c r="J23" s="33"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="33" t="s">
         <v>304</v>
       </c>
-      <c r="V23" s="31"/>
-      <c r="W23" s="31"/>
-      <c r="X23" s="35"/>
+      <c r="V23" s="33"/>
+      <c r="W23" s="33"/>
+      <c r="X23" s="37"/>
     </row>
     <row r="24" customFormat="1" ht="76" customHeight="1" spans="1:24">
-      <c r="A24" s="18"/>
-      <c r="B24" s="29"/>
-      <c r="C24" s="30" t="s">
-        <v>395</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="E24" s="30"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="31" t="s">
+      <c r="A24" s="19"/>
+      <c r="B24" s="31"/>
+      <c r="C24" s="32" t="s">
+        <v>399</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="E24" s="32"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="36" t="s">
+      <c r="H24" s="33"/>
+      <c r="I24" s="33"/>
+      <c r="J24" s="33"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="38" t="s">
         <v>193</v>
       </c>
-      <c r="M24" s="36"/>
-      <c r="N24" s="36"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="33" t="s">
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35" t="s">
         <v>238</v>
       </c>
-      <c r="Q24" s="33"/>
-      <c r="R24" s="33"/>
-      <c r="S24" s="33"/>
-      <c r="T24" s="33"/>
-      <c r="U24" s="31" t="s">
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="35"/>
+      <c r="U24" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="V24" s="31"/>
-      <c r="W24" s="31"/>
-      <c r="X24" s="35"/>
+      <c r="V24" s="33"/>
+      <c r="W24" s="33"/>
+      <c r="X24" s="37"/>
     </row>
-    <row r="25" customFormat="1" ht="100.8" spans="1:24">
-      <c r="A25" s="18"/>
-      <c r="B25" s="29"/>
-      <c r="C25" s="30" t="s">
-        <v>397</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="E25" s="30"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="31" t="s">
+    <row r="25" customFormat="1" ht="94.5" spans="1:24">
+      <c r="A25" s="19"/>
+      <c r="B25" s="31"/>
+      <c r="C25" s="32" t="s">
+        <v>401</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="E25" s="32"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="33" t="s">
         <v>160</v>
       </c>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="31"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="36" t="s">
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="J25" s="33"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="38" t="s">
         <v>196</v>
       </c>
-      <c r="M25" s="36"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="33"/>
-      <c r="P25" s="33" t="s">
+      <c r="M25" s="38"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35" t="s">
         <v>239</v>
       </c>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="33"/>
-      <c r="S25" s="33"/>
-      <c r="T25" s="33"/>
-      <c r="U25" s="31" t="s">
+      <c r="Q25" s="35"/>
+      <c r="R25" s="35"/>
+      <c r="S25" s="35"/>
+      <c r="T25" s="35"/>
+      <c r="U25" s="33" t="s">
         <v>306</v>
       </c>
-      <c r="V25" s="31"/>
-      <c r="W25" s="31"/>
-      <c r="X25" s="35"/>
+      <c r="V25" s="33"/>
+      <c r="W25" s="33"/>
+      <c r="X25" s="37"/>
     </row>
-    <row r="26" s="13" customFormat="1" ht="115.95" spans="1:24">
-      <c r="A26" s="18"/>
-      <c r="B26" s="29"/>
-      <c r="C26" s="30" t="s">
-        <v>399</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="E26" s="30"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="31" t="s">
+    <row r="26" s="14" customFormat="1" ht="68.25" spans="1:24">
+      <c r="A26" s="19"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="32" t="s">
+        <v>403</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>404</v>
+      </c>
+      <c r="E26" s="32"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="33" t="s">
         <v>161</v>
       </c>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="36" t="s">
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="J26" s="33"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="38" t="s">
         <v>197</v>
       </c>
-      <c r="M26" s="36"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="33"/>
-      <c r="P26" s="33" t="s">
+      <c r="M26" s="38"/>
+      <c r="N26" s="38"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35" t="s">
         <v>240</v>
       </c>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="31" t="s">
-        <v>401</v>
-      </c>
-      <c r="V26" s="31"/>
-      <c r="W26" s="31"/>
-      <c r="X26" s="35"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="35"/>
+      <c r="T26" s="35"/>
+      <c r="U26" s="33" t="s">
+        <v>405</v>
+      </c>
+      <c r="V26" s="33"/>
+      <c r="W26" s="33"/>
+      <c r="X26" s="37"/>
     </row>
-    <row r="27" s="12" customFormat="1" ht="72" spans="1:24">
-      <c r="A27" s="18" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="29" t="s">
-        <v>402</v>
-      </c>
-      <c r="C27" s="30" t="s">
-        <v>403</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="E27" s="30"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="31" t="s">
+    <row r="27" s="13" customFormat="1" ht="67.5" spans="1:24">
+      <c r="A27" s="30" t="s">
+        <v>406</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>407</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>408</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>409</v>
+      </c>
+      <c r="E27" s="32"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="36" t="s">
+      <c r="H27" s="33"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="33"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="M27" s="36"/>
-      <c r="N27" s="36"/>
-      <c r="O27" s="33" t="s">
+      <c r="M27" s="38"/>
+      <c r="N27" s="38"/>
+      <c r="O27" s="35" t="s">
         <v>222</v>
       </c>
-      <c r="P27" s="33" t="s">
+      <c r="P27" s="35" t="s">
         <v>241</v>
       </c>
-      <c r="Q27" s="33" t="s">
+      <c r="Q27" s="35" t="s">
         <v>259</v>
       </c>
-      <c r="R27" s="33"/>
-      <c r="S27" s="33"/>
-      <c r="T27" s="33"/>
-      <c r="U27" s="31" t="s">
+      <c r="R27" s="35"/>
+      <c r="S27" s="35"/>
+      <c r="T27" s="35"/>
+      <c r="U27" s="33" t="s">
         <v>308</v>
       </c>
-      <c r="V27" s="31"/>
-      <c r="W27" s="31"/>
-      <c r="X27" s="35"/>
+      <c r="V27" s="33"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="37"/>
     </row>
-    <row r="28" customFormat="1" ht="230.4" spans="1:24">
-      <c r="A28" s="18"/>
-      <c r="B28" s="29"/>
-      <c r="C28" s="30" t="s">
-        <v>405</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="E28" s="30"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="31" t="s">
+    <row r="28" customFormat="1" ht="189" spans="1:24">
+      <c r="A28" s="19"/>
+      <c r="B28" s="31"/>
+      <c r="C28" s="32" t="s">
+        <v>410</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="E28" s="32"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H28" s="31"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="31"/>
-      <c r="K28" s="38" t="s">
+      <c r="H28" s="33"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="33"/>
+      <c r="K28" s="40" t="s">
         <v>177</v>
       </c>
-      <c r="L28" s="36" t="s">
+      <c r="L28" s="38" t="s">
         <v>199</v>
       </c>
-      <c r="M28" s="36"/>
-      <c r="N28" s="36"/>
-      <c r="O28" s="33" t="s">
+      <c r="M28" s="38"/>
+      <c r="N28" s="38"/>
+      <c r="O28" s="35" t="s">
         <v>223</v>
       </c>
-      <c r="P28" s="33" t="s">
+      <c r="P28" s="35" t="s">
         <v>242</v>
       </c>
-      <c r="Q28" s="33" t="s">
+      <c r="Q28" s="35" t="s">
         <v>260</v>
       </c>
-      <c r="R28" s="33"/>
-      <c r="S28" s="33"/>
-      <c r="T28" s="33"/>
-      <c r="U28" s="31" t="s">
+      <c r="R28" s="35"/>
+      <c r="S28" s="35"/>
+      <c r="T28" s="35"/>
+      <c r="U28" s="33" t="s">
         <v>309</v>
       </c>
-      <c r="V28" s="31"/>
-      <c r="W28" s="31"/>
-      <c r="X28" s="35"/>
+      <c r="V28" s="33"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="37"/>
     </row>
-    <row r="29" s="13" customFormat="1" ht="159.15" spans="1:24">
-      <c r="A29" s="18"/>
-      <c r="B29" s="29"/>
-      <c r="C29" s="30" t="s">
-        <v>407</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="E29" s="30"/>
-      <c r="F29" s="2"/>
-      <c r="G29" s="31" t="s">
+    <row r="29" s="14" customFormat="1" ht="149.25" spans="1:24">
+      <c r="A29" s="19"/>
+      <c r="B29" s="31"/>
+      <c r="C29" s="32" t="s">
+        <v>412</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>413</v>
+      </c>
+      <c r="E29" s="32"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="33" t="s">
         <v>162</v>
       </c>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
-      <c r="J29" s="31"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="36" t="s">
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
+      <c r="J29" s="33"/>
+      <c r="K29" s="33"/>
+      <c r="L29" s="38" t="s">
         <v>200</v>
       </c>
-      <c r="M29" s="36"/>
-      <c r="N29" s="36"/>
-      <c r="O29" s="33" t="s">
+      <c r="M29" s="38"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="35" t="s">
         <v>224</v>
       </c>
-      <c r="P29" s="33" t="s">
+      <c r="P29" s="35" t="s">
         <v>243</v>
       </c>
-      <c r="Q29" s="33" t="s">
+      <c r="Q29" s="35" t="s">
         <v>261</v>
       </c>
-      <c r="R29" s="33"/>
-      <c r="S29" s="33"/>
-      <c r="T29" s="33"/>
-      <c r="U29" s="31" t="s">
+      <c r="R29" s="35"/>
+      <c r="S29" s="35"/>
+      <c r="T29" s="35"/>
+      <c r="U29" s="33" t="s">
         <v>310</v>
       </c>
-      <c r="V29" s="31"/>
-      <c r="W29" s="31"/>
-      <c r="X29" s="35"/>
+      <c r="V29" s="33"/>
+      <c r="W29" s="33"/>
+      <c r="X29" s="37"/>
     </row>
-    <row r="30" s="12" customFormat="1" ht="115.2" spans="1:24">
-      <c r="A30" s="18" t="s">
-        <v>5</v>
-      </c>
-      <c r="B30" s="29" t="s">
+    <row r="30" s="13" customFormat="1" ht="108" spans="1:24">
+      <c r="A30" s="30" t="s">
+        <v>414</v>
+      </c>
+      <c r="B30" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="30" t="s">
-        <v>409</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="E30" s="30"/>
-      <c r="F30" s="2"/>
-      <c r="G30" s="31" t="s">
+      <c r="C30" s="32" t="s">
+        <v>415</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>416</v>
+      </c>
+      <c r="E30" s="32"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
-      <c r="J30" s="31"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="36" t="s">
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="38" t="s">
         <v>201</v>
       </c>
-      <c r="M30" s="36"/>
-      <c r="N30" s="36"/>
-      <c r="O30" s="33"/>
-      <c r="P30" s="33"/>
-      <c r="Q30" s="33" t="s">
+      <c r="M30" s="38"/>
+      <c r="N30" s="38"/>
+      <c r="O30" s="35"/>
+      <c r="P30" s="35"/>
+      <c r="Q30" s="35" t="s">
         <v>262</v>
       </c>
-      <c r="R30" s="33"/>
-      <c r="S30" s="33"/>
-      <c r="T30" s="33"/>
-      <c r="U30" s="31" t="s">
+      <c r="R30" s="35"/>
+      <c r="S30" s="35"/>
+      <c r="T30" s="35"/>
+      <c r="U30" s="33" t="s">
         <v>311</v>
       </c>
-      <c r="V30" s="31"/>
-      <c r="W30" s="31"/>
-      <c r="X30" s="35"/>
+      <c r="V30" s="33"/>
+      <c r="W30" s="33"/>
+      <c r="X30" s="37"/>
     </row>
-    <row r="31" customFormat="1" ht="144" spans="1:24">
-      <c r="A31" s="18"/>
-      <c r="B31" s="29"/>
-      <c r="C31" s="30" t="s">
-        <v>411</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="E31" s="30"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="31" t="s">
+    <row r="31" customFormat="1" ht="135" spans="1:24">
+      <c r="A31" s="19"/>
+      <c r="B31" s="31"/>
+      <c r="C31" s="32" t="s">
+        <v>417</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>418</v>
+      </c>
+      <c r="E31" s="32"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
-      <c r="J31" s="31"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="36" t="s">
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
+      <c r="J31" s="33"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="38" t="s">
         <v>202</v>
       </c>
-      <c r="M31" s="36"/>
-      <c r="N31" s="36"/>
-      <c r="O31" s="33"/>
-      <c r="P31" s="33"/>
-      <c r="Q31" s="33"/>
-      <c r="R31" s="33"/>
-      <c r="S31" s="33"/>
-      <c r="T31" s="33"/>
-      <c r="U31" s="31" t="s">
+      <c r="M31" s="38"/>
+      <c r="N31" s="38"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="33" t="s">
         <v>312</v>
       </c>
-      <c r="V31" s="31"/>
-      <c r="W31" s="31"/>
-      <c r="X31" s="35"/>
+      <c r="V31" s="33"/>
+      <c r="W31" s="33"/>
+      <c r="X31" s="37"/>
     </row>
-    <row r="32" customFormat="1" ht="100.8" spans="1:24">
-      <c r="A32" s="18"/>
-      <c r="B32" s="29"/>
-      <c r="C32" s="30" t="s">
-        <v>413</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="E32" s="30"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="31" t="s">
+    <row r="32" customFormat="1" ht="94.5" spans="1:24">
+      <c r="A32" s="19"/>
+      <c r="B32" s="31"/>
+      <c r="C32" s="32" t="s">
+        <v>419</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="E32" s="32"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
-      <c r="J32" s="31"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="36" t="s">
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
+      <c r="J32" s="33"/>
+      <c r="K32" s="33"/>
+      <c r="L32" s="38" t="s">
         <v>203</v>
       </c>
-      <c r="M32" s="36"/>
-      <c r="N32" s="36"/>
-      <c r="O32" s="33"/>
-      <c r="P32" s="33"/>
-      <c r="Q32" s="33"/>
-      <c r="R32" s="33" t="s">
+      <c r="M32" s="38"/>
+      <c r="N32" s="38"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
+      <c r="R32" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="S32" s="33"/>
-      <c r="T32" s="33" t="s">
+      <c r="S32" s="35"/>
+      <c r="T32" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="U32" s="31" t="s">
+      <c r="U32" s="33" t="s">
         <v>313</v>
       </c>
-      <c r="V32" s="31"/>
-      <c r="W32" s="31"/>
-      <c r="X32" s="35"/>
+      <c r="V32" s="33"/>
+      <c r="W32" s="33"/>
+      <c r="X32" s="37"/>
     </row>
-    <row r="33" customFormat="1" ht="158.4" spans="1:24">
-      <c r="A33" s="18"/>
-      <c r="B33" s="29"/>
-      <c r="C33" s="30" t="s">
-        <v>415</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="E33" s="30"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="31" t="s">
+    <row r="33" customFormat="1" ht="148.5" spans="1:24">
+      <c r="A33" s="19"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="32" t="s">
+        <v>421</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="E33" s="32"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
-      <c r="J33" s="31"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="36" t="s">
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
+      <c r="J33" s="33"/>
+      <c r="K33" s="33"/>
+      <c r="L33" s="38" t="s">
         <v>204</v>
       </c>
-      <c r="M33" s="36"/>
-      <c r="N33" s="36"/>
-      <c r="O33" s="33"/>
-      <c r="P33" s="33"/>
-      <c r="Q33" s="33"/>
-      <c r="R33" s="33"/>
-      <c r="S33" s="33"/>
-      <c r="T33" s="33" t="s">
+      <c r="M33" s="38"/>
+      <c r="N33" s="38"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="35"/>
+      <c r="R33" s="35"/>
+      <c r="S33" s="35"/>
+      <c r="T33" s="35" t="s">
         <v>278</v>
       </c>
-      <c r="U33" s="31" t="s">
+      <c r="U33" s="33" t="s">
         <v>314</v>
       </c>
-      <c r="V33" s="31"/>
-      <c r="W33" s="31"/>
-      <c r="X33" s="35"/>
+      <c r="V33" s="33"/>
+      <c r="W33" s="33"/>
+      <c r="X33" s="37"/>
     </row>
-    <row r="34" customFormat="1" ht="144" spans="1:24">
-      <c r="A34" s="18"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="30" t="s">
-        <v>417</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="E34" s="30"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="31" t="s">
+    <row r="34" customFormat="1" ht="135" spans="1:24">
+      <c r="A34" s="19"/>
+      <c r="B34" s="31"/>
+      <c r="C34" s="32" t="s">
+        <v>423</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>424</v>
+      </c>
+      <c r="E34" s="32"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="31"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36"/>
-      <c r="O34" s="33"/>
-      <c r="P34" s="33"/>
-      <c r="Q34" s="33"/>
-      <c r="R34" s="33"/>
-      <c r="S34" s="33"/>
-      <c r="T34" s="33" t="s">
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="38"/>
+      <c r="M34" s="38"/>
+      <c r="N34" s="38"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="35"/>
+      <c r="R34" s="35"/>
+      <c r="S34" s="35"/>
+      <c r="T34" s="35" t="s">
         <v>279</v>
       </c>
-      <c r="U34" s="39" t="s">
+      <c r="U34" s="41" t="s">
         <v>315</v>
       </c>
-      <c r="V34" s="39"/>
-      <c r="W34" s="39"/>
-      <c r="X34" s="40"/>
+      <c r="V34" s="41"/>
+      <c r="W34" s="41"/>
+      <c r="X34" s="42"/>
     </row>
-    <row r="35" s="13" customFormat="1" ht="173.55" spans="1:24">
-      <c r="A35" s="18"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="30" t="s">
-        <v>419</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="E35" s="30"/>
-      <c r="F35" s="2"/>
-      <c r="G35" s="31" t="s">
+    <row r="35" s="14" customFormat="1" ht="162.75" spans="1:24">
+      <c r="A35" s="19"/>
+      <c r="B35" s="31"/>
+      <c r="C35" s="32" t="s">
+        <v>425</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="E35" s="32"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
-      <c r="J35" s="31"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="36" t="s">
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
+      <c r="J35" s="33"/>
+      <c r="K35" s="33"/>
+      <c r="L35" s="38" t="s">
         <v>205</v>
       </c>
-      <c r="M35" s="36"/>
-      <c r="N35" s="36"/>
-      <c r="O35" s="33"/>
-      <c r="P35" s="33" t="s">
+      <c r="M35" s="38"/>
+      <c r="N35" s="38"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35" t="s">
         <v>244</v>
       </c>
-      <c r="Q35" s="33"/>
-      <c r="R35" s="33"/>
-      <c r="S35" s="33"/>
-      <c r="T35" s="33"/>
-      <c r="U35" s="31" t="s">
+      <c r="Q35" s="35"/>
+      <c r="R35" s="35"/>
+      <c r="S35" s="35"/>
+      <c r="T35" s="35"/>
+      <c r="U35" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="V35" s="31"/>
-      <c r="W35" s="31"/>
-      <c r="X35" s="35"/>
+      <c r="V35" s="33"/>
+      <c r="W35" s="33"/>
+      <c r="X35" s="37"/>
     </row>
-    <row r="36" s="12" customFormat="1" ht="144" spans="1:24">
-      <c r="A36" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B36" s="29" t="s">
+    <row r="36" s="13" customFormat="1" ht="121.5" spans="1:24">
+      <c r="A36" s="30" t="s">
+        <v>427</v>
+      </c>
+      <c r="B36" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="30" t="s">
-        <v>421</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="E36" s="30"/>
-      <c r="F36" s="2"/>
-      <c r="G36" s="31" t="s">
+      <c r="C36" s="32" t="s">
+        <v>428</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>429</v>
+      </c>
+      <c r="E36" s="32"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
-      <c r="J36" s="31"/>
-      <c r="K36" s="31"/>
-      <c r="L36" s="36" t="s">
-        <v>423</v>
-      </c>
-      <c r="M36" s="36"/>
-      <c r="N36" s="36"/>
-      <c r="O36" s="33"/>
-      <c r="P36" s="33"/>
-      <c r="Q36" s="33" t="s">
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
+      <c r="J36" s="33"/>
+      <c r="K36" s="33"/>
+      <c r="L36" s="38" t="s">
+        <v>430</v>
+      </c>
+      <c r="M36" s="38"/>
+      <c r="N36" s="38"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="35" t="s">
         <v>263</v>
       </c>
-      <c r="R36" s="33"/>
-      <c r="S36" s="33"/>
-      <c r="T36" s="33" t="s">
+      <c r="R36" s="35"/>
+      <c r="S36" s="35"/>
+      <c r="T36" s="35" t="s">
         <v>280</v>
       </c>
-      <c r="U36" s="31" t="s">
+      <c r="U36" s="33" t="s">
         <v>316</v>
       </c>
-      <c r="V36" s="31"/>
-      <c r="W36" s="31"/>
-      <c r="X36" s="35"/>
+      <c r="V36" s="33"/>
+      <c r="W36" s="33"/>
+      <c r="X36" s="37"/>
     </row>
-    <row r="37" customFormat="1" ht="144" spans="1:24">
-      <c r="A37" s="18"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="30" t="s">
-        <v>424</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="E37" s="30"/>
-      <c r="F37" s="2"/>
-      <c r="G37" s="31" t="s">
+    <row r="37" customFormat="1" ht="135" spans="1:24">
+      <c r="A37" s="19"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="32" t="s">
+        <v>431</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E37" s="32"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="38" t="s">
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
+      <c r="J37" s="33"/>
+      <c r="K37" s="40" t="s">
         <v>178</v>
       </c>
-      <c r="L37" s="36" t="s">
+      <c r="L37" s="38" t="s">
         <v>207</v>
       </c>
-      <c r="M37" s="36"/>
-      <c r="N37" s="36"/>
-      <c r="O37" s="33"/>
-      <c r="P37" s="33"/>
-      <c r="Q37" s="33"/>
-      <c r="R37" s="33"/>
-      <c r="S37" s="33" t="s">
+      <c r="M37" s="38"/>
+      <c r="N37" s="38"/>
+      <c r="O37" s="35"/>
+      <c r="P37" s="35"/>
+      <c r="Q37" s="35"/>
+      <c r="R37" s="35"/>
+      <c r="S37" s="35" t="s">
         <v>272</v>
       </c>
-      <c r="T37" s="33" t="s">
+      <c r="T37" s="35" t="s">
         <v>281</v>
       </c>
-      <c r="U37" s="31" t="s">
+      <c r="U37" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="V37" s="31"/>
-      <c r="W37" s="31"/>
-      <c r="X37" s="35"/>
+      <c r="V37" s="33"/>
+      <c r="W37" s="33"/>
+      <c r="X37" s="37"/>
     </row>
-    <row r="38" s="13" customFormat="1" ht="115.95" spans="1:24">
-      <c r="A38" s="18"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="30" t="s">
-        <v>426</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="E38" s="30"/>
-      <c r="F38" s="2"/>
-      <c r="G38" s="31" t="s">
+    <row r="38" s="14" customFormat="1" ht="108.75" spans="1:24">
+      <c r="A38" s="19"/>
+      <c r="B38" s="31"/>
+      <c r="C38" s="32" t="s">
+        <v>433</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="E38" s="32"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="31"/>
-      <c r="L38" s="36"/>
-      <c r="M38" s="36"/>
-      <c r="N38" s="36"/>
-      <c r="O38" s="33"/>
-      <c r="P38" s="33"/>
-      <c r="Q38" s="33" t="s">
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
+      <c r="L38" s="38"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="38"/>
+      <c r="O38" s="35"/>
+      <c r="P38" s="35"/>
+      <c r="Q38" s="35" t="s">
         <v>263</v>
       </c>
-      <c r="R38" s="33"/>
-      <c r="S38" s="33"/>
-      <c r="T38" s="33"/>
-      <c r="U38" s="31" t="s">
+      <c r="R38" s="35"/>
+      <c r="S38" s="35"/>
+      <c r="T38" s="35"/>
+      <c r="U38" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="V38" s="31"/>
-      <c r="W38" s="31"/>
-      <c r="X38" s="35"/>
+      <c r="V38" s="33"/>
+      <c r="W38" s="33"/>
+      <c r="X38" s="37"/>
     </row>
-    <row r="39" s="12" customFormat="1" ht="144" spans="1:24">
-      <c r="A39" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" s="29" t="s">
-        <v>428</v>
-      </c>
-      <c r="C39" s="30" t="s">
-        <v>429</v>
-      </c>
-      <c r="D39" s="41" t="s">
-        <v>430</v>
-      </c>
-      <c r="E39" s="30"/>
-      <c r="F39" s="2"/>
-      <c r="G39" s="31" t="s">
+    <row r="39" s="13" customFormat="1" ht="135" spans="1:24">
+      <c r="A39" s="30" t="s">
+        <v>435</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>436</v>
+      </c>
+      <c r="C39" s="32" t="s">
+        <v>437</v>
+      </c>
+      <c r="D39" s="43" t="s">
+        <v>438</v>
+      </c>
+      <c r="E39" s="32"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
-      <c r="L39" s="36"/>
-      <c r="M39" s="36"/>
-      <c r="N39" s="36"/>
-      <c r="O39" s="33"/>
-      <c r="P39" s="33" t="s">
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="38"/>
+      <c r="M39" s="38"/>
+      <c r="N39" s="38"/>
+      <c r="O39" s="35"/>
+      <c r="P39" s="35" t="s">
         <v>245</v>
       </c>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="33"/>
-      <c r="S39" s="33"/>
-      <c r="T39" s="33"/>
-      <c r="U39" s="31" t="s">
+      <c r="Q39" s="35"/>
+      <c r="R39" s="35"/>
+      <c r="S39" s="35"/>
+      <c r="T39" s="35"/>
+      <c r="U39" s="33" t="s">
         <v>318</v>
       </c>
-      <c r="V39" s="31"/>
-      <c r="W39" s="31"/>
-      <c r="X39" s="35"/>
+      <c r="V39" s="33"/>
+      <c r="W39" s="33"/>
+      <c r="X39" s="37"/>
     </row>
-    <row r="40" customFormat="1" ht="216" spans="1:24">
-      <c r="A40" s="18"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="30" t="s">
-        <v>431</v>
-      </c>
-      <c r="D40" s="30" t="s">
-        <v>432</v>
-      </c>
-      <c r="E40" s="30"/>
-      <c r="F40" s="2"/>
-      <c r="G40" s="31" t="s">
+    <row r="40" customFormat="1" ht="189" spans="1:24">
+      <c r="A40" s="19"/>
+      <c r="B40" s="31"/>
+      <c r="C40" s="32" t="s">
+        <v>439</v>
+      </c>
+      <c r="D40" s="32" t="s">
+        <v>440</v>
+      </c>
+      <c r="E40" s="32"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
-      <c r="L40" s="36" t="s">
+      <c r="H40" s="33"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="33"/>
+      <c r="K40" s="33"/>
+      <c r="L40" s="38" t="s">
         <v>208</v>
       </c>
-      <c r="M40" s="36"/>
-      <c r="N40" s="36"/>
-      <c r="O40" s="33" t="s">
+      <c r="M40" s="38"/>
+      <c r="N40" s="38"/>
+      <c r="O40" s="35" t="s">
         <v>225</v>
       </c>
-      <c r="P40" s="33" t="s">
+      <c r="P40" s="35" t="s">
         <v>246</v>
       </c>
-      <c r="Q40" s="33"/>
-      <c r="R40" s="33"/>
-      <c r="S40" s="33"/>
-      <c r="T40" s="33"/>
-      <c r="U40" s="31" t="s">
+      <c r="Q40" s="35"/>
+      <c r="R40" s="35"/>
+      <c r="S40" s="35"/>
+      <c r="T40" s="35"/>
+      <c r="U40" s="33" t="s">
         <v>319</v>
       </c>
-      <c r="V40" s="31"/>
-      <c r="W40" s="31"/>
-      <c r="X40" s="35"/>
+      <c r="V40" s="33"/>
+      <c r="W40" s="33"/>
+      <c r="X40" s="37"/>
     </row>
-    <row r="41" customFormat="1" ht="129.6" spans="1:24">
-      <c r="A41" s="18"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="30" t="s">
-        <v>433</v>
-      </c>
-      <c r="D41" s="41" t="s">
-        <v>434</v>
-      </c>
-      <c r="E41" s="30"/>
-      <c r="F41" s="2"/>
-      <c r="G41" s="31" t="s">
+    <row r="41" customFormat="1" ht="121.5" spans="1:24">
+      <c r="A41" s="19"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="32" t="s">
+        <v>441</v>
+      </c>
+      <c r="D41" s="43" t="s">
+        <v>442</v>
+      </c>
+      <c r="E41" s="32"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="31"/>
-      <c r="L41" s="36" t="s">
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
+      <c r="L41" s="38" t="s">
         <v>209</v>
       </c>
-      <c r="M41" s="36"/>
-      <c r="N41" s="36"/>
-      <c r="O41" s="33"/>
-      <c r="P41" s="33" t="s">
+      <c r="M41" s="38"/>
+      <c r="N41" s="38"/>
+      <c r="O41" s="35"/>
+      <c r="P41" s="35" t="s">
         <v>247</v>
       </c>
-      <c r="Q41" s="33" t="s">
+      <c r="Q41" s="35" t="s">
         <v>264</v>
       </c>
-      <c r="R41" s="33"/>
-      <c r="S41" s="33"/>
-      <c r="T41" s="33"/>
-      <c r="U41" s="31" t="s">
+      <c r="R41" s="35"/>
+      <c r="S41" s="35"/>
+      <c r="T41" s="35"/>
+      <c r="U41" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="V41" s="31"/>
-      <c r="W41" s="31"/>
-      <c r="X41" s="35"/>
+      <c r="V41" s="33"/>
+      <c r="W41" s="33"/>
+      <c r="X41" s="37"/>
     </row>
-    <row r="42" customFormat="1" ht="172.8" spans="1:24">
-      <c r="A42" s="18"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="30" t="s">
-        <v>435</v>
-      </c>
-      <c r="D42" s="41" t="s">
-        <v>436</v>
-      </c>
-      <c r="E42" s="30"/>
-      <c r="F42" s="2"/>
-      <c r="G42" s="31" t="s">
+    <row r="42" customFormat="1" ht="162" spans="1:24">
+      <c r="A42" s="19"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="32" t="s">
+        <v>443</v>
+      </c>
+      <c r="D42" s="43" t="s">
+        <v>444</v>
+      </c>
+      <c r="E42" s="32"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H42" s="31"/>
-      <c r="I42" s="31"/>
-      <c r="J42" s="31"/>
-      <c r="K42" s="31"/>
-      <c r="L42" s="36" t="s">
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="38" t="s">
         <v>210</v>
       </c>
-      <c r="M42" s="36"/>
-      <c r="N42" s="36"/>
-      <c r="O42" s="33" t="s">
+      <c r="M42" s="38"/>
+      <c r="N42" s="38"/>
+      <c r="O42" s="35" t="s">
         <v>226</v>
       </c>
-      <c r="P42" s="33" t="s">
+      <c r="P42" s="35" t="s">
         <v>248</v>
       </c>
-      <c r="Q42" s="33"/>
-      <c r="R42" s="33"/>
-      <c r="S42" s="33"/>
-      <c r="T42" s="33" t="s">
+      <c r="Q42" s="35"/>
+      <c r="R42" s="35"/>
+      <c r="S42" s="35"/>
+      <c r="T42" s="35" t="s">
         <v>276</v>
       </c>
-      <c r="U42" s="39" t="s">
+      <c r="U42" s="41" t="s">
         <v>155</v>
       </c>
-      <c r="V42" s="39"/>
-      <c r="W42" s="39"/>
-      <c r="X42" s="37" t="s">
+      <c r="V42" s="41"/>
+      <c r="W42" s="41"/>
+      <c r="X42" s="39" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="216" spans="1:24">
-      <c r="A43" s="18"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="30" t="s">
-        <v>437</v>
-      </c>
-      <c r="D43" s="41" t="s">
-        <v>438</v>
-      </c>
-      <c r="E43" s="30"/>
-      <c r="F43" s="2"/>
-      <c r="G43" s="31" t="s">
+    <row r="43" customFormat="1" ht="189" spans="1:24">
+      <c r="A43" s="19"/>
+      <c r="B43" s="31"/>
+      <c r="C43" s="32" t="s">
+        <v>445</v>
+      </c>
+      <c r="D43" s="43" t="s">
+        <v>446</v>
+      </c>
+      <c r="E43" s="32"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H43" s="31"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-      <c r="K43" s="31"/>
-      <c r="L43" s="36" t="s">
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
+      <c r="J43" s="33"/>
+      <c r="K43" s="33"/>
+      <c r="L43" s="38" t="s">
         <v>211</v>
       </c>
-      <c r="M43" s="36"/>
-      <c r="N43" s="36"/>
-      <c r="O43" s="33" t="s">
+      <c r="M43" s="38"/>
+      <c r="N43" s="38"/>
+      <c r="O43" s="35" t="s">
         <v>226</v>
       </c>
-      <c r="P43" s="33" t="s">
+      <c r="P43" s="35" t="s">
         <v>249</v>
       </c>
-      <c r="Q43" s="33"/>
-      <c r="R43" s="33" t="s">
+      <c r="Q43" s="35"/>
+      <c r="R43" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="S43" s="33"/>
-      <c r="T43" s="33" t="s">
+      <c r="S43" s="35"/>
+      <c r="T43" s="35" t="s">
         <v>276</v>
       </c>
-      <c r="U43" s="31" t="s">
+      <c r="U43" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="V43" s="31"/>
-      <c r="W43" s="31"/>
-      <c r="X43" s="37" t="s">
+      <c r="V43" s="33"/>
+      <c r="W43" s="33"/>
+      <c r="X43" s="39" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="187.2" spans="1:24">
-      <c r="A44" s="18"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="30" t="s">
-        <v>439</v>
-      </c>
-      <c r="D44" s="41" t="s">
-        <v>440</v>
-      </c>
-      <c r="E44" s="30"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="31" t="s">
+    <row r="44" customFormat="1" ht="175.5" spans="1:24">
+      <c r="A44" s="19"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="32" t="s">
+        <v>447</v>
+      </c>
+      <c r="D44" s="43" t="s">
+        <v>448</v>
+      </c>
+      <c r="E44" s="32"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H44" s="31"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="31"/>
-      <c r="K44" s="31"/>
-      <c r="L44" s="36"/>
-      <c r="M44" s="36"/>
-      <c r="N44" s="36"/>
-      <c r="O44" s="33"/>
-      <c r="P44" s="33"/>
-      <c r="Q44" s="33"/>
-      <c r="R44" s="33"/>
-      <c r="S44" s="33"/>
-      <c r="T44" s="33"/>
-      <c r="U44" s="31" t="s">
+      <c r="H44" s="33"/>
+      <c r="I44" s="33"/>
+      <c r="J44" s="33"/>
+      <c r="K44" s="33"/>
+      <c r="L44" s="38"/>
+      <c r="M44" s="38"/>
+      <c r="N44" s="38"/>
+      <c r="O44" s="35"/>
+      <c r="P44" s="35"/>
+      <c r="Q44" s="35"/>
+      <c r="R44" s="35"/>
+      <c r="S44" s="35"/>
+      <c r="T44" s="35"/>
+      <c r="U44" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="V44" s="31"/>
-      <c r="W44" s="31"/>
-      <c r="X44" s="35"/>
+      <c r="V44" s="33"/>
+      <c r="W44" s="33"/>
+      <c r="X44" s="37"/>
     </row>
-    <row r="45" s="13" customFormat="1" ht="216.75" spans="1:24">
-      <c r="A45" s="18"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="30" t="s">
-        <v>441</v>
-      </c>
-      <c r="D45" s="41" t="s">
-        <v>442</v>
-      </c>
-      <c r="E45" s="30"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="31" t="s">
+    <row r="45" s="14" customFormat="1" ht="189.75" spans="1:24">
+      <c r="A45" s="19"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="32" t="s">
+        <v>449</v>
+      </c>
+      <c r="D45" s="43" t="s">
+        <v>450</v>
+      </c>
+      <c r="E45" s="32"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="H45" s="31"/>
-      <c r="I45" s="31"/>
-      <c r="J45" s="31"/>
-      <c r="K45" s="31"/>
-      <c r="L45" s="36" t="s">
+      <c r="H45" s="33"/>
+      <c r="I45" s="33"/>
+      <c r="J45" s="33"/>
+      <c r="K45" s="33"/>
+      <c r="L45" s="38" t="s">
         <v>212</v>
       </c>
-      <c r="M45" s="36"/>
-      <c r="N45" s="36"/>
-      <c r="O45" s="33"/>
-      <c r="P45" s="33" t="s">
+      <c r="M45" s="38"/>
+      <c r="N45" s="38"/>
+      <c r="O45" s="35"/>
+      <c r="P45" s="35" t="s">
         <v>250</v>
       </c>
-      <c r="Q45" s="33"/>
-      <c r="R45" s="33"/>
-      <c r="S45" s="33"/>
-      <c r="T45" s="33"/>
-      <c r="U45" s="31" t="s">
+      <c r="Q45" s="35"/>
+      <c r="R45" s="35"/>
+      <c r="S45" s="35"/>
+      <c r="T45" s="35"/>
+      <c r="U45" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="V45" s="31"/>
-      <c r="W45" s="31"/>
-      <c r="X45" s="35"/>
+      <c r="V45" s="33"/>
+      <c r="W45" s="33"/>
+      <c r="X45" s="37"/>
     </row>
-    <row r="46" s="12" customFormat="1" ht="158.4" spans="1:24">
-      <c r="A46" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="B46" s="29" t="s">
+    <row r="46" s="13" customFormat="1" ht="148.5" spans="1:24">
+      <c r="A46" s="30" t="s">
+        <v>451</v>
+      </c>
+      <c r="B46" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="C46" s="30" t="s">
-        <v>443</v>
-      </c>
-      <c r="D46" s="41" t="s">
-        <v>444</v>
-      </c>
-      <c r="E46" s="30"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="31" t="s">
+      <c r="C46" s="32" t="s">
+        <v>452</v>
+      </c>
+      <c r="D46" s="43" t="s">
+        <v>453</v>
+      </c>
+      <c r="E46" s="32"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="33" t="s">
         <v>166</v>
       </c>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="31"/>
-      <c r="K46" s="31"/>
-      <c r="L46" s="36" t="s">
+      <c r="H46" s="33"/>
+      <c r="I46" s="33"/>
+      <c r="J46" s="33"/>
+      <c r="K46" s="33"/>
+      <c r="L46" s="38" t="s">
         <v>213</v>
       </c>
-      <c r="M46" s="36"/>
-      <c r="N46" s="36"/>
-      <c r="O46" s="33" t="s">
+      <c r="M46" s="38"/>
+      <c r="N46" s="38"/>
+      <c r="O46" s="35" t="s">
         <v>227</v>
       </c>
-      <c r="P46" s="33" t="s">
+      <c r="P46" s="35" t="s">
         <v>251</v>
       </c>
-      <c r="Q46" s="33"/>
-      <c r="R46" s="33"/>
-      <c r="S46" s="33"/>
-      <c r="T46" s="33"/>
-      <c r="U46" s="31" t="s">
+      <c r="Q46" s="35"/>
+      <c r="R46" s="35"/>
+      <c r="S46" s="35"/>
+      <c r="T46" s="35"/>
+      <c r="U46" s="33" t="s">
         <v>320</v>
       </c>
-      <c r="V46" s="31"/>
-      <c r="W46" s="31"/>
-      <c r="X46" s="35"/>
+      <c r="V46" s="33"/>
+      <c r="W46" s="33"/>
+      <c r="X46" s="37"/>
     </row>
-    <row r="47" customFormat="1" ht="100.8" spans="1:24">
-      <c r="A47" s="18"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="30" t="s">
-        <v>445</v>
-      </c>
-      <c r="D47" s="41" t="s">
-        <v>446</v>
-      </c>
-      <c r="E47" s="30"/>
-      <c r="F47" s="2"/>
-      <c r="G47" s="31" t="s">
+    <row r="47" customFormat="1" ht="94.5" spans="1:24">
+      <c r="A47" s="19"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="32" t="s">
+        <v>454</v>
+      </c>
+      <c r="D47" s="43" t="s">
+        <v>455</v>
+      </c>
+      <c r="E47" s="32"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="33" t="s">
         <v>167</v>
       </c>
-      <c r="H47" s="31"/>
-      <c r="I47" s="31"/>
-      <c r="J47" s="31"/>
-      <c r="K47" s="31"/>
-      <c r="L47" s="36" t="s">
+      <c r="H47" s="33"/>
+      <c r="I47" s="33"/>
+      <c r="J47" s="33"/>
+      <c r="K47" s="33"/>
+      <c r="L47" s="38" t="s">
         <v>214</v>
       </c>
-      <c r="M47" s="36"/>
-      <c r="N47" s="36"/>
-      <c r="O47" s="33"/>
-      <c r="P47" s="33" t="s">
+      <c r="M47" s="38"/>
+      <c r="N47" s="38"/>
+      <c r="O47" s="35"/>
+      <c r="P47" s="35" t="s">
         <v>252</v>
       </c>
-      <c r="Q47" s="33"/>
-      <c r="R47" s="33"/>
-      <c r="S47" s="33"/>
-      <c r="T47" s="33" t="s">
+      <c r="Q47" s="35"/>
+      <c r="R47" s="35"/>
+      <c r="S47" s="35"/>
+      <c r="T47" s="35" t="s">
         <v>277</v>
       </c>
-      <c r="U47" s="31" t="s">
+      <c r="U47" s="33" t="s">
         <v>321</v>
       </c>
-      <c r="V47" s="31"/>
-      <c r="W47" s="31"/>
-      <c r="X47" s="35"/>
+      <c r="V47" s="33"/>
+      <c r="W47" s="33"/>
+      <c r="X47" s="37"/>
     </row>
-    <row r="48" s="13" customFormat="1" ht="144.75" spans="1:24">
-      <c r="A48" s="18"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="30" t="s">
-        <v>447</v>
-      </c>
-      <c r="D48" s="41" t="s">
-        <v>448</v>
-      </c>
-      <c r="E48" s="30"/>
-      <c r="F48" s="2"/>
-      <c r="G48" s="31" t="s">
+    <row r="48" s="14" customFormat="1" ht="135.75" spans="1:24">
+      <c r="A48" s="19"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="32" t="s">
+        <v>456</v>
+      </c>
+      <c r="D48" s="43" t="s">
+        <v>457</v>
+      </c>
+      <c r="E48" s="32"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="H48" s="31"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="31"/>
-      <c r="K48" s="31"/>
-      <c r="L48" s="36" t="s">
+      <c r="H48" s="33"/>
+      <c r="I48" s="33"/>
+      <c r="J48" s="33"/>
+      <c r="K48" s="33"/>
+      <c r="L48" s="38" t="s">
         <v>215</v>
       </c>
-      <c r="M48" s="36"/>
-      <c r="N48" s="36"/>
-      <c r="O48" s="33"/>
-      <c r="P48" s="33" t="s">
+      <c r="M48" s="38"/>
+      <c r="N48" s="38"/>
+      <c r="O48" s="35"/>
+      <c r="P48" s="35" t="s">
         <v>253</v>
       </c>
-      <c r="Q48" s="33"/>
-      <c r="R48" s="33"/>
-      <c r="S48" s="33"/>
-      <c r="T48" s="33"/>
-      <c r="U48" s="31" t="s">
+      <c r="Q48" s="35"/>
+      <c r="R48" s="35"/>
+      <c r="S48" s="35"/>
+      <c r="T48" s="35"/>
+      <c r="U48" s="33" t="s">
         <v>322</v>
       </c>
-      <c r="V48" s="31"/>
-      <c r="W48" s="31"/>
-      <c r="X48" s="35"/>
+      <c r="V48" s="33"/>
+      <c r="W48" s="33"/>
+      <c r="X48" s="37"/>
     </row>
-    <row r="49" s="12" customFormat="1" ht="187.2" spans="1:24">
-      <c r="A49" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B49" s="29" t="s">
+    <row r="49" s="13" customFormat="1" ht="175.5" spans="1:24">
+      <c r="A49" s="30" t="s">
+        <v>458</v>
+      </c>
+      <c r="B49" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="30" t="s">
-        <v>449</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="E49" s="30"/>
-      <c r="F49" s="2"/>
-      <c r="G49" s="31" t="s">
+      <c r="C49" s="32" t="s">
+        <v>459</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="E49" s="32"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="33" t="s">
         <v>169</v>
       </c>
-      <c r="H49" s="31"/>
-      <c r="I49" s="31"/>
-      <c r="J49" s="31"/>
-      <c r="K49" s="31"/>
-      <c r="L49" s="36"/>
-      <c r="M49" s="36"/>
-      <c r="N49" s="36"/>
-      <c r="O49" s="33" t="s">
+      <c r="H49" s="33"/>
+      <c r="I49" s="33"/>
+      <c r="J49" s="33"/>
+      <c r="K49" s="33"/>
+      <c r="L49" s="38"/>
+      <c r="M49" s="38"/>
+      <c r="N49" s="38"/>
+      <c r="O49" s="35" t="s">
         <v>228</v>
       </c>
-      <c r="P49" s="33" t="s">
+      <c r="P49" s="35" t="s">
         <v>254</v>
       </c>
-      <c r="Q49" s="33" t="s">
+      <c r="Q49" s="35" t="s">
         <v>265</v>
       </c>
-      <c r="R49" s="33"/>
-      <c r="S49" s="33"/>
-      <c r="T49" s="33"/>
-      <c r="U49" s="31" t="s">
+      <c r="R49" s="35"/>
+      <c r="S49" s="35"/>
+      <c r="T49" s="35"/>
+      <c r="U49" s="33" t="s">
         <v>323</v>
       </c>
-      <c r="V49" s="31"/>
-      <c r="W49" s="31"/>
-      <c r="X49" s="35"/>
+      <c r="V49" s="33"/>
+      <c r="W49" s="33"/>
+      <c r="X49" s="37"/>
     </row>
-    <row r="50" customFormat="1" ht="144" spans="1:24">
-      <c r="A50" s="18"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="30" t="s">
-        <v>451</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="E50" s="30"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="31" t="s">
+    <row r="50" customFormat="1" ht="135" spans="1:24">
+      <c r="A50" s="19"/>
+      <c r="B50" s="31"/>
+      <c r="C50" s="32" t="s">
+        <v>461</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>462</v>
+      </c>
+      <c r="E50" s="32"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="H50" s="31"/>
-      <c r="I50" s="31"/>
-      <c r="J50" s="31"/>
-      <c r="K50" s="31"/>
-      <c r="L50" s="36"/>
-      <c r="M50" s="36"/>
-      <c r="N50" s="36"/>
-      <c r="O50" s="33"/>
-      <c r="P50" s="33" t="s">
+      <c r="H50" s="33"/>
+      <c r="I50" s="33"/>
+      <c r="J50" s="33"/>
+      <c r="K50" s="33"/>
+      <c r="L50" s="38"/>
+      <c r="M50" s="38"/>
+      <c r="N50" s="38"/>
+      <c r="O50" s="35"/>
+      <c r="P50" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="Q50" s="33" t="s">
+      <c r="Q50" s="35" t="s">
         <v>266</v>
       </c>
-      <c r="R50" s="33"/>
-      <c r="S50" s="33"/>
-      <c r="T50" s="33"/>
-      <c r="U50" s="31" t="s">
+      <c r="R50" s="35"/>
+      <c r="S50" s="35"/>
+      <c r="T50" s="35"/>
+      <c r="U50" s="33" t="s">
         <v>324</v>
       </c>
-      <c r="V50" s="31"/>
-      <c r="W50" s="31"/>
-      <c r="X50" s="35"/>
+      <c r="V50" s="33"/>
+      <c r="W50" s="33"/>
+      <c r="X50" s="37"/>
     </row>
-    <row r="51" customFormat="1" ht="172.8" spans="1:24">
-      <c r="A51" s="18"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="30" t="s">
-        <v>453</v>
-      </c>
-      <c r="D51" s="41" t="s">
-        <v>454</v>
-      </c>
-      <c r="E51" s="30"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="31" t="s">
+    <row r="51" customFormat="1" ht="162" spans="1:24">
+      <c r="A51" s="19"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="32" t="s">
+        <v>463</v>
+      </c>
+      <c r="D51" s="43" t="s">
+        <v>464</v>
+      </c>
+      <c r="E51" s="32"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="33" t="s">
         <v>155</v>
       </c>
-      <c r="H51" s="31"/>
-      <c r="I51" s="31"/>
-      <c r="J51" s="31"/>
-      <c r="K51" s="31"/>
-      <c r="L51" s="36" t="s">
-        <v>455</v>
-      </c>
-      <c r="M51" s="36"/>
-      <c r="N51" s="36"/>
-      <c r="O51" s="33"/>
-      <c r="P51" s="33"/>
-      <c r="Q51" s="33"/>
-      <c r="R51" s="33"/>
-      <c r="S51" s="33"/>
-      <c r="T51" s="33" t="s">
+      <c r="H51" s="33"/>
+      <c r="I51" s="33"/>
+      <c r="J51" s="33"/>
+      <c r="K51" s="33"/>
+      <c r="L51" s="38" t="s">
+        <v>465</v>
+      </c>
+      <c r="M51" s="38"/>
+      <c r="N51" s="38"/>
+      <c r="O51" s="35"/>
+      <c r="P51" s="35"/>
+      <c r="Q51" s="35"/>
+      <c r="R51" s="35"/>
+      <c r="S51" s="35"/>
+      <c r="T51" s="35" t="s">
         <v>282</v>
       </c>
-      <c r="U51" s="31" t="s">
+      <c r="U51" s="33" t="s">
         <v>315</v>
       </c>
-      <c r="V51" s="31"/>
-      <c r="W51" s="31"/>
-      <c r="X51" s="35"/>
+      <c r="V51" s="33"/>
+      <c r="W51" s="33"/>
+      <c r="X51" s="37"/>
     </row>
-    <row r="52" s="13" customFormat="1" ht="144.75" spans="1:24">
-      <c r="A52" s="42"/>
-      <c r="B52" s="43"/>
-      <c r="C52" s="44" t="s">
-        <v>456</v>
-      </c>
-      <c r="D52" s="45" t="s">
-        <v>457</v>
-      </c>
-      <c r="E52" s="44"/>
-      <c r="F52" s="46"/>
-      <c r="G52" s="47" t="s">
+    <row r="52" s="14" customFormat="1" ht="122.25" spans="1:24">
+      <c r="A52" s="44"/>
+      <c r="B52" s="45"/>
+      <c r="C52" s="46" t="s">
+        <v>466</v>
+      </c>
+      <c r="D52" s="47" t="s">
+        <v>467</v>
+      </c>
+      <c r="E52" s="46"/>
+      <c r="F52" s="48"/>
+      <c r="G52" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="H52" s="47"/>
-      <c r="I52" s="47"/>
-      <c r="J52" s="47"/>
-      <c r="K52" s="47"/>
-      <c r="L52" s="48"/>
-      <c r="M52" s="48"/>
-      <c r="N52" s="48"/>
-      <c r="O52" s="49"/>
-      <c r="P52" s="49" t="s">
+      <c r="H52" s="49"/>
+      <c r="I52" s="49"/>
+      <c r="J52" s="49"/>
+      <c r="K52" s="49"/>
+      <c r="L52" s="50"/>
+      <c r="M52" s="50"/>
+      <c r="N52" s="50"/>
+      <c r="O52" s="51"/>
+      <c r="P52" s="51" t="s">
         <v>256</v>
       </c>
-      <c r="Q52" s="49" t="s">
+      <c r="Q52" s="51" t="s">
         <v>263</v>
       </c>
-      <c r="R52" s="49" t="s">
+      <c r="R52" s="51" t="s">
         <v>270</v>
       </c>
-      <c r="S52" s="49"/>
-      <c r="T52" s="49" t="s">
+      <c r="S52" s="51"/>
+      <c r="T52" s="51" t="s">
         <v>283</v>
       </c>
-      <c r="U52" s="47" t="s">
+      <c r="U52" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="V52" s="47"/>
-      <c r="W52" s="47"/>
-      <c r="X52" s="50"/>
+      <c r="V52" s="49"/>
+      <c r="W52" s="49"/>
+      <c r="X52" s="52"/>
     </row>
   </sheetData>
   <mergeCells count="179">
@@ -10661,7 +10774,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -10673,7 +10786,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -10683,161 +10796,320 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="3" max="3" width="21.25" customWidth="1"/>
+    <col min="4" max="4" width="77.1333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="9" t="s">
+        <v>468</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="7" t="s">
+        <v>474</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="4" ht="94.5" spans="1:4">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="5" ht="27" spans="1:4">
+      <c r="A5" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>489</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="9" ht="27" spans="1:4">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="7" t="s">
+        <v>494</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="11" ht="40.5" spans="1:4">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="12" ht="27" spans="1:4">
+      <c r="A12" s="12"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>499</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A1:A4"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="B1:B4"/>
+    <mergeCell ref="B8:B12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="39.8796296296296" customWidth="1"/>
+    <col min="2" max="2" width="39.8833333333333" customWidth="1"/>
     <col min="3" max="3" width="63.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="8"/>
+      <c r="A1" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="2"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="9"/>
-      <c r="B2" s="10" t="s">
-        <v>459</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>460</v>
+      <c r="A2" s="3"/>
+      <c r="B2" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>501</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="10"/>
-      <c r="C3" s="3" t="s">
-        <v>461</v>
+      <c r="A3" s="6"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="5" t="s">
+        <v>502</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="10"/>
-      <c r="C4" s="3" t="s">
-        <v>462</v>
+      <c r="A4" s="6"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="5" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="3" t="s">
-        <v>463</v>
+      <c r="A5" s="6"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="5" t="s">
+        <v>504</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="3"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="5"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="10" t="s">
-        <v>464</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>465</v>
+      <c r="A7" s="6"/>
+      <c r="B7" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="3" t="s">
-        <v>466</v>
+      <c r="A8" s="6"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="5" t="s">
+        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="3" t="s">
-        <v>467</v>
+      <c r="A9" s="6"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="5" t="s">
+        <v>508</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="3" t="s">
-        <v>468</v>
+      <c r="A10" s="6"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="5" t="s">
+        <v>509</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="3"/>
+      <c r="A11" s="6"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="5"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="10" t="s">
-        <v>469</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>470</v>
+      <c r="A12" s="6"/>
+      <c r="B12" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>511</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="3" t="s">
-        <v>471</v>
+      <c r="A13" s="6"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="5" t="s">
+        <v>512</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="10"/>
-      <c r="C14" s="3" t="s">
-        <v>472</v>
+      <c r="A14" s="6"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5" t="s">
+        <v>513</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="3" t="s">
-        <v>473</v>
+      <c r="A15" s="6"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="5" t="s">
+        <v>514</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="10"/>
-      <c r="C16" s="3" t="s">
-        <v>474</v>
+      <c r="A16" s="6"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="2"/>
-      <c r="C17" s="3"/>
+      <c r="A17" s="6"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="5"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="10" t="s">
-        <v>475</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>476</v>
+      <c r="A18" s="6"/>
+      <c r="B18" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>517</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="2" t="s">
-        <v>477</v>
+      <c r="A19" s="6"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="7" t="s">
+        <v>518</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="2" t="s">
-        <v>478</v>
+      <c r="A20" s="6"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="7" t="s">
+        <v>519</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="2" t="s">
-        <v>479</v>
+      <c r="A21" s="6"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="7" t="s">
+        <v>520</v>
       </c>
     </row>
   </sheetData>
@@ -10853,170 +11125,11 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
-  <cols>
-    <col min="2" max="2" width="31" customWidth="1"/>
-    <col min="3" max="3" width="21.25" customWidth="1"/>
-    <col min="4" max="4" width="77.1296296296296" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="4" ht="100.8" spans="1:4">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="5" ht="28.8" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="9" ht="28.8" spans="1:4">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="11" ht="43.2" spans="1:4">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="12" ht="28.8" spans="1:4">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>510</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:A4"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="B1:B4"/>
-    <mergeCell ref="B8:B12"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -11027,7 +11140,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="526">
   <si>
     <t>项目整合管理</t>
   </si>
@@ -3842,37 +3842,31 @@
 管理</t>
   </si>
   <si>
-    <t>工作内容：识别、协调项目管理各过程、活动，贯穿项目始终,具备建立联系和统一的性质</t>
+    <t>识别、联系、统一协调项目管理各过程，并贯穿项目始终</t>
   </si>
   <si>
     <t>制定项目章程
-（启动过程组）</t>
-  </si>
-  <si>
-    <t>1明确项目正式地位
-2确认组织战略目标联系
-3展示组织对项目的承诺
-4正式批准项目
-5授权项目经理使用组织资源</t>
-  </si>
-  <si>
-    <t>制定项目管理计划（规划过程组）</t>
-  </si>
-  <si>
-    <t>1确定项目工作的基础和执行方式
-2识别、定义、统一协调项目计划的各部分</t>
+（启动）</t>
+  </si>
+  <si>
+    <t>1确定项目正式地位、战略联系、组织承诺 2正式批准项目和授权项目经理使用组织资源</t>
+  </si>
+  <si>
+    <t>制定项目管理计划（规划）</t>
+  </si>
+  <si>
+    <t>1识别、定义、联系、统一协调项目管理计划的各部分
+2确定项目工作基础和执行方式</t>
   </si>
   <si>
     <t>项目管理子计划</t>
   </si>
   <si>
-    <t>指导与管理项目工作（执行过程组）</t>
-  </si>
-  <si>
-    <t>1提高项目成功可能性
-2执行项目管理计划中的工作
-3实施已批准的变更请求
-4管理项目工作和可交付成果</t>
+    <t>指导与管理项目工作（执行）</t>
+  </si>
+  <si>
+    <t>1执行项目管理计划中的工作 2实施已批准的变更请求
+3管理项目工作和可交付成果</t>
   </si>
   <si>
     <t>可交付成果
@@ -3881,73 +3875,66 @@
 变更请求</t>
   </si>
   <si>
-    <t>管理项目知识（执行过程组）</t>
-  </si>
-  <si>
-    <t>1已有知识用来创造和改进项目成果
-2新知识可用来支持组织运营和未来项目
-3使用已有知识
-4生成新知识
-5帮助组织学习并实现项目目标</t>
-  </si>
-  <si>
-    <t>监控项目工作（监控过程组）</t>
-  </si>
-  <si>
-    <t>1实现项目管理计划中定的绩效目标
-2让干系人了解项目当前状况
-3让干系人认可处理绩效问题的行动
-3对项目进展进行跟踪、审查、报告
-4通过成本和进度预测了解项目未来状态</t>
+    <t>管理项目知识（执行）</t>
+  </si>
+  <si>
+    <t>1使用已有的知识创造改进项目成果
+2生成的新知识支持组织运营和未来项目</t>
+  </si>
+  <si>
+    <t>监控项目工作（监控）</t>
+  </si>
+  <si>
+    <t>1对项目进展进行跟踪、审查、报告
+2通过成本进度情况预测项目未来状态
+3使干系人了解项目情况和认可项目行动</t>
   </si>
   <si>
     <t>工作绩效信息（非数据）
 协议</t>
   </si>
   <si>
-    <t>实施整体变更控制（监控过程组）</t>
-  </si>
-  <si>
-    <t>1管理、审查、批准可交付成果、项目文件、项目管理计划的变更
-2沟通变更处理结果</t>
-  </si>
-  <si>
-    <t>结束项目或阶段（收尾过程组）</t>
-  </si>
-  <si>
-    <t>1终结项目、阶段的所有活动
-2存档项目、阶段信息
-3释放组织团队资源</t>
+    <t>实施整体变更控制（监控）</t>
+  </si>
+  <si>
+    <t>1管理、沟通、审查、批准项目可交付成果、项目管理计划、项目文件的变更</t>
+  </si>
+  <si>
+    <t>结束项目或阶段（收尾）</t>
+  </si>
+  <si>
+    <t>1存档项目阶段信息
+2释放资源
+3终结项目阶段活动</t>
   </si>
   <si>
     <t>项目范围
 管理</t>
   </si>
   <si>
-    <t>定义和控制项目、产品的范围,确保项目只做需要做的全部工作</t>
-  </si>
-  <si>
-    <t>规划范围管理（规划过程组）</t>
-  </si>
-  <si>
-    <t>1作为管理项目范围的指南和方向
-2定义、确认、控制项目范围</t>
-  </si>
-  <si>
-    <t>收集需求（规划过程组）</t>
-  </si>
-  <si>
-    <t>1是定义产品范围和项目范围的基础
-2确定、记录、管理干系人需要和需求</t>
-  </si>
-  <si>
-    <t>定义范围（规划过程组）</t>
-  </si>
-  <si>
-    <t>1对项目产品、服务成果的边界和验收标准的详细描述</t>
-  </si>
-  <si>
-    <t>创建WBS（规划过程组）</t>
+    <t>定义、规划和控制项目范围和产品范围--不超范围</t>
+  </si>
+  <si>
+    <t>规划范围管理（规划）</t>
+  </si>
+  <si>
+    <t>1定义、确认、控制项目范围 2作为管理项目范围的指南方向</t>
+  </si>
+  <si>
+    <t>收集需求（规划）</t>
+  </si>
+  <si>
+    <t>1确定、记录、管理干系人需求
+2作为产品范围和项目范围的基础</t>
+  </si>
+  <si>
+    <t>定义范围（规划）</t>
+  </si>
+  <si>
+    <t>1详细描述项目产品、服务成果的边界和验收标准</t>
+  </si>
+  <si>
+    <t>创建WBS（规划）</t>
   </si>
   <si>
     <t>1确定进度基准
@@ -3955,7 +3942,7 @@
 3把项目可交付成果、工作分解成小且易管理的组件</t>
   </si>
   <si>
-    <t>确认范围（监控过程组）</t>
+    <t>确认范围（监控）</t>
   </si>
   <si>
     <t>1提高最终产品、服务成果被验收的可能性
@@ -3965,7 +3952,7 @@
     <t>验收的可交付成果</t>
   </si>
   <si>
-    <t>控制范围（监控过程组）</t>
+    <t>控制范围（监控）</t>
   </si>
   <si>
     <t>1监督项目和产品的范围
@@ -3977,41 +3964,44 @@
 管理</t>
   </si>
   <si>
-    <t>规划进度管理（规划过程组）</t>
+    <t>对项目进度进行规划、估算、管理、控制的过程--批准时间内</t>
+  </si>
+  <si>
+    <t>规划进度管理（规划）</t>
   </si>
   <si>
     <t>1是管理项目进度的指南和方向
 2规划、编制、管理、执行、控制项目进度</t>
   </si>
   <si>
-    <t>定义活动（规划过程组）</t>
+    <t>定义活动（规划）</t>
   </si>
   <si>
     <t>1为完成项目可交付成果，将工作包分解为进度活动
 2是项目进度估算、规划、执行、监督和控制的基础</t>
   </si>
   <si>
-    <t>排列活动顺序（规划过程组）</t>
+    <t>排列活动顺序（规划）</t>
   </si>
   <si>
     <t>1识别记录项目活动之间逻辑关系
 2使项目在制约因素下获得最高的效率</t>
   </si>
   <si>
-    <t>估算活动持续时间（规划过程组）</t>
+    <t>估算活动持续时间（规划）</t>
   </si>
   <si>
     <t>1估算完成单项活动所需花费的时间量</t>
   </si>
   <si>
-    <t>制定进度计划（规划过程组）</t>
+    <t>制定进度计划（规划）</t>
   </si>
   <si>
     <t>1确定进度基准
 2创建具有计划日期的进度模型，以便项目执行和监控3分析活动顺序、持续时间、资源需求和进度制约因素，</t>
   </si>
   <si>
-    <t>控制进度（监控过程组）</t>
+    <t>控制进度（监控）</t>
   </si>
   <si>
     <t>1维护进度基准
@@ -4024,24 +4014,24 @@
 管理</t>
   </si>
   <si>
-    <t>对成本进行规划、估算、预算、筹资、管理和控制，使得项目在预算内完成</t>
-  </si>
-  <si>
-    <t>规划成本管理（规划过程组）</t>
+    <t>对项目成本进行规划、估算、预算、筹资、管理、控制的过程--预算内</t>
+  </si>
+  <si>
+    <t>规划成本管理（规划）</t>
   </si>
   <si>
     <t>1管理项目成本的指南和方向
 2估算、预算、管理、监督、控制项目成本</t>
   </si>
   <si>
-    <t>估算成本（规划过程组）</t>
+    <t>估算成本（规划）</t>
   </si>
   <si>
     <t>1确定项目所需的资金
 2对项目所需资源成本进行近似估算</t>
   </si>
   <si>
-    <t>制定预算（规划过程组）</t>
+    <t>制定预算（规划）</t>
   </si>
   <si>
     <t>1确定项目成本基准
@@ -4049,7 +4039,7 @@
 3汇总所有活动、工作包的估算成本</t>
   </si>
   <si>
-    <t>控制成本（监控过程组）</t>
+    <t>控制成本（监控）</t>
   </si>
   <si>
     <t>1维护成本基准
@@ -4066,17 +4056,16 @@
 管理</t>
   </si>
   <si>
-    <t>确定质量目标方针，并执行质量规划、保证、控
-制、改进的活动</t>
-  </si>
-  <si>
-    <t>规划质量管理（规划过程组）</t>
+    <t>对项目质量进行规划、保证、控制、改进的过程--质量目标内</t>
+  </si>
+  <si>
+    <t>规划质量管理（规划）</t>
   </si>
   <si>
     <t>1规划并证明，识别可交付成果质量的要求和标准</t>
   </si>
   <si>
-    <t>管理质量（执行过程组）</t>
+    <t>管理质量（执行）</t>
   </si>
   <si>
     <t>1将质量管理计划转化质量活动
@@ -4086,7 +4075,7 @@
 5识别无效过程和导致质量低劣的原因</t>
   </si>
   <si>
-    <t>控制质量（监控过程组）</t>
+    <t>控制质量（监控）</t>
   </si>
   <si>
     <t>1核实项目可交付成果满足最终验收质量要求
@@ -4098,21 +4087,24 @@
 管理</t>
   </si>
   <si>
-    <t>规划资源管理（规划过程组）</t>
+    <t>对项目团队资源和实物资源进行规划、估算、获取、管理、控制的过程--批准资源内</t>
+  </si>
+  <si>
+    <t>规划资源管理（规划）</t>
   </si>
   <si>
     <t>1确定适用于项目资源的管理方法和管理程度
 2估算、获取、管理和利用团队及其实物资源</t>
   </si>
   <si>
-    <t>估算活动资源（规划过程组）</t>
+    <t>估算活动资源（规划）</t>
   </si>
   <si>
     <t>1明确完成项目所需的资源种类、数量和特性
 2估算执行项目所需的团队资源和实物资源如：材料、设备的类型和数量</t>
   </si>
   <si>
-    <t>获取资源（执行过程组）</t>
+    <t>获取资源（执行）</t>
   </si>
   <si>
     <t>1概述和指导资源的选择
@@ -4120,21 +4112,21 @@
 3获取项目所需的团队资源和实物资源</t>
   </si>
   <si>
-    <t>建设团队（执行过程组）</t>
+    <t>建设团队（执行）</t>
   </si>
   <si>
     <t>1改进团队协作、人际关系、激励员工，减少摩擦、提升项目绩效
 2提高工作能力，促进团队成员互动，改善团队整体氛围，以提高项目绩效的过程</t>
   </si>
   <si>
-    <t>管理团队（执行过程组）</t>
+    <t>管理团队（执行）</t>
   </si>
   <si>
     <t>1影响团队行为、管理冲突、解决问题
 2跟踪团队成员工作表现、提供反馈、解决问题并管理团队变更以优化项目绩效的过程</t>
   </si>
   <si>
-    <t>控制资源（监控过程组）</t>
+    <t>控制资源（监控）</t>
   </si>
   <si>
     <t>1确保按计划为项目分配实物资源
@@ -4147,7 +4139,10 @@
 管理</t>
   </si>
   <si>
-    <t>规划沟通管理（规划过程组）</t>
+    <t>对项目沟通进行规划、管理、控制的过程</t>
+  </si>
+  <si>
+    <t>规划沟通管理（规划）</t>
   </si>
   <si>
     <t>1基于每个干系人的息需求、组织资产、项目的需求编制书面沟通计划
@@ -4160,14 +4155,14 @@
 沟通方法（互动、推式、拉式）</t>
   </si>
   <si>
-    <t>管理沟通（执行过程组）</t>
+    <t>管理沟通（执行）</t>
   </si>
   <si>
     <t>1促成干系人之间的有效信息流动
 2确保项目信息及时且恰当的收集、生成、发布、存储、检索、管理、监督和最终处置</t>
   </si>
   <si>
-    <t>监督沟通（监控过程组）</t>
+    <t>监督沟通（监控）</t>
   </si>
   <si>
     <t>1按沟通管理计划和干系人参与计划的要求优化信息传递流程
@@ -4178,17 +4173,17 @@
 管理</t>
   </si>
   <si>
-    <t>项目内对风险进行规划、识别、分析、管理和控制的过程</t>
-  </si>
-  <si>
-    <t>规划风险管理（规划过程组）</t>
+    <t>对项目风险进行规划、识别、分析、管理、控制的过程</t>
+  </si>
+  <si>
+    <t>规划风险管理（规划）</t>
   </si>
   <si>
     <t>1定义如何实施项目风险管理活动
 2确保风险管理的水平、方法和可见度与项目风险程度和对组织干系人重要重读相匹配</t>
   </si>
   <si>
-    <t>识别风险（规划过程组）</t>
+    <t>识别风险（规划）</t>
   </si>
   <si>
     <r>
@@ -4238,7 +4233,7 @@
     </r>
   </si>
   <si>
-    <t>实施定性风险分析（规划过程组）</t>
+    <t>实施定性风险分析（规划）</t>
   </si>
   <si>
     <t xml:space="preserve">1重点关注高优先级的风险
@@ -4246,7 +4241,7 @@
 </t>
   </si>
   <si>
-    <t>实施定量风险分析（规划过程组）</t>
+    <t>实施定量风险分析（规划）</t>
   </si>
   <si>
     <t xml:space="preserve">1量化整体项目风险最大可能性
@@ -4255,7 +4250,7 @@
 </t>
   </si>
   <si>
-    <t>规划风险应对（规划过程组）</t>
+    <t>规划风险应对（规划）</t>
   </si>
   <si>
     <t>1应对项目风险，而制定可选方案、应对策略并商定应对行动
@@ -4264,7 +4259,7 @@
 4根据需要将相关活动添加进项目文件和项目管理计划中</t>
   </si>
   <si>
-    <t>实施风险应对（执行过程组）</t>
+    <t>实施风险应对（执行）</t>
   </si>
   <si>
     <t>1执行商定的风险应对计划的过程
@@ -4273,7 +4268,7 @@
 3管理整体项目风险入口、最小化单个项目威胁，以及最大化单个项目机会</t>
   </si>
   <si>
-    <t>监督风险（监控过程组）</t>
+    <t>监督风险（监控）</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -4285,21 +4280,24 @@
 管理</t>
   </si>
   <si>
-    <t>规划采购管理（规划过程组）</t>
+    <t>对项目采购进行规划、管理、控制的过程</t>
+  </si>
+  <si>
+    <t>规划采购管理（规划）</t>
   </si>
   <si>
     <t>1确定是否从项目外部获取货物和服务，2确定将在什么时间、以什么方式获取什么货物和服务
 3记录项目采购决策、明确采购方法，及识别潜在卖方</t>
   </si>
   <si>
-    <t>实施采购（执行过程组）</t>
+    <t>实施采购（执行）</t>
   </si>
   <si>
     <t>1选定合格卖方并签署关于货物或服务交付的法律协议
 2获取卖方应答、选择卖方并授予合同</t>
   </si>
   <si>
-    <t>控制采购（监控过程组）</t>
+    <t>控制采购（监控）</t>
   </si>
   <si>
     <t>1确保买卖双方履行法律协议，满足项目需求
@@ -4310,21 +4308,24 @@
 人管理 </t>
   </si>
   <si>
-    <t>识别干系人（启动过程组）</t>
+    <t>对项目干系人进行识别、规划、管理、控制的过程--维持提升满意度</t>
+  </si>
+  <si>
+    <t>识别干系人（启动）</t>
   </si>
   <si>
     <t>1使项目团队能够建立对每个干系人或干系人群体的适度关注
 2定期识别项目干系人，分析和记录他们的利益、参与度、项目依赖性、影响力和对项目成功的潜在影响</t>
   </si>
   <si>
-    <t>规划干系人参与（规划过程组）</t>
+    <t>规划干系人参与（规划）</t>
   </si>
   <si>
     <t>1提供与干系人进行有效互动的可行计划
 2根据干系人的需求、期望、利益和对项目的潜在影响，制定项目干系人参与项目的方法</t>
   </si>
   <si>
-    <t>管理干系人参与（执行过程组）</t>
+    <t>管理干系人参与（执行）</t>
   </si>
   <si>
     <t>1尽可能提高干系人的支持度，并降低干系人的抵制程度
@@ -4334,7 +4335,7 @@
     <t>基本规则</t>
   </si>
   <si>
-    <t>监督干系人参与（监控过程组）</t>
+    <t>监督干系人参与（监控）</t>
   </si>
   <si>
     <t>1维持或提升干系人参与活动的效率和效果
@@ -4464,6 +4465,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>项目建议书内容</t>
     </r>
     <r>
@@ -4492,6 +4500,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>可行性研究的内容【</t>
     </r>
     <r>
@@ -4533,6 +4548,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>技术可行性分析内容【</t>
     </r>
     <r>
@@ -8647,7 +8669,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="4" s="13" customFormat="1" ht="121.5" spans="1:24">
+    <row r="4" s="13" customFormat="1" ht="94.5" spans="1:24">
       <c r="A4" s="30" t="s">
         <v>348</v>
       </c>
@@ -8689,7 +8711,7 @@
       <c r="W4" s="33"/>
       <c r="X4" s="37"/>
     </row>
-    <row r="5" ht="81" spans="1:24">
+    <row r="5" ht="94.5" spans="1:24">
       <c r="A5" s="19"/>
       <c r="B5" s="31"/>
       <c r="C5" s="32" t="s">
@@ -8727,7 +8749,7 @@
       <c r="W5" s="33"/>
       <c r="X5" s="37"/>
     </row>
-    <row r="6" ht="108" spans="1:24">
+    <row r="6" ht="81" spans="1:24">
       <c r="A6" s="19"/>
       <c r="B6" s="31"/>
       <c r="C6" s="32" t="s">
@@ -8761,7 +8783,7 @@
       <c r="W6" s="33"/>
       <c r="X6" s="37"/>
     </row>
-    <row r="7" ht="148.5" spans="1:24">
+    <row r="7" ht="81" spans="1:24">
       <c r="A7" s="19"/>
       <c r="B7" s="31"/>
       <c r="C7" s="32" t="s">
@@ -8797,7 +8819,7 @@
       <c r="W7" s="33"/>
       <c r="X7" s="37"/>
     </row>
-    <row r="8" customFormat="1" ht="189" spans="1:24">
+    <row r="8" customFormat="1" ht="121.5" spans="1:24">
       <c r="A8" s="19"/>
       <c r="B8" s="31"/>
       <c r="C8" s="32" t="s">
@@ -8835,7 +8857,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="94.5" spans="1:24">
+    <row r="9" customFormat="1" ht="81" spans="1:24">
       <c r="A9" s="19"/>
       <c r="B9" s="31"/>
       <c r="C9" s="32" t="s">
@@ -8873,7 +8895,7 @@
       <c r="W9" s="33"/>
       <c r="X9" s="37"/>
     </row>
-    <row r="10" s="14" customFormat="1" ht="81.75" spans="1:24">
+    <row r="10" s="14" customFormat="1" ht="68.25" spans="1:24">
       <c r="A10" s="19"/>
       <c r="B10" s="31"/>
       <c r="C10" s="32" t="s">
@@ -9162,13 +9184,13 @@
         <v>382</v>
       </c>
       <c r="B17" s="31" t="s">
-        <v>12</v>
+        <v>383</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E17" s="32"/>
       <c r="F17" s="7"/>
@@ -9199,10 +9221,10 @@
       <c r="A18" s="19"/>
       <c r="B18" s="31"/>
       <c r="C18" s="32" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="E18" s="32"/>
       <c r="F18" s="7"/>
@@ -9235,10 +9257,10 @@
       <c r="A19" s="19"/>
       <c r="B19" s="31"/>
       <c r="C19" s="32" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E19" s="32"/>
       <c r="F19" s="7"/>
@@ -9271,10 +9293,10 @@
       <c r="A20" s="19"/>
       <c r="B20" s="31"/>
       <c r="C20" s="32" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E20" s="32"/>
       <c r="F20" s="7"/>
@@ -9309,10 +9331,10 @@
       <c r="A21" s="19"/>
       <c r="B21" s="31"/>
       <c r="C21" s="32" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E21" s="32"/>
       <c r="F21" s="7"/>
@@ -9347,10 +9369,10 @@
       <c r="A22" s="19"/>
       <c r="B22" s="31"/>
       <c r="C22" s="32" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E22" s="32"/>
       <c r="F22" s="7"/>
@@ -9383,16 +9405,16 @@
     </row>
     <row r="23" s="13" customFormat="1" ht="67.5" spans="1:24">
       <c r="A23" s="30" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B23" s="31" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C23" s="32" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="E23" s="32"/>
       <c r="F23" s="7"/>
@@ -9423,10 +9445,10 @@
       <c r="A24" s="19"/>
       <c r="B24" s="31"/>
       <c r="C24" s="32" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E24" s="32"/>
       <c r="F24" s="7"/>
@@ -9461,10 +9483,10 @@
       <c r="A25" s="19"/>
       <c r="B25" s="31"/>
       <c r="C25" s="32" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E25" s="32"/>
       <c r="F25" s="7"/>
@@ -9499,10 +9521,10 @@
       <c r="A26" s="19"/>
       <c r="B26" s="31"/>
       <c r="C26" s="32" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E26" s="32"/>
       <c r="F26" s="7"/>
@@ -9527,7 +9549,7 @@
       <c r="S26" s="35"/>
       <c r="T26" s="35"/>
       <c r="U26" s="33" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="V26" s="33"/>
       <c r="W26" s="33"/>
@@ -9535,16 +9557,16 @@
     </row>
     <row r="27" s="13" customFormat="1" ht="67.5" spans="1:24">
       <c r="A27" s="30" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B27" s="31" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C27" s="32" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="E27" s="32"/>
       <c r="F27" s="7"/>
@@ -9583,10 +9605,10 @@
       <c r="A28" s="19"/>
       <c r="B28" s="31"/>
       <c r="C28" s="32" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="7"/>
@@ -9627,10 +9649,10 @@
       <c r="A29" s="19"/>
       <c r="B29" s="31"/>
       <c r="C29" s="32" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E29" s="32"/>
       <c r="F29" s="7"/>
@@ -9667,16 +9689,16 @@
     </row>
     <row r="30" s="13" customFormat="1" ht="108" spans="1:24">
       <c r="A30" s="30" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>15</v>
+        <v>416</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="7"/>
@@ -9711,10 +9733,10 @@
       <c r="A31" s="19"/>
       <c r="B31" s="31"/>
       <c r="C31" s="32" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="7"/>
@@ -9747,10 +9769,10 @@
       <c r="A32" s="19"/>
       <c r="B32" s="31"/>
       <c r="C32" s="32" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="7"/>
@@ -9787,10 +9809,10 @@
       <c r="A33" s="19"/>
       <c r="B33" s="31"/>
       <c r="C33" s="32" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E33" s="32"/>
       <c r="F33" s="7"/>
@@ -9825,10 +9847,10 @@
       <c r="A34" s="19"/>
       <c r="B34" s="31"/>
       <c r="C34" s="32" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="7"/>
@@ -9861,10 +9883,10 @@
       <c r="A35" s="19"/>
       <c r="B35" s="31"/>
       <c r="C35" s="32" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="7"/>
@@ -9897,16 +9919,16 @@
     </row>
     <row r="36" s="13" customFormat="1" ht="121.5" spans="1:24">
       <c r="A36" s="30" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="B36" s="31" t="s">
-        <v>16</v>
+        <v>430</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="7"/>
@@ -9918,7 +9940,7 @@
       <c r="J36" s="33"/>
       <c r="K36" s="33"/>
       <c r="L36" s="38" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="M36" s="38"/>
       <c r="N36" s="38"/>
@@ -9943,10 +9965,10 @@
       <c r="A37" s="19"/>
       <c r="B37" s="31"/>
       <c r="C37" s="32" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="7"/>
@@ -9985,10 +10007,10 @@
       <c r="A38" s="19"/>
       <c r="B38" s="31"/>
       <c r="C38" s="32" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E38" s="32"/>
       <c r="F38" s="7"/>
@@ -10019,16 +10041,16 @@
     </row>
     <row r="39" s="13" customFormat="1" ht="135" spans="1:24">
       <c r="A39" s="30" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="E39" s="32"/>
       <c r="F39" s="7"/>
@@ -10061,10 +10083,10 @@
       <c r="A40" s="19"/>
       <c r="B40" s="31"/>
       <c r="C40" s="32" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D40" s="32" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E40" s="32"/>
       <c r="F40" s="7"/>
@@ -10101,10 +10123,10 @@
       <c r="A41" s="19"/>
       <c r="B41" s="31"/>
       <c r="C41" s="32" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="D41" s="43" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E41" s="32"/>
       <c r="F41" s="7"/>
@@ -10141,10 +10163,10 @@
       <c r="A42" s="19"/>
       <c r="B42" s="31"/>
       <c r="C42" s="32" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E42" s="32"/>
       <c r="F42" s="7"/>
@@ -10185,10 +10207,10 @@
       <c r="A43" s="19"/>
       <c r="B43" s="31"/>
       <c r="C43" s="32" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="E43" s="32"/>
       <c r="F43" s="7"/>
@@ -10231,10 +10253,10 @@
       <c r="A44" s="19"/>
       <c r="B44" s="31"/>
       <c r="C44" s="32" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E44" s="32"/>
       <c r="F44" s="7"/>
@@ -10265,10 +10287,10 @@
       <c r="A45" s="19"/>
       <c r="B45" s="31"/>
       <c r="C45" s="32" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D45" s="43" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E45" s="32"/>
       <c r="F45" s="7"/>
@@ -10301,16 +10323,16 @@
     </row>
     <row r="46" s="13" customFormat="1" ht="148.5" spans="1:24">
       <c r="A46" s="30" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B46" s="31" t="s">
-        <v>18</v>
+        <v>455</v>
       </c>
       <c r="C46" s="32" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D46" s="43" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="E46" s="32"/>
       <c r="F46" s="7"/>
@@ -10347,10 +10369,10 @@
       <c r="A47" s="19"/>
       <c r="B47" s="31"/>
       <c r="C47" s="32" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D47" s="43" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E47" s="32"/>
       <c r="F47" s="7"/>
@@ -10387,10 +10409,10 @@
       <c r="A48" s="19"/>
       <c r="B48" s="31"/>
       <c r="C48" s="32" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D48" s="43" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E48" s="32"/>
       <c r="F48" s="7"/>
@@ -10423,16 +10445,16 @@
     </row>
     <row r="49" s="13" customFormat="1" ht="175.5" spans="1:24">
       <c r="A49" s="30" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B49" s="31" t="s">
-        <v>19</v>
+        <v>463</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="E49" s="32"/>
       <c r="F49" s="7"/>
@@ -10469,10 +10491,10 @@
       <c r="A50" s="19"/>
       <c r="B50" s="31"/>
       <c r="C50" s="32" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="E50" s="32"/>
       <c r="F50" s="7"/>
@@ -10507,10 +10529,10 @@
       <c r="A51" s="19"/>
       <c r="B51" s="31"/>
       <c r="C51" s="32" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="D51" s="43" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="E51" s="32"/>
       <c r="F51" s="7"/>
@@ -10522,7 +10544,7 @@
       <c r="J51" s="33"/>
       <c r="K51" s="33"/>
       <c r="L51" s="38" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="M51" s="38"/>
       <c r="N51" s="38"/>
@@ -10545,10 +10567,10 @@
       <c r="A52" s="44"/>
       <c r="B52" s="45"/>
       <c r="C52" s="46" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="D52" s="47" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="E52" s="46"/>
       <c r="F52" s="48"/>
@@ -10806,138 +10828,138 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="9" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
       <c r="C2" s="7" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="7" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="4" ht="94.5" spans="1:4">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="5" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="5" ht="27" spans="1:4">
       <c r="A5" s="7" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="7" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="7" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="10" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:4">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="7" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
       <c r="C10" s="7" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" ht="40.5" spans="1:4">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="7" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="12" ht="27" spans="1:4">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="7" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
   </sheetData>
@@ -10965,7 +10987,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
@@ -10973,31 +10995,31 @@
     <row r="2" spans="1:3">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -11008,31 +11030,31 @@
     <row r="7" spans="1:3">
       <c r="A7" s="6"/>
       <c r="B7" s="8" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -11043,38 +11065,38 @@
     <row r="12" spans="1:3">
       <c r="A12" s="6"/>
       <c r="B12" s="8" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="6"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6"/>
       <c r="B14" s="4"/>
       <c r="C14" s="5" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6"/>
       <c r="B15" s="4"/>
       <c r="C15" s="5" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="6"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -11085,31 +11107,31 @@
     <row r="18" spans="1:3">
       <c r="A18" s="6"/>
       <c r="B18" s="8" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
       <c r="C19" s="7" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6"/>
       <c r="B20" s="4"/>
       <c r="C20" s="7" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="6"/>
       <c r="B21" s="4"/>
       <c r="C21" s="7" t="s">
-        <v>520</v>
+        <v>525</v>
       </c>
     </row>
   </sheetData>

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="29868" windowHeight="13500" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="49过程输入输出工具-横版" sheetId="1" state="hidden" r:id="rId1"/>
@@ -3918,7 +3918,8 @@
     <t>规划范围管理（规划）</t>
   </si>
   <si>
-    <t>1定义、确认、控制项目范围 2作为管理项目范围的指南方向</t>
+    <t>1定义、确认、控制项目范围
+2作为管理项目范围的指南</t>
   </si>
   <si>
     <t>收集需求（规划）</t>
@@ -3937,16 +3938,15 @@
     <t>创建WBS（规划）</t>
   </si>
   <si>
-    <t>1确定进度基准
-2形成交付内容架构
-3把项目可交付成果、工作分解成小且易管理的组件</t>
+    <t>1把项目工作和可交付成果分解成易管理的小组件
+2确定范围基准</t>
   </si>
   <si>
     <t>确认范围（监控）</t>
   </si>
   <si>
-    <t>1提高最终产品、服务成果被验收的可能性
-2客观性的验收项目可交付成果</t>
+    <t>1验收项目可交付成果
+2提高可交付成果最终验收可能</t>
   </si>
   <si>
     <t>验收的可交付成果</t>
@@ -3955,9 +3955,7 @@
     <t>控制范围（监控）</t>
   </si>
   <si>
-    <t>1监督项目和产品的范围
-2维护项目范围基准
-3管理范围基准变更</t>
+    <t>1监督项目范围和产品范围 2维护范围基准、管理范围基准变更</t>
   </si>
   <si>
     <t>项目进度
@@ -3970,44 +3968,41 @@
     <t>规划进度管理（规划）</t>
   </si>
   <si>
-    <t>1是管理项目进度的指南和方向
-2规划、编制、管理、执行、控制项目进度</t>
+    <t>1规划、编制、管理、执行、控制项目进度
+2作为管理项目进度的指南</t>
   </si>
   <si>
     <t>定义活动（规划）</t>
   </si>
   <si>
-    <t>1为完成项目可交付成果，将工作包分解为进度活动
-2是项目进度估算、规划、执行、监督和控制的基础</t>
+    <t>1将工作包分解为进度活动 2是项目进度估算、规划、执行、监督和控制的基础</t>
   </si>
   <si>
     <t>排列活动顺序（规划）</t>
   </si>
   <si>
-    <t>1识别记录项目活动之间逻辑关系
-2使项目在制约因素下获得最高的效率</t>
+    <t>1识别整理项目活动间的逻辑关系
+2使项目在制约因素下获得最高效率</t>
   </si>
   <si>
     <t>估算活动持续时间（规划）</t>
   </si>
   <si>
-    <t>1估算完成单项活动所需花费的时间量</t>
+    <t>1估算完成单项活动需要花费的时间量</t>
   </si>
   <si>
     <t>制定进度计划（规划）</t>
   </si>
   <si>
-    <t>1确定进度基准
-2创建具有计划日期的进度模型，以便项目执行和监控3分析活动顺序、持续时间、资源需求和进度制约因素，</t>
+    <t>1分析活动顺序、持续时间、资源需求、进度制约因素 2创建具有计划日期的进度模型供项目执行和监控
+3确定进度基准</t>
   </si>
   <si>
     <t>控制进度（监控）</t>
   </si>
   <si>
-    <t>1维护进度基准
-2监督项目状态
-3更新项目进度
-4管理进度基准变更</t>
+    <t>1监督项目状态、更新项目进度
+2维护进度基准、管理进度基准变更</t>
   </si>
   <si>
     <t>项目成本
@@ -4020,8 +4015,8 @@
     <t>规划成本管理（规划）</t>
   </si>
   <si>
-    <t>1管理项目成本的指南和方向
-2估算、预算、管理、监督、控制项目成本</t>
+    <t>1估算、预算、管理、监控项目成本
+2作为管理项目成本的指南</t>
   </si>
   <si>
     <t>估算成本（规划）</t>
@@ -4034,18 +4029,14 @@
     <t>制定预算（规划）</t>
   </si>
   <si>
-    <t>1确定项目成本基准
-2方便监督和控制项目绩效
-3汇总所有活动、工作包的估算成本</t>
+    <t>1汇总项目所有活动和工作包的估算成本 2确定项目成本基准</t>
   </si>
   <si>
     <t>控制成本（监控）</t>
   </si>
   <si>
-    <t>1维护成本基准
-2监督项目状态
-3更新项目成本
-4管理成本基准变更</t>
+    <t>1监督项目状态、更新项目成本
+2维护成本基准、管理成本基准变更</t>
   </si>
   <si>
     <t>工作绩效信息
@@ -4062,25 +4053,24 @@
     <t>规划质量管理（规划）</t>
   </si>
   <si>
-    <t>1规划并证明，识别可交付成果质量的要求和标准</t>
+    <t>1规划和证明识别可交付成果的质量要求标准</t>
   </si>
   <si>
     <t>管理质量（执行）</t>
   </si>
   <si>
-    <t>1将质量管理计划转化质量活动
-2把质量政策用于项目
-3使用质量控制数据结果，向干系人展示项目的质量状态
-4提高实现质量目标的可能性
-5识别无效过程和导致质量低劣的原因</t>
+    <t>1将质量政策和质量管理计划转换成质量活动
+2识别无效过程和导致质量低劣的原因
+3提高实现质量目标的可能性
+4使用质量控制数据向干系人展示质量状态</t>
   </si>
   <si>
     <t>控制质量（监控）</t>
   </si>
   <si>
-    <t>1核实项目可交付成果满足最终验收质量要求
-2监督和记录质量管理活动执行结果
-3确保项目输出满足规范标准要求和客户期望</t>
+    <t>1监督记录质量管理活动执行结果
+2核实项目可交付成果满足最终验收质量要求
+3确保项目输出满足规范要求和客户期望</t>
   </si>
   <si>
     <t>项目资源
@@ -4093,45 +4083,40 @@
     <t>规划资源管理（规划）</t>
   </si>
   <si>
-    <t>1确定适用于项目资源的管理方法和管理程度
-2估算、获取、管理和利用团队及其实物资源</t>
+    <t>1确定使用项目资源管理的方法
+2估算、获取、管理利用团队资源和实物资源</t>
   </si>
   <si>
     <t>估算活动资源（规划）</t>
   </si>
   <si>
-    <t>1明确完成项目所需的资源种类、数量和特性
-2估算执行项目所需的团队资源和实物资源如：材料、设备的类型和数量</t>
+    <t>1估算项目所需团队和实物资源
+2明确完成项目所需资源种类、数量</t>
   </si>
   <si>
     <t>获取资源（执行）</t>
   </si>
   <si>
-    <t>1概述和指导资源的选择
-2将资源分配给相应的活动
-3获取项目所需的团队资源和实物资源</t>
+    <t>1获取项目所需团队资源和实物资源
+2将资源分配给相应的活动</t>
   </si>
   <si>
     <t>建设团队（执行）</t>
   </si>
   <si>
-    <t>1改进团队协作、人际关系、激励员工，减少摩擦、提升项目绩效
-2提高工作能力，促进团队成员互动，改善团队整体氛围，以提高项目绩效的过程</t>
+    <t>1改善团队人际关系、激励员工、提高工作能力、改善团队氛围、提高项目绩效</t>
   </si>
   <si>
     <t>管理团队（执行）</t>
   </si>
   <si>
-    <t>1影响团队行为、管理冲突、解决问题
-2跟踪团队成员工作表现、提供反馈、解决问题并管理团队变更以优化项目绩效的过程</t>
+    <t>1追踪团队成员工作、管理团队变更 2影响团队行为、管理团队冲突并解决问题</t>
   </si>
   <si>
     <t>控制资源（监控）</t>
   </si>
   <si>
-    <t>1确保按计划为项目分配实物资源
-2根据资源使用计划监督资源实际使用情况，并采取纠正措施
-3确保资源适时、适地用于项目
+    <t>1根据资源使用计划监督纠正资源的使用 2按计划分配实物资源，确保资源合理使用
 3资源释放</t>
   </si>
   <si>
@@ -4145,9 +4130,7 @@
     <t>规划沟通管理（规划）</t>
   </si>
   <si>
-    <t>1基于每个干系人的息需求、组织资产、项目的需求编制书面沟通计划
-2及时向干系人提供信息
-3引导干系人有效参与项目</t>
+    <t>1基于干系人需求、项目需求编制书面沟通计划 2向干系人提供信息并引导干系人有效参与项目</t>
   </si>
   <si>
     <t>沟通需求分析
@@ -4158,14 +4141,14 @@
     <t>管理沟通（执行）</t>
   </si>
   <si>
-    <t>1促成干系人之间的有效信息流动
-2确保项目信息及时且恰当的收集、生成、发布、存储、检索、管理、监督和最终处置</t>
+    <t>1促成干系人间有效信息流动
+2确保项目信息及时恰当的收集、生成、发布、存储、检索、管理、监督、最终处置</t>
   </si>
   <si>
     <t>监督沟通（监控）</t>
   </si>
   <si>
-    <t>1按沟通管理计划和干系人参与计划的要求优化信息传递流程
+    <t>1按沟通管理计划和干系人参与计划的要求优化信息传递
 2确保满足项目和干系人的信息需求</t>
   </si>
   <si>
@@ -5885,8 +5868,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2794000" y="17538700"/>
-          <a:ext cx="11545570" cy="6191250"/>
+          <a:off x="2514600" y="18841720"/>
+          <a:ext cx="10575290" cy="6602730"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6153,43 +6136,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AY27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.1083333333333" customWidth="1"/>
-    <col min="2" max="2" width="22.5583333333333" customWidth="1"/>
-    <col min="3" max="3" width="29.3833333333333" customWidth="1"/>
+    <col min="1" max="1" width="14.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="22.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="29.3796296296296" customWidth="1"/>
     <col min="4" max="4" width="33.75" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="28.1333333333333" customWidth="1"/>
-    <col min="7" max="7" width="29.3833333333333" customWidth="1"/>
+    <col min="6" max="6" width="28.1296296296296" customWidth="1"/>
+    <col min="7" max="7" width="29.3796296296296" customWidth="1"/>
     <col min="8" max="8" width="33.75" customWidth="1"/>
     <col min="9" max="9" width="31.5" customWidth="1"/>
-    <col min="10" max="10" width="29.3833333333333" customWidth="1"/>
-    <col min="11" max="12" width="24.8833333333333" customWidth="1"/>
-    <col min="13" max="13" width="24.1333333333333" customWidth="1"/>
-    <col min="14" max="15" width="24.8833333333333" customWidth="1"/>
-    <col min="16" max="16" width="29.3833333333333" customWidth="1"/>
-    <col min="17" max="17" width="24.8833333333333" customWidth="1"/>
-    <col min="18" max="18" width="29.3833333333333" customWidth="1"/>
+    <col min="10" max="10" width="29.3796296296296" customWidth="1"/>
+    <col min="11" max="12" width="24.8796296296296" customWidth="1"/>
+    <col min="13" max="13" width="24.1296296296296" customWidth="1"/>
+    <col min="14" max="15" width="24.8796296296296" customWidth="1"/>
+    <col min="16" max="16" width="29.3796296296296" customWidth="1"/>
+    <col min="17" max="17" width="24.8796296296296" customWidth="1"/>
+    <col min="18" max="18" width="29.3796296296296" customWidth="1"/>
     <col min="19" max="19" width="32.5" customWidth="1"/>
-    <col min="20" max="20" width="29.3833333333333" customWidth="1"/>
-    <col min="21" max="21" width="24.8833333333333" customWidth="1"/>
-    <col min="22" max="22" width="29.3833333333333" customWidth="1"/>
-    <col min="23" max="25" width="24.8833333333333" customWidth="1"/>
-    <col min="26" max="26" width="29.3833333333333" customWidth="1"/>
-    <col min="27" max="28" width="24.8833333333333" customWidth="1"/>
-    <col min="29" max="30" width="29.3833333333333" customWidth="1"/>
-    <col min="31" max="34" width="24.8833333333333" customWidth="1"/>
-    <col min="35" max="35" width="29.3833333333333" customWidth="1"/>
-    <col min="36" max="37" width="24.8833333333333" customWidth="1"/>
-    <col min="38" max="38" width="29.3833333333333" customWidth="1"/>
-    <col min="39" max="39" width="24.8833333333333" customWidth="1"/>
+    <col min="20" max="20" width="29.3796296296296" customWidth="1"/>
+    <col min="21" max="21" width="24.8796296296296" customWidth="1"/>
+    <col min="22" max="22" width="29.3796296296296" customWidth="1"/>
+    <col min="23" max="25" width="24.8796296296296" customWidth="1"/>
+    <col min="26" max="26" width="29.3796296296296" customWidth="1"/>
+    <col min="27" max="28" width="24.8796296296296" customWidth="1"/>
+    <col min="29" max="30" width="29.3796296296296" customWidth="1"/>
+    <col min="31" max="34" width="24.8796296296296" customWidth="1"/>
+    <col min="35" max="35" width="29.3796296296296" customWidth="1"/>
+    <col min="36" max="37" width="24.8796296296296" customWidth="1"/>
+    <col min="38" max="38" width="29.3796296296296" customWidth="1"/>
+    <col min="39" max="39" width="24.8796296296296" customWidth="1"/>
     <col min="40" max="41" width="33.75" customWidth="1"/>
-    <col min="42" max="43" width="29.3833333333333" customWidth="1"/>
-    <col min="44" max="44" width="24.8833333333333" customWidth="1"/>
-    <col min="45" max="45" width="29.3833333333333" customWidth="1"/>
-    <col min="46" max="47" width="24.8833333333333" customWidth="1"/>
-    <col min="48" max="48" width="27.1333333333333" customWidth="1"/>
+    <col min="42" max="43" width="29.3796296296296" customWidth="1"/>
+    <col min="44" max="44" width="24.8796296296296" customWidth="1"/>
+    <col min="45" max="45" width="29.3796296296296" customWidth="1"/>
+    <col min="46" max="47" width="24.8796296296296" customWidth="1"/>
+    <col min="48" max="48" width="27.1296296296296" customWidth="1"/>
     <col min="49" max="51" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6490,7 +6473,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" s="53" customFormat="1" ht="108" spans="1:51">
+    <row r="4" s="53" customFormat="1" ht="115.2" spans="1:51">
       <c r="A4" s="66"/>
       <c r="B4" s="66"/>
       <c r="C4" s="32" t="s">
@@ -6641,7 +6624,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" s="53" customFormat="1" ht="94.5" spans="1:51">
+    <row r="5" s="53" customFormat="1" ht="100.8" spans="1:51">
       <c r="A5" s="66"/>
       <c r="B5" s="66"/>
       <c r="C5" s="32"/>
@@ -6740,7 +6723,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" s="53" customFormat="1" ht="27" spans="1:51">
+    <row r="6" s="53" customFormat="1" ht="28.8" spans="1:51">
       <c r="A6" s="66"/>
       <c r="B6" s="66"/>
       <c r="C6" s="69" t="s">
@@ -6891,7 +6874,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7" s="53" customFormat="1" ht="54" spans="1:51">
+    <row r="7" s="53" customFormat="1" ht="57.6" spans="1:51">
       <c r="A7" s="70" t="s">
         <v>143</v>
       </c>
@@ -7046,7 +7029,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" ht="67.5" spans="1:51">
+    <row r="8" ht="72" spans="1:51">
       <c r="A8" s="72"/>
       <c r="B8" s="73" t="s">
         <v>147</v>
@@ -7199,7 +7182,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="9" ht="40.5" spans="1:51">
+    <row r="9" ht="43.2" spans="1:51">
       <c r="A9" s="72"/>
       <c r="B9" s="26" t="s">
         <v>170</v>
@@ -7258,7 +7241,7 @@
       <c r="AX9" s="76"/>
       <c r="AY9" s="76"/>
     </row>
-    <row r="10" ht="81" spans="1:51">
+    <row r="10" ht="86.4" spans="1:51">
       <c r="A10" s="77"/>
       <c r="B10" s="26" t="s">
         <v>173</v>
@@ -7437,7 +7420,7 @@
       <c r="AX12" s="54"/>
       <c r="AY12" s="54"/>
     </row>
-    <row r="14" ht="94.5" spans="1:51">
+    <row r="14" ht="115.2" spans="1:51">
       <c r="A14" s="81" t="s">
         <v>183</v>
       </c>
@@ -7615,7 +7598,7 @@
       <c r="AX15" s="80"/>
       <c r="AY15" s="80"/>
     </row>
-    <row r="16" ht="67.5" spans="1:51">
+    <row r="16" ht="72" spans="1:51">
       <c r="A16" s="86"/>
       <c r="B16" s="87" t="s">
         <v>218</v>
@@ -7692,7 +7675,7 @@
       <c r="AX16" s="80"/>
       <c r="AY16" s="80"/>
     </row>
-    <row r="17" ht="81" spans="1:51">
+    <row r="17" ht="86.4" spans="1:51">
       <c r="A17" s="86"/>
       <c r="B17" s="87" t="s">
         <v>229</v>
@@ -7801,7 +7784,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="18" ht="81" spans="1:51">
+    <row r="18" ht="86.4" spans="1:51">
       <c r="A18" s="86"/>
       <c r="B18" s="87" t="s">
         <v>257</v>
@@ -7878,7 +7861,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="19" ht="40.5" spans="1:51">
+    <row r="19" ht="43.2" spans="1:51">
       <c r="A19" s="86"/>
       <c r="B19" s="87" t="s">
         <v>267</v>
@@ -7945,7 +7928,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="20" ht="54" spans="1:51">
+    <row r="20" ht="57.6" spans="1:51">
       <c r="A20" s="86"/>
       <c r="B20" s="87" t="s">
         <v>271</v>
@@ -8002,7 +7985,7 @@
       <c r="AX20" s="80"/>
       <c r="AY20" s="80"/>
     </row>
-    <row r="21" ht="81" spans="1:51">
+    <row r="21" ht="86.4" spans="1:51">
       <c r="A21" s="86"/>
       <c r="B21" s="91" t="s">
         <v>273</v>
@@ -8140,7 +8123,7 @@
       <c r="AX22" s="80"/>
       <c r="AY22" s="80"/>
     </row>
-    <row r="24" ht="108" spans="1:51">
+    <row r="24" ht="115.2" spans="1:51">
       <c r="A24" s="70" t="s">
         <v>285</v>
       </c>
@@ -8350,7 +8333,7 @@
       <c r="AX25" s="76"/>
       <c r="AY25" s="76"/>
     </row>
-    <row r="26" customFormat="1" ht="94.5" spans="1:51">
+    <row r="26" customFormat="1" ht="100.8" spans="1:51">
       <c r="A26" s="77"/>
       <c r="B26" s="26" t="s">
         <v>326</v>
@@ -8415,7 +8398,7 @@
       <c r="AX26" s="76"/>
       <c r="AY26" s="76"/>
     </row>
-    <row r="27" s="54" customFormat="1" ht="27" spans="1:51">
+    <row r="27" s="54" customFormat="1" ht="28.8" spans="1:51">
       <c r="A27" s="78" t="s">
         <v>332</v>
       </c>
@@ -8502,27 +8485,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:X52"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="13.1083333333333" customWidth="1"/>
+    <col min="2" max="2" width="13.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="14.8916666666667" customWidth="1"/>
-    <col min="8" max="8" width="13.1083333333333" customWidth="1"/>
-    <col min="9" max="9" width="13.225" customWidth="1"/>
+    <col min="6" max="6" width="14.8888888888889" customWidth="1"/>
+    <col min="8" max="8" width="13.1111111111111" customWidth="1"/>
+    <col min="9" max="9" width="13.2222222222222" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="9.775" customWidth="1"/>
-    <col min="12" max="12" width="4.775" customWidth="1"/>
+    <col min="11" max="11" width="9.77777777777778" customWidth="1"/>
+    <col min="12" max="12" width="4.77777777777778" customWidth="1"/>
     <col min="13" max="13" width="5.66666666666667" customWidth="1"/>
     <col min="15" max="15" width="9.66666666666667" customWidth="1"/>
     <col min="16" max="16" width="14.3333333333333" customWidth="1"/>
     <col min="17" max="17" width="9.66666666666667" customWidth="1"/>
-    <col min="19" max="19" width="11.4416666666667" customWidth="1"/>
-    <col min="20" max="20" width="13.5583333333333" customWidth="1"/>
-    <col min="21" max="21" width="9.10833333333333" customWidth="1"/>
-    <col min="23" max="23" width="12.8916666666667" customWidth="1"/>
-    <col min="24" max="24" width="10.225" customWidth="1"/>
+    <col min="19" max="19" width="11.4444444444444" customWidth="1"/>
+    <col min="20" max="20" width="13.5555555555556" customWidth="1"/>
+    <col min="21" max="21" width="9.11111111111111" customWidth="1"/>
+    <col min="23" max="23" width="12.8888888888889" customWidth="1"/>
+    <col min="24" max="24" width="10.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24">
@@ -8607,7 +8590,7 @@
       <c r="W2" s="22"/>
       <c r="X2" s="24"/>
     </row>
-    <row r="3" ht="81.75" spans="1:24">
+    <row r="3" ht="87.15" spans="1:24">
       <c r="A3" s="19"/>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -8669,7 +8652,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="4" s="13" customFormat="1" ht="94.5" spans="1:24">
+    <row r="4" s="13" customFormat="1" ht="100.8" spans="1:24">
       <c r="A4" s="30" t="s">
         <v>348</v>
       </c>
@@ -8711,7 +8694,7 @@
       <c r="W4" s="33"/>
       <c r="X4" s="37"/>
     </row>
-    <row r="5" ht="94.5" spans="1:24">
+    <row r="5" ht="100.8" spans="1:24">
       <c r="A5" s="19"/>
       <c r="B5" s="31"/>
       <c r="C5" s="32" t="s">
@@ -8749,7 +8732,7 @@
       <c r="W5" s="33"/>
       <c r="X5" s="37"/>
     </row>
-    <row r="6" ht="81" spans="1:24">
+    <row r="6" ht="100.8" spans="1:24">
       <c r="A6" s="19"/>
       <c r="B6" s="31"/>
       <c r="C6" s="32" t="s">
@@ -8783,7 +8766,7 @@
       <c r="W6" s="33"/>
       <c r="X6" s="37"/>
     </row>
-    <row r="7" ht="81" spans="1:24">
+    <row r="7" ht="86.4" spans="1:24">
       <c r="A7" s="19"/>
       <c r="B7" s="31"/>
       <c r="C7" s="32" t="s">
@@ -8819,7 +8802,7 @@
       <c r="W7" s="33"/>
       <c r="X7" s="37"/>
     </row>
-    <row r="8" customFormat="1" ht="121.5" spans="1:24">
+    <row r="8" customFormat="1" ht="129.6" spans="1:24">
       <c r="A8" s="19"/>
       <c r="B8" s="31"/>
       <c r="C8" s="32" t="s">
@@ -8857,7 +8840,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="81" spans="1:24">
+    <row r="9" customFormat="1" ht="86.4" spans="1:24">
       <c r="A9" s="19"/>
       <c r="B9" s="31"/>
       <c r="C9" s="32" t="s">
@@ -8895,7 +8878,7 @@
       <c r="W9" s="33"/>
       <c r="X9" s="37"/>
     </row>
-    <row r="10" s="14" customFormat="1" ht="68.25" spans="1:24">
+    <row r="10" s="14" customFormat="1" ht="72.75" spans="1:24">
       <c r="A10" s="19"/>
       <c r="B10" s="31"/>
       <c r="C10" s="32" t="s">
@@ -8931,7 +8914,7 @@
       <c r="W10" s="33"/>
       <c r="X10" s="37"/>
     </row>
-    <row r="11" s="13" customFormat="1" ht="67.5" spans="1:24">
+    <row r="11" s="13" customFormat="1" ht="72" spans="1:24">
       <c r="A11" s="30" t="s">
         <v>367</v>
       </c>
@@ -8969,7 +8952,7 @@
       <c r="W11" s="33"/>
       <c r="X11" s="37"/>
     </row>
-    <row r="12" customFormat="1" ht="81" spans="1:24">
+    <row r="12" customFormat="1" ht="86.4" spans="1:24">
       <c r="A12" s="19"/>
       <c r="B12" s="31"/>
       <c r="C12" s="32" t="s">
@@ -9019,7 +9002,7 @@
       <c r="W12" s="33"/>
       <c r="X12" s="37"/>
     </row>
-    <row r="13" customFormat="1" ht="54" spans="1:24">
+    <row r="13" customFormat="1" ht="57.6" spans="1:24">
       <c r="A13" s="19"/>
       <c r="B13" s="31"/>
       <c r="C13" s="32" t="s">
@@ -9063,7 +9046,7 @@
       <c r="W13" s="33"/>
       <c r="X13" s="37"/>
     </row>
-    <row r="14" customFormat="1" ht="94.5" spans="1:24">
+    <row r="14" customFormat="1" ht="86.4" spans="1:24">
       <c r="A14" s="19"/>
       <c r="B14" s="31"/>
       <c r="C14" s="32" t="s">
@@ -9101,7 +9084,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="81" spans="1:24">
+    <row r="15" customFormat="1" ht="86.4" spans="1:24">
       <c r="A15" s="19"/>
       <c r="B15" s="31"/>
       <c r="C15" s="32" t="s">
@@ -9143,7 +9126,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="16" s="14" customFormat="1" ht="81.75" spans="1:24">
+    <row r="16" s="14" customFormat="1" ht="72.75" spans="1:24">
       <c r="A16" s="19"/>
       <c r="B16" s="31"/>
       <c r="C16" s="32" t="s">
@@ -9179,7 +9162,7 @@
       <c r="W16" s="33"/>
       <c r="X16" s="37"/>
     </row>
-    <row r="17" s="13" customFormat="1" ht="81" spans="1:24">
+    <row r="17" s="13" customFormat="1" ht="86.4" spans="1:24">
       <c r="A17" s="30" t="s">
         <v>382</v>
       </c>
@@ -9217,7 +9200,7 @@
       <c r="W17" s="33"/>
       <c r="X17" s="37"/>
     </row>
-    <row r="18" customFormat="1" ht="108" spans="1:24">
+    <row r="18" customFormat="1" ht="86.4" spans="1:24">
       <c r="A18" s="19"/>
       <c r="B18" s="31"/>
       <c r="C18" s="32" t="s">
@@ -9253,7 +9236,7 @@
       <c r="W18" s="33"/>
       <c r="X18" s="37"/>
     </row>
-    <row r="19" customFormat="1" ht="81" spans="1:24">
+    <row r="19" customFormat="1" ht="86.4" spans="1:24">
       <c r="A19" s="19"/>
       <c r="B19" s="31"/>
       <c r="C19" s="32" t="s">
@@ -9289,7 +9272,7 @@
       <c r="W19" s="33"/>
       <c r="X19" s="37"/>
     </row>
-    <row r="20" customFormat="1" ht="54" spans="1:24">
+    <row r="20" customFormat="1" ht="57.6" spans="1:24">
       <c r="A20" s="19"/>
       <c r="B20" s="31"/>
       <c r="C20" s="32" t="s">
@@ -9327,7 +9310,7 @@
       <c r="W20" s="33"/>
       <c r="X20" s="37"/>
     </row>
-    <row r="21" customFormat="1" ht="121.5" spans="1:24">
+    <row r="21" customFormat="1" ht="144" spans="1:24">
       <c r="A21" s="19"/>
       <c r="B21" s="31"/>
       <c r="C21" s="32" t="s">
@@ -9365,7 +9348,7 @@
       <c r="W21" s="33"/>
       <c r="X21" s="37"/>
     </row>
-    <row r="22" s="14" customFormat="1" ht="81.75" spans="1:24">
+    <row r="22" s="14" customFormat="1" ht="87.15" spans="1:24">
       <c r="A22" s="19"/>
       <c r="B22" s="31"/>
       <c r="C22" s="32" t="s">
@@ -9403,7 +9386,7 @@
       <c r="W22" s="33"/>
       <c r="X22" s="37"/>
     </row>
-    <row r="23" s="13" customFormat="1" ht="67.5" spans="1:24">
+    <row r="23" s="13" customFormat="1" ht="72" spans="1:24">
       <c r="A23" s="30" t="s">
         <v>396</v>
       </c>
@@ -9479,7 +9462,7 @@
       <c r="W24" s="33"/>
       <c r="X24" s="37"/>
     </row>
-    <row r="25" customFormat="1" ht="94.5" spans="1:24">
+    <row r="25" customFormat="1" ht="72" spans="1:24">
       <c r="A25" s="19"/>
       <c r="B25" s="31"/>
       <c r="C25" s="32" t="s">
@@ -9517,7 +9500,7 @@
       <c r="W25" s="33"/>
       <c r="X25" s="37"/>
     </row>
-    <row r="26" s="14" customFormat="1" ht="68.25" spans="1:24">
+    <row r="26" s="14" customFormat="1" ht="87.15" spans="1:24">
       <c r="A26" s="19"/>
       <c r="B26" s="31"/>
       <c r="C26" s="32" t="s">
@@ -9555,7 +9538,7 @@
       <c r="W26" s="33"/>
       <c r="X26" s="37"/>
     </row>
-    <row r="27" s="13" customFormat="1" ht="67.5" spans="1:24">
+    <row r="27" s="13" customFormat="1" ht="72" spans="1:24">
       <c r="A27" s="30" t="s">
         <v>407</v>
       </c>
@@ -9601,7 +9584,7 @@
       <c r="W27" s="33"/>
       <c r="X27" s="37"/>
     </row>
-    <row r="28" customFormat="1" ht="189" spans="1:24">
+    <row r="28" customFormat="1" ht="201.6" spans="1:24">
       <c r="A28" s="19"/>
       <c r="B28" s="31"/>
       <c r="C28" s="32" t="s">
@@ -9645,7 +9628,7 @@
       <c r="W28" s="33"/>
       <c r="X28" s="37"/>
     </row>
-    <row r="29" s="14" customFormat="1" ht="149.25" spans="1:24">
+    <row r="29" s="14" customFormat="1" ht="144.75" spans="1:24">
       <c r="A29" s="19"/>
       <c r="B29" s="31"/>
       <c r="C29" s="32" t="s">
@@ -9687,7 +9670,7 @@
       <c r="W29" s="33"/>
       <c r="X29" s="37"/>
     </row>
-    <row r="30" s="13" customFormat="1" ht="108" spans="1:24">
+    <row r="30" s="13" customFormat="1" ht="100.8" spans="1:24">
       <c r="A30" s="30" t="s">
         <v>415</v>
       </c>
@@ -9729,7 +9712,7 @@
       <c r="W30" s="33"/>
       <c r="X30" s="37"/>
     </row>
-    <row r="31" customFormat="1" ht="135" spans="1:24">
+    <row r="31" customFormat="1" ht="86.4" spans="1:24">
       <c r="A31" s="19"/>
       <c r="B31" s="31"/>
       <c r="C31" s="32" t="s">
@@ -9765,7 +9748,7 @@
       <c r="W31" s="33"/>
       <c r="X31" s="37"/>
     </row>
-    <row r="32" customFormat="1" ht="94.5" spans="1:24">
+    <row r="32" customFormat="1" ht="72" spans="1:24">
       <c r="A32" s="19"/>
       <c r="B32" s="31"/>
       <c r="C32" s="32" t="s">
@@ -9805,7 +9788,7 @@
       <c r="W32" s="33"/>
       <c r="X32" s="37"/>
     </row>
-    <row r="33" customFormat="1" ht="148.5" spans="1:24">
+    <row r="33" customFormat="1" ht="86.4" spans="1:24">
       <c r="A33" s="19"/>
       <c r="B33" s="31"/>
       <c r="C33" s="32" t="s">
@@ -9843,7 +9826,7 @@
       <c r="W33" s="33"/>
       <c r="X33" s="37"/>
     </row>
-    <row r="34" customFormat="1" ht="135" spans="1:24">
+    <row r="34" customFormat="1" ht="86.4" spans="1:24">
       <c r="A34" s="19"/>
       <c r="B34" s="31"/>
       <c r="C34" s="32" t="s">
@@ -9879,7 +9862,7 @@
       <c r="W34" s="41"/>
       <c r="X34" s="42"/>
     </row>
-    <row r="35" s="14" customFormat="1" ht="162.75" spans="1:24">
+    <row r="35" s="14" customFormat="1" ht="115.95" spans="1:24">
       <c r="A35" s="19"/>
       <c r="B35" s="31"/>
       <c r="C35" s="32" t="s">
@@ -9917,7 +9900,7 @@
       <c r="W35" s="33"/>
       <c r="X35" s="37"/>
     </row>
-    <row r="36" s="13" customFormat="1" ht="121.5" spans="1:24">
+    <row r="36" s="13" customFormat="1" ht="100.8" spans="1:24">
       <c r="A36" s="30" t="s">
         <v>429</v>
       </c>
@@ -9961,7 +9944,7 @@
       <c r="W36" s="33"/>
       <c r="X36" s="37"/>
     </row>
-    <row r="37" customFormat="1" ht="135" spans="1:24">
+    <row r="37" customFormat="1" ht="144" spans="1:24">
       <c r="A37" s="19"/>
       <c r="B37" s="31"/>
       <c r="C37" s="32" t="s">
@@ -10003,7 +9986,7 @@
       <c r="W37" s="33"/>
       <c r="X37" s="37"/>
     </row>
-    <row r="38" s="14" customFormat="1" ht="108.75" spans="1:24">
+    <row r="38" s="14" customFormat="1" ht="115.95" spans="1:24">
       <c r="A38" s="19"/>
       <c r="B38" s="31"/>
       <c r="C38" s="32" t="s">
@@ -10039,7 +10022,7 @@
       <c r="W38" s="33"/>
       <c r="X38" s="37"/>
     </row>
-    <row r="39" s="13" customFormat="1" ht="135" spans="1:24">
+    <row r="39" s="13" customFormat="1" ht="144" spans="1:24">
       <c r="A39" s="30" t="s">
         <v>438</v>
       </c>
@@ -10079,7 +10062,7 @@
       <c r="W39" s="33"/>
       <c r="X39" s="37"/>
     </row>
-    <row r="40" customFormat="1" ht="189" spans="1:24">
+    <row r="40" customFormat="1" ht="216" spans="1:24">
       <c r="A40" s="19"/>
       <c r="B40" s="31"/>
       <c r="C40" s="32" t="s">
@@ -10119,7 +10102,7 @@
       <c r="W40" s="33"/>
       <c r="X40" s="37"/>
     </row>
-    <row r="41" customFormat="1" ht="121.5" spans="1:24">
+    <row r="41" customFormat="1" ht="129.6" spans="1:24">
       <c r="A41" s="19"/>
       <c r="B41" s="31"/>
       <c r="C41" s="32" t="s">
@@ -10159,7 +10142,7 @@
       <c r="W41" s="33"/>
       <c r="X41" s="37"/>
     </row>
-    <row r="42" customFormat="1" ht="162" spans="1:24">
+    <row r="42" customFormat="1" ht="172.8" spans="1:24">
       <c r="A42" s="19"/>
       <c r="B42" s="31"/>
       <c r="C42" s="32" t="s">
@@ -10203,7 +10186,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="189" spans="1:24">
+    <row r="43" customFormat="1" ht="216" spans="1:24">
       <c r="A43" s="19"/>
       <c r="B43" s="31"/>
       <c r="C43" s="32" t="s">
@@ -10249,7 +10232,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="175.5" spans="1:24">
+    <row r="44" customFormat="1" ht="187.2" spans="1:24">
       <c r="A44" s="19"/>
       <c r="B44" s="31"/>
       <c r="C44" s="32" t="s">
@@ -10283,7 +10266,7 @@
       <c r="W44" s="33"/>
       <c r="X44" s="37"/>
     </row>
-    <row r="45" s="14" customFormat="1" ht="189.75" spans="1:24">
+    <row r="45" s="14" customFormat="1" ht="216.75" spans="1:24">
       <c r="A45" s="19"/>
       <c r="B45" s="31"/>
       <c r="C45" s="32" t="s">
@@ -10321,7 +10304,7 @@
       <c r="W45" s="33"/>
       <c r="X45" s="37"/>
     </row>
-    <row r="46" s="13" customFormat="1" ht="148.5" spans="1:24">
+    <row r="46" s="13" customFormat="1" ht="158.4" spans="1:24">
       <c r="A46" s="30" t="s">
         <v>454</v>
       </c>
@@ -10365,7 +10348,7 @@
       <c r="W46" s="33"/>
       <c r="X46" s="37"/>
     </row>
-    <row r="47" customFormat="1" ht="94.5" spans="1:24">
+    <row r="47" customFormat="1" ht="100.8" spans="1:24">
       <c r="A47" s="19"/>
       <c r="B47" s="31"/>
       <c r="C47" s="32" t="s">
@@ -10405,7 +10388,7 @@
       <c r="W47" s="33"/>
       <c r="X47" s="37"/>
     </row>
-    <row r="48" s="14" customFormat="1" ht="135.75" spans="1:24">
+    <row r="48" s="14" customFormat="1" ht="144.75" spans="1:24">
       <c r="A48" s="19"/>
       <c r="B48" s="31"/>
       <c r="C48" s="32" t="s">
@@ -10443,7 +10426,7 @@
       <c r="W48" s="33"/>
       <c r="X48" s="37"/>
     </row>
-    <row r="49" s="13" customFormat="1" ht="175.5" spans="1:24">
+    <row r="49" s="13" customFormat="1" ht="187.2" spans="1:24">
       <c r="A49" s="30" t="s">
         <v>462</v>
       </c>
@@ -10487,7 +10470,7 @@
       <c r="W49" s="33"/>
       <c r="X49" s="37"/>
     </row>
-    <row r="50" customFormat="1" ht="135" spans="1:24">
+    <row r="50" customFormat="1" ht="144" spans="1:24">
       <c r="A50" s="19"/>
       <c r="B50" s="31"/>
       <c r="C50" s="32" t="s">
@@ -10525,7 +10508,7 @@
       <c r="W50" s="33"/>
       <c r="X50" s="37"/>
     </row>
-    <row r="51" customFormat="1" ht="162" spans="1:24">
+    <row r="51" customFormat="1" ht="172.8" spans="1:24">
       <c r="A51" s="19"/>
       <c r="B51" s="31"/>
       <c r="C51" s="32" t="s">
@@ -10563,7 +10546,7 @@
       <c r="W51" s="33"/>
       <c r="X51" s="37"/>
     </row>
-    <row r="52" s="14" customFormat="1" ht="122.25" spans="1:24">
+    <row r="52" s="14" customFormat="1" ht="144.75" spans="1:24">
       <c r="A52" s="44"/>
       <c r="B52" s="45"/>
       <c r="C52" s="46" t="s">
@@ -10796,7 +10779,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -10808,7 +10791,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -10819,11 +10802,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="21.25" customWidth="1"/>
-    <col min="4" max="4" width="77.1333333333333" customWidth="1"/>
+    <col min="4" max="4" width="77.1296296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10860,7 +10843,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="4" ht="94.5" spans="1:4">
+    <row r="4" ht="100.8" spans="1:4">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="5" t="s">
@@ -10870,7 +10853,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="5" ht="27" spans="1:4">
+    <row r="5" ht="28.8" spans="1:4">
       <c r="A5" s="7" t="s">
         <v>483</v>
       </c>
@@ -10922,7 +10905,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="9" ht="27" spans="1:4">
+    <row r="9" ht="28.8" spans="1:4">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="7" t="s">
@@ -10942,7 +10925,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="11" ht="40.5" spans="1:4">
+    <row r="11" ht="43.2" spans="1:4">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="7" t="s">
@@ -10952,7 +10935,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="12" ht="27" spans="1:4">
+    <row r="12" ht="28.8" spans="1:4">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="7" t="s">
@@ -10978,10 +10961,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="39.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="39.8796296296296" customWidth="1"/>
     <col min="3" max="3" width="63.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11151,7 +11134,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -11162,7 +11145,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13500" firstSheet="1" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="49过程输入输出工具-横版" sheetId="1" state="hidden" r:id="rId1"/>
@@ -3859,7 +3859,7 @@
 2确定项目工作基础和执行方式</t>
   </si>
   <si>
-    <t>项目管理子计划</t>
+    <t>项目管理计划各组成部分</t>
   </si>
   <si>
     <t>指导与管理项目工作（执行）</t>
@@ -4163,100 +4163,50 @@
   </si>
   <si>
     <t>1定义如何实施项目风险管理活动
-2确保风险管理的水平、方法和可见度与项目风险程度和对组织干系人重要重读相匹配</t>
+2确保风险管理水平与项目风险程度和对干系人重要程度相匹配</t>
   </si>
   <si>
     <t>识别风险（规划）</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">1记录单个项目风险和整体项目风险来源
-2汇总相关信息，以便项目团队能够恰当地应对已识别的风险  </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3识别单个项目风险以及整体项目风险的来源，并记录风险特征的过程</t>
-    </r>
+    <t>1识别记录项目单个风险和整体风险来源
+2记录风险特征</t>
   </si>
   <si>
     <t>实施定性风险分析（规划）</t>
   </si>
   <si>
-    <t xml:space="preserve">1重点关注高优先级的风险
-2通过评估单个项目风险发生的概率和影响及其他特征，对风险进行优先级排序
-</t>
+    <t>1评估单个风险发生的概率和影响来对风险进行优先级排序</t>
   </si>
   <si>
     <t>实施定量风险分析（规划）</t>
   </si>
   <si>
-    <t xml:space="preserve">1量化整体项目风险最大可能性
-2提供额外的定量风险信息，以支持风险应对规划
-3就单个项目风险对整体项目目标的影响进行定量分析
-</t>
+    <t>1对单个风险对项目目标影响做定量分析
+2量化项目整体风险最大可能性</t>
   </si>
   <si>
     <t>规划风险应对（规划）</t>
   </si>
   <si>
-    <t>1应对项目风险，而制定可选方案、应对策略并商定应对行动
-2制定整体项目风险和单个项目风险的应对方法
-3分配资源
-4根据需要将相关活动添加进项目文件和项目管理计划中</t>
+    <t>1对项目整体风险和单个风险制定可选方案和应对策略及行动
+2分配风险应对资源
+3将应对风险的活动添加到项目管理计划和项目文件中</t>
   </si>
   <si>
     <t>实施风险应对（执行）</t>
   </si>
   <si>
-    <t>1执行商定的风险应对计划的过程
-作用：
-2确保按计划执行商定的风险应对措施
-3管理整体项目风险入口、最小化单个项目威胁，以及最大化单个项目机会</t>
+    <t>1按计划执行风险应对措施
+2最小化风险，最大化机会</t>
   </si>
   <si>
     <t>监督风险（监控）</t>
   </si>
   <si>
-    <t xml:space="preserve">
-1保证项目决策是在整体项目风险和单个项目风险当前信息的基础上运行
-2监督风险应对计划的实施3跟踪已识别风险、识别和分析新风险，4评估风险管理有效性的过程</t>
+    <t>1监督风险应对计划的实施
+2跟踪已识别风险，识别分析新风险
+3评估风险管理有效性</t>
   </si>
   <si>
     <t>项目采购
@@ -4269,22 +4219,20 @@
     <t>规划采购管理（规划）</t>
   </si>
   <si>
-    <t>1确定是否从项目外部获取货物和服务，2确定将在什么时间、以什么方式获取什么货物和服务
-3记录项目采购决策、明确采购方法，及识别潜在卖方</t>
+    <t>1确定是否从外部获取货物服务，获取什么样的、何时、如何获取外部货物服务
+2明确采购决策、方法并识别潜在卖方</t>
   </si>
   <si>
     <t>实施采购（执行）</t>
   </si>
   <si>
-    <t>1选定合格卖方并签署关于货物或服务交付的法律协议
-2获取卖方应答、选择卖方并授予合同</t>
+    <t>1选定合格卖方并授予合同协议</t>
   </si>
   <si>
     <t>控制采购（监控）</t>
   </si>
   <si>
-    <t>1确保买卖双方履行法律协议，满足项目需求
-2管理采购关系、监督合同绩效、实施必要的变更和纠偏，以及关闭合同</t>
+    <t>1监控买卖双方履行合同协议 2管理采购关系、监督合同绩效、实施必要变更和纠偏、关闭合同</t>
   </si>
   <si>
     <t xml:space="preserve">项目干系
@@ -4297,22 +4245,19 @@
     <t>识别干系人（启动）</t>
   </si>
   <si>
-    <t>1使项目团队能够建立对每个干系人或干系人群体的适度关注
-2定期识别项目干系人，分析和记录他们的利益、参与度、项目依赖性、影响力和对项目成功的潜在影响</t>
+    <t>1定期识别干系人、记录干系人利益、参与度、项目依赖、影响力</t>
   </si>
   <si>
     <t>规划干系人参与（规划）</t>
   </si>
   <si>
-    <t>1提供与干系人进行有效互动的可行计划
-2根据干系人的需求、期望、利益和对项目的潜在影响，制定项目干系人参与项目的方法</t>
+    <t>1根据干系人需求、期望、利益、影响制定与干系人有效互动参与的计划</t>
   </si>
   <si>
     <t>管理干系人参与（执行）</t>
   </si>
   <si>
-    <t>1尽可能提高干系人的支持度，并降低干系人的抵制程度
-2通过与干系人进行沟通协作，以满足其需求与期望、处理问题，并促进干系人合理参与</t>
+    <t>1与干系人沟通并满足其需求、期望，促进干系人合理参与项目，提高支持，降低抵制</t>
   </si>
   <si>
     <t>基本规则</t>
@@ -4321,8 +4266,7 @@
     <t>监督干系人参与（监控）</t>
   </si>
   <si>
-    <t>1维持或提升干系人参与活动的效率和效果
-2监督项目干系人的关系，并通过修订参与策略和计划来引导干系人合理参与项目</t>
+    <t>1监督干系人关系，引导干系人参与，维持提升干系人参与效率效果</t>
   </si>
   <si>
     <t>进度管理</t>
@@ -5868,8 +5812,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2514600" y="18841720"/>
-          <a:ext cx="10575290" cy="6602730"/>
+          <a:off x="2794000" y="17538700"/>
+          <a:ext cx="11545570" cy="6191250"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6136,43 +6080,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AY27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="14.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="22.5555555555556" customWidth="1"/>
-    <col min="3" max="3" width="29.3796296296296" customWidth="1"/>
+    <col min="1" max="1" width="14.1083333333333" customWidth="1"/>
+    <col min="2" max="2" width="22.5583333333333" customWidth="1"/>
+    <col min="3" max="3" width="29.3833333333333" customWidth="1"/>
     <col min="4" max="4" width="33.75" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="28.1296296296296" customWidth="1"/>
-    <col min="7" max="7" width="29.3796296296296" customWidth="1"/>
+    <col min="6" max="6" width="28.1333333333333" customWidth="1"/>
+    <col min="7" max="7" width="29.3833333333333" customWidth="1"/>
     <col min="8" max="8" width="33.75" customWidth="1"/>
     <col min="9" max="9" width="31.5" customWidth="1"/>
-    <col min="10" max="10" width="29.3796296296296" customWidth="1"/>
-    <col min="11" max="12" width="24.8796296296296" customWidth="1"/>
-    <col min="13" max="13" width="24.1296296296296" customWidth="1"/>
-    <col min="14" max="15" width="24.8796296296296" customWidth="1"/>
-    <col min="16" max="16" width="29.3796296296296" customWidth="1"/>
-    <col min="17" max="17" width="24.8796296296296" customWidth="1"/>
-    <col min="18" max="18" width="29.3796296296296" customWidth="1"/>
+    <col min="10" max="10" width="29.3833333333333" customWidth="1"/>
+    <col min="11" max="12" width="24.8833333333333" customWidth="1"/>
+    <col min="13" max="13" width="24.1333333333333" customWidth="1"/>
+    <col min="14" max="15" width="24.8833333333333" customWidth="1"/>
+    <col min="16" max="16" width="29.3833333333333" customWidth="1"/>
+    <col min="17" max="17" width="24.8833333333333" customWidth="1"/>
+    <col min="18" max="18" width="29.3833333333333" customWidth="1"/>
     <col min="19" max="19" width="32.5" customWidth="1"/>
-    <col min="20" max="20" width="29.3796296296296" customWidth="1"/>
-    <col min="21" max="21" width="24.8796296296296" customWidth="1"/>
-    <col min="22" max="22" width="29.3796296296296" customWidth="1"/>
-    <col min="23" max="25" width="24.8796296296296" customWidth="1"/>
-    <col min="26" max="26" width="29.3796296296296" customWidth="1"/>
-    <col min="27" max="28" width="24.8796296296296" customWidth="1"/>
-    <col min="29" max="30" width="29.3796296296296" customWidth="1"/>
-    <col min="31" max="34" width="24.8796296296296" customWidth="1"/>
-    <col min="35" max="35" width="29.3796296296296" customWidth="1"/>
-    <col min="36" max="37" width="24.8796296296296" customWidth="1"/>
-    <col min="38" max="38" width="29.3796296296296" customWidth="1"/>
-    <col min="39" max="39" width="24.8796296296296" customWidth="1"/>
+    <col min="20" max="20" width="29.3833333333333" customWidth="1"/>
+    <col min="21" max="21" width="24.8833333333333" customWidth="1"/>
+    <col min="22" max="22" width="29.3833333333333" customWidth="1"/>
+    <col min="23" max="25" width="24.8833333333333" customWidth="1"/>
+    <col min="26" max="26" width="29.3833333333333" customWidth="1"/>
+    <col min="27" max="28" width="24.8833333333333" customWidth="1"/>
+    <col min="29" max="30" width="29.3833333333333" customWidth="1"/>
+    <col min="31" max="34" width="24.8833333333333" customWidth="1"/>
+    <col min="35" max="35" width="29.3833333333333" customWidth="1"/>
+    <col min="36" max="37" width="24.8833333333333" customWidth="1"/>
+    <col min="38" max="38" width="29.3833333333333" customWidth="1"/>
+    <col min="39" max="39" width="24.8833333333333" customWidth="1"/>
     <col min="40" max="41" width="33.75" customWidth="1"/>
-    <col min="42" max="43" width="29.3796296296296" customWidth="1"/>
-    <col min="44" max="44" width="24.8796296296296" customWidth="1"/>
-    <col min="45" max="45" width="29.3796296296296" customWidth="1"/>
-    <col min="46" max="47" width="24.8796296296296" customWidth="1"/>
-    <col min="48" max="48" width="27.1296296296296" customWidth="1"/>
+    <col min="42" max="43" width="29.3833333333333" customWidth="1"/>
+    <col min="44" max="44" width="24.8833333333333" customWidth="1"/>
+    <col min="45" max="45" width="29.3833333333333" customWidth="1"/>
+    <col min="46" max="47" width="24.8833333333333" customWidth="1"/>
+    <col min="48" max="48" width="27.1333333333333" customWidth="1"/>
     <col min="49" max="51" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6473,7 +6417,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" s="53" customFormat="1" ht="115.2" spans="1:51">
+    <row r="4" s="53" customFormat="1" ht="108" spans="1:51">
       <c r="A4" s="66"/>
       <c r="B4" s="66"/>
       <c r="C4" s="32" t="s">
@@ -6624,7 +6568,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" s="53" customFormat="1" ht="100.8" spans="1:51">
+    <row r="5" s="53" customFormat="1" ht="94.5" spans="1:51">
       <c r="A5" s="66"/>
       <c r="B5" s="66"/>
       <c r="C5" s="32"/>
@@ -6723,7 +6667,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" s="53" customFormat="1" ht="28.8" spans="1:51">
+    <row r="6" s="53" customFormat="1" ht="27" spans="1:51">
       <c r="A6" s="66"/>
       <c r="B6" s="66"/>
       <c r="C6" s="69" t="s">
@@ -6874,7 +6818,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7" s="53" customFormat="1" ht="57.6" spans="1:51">
+    <row r="7" s="53" customFormat="1" ht="54" spans="1:51">
       <c r="A7" s="70" t="s">
         <v>143</v>
       </c>
@@ -7029,7 +6973,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" ht="72" spans="1:51">
+    <row r="8" ht="67.5" spans="1:51">
       <c r="A8" s="72"/>
       <c r="B8" s="73" t="s">
         <v>147</v>
@@ -7182,7 +7126,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="9" ht="43.2" spans="1:51">
+    <row r="9" ht="40.5" spans="1:51">
       <c r="A9" s="72"/>
       <c r="B9" s="26" t="s">
         <v>170</v>
@@ -7241,7 +7185,7 @@
       <c r="AX9" s="76"/>
       <c r="AY9" s="76"/>
     </row>
-    <row r="10" ht="86.4" spans="1:51">
+    <row r="10" ht="81" spans="1:51">
       <c r="A10" s="77"/>
       <c r="B10" s="26" t="s">
         <v>173</v>
@@ -7420,7 +7364,7 @@
       <c r="AX12" s="54"/>
       <c r="AY12" s="54"/>
     </row>
-    <row r="14" ht="115.2" spans="1:51">
+    <row r="14" ht="94.5" spans="1:51">
       <c r="A14" s="81" t="s">
         <v>183</v>
       </c>
@@ -7598,7 +7542,7 @@
       <c r="AX15" s="80"/>
       <c r="AY15" s="80"/>
     </row>
-    <row r="16" ht="72" spans="1:51">
+    <row r="16" ht="67.5" spans="1:51">
       <c r="A16" s="86"/>
       <c r="B16" s="87" t="s">
         <v>218</v>
@@ -7675,7 +7619,7 @@
       <c r="AX16" s="80"/>
       <c r="AY16" s="80"/>
     </row>
-    <row r="17" ht="86.4" spans="1:51">
+    <row r="17" ht="81" spans="1:51">
       <c r="A17" s="86"/>
       <c r="B17" s="87" t="s">
         <v>229</v>
@@ -7784,7 +7728,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="18" ht="86.4" spans="1:51">
+    <row r="18" ht="81" spans="1:51">
       <c r="A18" s="86"/>
       <c r="B18" s="87" t="s">
         <v>257</v>
@@ -7861,7 +7805,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="19" ht="43.2" spans="1:51">
+    <row r="19" ht="40.5" spans="1:51">
       <c r="A19" s="86"/>
       <c r="B19" s="87" t="s">
         <v>267</v>
@@ -7928,7 +7872,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="20" ht="57.6" spans="1:51">
+    <row r="20" ht="54" spans="1:51">
       <c r="A20" s="86"/>
       <c r="B20" s="87" t="s">
         <v>271</v>
@@ -7985,7 +7929,7 @@
       <c r="AX20" s="80"/>
       <c r="AY20" s="80"/>
     </row>
-    <row r="21" ht="86.4" spans="1:51">
+    <row r="21" ht="81" spans="1:51">
       <c r="A21" s="86"/>
       <c r="B21" s="91" t="s">
         <v>273</v>
@@ -8123,7 +8067,7 @@
       <c r="AX22" s="80"/>
       <c r="AY22" s="80"/>
     </row>
-    <row r="24" ht="115.2" spans="1:51">
+    <row r="24" ht="108" spans="1:51">
       <c r="A24" s="70" t="s">
         <v>285</v>
       </c>
@@ -8333,7 +8277,7 @@
       <c r="AX25" s="76"/>
       <c r="AY25" s="76"/>
     </row>
-    <row r="26" customFormat="1" ht="100.8" spans="1:51">
+    <row r="26" customFormat="1" ht="94.5" spans="1:51">
       <c r="A26" s="77"/>
       <c r="B26" s="26" t="s">
         <v>326</v>
@@ -8398,7 +8342,7 @@
       <c r="AX26" s="76"/>
       <c r="AY26" s="76"/>
     </row>
-    <row r="27" s="54" customFormat="1" ht="28.8" spans="1:51">
+    <row r="27" s="54" customFormat="1" ht="27" spans="1:51">
       <c r="A27" s="78" t="s">
         <v>332</v>
       </c>
@@ -8485,27 +8429,27 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:X52"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="13.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="13.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="14.8888888888889" customWidth="1"/>
-    <col min="8" max="8" width="13.1111111111111" customWidth="1"/>
-    <col min="9" max="9" width="13.2222222222222" customWidth="1"/>
+    <col min="6" max="6" width="14.8916666666667" customWidth="1"/>
+    <col min="8" max="8" width="13.1083333333333" customWidth="1"/>
+    <col min="9" max="9" width="13.225" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="9.77777777777778" customWidth="1"/>
-    <col min="12" max="12" width="4.77777777777778" customWidth="1"/>
+    <col min="11" max="11" width="9.775" customWidth="1"/>
+    <col min="12" max="12" width="4.775" customWidth="1"/>
     <col min="13" max="13" width="5.66666666666667" customWidth="1"/>
     <col min="15" max="15" width="9.66666666666667" customWidth="1"/>
     <col min="16" max="16" width="14.3333333333333" customWidth="1"/>
     <col min="17" max="17" width="9.66666666666667" customWidth="1"/>
-    <col min="19" max="19" width="11.4444444444444" customWidth="1"/>
-    <col min="20" max="20" width="13.5555555555556" customWidth="1"/>
-    <col min="21" max="21" width="9.11111111111111" customWidth="1"/>
-    <col min="23" max="23" width="12.8888888888889" customWidth="1"/>
-    <col min="24" max="24" width="10.2222222222222" customWidth="1"/>
+    <col min="19" max="19" width="11.4416666666667" customWidth="1"/>
+    <col min="20" max="20" width="13.5583333333333" customWidth="1"/>
+    <col min="21" max="21" width="9.10833333333333" customWidth="1"/>
+    <col min="23" max="23" width="12.8916666666667" customWidth="1"/>
+    <col min="24" max="24" width="10.225" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24">
@@ -8590,7 +8534,7 @@
       <c r="W2" s="22"/>
       <c r="X2" s="24"/>
     </row>
-    <row r="3" ht="87.15" spans="1:24">
+    <row r="3" ht="81.75" spans="1:24">
       <c r="A3" s="19"/>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -8652,7 +8596,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="4" s="13" customFormat="1" ht="100.8" spans="1:24">
+    <row r="4" s="13" customFormat="1" ht="94.5" spans="1:24">
       <c r="A4" s="30" t="s">
         <v>348</v>
       </c>
@@ -8694,7 +8638,7 @@
       <c r="W4" s="33"/>
       <c r="X4" s="37"/>
     </row>
-    <row r="5" ht="100.8" spans="1:24">
+    <row r="5" ht="94.5" spans="1:24">
       <c r="A5" s="19"/>
       <c r="B5" s="31"/>
       <c r="C5" s="32" t="s">
@@ -8732,7 +8676,7 @@
       <c r="W5" s="33"/>
       <c r="X5" s="37"/>
     </row>
-    <row r="6" ht="100.8" spans="1:24">
+    <row r="6" ht="81" spans="1:24">
       <c r="A6" s="19"/>
       <c r="B6" s="31"/>
       <c r="C6" s="32" t="s">
@@ -8766,7 +8710,7 @@
       <c r="W6" s="33"/>
       <c r="X6" s="37"/>
     </row>
-    <row r="7" ht="86.4" spans="1:24">
+    <row r="7" ht="81" spans="1:24">
       <c r="A7" s="19"/>
       <c r="B7" s="31"/>
       <c r="C7" s="32" t="s">
@@ -8802,7 +8746,7 @@
       <c r="W7" s="33"/>
       <c r="X7" s="37"/>
     </row>
-    <row r="8" customFormat="1" ht="129.6" spans="1:24">
+    <row r="8" customFormat="1" ht="121.5" spans="1:24">
       <c r="A8" s="19"/>
       <c r="B8" s="31"/>
       <c r="C8" s="32" t="s">
@@ -8840,7 +8784,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="86.4" spans="1:24">
+    <row r="9" customFormat="1" ht="81" spans="1:24">
       <c r="A9" s="19"/>
       <c r="B9" s="31"/>
       <c r="C9" s="32" t="s">
@@ -8878,7 +8822,7 @@
       <c r="W9" s="33"/>
       <c r="X9" s="37"/>
     </row>
-    <row r="10" s="14" customFormat="1" ht="72.75" spans="1:24">
+    <row r="10" s="14" customFormat="1" ht="68.25" spans="1:24">
       <c r="A10" s="19"/>
       <c r="B10" s="31"/>
       <c r="C10" s="32" t="s">
@@ -8914,7 +8858,7 @@
       <c r="W10" s="33"/>
       <c r="X10" s="37"/>
     </row>
-    <row r="11" s="13" customFormat="1" ht="72" spans="1:24">
+    <row r="11" s="13" customFormat="1" ht="54" spans="1:24">
       <c r="A11" s="30" t="s">
         <v>367</v>
       </c>
@@ -8952,7 +8896,7 @@
       <c r="W11" s="33"/>
       <c r="X11" s="37"/>
     </row>
-    <row r="12" customFormat="1" ht="86.4" spans="1:24">
+    <row r="12" customFormat="1" ht="81" spans="1:24">
       <c r="A12" s="19"/>
       <c r="B12" s="31"/>
       <c r="C12" s="32" t="s">
@@ -9002,7 +8946,7 @@
       <c r="W12" s="33"/>
       <c r="X12" s="37"/>
     </row>
-    <row r="13" customFormat="1" ht="57.6" spans="1:24">
+    <row r="13" customFormat="1" ht="54" spans="1:24">
       <c r="A13" s="19"/>
       <c r="B13" s="31"/>
       <c r="C13" s="32" t="s">
@@ -9046,7 +8990,7 @@
       <c r="W13" s="33"/>
       <c r="X13" s="37"/>
     </row>
-    <row r="14" customFormat="1" ht="86.4" spans="1:24">
+    <row r="14" customFormat="1" ht="67.5" spans="1:24">
       <c r="A14" s="19"/>
       <c r="B14" s="31"/>
       <c r="C14" s="32" t="s">
@@ -9084,7 +9028,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="15" customFormat="1" ht="86.4" spans="1:24">
+    <row r="15" customFormat="1" ht="81" spans="1:24">
       <c r="A15" s="19"/>
       <c r="B15" s="31"/>
       <c r="C15" s="32" t="s">
@@ -9126,7 +9070,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="16" s="14" customFormat="1" ht="72.75" spans="1:24">
+    <row r="16" s="14" customFormat="1" ht="68.25" spans="1:24">
       <c r="A16" s="19"/>
       <c r="B16" s="31"/>
       <c r="C16" s="32" t="s">
@@ -9162,7 +9106,7 @@
       <c r="W16" s="33"/>
       <c r="X16" s="37"/>
     </row>
-    <row r="17" s="13" customFormat="1" ht="86.4" spans="1:24">
+    <row r="17" s="13" customFormat="1" ht="67.5" spans="1:24">
       <c r="A17" s="30" t="s">
         <v>382</v>
       </c>
@@ -9200,7 +9144,7 @@
       <c r="W17" s="33"/>
       <c r="X17" s="37"/>
     </row>
-    <row r="18" customFormat="1" ht="86.4" spans="1:24">
+    <row r="18" customFormat="1" ht="81" spans="1:24">
       <c r="A18" s="19"/>
       <c r="B18" s="31"/>
       <c r="C18" s="32" t="s">
@@ -9236,7 +9180,7 @@
       <c r="W18" s="33"/>
       <c r="X18" s="37"/>
     </row>
-    <row r="19" customFormat="1" ht="86.4" spans="1:24">
+    <row r="19" customFormat="1" ht="81" spans="1:24">
       <c r="A19" s="19"/>
       <c r="B19" s="31"/>
       <c r="C19" s="32" t="s">
@@ -9272,7 +9216,7 @@
       <c r="W19" s="33"/>
       <c r="X19" s="37"/>
     </row>
-    <row r="20" customFormat="1" ht="57.6" spans="1:24">
+    <row r="20" customFormat="1" ht="54" spans="1:24">
       <c r="A20" s="19"/>
       <c r="B20" s="31"/>
       <c r="C20" s="32" t="s">
@@ -9310,7 +9254,7 @@
       <c r="W20" s="33"/>
       <c r="X20" s="37"/>
     </row>
-    <row r="21" customFormat="1" ht="144" spans="1:24">
+    <row r="21" customFormat="1" ht="121.5" spans="1:24">
       <c r="A21" s="19"/>
       <c r="B21" s="31"/>
       <c r="C21" s="32" t="s">
@@ -9348,7 +9292,7 @@
       <c r="W21" s="33"/>
       <c r="X21" s="37"/>
     </row>
-    <row r="22" s="14" customFormat="1" ht="87.15" spans="1:24">
+    <row r="22" s="14" customFormat="1" ht="81.75" spans="1:24">
       <c r="A22" s="19"/>
       <c r="B22" s="31"/>
       <c r="C22" s="32" t="s">
@@ -9386,7 +9330,7 @@
       <c r="W22" s="33"/>
       <c r="X22" s="37"/>
     </row>
-    <row r="23" s="13" customFormat="1" ht="72" spans="1:24">
+    <row r="23" s="13" customFormat="1" ht="67.5" spans="1:24">
       <c r="A23" s="30" t="s">
         <v>396</v>
       </c>
@@ -9462,7 +9406,7 @@
       <c r="W24" s="33"/>
       <c r="X24" s="37"/>
     </row>
-    <row r="25" customFormat="1" ht="72" spans="1:24">
+    <row r="25" customFormat="1" ht="67.5" spans="1:24">
       <c r="A25" s="19"/>
       <c r="B25" s="31"/>
       <c r="C25" s="32" t="s">
@@ -9500,7 +9444,7 @@
       <c r="W25" s="33"/>
       <c r="X25" s="37"/>
     </row>
-    <row r="26" s="14" customFormat="1" ht="87.15" spans="1:24">
+    <row r="26" s="14" customFormat="1" ht="81.75" spans="1:24">
       <c r="A26" s="19"/>
       <c r="B26" s="31"/>
       <c r="C26" s="32" t="s">
@@ -9538,7 +9482,7 @@
       <c r="W26" s="33"/>
       <c r="X26" s="37"/>
     </row>
-    <row r="27" s="13" customFormat="1" ht="72" spans="1:24">
+    <row r="27" s="13" customFormat="1" ht="67.5" spans="1:24">
       <c r="A27" s="30" t="s">
         <v>407</v>
       </c>
@@ -9584,7 +9528,7 @@
       <c r="W27" s="33"/>
       <c r="X27" s="37"/>
     </row>
-    <row r="28" customFormat="1" ht="201.6" spans="1:24">
+    <row r="28" customFormat="1" ht="162" spans="1:24">
       <c r="A28" s="19"/>
       <c r="B28" s="31"/>
       <c r="C28" s="32" t="s">
@@ -9628,7 +9572,7 @@
       <c r="W28" s="33"/>
       <c r="X28" s="37"/>
     </row>
-    <row r="29" s="14" customFormat="1" ht="144.75" spans="1:24">
+    <row r="29" s="14" customFormat="1" ht="135.75" spans="1:24">
       <c r="A29" s="19"/>
       <c r="B29" s="31"/>
       <c r="C29" s="32" t="s">
@@ -9670,7 +9614,7 @@
       <c r="W29" s="33"/>
       <c r="X29" s="37"/>
     </row>
-    <row r="30" s="13" customFormat="1" ht="100.8" spans="1:24">
+    <row r="30" s="13" customFormat="1" ht="94.5" spans="1:24">
       <c r="A30" s="30" t="s">
         <v>415</v>
       </c>
@@ -9712,7 +9656,7 @@
       <c r="W30" s="33"/>
       <c r="X30" s="37"/>
     </row>
-    <row r="31" customFormat="1" ht="86.4" spans="1:24">
+    <row r="31" customFormat="1" ht="81" spans="1:24">
       <c r="A31" s="19"/>
       <c r="B31" s="31"/>
       <c r="C31" s="32" t="s">
@@ -9748,7 +9692,7 @@
       <c r="W31" s="33"/>
       <c r="X31" s="37"/>
     </row>
-    <row r="32" customFormat="1" ht="72" spans="1:24">
+    <row r="32" customFormat="1" ht="67.5" spans="1:24">
       <c r="A32" s="19"/>
       <c r="B32" s="31"/>
       <c r="C32" s="32" t="s">
@@ -9788,7 +9732,7 @@
       <c r="W32" s="33"/>
       <c r="X32" s="37"/>
     </row>
-    <row r="33" customFormat="1" ht="86.4" spans="1:24">
+    <row r="33" customFormat="1" ht="81" spans="1:24">
       <c r="A33" s="19"/>
       <c r="B33" s="31"/>
       <c r="C33" s="32" t="s">
@@ -9826,7 +9770,7 @@
       <c r="W33" s="33"/>
       <c r="X33" s="37"/>
     </row>
-    <row r="34" customFormat="1" ht="86.4" spans="1:24">
+    <row r="34" customFormat="1" ht="81" spans="1:24">
       <c r="A34" s="19"/>
       <c r="B34" s="31"/>
       <c r="C34" s="32" t="s">
@@ -9862,7 +9806,7 @@
       <c r="W34" s="41"/>
       <c r="X34" s="42"/>
     </row>
-    <row r="35" s="14" customFormat="1" ht="115.95" spans="1:24">
+    <row r="35" s="14" customFormat="1" ht="95.25" spans="1:24">
       <c r="A35" s="19"/>
       <c r="B35" s="31"/>
       <c r="C35" s="32" t="s">
@@ -9900,7 +9844,7 @@
       <c r="W35" s="33"/>
       <c r="X35" s="37"/>
     </row>
-    <row r="36" s="13" customFormat="1" ht="100.8" spans="1:24">
+    <row r="36" s="13" customFormat="1" ht="94.5" spans="1:24">
       <c r="A36" s="30" t="s">
         <v>429</v>
       </c>
@@ -9944,7 +9888,7 @@
       <c r="W36" s="33"/>
       <c r="X36" s="37"/>
     </row>
-    <row r="37" customFormat="1" ht="144" spans="1:24">
+    <row r="37" customFormat="1" ht="108" spans="1:24">
       <c r="A37" s="19"/>
       <c r="B37" s="31"/>
       <c r="C37" s="32" t="s">
@@ -9986,7 +9930,7 @@
       <c r="W37" s="33"/>
       <c r="X37" s="37"/>
     </row>
-    <row r="38" s="14" customFormat="1" ht="115.95" spans="1:24">
+    <row r="38" s="14" customFormat="1" ht="95.25" spans="1:24">
       <c r="A38" s="19"/>
       <c r="B38" s="31"/>
       <c r="C38" s="32" t="s">
@@ -10022,7 +9966,7 @@
       <c r="W38" s="33"/>
       <c r="X38" s="37"/>
     </row>
-    <row r="39" s="13" customFormat="1" ht="144" spans="1:24">
+    <row r="39" s="13" customFormat="1" ht="108" spans="1:24">
       <c r="A39" s="30" t="s">
         <v>438</v>
       </c>
@@ -10062,13 +10006,13 @@
       <c r="W39" s="33"/>
       <c r="X39" s="37"/>
     </row>
-    <row r="40" customFormat="1" ht="216" spans="1:24">
+    <row r="40" customFormat="1" ht="67.5" spans="1:24">
       <c r="A40" s="19"/>
       <c r="B40" s="31"/>
       <c r="C40" s="32" t="s">
         <v>442</v>
       </c>
-      <c r="D40" s="32" t="s">
+      <c r="D40" s="43" t="s">
         <v>443</v>
       </c>
       <c r="E40" s="32"/>
@@ -10102,7 +10046,7 @@
       <c r="W40" s="33"/>
       <c r="X40" s="37"/>
     </row>
-    <row r="41" customFormat="1" ht="129.6" spans="1:24">
+    <row r="41" customFormat="1" ht="81" spans="1:24">
       <c r="A41" s="19"/>
       <c r="B41" s="31"/>
       <c r="C41" s="32" t="s">
@@ -10142,7 +10086,7 @@
       <c r="W41" s="33"/>
       <c r="X41" s="37"/>
     </row>
-    <row r="42" customFormat="1" ht="172.8" spans="1:24">
+    <row r="42" customFormat="1" ht="81" spans="1:24">
       <c r="A42" s="19"/>
       <c r="B42" s="31"/>
       <c r="C42" s="32" t="s">
@@ -10186,7 +10130,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="216" spans="1:24">
+    <row r="43" customFormat="1" ht="148.5" spans="1:24">
       <c r="A43" s="19"/>
       <c r="B43" s="31"/>
       <c r="C43" s="32" t="s">
@@ -10232,7 +10176,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="187.2" spans="1:24">
+    <row r="44" customFormat="1" ht="54" spans="1:24">
       <c r="A44" s="19"/>
       <c r="B44" s="31"/>
       <c r="C44" s="32" t="s">
@@ -10266,7 +10210,7 @@
       <c r="W44" s="33"/>
       <c r="X44" s="37"/>
     </row>
-    <row r="45" s="14" customFormat="1" ht="216.75" spans="1:24">
+    <row r="45" s="14" customFormat="1" ht="95.25" spans="1:24">
       <c r="A45" s="19"/>
       <c r="B45" s="31"/>
       <c r="C45" s="32" t="s">
@@ -10304,7 +10248,7 @@
       <c r="W45" s="33"/>
       <c r="X45" s="37"/>
     </row>
-    <row r="46" s="13" customFormat="1" ht="158.4" spans="1:24">
+    <row r="46" s="13" customFormat="1" ht="121.5" spans="1:24">
       <c r="A46" s="30" t="s">
         <v>454</v>
       </c>
@@ -10348,7 +10292,7 @@
       <c r="W46" s="33"/>
       <c r="X46" s="37"/>
     </row>
-    <row r="47" customFormat="1" ht="100.8" spans="1:24">
+    <row r="47" customFormat="1" ht="40.5" spans="1:24">
       <c r="A47" s="19"/>
       <c r="B47" s="31"/>
       <c r="C47" s="32" t="s">
@@ -10388,7 +10332,7 @@
       <c r="W47" s="33"/>
       <c r="X47" s="37"/>
     </row>
-    <row r="48" s="14" customFormat="1" ht="144.75" spans="1:24">
+    <row r="48" s="14" customFormat="1" ht="95.25" spans="1:24">
       <c r="A48" s="19"/>
       <c r="B48" s="31"/>
       <c r="C48" s="32" t="s">
@@ -10426,7 +10370,7 @@
       <c r="W48" s="33"/>
       <c r="X48" s="37"/>
     </row>
-    <row r="49" s="13" customFormat="1" ht="187.2" spans="1:24">
+    <row r="49" s="13" customFormat="1" ht="148.5" spans="1:24">
       <c r="A49" s="30" t="s">
         <v>462</v>
       </c>
@@ -10470,7 +10414,7 @@
       <c r="W49" s="33"/>
       <c r="X49" s="37"/>
     </row>
-    <row r="50" customFormat="1" ht="144" spans="1:24">
+    <row r="50" customFormat="1" ht="81" spans="1:24">
       <c r="A50" s="19"/>
       <c r="B50" s="31"/>
       <c r="C50" s="32" t="s">
@@ -10508,7 +10452,7 @@
       <c r="W50" s="33"/>
       <c r="X50" s="37"/>
     </row>
-    <row r="51" customFormat="1" ht="172.8" spans="1:24">
+    <row r="51" customFormat="1" ht="94.5" spans="1:24">
       <c r="A51" s="19"/>
       <c r="B51" s="31"/>
       <c r="C51" s="32" t="s">
@@ -10546,7 +10490,7 @@
       <c r="W51" s="33"/>
       <c r="X51" s="37"/>
     </row>
-    <row r="52" s="14" customFormat="1" ht="144.75" spans="1:24">
+    <row r="52" s="14" customFormat="1" ht="68.25" spans="1:24">
       <c r="A52" s="44"/>
       <c r="B52" s="45"/>
       <c r="C52" s="46" t="s">
@@ -10779,7 +10723,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -10791,7 +10735,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -10802,11 +10746,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="21.25" customWidth="1"/>
-    <col min="4" max="4" width="77.1296296296296" customWidth="1"/>
+    <col min="4" max="4" width="77.1333333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
@@ -10843,7 +10787,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="4" ht="100.8" spans="1:4">
+    <row r="4" ht="94.5" spans="1:4">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="5" t="s">
@@ -10853,7 +10797,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="5" ht="28.8" spans="1:4">
+    <row r="5" ht="27" spans="1:4">
       <c r="A5" s="7" t="s">
         <v>483</v>
       </c>
@@ -10905,7 +10849,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="9" ht="28.8" spans="1:4">
+    <row r="9" ht="27" spans="1:4">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="7" t="s">
@@ -10925,7 +10869,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="11" ht="43.2" spans="1:4">
+    <row r="11" ht="40.5" spans="1:4">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="7" t="s">
@@ -10935,7 +10879,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="12" ht="28.8" spans="1:4">
+    <row r="12" ht="27" spans="1:4">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="7" t="s">
@@ -10961,10 +10905,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="39.8796296296296" customWidth="1"/>
+    <col min="2" max="2" width="39.8833333333333" customWidth="1"/>
     <col min="3" max="3" width="63.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11134,7 +11078,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -11145,7 +11089,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="526">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="528">
   <si>
     <t>项目整合管理</t>
   </si>
@@ -4022,8 +4022,7 @@
     <t>估算成本（规划）</t>
   </si>
   <si>
-    <t>1确定项目所需的资金
-2对项目所需资源成本进行近似估算</t>
+    <t>1对项目资源成本进行估算来确定项目所需资金</t>
   </si>
   <si>
     <t>制定预算（规划）</t>
@@ -4039,8 +4038,7 @@
 2维护成本基准、管理成本基准变更</t>
   </si>
   <si>
-    <t>工作绩效信息
-成本预测</t>
+    <t>成本预测</t>
   </si>
   <si>
     <t>项目质量
@@ -4054,6 +4052,11 @@
   </si>
   <si>
     <t>1规划和证明识别可交付成果的质量要求标准</t>
+  </si>
+  <si>
+    <t>头脑风暴
+访谈
+标杆对照</t>
   </si>
   <si>
     <t>管理质量（执行）</t>
@@ -4182,8 +4185,13 @@
     <t>实施定量风险分析（规划）</t>
   </si>
   <si>
-    <t>1对单个风险对项目目标影响做定量分析
+    <t>1单个风险对项目目标影响做定量分析
 2量化项目整体风险最大可能性</t>
+  </si>
+  <si>
+    <t>模拟（蒙特卡洛分析）
+敏感性分析（龙卷风）
+决策树分析</t>
   </si>
   <si>
     <t>规划风险应对（规划）</t>
@@ -4219,7 +4227,7 @@
     <t>规划采购管理（规划）</t>
   </si>
   <si>
-    <t>1确定是否从外部获取货物服务，获取什么样的、何时、如何获取外部货物服务
+    <t>1确定是否从外部获取货物服务，获取什么样的、怎么、何时获取外部货物服务
 2明确采购决策、方法并识别潜在卖方</t>
   </si>
   <si>
@@ -9254,7 +9262,7 @@
       <c r="W20" s="33"/>
       <c r="X20" s="37"/>
     </row>
-    <row r="21" customFormat="1" ht="121.5" spans="1:24">
+    <row r="21" customFormat="1" ht="137" customHeight="1" spans="1:24">
       <c r="A21" s="19"/>
       <c r="B21" s="31"/>
       <c r="C21" s="32" t="s">
@@ -9510,7 +9518,7 @@
       <c r="M27" s="38"/>
       <c r="N27" s="38"/>
       <c r="O27" s="35" t="s">
-        <v>222</v>
+        <v>411</v>
       </c>
       <c r="P27" s="35" t="s">
         <v>241</v>
@@ -9532,10 +9540,10 @@
       <c r="A28" s="19"/>
       <c r="B28" s="31"/>
       <c r="C28" s="32" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E28" s="32"/>
       <c r="F28" s="7"/>
@@ -9576,10 +9584,10 @@
       <c r="A29" s="19"/>
       <c r="B29" s="31"/>
       <c r="C29" s="32" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E29" s="32"/>
       <c r="F29" s="7"/>
@@ -9616,16 +9624,16 @@
     </row>
     <row r="30" s="13" customFormat="1" ht="94.5" spans="1:24">
       <c r="A30" s="30" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C30" s="32" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="7"/>
@@ -9660,10 +9668,10 @@
       <c r="A31" s="19"/>
       <c r="B31" s="31"/>
       <c r="C31" s="32" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E31" s="32"/>
       <c r="F31" s="7"/>
@@ -9696,10 +9704,10 @@
       <c r="A32" s="19"/>
       <c r="B32" s="31"/>
       <c r="C32" s="32" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E32" s="32"/>
       <c r="F32" s="7"/>
@@ -9736,10 +9744,10 @@
       <c r="A33" s="19"/>
       <c r="B33" s="31"/>
       <c r="C33" s="32" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E33" s="32"/>
       <c r="F33" s="7"/>
@@ -9774,10 +9782,10 @@
       <c r="A34" s="19"/>
       <c r="B34" s="31"/>
       <c r="C34" s="32" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E34" s="32"/>
       <c r="F34" s="7"/>
@@ -9810,10 +9818,10 @@
       <c r="A35" s="19"/>
       <c r="B35" s="31"/>
       <c r="C35" s="32" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E35" s="32"/>
       <c r="F35" s="7"/>
@@ -9846,16 +9854,16 @@
     </row>
     <row r="36" s="13" customFormat="1" ht="94.5" spans="1:24">
       <c r="A36" s="30" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B36" s="31" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C36" s="32" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E36" s="32"/>
       <c r="F36" s="7"/>
@@ -9867,7 +9875,7 @@
       <c r="J36" s="33"/>
       <c r="K36" s="33"/>
       <c r="L36" s="38" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M36" s="38"/>
       <c r="N36" s="38"/>
@@ -9892,10 +9900,10 @@
       <c r="A37" s="19"/>
       <c r="B37" s="31"/>
       <c r="C37" s="32" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E37" s="32"/>
       <c r="F37" s="7"/>
@@ -9934,10 +9942,10 @@
       <c r="A38" s="19"/>
       <c r="B38" s="31"/>
       <c r="C38" s="32" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E38" s="32"/>
       <c r="F38" s="7"/>
@@ -9968,16 +9976,16 @@
     </row>
     <row r="39" s="13" customFormat="1" ht="108" spans="1:24">
       <c r="A39" s="30" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B39" s="31" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C39" s="32" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D39" s="43" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E39" s="32"/>
       <c r="F39" s="7"/>
@@ -10010,10 +10018,10 @@
       <c r="A40" s="19"/>
       <c r="B40" s="31"/>
       <c r="C40" s="32" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="D40" s="43" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E40" s="32"/>
       <c r="F40" s="7"/>
@@ -10050,10 +10058,10 @@
       <c r="A41" s="19"/>
       <c r="B41" s="31"/>
       <c r="C41" s="32" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D41" s="43" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E41" s="32"/>
       <c r="F41" s="7"/>
@@ -10090,10 +10098,10 @@
       <c r="A42" s="19"/>
       <c r="B42" s="31"/>
       <c r="C42" s="32" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D42" s="43" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E42" s="32"/>
       <c r="F42" s="7"/>
@@ -10113,7 +10121,7 @@
         <v>226</v>
       </c>
       <c r="P42" s="35" t="s">
-        <v>248</v>
+        <v>449</v>
       </c>
       <c r="Q42" s="35"/>
       <c r="R42" s="35"/>
@@ -10134,10 +10142,10 @@
       <c r="A43" s="19"/>
       <c r="B43" s="31"/>
       <c r="C43" s="32" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="D43" s="43" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E43" s="32"/>
       <c r="F43" s="7"/>
@@ -10180,10 +10188,10 @@
       <c r="A44" s="19"/>
       <c r="B44" s="31"/>
       <c r="C44" s="32" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D44" s="43" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E44" s="32"/>
       <c r="F44" s="7"/>
@@ -10214,10 +10222,10 @@
       <c r="A45" s="19"/>
       <c r="B45" s="31"/>
       <c r="C45" s="32" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="D45" s="43" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E45" s="32"/>
       <c r="F45" s="7"/>
@@ -10250,16 +10258,16 @@
     </row>
     <row r="46" s="13" customFormat="1" ht="121.5" spans="1:24">
       <c r="A46" s="30" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B46" s="31" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C46" s="32" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D46" s="43" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E46" s="32"/>
       <c r="F46" s="7"/>
@@ -10296,10 +10304,10 @@
       <c r="A47" s="19"/>
       <c r="B47" s="31"/>
       <c r="C47" s="32" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="D47" s="43" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E47" s="32"/>
       <c r="F47" s="7"/>
@@ -10336,10 +10344,10 @@
       <c r="A48" s="19"/>
       <c r="B48" s="31"/>
       <c r="C48" s="32" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="D48" s="43" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E48" s="32"/>
       <c r="F48" s="7"/>
@@ -10372,16 +10380,16 @@
     </row>
     <row r="49" s="13" customFormat="1" ht="148.5" spans="1:24">
       <c r="A49" s="30" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B49" s="31" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E49" s="32"/>
       <c r="F49" s="7"/>
@@ -10418,10 +10426,10 @@
       <c r="A50" s="19"/>
       <c r="B50" s="31"/>
       <c r="C50" s="32" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E50" s="32"/>
       <c r="F50" s="7"/>
@@ -10456,10 +10464,10 @@
       <c r="A51" s="19"/>
       <c r="B51" s="31"/>
       <c r="C51" s="32" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="D51" s="43" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E51" s="32"/>
       <c r="F51" s="7"/>
@@ -10471,7 +10479,7 @@
       <c r="J51" s="33"/>
       <c r="K51" s="33"/>
       <c r="L51" s="38" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="M51" s="38"/>
       <c r="N51" s="38"/>
@@ -10494,10 +10502,10 @@
       <c r="A52" s="44"/>
       <c r="B52" s="45"/>
       <c r="C52" s="46" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="D52" s="47" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E52" s="46"/>
       <c r="F52" s="48"/>
@@ -10755,138 +10763,138 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="9" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
       <c r="C2" s="7" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="7" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
     </row>
     <row r="4" ht="94.5" spans="1:4">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="5" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
     </row>
     <row r="5" ht="27" spans="1:4">
       <c r="A5" s="7" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="7" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="7" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="10" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:4">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="7" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
       <c r="C10" s="7" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
     </row>
     <row r="11" ht="40.5" spans="1:4">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="7" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
     </row>
     <row r="12" ht="27" spans="1:4">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="7" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
   </sheetData>
@@ -10914,7 +10922,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
@@ -10922,31 +10930,31 @@
     <row r="2" spans="1:3">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -10957,31 +10965,31 @@
     <row r="7" spans="1:3">
       <c r="A7" s="6"/>
       <c r="B7" s="8" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -10992,38 +11000,38 @@
     <row r="12" spans="1:3">
       <c r="A12" s="6"/>
       <c r="B12" s="8" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="6"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6"/>
       <c r="B14" s="4"/>
       <c r="C14" s="5" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6"/>
       <c r="B15" s="4"/>
       <c r="C15" s="5" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="6"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -11034,31 +11042,31 @@
     <row r="18" spans="1:3">
       <c r="A18" s="6"/>
       <c r="B18" s="8" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
       <c r="C19" s="7" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6"/>
       <c r="B20" s="4"/>
       <c r="C20" s="7" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="6"/>
       <c r="B21" s="4"/>
       <c r="C21" s="7" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
   </sheetData>

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="896" uniqueCount="535">
   <si>
     <t>项目整合管理</t>
   </si>
@@ -3790,6 +3790,9 @@
 变更请求</t>
   </si>
   <si>
+    <t>49过程立足于绩效系统2025和2026工程去理解</t>
+  </si>
+  <si>
     <t>十大管理</t>
   </si>
   <si>
@@ -3809,10 +3812,19 @@
     <t>写作思路</t>
   </si>
   <si>
+    <t>非整规划输入</t>
+  </si>
+  <si>
+    <t>非整监控输入</t>
+  </si>
+  <si>
     <t>通用输入</t>
   </si>
   <si>
     <t>通用工具技术</t>
+  </si>
+  <si>
+    <t>非整监控输出</t>
   </si>
   <si>
     <t>通用输出</t>
@@ -3842,7 +3854,7 @@
 管理</t>
   </si>
   <si>
-    <t>识别、联系、统一协调项目管理各过程，并贯穿项目始终</t>
+    <t>识别、定义、联系、统一协调项目管理各过程，并贯穿项目始终</t>
   </si>
   <si>
     <t>制定项目章程
@@ -3860,6 +3872,12 @@
   </si>
   <si>
     <t>项目管理计划各组成部分</t>
+  </si>
+  <si>
+    <t>头脑风暴
+焦点小组
+访谈
+核对单</t>
   </si>
   <si>
     <t>指导与管理项目工作（执行）</t>
@@ -3890,7 +3908,7 @@
 3使干系人了解项目情况和认可项目行动</t>
   </si>
   <si>
-    <t>工作绩效信息（非数据）
+    <t>工作绩效信息
 协议</t>
   </si>
   <si>
@@ -3898,6 +3916,10 @@
   </si>
   <si>
     <t>1管理、沟通、审查、批准项目可交付成果、项目管理计划、项目文件的变更</t>
+  </si>
+  <si>
+    <t>工作绩效报告
+变更请求</t>
   </si>
   <si>
     <t>结束项目或阶段（收尾）</t>
@@ -3926,7 +3948,14 @@
   </si>
   <si>
     <t>1确定、记录、管理干系人需求
-2作为产品范围和项目范围的基础</t>
+2作为项目范围和产品范围的基础</t>
+  </si>
+  <si>
+    <t>头脑风暴
+焦点小组
+访谈
+问卷调查
+标杆对照</t>
   </si>
   <si>
     <t>定义范围（规划）</t>
@@ -3975,7 +4004,7 @@
     <t>定义活动（规划）</t>
   </si>
   <si>
-    <t>1将工作包分解为进度活动 2是项目进度估算、规划、执行、监督和控制的基础</t>
+    <t>1将工作包分解为进度活动 2是项目进度估算、规划、执行、监控的基础</t>
   </si>
   <si>
     <t>排列活动顺序（规划）</t>
@@ -4022,7 +4051,7 @@
     <t>估算成本（规划）</t>
   </si>
   <si>
-    <t>1对项目资源成本进行估算来确定项目所需资金</t>
+    <t>1对项目所需资源成本进行估算来确定项目所需资金</t>
   </si>
   <si>
     <t>制定预算（规划）</t>
@@ -5446,7 +5475,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -5491,6 +5520,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5796,14 +5828,14 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>340995</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1847850</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>233045</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5820,8 +5852,55 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2794000" y="17538700"/>
-          <a:ext cx="11545570" cy="6191250"/>
+          <a:off x="2794000" y="17536795"/>
+          <a:ext cx="5043805" cy="2710815"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>153670</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>196850</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="图片 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="153670" y="180975"/>
+          <a:ext cx="6856095" cy="2701925"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6131,2274 +6210,2274 @@
     <row r="1" spans="1:51">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="56" t="s">
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
+      <c r="J1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="K1" s="56"/>
-      <c r="L1" s="56"/>
-      <c r="M1" s="56"/>
-      <c r="N1" s="56"/>
-      <c r="O1" s="56"/>
-      <c r="P1" s="56" t="s">
+      <c r="K1" s="57"/>
+      <c r="L1" s="57"/>
+      <c r="M1" s="57"/>
+      <c r="N1" s="57"/>
+      <c r="O1" s="57"/>
+      <c r="P1" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="56"/>
-      <c r="R1" s="56"/>
-      <c r="S1" s="56"/>
-      <c r="T1" s="56"/>
-      <c r="U1" s="56"/>
-      <c r="V1" s="56" t="s">
+      <c r="Q1" s="57"/>
+      <c r="R1" s="57"/>
+      <c r="S1" s="57"/>
+      <c r="T1" s="57"/>
+      <c r="U1" s="57"/>
+      <c r="V1" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="56"/>
-      <c r="X1" s="56"/>
-      <c r="Y1" s="56"/>
-      <c r="Z1" s="56" t="s">
+      <c r="W1" s="57"/>
+      <c r="X1" s="57"/>
+      <c r="Y1" s="57"/>
+      <c r="Z1" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="56"/>
-      <c r="AB1" s="56"/>
-      <c r="AC1" s="56" t="s">
+      <c r="AA1" s="57"/>
+      <c r="AB1" s="57"/>
+      <c r="AC1" s="57" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="56"/>
-      <c r="AE1" s="56"/>
-      <c r="AF1" s="56"/>
-      <c r="AG1" s="56"/>
-      <c r="AH1" s="56"/>
-      <c r="AI1" s="56" t="s">
+      <c r="AD1" s="57"/>
+      <c r="AE1" s="57"/>
+      <c r="AF1" s="57"/>
+      <c r="AG1" s="57"/>
+      <c r="AH1" s="57"/>
+      <c r="AI1" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="AJ1" s="56"/>
-      <c r="AK1" s="56"/>
-      <c r="AL1" s="56" t="s">
+      <c r="AJ1" s="57"/>
+      <c r="AK1" s="57"/>
+      <c r="AL1" s="57" t="s">
         <v>7</v>
       </c>
-      <c r="AM1" s="56"/>
-      <c r="AN1" s="56"/>
-      <c r="AO1" s="56"/>
-      <c r="AP1" s="56"/>
-      <c r="AQ1" s="56"/>
-      <c r="AR1" s="56"/>
-      <c r="AS1" s="56" t="s">
+      <c r="AM1" s="57"/>
+      <c r="AN1" s="57"/>
+      <c r="AO1" s="57"/>
+      <c r="AP1" s="57"/>
+      <c r="AQ1" s="57"/>
+      <c r="AR1" s="57"/>
+      <c r="AS1" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="AT1" s="56"/>
-      <c r="AU1" s="56"/>
-      <c r="AV1" s="56" t="s">
+      <c r="AT1" s="57"/>
+      <c r="AU1" s="57"/>
+      <c r="AV1" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="AW1" s="56"/>
-      <c r="AX1" s="56"/>
-      <c r="AY1" s="56"/>
+      <c r="AW1" s="57"/>
+      <c r="AX1" s="57"/>
+      <c r="AY1" s="57"/>
     </row>
     <row r="2" customFormat="1" ht="58" customHeight="1" spans="1:51">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="58" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="59" t="s">
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="60" t="s">
         <v>11</v>
       </c>
-      <c r="K2" s="60"/>
-      <c r="L2" s="60"/>
-      <c r="M2" s="60"/>
-      <c r="N2" s="60"/>
-      <c r="O2" s="60"/>
-      <c r="P2" s="61" t="s">
+      <c r="K2" s="61"/>
+      <c r="L2" s="61"/>
+      <c r="M2" s="61"/>
+      <c r="N2" s="61"/>
+      <c r="O2" s="61"/>
+      <c r="P2" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="Q2" s="60"/>
-      <c r="R2" s="60"/>
-      <c r="S2" s="60"/>
-      <c r="T2" s="60"/>
-      <c r="U2" s="62"/>
-      <c r="V2" s="61" t="s">
+      <c r="Q2" s="61"/>
+      <c r="R2" s="61"/>
+      <c r="S2" s="61"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="63"/>
+      <c r="V2" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="W2" s="60"/>
-      <c r="X2" s="60"/>
-      <c r="Y2" s="62"/>
-      <c r="Z2" s="59" t="s">
+      <c r="W2" s="61"/>
+      <c r="X2" s="61"/>
+      <c r="Y2" s="63"/>
+      <c r="Z2" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="60"/>
-      <c r="AB2" s="62"/>
-      <c r="AC2" s="61" t="s">
+      <c r="AA2" s="61"/>
+      <c r="AB2" s="63"/>
+      <c r="AC2" s="62" t="s">
         <v>15</v>
       </c>
-      <c r="AD2" s="60"/>
-      <c r="AE2" s="60"/>
-      <c r="AF2" s="60"/>
-      <c r="AG2" s="60"/>
-      <c r="AH2" s="62"/>
-      <c r="AI2" s="61" t="s">
+      <c r="AD2" s="61"/>
+      <c r="AE2" s="61"/>
+      <c r="AF2" s="61"/>
+      <c r="AG2" s="61"/>
+      <c r="AH2" s="63"/>
+      <c r="AI2" s="62" t="s">
         <v>16</v>
       </c>
-      <c r="AJ2" s="60"/>
-      <c r="AK2" s="62"/>
-      <c r="AL2" s="61" t="s">
+      <c r="AJ2" s="61"/>
+      <c r="AK2" s="63"/>
+      <c r="AL2" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="AM2" s="60"/>
-      <c r="AN2" s="60"/>
-      <c r="AO2" s="60"/>
-      <c r="AP2" s="60"/>
-      <c r="AQ2" s="60"/>
-      <c r="AR2" s="62"/>
-      <c r="AS2" s="63" t="s">
+      <c r="AM2" s="61"/>
+      <c r="AN2" s="61"/>
+      <c r="AO2" s="61"/>
+      <c r="AP2" s="61"/>
+      <c r="AQ2" s="61"/>
+      <c r="AR2" s="63"/>
+      <c r="AS2" s="64" t="s">
         <v>18</v>
       </c>
-      <c r="AT2" s="64"/>
-      <c r="AU2" s="65"/>
-      <c r="AV2" s="61" t="s">
+      <c r="AT2" s="65"/>
+      <c r="AU2" s="66"/>
+      <c r="AV2" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="AW2" s="60"/>
-      <c r="AX2" s="60"/>
-      <c r="AY2" s="62"/>
+      <c r="AW2" s="61"/>
+      <c r="AX2" s="61"/>
+      <c r="AY2" s="63"/>
     </row>
-    <row r="3" s="53" customFormat="1" spans="1:51">
-      <c r="A3" s="66"/>
-      <c r="B3" s="66"/>
-      <c r="C3" s="67" t="s">
+    <row r="3" s="54" customFormat="1" spans="1:51">
+      <c r="A3" s="67"/>
+      <c r="B3" s="67"/>
+      <c r="C3" s="68" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="67" t="s">
+      <c r="D3" s="68" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="67" t="s">
+      <c r="E3" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="F3" s="67" t="s">
+      <c r="F3" s="68" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="67" t="s">
+      <c r="G3" s="68" t="s">
         <v>24</v>
       </c>
-      <c r="H3" s="67" t="s">
+      <c r="H3" s="68" t="s">
         <v>25</v>
       </c>
-      <c r="I3" s="67" t="s">
+      <c r="I3" s="68" t="s">
         <v>26</v>
       </c>
-      <c r="J3" s="68" t="s">
+      <c r="J3" s="69" t="s">
         <v>27</v>
       </c>
-      <c r="K3" s="68" t="s">
+      <c r="K3" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="L3" s="68" t="s">
+      <c r="L3" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="68" t="s">
+      <c r="M3" s="69" t="s">
         <v>30</v>
       </c>
-      <c r="N3" s="68" t="s">
+      <c r="N3" s="69" t="s">
         <v>31</v>
       </c>
-      <c r="O3" s="68" t="s">
+      <c r="O3" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="P3" s="68" t="s">
+      <c r="P3" s="69" t="s">
         <v>33</v>
       </c>
-      <c r="Q3" s="68" t="s">
+      <c r="Q3" s="69" t="s">
         <v>34</v>
       </c>
-      <c r="R3" s="68" t="s">
+      <c r="R3" s="69" t="s">
         <v>35</v>
       </c>
-      <c r="S3" s="68" t="s">
+      <c r="S3" s="69" t="s">
         <v>36</v>
       </c>
-      <c r="T3" s="68" t="s">
+      <c r="T3" s="69" t="s">
         <v>37</v>
       </c>
-      <c r="U3" s="68" t="s">
+      <c r="U3" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="V3" s="68" t="s">
+      <c r="V3" s="69" t="s">
         <v>39</v>
       </c>
-      <c r="W3" s="68" t="s">
+      <c r="W3" s="69" t="s">
         <v>40</v>
       </c>
-      <c r="X3" s="68" t="s">
+      <c r="X3" s="69" t="s">
         <v>41</v>
       </c>
-      <c r="Y3" s="68" t="s">
+      <c r="Y3" s="69" t="s">
         <v>42</v>
       </c>
-      <c r="Z3" s="68" t="s">
+      <c r="Z3" s="69" t="s">
         <v>43</v>
       </c>
-      <c r="AA3" s="68" t="s">
+      <c r="AA3" s="69" t="s">
         <v>44</v>
       </c>
-      <c r="AB3" s="68" t="s">
+      <c r="AB3" s="69" t="s">
         <v>45</v>
       </c>
-      <c r="AC3" s="68" t="s">
+      <c r="AC3" s="69" t="s">
         <v>46</v>
       </c>
-      <c r="AD3" s="68" t="s">
+      <c r="AD3" s="69" t="s">
         <v>47</v>
       </c>
-      <c r="AE3" s="68" t="s">
+      <c r="AE3" s="69" t="s">
         <v>48</v>
       </c>
-      <c r="AF3" s="68" t="s">
+      <c r="AF3" s="69" t="s">
         <v>49</v>
       </c>
-      <c r="AG3" s="68" t="s">
+      <c r="AG3" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="AH3" s="68" t="s">
+      <c r="AH3" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="AI3" s="68" t="s">
+      <c r="AI3" s="69" t="s">
         <v>52</v>
       </c>
-      <c r="AJ3" s="68" t="s">
+      <c r="AJ3" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="AK3" s="68" t="s">
+      <c r="AK3" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="AL3" s="68" t="s">
+      <c r="AL3" s="69" t="s">
         <v>55</v>
       </c>
-      <c r="AM3" s="68" t="s">
+      <c r="AM3" s="69" t="s">
         <v>56</v>
       </c>
-      <c r="AN3" s="68" t="s">
+      <c r="AN3" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="AO3" s="68" t="s">
+      <c r="AO3" s="69" t="s">
         <v>58</v>
       </c>
-      <c r="AP3" s="68" t="s">
+      <c r="AP3" s="69" t="s">
         <v>59</v>
       </c>
-      <c r="AQ3" s="68" t="s">
+      <c r="AQ3" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="AR3" s="68" t="s">
+      <c r="AR3" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="AS3" s="67" t="s">
+      <c r="AS3" s="68" t="s">
         <v>62</v>
       </c>
-      <c r="AT3" s="67" t="s">
+      <c r="AT3" s="68" t="s">
         <v>63</v>
       </c>
-      <c r="AU3" s="67" t="s">
+      <c r="AU3" s="68" t="s">
         <v>64</v>
       </c>
-      <c r="AV3" s="67" t="s">
+      <c r="AV3" s="68" t="s">
         <v>65</v>
       </c>
-      <c r="AW3" s="67" t="s">
+      <c r="AW3" s="68" t="s">
         <v>66</v>
       </c>
-      <c r="AX3" s="67" t="s">
+      <c r="AX3" s="68" t="s">
         <v>67</v>
       </c>
-      <c r="AY3" s="67" t="s">
+      <c r="AY3" s="68" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="4" s="53" customFormat="1" ht="108" spans="1:51">
-      <c r="A4" s="66"/>
-      <c r="B4" s="66"/>
-      <c r="C4" s="32" t="s">
+    <row r="4" s="54" customFormat="1" ht="108" spans="1:51">
+      <c r="A4" s="67"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="33" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="32" t="s">
+      <c r="D4" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="32" t="s">
+      <c r="E4" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="32" t="s">
+      <c r="G4" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="32" t="s">
+      <c r="I4" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="32" t="s">
+      <c r="J4" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="32" t="s">
+      <c r="K4" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="32" t="s">
+      <c r="L4" s="33" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="32" t="s">
+      <c r="M4" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="N4" s="32" t="s">
+      <c r="N4" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="O4" s="32" t="s">
+      <c r="O4" s="33" t="s">
         <v>81</v>
       </c>
-      <c r="P4" s="32" t="s">
+      <c r="P4" s="33" t="s">
         <v>82</v>
       </c>
-      <c r="Q4" s="32" t="s">
+      <c r="Q4" s="33" t="s">
         <v>83</v>
       </c>
-      <c r="R4" s="32" t="s">
+      <c r="R4" s="33" t="s">
         <v>84</v>
       </c>
-      <c r="S4" s="32" t="s">
+      <c r="S4" s="33" t="s">
         <v>85</v>
       </c>
-      <c r="T4" s="32" t="s">
+      <c r="T4" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="U4" s="32" t="s">
+      <c r="U4" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="V4" s="32" t="s">
+      <c r="V4" s="33" t="s">
         <v>88</v>
       </c>
-      <c r="W4" s="32" t="s">
+      <c r="W4" s="33" t="s">
         <v>89</v>
       </c>
-      <c r="X4" s="32" t="s">
+      <c r="X4" s="33" t="s">
         <v>90</v>
       </c>
-      <c r="Y4" s="32" t="s">
+      <c r="Y4" s="33" t="s">
         <v>91</v>
       </c>
-      <c r="Z4" s="32" t="s">
+      <c r="Z4" s="33" t="s">
         <v>92</v>
       </c>
-      <c r="AA4" s="32" t="s">
+      <c r="AA4" s="33" t="s">
         <v>93</v>
       </c>
-      <c r="AB4" s="32" t="s">
+      <c r="AB4" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="AC4" s="32" t="s">
+      <c r="AC4" s="33" t="s">
         <v>95</v>
       </c>
-      <c r="AD4" s="32" t="s">
+      <c r="AD4" s="33" t="s">
         <v>96</v>
       </c>
-      <c r="AE4" s="32" t="s">
+      <c r="AE4" s="33" t="s">
         <v>97</v>
       </c>
-      <c r="AF4" s="32" t="s">
+      <c r="AF4" s="33" t="s">
         <v>98</v>
       </c>
-      <c r="AG4" s="32" t="s">
+      <c r="AG4" s="33" t="s">
         <v>99</v>
       </c>
-      <c r="AH4" s="32" t="s">
+      <c r="AH4" s="33" t="s">
         <v>100</v>
       </c>
-      <c r="AI4" s="32" t="s">
+      <c r="AI4" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="AJ4" s="32" t="s">
+      <c r="AJ4" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="AK4" s="32" t="s">
+      <c r="AK4" s="33" t="s">
         <v>103</v>
       </c>
-      <c r="AL4" s="32" t="s">
+      <c r="AL4" s="33" t="s">
         <v>104</v>
       </c>
-      <c r="AM4" s="32" t="s">
+      <c r="AM4" s="33" t="s">
         <v>105</v>
       </c>
-      <c r="AN4" s="32" t="s">
+      <c r="AN4" s="33" t="s">
         <v>106</v>
       </c>
-      <c r="AO4" s="32" t="s">
+      <c r="AO4" s="33" t="s">
         <v>107</v>
       </c>
-      <c r="AP4" s="32" t="s">
+      <c r="AP4" s="33" t="s">
         <v>108</v>
       </c>
-      <c r="AQ4" s="32" t="s">
+      <c r="AQ4" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="AR4" s="32" t="s">
+      <c r="AR4" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="AS4" s="32" t="s">
+      <c r="AS4" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="AT4" s="32" t="s">
+      <c r="AT4" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="AU4" s="32" t="s">
+      <c r="AU4" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="AV4" s="32" t="s">
+      <c r="AV4" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="AW4" s="32" t="s">
+      <c r="AW4" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="AX4" s="32" t="s">
+      <c r="AX4" s="33" t="s">
         <v>116</v>
       </c>
-      <c r="AY4" s="32" t="s">
+      <c r="AY4" s="33" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" s="53" customFormat="1" ht="94.5" spans="1:51">
-      <c r="A5" s="66"/>
-      <c r="B5" s="66"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="32"/>
-      <c r="L5" s="32"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
-      <c r="O5" s="32"/>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="32"/>
-      <c r="R5" s="32"/>
-      <c r="S5" s="32"/>
-      <c r="T5" s="32"/>
-      <c r="U5" s="32"/>
-      <c r="V5" s="32"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="32"/>
-      <c r="Y5" s="32"/>
-      <c r="Z5" s="32"/>
-      <c r="AA5" s="32"/>
-      <c r="AB5" s="32"/>
-      <c r="AC5" s="32" t="s">
+    <row r="5" s="54" customFormat="1" ht="94.5" spans="1:51">
+      <c r="A5" s="67"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
+      <c r="J5" s="33"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="33"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="33"/>
+      <c r="P5" s="33"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="33"/>
+      <c r="S5" s="33"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="33"/>
+      <c r="Y5" s="33"/>
+      <c r="Z5" s="33"/>
+      <c r="AA5" s="33"/>
+      <c r="AB5" s="33"/>
+      <c r="AC5" s="33" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="32" t="s">
+      <c r="AD5" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="AE5" s="32" t="s">
+      <c r="AE5" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="AF5" s="32" t="s">
+      <c r="AF5" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="AG5" s="32" t="s">
+      <c r="AG5" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="AH5" s="32" t="s">
+      <c r="AH5" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="AI5" s="32" t="s">
+      <c r="AI5" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="AJ5" s="32" t="s">
+      <c r="AJ5" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="AK5" s="32" t="s">
+      <c r="AK5" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="AL5" s="32" t="s">
+      <c r="AL5" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="AM5" s="32" t="s">
+      <c r="AM5" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="AN5" s="32" t="s">
+      <c r="AN5" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="AO5" s="32" t="s">
+      <c r="AO5" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="AP5" s="32" t="s">
+      <c r="AP5" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="AQ5" s="32" t="s">
+      <c r="AQ5" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="AR5" s="32" t="s">
+      <c r="AR5" s="33" t="s">
         <v>133</v>
       </c>
-      <c r="AS5" s="32" t="s">
+      <c r="AS5" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="AT5" s="32" t="s">
+      <c r="AT5" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="AU5" s="32" t="s">
+      <c r="AU5" s="33" t="s">
         <v>136</v>
       </c>
-      <c r="AV5" s="32" t="s">
+      <c r="AV5" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="AW5" s="32" t="s">
+      <c r="AW5" s="33" t="s">
         <v>138</v>
       </c>
-      <c r="AX5" s="32" t="s">
+      <c r="AX5" s="33" t="s">
         <v>139</v>
       </c>
-      <c r="AY5" s="32" t="s">
+      <c r="AY5" s="33" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="6" s="53" customFormat="1" ht="27" spans="1:51">
-      <c r="A6" s="66"/>
-      <c r="B6" s="66"/>
-      <c r="C6" s="69" t="s">
+    <row r="6" s="54" customFormat="1" ht="27" spans="1:51">
+      <c r="A6" s="67"/>
+      <c r="B6" s="67"/>
+      <c r="C6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="69" t="s">
+      <c r="D6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="E6" s="69" t="s">
+      <c r="E6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="F6" s="69" t="s">
+      <c r="F6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="G6" s="69" t="s">
+      <c r="G6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="H6" s="69" t="s">
+      <c r="H6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="J6" s="69" t="s">
+      <c r="J6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="K6" s="69" t="s">
+      <c r="K6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="L6" s="69" t="s">
+      <c r="L6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="M6" s="69" t="s">
+      <c r="M6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="N6" s="69" t="s">
+      <c r="N6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="O6" s="69" t="s">
+      <c r="O6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="P6" s="69" t="s">
+      <c r="P6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="Q6" s="69" t="s">
+      <c r="Q6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="R6" s="69" t="s">
+      <c r="R6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="S6" s="69" t="s">
+      <c r="S6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="T6" s="69" t="s">
+      <c r="T6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="U6" s="69" t="s">
+      <c r="U6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="V6" s="32" t="s">
+      <c r="V6" s="33" t="s">
         <v>142</v>
       </c>
-      <c r="W6" s="69" t="s">
+      <c r="W6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="X6" s="69" t="s">
+      <c r="X6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="Y6" s="69" t="s">
+      <c r="Y6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="Z6" s="69" t="s">
+      <c r="Z6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AA6" s="69" t="s">
+      <c r="AA6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AB6" s="69" t="s">
+      <c r="AB6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AC6" s="69" t="s">
+      <c r="AC6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AD6" s="69" t="s">
+      <c r="AD6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AE6" s="69" t="s">
+      <c r="AE6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AF6" s="69" t="s">
+      <c r="AF6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AG6" s="69" t="s">
+      <c r="AG6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AH6" s="69" t="s">
+      <c r="AH6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AI6" s="69" t="s">
+      <c r="AI6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AJ6" s="69" t="s">
+      <c r="AJ6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AK6" s="69" t="s">
+      <c r="AK6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AL6" s="69" t="s">
+      <c r="AL6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AM6" s="69" t="s">
+      <c r="AM6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AN6" s="69" t="s">
+      <c r="AN6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AO6" s="69" t="s">
+      <c r="AO6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AP6" s="69" t="s">
+      <c r="AP6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AQ6" s="69" t="s">
+      <c r="AQ6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AR6" s="69" t="s">
+      <c r="AR6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AS6" s="69" t="s">
+      <c r="AS6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AT6" s="69" t="s">
+      <c r="AT6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AU6" s="69" t="s">
+      <c r="AU6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AV6" s="69" t="s">
+      <c r="AV6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AW6" s="69" t="s">
+      <c r="AW6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AX6" s="69" t="s">
+      <c r="AX6" s="70" t="s">
         <v>141</v>
       </c>
-      <c r="AY6" s="69" t="s">
+      <c r="AY6" s="70" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="7" s="53" customFormat="1" ht="54" spans="1:51">
-      <c r="A7" s="70" t="s">
+    <row r="7" s="54" customFormat="1" ht="54" spans="1:51">
+      <c r="A7" s="71" t="s">
         <v>143</v>
       </c>
-      <c r="B7" s="69" t="s">
+      <c r="B7" s="70" t="s">
         <v>144</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="72" t="s">
         <v>145</v>
       </c>
-      <c r="D7" s="69" t="s">
+      <c r="D7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="E7" s="69" t="s">
+      <c r="E7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="F7" s="69" t="s">
+      <c r="F7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="G7" s="69" t="s">
+      <c r="G7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="H7" s="69" t="s">
+      <c r="H7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="I7" s="69" t="s">
+      <c r="I7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="J7" s="69" t="s">
+      <c r="J7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="K7" s="69" t="s">
+      <c r="K7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="L7" s="69" t="s">
+      <c r="L7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="M7" s="69" t="s">
+      <c r="M7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="N7" s="69" t="s">
+      <c r="N7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="O7" s="69" t="s">
+      <c r="O7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="P7" s="69" t="s">
+      <c r="P7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="Q7" s="69" t="s">
+      <c r="Q7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="R7" s="69" t="s">
+      <c r="R7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="S7" s="69" t="s">
+      <c r="S7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="T7" s="69" t="s">
+      <c r="T7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="U7" s="69" t="s">
+      <c r="U7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="V7" s="32" t="s">
+      <c r="V7" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="W7" s="69" t="s">
+      <c r="W7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="X7" s="69" t="s">
+      <c r="X7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="Y7" s="69" t="s">
+      <c r="Y7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="Z7" s="69" t="s">
+      <c r="Z7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AA7" s="69" t="s">
+      <c r="AA7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AB7" s="69" t="s">
+      <c r="AB7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AC7" s="69" t="s">
+      <c r="AC7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AD7" s="69" t="s">
+      <c r="AD7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AE7" s="69" t="s">
+      <c r="AE7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AF7" s="69" t="s">
+      <c r="AF7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AG7" s="69" t="s">
+      <c r="AG7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AH7" s="69" t="s">
+      <c r="AH7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AI7" s="69" t="s">
+      <c r="AI7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AJ7" s="69" t="s">
+      <c r="AJ7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AK7" s="69" t="s">
+      <c r="AK7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AL7" s="69" t="s">
+      <c r="AL7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AM7" s="69" t="s">
+      <c r="AM7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AN7" s="69" t="s">
+      <c r="AN7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AO7" s="69" t="s">
+      <c r="AO7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AP7" s="69" t="s">
+      <c r="AP7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AQ7" s="69" t="s">
+      <c r="AQ7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AR7" s="69" t="s">
+      <c r="AR7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AS7" s="69" t="s">
+      <c r="AS7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AT7" s="69" t="s">
+      <c r="AT7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AU7" s="69" t="s">
+      <c r="AU7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AV7" s="69" t="s">
+      <c r="AV7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AW7" s="69" t="s">
+      <c r="AW7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AX7" s="69" t="s">
+      <c r="AX7" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="AY7" s="69" t="s">
+      <c r="AY7" s="70" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="8" ht="67.5" spans="1:51">
-      <c r="A8" s="72"/>
-      <c r="B8" s="73" t="s">
+      <c r="A8" s="73"/>
+      <c r="B8" s="74" t="s">
         <v>147</v>
       </c>
-      <c r="C8" s="74" t="s">
+      <c r="C8" s="75" t="s">
         <v>148</v>
       </c>
-      <c r="D8" s="74" t="s">
+      <c r="D8" s="75" t="s">
         <v>149</v>
       </c>
-      <c r="E8" s="74" t="s">
+      <c r="E8" s="75" t="s">
         <v>150</v>
       </c>
-      <c r="F8" s="74" t="s">
+      <c r="F8" s="75" t="s">
         <v>151</v>
       </c>
-      <c r="G8" s="74" t="s">
+      <c r="G8" s="75" t="s">
         <v>152</v>
       </c>
-      <c r="H8" s="74" t="s">
+      <c r="H8" s="75" t="s">
         <v>153</v>
       </c>
-      <c r="I8" s="74" t="s">
+      <c r="I8" s="75" t="s">
         <v>154</v>
       </c>
-      <c r="J8" s="74" t="s">
+      <c r="J8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="K8" s="74" t="s">
+      <c r="K8" s="75" t="s">
         <v>156</v>
       </c>
-      <c r="L8" s="74" t="s">
+      <c r="L8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="M8" s="74" t="s">
+      <c r="M8" s="75" t="s">
         <v>157</v>
       </c>
-      <c r="N8" s="74" t="s">
+      <c r="N8" s="75" t="s">
         <v>158</v>
       </c>
-      <c r="O8" s="74" t="s">
+      <c r="O8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="P8" s="74" t="s">
+      <c r="P8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="Q8" s="74" t="s">
+      <c r="Q8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="R8" s="74" t="s">
+      <c r="R8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="S8" s="74" t="s">
+      <c r="S8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="T8" s="74" t="s">
+      <c r="T8" s="75" t="s">
         <v>159</v>
       </c>
-      <c r="U8" s="74" t="s">
+      <c r="U8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="V8" s="74" t="s">
+      <c r="V8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="W8" s="74" t="s">
+      <c r="W8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="X8" s="74" t="s">
+      <c r="X8" s="75" t="s">
         <v>160</v>
       </c>
-      <c r="Y8" s="74" t="s">
+      <c r="Y8" s="75" t="s">
         <v>161</v>
       </c>
-      <c r="Z8" s="74" t="s">
+      <c r="Z8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AA8" s="74" t="s">
+      <c r="AA8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AB8" s="74" t="s">
+      <c r="AB8" s="75" t="s">
         <v>162</v>
       </c>
-      <c r="AC8" s="74" t="s">
+      <c r="AC8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AD8" s="74" t="s">
+      <c r="AD8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AE8" s="74" t="s">
+      <c r="AE8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AF8" s="74" t="s">
+      <c r="AF8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AG8" s="74" t="s">
+      <c r="AG8" s="75" t="s">
         <v>163</v>
       </c>
-      <c r="AH8" s="74" t="s">
+      <c r="AH8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AI8" s="74" t="s">
+      <c r="AI8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AJ8" s="74" t="s">
+      <c r="AJ8" s="75" t="s">
         <v>164</v>
       </c>
-      <c r="AK8" s="74" t="s">
+      <c r="AK8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AL8" s="74" t="s">
+      <c r="AL8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AM8" s="74" t="s">
+      <c r="AM8" s="75" t="s">
         <v>165</v>
       </c>
-      <c r="AN8" s="74" t="s">
+      <c r="AN8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AO8" s="74" t="s">
+      <c r="AO8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AP8" s="74" t="s">
+      <c r="AP8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AQ8" s="74" t="s">
+      <c r="AQ8" s="75" t="s">
         <v>155</v>
       </c>
-      <c r="AR8" s="74" t="s">
+      <c r="AR8" s="75" t="s">
         <v>164</v>
       </c>
-      <c r="AS8" s="75" t="s">
+      <c r="AS8" s="76" t="s">
         <v>166</v>
       </c>
-      <c r="AT8" s="75" t="s">
+      <c r="AT8" s="76" t="s">
         <v>167</v>
       </c>
-      <c r="AU8" s="75" t="s">
+      <c r="AU8" s="76" t="s">
         <v>168</v>
       </c>
-      <c r="AV8" s="75" t="s">
+      <c r="AV8" s="76" t="s">
         <v>169</v>
       </c>
-      <c r="AW8" s="75" t="s">
+      <c r="AW8" s="76" t="s">
         <v>159</v>
       </c>
-      <c r="AX8" s="76" t="s">
+      <c r="AX8" s="77" t="s">
         <v>155</v>
       </c>
-      <c r="AY8" s="76" t="s">
+      <c r="AY8" s="77" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="9" ht="40.5" spans="1:51">
-      <c r="A9" s="72"/>
-      <c r="B9" s="26" t="s">
+      <c r="A9" s="73"/>
+      <c r="B9" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="C9" s="75"/>
-      <c r="D9" s="75"/>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
-      <c r="J9" s="75"/>
-      <c r="K9" s="75" t="s">
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="76"/>
+      <c r="F9" s="76"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="76"/>
+      <c r="J9" s="76"/>
+      <c r="K9" s="76" t="s">
         <v>171</v>
       </c>
-      <c r="L9" s="75"/>
-      <c r="M9" s="75"/>
-      <c r="N9" s="75" t="s">
+      <c r="L9" s="76"/>
+      <c r="M9" s="76"/>
+      <c r="N9" s="76" t="s">
         <v>172</v>
       </c>
-      <c r="O9" s="75"/>
-      <c r="P9" s="75"/>
-      <c r="Q9" s="75"/>
-      <c r="R9" s="75"/>
-      <c r="S9" s="75"/>
-      <c r="T9" s="75"/>
-      <c r="U9" s="75"/>
-      <c r="V9" s="75"/>
-      <c r="W9" s="75"/>
-      <c r="X9" s="75"/>
-      <c r="Y9" s="75"/>
-      <c r="Z9" s="75"/>
-      <c r="AA9" s="75"/>
-      <c r="AB9" s="75"/>
-      <c r="AC9" s="75"/>
-      <c r="AD9" s="75"/>
-      <c r="AE9" s="75"/>
-      <c r="AF9" s="75"/>
-      <c r="AG9" s="75"/>
-      <c r="AH9" s="75"/>
-      <c r="AI9" s="75"/>
-      <c r="AJ9" s="75"/>
-      <c r="AK9" s="75"/>
-      <c r="AL9" s="75"/>
-      <c r="AM9" s="75"/>
-      <c r="AN9" s="75"/>
-      <c r="AO9" s="75"/>
-      <c r="AP9" s="75"/>
-      <c r="AQ9" s="75"/>
-      <c r="AR9" s="75"/>
-      <c r="AS9" s="75"/>
-      <c r="AT9" s="75"/>
-      <c r="AU9" s="75"/>
-      <c r="AV9" s="75"/>
-      <c r="AW9" s="75"/>
-      <c r="AX9" s="76"/>
-      <c r="AY9" s="76"/>
+      <c r="O9" s="76"/>
+      <c r="P9" s="76"/>
+      <c r="Q9" s="76"/>
+      <c r="R9" s="76"/>
+      <c r="S9" s="76"/>
+      <c r="T9" s="76"/>
+      <c r="U9" s="76"/>
+      <c r="V9" s="76"/>
+      <c r="W9" s="76"/>
+      <c r="X9" s="76"/>
+      <c r="Y9" s="76"/>
+      <c r="Z9" s="76"/>
+      <c r="AA9" s="76"/>
+      <c r="AB9" s="76"/>
+      <c r="AC9" s="76"/>
+      <c r="AD9" s="76"/>
+      <c r="AE9" s="76"/>
+      <c r="AF9" s="76"/>
+      <c r="AG9" s="76"/>
+      <c r="AH9" s="76"/>
+      <c r="AI9" s="76"/>
+      <c r="AJ9" s="76"/>
+      <c r="AK9" s="76"/>
+      <c r="AL9" s="76"/>
+      <c r="AM9" s="76"/>
+      <c r="AN9" s="76"/>
+      <c r="AO9" s="76"/>
+      <c r="AP9" s="76"/>
+      <c r="AQ9" s="76"/>
+      <c r="AR9" s="76"/>
+      <c r="AS9" s="76"/>
+      <c r="AT9" s="76"/>
+      <c r="AU9" s="76"/>
+      <c r="AV9" s="76"/>
+      <c r="AW9" s="76"/>
+      <c r="AX9" s="77"/>
+      <c r="AY9" s="77"/>
     </row>
     <row r="10" ht="81" spans="1:51">
-      <c r="A10" s="77"/>
-      <c r="B10" s="26" t="s">
+      <c r="A10" s="78"/>
+      <c r="B10" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="C10" s="75"/>
-      <c r="D10" s="75"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
-      <c r="J10" s="75"/>
-      <c r="K10" s="75" t="s">
+      <c r="C10" s="76"/>
+      <c r="D10" s="76"/>
+      <c r="E10" s="76"/>
+      <c r="F10" s="76"/>
+      <c r="G10" s="76"/>
+      <c r="H10" s="76"/>
+      <c r="I10" s="76"/>
+      <c r="J10" s="76"/>
+      <c r="K10" s="76" t="s">
         <v>174</v>
       </c>
-      <c r="L10" s="75" t="s">
+      <c r="L10" s="76" t="s">
         <v>175</v>
       </c>
-      <c r="M10" s="75"/>
-      <c r="N10" s="75" t="s">
+      <c r="M10" s="76"/>
+      <c r="N10" s="76" t="s">
         <v>176</v>
       </c>
-      <c r="O10" s="75"/>
-      <c r="P10" s="75"/>
-      <c r="Q10" s="75"/>
-      <c r="R10" s="75"/>
-      <c r="S10" s="75"/>
-      <c r="T10" s="75"/>
-      <c r="U10" s="75"/>
-      <c r="V10" s="75"/>
-      <c r="W10" s="75"/>
-      <c r="X10" s="75"/>
-      <c r="Y10" s="75"/>
-      <c r="Z10" s="75"/>
-      <c r="AA10" s="75" t="s">
+      <c r="O10" s="76"/>
+      <c r="P10" s="76"/>
+      <c r="Q10" s="76"/>
+      <c r="R10" s="76"/>
+      <c r="S10" s="76"/>
+      <c r="T10" s="76"/>
+      <c r="U10" s="76"/>
+      <c r="V10" s="76"/>
+      <c r="W10" s="76"/>
+      <c r="X10" s="76"/>
+      <c r="Y10" s="76"/>
+      <c r="Z10" s="76"/>
+      <c r="AA10" s="76" t="s">
         <v>177</v>
       </c>
-      <c r="AB10" s="75"/>
-      <c r="AC10" s="75"/>
-      <c r="AD10" s="75"/>
-      <c r="AE10" s="75"/>
-      <c r="AF10" s="75"/>
-      <c r="AG10" s="75"/>
-      <c r="AH10" s="75"/>
-      <c r="AI10" s="75"/>
-      <c r="AJ10" s="75" t="s">
+      <c r="AB10" s="76"/>
+      <c r="AC10" s="76"/>
+      <c r="AD10" s="76"/>
+      <c r="AE10" s="76"/>
+      <c r="AF10" s="76"/>
+      <c r="AG10" s="76"/>
+      <c r="AH10" s="76"/>
+      <c r="AI10" s="76"/>
+      <c r="AJ10" s="76" t="s">
         <v>178</v>
       </c>
-      <c r="AK10" s="75"/>
-      <c r="AL10" s="75"/>
-      <c r="AM10" s="75"/>
-      <c r="AN10" s="75"/>
-      <c r="AO10" s="75"/>
-      <c r="AP10" s="75"/>
-      <c r="AQ10" s="75"/>
-      <c r="AR10" s="75"/>
-      <c r="AS10" s="75"/>
-      <c r="AT10" s="75"/>
-      <c r="AU10" s="75"/>
-      <c r="AV10" s="75"/>
-      <c r="AW10" s="75"/>
-      <c r="AX10" s="76"/>
-      <c r="AY10" s="76"/>
+      <c r="AK10" s="76"/>
+      <c r="AL10" s="76"/>
+      <c r="AM10" s="76"/>
+      <c r="AN10" s="76"/>
+      <c r="AO10" s="76"/>
+      <c r="AP10" s="76"/>
+      <c r="AQ10" s="76"/>
+      <c r="AR10" s="76"/>
+      <c r="AS10" s="76"/>
+      <c r="AT10" s="76"/>
+      <c r="AU10" s="76"/>
+      <c r="AV10" s="76"/>
+      <c r="AW10" s="76"/>
+      <c r="AX10" s="77"/>
+      <c r="AY10" s="77"/>
     </row>
     <row r="11" spans="1:51">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="79" t="s">
         <v>179</v>
       </c>
-      <c r="B11" s="79" t="s">
+      <c r="B11" s="80" t="s">
         <v>180</v>
       </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
-      <c r="F11" s="54"/>
-      <c r="G11" s="54"/>
-      <c r="H11" s="54"/>
-      <c r="I11" s="54"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="54"/>
-      <c r="L11" s="54"/>
-      <c r="M11" s="54"/>
-      <c r="N11" s="54"/>
-      <c r="O11" s="54"/>
-      <c r="P11" s="54"/>
-      <c r="Q11" s="54"/>
-      <c r="R11" s="54"/>
-      <c r="S11" s="54"/>
-      <c r="T11" s="54"/>
-      <c r="U11" s="54"/>
-      <c r="V11" s="54"/>
-      <c r="W11" s="54"/>
-      <c r="X11" s="54"/>
-      <c r="Y11" s="54"/>
-      <c r="Z11" s="54"/>
-      <c r="AA11" s="54"/>
-      <c r="AB11" s="54"/>
-      <c r="AC11" s="54"/>
-      <c r="AD11" s="54"/>
-      <c r="AE11" s="54"/>
-      <c r="AF11" s="54"/>
-      <c r="AG11" s="54"/>
-      <c r="AH11" s="54"/>
-      <c r="AI11" s="54"/>
-      <c r="AJ11" s="54"/>
-      <c r="AK11" s="54"/>
-      <c r="AL11" s="54"/>
-      <c r="AM11" s="54"/>
-      <c r="AN11" s="54"/>
-      <c r="AO11" s="54"/>
-      <c r="AP11" s="54"/>
-      <c r="AQ11" s="54"/>
-      <c r="AR11" s="54"/>
-      <c r="AS11" s="54"/>
-      <c r="AT11" s="54"/>
-      <c r="AU11" s="54"/>
-      <c r="AV11" s="54"/>
-      <c r="AW11" s="54"/>
-      <c r="AX11" s="54"/>
-      <c r="AY11" s="54"/>
+      <c r="C11" s="55"/>
+      <c r="D11" s="55"/>
+      <c r="E11" s="55"/>
+      <c r="F11" s="55"/>
+      <c r="G11" s="55"/>
+      <c r="H11" s="55"/>
+      <c r="I11" s="55"/>
+      <c r="J11" s="55"/>
+      <c r="K11" s="55"/>
+      <c r="L11" s="55"/>
+      <c r="M11" s="55"/>
+      <c r="N11" s="55"/>
+      <c r="O11" s="55"/>
+      <c r="P11" s="55"/>
+      <c r="Q11" s="55"/>
+      <c r="R11" s="55"/>
+      <c r="S11" s="55"/>
+      <c r="T11" s="55"/>
+      <c r="U11" s="55"/>
+      <c r="V11" s="55"/>
+      <c r="W11" s="55"/>
+      <c r="X11" s="55"/>
+      <c r="Y11" s="55"/>
+      <c r="Z11" s="55"/>
+      <c r="AA11" s="55"/>
+      <c r="AB11" s="55"/>
+      <c r="AC11" s="55"/>
+      <c r="AD11" s="55"/>
+      <c r="AE11" s="55"/>
+      <c r="AF11" s="55"/>
+      <c r="AG11" s="55"/>
+      <c r="AH11" s="55"/>
+      <c r="AI11" s="55"/>
+      <c r="AJ11" s="55"/>
+      <c r="AK11" s="55"/>
+      <c r="AL11" s="55"/>
+      <c r="AM11" s="55"/>
+      <c r="AN11" s="55"/>
+      <c r="AO11" s="55"/>
+      <c r="AP11" s="55"/>
+      <c r="AQ11" s="55"/>
+      <c r="AR11" s="55"/>
+      <c r="AS11" s="55"/>
+      <c r="AT11" s="55"/>
+      <c r="AU11" s="55"/>
+      <c r="AV11" s="55"/>
+      <c r="AW11" s="55"/>
+      <c r="AX11" s="55"/>
+      <c r="AY11" s="55"/>
     </row>
     <row r="12" spans="1:51">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="79" t="s">
         <v>181</v>
       </c>
-      <c r="B12" s="80" t="s">
+      <c r="B12" s="81" t="s">
         <v>182</v>
       </c>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="54"/>
-      <c r="I12" s="54"/>
-      <c r="J12" s="54"/>
-      <c r="K12" s="54"/>
-      <c r="L12" s="54"/>
-      <c r="M12" s="54"/>
-      <c r="N12" s="54"/>
-      <c r="O12" s="54"/>
-      <c r="P12" s="54"/>
-      <c r="Q12" s="54"/>
-      <c r="R12" s="54"/>
-      <c r="S12" s="54"/>
-      <c r="T12" s="54"/>
-      <c r="U12" s="54"/>
-      <c r="V12" s="54"/>
-      <c r="W12" s="54"/>
-      <c r="X12" s="54"/>
-      <c r="Y12" s="54"/>
-      <c r="Z12" s="54"/>
-      <c r="AA12" s="54"/>
-      <c r="AB12" s="54"/>
-      <c r="AC12" s="54"/>
-      <c r="AD12" s="54"/>
-      <c r="AE12" s="54"/>
-      <c r="AF12" s="54"/>
-      <c r="AG12" s="54"/>
-      <c r="AH12" s="54"/>
-      <c r="AI12" s="54"/>
-      <c r="AJ12" s="54"/>
-      <c r="AK12" s="54"/>
-      <c r="AL12" s="54"/>
-      <c r="AM12" s="54"/>
-      <c r="AN12" s="54"/>
-      <c r="AO12" s="54"/>
-      <c r="AP12" s="54"/>
-      <c r="AQ12" s="54"/>
-      <c r="AR12" s="54"/>
-      <c r="AS12" s="54"/>
-      <c r="AT12" s="54"/>
-      <c r="AU12" s="54"/>
-      <c r="AV12" s="54"/>
-      <c r="AW12" s="54"/>
-      <c r="AX12" s="54"/>
-      <c r="AY12" s="54"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="55"/>
+      <c r="K12" s="55"/>
+      <c r="L12" s="55"/>
+      <c r="M12" s="55"/>
+      <c r="N12" s="55"/>
+      <c r="O12" s="55"/>
+      <c r="P12" s="55"/>
+      <c r="Q12" s="55"/>
+      <c r="R12" s="55"/>
+      <c r="S12" s="55"/>
+      <c r="T12" s="55"/>
+      <c r="U12" s="55"/>
+      <c r="V12" s="55"/>
+      <c r="W12" s="55"/>
+      <c r="X12" s="55"/>
+      <c r="Y12" s="55"/>
+      <c r="Z12" s="55"/>
+      <c r="AA12" s="55"/>
+      <c r="AB12" s="55"/>
+      <c r="AC12" s="55"/>
+      <c r="AD12" s="55"/>
+      <c r="AE12" s="55"/>
+      <c r="AF12" s="55"/>
+      <c r="AG12" s="55"/>
+      <c r="AH12" s="55"/>
+      <c r="AI12" s="55"/>
+      <c r="AJ12" s="55"/>
+      <c r="AK12" s="55"/>
+      <c r="AL12" s="55"/>
+      <c r="AM12" s="55"/>
+      <c r="AN12" s="55"/>
+      <c r="AO12" s="55"/>
+      <c r="AP12" s="55"/>
+      <c r="AQ12" s="55"/>
+      <c r="AR12" s="55"/>
+      <c r="AS12" s="55"/>
+      <c r="AT12" s="55"/>
+      <c r="AU12" s="55"/>
+      <c r="AV12" s="55"/>
+      <c r="AW12" s="55"/>
+      <c r="AX12" s="55"/>
+      <c r="AY12" s="55"/>
     </row>
     <row r="14" ht="94.5" spans="1:51">
-      <c r="A14" s="81" t="s">
+      <c r="A14" s="82" t="s">
         <v>183</v>
       </c>
-      <c r="B14" s="82" t="s">
+      <c r="B14" s="83" t="s">
         <v>184</v>
       </c>
-      <c r="C14" s="83"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="84" t="s">
+      <c r="C14" s="84"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="85" t="s">
         <v>185</v>
       </c>
-      <c r="G14" s="84"/>
-      <c r="H14" s="84" t="s">
+      <c r="G14" s="85"/>
+      <c r="H14" s="85" t="s">
         <v>186</v>
       </c>
-      <c r="I14" s="84"/>
-      <c r="J14" s="84"/>
-      <c r="K14" s="84" t="s">
+      <c r="I14" s="85"/>
+      <c r="J14" s="85"/>
+      <c r="K14" s="85" t="s">
         <v>187</v>
       </c>
-      <c r="L14" s="84" t="s">
+      <c r="L14" s="85" t="s">
         <v>188</v>
       </c>
-      <c r="M14" s="84" t="s">
+      <c r="M14" s="85" t="s">
         <v>189</v>
       </c>
-      <c r="N14" s="84" t="s">
+      <c r="N14" s="85" t="s">
         <v>190</v>
       </c>
-      <c r="O14" s="84"/>
-      <c r="P14" s="84"/>
-      <c r="Q14" s="84" t="s">
+      <c r="O14" s="85"/>
+      <c r="P14" s="85"/>
+      <c r="Q14" s="85" t="s">
         <v>191</v>
       </c>
-      <c r="R14" s="84" t="s">
+      <c r="R14" s="85" t="s">
         <v>192</v>
       </c>
-      <c r="S14" s="84" t="s">
+      <c r="S14" s="85" t="s">
         <v>193</v>
       </c>
-      <c r="T14" s="84" t="s">
+      <c r="T14" s="85" t="s">
         <v>194</v>
       </c>
-      <c r="U14" s="84" t="s">
+      <c r="U14" s="85" t="s">
         <v>195</v>
       </c>
-      <c r="V14" s="84"/>
-      <c r="W14" s="84" t="s">
+      <c r="V14" s="85"/>
+      <c r="W14" s="85" t="s">
         <v>193</v>
       </c>
-      <c r="X14" s="84" t="s">
+      <c r="X14" s="85" t="s">
         <v>196</v>
       </c>
-      <c r="Y14" s="84" t="s">
+      <c r="Y14" s="85" t="s">
         <v>197</v>
       </c>
-      <c r="Z14" s="84" t="s">
+      <c r="Z14" s="85" t="s">
         <v>198</v>
       </c>
-      <c r="AA14" s="84" t="s">
+      <c r="AA14" s="85" t="s">
         <v>199</v>
       </c>
-      <c r="AB14" s="84" t="s">
+      <c r="AB14" s="85" t="s">
         <v>200</v>
       </c>
-      <c r="AC14" s="84" t="s">
+      <c r="AC14" s="85" t="s">
         <v>201</v>
       </c>
-      <c r="AD14" s="84" t="s">
+      <c r="AD14" s="85" t="s">
         <v>202</v>
       </c>
-      <c r="AE14" s="84" t="s">
+      <c r="AE14" s="85" t="s">
         <v>203</v>
       </c>
-      <c r="AF14" s="84" t="s">
+      <c r="AF14" s="85" t="s">
         <v>204</v>
       </c>
-      <c r="AG14" s="84"/>
-      <c r="AH14" s="84" t="s">
+      <c r="AG14" s="85"/>
+      <c r="AH14" s="85" t="s">
         <v>205</v>
       </c>
-      <c r="AI14" s="84" t="s">
+      <c r="AI14" s="85" t="s">
         <v>206</v>
       </c>
-      <c r="AJ14" s="84" t="s">
+      <c r="AJ14" s="85" t="s">
         <v>207</v>
       </c>
-      <c r="AK14" s="84"/>
-      <c r="AL14" s="84"/>
-      <c r="AM14" s="84" t="s">
+      <c r="AK14" s="85"/>
+      <c r="AL14" s="85"/>
+      <c r="AM14" s="85" t="s">
         <v>208</v>
       </c>
-      <c r="AN14" s="84" t="s">
+      <c r="AN14" s="85" t="s">
         <v>209</v>
       </c>
-      <c r="AO14" s="84" t="s">
+      <c r="AO14" s="85" t="s">
         <v>210</v>
       </c>
-      <c r="AP14" s="84" t="s">
+      <c r="AP14" s="85" t="s">
         <v>211</v>
       </c>
-      <c r="AQ14" s="84"/>
-      <c r="AR14" s="84" t="s">
+      <c r="AQ14" s="85"/>
+      <c r="AR14" s="85" t="s">
         <v>212</v>
       </c>
-      <c r="AS14" s="85" t="s">
+      <c r="AS14" s="86" t="s">
         <v>213</v>
       </c>
-      <c r="AT14" s="84" t="s">
+      <c r="AT14" s="85" t="s">
         <v>214</v>
       </c>
-      <c r="AU14" s="84" t="s">
+      <c r="AU14" s="85" t="s">
         <v>215</v>
       </c>
-      <c r="AV14" s="76"/>
-      <c r="AW14" s="76"/>
-      <c r="AX14" s="75" t="s">
+      <c r="AV14" s="77"/>
+      <c r="AW14" s="77"/>
+      <c r="AX14" s="76" t="s">
         <v>216</v>
       </c>
-      <c r="AY14" s="75"/>
+      <c r="AY14" s="76"/>
     </row>
     <row r="15" spans="1:51">
-      <c r="A15" s="86"/>
-      <c r="B15" s="87" t="s">
+      <c r="A15" s="87"/>
+      <c r="B15" s="88" t="s">
         <v>217</v>
       </c>
-      <c r="C15" s="88"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="80"/>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="80"/>
-      <c r="L15" s="80"/>
-      <c r="M15" s="80"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="80"/>
-      <c r="Q15" s="80"/>
-      <c r="R15" s="80"/>
-      <c r="S15" s="80"/>
-      <c r="T15" s="80"/>
-      <c r="U15" s="80"/>
-      <c r="V15" s="80"/>
-      <c r="W15" s="80"/>
-      <c r="X15" s="80"/>
-      <c r="Y15" s="80"/>
-      <c r="Z15" s="80"/>
-      <c r="AA15" s="80"/>
-      <c r="AB15" s="80"/>
-      <c r="AC15" s="80"/>
-      <c r="AD15" s="80"/>
-      <c r="AE15" s="80"/>
-      <c r="AF15" s="80"/>
-      <c r="AG15" s="80"/>
-      <c r="AH15" s="80"/>
-      <c r="AI15" s="80"/>
-      <c r="AJ15" s="80"/>
-      <c r="AK15" s="80"/>
-      <c r="AL15" s="80"/>
-      <c r="AM15" s="80"/>
-      <c r="AN15" s="80"/>
-      <c r="AO15" s="80"/>
-      <c r="AP15" s="80"/>
-      <c r="AQ15" s="80"/>
-      <c r="AR15" s="80"/>
-      <c r="AS15" s="80"/>
-      <c r="AT15" s="80"/>
-      <c r="AU15" s="80"/>
-      <c r="AV15" s="80"/>
-      <c r="AW15" s="80"/>
-      <c r="AX15" s="80"/>
-      <c r="AY15" s="80"/>
+      <c r="C15" s="89"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="81"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="81"/>
+      <c r="N15" s="81"/>
+      <c r="O15" s="81"/>
+      <c r="P15" s="81"/>
+      <c r="Q15" s="81"/>
+      <c r="R15" s="81"/>
+      <c r="S15" s="81"/>
+      <c r="T15" s="81"/>
+      <c r="U15" s="81"/>
+      <c r="V15" s="81"/>
+      <c r="W15" s="81"/>
+      <c r="X15" s="81"/>
+      <c r="Y15" s="81"/>
+      <c r="Z15" s="81"/>
+      <c r="AA15" s="81"/>
+      <c r="AB15" s="81"/>
+      <c r="AC15" s="81"/>
+      <c r="AD15" s="81"/>
+      <c r="AE15" s="81"/>
+      <c r="AF15" s="81"/>
+      <c r="AG15" s="81"/>
+      <c r="AH15" s="81"/>
+      <c r="AI15" s="81"/>
+      <c r="AJ15" s="81"/>
+      <c r="AK15" s="81"/>
+      <c r="AL15" s="81"/>
+      <c r="AM15" s="81"/>
+      <c r="AN15" s="81"/>
+      <c r="AO15" s="81"/>
+      <c r="AP15" s="81"/>
+      <c r="AQ15" s="81"/>
+      <c r="AR15" s="81"/>
+      <c r="AS15" s="81"/>
+      <c r="AT15" s="81"/>
+      <c r="AU15" s="81"/>
+      <c r="AV15" s="81"/>
+      <c r="AW15" s="81"/>
+      <c r="AX15" s="81"/>
+      <c r="AY15" s="81"/>
     </row>
     <row r="16" ht="67.5" spans="1:51">
-      <c r="A16" s="86"/>
-      <c r="B16" s="87" t="s">
+      <c r="A16" s="87"/>
+      <c r="B16" s="88" t="s">
         <v>218</v>
       </c>
-      <c r="C16" s="89" t="s">
+      <c r="C16" s="90" t="s">
         <v>219</v>
       </c>
-      <c r="D16" s="90" t="s">
+      <c r="D16" s="91" t="s">
         <v>220</v>
       </c>
-      <c r="E16" s="80"/>
-      <c r="F16" s="80"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="80"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="80"/>
-      <c r="K16" s="90" t="s">
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="91" t="s">
         <v>221</v>
       </c>
-      <c r="L16" s="80"/>
-      <c r="M16" s="80"/>
-      <c r="N16" s="80"/>
-      <c r="O16" s="80"/>
-      <c r="P16" s="80"/>
-      <c r="Q16" s="80"/>
-      <c r="R16" s="80"/>
-      <c r="S16" s="80"/>
-      <c r="T16" s="80"/>
-      <c r="U16" s="80"/>
-      <c r="V16" s="80"/>
-      <c r="W16" s="80"/>
-      <c r="X16" s="80"/>
-      <c r="Y16" s="80"/>
-      <c r="Z16" s="90" t="s">
+      <c r="L16" s="81"/>
+      <c r="M16" s="81"/>
+      <c r="N16" s="81"/>
+      <c r="O16" s="81"/>
+      <c r="P16" s="81"/>
+      <c r="Q16" s="81"/>
+      <c r="R16" s="81"/>
+      <c r="S16" s="81"/>
+      <c r="T16" s="81"/>
+      <c r="U16" s="81"/>
+      <c r="V16" s="81"/>
+      <c r="W16" s="81"/>
+      <c r="X16" s="81"/>
+      <c r="Y16" s="81"/>
+      <c r="Z16" s="91" t="s">
         <v>222</v>
       </c>
-      <c r="AA16" s="80" t="s">
+      <c r="AA16" s="81" t="s">
         <v>223</v>
       </c>
-      <c r="AB16" s="90" t="s">
+      <c r="AB16" s="91" t="s">
         <v>224</v>
       </c>
-      <c r="AC16" s="80"/>
-      <c r="AD16" s="80"/>
-      <c r="AE16" s="80"/>
-      <c r="AF16" s="80"/>
-      <c r="AG16" s="80"/>
-      <c r="AH16" s="80"/>
-      <c r="AI16" s="80"/>
-      <c r="AJ16" s="80"/>
-      <c r="AK16" s="80"/>
-      <c r="AL16" s="80"/>
-      <c r="AM16" s="90" t="s">
+      <c r="AC16" s="81"/>
+      <c r="AD16" s="81"/>
+      <c r="AE16" s="81"/>
+      <c r="AF16" s="81"/>
+      <c r="AG16" s="81"/>
+      <c r="AH16" s="81"/>
+      <c r="AI16" s="81"/>
+      <c r="AJ16" s="81"/>
+      <c r="AK16" s="81"/>
+      <c r="AL16" s="81"/>
+      <c r="AM16" s="91" t="s">
         <v>225</v>
       </c>
-      <c r="AN16" s="80"/>
-      <c r="AO16" s="80" t="s">
+      <c r="AN16" s="81"/>
+      <c r="AO16" s="81" t="s">
         <v>226</v>
       </c>
-      <c r="AP16" s="80" t="s">
+      <c r="AP16" s="81" t="s">
         <v>226</v>
       </c>
-      <c r="AQ16" s="80"/>
-      <c r="AR16" s="80"/>
-      <c r="AS16" s="80" t="s">
+      <c r="AQ16" s="81"/>
+      <c r="AR16" s="81"/>
+      <c r="AS16" s="81" t="s">
         <v>227</v>
       </c>
-      <c r="AT16" s="80"/>
-      <c r="AU16" s="80"/>
-      <c r="AV16" s="90" t="s">
+      <c r="AT16" s="81"/>
+      <c r="AU16" s="81"/>
+      <c r="AV16" s="91" t="s">
         <v>228</v>
       </c>
-      <c r="AW16" s="80"/>
-      <c r="AX16" s="80"/>
-      <c r="AY16" s="80"/>
+      <c r="AW16" s="81"/>
+      <c r="AX16" s="81"/>
+      <c r="AY16" s="81"/>
     </row>
     <row r="17" ht="81" spans="1:51">
-      <c r="A17" s="86"/>
-      <c r="B17" s="87" t="s">
+      <c r="A17" s="87"/>
+      <c r="B17" s="88" t="s">
         <v>229</v>
       </c>
-      <c r="C17" s="88"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="80"/>
-      <c r="F17" s="80"/>
-      <c r="G17" s="90" t="s">
+      <c r="C17" s="89"/>
+      <c r="D17" s="81"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="91" t="s">
         <v>230</v>
       </c>
-      <c r="H17" s="80"/>
-      <c r="I17" s="90" t="s">
+      <c r="H17" s="81"/>
+      <c r="I17" s="91" t="s">
         <v>231</v>
       </c>
-      <c r="J17" s="80"/>
-      <c r="K17" s="80" t="s">
+      <c r="J17" s="81"/>
+      <c r="K17" s="81" t="s">
         <v>232</v>
       </c>
-      <c r="L17" s="80" t="s">
+      <c r="L17" s="81" t="s">
         <v>233</v>
       </c>
-      <c r="M17" s="80"/>
-      <c r="N17" s="80"/>
-      <c r="O17" s="90" t="s">
+      <c r="M17" s="81"/>
+      <c r="N17" s="81"/>
+      <c r="O17" s="91" t="s">
         <v>234</v>
       </c>
-      <c r="P17" s="80"/>
-      <c r="Q17" s="80"/>
-      <c r="R17" s="80"/>
-      <c r="S17" s="90" t="s">
+      <c r="P17" s="81"/>
+      <c r="Q17" s="81"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="91" t="s">
         <v>235</v>
       </c>
-      <c r="T17" s="90" t="s">
+      <c r="T17" s="91" t="s">
         <v>236</v>
       </c>
-      <c r="U17" s="90" t="s">
+      <c r="U17" s="91" t="s">
         <v>237</v>
       </c>
-      <c r="V17" s="80"/>
-      <c r="W17" s="90" t="s">
+      <c r="V17" s="81"/>
+      <c r="W17" s="91" t="s">
         <v>238</v>
       </c>
-      <c r="X17" s="80" t="s">
+      <c r="X17" s="81" t="s">
         <v>239</v>
       </c>
-      <c r="Y17" s="90" t="s">
+      <c r="Y17" s="91" t="s">
         <v>240</v>
       </c>
-      <c r="Z17" s="90" t="s">
+      <c r="Z17" s="91" t="s">
         <v>241</v>
       </c>
-      <c r="AA17" s="90" t="s">
+      <c r="AA17" s="91" t="s">
         <v>242</v>
       </c>
-      <c r="AB17" s="90" t="s">
+      <c r="AB17" s="91" t="s">
         <v>243</v>
       </c>
-      <c r="AC17" s="80"/>
-      <c r="AD17" s="80"/>
-      <c r="AE17" s="80"/>
-      <c r="AF17" s="80"/>
-      <c r="AG17" s="80"/>
-      <c r="AH17" s="90" t="s">
+      <c r="AC17" s="81"/>
+      <c r="AD17" s="81"/>
+      <c r="AE17" s="81"/>
+      <c r="AF17" s="81"/>
+      <c r="AG17" s="81"/>
+      <c r="AH17" s="91" t="s">
         <v>244</v>
       </c>
-      <c r="AI17" s="80"/>
-      <c r="AJ17" s="80"/>
-      <c r="AK17" s="80"/>
-      <c r="AL17" s="80" t="s">
+      <c r="AI17" s="81"/>
+      <c r="AJ17" s="81"/>
+      <c r="AK17" s="81"/>
+      <c r="AL17" s="81" t="s">
         <v>245</v>
       </c>
-      <c r="AM17" s="90" t="s">
+      <c r="AM17" s="91" t="s">
         <v>246</v>
       </c>
-      <c r="AN17" s="90" t="s">
+      <c r="AN17" s="91" t="s">
         <v>247</v>
       </c>
-      <c r="AO17" s="90" t="s">
+      <c r="AO17" s="91" t="s">
         <v>248</v>
       </c>
-      <c r="AP17" s="90" t="s">
+      <c r="AP17" s="91" t="s">
         <v>249</v>
       </c>
-      <c r="AQ17" s="80"/>
-      <c r="AR17" s="90" t="s">
+      <c r="AQ17" s="81"/>
+      <c r="AR17" s="91" t="s">
         <v>250</v>
       </c>
-      <c r="AS17" s="80" t="s">
+      <c r="AS17" s="81" t="s">
         <v>251</v>
       </c>
-      <c r="AT17" s="80" t="s">
+      <c r="AT17" s="81" t="s">
         <v>252</v>
       </c>
-      <c r="AU17" s="90" t="s">
+      <c r="AU17" s="91" t="s">
         <v>253</v>
       </c>
-      <c r="AV17" s="90" t="s">
+      <c r="AV17" s="91" t="s">
         <v>254</v>
       </c>
-      <c r="AW17" s="90" t="s">
+      <c r="AW17" s="91" t="s">
         <v>255</v>
       </c>
-      <c r="AX17" s="80"/>
-      <c r="AY17" s="90" t="s">
+      <c r="AX17" s="81"/>
+      <c r="AY17" s="91" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="18" ht="81" spans="1:51">
-      <c r="A18" s="86"/>
-      <c r="B18" s="87" t="s">
+      <c r="A18" s="87"/>
+      <c r="B18" s="88" t="s">
         <v>257</v>
       </c>
-      <c r="C18" s="88"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="80"/>
-      <c r="F18" s="80"/>
-      <c r="G18" s="80"/>
-      <c r="H18" s="80"/>
-      <c r="I18" s="80"/>
-      <c r="J18" s="80"/>
-      <c r="K18" s="90" t="s">
+      <c r="C18" s="89"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="91" t="s">
         <v>258</v>
       </c>
-      <c r="L18" s="80"/>
-      <c r="M18" s="80"/>
-      <c r="N18" s="80"/>
-      <c r="O18" s="80"/>
-      <c r="P18" s="80"/>
-      <c r="Q18" s="80"/>
-      <c r="R18" s="80"/>
-      <c r="S18" s="80"/>
-      <c r="T18" s="80"/>
-      <c r="U18" s="80"/>
-      <c r="V18" s="80"/>
-      <c r="W18" s="80"/>
-      <c r="X18" s="80"/>
-      <c r="Y18" s="80"/>
-      <c r="Z18" s="90" t="s">
+      <c r="L18" s="81"/>
+      <c r="M18" s="81"/>
+      <c r="N18" s="81"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="81"/>
+      <c r="R18" s="81"/>
+      <c r="S18" s="81"/>
+      <c r="T18" s="81"/>
+      <c r="U18" s="81"/>
+      <c r="V18" s="81"/>
+      <c r="W18" s="81"/>
+      <c r="X18" s="81"/>
+      <c r="Y18" s="81"/>
+      <c r="Z18" s="91" t="s">
         <v>259</v>
       </c>
-      <c r="AA18" s="90" t="s">
+      <c r="AA18" s="91" t="s">
         <v>260</v>
       </c>
-      <c r="AB18" s="90" t="s">
+      <c r="AB18" s="91" t="s">
         <v>261</v>
       </c>
-      <c r="AC18" s="90" t="s">
+      <c r="AC18" s="91" t="s">
         <v>262</v>
       </c>
-      <c r="AD18" s="80"/>
-      <c r="AE18" s="80"/>
-      <c r="AF18" s="80"/>
-      <c r="AG18" s="80"/>
-      <c r="AH18" s="80"/>
-      <c r="AI18" s="80" t="s">
+      <c r="AD18" s="81"/>
+      <c r="AE18" s="81"/>
+      <c r="AF18" s="81"/>
+      <c r="AG18" s="81"/>
+      <c r="AH18" s="81"/>
+      <c r="AI18" s="81" t="s">
         <v>263</v>
       </c>
-      <c r="AJ18" s="80"/>
-      <c r="AK18" s="80" t="s">
+      <c r="AJ18" s="81"/>
+      <c r="AK18" s="81" t="s">
         <v>263</v>
       </c>
-      <c r="AL18" s="80"/>
-      <c r="AM18" s="80"/>
-      <c r="AN18" s="90" t="s">
+      <c r="AL18" s="81"/>
+      <c r="AM18" s="81"/>
+      <c r="AN18" s="91" t="s">
         <v>264</v>
       </c>
-      <c r="AO18" s="80"/>
-      <c r="AP18" s="80"/>
-      <c r="AQ18" s="80"/>
-      <c r="AR18" s="80"/>
-      <c r="AS18" s="80"/>
-      <c r="AT18" s="80"/>
-      <c r="AU18" s="80"/>
-      <c r="AV18" s="90" t="s">
+      <c r="AO18" s="81"/>
+      <c r="AP18" s="81"/>
+      <c r="AQ18" s="81"/>
+      <c r="AR18" s="81"/>
+      <c r="AS18" s="81"/>
+      <c r="AT18" s="81"/>
+      <c r="AU18" s="81"/>
+      <c r="AV18" s="91" t="s">
         <v>265</v>
       </c>
-      <c r="AW18" s="90" t="s">
+      <c r="AW18" s="91" t="s">
         <v>266</v>
       </c>
-      <c r="AX18" s="80"/>
-      <c r="AY18" s="90" t="s">
+      <c r="AX18" s="81"/>
+      <c r="AY18" s="91" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="19" ht="40.5" spans="1:51">
-      <c r="A19" s="86"/>
-      <c r="B19" s="87" t="s">
+      <c r="A19" s="87"/>
+      <c r="B19" s="88" t="s">
         <v>267</v>
       </c>
-      <c r="C19" s="88"/>
-      <c r="D19" s="80"/>
-      <c r="E19" s="80"/>
-      <c r="F19" s="80"/>
-      <c r="G19" s="80"/>
-      <c r="H19" s="90" t="s">
+      <c r="C19" s="89"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="91" t="s">
         <v>268</v>
       </c>
-      <c r="I19" s="80"/>
-      <c r="J19" s="80"/>
-      <c r="K19" s="90" t="s">
+      <c r="I19" s="81"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="91" t="s">
         <v>268</v>
       </c>
-      <c r="L19" s="80" t="s">
+      <c r="L19" s="81" t="s">
         <v>269</v>
       </c>
-      <c r="M19" s="80"/>
-      <c r="N19" s="80"/>
-      <c r="O19" s="80"/>
-      <c r="P19" s="80"/>
-      <c r="Q19" s="80"/>
-      <c r="R19" s="80"/>
-      <c r="S19" s="80"/>
-      <c r="T19" s="80"/>
-      <c r="U19" s="80"/>
-      <c r="V19" s="80"/>
-      <c r="W19" s="80"/>
-      <c r="X19" s="80"/>
-      <c r="Y19" s="80"/>
-      <c r="Z19" s="80"/>
-      <c r="AA19" s="80"/>
-      <c r="AB19" s="80"/>
-      <c r="AC19" s="80"/>
-      <c r="AD19" s="80"/>
-      <c r="AE19" s="80" t="s">
+      <c r="M19" s="81"/>
+      <c r="N19" s="81"/>
+      <c r="O19" s="81"/>
+      <c r="P19" s="81"/>
+      <c r="Q19" s="81"/>
+      <c r="R19" s="81"/>
+      <c r="S19" s="81"/>
+      <c r="T19" s="81"/>
+      <c r="U19" s="81"/>
+      <c r="V19" s="81"/>
+      <c r="W19" s="81"/>
+      <c r="X19" s="81"/>
+      <c r="Y19" s="81"/>
+      <c r="Z19" s="81"/>
+      <c r="AA19" s="81"/>
+      <c r="AB19" s="81"/>
+      <c r="AC19" s="81"/>
+      <c r="AD19" s="81"/>
+      <c r="AE19" s="81" t="s">
         <v>269</v>
       </c>
-      <c r="AF19" s="80"/>
-      <c r="AG19" s="80"/>
-      <c r="AH19" s="80"/>
-      <c r="AI19" s="80"/>
-      <c r="AJ19" s="80"/>
-      <c r="AK19" s="80"/>
-      <c r="AL19" s="80"/>
-      <c r="AM19" s="80"/>
-      <c r="AN19" s="80"/>
-      <c r="AO19" s="80"/>
-      <c r="AP19" s="80" t="s">
+      <c r="AF19" s="81"/>
+      <c r="AG19" s="81"/>
+      <c r="AH19" s="81"/>
+      <c r="AI19" s="81"/>
+      <c r="AJ19" s="81"/>
+      <c r="AK19" s="81"/>
+      <c r="AL19" s="81"/>
+      <c r="AM19" s="81"/>
+      <c r="AN19" s="81"/>
+      <c r="AO19" s="81"/>
+      <c r="AP19" s="81" t="s">
         <v>269</v>
       </c>
-      <c r="AQ19" s="80"/>
-      <c r="AR19" s="80"/>
-      <c r="AS19" s="80"/>
-      <c r="AT19" s="80"/>
-      <c r="AU19" s="80"/>
-      <c r="AV19" s="90"/>
-      <c r="AW19" s="90"/>
-      <c r="AX19" s="80"/>
-      <c r="AY19" s="90" t="s">
+      <c r="AQ19" s="81"/>
+      <c r="AR19" s="81"/>
+      <c r="AS19" s="81"/>
+      <c r="AT19" s="81"/>
+      <c r="AU19" s="81"/>
+      <c r="AV19" s="91"/>
+      <c r="AW19" s="91"/>
+      <c r="AX19" s="81"/>
+      <c r="AY19" s="91" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="20" ht="54" spans="1:51">
-      <c r="A20" s="86"/>
-      <c r="B20" s="87" t="s">
+      <c r="A20" s="87"/>
+      <c r="B20" s="88" t="s">
         <v>271</v>
       </c>
-      <c r="C20" s="88"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="80"/>
-      <c r="F20" s="80"/>
-      <c r="G20" s="80"/>
-      <c r="H20" s="80"/>
-      <c r="I20" s="80"/>
-      <c r="J20" s="80"/>
-      <c r="K20" s="80"/>
-      <c r="L20" s="80"/>
-      <c r="M20" s="80"/>
-      <c r="N20" s="80"/>
-      <c r="O20" s="80"/>
-      <c r="P20" s="80"/>
-      <c r="Q20" s="80"/>
-      <c r="R20" s="80"/>
-      <c r="S20" s="80"/>
-      <c r="T20" s="80"/>
-      <c r="U20" s="80"/>
-      <c r="V20" s="80"/>
-      <c r="W20" s="80"/>
-      <c r="X20" s="80"/>
-      <c r="Y20" s="80"/>
-      <c r="Z20" s="80"/>
-      <c r="AA20" s="80"/>
-      <c r="AB20" s="80"/>
-      <c r="AC20" s="80"/>
-      <c r="AD20" s="80"/>
-      <c r="AE20" s="80"/>
-      <c r="AF20" s="80"/>
-      <c r="AG20" s="80"/>
-      <c r="AH20" s="80"/>
-      <c r="AI20" s="80"/>
-      <c r="AJ20" s="90" t="s">
+      <c r="C20" s="89"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="81"/>
+      <c r="M20" s="81"/>
+      <c r="N20" s="81"/>
+      <c r="O20" s="81"/>
+      <c r="P20" s="81"/>
+      <c r="Q20" s="81"/>
+      <c r="R20" s="81"/>
+      <c r="S20" s="81"/>
+      <c r="T20" s="81"/>
+      <c r="U20" s="81"/>
+      <c r="V20" s="81"/>
+      <c r="W20" s="81"/>
+      <c r="X20" s="81"/>
+      <c r="Y20" s="81"/>
+      <c r="Z20" s="81"/>
+      <c r="AA20" s="81"/>
+      <c r="AB20" s="81"/>
+      <c r="AC20" s="81"/>
+      <c r="AD20" s="81"/>
+      <c r="AE20" s="81"/>
+      <c r="AF20" s="81"/>
+      <c r="AG20" s="81"/>
+      <c r="AH20" s="81"/>
+      <c r="AI20" s="81"/>
+      <c r="AJ20" s="91" t="s">
         <v>272</v>
       </c>
-      <c r="AK20" s="80"/>
-      <c r="AL20" s="80"/>
-      <c r="AM20" s="80"/>
-      <c r="AN20" s="80"/>
-      <c r="AO20" s="80"/>
-      <c r="AP20" s="80"/>
-      <c r="AQ20" s="80"/>
-      <c r="AR20" s="80"/>
-      <c r="AS20" s="80"/>
-      <c r="AT20" s="80"/>
-      <c r="AU20" s="80"/>
-      <c r="AV20" s="90"/>
-      <c r="AW20" s="90"/>
-      <c r="AX20" s="80"/>
-      <c r="AY20" s="80"/>
+      <c r="AK20" s="81"/>
+      <c r="AL20" s="81"/>
+      <c r="AM20" s="81"/>
+      <c r="AN20" s="81"/>
+      <c r="AO20" s="81"/>
+      <c r="AP20" s="81"/>
+      <c r="AQ20" s="81"/>
+      <c r="AR20" s="81"/>
+      <c r="AS20" s="81"/>
+      <c r="AT20" s="81"/>
+      <c r="AU20" s="81"/>
+      <c r="AV20" s="91"/>
+      <c r="AW20" s="91"/>
+      <c r="AX20" s="81"/>
+      <c r="AY20" s="81"/>
     </row>
     <row r="21" ht="81" spans="1:51">
-      <c r="A21" s="86"/>
-      <c r="B21" s="91" t="s">
+      <c r="A21" s="87"/>
+      <c r="B21" s="92" t="s">
         <v>273</v>
       </c>
-      <c r="C21" s="89" t="s">
+      <c r="C21" s="90" t="s">
         <v>274</v>
       </c>
-      <c r="D21" s="89" t="s">
+      <c r="D21" s="90" t="s">
         <v>274</v>
       </c>
-      <c r="E21" s="80"/>
-      <c r="F21" s="80"/>
-      <c r="G21" s="80"/>
-      <c r="H21" s="80"/>
-      <c r="I21" s="80"/>
-      <c r="J21" s="80"/>
-      <c r="K21" s="90" t="s">
+      <c r="E21" s="81"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="81"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="81"/>
+      <c r="K21" s="91" t="s">
         <v>275</v>
       </c>
-      <c r="L21" s="80" t="s">
+      <c r="L21" s="81" t="s">
         <v>276</v>
       </c>
-      <c r="M21" s="80"/>
-      <c r="N21" s="80"/>
-      <c r="O21" s="80"/>
-      <c r="P21" s="80"/>
-      <c r="Q21" s="80"/>
-      <c r="R21" s="80"/>
-      <c r="S21" s="80"/>
-      <c r="T21" s="80"/>
-      <c r="U21" s="80"/>
-      <c r="V21" s="80"/>
-      <c r="W21" s="80"/>
-      <c r="X21" s="80"/>
-      <c r="Y21" s="80"/>
-      <c r="Z21" s="80"/>
-      <c r="AA21" s="80"/>
-      <c r="AB21" s="80"/>
-      <c r="AC21" s="80"/>
-      <c r="AD21" s="80"/>
-      <c r="AE21" s="80" t="s">
+      <c r="M21" s="81"/>
+      <c r="N21" s="81"/>
+      <c r="O21" s="81"/>
+      <c r="P21" s="81"/>
+      <c r="Q21" s="81"/>
+      <c r="R21" s="81"/>
+      <c r="S21" s="81"/>
+      <c r="T21" s="81"/>
+      <c r="U21" s="81"/>
+      <c r="V21" s="81"/>
+      <c r="W21" s="81"/>
+      <c r="X21" s="81"/>
+      <c r="Y21" s="81"/>
+      <c r="Z21" s="81"/>
+      <c r="AA21" s="81"/>
+      <c r="AB21" s="81"/>
+      <c r="AC21" s="81"/>
+      <c r="AD21" s="81"/>
+      <c r="AE21" s="81" t="s">
         <v>277</v>
       </c>
-      <c r="AF21" s="90" t="s">
+      <c r="AF21" s="91" t="s">
         <v>278</v>
       </c>
-      <c r="AG21" s="90" t="s">
+      <c r="AG21" s="91" t="s">
         <v>279</v>
       </c>
-      <c r="AH21" s="80"/>
-      <c r="AI21" s="90" t="s">
+      <c r="AH21" s="81"/>
+      <c r="AI21" s="91" t="s">
         <v>280</v>
       </c>
-      <c r="AJ21" s="90" t="s">
+      <c r="AJ21" s="91" t="s">
         <v>281</v>
       </c>
-      <c r="AK21" s="80"/>
-      <c r="AL21" s="80"/>
-      <c r="AM21" s="80"/>
-      <c r="AN21" s="80"/>
-      <c r="AO21" s="80" t="s">
+      <c r="AK21" s="81"/>
+      <c r="AL21" s="81"/>
+      <c r="AM21" s="81"/>
+      <c r="AN21" s="81"/>
+      <c r="AO21" s="81" t="s">
         <v>276</v>
       </c>
-      <c r="AP21" s="80" t="s">
+      <c r="AP21" s="81" t="s">
         <v>276</v>
       </c>
-      <c r="AQ21" s="80"/>
-      <c r="AR21" s="80"/>
-      <c r="AS21" s="80"/>
-      <c r="AT21" s="80" t="s">
+      <c r="AQ21" s="81"/>
+      <c r="AR21" s="81"/>
+      <c r="AS21" s="81"/>
+      <c r="AT21" s="81" t="s">
         <v>277</v>
       </c>
-      <c r="AU21" s="80"/>
-      <c r="AV21" s="80"/>
-      <c r="AW21" s="80"/>
-      <c r="AX21" s="90" t="s">
+      <c r="AU21" s="81"/>
+      <c r="AV21" s="81"/>
+      <c r="AW21" s="81"/>
+      <c r="AX21" s="91" t="s">
         <v>282</v>
       </c>
-      <c r="AY21" s="90" t="s">
+      <c r="AY21" s="91" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="22" customFormat="1" spans="1:51">
-      <c r="A22" s="92"/>
-      <c r="B22" s="87" t="s">
+      <c r="A22" s="93"/>
+      <c r="B22" s="88" t="s">
         <v>284</v>
       </c>
-      <c r="C22" s="88"/>
-      <c r="D22" s="80"/>
-      <c r="E22" s="80"/>
-      <c r="F22" s="80"/>
-      <c r="G22" s="80"/>
-      <c r="H22" s="80"/>
-      <c r="I22" s="80"/>
-      <c r="J22" s="80"/>
-      <c r="K22" s="80"/>
-      <c r="L22" s="80"/>
-      <c r="M22" s="80"/>
-      <c r="N22" s="80"/>
-      <c r="O22" s="80"/>
-      <c r="P22" s="80"/>
-      <c r="Q22" s="80"/>
-      <c r="R22" s="80"/>
-      <c r="S22" s="80"/>
-      <c r="T22" s="80"/>
-      <c r="U22" s="80"/>
-      <c r="V22" s="80"/>
-      <c r="W22" s="80"/>
-      <c r="X22" s="80"/>
-      <c r="Y22" s="80"/>
-      <c r="Z22" s="80"/>
-      <c r="AA22" s="80"/>
-      <c r="AB22" s="80"/>
-      <c r="AC22" s="80"/>
-      <c r="AD22" s="80"/>
-      <c r="AE22" s="80"/>
-      <c r="AF22" s="80"/>
-      <c r="AG22" s="80"/>
-      <c r="AH22" s="80"/>
-      <c r="AI22" s="80"/>
-      <c r="AJ22" s="80"/>
-      <c r="AK22" s="80"/>
-      <c r="AL22" s="80"/>
-      <c r="AM22" s="80"/>
-      <c r="AN22" s="80"/>
-      <c r="AO22" s="80"/>
-      <c r="AP22" s="80"/>
-      <c r="AQ22" s="80"/>
-      <c r="AR22" s="80"/>
-      <c r="AS22" s="80"/>
-      <c r="AT22" s="80"/>
-      <c r="AU22" s="80"/>
-      <c r="AV22" s="90"/>
-      <c r="AW22" s="90"/>
-      <c r="AX22" s="80"/>
-      <c r="AY22" s="80"/>
+      <c r="C22" s="89"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="81"/>
+      <c r="K22" s="81"/>
+      <c r="L22" s="81"/>
+      <c r="M22" s="81"/>
+      <c r="N22" s="81"/>
+      <c r="O22" s="81"/>
+      <c r="P22" s="81"/>
+      <c r="Q22" s="81"/>
+      <c r="R22" s="81"/>
+      <c r="S22" s="81"/>
+      <c r="T22" s="81"/>
+      <c r="U22" s="81"/>
+      <c r="V22" s="81"/>
+      <c r="W22" s="81"/>
+      <c r="X22" s="81"/>
+      <c r="Y22" s="81"/>
+      <c r="Z22" s="81"/>
+      <c r="AA22" s="81"/>
+      <c r="AB22" s="81"/>
+      <c r="AC22" s="81"/>
+      <c r="AD22" s="81"/>
+      <c r="AE22" s="81"/>
+      <c r="AF22" s="81"/>
+      <c r="AG22" s="81"/>
+      <c r="AH22" s="81"/>
+      <c r="AI22" s="81"/>
+      <c r="AJ22" s="81"/>
+      <c r="AK22" s="81"/>
+      <c r="AL22" s="81"/>
+      <c r="AM22" s="81"/>
+      <c r="AN22" s="81"/>
+      <c r="AO22" s="81"/>
+      <c r="AP22" s="81"/>
+      <c r="AQ22" s="81"/>
+      <c r="AR22" s="81"/>
+      <c r="AS22" s="81"/>
+      <c r="AT22" s="81"/>
+      <c r="AU22" s="81"/>
+      <c r="AV22" s="91"/>
+      <c r="AW22" s="91"/>
+      <c r="AX22" s="81"/>
+      <c r="AY22" s="81"/>
     </row>
     <row r="24" ht="108" spans="1:51">
-      <c r="A24" s="70" t="s">
+      <c r="A24" s="71" t="s">
         <v>285</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="C24" s="75" t="s">
+      <c r="C24" s="76" t="s">
         <v>287</v>
       </c>
-      <c r="D24" s="75" t="s">
+      <c r="D24" s="76" t="s">
         <v>170</v>
       </c>
-      <c r="E24" s="75" t="s">
+      <c r="E24" s="76" t="s">
         <v>288</v>
       </c>
-      <c r="F24" s="75" t="s">
+      <c r="F24" s="76" t="s">
         <v>289</v>
       </c>
-      <c r="G24" s="75" t="s">
+      <c r="G24" s="76" t="s">
         <v>290</v>
       </c>
-      <c r="H24" s="75" t="s">
+      <c r="H24" s="76" t="s">
         <v>291</v>
       </c>
-      <c r="I24" s="75" t="s">
+      <c r="I24" s="76" t="s">
         <v>292</v>
       </c>
-      <c r="J24" s="75" t="s">
+      <c r="J24" s="76" t="s">
         <v>293</v>
       </c>
-      <c r="K24" s="75" t="s">
+      <c r="K24" s="76" t="s">
         <v>294</v>
       </c>
-      <c r="L24" s="75" t="s">
+      <c r="L24" s="76" t="s">
         <v>295</v>
       </c>
-      <c r="M24" s="75" t="s">
+      <c r="M24" s="76" t="s">
         <v>296</v>
       </c>
-      <c r="N24" s="75" t="s">
+      <c r="N24" s="76" t="s">
         <v>297</v>
       </c>
-      <c r="O24" s="75" t="s">
+      <c r="O24" s="76" t="s">
         <v>155</v>
       </c>
-      <c r="P24" s="75" t="s">
+      <c r="P24" s="76" t="s">
         <v>298</v>
       </c>
-      <c r="Q24" s="75" t="s">
+      <c r="Q24" s="76" t="s">
         <v>299</v>
       </c>
-      <c r="R24" s="75" t="s">
+      <c r="R24" s="76" t="s">
         <v>300</v>
       </c>
-      <c r="S24" s="75" t="s">
+      <c r="S24" s="76" t="s">
         <v>301</v>
       </c>
-      <c r="T24" s="75" t="s">
+      <c r="T24" s="76" t="s">
         <v>302</v>
       </c>
-      <c r="U24" s="75" t="s">
+      <c r="U24" s="76" t="s">
         <v>303</v>
       </c>
-      <c r="V24" s="75" t="s">
+      <c r="V24" s="76" t="s">
         <v>304</v>
       </c>
-      <c r="W24" s="75" t="s">
+      <c r="W24" s="76" t="s">
         <v>305</v>
       </c>
-      <c r="X24" s="75" t="s">
+      <c r="X24" s="76" t="s">
         <v>306</v>
       </c>
-      <c r="Y24" s="75" t="s">
+      <c r="Y24" s="76" t="s">
         <v>307</v>
       </c>
-      <c r="Z24" s="75" t="s">
+      <c r="Z24" s="76" t="s">
         <v>308</v>
       </c>
-      <c r="AA24" s="75" t="s">
+      <c r="AA24" s="76" t="s">
         <v>309</v>
       </c>
-      <c r="AB24" s="75" t="s">
+      <c r="AB24" s="76" t="s">
         <v>310</v>
       </c>
-      <c r="AC24" s="75" t="s">
+      <c r="AC24" s="76" t="s">
         <v>311</v>
       </c>
-      <c r="AD24" s="75" t="s">
+      <c r="AD24" s="76" t="s">
         <v>312</v>
       </c>
-      <c r="AE24" s="75" t="s">
+      <c r="AE24" s="76" t="s">
         <v>313</v>
       </c>
-      <c r="AF24" s="75" t="s">
+      <c r="AF24" s="76" t="s">
         <v>314</v>
       </c>
-      <c r="AG24" s="75" t="s">
+      <c r="AG24" s="76" t="s">
         <v>315</v>
       </c>
-      <c r="AH24" s="75" t="s">
+      <c r="AH24" s="76" t="s">
         <v>155</v>
       </c>
-      <c r="AI24" s="75" t="s">
+      <c r="AI24" s="76" t="s">
         <v>316</v>
       </c>
-      <c r="AJ24" s="75" t="s">
+      <c r="AJ24" s="76" t="s">
         <v>317</v>
       </c>
-      <c r="AK24" s="75" t="s">
+      <c r="AK24" s="76" t="s">
         <v>155</v>
       </c>
-      <c r="AL24" s="75" t="s">
+      <c r="AL24" s="76" t="s">
         <v>318</v>
       </c>
-      <c r="AM24" s="75" t="s">
+      <c r="AM24" s="76" t="s">
         <v>319</v>
       </c>
-      <c r="AN24" s="75" t="s">
+      <c r="AN24" s="76" t="s">
         <v>155</v>
       </c>
-      <c r="AO24" s="75" t="s">
+      <c r="AO24" s="76" t="s">
         <v>155</v>
       </c>
-      <c r="AP24" s="75" t="s">
+      <c r="AP24" s="76" t="s">
         <v>315</v>
       </c>
-      <c r="AQ24" s="75" t="s">
+      <c r="AQ24" s="76" t="s">
         <v>315</v>
       </c>
-      <c r="AR24" s="75" t="s">
+      <c r="AR24" s="76" t="s">
         <v>155</v>
       </c>
-      <c r="AS24" s="75" t="s">
+      <c r="AS24" s="76" t="s">
         <v>320</v>
       </c>
-      <c r="AT24" s="75" t="s">
+      <c r="AT24" s="76" t="s">
         <v>321</v>
       </c>
-      <c r="AU24" s="75" t="s">
+      <c r="AU24" s="76" t="s">
         <v>322</v>
       </c>
-      <c r="AV24" s="75" t="s">
+      <c r="AV24" s="76" t="s">
         <v>323</v>
       </c>
-      <c r="AW24" s="76" t="s">
+      <c r="AW24" s="77" t="s">
         <v>324</v>
       </c>
-      <c r="AX24" s="76" t="s">
+      <c r="AX24" s="77" t="s">
         <v>315</v>
       </c>
-      <c r="AY24" s="76" t="s">
+      <c r="AY24" s="77" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="25" customFormat="1" spans="1:51">
-      <c r="A25" s="72"/>
-      <c r="B25" s="26" t="s">
+      <c r="A25" s="73"/>
+      <c r="B25" s="27" t="s">
         <v>325</v>
       </c>
-      <c r="C25" s="75"/>
-      <c r="D25" s="75"/>
-      <c r="E25" s="75"/>
-      <c r="F25" s="75"/>
-      <c r="G25" s="75"/>
-      <c r="H25" s="75"/>
-      <c r="I25" s="75"/>
-      <c r="J25" s="75"/>
-      <c r="K25" s="75"/>
-      <c r="L25" s="75"/>
-      <c r="M25" s="75"/>
-      <c r="N25" s="75"/>
-      <c r="O25" s="75"/>
-      <c r="P25" s="75"/>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="75"/>
-      <c r="S25" s="75"/>
-      <c r="T25" s="75"/>
-      <c r="U25" s="75"/>
-      <c r="V25" s="75"/>
-      <c r="W25" s="75"/>
-      <c r="X25" s="75"/>
-      <c r="Y25" s="75"/>
-      <c r="Z25" s="75"/>
-      <c r="AA25" s="75"/>
-      <c r="AB25" s="75"/>
-      <c r="AC25" s="75"/>
-      <c r="AD25" s="75"/>
-      <c r="AE25" s="75"/>
-      <c r="AF25" s="75"/>
-      <c r="AG25" s="75"/>
-      <c r="AH25" s="75"/>
-      <c r="AI25" s="75"/>
-      <c r="AJ25" s="75"/>
-      <c r="AK25" s="75"/>
-      <c r="AL25" s="75"/>
-      <c r="AM25" s="75"/>
-      <c r="AN25" s="75"/>
-      <c r="AO25" s="75"/>
-      <c r="AP25" s="75"/>
-      <c r="AQ25" s="75"/>
-      <c r="AR25" s="75"/>
-      <c r="AS25" s="75"/>
-      <c r="AT25" s="75"/>
-      <c r="AU25" s="75"/>
-      <c r="AV25" s="75"/>
-      <c r="AW25" s="76"/>
-      <c r="AX25" s="76"/>
-      <c r="AY25" s="76"/>
+      <c r="C25" s="76"/>
+      <c r="D25" s="76"/>
+      <c r="E25" s="76"/>
+      <c r="F25" s="76"/>
+      <c r="G25" s="76"/>
+      <c r="H25" s="76"/>
+      <c r="I25" s="76"/>
+      <c r="J25" s="76"/>
+      <c r="K25" s="76"/>
+      <c r="L25" s="76"/>
+      <c r="M25" s="76"/>
+      <c r="N25" s="76"/>
+      <c r="O25" s="76"/>
+      <c r="P25" s="76"/>
+      <c r="Q25" s="76"/>
+      <c r="R25" s="76"/>
+      <c r="S25" s="76"/>
+      <c r="T25" s="76"/>
+      <c r="U25" s="76"/>
+      <c r="V25" s="76"/>
+      <c r="W25" s="76"/>
+      <c r="X25" s="76"/>
+      <c r="Y25" s="76"/>
+      <c r="Z25" s="76"/>
+      <c r="AA25" s="76"/>
+      <c r="AB25" s="76"/>
+      <c r="AC25" s="76"/>
+      <c r="AD25" s="76"/>
+      <c r="AE25" s="76"/>
+      <c r="AF25" s="76"/>
+      <c r="AG25" s="76"/>
+      <c r="AH25" s="76"/>
+      <c r="AI25" s="76"/>
+      <c r="AJ25" s="76"/>
+      <c r="AK25" s="76"/>
+      <c r="AL25" s="76"/>
+      <c r="AM25" s="76"/>
+      <c r="AN25" s="76"/>
+      <c r="AO25" s="76"/>
+      <c r="AP25" s="76"/>
+      <c r="AQ25" s="76"/>
+      <c r="AR25" s="76"/>
+      <c r="AS25" s="76"/>
+      <c r="AT25" s="76"/>
+      <c r="AU25" s="76"/>
+      <c r="AV25" s="76"/>
+      <c r="AW25" s="77"/>
+      <c r="AX25" s="77"/>
+      <c r="AY25" s="77"/>
     </row>
     <row r="26" customFormat="1" ht="94.5" spans="1:51">
-      <c r="A26" s="77"/>
-      <c r="B26" s="26" t="s">
+      <c r="A26" s="78"/>
+      <c r="B26" s="27" t="s">
         <v>326</v>
       </c>
-      <c r="C26" s="75"/>
-      <c r="D26" s="75"/>
-      <c r="E26" s="75"/>
-      <c r="F26" s="75"/>
-      <c r="G26" s="75" t="s">
+      <c r="C26" s="76"/>
+      <c r="D26" s="76"/>
+      <c r="E26" s="76"/>
+      <c r="F26" s="76"/>
+      <c r="G26" s="76" t="s">
         <v>327</v>
       </c>
-      <c r="H26" s="75"/>
-      <c r="I26" s="75"/>
-      <c r="J26" s="75"/>
-      <c r="K26" s="75"/>
-      <c r="L26" s="75"/>
-      <c r="M26" s="75" t="s">
+      <c r="H26" s="76"/>
+      <c r="I26" s="76"/>
+      <c r="J26" s="76"/>
+      <c r="K26" s="76"/>
+      <c r="L26" s="76"/>
+      <c r="M26" s="76" t="s">
         <v>328</v>
       </c>
-      <c r="N26" s="75" t="s">
+      <c r="N26" s="76" t="s">
         <v>329</v>
       </c>
-      <c r="O26" s="75"/>
-      <c r="P26" s="75"/>
-      <c r="Q26" s="75"/>
-      <c r="R26" s="75"/>
-      <c r="S26" s="75"/>
-      <c r="T26" s="75"/>
-      <c r="U26" s="75"/>
-      <c r="V26" s="75"/>
-      <c r="W26" s="75"/>
-      <c r="X26" s="75"/>
-      <c r="Y26" s="75"/>
-      <c r="Z26" s="75"/>
-      <c r="AA26" s="75"/>
-      <c r="AB26" s="75"/>
-      <c r="AC26" s="75"/>
-      <c r="AD26" s="75"/>
-      <c r="AE26" s="75"/>
-      <c r="AF26" s="75"/>
-      <c r="AG26" s="75"/>
-      <c r="AH26" s="75"/>
-      <c r="AI26" s="75"/>
-      <c r="AJ26" s="75"/>
-      <c r="AK26" s="75"/>
-      <c r="AL26" s="75"/>
-      <c r="AM26" s="75"/>
-      <c r="AN26" s="75"/>
-      <c r="AO26" s="75" t="s">
+      <c r="O26" s="76"/>
+      <c r="P26" s="76"/>
+      <c r="Q26" s="76"/>
+      <c r="R26" s="76"/>
+      <c r="S26" s="76"/>
+      <c r="T26" s="76"/>
+      <c r="U26" s="76"/>
+      <c r="V26" s="76"/>
+      <c r="W26" s="76"/>
+      <c r="X26" s="76"/>
+      <c r="Y26" s="76"/>
+      <c r="Z26" s="76"/>
+      <c r="AA26" s="76"/>
+      <c r="AB26" s="76"/>
+      <c r="AC26" s="76"/>
+      <c r="AD26" s="76"/>
+      <c r="AE26" s="76"/>
+      <c r="AF26" s="76"/>
+      <c r="AG26" s="76"/>
+      <c r="AH26" s="76"/>
+      <c r="AI26" s="76"/>
+      <c r="AJ26" s="76"/>
+      <c r="AK26" s="76"/>
+      <c r="AL26" s="76"/>
+      <c r="AM26" s="76"/>
+      <c r="AN26" s="76"/>
+      <c r="AO26" s="76" t="s">
         <v>330</v>
       </c>
-      <c r="AP26" s="75" t="s">
+      <c r="AP26" s="76" t="s">
         <v>331</v>
       </c>
-      <c r="AQ26" s="75"/>
-      <c r="AR26" s="75"/>
-      <c r="AS26" s="75"/>
-      <c r="AT26" s="75"/>
-      <c r="AU26" s="75"/>
-      <c r="AV26" s="75"/>
-      <c r="AW26" s="76"/>
-      <c r="AX26" s="76"/>
-      <c r="AY26" s="76"/>
+      <c r="AQ26" s="76"/>
+      <c r="AR26" s="76"/>
+      <c r="AS26" s="76"/>
+      <c r="AT26" s="76"/>
+      <c r="AU26" s="76"/>
+      <c r="AV26" s="76"/>
+      <c r="AW26" s="77"/>
+      <c r="AX26" s="77"/>
+      <c r="AY26" s="77"/>
     </row>
-    <row r="27" s="54" customFormat="1" ht="27" spans="1:51">
-      <c r="A27" s="78" t="s">
+    <row r="27" s="55" customFormat="1" ht="27" spans="1:51">
+      <c r="A27" s="79" t="s">
         <v>332</v>
       </c>
-      <c r="B27" s="90" t="s">
+      <c r="B27" s="91" t="s">
         <v>333</v>
       </c>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
-      <c r="H27" s="93"/>
-      <c r="I27" s="93"/>
-      <c r="J27" s="93"/>
-      <c r="K27" s="93"/>
-      <c r="L27" s="93"/>
-      <c r="M27" s="93"/>
-      <c r="N27" s="93"/>
-      <c r="O27" s="93"/>
-      <c r="P27" s="93"/>
-      <c r="Q27" s="93"/>
-      <c r="R27" s="93"/>
-      <c r="S27" s="93"/>
-      <c r="T27" s="93"/>
-      <c r="U27" s="93"/>
-      <c r="V27" s="93"/>
-      <c r="W27" s="93"/>
-      <c r="X27" s="93"/>
-      <c r="Y27" s="93"/>
-      <c r="Z27" s="93"/>
-      <c r="AA27" s="93"/>
-      <c r="AB27" s="93"/>
-      <c r="AC27" s="93"/>
-      <c r="AD27" s="93"/>
-      <c r="AE27" s="93"/>
-      <c r="AF27" s="93"/>
-      <c r="AG27" s="93"/>
-      <c r="AH27" s="93"/>
-      <c r="AI27" s="93"/>
-      <c r="AJ27" s="93"/>
-      <c r="AK27" s="93"/>
-      <c r="AL27" s="93"/>
-      <c r="AM27" s="93"/>
-      <c r="AN27" s="93"/>
-      <c r="AO27" s="93"/>
-      <c r="AP27" s="93"/>
-      <c r="AQ27" s="93"/>
-      <c r="AR27" s="93"/>
+      <c r="C27" s="94"/>
+      <c r="D27" s="94"/>
+      <c r="E27" s="94"/>
+      <c r="F27" s="94"/>
+      <c r="G27" s="94"/>
+      <c r="H27" s="94"/>
+      <c r="I27" s="94"/>
+      <c r="J27" s="94"/>
+      <c r="K27" s="94"/>
+      <c r="L27" s="94"/>
+      <c r="M27" s="94"/>
+      <c r="N27" s="94"/>
+      <c r="O27" s="94"/>
+      <c r="P27" s="94"/>
+      <c r="Q27" s="94"/>
+      <c r="R27" s="94"/>
+      <c r="S27" s="94"/>
+      <c r="T27" s="94"/>
+      <c r="U27" s="94"/>
+      <c r="V27" s="94"/>
+      <c r="W27" s="94"/>
+      <c r="X27" s="94"/>
+      <c r="Y27" s="94"/>
+      <c r="Z27" s="94"/>
+      <c r="AA27" s="94"/>
+      <c r="AB27" s="94"/>
+      <c r="AC27" s="94"/>
+      <c r="AD27" s="94"/>
+      <c r="AE27" s="94"/>
+      <c r="AF27" s="94"/>
+      <c r="AG27" s="94"/>
+      <c r="AH27" s="94"/>
+      <c r="AI27" s="94"/>
+      <c r="AJ27" s="94"/>
+      <c r="AK27" s="94"/>
+      <c r="AL27" s="94"/>
+      <c r="AM27" s="94"/>
+      <c r="AN27" s="94"/>
+      <c r="AO27" s="94"/>
+      <c r="AP27" s="94"/>
+      <c r="AQ27" s="94"/>
+      <c r="AR27" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="23">
@@ -8436,14 +8515,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:X52"/>
+  <dimension ref="A18:X70"/>
   <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
   <cols>
     <col min="2" max="2" width="13.1083333333333" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="14.8916666666667" customWidth="1"/>
+    <col min="6" max="6" width="12.4916666666667" customWidth="1"/>
+    <col min="7" max="7" width="11.9166666666667" customWidth="1"/>
     <col min="8" max="8" width="13.1083333333333" customWidth="1"/>
     <col min="9" max="9" width="13.225" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
@@ -8455,2153 +8535,2115 @@
     <col min="17" max="17" width="9.66666666666667" customWidth="1"/>
     <col min="19" max="19" width="11.4416666666667" customWidth="1"/>
     <col min="20" max="20" width="13.5583333333333" customWidth="1"/>
-    <col min="21" max="21" width="9.10833333333333" customWidth="1"/>
+    <col min="21" max="21" width="12.2083333333333" customWidth="1"/>
     <col min="23" max="23" width="12.8916666666667" customWidth="1"/>
     <col min="24" max="24" width="10.225" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
-      <c r="A1" s="15" t="s">
+    <row r="18" ht="14.25" spans="1:24">
+      <c r="A18" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+    </row>
+    <row r="19" spans="1:24">
+      <c r="A19" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="B19" s="17" t="s">
         <v>336</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="C19" s="18" t="s">
         <v>337</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="D19" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="E19" s="18" t="s">
         <v>339</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="F19" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="G19" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
-      <c r="L1" s="17" t="s">
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="M1" s="17"/>
-      <c r="N1" s="17"/>
-      <c r="O1" s="17"/>
-      <c r="P1" s="17"/>
-      <c r="Q1" s="17"/>
-      <c r="R1" s="17"/>
-      <c r="S1" s="17"/>
-      <c r="T1" s="17"/>
-      <c r="U1" s="17" t="s">
+      <c r="M19" s="18"/>
+      <c r="N19" s="18"/>
+      <c r="O19" s="18"/>
+      <c r="P19" s="18"/>
+      <c r="Q19" s="18"/>
+      <c r="R19" s="18"/>
+      <c r="S19" s="18"/>
+      <c r="T19" s="18"/>
+      <c r="U19" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="V1" s="17"/>
-      <c r="W1" s="17"/>
-      <c r="X1" s="18"/>
+      <c r="V19" s="18"/>
+      <c r="W19" s="18"/>
+      <c r="X19" s="19"/>
     </row>
-    <row r="2" spans="1:24">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>181</v>
-      </c>
-      <c r="I2" s="22" t="s">
-        <v>340</v>
-      </c>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="23" t="s">
+    <row r="20" spans="1:24">
+      <c r="A20" s="20"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="22" t="s">
         <v>341</v>
       </c>
-      <c r="M2" s="23"/>
-      <c r="N2" s="23"/>
-      <c r="O2" s="23"/>
-      <c r="P2" s="23"/>
-      <c r="Q2" s="23"/>
-      <c r="R2" s="23"/>
-      <c r="S2" s="23"/>
-      <c r="T2" s="23"/>
-      <c r="U2" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="V2" s="22" t="s">
+      <c r="H20" s="22" t="s">
         <v>342</v>
       </c>
-      <c r="W2" s="22"/>
-      <c r="X2" s="24"/>
+      <c r="I20" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="24" t="s">
+        <v>344</v>
+      </c>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
+      <c r="S20" s="24"/>
+      <c r="T20" s="24"/>
+      <c r="U20" s="22" t="s">
+        <v>345</v>
+      </c>
+      <c r="V20" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="W20" s="23"/>
+      <c r="X20" s="25"/>
     </row>
-    <row r="3" ht="81.75" spans="1:24">
-      <c r="A3" s="19"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="25" t="s">
+    <row r="21" ht="81.75" spans="1:24">
+      <c r="A21" s="20"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="H3" s="25" t="s">
+      <c r="H21" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="I3" s="26" t="s">
-        <v>343</v>
-      </c>
-      <c r="J3" s="26" t="s">
+      <c r="I21" s="27" t="s">
+        <v>347</v>
+      </c>
+      <c r="J21" s="27" t="s">
         <v>170</v>
       </c>
-      <c r="K3" s="26" t="s">
+      <c r="K21" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="L3" s="27" t="s">
-        <v>344</v>
-      </c>
-      <c r="M3" s="28" t="s">
+      <c r="L21" s="28" t="s">
+        <v>348</v>
+      </c>
+      <c r="M21" s="29" t="s">
         <v>217</v>
       </c>
-      <c r="N3" s="27" t="s">
-        <v>345</v>
-      </c>
-      <c r="O3" s="28" t="s">
+      <c r="N21" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="O21" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="P3" s="28" t="s">
+      <c r="P21" s="29" t="s">
         <v>229</v>
       </c>
-      <c r="Q3" s="28" t="s">
+      <c r="Q21" s="29" t="s">
         <v>257</v>
       </c>
-      <c r="R3" s="28" t="s">
+      <c r="R21" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="S3" s="27" t="s">
-        <v>346</v>
-      </c>
-      <c r="T3" s="27" t="s">
-        <v>347</v>
-      </c>
-      <c r="U3" s="25" t="s">
+      <c r="S21" s="28" t="s">
+        <v>350</v>
+      </c>
+      <c r="T21" s="28" t="s">
+        <v>351</v>
+      </c>
+      <c r="U21" s="26" t="s">
         <v>333</v>
       </c>
-      <c r="V3" s="26" t="s">
+      <c r="V21" s="27" t="s">
         <v>286</v>
       </c>
-      <c r="W3" s="26" t="s">
+      <c r="W21" s="27" t="s">
         <v>325</v>
       </c>
-      <c r="X3" s="29" t="s">
+      <c r="X21" s="30" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="4" s="13" customFormat="1" ht="94.5" spans="1:24">
-      <c r="A4" s="30" t="s">
-        <v>348</v>
-      </c>
-      <c r="B4" s="31" t="s">
-        <v>349</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>350</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>351</v>
-      </c>
-      <c r="E4" s="32"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="33" t="s">
-        <v>148</v>
-      </c>
-      <c r="H4" s="33"/>
-      <c r="I4" s="33"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="35" t="s">
+    <row r="22" s="13" customFormat="1" ht="94.5" spans="1:24">
+      <c r="A22" s="31" t="s">
+        <v>352</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>353</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>354</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="E22" s="33"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="36" t="s">
         <v>219</v>
       </c>
-      <c r="P4" s="36"/>
-      <c r="Q4" s="36"/>
-      <c r="R4" s="36"/>
-      <c r="S4" s="36"/>
-      <c r="T4" s="35" t="s">
+      <c r="P22" s="37"/>
+      <c r="Q22" s="37"/>
+      <c r="R22" s="37"/>
+      <c r="S22" s="37"/>
+      <c r="T22" s="36" t="s">
         <v>274</v>
       </c>
-      <c r="U4" s="33" t="s">
+      <c r="U22" s="34" t="s">
         <v>287</v>
       </c>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="37"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="38"/>
     </row>
-    <row r="5" ht="94.5" spans="1:24">
-      <c r="A5" s="19"/>
-      <c r="B5" s="31"/>
-      <c r="C5" s="32" t="s">
-        <v>352</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>353</v>
-      </c>
-      <c r="E5" s="32"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="33" t="s">
-        <v>354</v>
-      </c>
-      <c r="H5" s="33"/>
-      <c r="I5" s="33"/>
-      <c r="J5" s="33"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="P5" s="36"/>
-      <c r="Q5" s="36"/>
-      <c r="R5" s="36"/>
-      <c r="S5" s="36"/>
-      <c r="T5" s="35" t="s">
+    <row r="23" ht="94.5" spans="1:24">
+      <c r="A23" s="20"/>
+      <c r="B23" s="32"/>
+      <c r="C23" s="33" t="s">
+        <v>356</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="E23" s="33"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="34" t="s">
+        <v>358</v>
+      </c>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="36" t="s">
+        <v>359</v>
+      </c>
+      <c r="P23" s="37"/>
+      <c r="Q23" s="37"/>
+      <c r="R23" s="37"/>
+      <c r="S23" s="37"/>
+      <c r="T23" s="36" t="s">
         <v>274</v>
       </c>
-      <c r="U5" s="33" t="s">
+      <c r="U23" s="34" t="s">
         <v>170</v>
       </c>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="37"/>
+      <c r="V23" s="34"/>
+      <c r="W23" s="34"/>
+      <c r="X23" s="38"/>
     </row>
-    <row r="6" ht="81" spans="1:24">
-      <c r="A6" s="19"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="32" t="s">
-        <v>355</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="E6" s="32"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="33" t="s">
+    <row r="24" ht="81" spans="1:24">
+      <c r="A24" s="20"/>
+      <c r="B24" s="32"/>
+      <c r="C24" s="33" t="s">
+        <v>360</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="E24" s="33"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="34" t="s">
         <v>150</v>
       </c>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="33"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="35"/>
-      <c r="U6" s="33" t="s">
-        <v>357</v>
-      </c>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="37"/>
+      <c r="H24" s="34"/>
+      <c r="I24" s="34"/>
+      <c r="J24" s="34"/>
+      <c r="K24" s="34"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="36"/>
+      <c r="P24" s="37"/>
+      <c r="Q24" s="37"/>
+      <c r="R24" s="37"/>
+      <c r="S24" s="37"/>
+      <c r="T24" s="36"/>
+      <c r="U24" s="34" t="s">
+        <v>362</v>
+      </c>
+      <c r="V24" s="34"/>
+      <c r="W24" s="34"/>
+      <c r="X24" s="38"/>
     </row>
-    <row r="7" ht="81" spans="1:24">
-      <c r="A7" s="19"/>
-      <c r="B7" s="31"/>
-      <c r="C7" s="32" t="s">
-        <v>358</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>359</v>
-      </c>
-      <c r="E7" s="32"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="33" t="s">
+    <row r="25" ht="81" spans="1:24">
+      <c r="A25" s="20"/>
+      <c r="B25" s="32"/>
+      <c r="C25" s="33" t="s">
+        <v>363</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="E25" s="33"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="H7" s="33"/>
-      <c r="I7" s="33"/>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="38" t="s">
+      <c r="H25" s="34"/>
+      <c r="I25" s="34"/>
+      <c r="J25" s="34"/>
+      <c r="K25" s="34"/>
+      <c r="L25" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="M7" s="38"/>
-      <c r="N7" s="38"/>
-      <c r="O7" s="35"/>
-      <c r="P7" s="35"/>
-      <c r="Q7" s="35"/>
-      <c r="R7" s="35"/>
-      <c r="S7" s="35"/>
-      <c r="T7" s="35"/>
-      <c r="U7" s="33" t="s">
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="36"/>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="36"/>
+      <c r="R25" s="36"/>
+      <c r="S25" s="36"/>
+      <c r="T25" s="36"/>
+      <c r="U25" s="34" t="s">
         <v>289</v>
       </c>
-      <c r="V7" s="33"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="37"/>
+      <c r="V25" s="34"/>
+      <c r="W25" s="34"/>
+      <c r="X25" s="38"/>
     </row>
-    <row r="8" customFormat="1" ht="121.5" spans="1:24">
-      <c r="A8" s="19"/>
-      <c r="B8" s="31"/>
-      <c r="C8" s="32" t="s">
-        <v>360</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="E8" s="32"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="33" t="s">
-        <v>362</v>
-      </c>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="33"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="35" t="s">
+    <row r="26" customFormat="1" ht="121.5" spans="1:24">
+      <c r="A26" s="20"/>
+      <c r="B26" s="32"/>
+      <c r="C26" s="33" t="s">
+        <v>365</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>366</v>
+      </c>
+      <c r="E26" s="33"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="34" t="s">
+        <v>367</v>
+      </c>
+      <c r="H26" s="34"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="34"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="39"/>
+      <c r="M26" s="39"/>
+      <c r="N26" s="39"/>
+      <c r="O26" s="36"/>
+      <c r="P26" s="36" t="s">
         <v>230</v>
       </c>
-      <c r="Q8" s="35"/>
-      <c r="R8" s="35"/>
-      <c r="S8" s="35"/>
-      <c r="T8" s="35"/>
-      <c r="U8" s="33" t="s">
-        <v>290</v>
-      </c>
-      <c r="V8" s="33"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="39" t="s">
+      <c r="Q26" s="36"/>
+      <c r="R26" s="36"/>
+      <c r="S26" s="36"/>
+      <c r="T26" s="36"/>
+      <c r="U26" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="V26" s="34"/>
+      <c r="W26" s="34"/>
+      <c r="X26" s="40" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="9" customFormat="1" ht="81" spans="1:24">
-      <c r="A9" s="19"/>
-      <c r="B9" s="31"/>
-      <c r="C9" s="32" t="s">
-        <v>363</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="33" t="s">
-        <v>153</v>
-      </c>
-      <c r="H9" s="33"/>
-      <c r="I9" s="33"/>
-      <c r="J9" s="33"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="38" t="s">
+    <row r="27" customFormat="1" ht="81" spans="1:24">
+      <c r="A27" s="20"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="33" t="s">
+        <v>368</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="E27" s="33"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="34" t="s">
+        <v>370</v>
+      </c>
+      <c r="H27" s="34"/>
+      <c r="I27" s="34"/>
+      <c r="J27" s="34"/>
+      <c r="K27" s="34"/>
+      <c r="L27" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="M9" s="38"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="35"/>
-      <c r="P9" s="35"/>
-      <c r="Q9" s="35"/>
-      <c r="R9" s="35" t="s">
+      <c r="M27" s="39"/>
+      <c r="N27" s="39"/>
+      <c r="O27" s="36"/>
+      <c r="P27" s="36"/>
+      <c r="Q27" s="36"/>
+      <c r="R27" s="36" t="s">
         <v>268</v>
       </c>
-      <c r="S9" s="35"/>
-      <c r="T9" s="35"/>
-      <c r="U9" s="33" t="s">
-        <v>291</v>
-      </c>
-      <c r="V9" s="33"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="37"/>
+      <c r="S27" s="36"/>
+      <c r="T27" s="36"/>
+      <c r="U27" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="V27" s="34"/>
+      <c r="W27" s="34"/>
+      <c r="X27" s="38"/>
     </row>
-    <row r="10" s="14" customFormat="1" ht="68.25" spans="1:24">
-      <c r="A10" s="19"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="32" t="s">
-        <v>365</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="E10" s="32"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="33" t="s">
+    <row r="28" s="14" customFormat="1" ht="68.25" spans="1:24">
+      <c r="A28" s="20"/>
+      <c r="B28" s="32"/>
+      <c r="C28" s="33" t="s">
+        <v>371</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>372</v>
+      </c>
+      <c r="E28" s="33"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="H10" s="33"/>
-      <c r="I10" s="33"/>
-      <c r="J10" s="33"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="38"/>
-      <c r="M10" s="38"/>
-      <c r="N10" s="38"/>
-      <c r="O10" s="35"/>
-      <c r="P10" s="35" t="s">
+      <c r="H28" s="34"/>
+      <c r="I28" s="34"/>
+      <c r="J28" s="34"/>
+      <c r="K28" s="34"/>
+      <c r="L28" s="39"/>
+      <c r="M28" s="39"/>
+      <c r="N28" s="39"/>
+      <c r="O28" s="36"/>
+      <c r="P28" s="36" t="s">
         <v>231</v>
       </c>
-      <c r="Q10" s="35"/>
-      <c r="R10" s="35"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="35"/>
-      <c r="U10" s="33" t="s">
+      <c r="Q28" s="36"/>
+      <c r="R28" s="36"/>
+      <c r="S28" s="36"/>
+      <c r="T28" s="36"/>
+      <c r="U28" s="34" t="s">
         <v>292</v>
       </c>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="37"/>
+      <c r="V28" s="34"/>
+      <c r="W28" s="34"/>
+      <c r="X28" s="38"/>
     </row>
-    <row r="11" s="13" customFormat="1" ht="54" spans="1:24">
-      <c r="A11" s="30" t="s">
-        <v>367</v>
-      </c>
-      <c r="B11" s="31" t="s">
-        <v>368</v>
-      </c>
-      <c r="C11" s="32" t="s">
-        <v>369</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>370</v>
-      </c>
-      <c r="E11" s="32"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="33" t="s">
+    <row r="29" s="13" customFormat="1" ht="72" customHeight="1" spans="1:24">
+      <c r="A29" s="31" t="s">
+        <v>373</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>374</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>375</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>376</v>
+      </c>
+      <c r="E29" s="33"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="H11" s="33"/>
-      <c r="I11" s="33"/>
-      <c r="J11" s="33"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="38"/>
-      <c r="M11" s="38"/>
-      <c r="N11" s="38"/>
-      <c r="O11" s="35"/>
-      <c r="P11" s="35"/>
-      <c r="Q11" s="35"/>
-      <c r="R11" s="35"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="35"/>
-      <c r="U11" s="33" t="s">
+      <c r="H29" s="34"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34"/>
+      <c r="K29" s="34"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="39"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="36"/>
+      <c r="P29" s="36"/>
+      <c r="Q29" s="36"/>
+      <c r="R29" s="36"/>
+      <c r="S29" s="36"/>
+      <c r="T29" s="36"/>
+      <c r="U29" s="34" t="s">
         <v>293</v>
       </c>
-      <c r="V11" s="33"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="37"/>
+      <c r="V29" s="34"/>
+      <c r="W29" s="34"/>
+      <c r="X29" s="38"/>
     </row>
-    <row r="12" customFormat="1" ht="81" spans="1:24">
-      <c r="A12" s="19"/>
-      <c r="B12" s="31"/>
-      <c r="C12" s="32" t="s">
-        <v>371</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="E12" s="32"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="33" t="s">
+    <row r="30" customFormat="1" ht="81" spans="1:24">
+      <c r="A30" s="20"/>
+      <c r="B30" s="32"/>
+      <c r="C30" s="33" t="s">
+        <v>377</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>378</v>
+      </c>
+      <c r="E30" s="33"/>
+      <c r="F30" s="7"/>
+      <c r="G30" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="H12" s="33"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="40" t="s">
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="41" t="s">
         <v>171</v>
       </c>
-      <c r="K12" s="40" t="s">
+      <c r="K30" s="41" t="s">
         <v>174</v>
       </c>
-      <c r="L12" s="38" t="s">
+      <c r="L30" s="39" t="s">
         <v>187</v>
       </c>
-      <c r="M12" s="38"/>
-      <c r="N12" s="38"/>
-      <c r="O12" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="P12" s="35" t="s">
+      <c r="M30" s="39"/>
+      <c r="N30" s="39"/>
+      <c r="O30" s="36" t="s">
+        <v>379</v>
+      </c>
+      <c r="P30" s="36" t="s">
         <v>232</v>
       </c>
-      <c r="Q12" s="35" t="s">
+      <c r="Q30" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="R12" s="35" t="s">
+      <c r="R30" s="36" t="s">
         <v>268</v>
       </c>
-      <c r="S12" s="35"/>
-      <c r="T12" s="35" t="s">
+      <c r="S30" s="36"/>
+      <c r="T30" s="36" t="s">
         <v>275</v>
       </c>
-      <c r="U12" s="33" t="s">
+      <c r="U30" s="34" t="s">
         <v>294</v>
       </c>
-      <c r="V12" s="33"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="37"/>
+      <c r="V30" s="34"/>
+      <c r="W30" s="34"/>
+      <c r="X30" s="38"/>
     </row>
-    <row r="13" customFormat="1" ht="54" spans="1:24">
-      <c r="A13" s="19"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="32" t="s">
-        <v>373</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="E13" s="32"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="33" t="s">
+    <row r="31" customFormat="1" ht="54" spans="1:24">
+      <c r="A31" s="20"/>
+      <c r="B31" s="32"/>
+      <c r="C31" s="33" t="s">
+        <v>380</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>381</v>
+      </c>
+      <c r="E31" s="33"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="H13" s="33"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="33"/>
-      <c r="K13" s="40" t="s">
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="41" t="s">
         <v>175</v>
       </c>
-      <c r="L13" s="38" t="s">
+      <c r="L31" s="39" t="s">
         <v>188</v>
       </c>
-      <c r="M13" s="38"/>
-      <c r="N13" s="38"/>
-      <c r="O13" s="35"/>
-      <c r="P13" s="35" t="s">
+      <c r="M31" s="39"/>
+      <c r="N31" s="39"/>
+      <c r="O31" s="36"/>
+      <c r="P31" s="36" t="s">
         <v>233</v>
       </c>
-      <c r="Q13" s="35"/>
-      <c r="R13" s="35" t="s">
+      <c r="Q31" s="36"/>
+      <c r="R31" s="36" t="s">
         <v>269</v>
       </c>
-      <c r="S13" s="35"/>
-      <c r="T13" s="35" t="s">
+      <c r="S31" s="36"/>
+      <c r="T31" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="U13" s="33" t="s">
+      <c r="U31" s="34" t="s">
         <v>295</v>
       </c>
-      <c r="V13" s="33"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="37"/>
+      <c r="V31" s="34"/>
+      <c r="W31" s="34"/>
+      <c r="X31" s="38"/>
     </row>
-    <row r="14" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A14" s="19"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="32" t="s">
-        <v>375</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="E14" s="32"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="33" t="s">
+    <row r="32" customFormat="1" ht="82" customHeight="1" spans="1:24">
+      <c r="A32" s="20"/>
+      <c r="B32" s="32"/>
+      <c r="C32" s="33" t="s">
+        <v>382</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>383</v>
+      </c>
+      <c r="E32" s="33"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="34" t="s">
         <v>157</v>
       </c>
-      <c r="H14" s="33"/>
-      <c r="I14" s="33"/>
-      <c r="J14" s="33"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="38" t="s">
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34"/>
+      <c r="K32" s="34"/>
+      <c r="L32" s="39" t="s">
         <v>189</v>
       </c>
-      <c r="M14" s="38"/>
-      <c r="N14" s="38"/>
-      <c r="O14" s="35"/>
-      <c r="P14" s="35"/>
-      <c r="Q14" s="35"/>
-      <c r="R14" s="35"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="35"/>
-      <c r="U14" s="33" t="s">
+      <c r="M32" s="39"/>
+      <c r="N32" s="39"/>
+      <c r="O32" s="36"/>
+      <c r="P32" s="36"/>
+      <c r="Q32" s="36"/>
+      <c r="R32" s="36"/>
+      <c r="S32" s="36"/>
+      <c r="T32" s="36"/>
+      <c r="U32" s="34" t="s">
         <v>296</v>
       </c>
-      <c r="V14" s="33"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="39" t="s">
+      <c r="V32" s="34"/>
+      <c r="W32" s="34"/>
+      <c r="X32" s="40" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="15" customFormat="1" ht="81" spans="1:24">
-      <c r="A15" s="19"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="32" t="s">
-        <v>377</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>378</v>
-      </c>
-      <c r="E15" s="32"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="H15" s="33"/>
-      <c r="I15" s="33"/>
-      <c r="J15" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="K15" s="40" t="s">
-        <v>176</v>
-      </c>
-      <c r="L15" s="38" t="s">
-        <v>190</v>
-      </c>
-      <c r="M15" s="38"/>
-      <c r="N15" s="38"/>
-      <c r="O15" s="35"/>
-      <c r="P15" s="35"/>
-      <c r="Q15" s="35"/>
-      <c r="R15" s="35"/>
-      <c r="S15" s="35"/>
-      <c r="T15" s="35"/>
-      <c r="U15" s="33" t="s">
-        <v>379</v>
-      </c>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="39" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="16" s="14" customFormat="1" ht="68.25" spans="1:24">
-      <c r="A16" s="19"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="32" t="s">
-        <v>380</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>381</v>
-      </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H16" s="33"/>
-      <c r="I16" s="33"/>
-      <c r="J16" s="33"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="38"/>
-      <c r="M16" s="38"/>
-      <c r="N16" s="38"/>
-      <c r="O16" s="35"/>
-      <c r="P16" s="35" t="s">
-        <v>234</v>
-      </c>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="35"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="35"/>
-      <c r="U16" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="V16" s="33"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="37"/>
-    </row>
-    <row r="17" s="13" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A17" s="30" t="s">
-        <v>382</v>
-      </c>
-      <c r="B17" s="31" t="s">
-        <v>383</v>
-      </c>
-      <c r="C17" s="32" t="s">
-        <v>384</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>385</v>
-      </c>
-      <c r="E17" s="32"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H17" s="33"/>
-      <c r="I17" s="33"/>
-      <c r="J17" s="33"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="38"/>
-      <c r="M17" s="38"/>
-      <c r="N17" s="38"/>
-      <c r="O17" s="35"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="35"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="35"/>
-      <c r="U17" s="33" t="s">
-        <v>298</v>
-      </c>
-      <c r="V17" s="33"/>
-      <c r="W17" s="33"/>
-      <c r="X17" s="37"/>
-    </row>
-    <row r="18" customFormat="1" ht="81" spans="1:24">
-      <c r="A18" s="19"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="32" t="s">
-        <v>386</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>387</v>
-      </c>
-      <c r="E18" s="32"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H18" s="33"/>
-      <c r="I18" s="33"/>
-      <c r="J18" s="33"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="38" t="s">
-        <v>191</v>
-      </c>
-      <c r="M18" s="38"/>
-      <c r="N18" s="38"/>
-      <c r="O18" s="35"/>
-      <c r="P18" s="35"/>
-      <c r="Q18" s="35"/>
-      <c r="R18" s="35"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="35"/>
-      <c r="U18" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="V18" s="33"/>
-      <c r="W18" s="33"/>
-      <c r="X18" s="37"/>
-    </row>
-    <row r="19" customFormat="1" ht="81" spans="1:24">
-      <c r="A19" s="19"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="32" t="s">
-        <v>388</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>389</v>
-      </c>
-      <c r="E19" s="32"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H19" s="33"/>
-      <c r="I19" s="33"/>
-      <c r="J19" s="33"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="38" t="s">
-        <v>192</v>
-      </c>
-      <c r="M19" s="38"/>
-      <c r="N19" s="38"/>
-      <c r="O19" s="35"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="35"/>
-      <c r="R19" s="35"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="35"/>
-      <c r="U19" s="33" t="s">
-        <v>300</v>
-      </c>
-      <c r="V19" s="33"/>
-      <c r="W19" s="33"/>
-      <c r="X19" s="37"/>
-    </row>
-    <row r="20" customFormat="1" ht="54" spans="1:24">
-      <c r="A20" s="19"/>
-      <c r="B20" s="31"/>
-      <c r="C20" s="32" t="s">
-        <v>390</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>391</v>
-      </c>
-      <c r="E20" s="32"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H20" s="33"/>
-      <c r="I20" s="33"/>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="M20" s="38"/>
-      <c r="N20" s="38"/>
-      <c r="O20" s="35"/>
-      <c r="P20" s="35" t="s">
-        <v>235</v>
-      </c>
-      <c r="Q20" s="35"/>
-      <c r="R20" s="35"/>
-      <c r="S20" s="35"/>
-      <c r="T20" s="35"/>
-      <c r="U20" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="V20" s="33"/>
-      <c r="W20" s="33"/>
-      <c r="X20" s="37"/>
-    </row>
-    <row r="21" customFormat="1" ht="137" customHeight="1" spans="1:24">
-      <c r="A21" s="19"/>
-      <c r="B21" s="31"/>
-      <c r="C21" s="32" t="s">
-        <v>392</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>393</v>
-      </c>
-      <c r="E21" s="32"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="H21" s="33"/>
-      <c r="I21" s="33"/>
-      <c r="J21" s="33"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="38" t="s">
-        <v>194</v>
-      </c>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="35"/>
-      <c r="P21" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="35"/>
-      <c r="U21" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="V21" s="33"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="37"/>
-    </row>
-    <row r="22" s="14" customFormat="1" ht="81.75" spans="1:24">
-      <c r="A22" s="19"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="32" t="s">
-        <v>394</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>395</v>
-      </c>
-      <c r="E22" s="32"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H22" s="33"/>
-      <c r="I22" s="33"/>
-      <c r="J22" s="33"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="38" t="s">
-        <v>195</v>
-      </c>
-      <c r="M22" s="38"/>
-      <c r="N22" s="38"/>
-      <c r="O22" s="35"/>
-      <c r="P22" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="Q22" s="35"/>
-      <c r="R22" s="35"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="35"/>
-      <c r="U22" s="33" t="s">
-        <v>303</v>
-      </c>
-      <c r="V22" s="33"/>
-      <c r="W22" s="33"/>
-      <c r="X22" s="37"/>
-    </row>
-    <row r="23" s="13" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A23" s="30" t="s">
-        <v>396</v>
-      </c>
-      <c r="B23" s="31" t="s">
-        <v>397</v>
-      </c>
-      <c r="C23" s="32" t="s">
-        <v>398</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>399</v>
-      </c>
-      <c r="E23" s="32"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H23" s="33"/>
-      <c r="I23" s="33"/>
-      <c r="J23" s="33"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="38"/>
-      <c r="M23" s="38"/>
-      <c r="N23" s="38"/>
-      <c r="O23" s="35"/>
-      <c r="P23" s="35"/>
-      <c r="Q23" s="35"/>
-      <c r="R23" s="35"/>
-      <c r="S23" s="35"/>
-      <c r="T23" s="35"/>
-      <c r="U23" s="33" t="s">
-        <v>304</v>
-      </c>
-      <c r="V23" s="33"/>
-      <c r="W23" s="33"/>
-      <c r="X23" s="37"/>
-    </row>
-    <row r="24" customFormat="1" ht="76" customHeight="1" spans="1:24">
-      <c r="A24" s="19"/>
-      <c r="B24" s="31"/>
-      <c r="C24" s="32" t="s">
-        <v>400</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>401</v>
-      </c>
-      <c r="E24" s="32"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H24" s="33"/>
-      <c r="I24" s="33"/>
-      <c r="J24" s="33"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="38" t="s">
-        <v>193</v>
-      </c>
-      <c r="M24" s="38"/>
-      <c r="N24" s="38"/>
-      <c r="O24" s="35"/>
-      <c r="P24" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="Q24" s="35"/>
-      <c r="R24" s="35"/>
-      <c r="S24" s="35"/>
-      <c r="T24" s="35"/>
-      <c r="U24" s="33" t="s">
-        <v>305</v>
-      </c>
-      <c r="V24" s="33"/>
-      <c r="W24" s="33"/>
-      <c r="X24" s="37"/>
-    </row>
-    <row r="25" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A25" s="19"/>
-      <c r="B25" s="31"/>
-      <c r="C25" s="32" t="s">
-        <v>402</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>403</v>
-      </c>
-      <c r="E25" s="32"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="33" t="s">
-        <v>160</v>
-      </c>
-      <c r="H25" s="33"/>
-      <c r="I25" s="33"/>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="38" t="s">
-        <v>196</v>
-      </c>
-      <c r="M25" s="38"/>
-      <c r="N25" s="38"/>
-      <c r="O25" s="35"/>
-      <c r="P25" s="35" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q25" s="35"/>
-      <c r="R25" s="35"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="35"/>
-      <c r="U25" s="33" t="s">
-        <v>306</v>
-      </c>
-      <c r="V25" s="33"/>
-      <c r="W25" s="33"/>
-      <c r="X25" s="37"/>
-    </row>
-    <row r="26" s="14" customFormat="1" ht="81.75" spans="1:24">
-      <c r="A26" s="19"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="32" t="s">
-        <v>404</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>405</v>
-      </c>
-      <c r="E26" s="32"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="33" t="s">
-        <v>161</v>
-      </c>
-      <c r="H26" s="33"/>
-      <c r="I26" s="33"/>
-      <c r="J26" s="33"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="38" t="s">
-        <v>197</v>
-      </c>
-      <c r="M26" s="38"/>
-      <c r="N26" s="38"/>
-      <c r="O26" s="35"/>
-      <c r="P26" s="35" t="s">
-        <v>240</v>
-      </c>
-      <c r="Q26" s="35"/>
-      <c r="R26" s="35"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="35"/>
-      <c r="U26" s="33" t="s">
-        <v>406</v>
-      </c>
-      <c r="V26" s="33"/>
-      <c r="W26" s="33"/>
-      <c r="X26" s="37"/>
-    </row>
-    <row r="27" s="13" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A27" s="30" t="s">
-        <v>407</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>408</v>
-      </c>
-      <c r="C27" s="32" t="s">
-        <v>409</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>410</v>
-      </c>
-      <c r="E27" s="32"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H27" s="33"/>
-      <c r="I27" s="33"/>
-      <c r="J27" s="33"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="M27" s="38"/>
-      <c r="N27" s="38"/>
-      <c r="O27" s="35" t="s">
-        <v>411</v>
-      </c>
-      <c r="P27" s="35" t="s">
-        <v>241</v>
-      </c>
-      <c r="Q27" s="35" t="s">
-        <v>259</v>
-      </c>
-      <c r="R27" s="35"/>
-      <c r="S27" s="35"/>
-      <c r="T27" s="35"/>
-      <c r="U27" s="33" t="s">
-        <v>308</v>
-      </c>
-      <c r="V27" s="33"/>
-      <c r="W27" s="33"/>
-      <c r="X27" s="37"/>
-    </row>
-    <row r="28" customFormat="1" ht="162" spans="1:24">
-      <c r="A28" s="19"/>
-      <c r="B28" s="31"/>
-      <c r="C28" s="32" t="s">
-        <v>412</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="E28" s="32"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H28" s="33"/>
-      <c r="I28" s="33"/>
-      <c r="J28" s="33"/>
-      <c r="K28" s="40" t="s">
-        <v>177</v>
-      </c>
-      <c r="L28" s="38" t="s">
-        <v>199</v>
-      </c>
-      <c r="M28" s="38"/>
-      <c r="N28" s="38"/>
-      <c r="O28" s="35" t="s">
-        <v>223</v>
-      </c>
-      <c r="P28" s="35" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q28" s="35" t="s">
-        <v>260</v>
-      </c>
-      <c r="R28" s="35"/>
-      <c r="S28" s="35"/>
-      <c r="T28" s="35"/>
-      <c r="U28" s="33" t="s">
-        <v>309</v>
-      </c>
-      <c r="V28" s="33"/>
-      <c r="W28" s="33"/>
-      <c r="X28" s="37"/>
-    </row>
-    <row r="29" s="14" customFormat="1" ht="135.75" spans="1:24">
-      <c r="A29" s="19"/>
-      <c r="B29" s="31"/>
-      <c r="C29" s="32" t="s">
-        <v>414</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>415</v>
-      </c>
-      <c r="E29" s="32"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="33" t="s">
-        <v>162</v>
-      </c>
-      <c r="H29" s="33"/>
-      <c r="I29" s="33"/>
-      <c r="J29" s="33"/>
-      <c r="K29" s="33"/>
-      <c r="L29" s="38" t="s">
-        <v>200</v>
-      </c>
-      <c r="M29" s="38"/>
-      <c r="N29" s="38"/>
-      <c r="O29" s="35" t="s">
-        <v>224</v>
-      </c>
-      <c r="P29" s="35" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q29" s="35" t="s">
-        <v>261</v>
-      </c>
-      <c r="R29" s="35"/>
-      <c r="S29" s="35"/>
-      <c r="T29" s="35"/>
-      <c r="U29" s="33" t="s">
-        <v>310</v>
-      </c>
-      <c r="V29" s="33"/>
-      <c r="W29" s="33"/>
-      <c r="X29" s="37"/>
-    </row>
-    <row r="30" s="13" customFormat="1" ht="94.5" spans="1:24">
-      <c r="A30" s="30" t="s">
-        <v>416</v>
-      </c>
-      <c r="B30" s="31" t="s">
-        <v>417</v>
-      </c>
-      <c r="C30" s="32" t="s">
-        <v>418</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="E30" s="32"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H30" s="33"/>
-      <c r="I30" s="33"/>
-      <c r="J30" s="33"/>
-      <c r="K30" s="33"/>
-      <c r="L30" s="38" t="s">
-        <v>201</v>
-      </c>
-      <c r="M30" s="38"/>
-      <c r="N30" s="38"/>
-      <c r="O30" s="35"/>
-      <c r="P30" s="35"/>
-      <c r="Q30" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="R30" s="35"/>
-      <c r="S30" s="35"/>
-      <c r="T30" s="35"/>
-      <c r="U30" s="33" t="s">
-        <v>311</v>
-      </c>
-      <c r="V30" s="33"/>
-      <c r="W30" s="33"/>
-      <c r="X30" s="37"/>
-    </row>
-    <row r="31" customFormat="1" ht="81" spans="1:24">
-      <c r="A31" s="19"/>
-      <c r="B31" s="31"/>
-      <c r="C31" s="32" t="s">
-        <v>420</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>421</v>
-      </c>
-      <c r="E31" s="32"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="33"/>
-      <c r="K31" s="33"/>
-      <c r="L31" s="38" t="s">
-        <v>202</v>
-      </c>
-      <c r="M31" s="38"/>
-      <c r="N31" s="38"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="33" t="s">
-        <v>312</v>
-      </c>
-      <c r="V31" s="33"/>
-      <c r="W31" s="33"/>
-      <c r="X31" s="37"/>
-    </row>
-    <row r="32" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A32" s="19"/>
-      <c r="B32" s="31"/>
-      <c r="C32" s="32" t="s">
-        <v>422</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>423</v>
-      </c>
-      <c r="E32" s="32"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="H32" s="33"/>
-      <c r="I32" s="33"/>
-      <c r="J32" s="33"/>
-      <c r="K32" s="33"/>
-      <c r="L32" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="M32" s="38"/>
-      <c r="N32" s="38"/>
-      <c r="O32" s="35"/>
-      <c r="P32" s="35"/>
-      <c r="Q32" s="35"/>
-      <c r="R32" s="35" t="s">
-        <v>269</v>
-      </c>
-      <c r="S32" s="35"/>
-      <c r="T32" s="35" t="s">
-        <v>277</v>
-      </c>
-      <c r="U32" s="33" t="s">
-        <v>313</v>
-      </c>
-      <c r="V32" s="33"/>
-      <c r="W32" s="33"/>
-      <c r="X32" s="37"/>
     </row>
     <row r="33" customFormat="1" ht="81" spans="1:24">
-      <c r="A33" s="19"/>
-      <c r="B33" s="31"/>
-      <c r="C33" s="32" t="s">
+      <c r="A33" s="20"/>
+      <c r="B33" s="32"/>
+      <c r="C33" s="33" t="s">
+        <v>384</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>385</v>
+      </c>
+      <c r="E33" s="33"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="41" t="s">
+        <v>172</v>
+      </c>
+      <c r="K33" s="41" t="s">
+        <v>176</v>
+      </c>
+      <c r="L33" s="39" t="s">
+        <v>190</v>
+      </c>
+      <c r="M33" s="39"/>
+      <c r="N33" s="39"/>
+      <c r="O33" s="36"/>
+      <c r="P33" s="36"/>
+      <c r="Q33" s="36"/>
+      <c r="R33" s="36"/>
+      <c r="S33" s="36"/>
+      <c r="T33" s="36"/>
+      <c r="U33" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="V33" s="34"/>
+      <c r="W33" s="34"/>
+      <c r="X33" s="40" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="34" s="14" customFormat="1" ht="68.25" spans="1:24">
+      <c r="A34" s="20"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="33" t="s">
+        <v>387</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>388</v>
+      </c>
+      <c r="E34" s="33"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="39"/>
+      <c r="M34" s="39"/>
+      <c r="N34" s="39"/>
+      <c r="O34" s="36"/>
+      <c r="P34" s="36" t="s">
+        <v>234</v>
+      </c>
+      <c r="Q34" s="36"/>
+      <c r="R34" s="36"/>
+      <c r="S34" s="36"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="V34" s="34"/>
+      <c r="W34" s="34"/>
+      <c r="X34" s="38"/>
+    </row>
+    <row r="35" s="13" customFormat="1" ht="82" customHeight="1" spans="1:24">
+      <c r="A35" s="31" t="s">
+        <v>389</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>390</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>391</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>392</v>
+      </c>
+      <c r="E35" s="33"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="34"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="39"/>
+      <c r="M35" s="39"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="36"/>
+      <c r="P35" s="36"/>
+      <c r="Q35" s="36"/>
+      <c r="R35" s="36"/>
+      <c r="S35" s="36"/>
+      <c r="T35" s="36"/>
+      <c r="U35" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="V35" s="34"/>
+      <c r="W35" s="34"/>
+      <c r="X35" s="38"/>
+    </row>
+    <row r="36" customFormat="1" ht="81" spans="1:24">
+      <c r="A36" s="20"/>
+      <c r="B36" s="32"/>
+      <c r="C36" s="33" t="s">
+        <v>393</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>394</v>
+      </c>
+      <c r="E36" s="33"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H36" s="34"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="34"/>
+      <c r="L36" s="39" t="s">
+        <v>191</v>
+      </c>
+      <c r="M36" s="39"/>
+      <c r="N36" s="39"/>
+      <c r="O36" s="36"/>
+      <c r="P36" s="36"/>
+      <c r="Q36" s="36"/>
+      <c r="R36" s="36"/>
+      <c r="S36" s="36"/>
+      <c r="T36" s="36"/>
+      <c r="U36" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="V36" s="34"/>
+      <c r="W36" s="34"/>
+      <c r="X36" s="38"/>
+    </row>
+    <row r="37" customFormat="1" ht="81" spans="1:24">
+      <c r="A37" s="20"/>
+      <c r="B37" s="32"/>
+      <c r="C37" s="33" t="s">
+        <v>395</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="E37" s="33"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H37" s="34"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="34"/>
+      <c r="K37" s="34"/>
+      <c r="L37" s="39" t="s">
+        <v>192</v>
+      </c>
+      <c r="M37" s="39"/>
+      <c r="N37" s="39"/>
+      <c r="O37" s="36"/>
+      <c r="P37" s="36"/>
+      <c r="Q37" s="36"/>
+      <c r="R37" s="36"/>
+      <c r="S37" s="36"/>
+      <c r="T37" s="36"/>
+      <c r="U37" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="V37" s="34"/>
+      <c r="W37" s="34"/>
+      <c r="X37" s="38"/>
+    </row>
+    <row r="38" customFormat="1" ht="54" spans="1:24">
+      <c r="A38" s="20"/>
+      <c r="B38" s="32"/>
+      <c r="C38" s="33" t="s">
+        <v>397</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>398</v>
+      </c>
+      <c r="E38" s="33"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H38" s="34"/>
+      <c r="I38" s="34"/>
+      <c r="J38" s="34"/>
+      <c r="K38" s="34"/>
+      <c r="L38" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="M38" s="39"/>
+      <c r="N38" s="39"/>
+      <c r="O38" s="36"/>
+      <c r="P38" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q38" s="36"/>
+      <c r="R38" s="36"/>
+      <c r="S38" s="36"/>
+      <c r="T38" s="36"/>
+      <c r="U38" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="V38" s="34"/>
+      <c r="W38" s="34"/>
+      <c r="X38" s="38"/>
+    </row>
+    <row r="39" customFormat="1" ht="137" customHeight="1" spans="1:24">
+      <c r="A39" s="20"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="33" t="s">
+        <v>399</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>400</v>
+      </c>
+      <c r="E39" s="33"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="H39" s="34"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="34"/>
+      <c r="K39" s="34"/>
+      <c r="L39" s="39" t="s">
+        <v>194</v>
+      </c>
+      <c r="M39" s="39"/>
+      <c r="N39" s="39"/>
+      <c r="O39" s="36"/>
+      <c r="P39" s="36" t="s">
+        <v>236</v>
+      </c>
+      <c r="Q39" s="36"/>
+      <c r="R39" s="36"/>
+      <c r="S39" s="36"/>
+      <c r="T39" s="36"/>
+      <c r="U39" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="V39" s="34"/>
+      <c r="W39" s="34"/>
+      <c r="X39" s="38"/>
+    </row>
+    <row r="40" s="14" customFormat="1" ht="81.75" spans="1:24">
+      <c r="A40" s="20"/>
+      <c r="B40" s="32"/>
+      <c r="C40" s="33" t="s">
+        <v>401</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="E40" s="33"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H40" s="34"/>
+      <c r="I40" s="34"/>
+      <c r="J40" s="34"/>
+      <c r="K40" s="34"/>
+      <c r="L40" s="39" t="s">
+        <v>195</v>
+      </c>
+      <c r="M40" s="39"/>
+      <c r="N40" s="39"/>
+      <c r="O40" s="36"/>
+      <c r="P40" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q40" s="36"/>
+      <c r="R40" s="36"/>
+      <c r="S40" s="36"/>
+      <c r="T40" s="36"/>
+      <c r="U40" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="V40" s="34"/>
+      <c r="W40" s="34"/>
+      <c r="X40" s="38"/>
+    </row>
+    <row r="41" s="13" customFormat="1" ht="67.5" spans="1:24">
+      <c r="A41" s="31" t="s">
+        <v>403</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>404</v>
+      </c>
+      <c r="C41" s="33" t="s">
+        <v>405</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="E41" s="33"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="34"/>
+      <c r="K41" s="34"/>
+      <c r="L41" s="39"/>
+      <c r="M41" s="39"/>
+      <c r="N41" s="39"/>
+      <c r="O41" s="36"/>
+      <c r="P41" s="36"/>
+      <c r="Q41" s="36"/>
+      <c r="R41" s="36"/>
+      <c r="S41" s="36"/>
+      <c r="T41" s="36"/>
+      <c r="U41" s="34" t="s">
+        <v>304</v>
+      </c>
+      <c r="V41" s="34"/>
+      <c r="W41" s="34"/>
+      <c r="X41" s="38"/>
+    </row>
+    <row r="42" customFormat="1" ht="76" customHeight="1" spans="1:24">
+      <c r="A42" s="20"/>
+      <c r="B42" s="32"/>
+      <c r="C42" s="33" t="s">
+        <v>407</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>408</v>
+      </c>
+      <c r="E42" s="33"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
+      <c r="K42" s="34"/>
+      <c r="L42" s="39" t="s">
+        <v>193</v>
+      </c>
+      <c r="M42" s="39"/>
+      <c r="N42" s="39"/>
+      <c r="O42" s="36"/>
+      <c r="P42" s="36" t="s">
+        <v>238</v>
+      </c>
+      <c r="Q42" s="36"/>
+      <c r="R42" s="36"/>
+      <c r="S42" s="36"/>
+      <c r="T42" s="36"/>
+      <c r="U42" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="V42" s="34"/>
+      <c r="W42" s="34"/>
+      <c r="X42" s="38"/>
+    </row>
+    <row r="43" customFormat="1" ht="67.5" spans="1:24">
+      <c r="A43" s="20"/>
+      <c r="B43" s="32"/>
+      <c r="C43" s="33" t="s">
+        <v>409</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>410</v>
+      </c>
+      <c r="E43" s="33"/>
+      <c r="F43" s="7"/>
+      <c r="G43" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="39" t="s">
+        <v>196</v>
+      </c>
+      <c r="M43" s="39"/>
+      <c r="N43" s="39"/>
+      <c r="O43" s="36"/>
+      <c r="P43" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q43" s="36"/>
+      <c r="R43" s="36"/>
+      <c r="S43" s="36"/>
+      <c r="T43" s="36"/>
+      <c r="U43" s="34" t="s">
+        <v>306</v>
+      </c>
+      <c r="V43" s="34"/>
+      <c r="W43" s="34"/>
+      <c r="X43" s="38"/>
+    </row>
+    <row r="44" s="14" customFormat="1" ht="81.75" spans="1:24">
+      <c r="A44" s="20"/>
+      <c r="B44" s="32"/>
+      <c r="C44" s="33" t="s">
+        <v>411</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>412</v>
+      </c>
+      <c r="E44" s="33"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="H44" s="34"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="34"/>
+      <c r="K44" s="34"/>
+      <c r="L44" s="39" t="s">
+        <v>197</v>
+      </c>
+      <c r="M44" s="39"/>
+      <c r="N44" s="39"/>
+      <c r="O44" s="36"/>
+      <c r="P44" s="36" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q44" s="36"/>
+      <c r="R44" s="36"/>
+      <c r="S44" s="36"/>
+      <c r="T44" s="36"/>
+      <c r="U44" s="34" t="s">
+        <v>413</v>
+      </c>
+      <c r="V44" s="34"/>
+      <c r="W44" s="34"/>
+      <c r="X44" s="38"/>
+    </row>
+    <row r="45" s="13" customFormat="1" ht="67.5" spans="1:24">
+      <c r="A45" s="31" t="s">
+        <v>414</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>415</v>
+      </c>
+      <c r="C45" s="33" t="s">
+        <v>416</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>417</v>
+      </c>
+      <c r="E45" s="33"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H45" s="34"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="34"/>
+      <c r="K45" s="34"/>
+      <c r="L45" s="39" t="s">
+        <v>198</v>
+      </c>
+      <c r="M45" s="39"/>
+      <c r="N45" s="39"/>
+      <c r="O45" s="36" t="s">
+        <v>418</v>
+      </c>
+      <c r="P45" s="36" t="s">
+        <v>241</v>
+      </c>
+      <c r="Q45" s="36" t="s">
+        <v>259</v>
+      </c>
+      <c r="R45" s="36"/>
+      <c r="S45" s="36"/>
+      <c r="T45" s="36"/>
+      <c r="U45" s="34" t="s">
+        <v>308</v>
+      </c>
+      <c r="V45" s="34"/>
+      <c r="W45" s="34"/>
+      <c r="X45" s="38"/>
+    </row>
+    <row r="46" customFormat="1" ht="162" spans="1:24">
+      <c r="A46" s="20"/>
+      <c r="B46" s="32"/>
+      <c r="C46" s="33" t="s">
+        <v>419</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>420</v>
+      </c>
+      <c r="E46" s="33"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
+      <c r="J46" s="34"/>
+      <c r="K46" s="41" t="s">
+        <v>177</v>
+      </c>
+      <c r="L46" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="M46" s="39"/>
+      <c r="N46" s="39"/>
+      <c r="O46" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="P46" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="Q46" s="36" t="s">
+        <v>260</v>
+      </c>
+      <c r="R46" s="36"/>
+      <c r="S46" s="36"/>
+      <c r="T46" s="36"/>
+      <c r="U46" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="V46" s="34"/>
+      <c r="W46" s="34"/>
+      <c r="X46" s="38"/>
+    </row>
+    <row r="47" s="14" customFormat="1" ht="135.75" spans="1:24">
+      <c r="A47" s="20"/>
+      <c r="B47" s="32"/>
+      <c r="C47" s="33" t="s">
+        <v>421</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="E47" s="33"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
+      <c r="J47" s="34"/>
+      <c r="K47" s="34"/>
+      <c r="L47" s="39" t="s">
+        <v>200</v>
+      </c>
+      <c r="M47" s="39"/>
+      <c r="N47" s="39"/>
+      <c r="O47" s="36" t="s">
+        <v>224</v>
+      </c>
+      <c r="P47" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q47" s="36" t="s">
+        <v>261</v>
+      </c>
+      <c r="R47" s="36"/>
+      <c r="S47" s="36"/>
+      <c r="T47" s="36"/>
+      <c r="U47" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="V47" s="34"/>
+      <c r="W47" s="34"/>
+      <c r="X47" s="38"/>
+    </row>
+    <row r="48" s="13" customFormat="1" ht="94.5" spans="1:24">
+      <c r="A48" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="B48" s="32" t="s">
         <v>424</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="C48" s="33" t="s">
         <v>425</v>
       </c>
-      <c r="E33" s="32"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="33" t="s">
+      <c r="D48" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="E48" s="33"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="H33" s="33"/>
-      <c r="I33" s="33"/>
-      <c r="J33" s="33"/>
-      <c r="K33" s="33"/>
-      <c r="L33" s="38" t="s">
+      <c r="H48" s="34"/>
+      <c r="I48" s="34"/>
+      <c r="J48" s="34"/>
+      <c r="K48" s="34"/>
+      <c r="L48" s="39" t="s">
+        <v>201</v>
+      </c>
+      <c r="M48" s="39"/>
+      <c r="N48" s="39"/>
+      <c r="O48" s="36"/>
+      <c r="P48" s="36"/>
+      <c r="Q48" s="36" t="s">
+        <v>262</v>
+      </c>
+      <c r="R48" s="36"/>
+      <c r="S48" s="36"/>
+      <c r="T48" s="36"/>
+      <c r="U48" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="V48" s="34"/>
+      <c r="W48" s="34"/>
+      <c r="X48" s="38"/>
+    </row>
+    <row r="49" customFormat="1" ht="81" spans="1:24">
+      <c r="A49" s="20"/>
+      <c r="B49" s="32"/>
+      <c r="C49" s="33" t="s">
+        <v>427</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="E49" s="33"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H49" s="34"/>
+      <c r="I49" s="34"/>
+      <c r="J49" s="34"/>
+      <c r="K49" s="34"/>
+      <c r="L49" s="39" t="s">
+        <v>202</v>
+      </c>
+      <c r="M49" s="39"/>
+      <c r="N49" s="39"/>
+      <c r="O49" s="36"/>
+      <c r="P49" s="36"/>
+      <c r="Q49" s="36"/>
+      <c r="R49" s="36"/>
+      <c r="S49" s="36"/>
+      <c r="T49" s="36"/>
+      <c r="U49" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="V49" s="34"/>
+      <c r="W49" s="34"/>
+      <c r="X49" s="38"/>
+    </row>
+    <row r="50" customFormat="1" ht="67.5" spans="1:24">
+      <c r="A50" s="20"/>
+      <c r="B50" s="32"/>
+      <c r="C50" s="33" t="s">
+        <v>429</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>430</v>
+      </c>
+      <c r="E50" s="33"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H50" s="34"/>
+      <c r="I50" s="34"/>
+      <c r="J50" s="34"/>
+      <c r="K50" s="34"/>
+      <c r="L50" s="39" t="s">
+        <v>203</v>
+      </c>
+      <c r="M50" s="39"/>
+      <c r="N50" s="39"/>
+      <c r="O50" s="36"/>
+      <c r="P50" s="36"/>
+      <c r="Q50" s="36"/>
+      <c r="R50" s="36" t="s">
+        <v>269</v>
+      </c>
+      <c r="S50" s="36"/>
+      <c r="T50" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="U50" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="V50" s="34"/>
+      <c r="W50" s="34"/>
+      <c r="X50" s="38"/>
+    </row>
+    <row r="51" customFormat="1" ht="81" spans="1:24">
+      <c r="A51" s="20"/>
+      <c r="B51" s="32"/>
+      <c r="C51" s="33" t="s">
+        <v>431</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>432</v>
+      </c>
+      <c r="E51" s="33"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="H51" s="34"/>
+      <c r="I51" s="34"/>
+      <c r="J51" s="34"/>
+      <c r="K51" s="34"/>
+      <c r="L51" s="39" t="s">
         <v>204</v>
       </c>
-      <c r="M33" s="38"/>
-      <c r="N33" s="38"/>
-      <c r="O33" s="35"/>
-      <c r="P33" s="35"/>
-      <c r="Q33" s="35"/>
-      <c r="R33" s="35"/>
-      <c r="S33" s="35"/>
-      <c r="T33" s="35" t="s">
+      <c r="M51" s="39"/>
+      <c r="N51" s="39"/>
+      <c r="O51" s="36"/>
+      <c r="P51" s="36"/>
+      <c r="Q51" s="36"/>
+      <c r="R51" s="36"/>
+      <c r="S51" s="36"/>
+      <c r="T51" s="36" t="s">
         <v>278</v>
       </c>
-      <c r="U33" s="33" t="s">
+      <c r="U51" s="34" t="s">
         <v>314</v>
       </c>
-      <c r="V33" s="33"/>
-      <c r="W33" s="33"/>
-      <c r="X33" s="37"/>
+      <c r="V51" s="34"/>
+      <c r="W51" s="34"/>
+      <c r="X51" s="38"/>
     </row>
-    <row r="34" customFormat="1" ht="81" spans="1:24">
-      <c r="A34" s="19"/>
-      <c r="B34" s="31"/>
-      <c r="C34" s="32" t="s">
-        <v>426</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>427</v>
-      </c>
-      <c r="E34" s="32"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="33" t="s">
+    <row r="52" customFormat="1" ht="81" spans="1:24">
+      <c r="A52" s="20"/>
+      <c r="B52" s="32"/>
+      <c r="C52" s="33" t="s">
+        <v>433</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>434</v>
+      </c>
+      <c r="E52" s="33"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="34" t="s">
         <v>163</v>
       </c>
-      <c r="H34" s="33"/>
-      <c r="I34" s="33"/>
-      <c r="J34" s="33"/>
-      <c r="K34" s="33"/>
-      <c r="L34" s="38"/>
-      <c r="M34" s="38"/>
-      <c r="N34" s="38"/>
-      <c r="O34" s="35"/>
-      <c r="P34" s="35"/>
-      <c r="Q34" s="35"/>
-      <c r="R34" s="35"/>
-      <c r="S34" s="35"/>
-      <c r="T34" s="35" t="s">
+      <c r="H52" s="34"/>
+      <c r="I52" s="34"/>
+      <c r="J52" s="34"/>
+      <c r="K52" s="34"/>
+      <c r="L52" s="39"/>
+      <c r="M52" s="39"/>
+      <c r="N52" s="39"/>
+      <c r="O52" s="36"/>
+      <c r="P52" s="36"/>
+      <c r="Q52" s="36"/>
+      <c r="R52" s="36"/>
+      <c r="S52" s="36"/>
+      <c r="T52" s="36" t="s">
         <v>279</v>
       </c>
-      <c r="U34" s="41" t="s">
+      <c r="U52" s="42" t="s">
         <v>315</v>
       </c>
-      <c r="V34" s="41"/>
-      <c r="W34" s="41"/>
-      <c r="X34" s="42"/>
+      <c r="V52" s="42"/>
+      <c r="W52" s="42"/>
+      <c r="X52" s="43"/>
     </row>
-    <row r="35" s="14" customFormat="1" ht="95.25" spans="1:24">
-      <c r="A35" s="19"/>
-      <c r="B35" s="31"/>
-      <c r="C35" s="32" t="s">
-        <v>428</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>429</v>
-      </c>
-      <c r="E35" s="32"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="33" t="s">
+    <row r="53" s="14" customFormat="1" ht="95.25" spans="1:24">
+      <c r="A53" s="20"/>
+      <c r="B53" s="32"/>
+      <c r="C53" s="33" t="s">
+        <v>435</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>436</v>
+      </c>
+      <c r="E53" s="33"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="H35" s="33"/>
-      <c r="I35" s="33"/>
-      <c r="J35" s="33"/>
-      <c r="K35" s="33"/>
-      <c r="L35" s="38" t="s">
+      <c r="H53" s="34"/>
+      <c r="I53" s="34"/>
+      <c r="J53" s="34"/>
+      <c r="K53" s="34"/>
+      <c r="L53" s="39" t="s">
         <v>205</v>
       </c>
-      <c r="M35" s="38"/>
-      <c r="N35" s="38"/>
-      <c r="O35" s="35"/>
-      <c r="P35" s="35" t="s">
+      <c r="M53" s="39"/>
+      <c r="N53" s="39"/>
+      <c r="O53" s="36"/>
+      <c r="P53" s="36" t="s">
         <v>244</v>
       </c>
-      <c r="Q35" s="35"/>
-      <c r="R35" s="35"/>
-      <c r="S35" s="35"/>
-      <c r="T35" s="35"/>
-      <c r="U35" s="33" t="s">
+      <c r="Q53" s="36"/>
+      <c r="R53" s="36"/>
+      <c r="S53" s="36"/>
+      <c r="T53" s="36"/>
+      <c r="U53" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="V35" s="33"/>
-      <c r="W35" s="33"/>
-      <c r="X35" s="37"/>
+      <c r="V53" s="34"/>
+      <c r="W53" s="34"/>
+      <c r="X53" s="38"/>
     </row>
-    <row r="36" s="13" customFormat="1" ht="94.5" spans="1:24">
-      <c r="A36" s="30" t="s">
-        <v>430</v>
-      </c>
-      <c r="B36" s="31" t="s">
-        <v>431</v>
-      </c>
-      <c r="C36" s="32" t="s">
-        <v>432</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>433</v>
-      </c>
-      <c r="E36" s="32"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="33" t="s">
+    <row r="54" s="13" customFormat="1" ht="94.5" spans="1:24">
+      <c r="A54" s="31" t="s">
+        <v>437</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>438</v>
+      </c>
+      <c r="C54" s="33" t="s">
+        <v>439</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>440</v>
+      </c>
+      <c r="E54" s="33"/>
+      <c r="F54" s="7"/>
+      <c r="G54" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="H36" s="33"/>
-      <c r="I36" s="33"/>
-      <c r="J36" s="33"/>
-      <c r="K36" s="33"/>
-      <c r="L36" s="38" t="s">
-        <v>434</v>
-      </c>
-      <c r="M36" s="38"/>
-      <c r="N36" s="38"/>
-      <c r="O36" s="35"/>
-      <c r="P36" s="35"/>
-      <c r="Q36" s="35" t="s">
+      <c r="H54" s="34"/>
+      <c r="I54" s="34"/>
+      <c r="J54" s="34"/>
+      <c r="K54" s="34"/>
+      <c r="L54" s="39" t="s">
+        <v>441</v>
+      </c>
+      <c r="M54" s="39"/>
+      <c r="N54" s="39"/>
+      <c r="O54" s="36"/>
+      <c r="P54" s="36"/>
+      <c r="Q54" s="36" t="s">
         <v>263</v>
       </c>
-      <c r="R36" s="35"/>
-      <c r="S36" s="35"/>
-      <c r="T36" s="35" t="s">
+      <c r="R54" s="36"/>
+      <c r="S54" s="36"/>
+      <c r="T54" s="36" t="s">
         <v>280</v>
       </c>
-      <c r="U36" s="33" t="s">
+      <c r="U54" s="34" t="s">
         <v>316</v>
       </c>
-      <c r="V36" s="33"/>
-      <c r="W36" s="33"/>
-      <c r="X36" s="37"/>
+      <c r="V54" s="34"/>
+      <c r="W54" s="34"/>
+      <c r="X54" s="38"/>
     </row>
-    <row r="37" customFormat="1" ht="108" spans="1:24">
-      <c r="A37" s="19"/>
-      <c r="B37" s="31"/>
-      <c r="C37" s="32" t="s">
-        <v>435</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>436</v>
-      </c>
-      <c r="E37" s="32"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="33" t="s">
+    <row r="55" customFormat="1" ht="108" spans="1:24">
+      <c r="A55" s="20"/>
+      <c r="B55" s="32"/>
+      <c r="C55" s="33" t="s">
+        <v>442</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>443</v>
+      </c>
+      <c r="E55" s="33"/>
+      <c r="F55" s="7"/>
+      <c r="G55" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
-      <c r="K37" s="40" t="s">
+      <c r="H55" s="34"/>
+      <c r="I55" s="34"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="41" t="s">
         <v>178</v>
       </c>
-      <c r="L37" s="38" t="s">
+      <c r="L55" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="M37" s="38"/>
-      <c r="N37" s="38"/>
-      <c r="O37" s="35"/>
-      <c r="P37" s="35"/>
-      <c r="Q37" s="35"/>
-      <c r="R37" s="35"/>
-      <c r="S37" s="35" t="s">
+      <c r="M55" s="39"/>
+      <c r="N55" s="39"/>
+      <c r="O55" s="36"/>
+      <c r="P55" s="36"/>
+      <c r="Q55" s="36"/>
+      <c r="R55" s="36"/>
+      <c r="S55" s="36" t="s">
         <v>272</v>
       </c>
-      <c r="T37" s="35" t="s">
+      <c r="T55" s="36" t="s">
         <v>281</v>
       </c>
-      <c r="U37" s="33" t="s">
+      <c r="U55" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="V37" s="33"/>
-      <c r="W37" s="33"/>
-      <c r="X37" s="37"/>
+      <c r="V55" s="34"/>
+      <c r="W55" s="34"/>
+      <c r="X55" s="38"/>
     </row>
-    <row r="38" s="14" customFormat="1" ht="95.25" spans="1:24">
-      <c r="A38" s="19"/>
-      <c r="B38" s="31"/>
-      <c r="C38" s="32" t="s">
-        <v>437</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>438</v>
-      </c>
-      <c r="E38" s="32"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="33" t="s">
+    <row r="56" s="14" customFormat="1" ht="95.25" spans="1:24">
+      <c r="A56" s="20"/>
+      <c r="B56" s="32"/>
+      <c r="C56" s="33" t="s">
+        <v>444</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>445</v>
+      </c>
+      <c r="E56" s="33"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="H38" s="33"/>
-      <c r="I38" s="33"/>
-      <c r="J38" s="33"/>
-      <c r="K38" s="33"/>
-      <c r="L38" s="38"/>
-      <c r="M38" s="38"/>
-      <c r="N38" s="38"/>
-      <c r="O38" s="35"/>
-      <c r="P38" s="35"/>
-      <c r="Q38" s="35" t="s">
+      <c r="H56" s="34"/>
+      <c r="I56" s="34"/>
+      <c r="J56" s="34"/>
+      <c r="K56" s="34"/>
+      <c r="L56" s="39"/>
+      <c r="M56" s="39"/>
+      <c r="N56" s="39"/>
+      <c r="O56" s="36"/>
+      <c r="P56" s="36"/>
+      <c r="Q56" s="36" t="s">
         <v>263</v>
       </c>
-      <c r="R38" s="35"/>
-      <c r="S38" s="35"/>
-      <c r="T38" s="35"/>
-      <c r="U38" s="33" t="s">
+      <c r="R56" s="36"/>
+      <c r="S56" s="36"/>
+      <c r="T56" s="36"/>
+      <c r="U56" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="V38" s="33"/>
-      <c r="W38" s="33"/>
-      <c r="X38" s="37"/>
+      <c r="V56" s="34"/>
+      <c r="W56" s="34"/>
+      <c r="X56" s="38"/>
     </row>
-    <row r="39" s="13" customFormat="1" ht="108" spans="1:24">
-      <c r="A39" s="30" t="s">
-        <v>439</v>
-      </c>
-      <c r="B39" s="31" t="s">
-        <v>440</v>
-      </c>
-      <c r="C39" s="32" t="s">
-        <v>441</v>
-      </c>
-      <c r="D39" s="43" t="s">
-        <v>442</v>
-      </c>
-      <c r="E39" s="32"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="33" t="s">
+    <row r="57" s="13" customFormat="1" ht="108" spans="1:24">
+      <c r="A57" s="31" t="s">
+        <v>446</v>
+      </c>
+      <c r="B57" s="32" t="s">
+        <v>447</v>
+      </c>
+      <c r="C57" s="33" t="s">
+        <v>448</v>
+      </c>
+      <c r="D57" s="44" t="s">
+        <v>449</v>
+      </c>
+      <c r="E57" s="33"/>
+      <c r="F57" s="7"/>
+      <c r="G57" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="H39" s="33"/>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33"/>
-      <c r="L39" s="38"/>
-      <c r="M39" s="38"/>
-      <c r="N39" s="38"/>
-      <c r="O39" s="35"/>
-      <c r="P39" s="35" t="s">
+      <c r="H57" s="34"/>
+      <c r="I57" s="34"/>
+      <c r="J57" s="34"/>
+      <c r="K57" s="34"/>
+      <c r="L57" s="39"/>
+      <c r="M57" s="39"/>
+      <c r="N57" s="39"/>
+      <c r="O57" s="36"/>
+      <c r="P57" s="36" t="s">
         <v>245</v>
       </c>
-      <c r="Q39" s="35"/>
-      <c r="R39" s="35"/>
-      <c r="S39" s="35"/>
-      <c r="T39" s="35"/>
-      <c r="U39" s="33" t="s">
+      <c r="Q57" s="36"/>
+      <c r="R57" s="36"/>
+      <c r="S57" s="36"/>
+      <c r="T57" s="36"/>
+      <c r="U57" s="34" t="s">
         <v>318</v>
       </c>
-      <c r="V39" s="33"/>
-      <c r="W39" s="33"/>
-      <c r="X39" s="37"/>
+      <c r="V57" s="34"/>
+      <c r="W57" s="34"/>
+      <c r="X57" s="38"/>
     </row>
-    <row r="40" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A40" s="19"/>
-      <c r="B40" s="31"/>
-      <c r="C40" s="32" t="s">
-        <v>443</v>
-      </c>
-      <c r="D40" s="43" t="s">
-        <v>444</v>
-      </c>
-      <c r="E40" s="32"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="33" t="s">
+    <row r="58" customFormat="1" ht="67.5" spans="1:24">
+      <c r="A58" s="20"/>
+      <c r="B58" s="32"/>
+      <c r="C58" s="33" t="s">
+        <v>450</v>
+      </c>
+      <c r="D58" s="44" t="s">
+        <v>451</v>
+      </c>
+      <c r="E58" s="33"/>
+      <c r="F58" s="7"/>
+      <c r="G58" s="34" t="s">
         <v>165</v>
       </c>
-      <c r="H40" s="33"/>
-      <c r="I40" s="33"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="33"/>
-      <c r="L40" s="38" t="s">
+      <c r="H58" s="34"/>
+      <c r="I58" s="34"/>
+      <c r="J58" s="34"/>
+      <c r="K58" s="34"/>
+      <c r="L58" s="39" t="s">
         <v>208</v>
       </c>
-      <c r="M40" s="38"/>
-      <c r="N40" s="38"/>
-      <c r="O40" s="35" t="s">
+      <c r="M58" s="39"/>
+      <c r="N58" s="39"/>
+      <c r="O58" s="36" t="s">
         <v>225</v>
       </c>
-      <c r="P40" s="35" t="s">
+      <c r="P58" s="36" t="s">
         <v>246</v>
       </c>
-      <c r="Q40" s="35"/>
-      <c r="R40" s="35"/>
-      <c r="S40" s="35"/>
-      <c r="T40" s="35"/>
-      <c r="U40" s="33" t="s">
+      <c r="Q58" s="36"/>
+      <c r="R58" s="36"/>
+      <c r="S58" s="36"/>
+      <c r="T58" s="36"/>
+      <c r="U58" s="34" t="s">
         <v>319</v>
       </c>
-      <c r="V40" s="33"/>
-      <c r="W40" s="33"/>
-      <c r="X40" s="37"/>
+      <c r="V58" s="34"/>
+      <c r="W58" s="34"/>
+      <c r="X58" s="38"/>
     </row>
-    <row r="41" customFormat="1" ht="81" spans="1:24">
-      <c r="A41" s="19"/>
-      <c r="B41" s="31"/>
-      <c r="C41" s="32" t="s">
-        <v>445</v>
-      </c>
-      <c r="D41" s="43" t="s">
-        <v>446</v>
-      </c>
-      <c r="E41" s="32"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="33" t="s">
+    <row r="59" customFormat="1" ht="81" spans="1:24">
+      <c r="A59" s="20"/>
+      <c r="B59" s="32"/>
+      <c r="C59" s="33" t="s">
+        <v>452</v>
+      </c>
+      <c r="D59" s="44" t="s">
+        <v>453</v>
+      </c>
+      <c r="E59" s="33"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="38" t="s">
+      <c r="H59" s="34"/>
+      <c r="I59" s="34"/>
+      <c r="J59" s="34"/>
+      <c r="K59" s="34"/>
+      <c r="L59" s="39" t="s">
         <v>209</v>
       </c>
-      <c r="M41" s="38"/>
-      <c r="N41" s="38"/>
-      <c r="O41" s="35"/>
-      <c r="P41" s="35" t="s">
+      <c r="M59" s="39"/>
+      <c r="N59" s="39"/>
+      <c r="O59" s="36"/>
+      <c r="P59" s="36" t="s">
         <v>247</v>
       </c>
-      <c r="Q41" s="35" t="s">
+      <c r="Q59" s="36" t="s">
         <v>264</v>
       </c>
-      <c r="R41" s="35"/>
-      <c r="S41" s="35"/>
-      <c r="T41" s="35"/>
-      <c r="U41" s="33" t="s">
+      <c r="R59" s="36"/>
+      <c r="S59" s="36"/>
+      <c r="T59" s="36"/>
+      <c r="U59" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="V41" s="33"/>
-      <c r="W41" s="33"/>
-      <c r="X41" s="37"/>
+      <c r="V59" s="34"/>
+      <c r="W59" s="34"/>
+      <c r="X59" s="38"/>
     </row>
-    <row r="42" customFormat="1" ht="81" spans="1:24">
-      <c r="A42" s="19"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="32" t="s">
-        <v>447</v>
-      </c>
-      <c r="D42" s="43" t="s">
-        <v>448</v>
-      </c>
-      <c r="E42" s="32"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="33" t="s">
+    <row r="60" customFormat="1" ht="81" spans="1:24">
+      <c r="A60" s="20"/>
+      <c r="B60" s="32"/>
+      <c r="C60" s="33" t="s">
+        <v>454</v>
+      </c>
+      <c r="D60" s="44" t="s">
+        <v>455</v>
+      </c>
+      <c r="E60" s="33"/>
+      <c r="F60" s="7"/>
+      <c r="G60" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="38" t="s">
+      <c r="H60" s="34"/>
+      <c r="I60" s="34"/>
+      <c r="J60" s="34"/>
+      <c r="K60" s="34"/>
+      <c r="L60" s="39" t="s">
         <v>210</v>
       </c>
-      <c r="M42" s="38"/>
-      <c r="N42" s="38"/>
-      <c r="O42" s="35" t="s">
+      <c r="M60" s="39"/>
+      <c r="N60" s="39"/>
+      <c r="O60" s="36" t="s">
         <v>226</v>
       </c>
-      <c r="P42" s="35" t="s">
-        <v>449</v>
-      </c>
-      <c r="Q42" s="35"/>
-      <c r="R42" s="35"/>
-      <c r="S42" s="35"/>
-      <c r="T42" s="35" t="s">
+      <c r="P60" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="Q60" s="36"/>
+      <c r="R60" s="36"/>
+      <c r="S60" s="36"/>
+      <c r="T60" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="U42" s="41" t="s">
+      <c r="U60" s="42" t="s">
         <v>155</v>
       </c>
-      <c r="V42" s="41"/>
-      <c r="W42" s="41"/>
-      <c r="X42" s="39" t="s">
+      <c r="V60" s="42"/>
+      <c r="W60" s="42"/>
+      <c r="X60" s="40" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="43" customFormat="1" ht="148.5" spans="1:24">
-      <c r="A43" s="19"/>
-      <c r="B43" s="31"/>
-      <c r="C43" s="32" t="s">
-        <v>450</v>
-      </c>
-      <c r="D43" s="43" t="s">
-        <v>451</v>
-      </c>
-      <c r="E43" s="32"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="33" t="s">
+    <row r="61" customFormat="1" ht="148.5" spans="1:24">
+      <c r="A61" s="20"/>
+      <c r="B61" s="32"/>
+      <c r="C61" s="33" t="s">
+        <v>457</v>
+      </c>
+      <c r="D61" s="44" t="s">
+        <v>458</v>
+      </c>
+      <c r="E61" s="33"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="38" t="s">
+      <c r="H61" s="34"/>
+      <c r="I61" s="34"/>
+      <c r="J61" s="34"/>
+      <c r="K61" s="34"/>
+      <c r="L61" s="39" t="s">
         <v>211</v>
       </c>
-      <c r="M43" s="38"/>
-      <c r="N43" s="38"/>
-      <c r="O43" s="35" t="s">
+      <c r="M61" s="39"/>
+      <c r="N61" s="39"/>
+      <c r="O61" s="36" t="s">
         <v>226</v>
       </c>
-      <c r="P43" s="35" t="s">
+      <c r="P61" s="36" t="s">
         <v>249</v>
       </c>
-      <c r="Q43" s="35"/>
-      <c r="R43" s="35" t="s">
+      <c r="Q61" s="36"/>
+      <c r="R61" s="36" t="s">
         <v>269</v>
       </c>
-      <c r="S43" s="35"/>
-      <c r="T43" s="35" t="s">
+      <c r="S61" s="36"/>
+      <c r="T61" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="U43" s="33" t="s">
+      <c r="U61" s="34" t="s">
         <v>315</v>
       </c>
-      <c r="V43" s="33"/>
-      <c r="W43" s="33"/>
-      <c r="X43" s="39" t="s">
+      <c r="V61" s="34"/>
+      <c r="W61" s="34"/>
+      <c r="X61" s="40" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="54" spans="1:24">
-      <c r="A44" s="19"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="32" t="s">
-        <v>452</v>
-      </c>
-      <c r="D44" s="43" t="s">
-        <v>453</v>
-      </c>
-      <c r="E44" s="32"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="33" t="s">
+    <row r="62" customFormat="1" ht="54" spans="1:24">
+      <c r="A62" s="20"/>
+      <c r="B62" s="32"/>
+      <c r="C62" s="33" t="s">
+        <v>459</v>
+      </c>
+      <c r="D62" s="44" t="s">
+        <v>460</v>
+      </c>
+      <c r="E62" s="33"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="H44" s="33"/>
-      <c r="I44" s="33"/>
-      <c r="J44" s="33"/>
-      <c r="K44" s="33"/>
-      <c r="L44" s="38"/>
-      <c r="M44" s="38"/>
-      <c r="N44" s="38"/>
-      <c r="O44" s="35"/>
-      <c r="P44" s="35"/>
-      <c r="Q44" s="35"/>
-      <c r="R44" s="35"/>
-      <c r="S44" s="35"/>
-      <c r="T44" s="35"/>
-      <c r="U44" s="33" t="s">
+      <c r="H62" s="34"/>
+      <c r="I62" s="34"/>
+      <c r="J62" s="34"/>
+      <c r="K62" s="34"/>
+      <c r="L62" s="39"/>
+      <c r="M62" s="39"/>
+      <c r="N62" s="39"/>
+      <c r="O62" s="36"/>
+      <c r="P62" s="36"/>
+      <c r="Q62" s="36"/>
+      <c r="R62" s="36"/>
+      <c r="S62" s="36"/>
+      <c r="T62" s="36"/>
+      <c r="U62" s="34" t="s">
         <v>315</v>
       </c>
-      <c r="V44" s="33"/>
-      <c r="W44" s="33"/>
-      <c r="X44" s="37"/>
+      <c r="V62" s="34"/>
+      <c r="W62" s="34"/>
+      <c r="X62" s="38"/>
     </row>
-    <row r="45" s="14" customFormat="1" ht="95.25" spans="1:24">
-      <c r="A45" s="19"/>
-      <c r="B45" s="31"/>
-      <c r="C45" s="32" t="s">
-        <v>454</v>
-      </c>
-      <c r="D45" s="43" t="s">
-        <v>455</v>
-      </c>
-      <c r="E45" s="32"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="33" t="s">
+    <row r="63" s="14" customFormat="1" ht="95.25" spans="1:24">
+      <c r="A63" s="20"/>
+      <c r="B63" s="32"/>
+      <c r="C63" s="33" t="s">
+        <v>461</v>
+      </c>
+      <c r="D63" s="44" t="s">
+        <v>462</v>
+      </c>
+      <c r="E63" s="33"/>
+      <c r="F63" s="7"/>
+      <c r="G63" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="H45" s="33"/>
-      <c r="I45" s="33"/>
-      <c r="J45" s="33"/>
-      <c r="K45" s="33"/>
-      <c r="L45" s="38" t="s">
+      <c r="H63" s="34"/>
+      <c r="I63" s="34"/>
+      <c r="J63" s="34"/>
+      <c r="K63" s="34"/>
+      <c r="L63" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="M45" s="38"/>
-      <c r="N45" s="38"/>
-      <c r="O45" s="35"/>
-      <c r="P45" s="35" t="s">
+      <c r="M63" s="39"/>
+      <c r="N63" s="39"/>
+      <c r="O63" s="36"/>
+      <c r="P63" s="36" t="s">
         <v>250</v>
       </c>
-      <c r="Q45" s="35"/>
-      <c r="R45" s="35"/>
-      <c r="S45" s="35"/>
-      <c r="T45" s="35"/>
-      <c r="U45" s="33" t="s">
+      <c r="Q63" s="36"/>
+      <c r="R63" s="36"/>
+      <c r="S63" s="36"/>
+      <c r="T63" s="36"/>
+      <c r="U63" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="V45" s="33"/>
-      <c r="W45" s="33"/>
-      <c r="X45" s="37"/>
+      <c r="V63" s="34"/>
+      <c r="W63" s="34"/>
+      <c r="X63" s="38"/>
     </row>
-    <row r="46" s="13" customFormat="1" ht="121.5" spans="1:24">
-      <c r="A46" s="30" t="s">
-        <v>456</v>
-      </c>
-      <c r="B46" s="31" t="s">
-        <v>457</v>
-      </c>
-      <c r="C46" s="32" t="s">
-        <v>458</v>
-      </c>
-      <c r="D46" s="43" t="s">
-        <v>459</v>
-      </c>
-      <c r="E46" s="32"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="33" t="s">
+    <row r="64" s="13" customFormat="1" ht="121.5" spans="1:24">
+      <c r="A64" s="31" t="s">
+        <v>463</v>
+      </c>
+      <c r="B64" s="32" t="s">
+        <v>464</v>
+      </c>
+      <c r="C64" s="33" t="s">
+        <v>465</v>
+      </c>
+      <c r="D64" s="44" t="s">
+        <v>466</v>
+      </c>
+      <c r="E64" s="33"/>
+      <c r="F64" s="7"/>
+      <c r="G64" s="34" t="s">
         <v>166</v>
       </c>
-      <c r="H46" s="33"/>
-      <c r="I46" s="33"/>
-      <c r="J46" s="33"/>
-      <c r="K46" s="33"/>
-      <c r="L46" s="38" t="s">
+      <c r="H64" s="34"/>
+      <c r="I64" s="34"/>
+      <c r="J64" s="34"/>
+      <c r="K64" s="34"/>
+      <c r="L64" s="39" t="s">
         <v>213</v>
       </c>
-      <c r="M46" s="38"/>
-      <c r="N46" s="38"/>
-      <c r="O46" s="35" t="s">
+      <c r="M64" s="39"/>
+      <c r="N64" s="39"/>
+      <c r="O64" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="P46" s="35" t="s">
+      <c r="P64" s="36" t="s">
         <v>251</v>
       </c>
-      <c r="Q46" s="35"/>
-      <c r="R46" s="35"/>
-      <c r="S46" s="35"/>
-      <c r="T46" s="35"/>
-      <c r="U46" s="33" t="s">
+      <c r="Q64" s="36"/>
+      <c r="R64" s="36"/>
+      <c r="S64" s="36"/>
+      <c r="T64" s="36"/>
+      <c r="U64" s="34" t="s">
         <v>320</v>
       </c>
-      <c r="V46" s="33"/>
-      <c r="W46" s="33"/>
-      <c r="X46" s="37"/>
+      <c r="V64" s="34"/>
+      <c r="W64" s="34"/>
+      <c r="X64" s="38"/>
     </row>
-    <row r="47" customFormat="1" ht="40.5" spans="1:24">
-      <c r="A47" s="19"/>
-      <c r="B47" s="31"/>
-      <c r="C47" s="32" t="s">
-        <v>460</v>
-      </c>
-      <c r="D47" s="43" t="s">
-        <v>461</v>
-      </c>
-      <c r="E47" s="32"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="33" t="s">
+    <row r="65" customFormat="1" ht="40.5" spans="1:24">
+      <c r="A65" s="20"/>
+      <c r="B65" s="32"/>
+      <c r="C65" s="33" t="s">
+        <v>467</v>
+      </c>
+      <c r="D65" s="44" t="s">
+        <v>468</v>
+      </c>
+      <c r="E65" s="33"/>
+      <c r="F65" s="7"/>
+      <c r="G65" s="34" t="s">
         <v>167</v>
       </c>
-      <c r="H47" s="33"/>
-      <c r="I47" s="33"/>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="38" t="s">
+      <c r="H65" s="34"/>
+      <c r="I65" s="34"/>
+      <c r="J65" s="34"/>
+      <c r="K65" s="34"/>
+      <c r="L65" s="39" t="s">
         <v>214</v>
       </c>
-      <c r="M47" s="38"/>
-      <c r="N47" s="38"/>
-      <c r="O47" s="35"/>
-      <c r="P47" s="35" t="s">
+      <c r="M65" s="39"/>
+      <c r="N65" s="39"/>
+      <c r="O65" s="36"/>
+      <c r="P65" s="36" t="s">
         <v>252</v>
       </c>
-      <c r="Q47" s="35"/>
-      <c r="R47" s="35"/>
-      <c r="S47" s="35"/>
-      <c r="T47" s="35" t="s">
+      <c r="Q65" s="36"/>
+      <c r="R65" s="36"/>
+      <c r="S65" s="36"/>
+      <c r="T65" s="36" t="s">
         <v>277</v>
       </c>
-      <c r="U47" s="33" t="s">
+      <c r="U65" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="V47" s="33"/>
-      <c r="W47" s="33"/>
-      <c r="X47" s="37"/>
+      <c r="V65" s="34"/>
+      <c r="W65" s="34"/>
+      <c r="X65" s="38"/>
     </row>
-    <row r="48" s="14" customFormat="1" ht="95.25" spans="1:24">
-      <c r="A48" s="19"/>
-      <c r="B48" s="31"/>
-      <c r="C48" s="32" t="s">
-        <v>462</v>
-      </c>
-      <c r="D48" s="43" t="s">
-        <v>463</v>
-      </c>
-      <c r="E48" s="32"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="33" t="s">
+    <row r="66" s="14" customFormat="1" ht="95.25" spans="1:24">
+      <c r="A66" s="20"/>
+      <c r="B66" s="32"/>
+      <c r="C66" s="33" t="s">
+        <v>469</v>
+      </c>
+      <c r="D66" s="44" t="s">
+        <v>470</v>
+      </c>
+      <c r="E66" s="33"/>
+      <c r="F66" s="7"/>
+      <c r="G66" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="33"/>
-      <c r="L48" s="38" t="s">
+      <c r="H66" s="34"/>
+      <c r="I66" s="34"/>
+      <c r="J66" s="34"/>
+      <c r="K66" s="34"/>
+      <c r="L66" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="M48" s="38"/>
-      <c r="N48" s="38"/>
-      <c r="O48" s="35"/>
-      <c r="P48" s="35" t="s">
+      <c r="M66" s="39"/>
+      <c r="N66" s="39"/>
+      <c r="O66" s="36"/>
+      <c r="P66" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="Q48" s="35"/>
-      <c r="R48" s="35"/>
-      <c r="S48" s="35"/>
-      <c r="T48" s="35"/>
-      <c r="U48" s="33" t="s">
+      <c r="Q66" s="36"/>
+      <c r="R66" s="36"/>
+      <c r="S66" s="36"/>
+      <c r="T66" s="36"/>
+      <c r="U66" s="34" t="s">
         <v>322</v>
       </c>
-      <c r="V48" s="33"/>
-      <c r="W48" s="33"/>
-      <c r="X48" s="37"/>
+      <c r="V66" s="34"/>
+      <c r="W66" s="34"/>
+      <c r="X66" s="38"/>
     </row>
-    <row r="49" s="13" customFormat="1" ht="148.5" spans="1:24">
-      <c r="A49" s="30" t="s">
-        <v>464</v>
-      </c>
-      <c r="B49" s="31" t="s">
-        <v>465</v>
-      </c>
-      <c r="C49" s="32" t="s">
-        <v>466</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>467</v>
-      </c>
-      <c r="E49" s="32"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="33" t="s">
+    <row r="67" s="13" customFormat="1" ht="148.5" spans="1:24">
+      <c r="A67" s="31" t="s">
+        <v>471</v>
+      </c>
+      <c r="B67" s="32" t="s">
+        <v>472</v>
+      </c>
+      <c r="C67" s="33" t="s">
+        <v>473</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>474</v>
+      </c>
+      <c r="E67" s="33"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="34" t="s">
         <v>169</v>
       </c>
-      <c r="H49" s="33"/>
-      <c r="I49" s="33"/>
-      <c r="J49" s="33"/>
-      <c r="K49" s="33"/>
-      <c r="L49" s="38"/>
-      <c r="M49" s="38"/>
-      <c r="N49" s="38"/>
-      <c r="O49" s="35" t="s">
+      <c r="H67" s="34"/>
+      <c r="I67" s="34"/>
+      <c r="J67" s="34"/>
+      <c r="K67" s="34"/>
+      <c r="L67" s="39"/>
+      <c r="M67" s="39"/>
+      <c r="N67" s="39"/>
+      <c r="O67" s="36" t="s">
         <v>228</v>
       </c>
-      <c r="P49" s="35" t="s">
+      <c r="P67" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="Q49" s="35" t="s">
+      <c r="Q67" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="R49" s="35"/>
-      <c r="S49" s="35"/>
-      <c r="T49" s="35"/>
-      <c r="U49" s="33" t="s">
+      <c r="R67" s="36"/>
+      <c r="S67" s="36"/>
+      <c r="T67" s="36"/>
+      <c r="U67" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="V49" s="33"/>
-      <c r="W49" s="33"/>
-      <c r="X49" s="37"/>
+      <c r="V67" s="34"/>
+      <c r="W67" s="34"/>
+      <c r="X67" s="38"/>
     </row>
-    <row r="50" customFormat="1" ht="81" spans="1:24">
-      <c r="A50" s="19"/>
-      <c r="B50" s="31"/>
-      <c r="C50" s="32" t="s">
-        <v>468</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>469</v>
-      </c>
-      <c r="E50" s="32"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="33" t="s">
+    <row r="68" customFormat="1" ht="81" spans="1:24">
+      <c r="A68" s="20"/>
+      <c r="B68" s="32"/>
+      <c r="C68" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="E68" s="33"/>
+      <c r="F68" s="7"/>
+      <c r="G68" s="34" t="s">
         <v>159</v>
       </c>
-      <c r="H50" s="33"/>
-      <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="33"/>
-      <c r="L50" s="38"/>
-      <c r="M50" s="38"/>
-      <c r="N50" s="38"/>
-      <c r="O50" s="35"/>
-      <c r="P50" s="35" t="s">
+      <c r="H68" s="34"/>
+      <c r="I68" s="34"/>
+      <c r="J68" s="34"/>
+      <c r="K68" s="34"/>
+      <c r="L68" s="39"/>
+      <c r="M68" s="39"/>
+      <c r="N68" s="39"/>
+      <c r="O68" s="36"/>
+      <c r="P68" s="36" t="s">
         <v>255</v>
       </c>
-      <c r="Q50" s="35" t="s">
+      <c r="Q68" s="36" t="s">
         <v>266</v>
       </c>
-      <c r="R50" s="35"/>
-      <c r="S50" s="35"/>
-      <c r="T50" s="35"/>
-      <c r="U50" s="33" t="s">
+      <c r="R68" s="36"/>
+      <c r="S68" s="36"/>
+      <c r="T68" s="36"/>
+      <c r="U68" s="34" t="s">
         <v>324</v>
       </c>
-      <c r="V50" s="33"/>
-      <c r="W50" s="33"/>
-      <c r="X50" s="37"/>
+      <c r="V68" s="34"/>
+      <c r="W68" s="34"/>
+      <c r="X68" s="38"/>
     </row>
-    <row r="51" customFormat="1" ht="94.5" spans="1:24">
-      <c r="A51" s="19"/>
-      <c r="B51" s="31"/>
-      <c r="C51" s="32" t="s">
-        <v>470</v>
-      </c>
-      <c r="D51" s="43" t="s">
-        <v>471</v>
-      </c>
-      <c r="E51" s="32"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="33" t="s">
+    <row r="69" customFormat="1" ht="94.5" spans="1:24">
+      <c r="A69" s="20"/>
+      <c r="B69" s="32"/>
+      <c r="C69" s="33" t="s">
+        <v>477</v>
+      </c>
+      <c r="D69" s="44" t="s">
+        <v>478</v>
+      </c>
+      <c r="E69" s="33"/>
+      <c r="F69" s="7"/>
+      <c r="G69" s="34" t="s">
         <v>155</v>
       </c>
-      <c r="H51" s="33"/>
-      <c r="I51" s="33"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="33"/>
-      <c r="L51" s="38" t="s">
-        <v>472</v>
-      </c>
-      <c r="M51" s="38"/>
-      <c r="N51" s="38"/>
-      <c r="O51" s="35"/>
-      <c r="P51" s="35"/>
-      <c r="Q51" s="35"/>
-      <c r="R51" s="35"/>
-      <c r="S51" s="35"/>
-      <c r="T51" s="35" t="s">
+      <c r="H69" s="34"/>
+      <c r="I69" s="34"/>
+      <c r="J69" s="34"/>
+      <c r="K69" s="34"/>
+      <c r="L69" s="39" t="s">
+        <v>479</v>
+      </c>
+      <c r="M69" s="39"/>
+      <c r="N69" s="39"/>
+      <c r="O69" s="36"/>
+      <c r="P69" s="36"/>
+      <c r="Q69" s="36"/>
+      <c r="R69" s="36"/>
+      <c r="S69" s="36"/>
+      <c r="T69" s="36" t="s">
         <v>282</v>
       </c>
-      <c r="U51" s="33" t="s">
+      <c r="U69" s="34" t="s">
         <v>315</v>
       </c>
-      <c r="V51" s="33"/>
-      <c r="W51" s="33"/>
-      <c r="X51" s="37"/>
+      <c r="V69" s="34"/>
+      <c r="W69" s="34"/>
+      <c r="X69" s="38"/>
     </row>
-    <row r="52" s="14" customFormat="1" ht="68.25" spans="1:24">
-      <c r="A52" s="44"/>
-      <c r="B52" s="45"/>
-      <c r="C52" s="46" t="s">
-        <v>473</v>
-      </c>
-      <c r="D52" s="47" t="s">
-        <v>474</v>
-      </c>
-      <c r="E52" s="46"/>
-      <c r="F52" s="48"/>
-      <c r="G52" s="49" t="s">
+    <row r="70" s="14" customFormat="1" ht="68.25" spans="1:24">
+      <c r="A70" s="45"/>
+      <c r="B70" s="46"/>
+      <c r="C70" s="47" t="s">
+        <v>480</v>
+      </c>
+      <c r="D70" s="48" t="s">
+        <v>481</v>
+      </c>
+      <c r="E70" s="47"/>
+      <c r="F70" s="49"/>
+      <c r="G70" s="50" t="s">
         <v>155</v>
       </c>
-      <c r="H52" s="49"/>
-      <c r="I52" s="49"/>
-      <c r="J52" s="49"/>
-      <c r="K52" s="49"/>
-      <c r="L52" s="50"/>
-      <c r="M52" s="50"/>
-      <c r="N52" s="50"/>
-      <c r="O52" s="51"/>
-      <c r="P52" s="51" t="s">
+      <c r="H70" s="50"/>
+      <c r="I70" s="50"/>
+      <c r="J70" s="50"/>
+      <c r="K70" s="50"/>
+      <c r="L70" s="51"/>
+      <c r="M70" s="51"/>
+      <c r="N70" s="51"/>
+      <c r="O70" s="52"/>
+      <c r="P70" s="52" t="s">
         <v>256</v>
       </c>
-      <c r="Q52" s="51" t="s">
+      <c r="Q70" s="52" t="s">
         <v>263</v>
       </c>
-      <c r="R52" s="51" t="s">
+      <c r="R70" s="52" t="s">
         <v>270</v>
       </c>
-      <c r="S52" s="51"/>
-      <c r="T52" s="51" t="s">
+      <c r="S70" s="52"/>
+      <c r="T70" s="52" t="s">
         <v>283</v>
       </c>
-      <c r="U52" s="49" t="s">
+      <c r="U70" s="50" t="s">
         <v>155</v>
       </c>
-      <c r="V52" s="49"/>
-      <c r="W52" s="49"/>
-      <c r="X52" s="52"/>
+      <c r="V70" s="50"/>
+      <c r="W70" s="50"/>
+      <c r="X70" s="53"/>
     </row>
   </sheetData>
-  <mergeCells count="179">
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:T1"/>
-    <mergeCell ref="U1:X1"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:T2"/>
-    <mergeCell ref="V2:X2"/>
-    <mergeCell ref="G4:K4"/>
-    <mergeCell ref="L4:N4"/>
-    <mergeCell ref="U4:X4"/>
-    <mergeCell ref="G5:K5"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="U5:X5"/>
-    <mergeCell ref="G6:K6"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="U6:X6"/>
-    <mergeCell ref="G7:K7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="U7:X7"/>
-    <mergeCell ref="G8:K8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="U8:W8"/>
-    <mergeCell ref="G9:K9"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="U9:X9"/>
-    <mergeCell ref="G10:K10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="U10:X10"/>
-    <mergeCell ref="G11:K11"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="U11:X11"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="U12:X12"/>
-    <mergeCell ref="G13:J13"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="U13:X13"/>
-    <mergeCell ref="G14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="U14:W14"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="U15:W15"/>
-    <mergeCell ref="G16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="U16:X16"/>
-    <mergeCell ref="G17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="U17:X17"/>
-    <mergeCell ref="G18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="U18:X18"/>
+  <mergeCells count="180">
+    <mergeCell ref="A18:K18"/>
     <mergeCell ref="G19:K19"/>
-    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L19:T19"/>
     <mergeCell ref="U19:X19"/>
-    <mergeCell ref="G20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="U20:X20"/>
-    <mergeCell ref="G21:K21"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="U21:X21"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="L20:T20"/>
+    <mergeCell ref="V20:X20"/>
     <mergeCell ref="G22:K22"/>
     <mergeCell ref="L22:N22"/>
     <mergeCell ref="U22:X22"/>
@@ -10616,28 +10658,28 @@
     <mergeCell ref="U25:X25"/>
     <mergeCell ref="G26:K26"/>
     <mergeCell ref="L26:N26"/>
-    <mergeCell ref="U26:X26"/>
+    <mergeCell ref="U26:W26"/>
     <mergeCell ref="G27:K27"/>
     <mergeCell ref="L27:N27"/>
     <mergeCell ref="U27:X27"/>
-    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="G28:K28"/>
     <mergeCell ref="L28:N28"/>
     <mergeCell ref="U28:X28"/>
     <mergeCell ref="G29:K29"/>
     <mergeCell ref="L29:N29"/>
     <mergeCell ref="U29:X29"/>
-    <mergeCell ref="G30:K30"/>
+    <mergeCell ref="G30:I30"/>
     <mergeCell ref="L30:N30"/>
     <mergeCell ref="U30:X30"/>
-    <mergeCell ref="G31:K31"/>
+    <mergeCell ref="G31:J31"/>
     <mergeCell ref="L31:N31"/>
     <mergeCell ref="U31:X31"/>
     <mergeCell ref="G32:K32"/>
     <mergeCell ref="L32:N32"/>
-    <mergeCell ref="U32:X32"/>
-    <mergeCell ref="G33:K33"/>
+    <mergeCell ref="U32:W32"/>
+    <mergeCell ref="G33:I33"/>
     <mergeCell ref="L33:N33"/>
-    <mergeCell ref="U33:X33"/>
+    <mergeCell ref="U33:W33"/>
     <mergeCell ref="G34:K34"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="U34:X34"/>
@@ -10647,7 +10689,7 @@
     <mergeCell ref="G36:K36"/>
     <mergeCell ref="L36:N36"/>
     <mergeCell ref="U36:X36"/>
-    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="G37:K37"/>
     <mergeCell ref="L37:N37"/>
     <mergeCell ref="U37:X37"/>
     <mergeCell ref="G38:K38"/>
@@ -10664,17 +10706,17 @@
     <mergeCell ref="U41:X41"/>
     <mergeCell ref="G42:K42"/>
     <mergeCell ref="L42:N42"/>
-    <mergeCell ref="U42:W42"/>
+    <mergeCell ref="U42:X42"/>
     <mergeCell ref="G43:K43"/>
     <mergeCell ref="L43:N43"/>
-    <mergeCell ref="U43:W43"/>
+    <mergeCell ref="U43:X43"/>
     <mergeCell ref="G44:K44"/>
     <mergeCell ref="L44:N44"/>
     <mergeCell ref="U44:X44"/>
     <mergeCell ref="G45:K45"/>
     <mergeCell ref="L45:N45"/>
     <mergeCell ref="U45:X45"/>
-    <mergeCell ref="G46:K46"/>
+    <mergeCell ref="G46:J46"/>
     <mergeCell ref="L46:N46"/>
     <mergeCell ref="U46:X46"/>
     <mergeCell ref="G47:K47"/>
@@ -10695,35 +10737,90 @@
     <mergeCell ref="G52:K52"/>
     <mergeCell ref="L52:N52"/>
     <mergeCell ref="U52:X52"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="A4:A10"/>
-    <mergeCell ref="A11:A16"/>
-    <mergeCell ref="A17:A22"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A27:A29"/>
-    <mergeCell ref="A30:A35"/>
-    <mergeCell ref="A36:A38"/>
-    <mergeCell ref="A39:A45"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="A49:A52"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="B4:B10"/>
-    <mergeCell ref="B11:B16"/>
-    <mergeCell ref="B17:B22"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="B30:B35"/>
-    <mergeCell ref="B36:B38"/>
-    <mergeCell ref="B39:B45"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="B49:B52"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:F3"/>
+    <mergeCell ref="G53:K53"/>
+    <mergeCell ref="L53:N53"/>
+    <mergeCell ref="U53:X53"/>
+    <mergeCell ref="G54:K54"/>
+    <mergeCell ref="L54:N54"/>
+    <mergeCell ref="U54:X54"/>
+    <mergeCell ref="G55:J55"/>
+    <mergeCell ref="L55:N55"/>
+    <mergeCell ref="U55:X55"/>
+    <mergeCell ref="G56:K56"/>
+    <mergeCell ref="L56:N56"/>
+    <mergeCell ref="U56:X56"/>
+    <mergeCell ref="G57:K57"/>
+    <mergeCell ref="L57:N57"/>
+    <mergeCell ref="U57:X57"/>
+    <mergeCell ref="G58:K58"/>
+    <mergeCell ref="L58:N58"/>
+    <mergeCell ref="U58:X58"/>
+    <mergeCell ref="G59:K59"/>
+    <mergeCell ref="L59:N59"/>
+    <mergeCell ref="U59:X59"/>
+    <mergeCell ref="G60:K60"/>
+    <mergeCell ref="L60:N60"/>
+    <mergeCell ref="U60:W60"/>
+    <mergeCell ref="G61:K61"/>
+    <mergeCell ref="L61:N61"/>
+    <mergeCell ref="U61:W61"/>
+    <mergeCell ref="G62:K62"/>
+    <mergeCell ref="L62:N62"/>
+    <mergeCell ref="U62:X62"/>
+    <mergeCell ref="G63:K63"/>
+    <mergeCell ref="L63:N63"/>
+    <mergeCell ref="U63:X63"/>
+    <mergeCell ref="G64:K64"/>
+    <mergeCell ref="L64:N64"/>
+    <mergeCell ref="U64:X64"/>
+    <mergeCell ref="G65:K65"/>
+    <mergeCell ref="L65:N65"/>
+    <mergeCell ref="U65:X65"/>
+    <mergeCell ref="G66:K66"/>
+    <mergeCell ref="L66:N66"/>
+    <mergeCell ref="U66:X66"/>
+    <mergeCell ref="G67:K67"/>
+    <mergeCell ref="L67:N67"/>
+    <mergeCell ref="U67:X67"/>
+    <mergeCell ref="G68:K68"/>
+    <mergeCell ref="L68:N68"/>
+    <mergeCell ref="U68:X68"/>
+    <mergeCell ref="G69:K69"/>
+    <mergeCell ref="L69:N69"/>
+    <mergeCell ref="U69:X69"/>
+    <mergeCell ref="G70:K70"/>
+    <mergeCell ref="L70:N70"/>
+    <mergeCell ref="U70:X70"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A22:A28"/>
+    <mergeCell ref="A29:A34"/>
+    <mergeCell ref="A35:A40"/>
+    <mergeCell ref="A41:A44"/>
+    <mergeCell ref="A45:A47"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="A54:A56"/>
+    <mergeCell ref="A57:A63"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="A67:A70"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="B22:B28"/>
+    <mergeCell ref="B29:B34"/>
+    <mergeCell ref="B35:B40"/>
+    <mergeCell ref="B41:B44"/>
+    <mergeCell ref="B45:B47"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="B54:B56"/>
+    <mergeCell ref="B57:B63"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="B67:B70"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="E19:E21"/>
+    <mergeCell ref="F19:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -10763,138 +10860,138 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="9" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="9"/>
       <c r="B2" s="9"/>
       <c r="C2" s="7" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="9"/>
       <c r="B3" s="9"/>
       <c r="C3" s="7" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
     </row>
     <row r="4" ht="94.5" spans="1:4">
       <c r="A4" s="9"/>
       <c r="B4" s="9"/>
       <c r="C4" s="5" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
     </row>
     <row r="5" ht="27" spans="1:4">
       <c r="A5" s="7" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="7" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="7" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="10" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:4">
       <c r="A9" s="11"/>
       <c r="B9" s="11"/>
       <c r="C9" s="7" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="11"/>
       <c r="B10" s="11"/>
       <c r="C10" s="7" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
     </row>
     <row r="11" ht="40.5" spans="1:4">
       <c r="A11" s="11"/>
       <c r="B11" s="11"/>
       <c r="C11" s="7" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
     </row>
     <row r="12" ht="27" spans="1:4">
       <c r="A12" s="12"/>
       <c r="B12" s="12"/>
       <c r="C12" s="7" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>
@@ -10922,7 +11019,7 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="2"/>
@@ -10930,31 +11027,31 @@
     <row r="2" spans="1:3">
       <c r="A2" s="3"/>
       <c r="B2" s="4" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="6"/>
       <c r="B3" s="4"/>
       <c r="C3" s="5" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6"/>
       <c r="B4" s="4"/>
       <c r="C4" s="5" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="6"/>
       <c r="B5" s="4"/>
       <c r="C5" s="5" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -10965,31 +11062,31 @@
     <row r="7" spans="1:3">
       <c r="A7" s="6"/>
       <c r="B7" s="8" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="6"/>
       <c r="B8" s="4"/>
       <c r="C8" s="5" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="6"/>
       <c r="B9" s="4"/>
       <c r="C9" s="5" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" s="6"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -11000,38 +11097,38 @@
     <row r="12" spans="1:3">
       <c r="A12" s="6"/>
       <c r="B12" s="8" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="6"/>
       <c r="B13" s="4"/>
       <c r="C13" s="5" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="6"/>
       <c r="B14" s="4"/>
       <c r="C14" s="5" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="6"/>
       <c r="B15" s="4"/>
       <c r="C15" s="5" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="6"/>
       <c r="B16" s="4"/>
       <c r="C16" s="5" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -11042,31 +11139,31 @@
     <row r="18" spans="1:3">
       <c r="A18" s="6"/>
       <c r="B18" s="8" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
       <c r="C19" s="7" t="s">
-        <v>525</v>
+        <v>532</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="6"/>
       <c r="B20" s="4"/>
       <c r="C20" s="7" t="s">
-        <v>526</v>
+        <v>533</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" s="6"/>
       <c r="B21" s="4"/>
       <c r="C21" s="7" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
     </row>
   </sheetData>

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" firstSheet="2" activeTab="3"/>
+    <workbookView windowWidth="29868" windowHeight="13500" firstSheet="2" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="49过程输入输出工具-横版" sheetId="1" state="hidden" r:id="rId1"/>
@@ -17,7 +17,8 @@
     <sheet name="计算公式汇总" sheetId="4" r:id="rId8"/>
     <sheet name="背默知识汇总" sheetId="3" r:id="rId9"/>
     <sheet name="案例答题技巧" sheetId="5" r:id="rId10"/>
-    <sheet name="论文套路技巧" sheetId="6" r:id="rId11"/>
+    <sheet name="论文模板" sheetId="6" r:id="rId11"/>
+    <sheet name="论文架构" sheetId="13" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1405" uniqueCount="701">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="728">
   <si>
     <t>项目整合管理</t>
   </si>
@@ -5202,6 +5203,87 @@
   </si>
   <si>
     <t>4）物资（产品）的可用性</t>
+  </si>
+  <si>
+    <t>背景</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  为应对金融市场竞争日趋激烈与客户需求多元化的双重挑战，破解某银行营销数据分散、绩效核算粗放、资源投放精准度不足等痛点，某行规划建设智慧营销绩效管理平台。项目通过整合多源业务数据、构建标准化智能指标体系及可视化监控能力，实现营销全流程闭环管理，持续提升营销效能与精细化运营水平。平台依托大数据、人工智能、云计算、实时计算及数据可视化等新兴技术，实现营销数据统一汇聚、智能建模、绩效指标自动核算、过程实时监控与效果闭环优化，有效提升银行营销精细化管理能力与资源配置效率，为营销决策提供科学支撑。2024年3月，我司通过公开招标成功中标该项目，合同金额382.7万元（其中硬件设备费用162万元），建设周期1年。项目核心建设内容包含六大模块：统一营销数据中心、智能绩效指标体系、营销活动全流程管理体系、AI营销洞察与预测分析、可视化绩效监控大屏、营销资源与费用管控模块。中标后，公司结合我在同类项目中的丰富管理经验，任命我为项目经理，全面负责项目整体规划、落地实施推进、多方资源协调对接，以及进度与质量全程管控，确保项目目标按期保质落地。我迅速组建10人专业项目团队，成员涵盖需求分析、系统架构、开发、测试、质量保证等关键岗位，为项目顺利推进筑牢基础。</t>
+  </si>
+  <si>
+    <t>过渡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  智慧营销绩效管理平台作为破解某银行营销痛点、提升运营效能的关键项目，涵盖多模块、多资源，且建设周期固定，XXXX成为????(功能作用)、保障项目按期保质交付的核心支撑。结合本人作为项目经理的履职实践，下文将重点探讨本项目中XXXX的具体实施策略、执行过程及优化措施。</t>
+  </si>
+  <si>
+    <t>结尾</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  经过一年的攻坚建设，目前该智慧营销绩效平台已按计划顺利完成全部建设任务，如期交付使用。项目成功落地六大核心模块，实现全行8类营销相关数据统一汇聚，数据整合效率提升60%；绩效核算周期由原人工统计的7个工作日缩短至1个工作日，核算准确率达99.8%；营销资源投放精准度提升45%，营销ROI较以往提升30%，有效破解了银行营销管理痛点，显著提升了营销精细化运营水平与资源配置效率，为银行营销决策提供了科学支撑。作为该项目的项目经理，全程主导项目规划、实施与管控的经历，让我收获颇丰。我深刻体会到，金融科技项目的成功落地，离不开项目团队的高效协作、精准的需求把控与严谨的过程管理。同时，也认识到新兴技术与金融业务深度融合的重要性，未来我将总结本次项目经验，弥补工作中的不足，提升自身项目管理能力，为金融科技领域的高质量发展贡献更多力量。</t>
+  </si>
+  <si>
+    <t>架构一定要清晰，不必拘泥老师的架构</t>
+  </si>
+  <si>
+    <t>套路</t>
+  </si>
+  <si>
+    <t>优点</t>
+  </si>
+  <si>
+    <t>缺点</t>
+  </si>
+  <si>
+    <t>架构类型</t>
+  </si>
+  <si>
+    <t>传统架构</t>
+  </si>
+  <si>
+    <t>小标题就是每个管理下的几个过程</t>
+  </si>
+  <si>
+    <t>凑字数，怼脸不好写的时候采用传统架构写</t>
+  </si>
+  <si>
+    <t>不清晰，已淘汰</t>
+  </si>
+  <si>
+    <t>怼脸架构</t>
+  </si>
+  <si>
+    <t>按题目要求分类，几个问题，小标题就分几个</t>
+  </si>
+  <si>
+    <t>清晰通过率高</t>
+  </si>
+  <si>
+    <t>PDCA架构</t>
+  </si>
+  <si>
+    <t>小标题按：启动过程组，规划过程组，执行过程组，监控过程组，收尾过程组</t>
+  </si>
+  <si>
+    <t>少见，不如传统</t>
+  </si>
+  <si>
+    <t>小标题中的小标题，要合理利用表格，但是表格字数不好凑，不用表格的话可以凑字数</t>
+  </si>
+  <si>
+    <t>架构梳理清楚，内容写上，想不过都难</t>
+  </si>
+  <si>
+    <t>举例可以凑字数</t>
+  </si>
+  <si>
+    <t>如何凑字数：3+1  重要性+表格直接回答子题目，列出各个过程定义作用+分别列出子子标题举例描述凑字数(2+1，2个过程1个其他)</t>
+  </si>
+  <si>
+    <t>表格写全，然后单独把子过程写出来举例，然后凑字数 2+1或3+1</t>
+  </si>
+  <si>
+    <t>成也架构败也架构</t>
   </si>
 </sst>
 </file>
@@ -5687,19 +5769,19 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="medium">
         <color auto="1"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="medium">
+      <top/>
+      <bottom style="medium">
         <color auto="1"/>
-      </top>
-      <bottom/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -6140,6 +6222,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -6182,9 +6270,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -6319,9 +6404,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -6546,8 +6628,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2794000" y="17536795"/>
-          <a:ext cx="5043805" cy="2710815"/>
+          <a:off x="2514600" y="18816955"/>
+          <a:ext cx="4562475" cy="2905125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6593,8 +6675,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9525" y="3952875"/>
-          <a:ext cx="6991985" cy="7565390"/>
+          <a:off x="9525" y="4215765"/>
+          <a:ext cx="6306185" cy="8068310"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6632,7 +6714,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9525" y="9525"/>
-          <a:ext cx="6922770" cy="3825240"/>
+          <a:ext cx="6236970" cy="4076700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6899,49 +6981,49 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AY27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.1083333333333" customWidth="1"/>
-    <col min="2" max="2" width="22.5583333333333" customWidth="1"/>
-    <col min="3" max="3" width="29.3833333333333" customWidth="1"/>
+    <col min="1" max="1" width="14.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="22.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="29.3796296296296" customWidth="1"/>
     <col min="4" max="4" width="33.75" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="28.1333333333333" customWidth="1"/>
-    <col min="7" max="7" width="29.3833333333333" customWidth="1"/>
+    <col min="6" max="6" width="28.1296296296296" customWidth="1"/>
+    <col min="7" max="7" width="29.3796296296296" customWidth="1"/>
     <col min="8" max="8" width="33.75" customWidth="1"/>
     <col min="9" max="9" width="31.5" customWidth="1"/>
-    <col min="10" max="10" width="29.3833333333333" customWidth="1"/>
-    <col min="11" max="12" width="24.8833333333333" customWidth="1"/>
-    <col min="13" max="13" width="24.1333333333333" customWidth="1"/>
-    <col min="14" max="15" width="24.8833333333333" customWidth="1"/>
-    <col min="16" max="16" width="29.3833333333333" customWidth="1"/>
-    <col min="17" max="17" width="24.8833333333333" customWidth="1"/>
-    <col min="18" max="18" width="29.3833333333333" customWidth="1"/>
+    <col min="10" max="10" width="29.3796296296296" customWidth="1"/>
+    <col min="11" max="12" width="24.8796296296296" customWidth="1"/>
+    <col min="13" max="13" width="24.1296296296296" customWidth="1"/>
+    <col min="14" max="15" width="24.8796296296296" customWidth="1"/>
+    <col min="16" max="16" width="29.3796296296296" customWidth="1"/>
+    <col min="17" max="17" width="24.8796296296296" customWidth="1"/>
+    <col min="18" max="18" width="29.3796296296296" customWidth="1"/>
     <col min="19" max="19" width="32.5" customWidth="1"/>
-    <col min="20" max="20" width="29.3833333333333" customWidth="1"/>
-    <col min="21" max="21" width="24.8833333333333" customWidth="1"/>
-    <col min="22" max="22" width="29.3833333333333" customWidth="1"/>
-    <col min="23" max="25" width="24.8833333333333" customWidth="1"/>
-    <col min="26" max="26" width="29.3833333333333" customWidth="1"/>
-    <col min="27" max="28" width="24.8833333333333" customWidth="1"/>
-    <col min="29" max="30" width="29.3833333333333" customWidth="1"/>
-    <col min="31" max="34" width="24.8833333333333" customWidth="1"/>
-    <col min="35" max="35" width="29.3833333333333" customWidth="1"/>
-    <col min="36" max="37" width="24.8833333333333" customWidth="1"/>
-    <col min="38" max="38" width="29.3833333333333" customWidth="1"/>
-    <col min="39" max="39" width="24.8833333333333" customWidth="1"/>
+    <col min="20" max="20" width="29.3796296296296" customWidth="1"/>
+    <col min="21" max="21" width="24.8796296296296" customWidth="1"/>
+    <col min="22" max="22" width="29.3796296296296" customWidth="1"/>
+    <col min="23" max="25" width="24.8796296296296" customWidth="1"/>
+    <col min="26" max="26" width="29.3796296296296" customWidth="1"/>
+    <col min="27" max="28" width="24.8796296296296" customWidth="1"/>
+    <col min="29" max="30" width="29.3796296296296" customWidth="1"/>
+    <col min="31" max="34" width="24.8796296296296" customWidth="1"/>
+    <col min="35" max="35" width="29.3796296296296" customWidth="1"/>
+    <col min="36" max="37" width="24.8796296296296" customWidth="1"/>
+    <col min="38" max="38" width="29.3796296296296" customWidth="1"/>
+    <col min="39" max="39" width="24.8796296296296" customWidth="1"/>
     <col min="40" max="41" width="33.75" customWidth="1"/>
-    <col min="42" max="43" width="29.3833333333333" customWidth="1"/>
-    <col min="44" max="44" width="24.8833333333333" customWidth="1"/>
-    <col min="45" max="45" width="29.3833333333333" customWidth="1"/>
-    <col min="46" max="47" width="24.8833333333333" customWidth="1"/>
-    <col min="48" max="48" width="27.1333333333333" customWidth="1"/>
+    <col min="42" max="43" width="29.3796296296296" customWidth="1"/>
+    <col min="44" max="44" width="24.8796296296296" customWidth="1"/>
+    <col min="45" max="45" width="29.3796296296296" customWidth="1"/>
+    <col min="46" max="47" width="24.8796296296296" customWidth="1"/>
+    <col min="48" max="48" width="27.1296296296296" customWidth="1"/>
     <col min="49" max="51" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:51">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6"/>
+      <c r="A1" s="8"/>
+      <c r="B1" s="8"/>
       <c r="C1" s="67" t="s">
         <v>0</v>
       </c>
@@ -7013,8 +7095,8 @@
       <c r="AY1" s="68"/>
     </row>
     <row r="2" customFormat="1" ht="58" customHeight="1" spans="1:51">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
+      <c r="A2" s="8"/>
+      <c r="B2" s="8"/>
       <c r="C2" s="69" t="s">
         <v>10</v>
       </c>
@@ -7236,257 +7318,257 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" s="65" customFormat="1" ht="108" spans="1:51">
+    <row r="4" s="65" customFormat="1" ht="115.2" spans="1:51">
       <c r="A4" s="78"/>
       <c r="B4" s="78"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="D4" s="35" t="s">
+      <c r="D4" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="35" t="s">
+      <c r="E4" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="G4" s="35" t="s">
+      <c r="G4" s="36" t="s">
         <v>73</v>
       </c>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="I4" s="35" t="s">
+      <c r="I4" s="36" t="s">
         <v>75</v>
       </c>
-      <c r="J4" s="35" t="s">
+      <c r="J4" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="L4" s="35" t="s">
+      <c r="L4" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="N4" s="35" t="s">
+      <c r="N4" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="O4" s="35" t="s">
+      <c r="O4" s="36" t="s">
         <v>81</v>
       </c>
-      <c r="P4" s="35" t="s">
+      <c r="P4" s="36" t="s">
         <v>82</v>
       </c>
-      <c r="Q4" s="35" t="s">
+      <c r="Q4" s="36" t="s">
         <v>83</v>
       </c>
-      <c r="R4" s="35" t="s">
+      <c r="R4" s="36" t="s">
         <v>84</v>
       </c>
-      <c r="S4" s="35" t="s">
+      <c r="S4" s="36" t="s">
         <v>85</v>
       </c>
-      <c r="T4" s="35" t="s">
+      <c r="T4" s="36" t="s">
         <v>86</v>
       </c>
-      <c r="U4" s="35" t="s">
+      <c r="U4" s="36" t="s">
         <v>87</v>
       </c>
-      <c r="V4" s="35" t="s">
+      <c r="V4" s="36" t="s">
         <v>88</v>
       </c>
-      <c r="W4" s="35" t="s">
+      <c r="W4" s="36" t="s">
         <v>89</v>
       </c>
-      <c r="X4" s="35" t="s">
+      <c r="X4" s="36" t="s">
         <v>90</v>
       </c>
-      <c r="Y4" s="35" t="s">
+      <c r="Y4" s="36" t="s">
         <v>91</v>
       </c>
-      <c r="Z4" s="35" t="s">
+      <c r="Z4" s="36" t="s">
         <v>92</v>
       </c>
-      <c r="AA4" s="35" t="s">
+      <c r="AA4" s="36" t="s">
         <v>93</v>
       </c>
-      <c r="AB4" s="35" t="s">
+      <c r="AB4" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="AC4" s="35" t="s">
+      <c r="AC4" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="AD4" s="35" t="s">
+      <c r="AD4" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="AE4" s="35" t="s">
+      <c r="AE4" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="AF4" s="35" t="s">
+      <c r="AF4" s="36" t="s">
         <v>98</v>
       </c>
-      <c r="AG4" s="35" t="s">
+      <c r="AG4" s="36" t="s">
         <v>99</v>
       </c>
-      <c r="AH4" s="35" t="s">
+      <c r="AH4" s="36" t="s">
         <v>100</v>
       </c>
-      <c r="AI4" s="35" t="s">
+      <c r="AI4" s="36" t="s">
         <v>101</v>
       </c>
-      <c r="AJ4" s="35" t="s">
+      <c r="AJ4" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="AK4" s="35" t="s">
+      <c r="AK4" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="AL4" s="35" t="s">
+      <c r="AL4" s="36" t="s">
         <v>104</v>
       </c>
-      <c r="AM4" s="35" t="s">
+      <c r="AM4" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="AN4" s="35" t="s">
+      <c r="AN4" s="36" t="s">
         <v>106</v>
       </c>
-      <c r="AO4" s="35" t="s">
+      <c r="AO4" s="36" t="s">
         <v>107</v>
       </c>
-      <c r="AP4" s="35" t="s">
+      <c r="AP4" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="AQ4" s="35" t="s">
+      <c r="AQ4" s="36" t="s">
         <v>109</v>
       </c>
-      <c r="AR4" s="35" t="s">
+      <c r="AR4" s="36" t="s">
         <v>110</v>
       </c>
-      <c r="AS4" s="35" t="s">
+      <c r="AS4" s="36" t="s">
         <v>111</v>
       </c>
-      <c r="AT4" s="35" t="s">
+      <c r="AT4" s="36" t="s">
         <v>112</v>
       </c>
-      <c r="AU4" s="35" t="s">
+      <c r="AU4" s="36" t="s">
         <v>113</v>
       </c>
-      <c r="AV4" s="35" t="s">
+      <c r="AV4" s="36" t="s">
         <v>114</v>
       </c>
-      <c r="AW4" s="35" t="s">
+      <c r="AW4" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="AX4" s="35" t="s">
+      <c r="AX4" s="36" t="s">
         <v>116</v>
       </c>
-      <c r="AY4" s="35" t="s">
+      <c r="AY4" s="36" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="5" s="65" customFormat="1" ht="94.5" spans="1:51">
+    <row r="5" s="65" customFormat="1" ht="100.8" spans="1:51">
       <c r="A5" s="78"/>
       <c r="B5" s="78"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="35"/>
-      <c r="V5" s="35"/>
-      <c r="W5" s="35"/>
-      <c r="X5" s="35"/>
-      <c r="Y5" s="35"/>
-      <c r="Z5" s="35"/>
-      <c r="AA5" s="35"/>
-      <c r="AB5" s="35"/>
-      <c r="AC5" s="35" t="s">
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="36"/>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="36"/>
+      <c r="Y5" s="36"/>
+      <c r="Z5" s="36"/>
+      <c r="AA5" s="36"/>
+      <c r="AB5" s="36"/>
+      <c r="AC5" s="36" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="35" t="s">
+      <c r="AD5" s="36" t="s">
         <v>119</v>
       </c>
-      <c r="AE5" s="35" t="s">
+      <c r="AE5" s="36" t="s">
         <v>120</v>
       </c>
-      <c r="AF5" s="35" t="s">
+      <c r="AF5" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="AG5" s="35" t="s">
+      <c r="AG5" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="AH5" s="35" t="s">
+      <c r="AH5" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="AI5" s="35" t="s">
+      <c r="AI5" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="AJ5" s="35" t="s">
+      <c r="AJ5" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="AK5" s="35" t="s">
+      <c r="AK5" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="AL5" s="35" t="s">
+      <c r="AL5" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="AM5" s="35" t="s">
+      <c r="AM5" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="AN5" s="35" t="s">
+      <c r="AN5" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="AO5" s="35" t="s">
+      <c r="AO5" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="AP5" s="35" t="s">
+      <c r="AP5" s="36" t="s">
         <v>131</v>
       </c>
-      <c r="AQ5" s="35" t="s">
+      <c r="AQ5" s="36" t="s">
         <v>132</v>
       </c>
-      <c r="AR5" s="35" t="s">
+      <c r="AR5" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="AS5" s="35" t="s">
+      <c r="AS5" s="36" t="s">
         <v>134</v>
       </c>
-      <c r="AT5" s="35" t="s">
+      <c r="AT5" s="36" t="s">
         <v>135</v>
       </c>
-      <c r="AU5" s="35" t="s">
+      <c r="AU5" s="36" t="s">
         <v>136</v>
       </c>
-      <c r="AV5" s="35" t="s">
+      <c r="AV5" s="36" t="s">
         <v>137</v>
       </c>
-      <c r="AW5" s="35" t="s">
+      <c r="AW5" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="AX5" s="35" t="s">
+      <c r="AX5" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="AY5" s="35" t="s">
+      <c r="AY5" s="36" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="6" s="65" customFormat="1" ht="27" spans="1:51">
+    <row r="6" s="65" customFormat="1" ht="28.8" spans="1:51">
       <c r="A6" s="78"/>
       <c r="B6" s="78"/>
       <c r="C6" s="81" t="s">
@@ -7546,7 +7628,7 @@
       <c r="U6" s="81" t="s">
         <v>141</v>
       </c>
-      <c r="V6" s="35" t="s">
+      <c r="V6" s="36" t="s">
         <v>142</v>
       </c>
       <c r="W6" s="81" t="s">
@@ -7637,7 +7719,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7" s="65" customFormat="1" ht="54" spans="1:51">
+    <row r="7" s="65" customFormat="1" ht="57.6" spans="1:51">
       <c r="A7" s="82" t="s">
         <v>143</v>
       </c>
@@ -7701,7 +7783,7 @@
       <c r="U7" s="81" t="s">
         <v>145</v>
       </c>
-      <c r="V7" s="35" t="s">
+      <c r="V7" s="36" t="s">
         <v>146</v>
       </c>
       <c r="W7" s="81" t="s">
@@ -7792,7 +7874,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" ht="67.5" spans="1:51">
+    <row r="8" ht="72" spans="1:51">
       <c r="A8" s="84"/>
       <c r="B8" s="85" t="s">
         <v>147</v>
@@ -7945,9 +8027,9 @@
         <v>155</v>
       </c>
     </row>
-    <row r="9" ht="40.5" spans="1:51">
+    <row r="9" ht="43.2" spans="1:51">
       <c r="A9" s="84"/>
-      <c r="B9" s="29" t="s">
+      <c r="B9" s="30" t="s">
         <v>170</v>
       </c>
       <c r="C9" s="87"/>
@@ -8004,9 +8086,9 @@
       <c r="AX9" s="88"/>
       <c r="AY9" s="88"/>
     </row>
-    <row r="10" ht="81" spans="1:51">
+    <row r="10" ht="86.4" spans="1:51">
       <c r="A10" s="89"/>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="30" t="s">
         <v>173</v>
       </c>
       <c r="C10" s="87"/>
@@ -8183,7 +8265,7 @@
       <c r="AX12" s="66"/>
       <c r="AY12" s="66"/>
     </row>
-    <row r="14" ht="94.5" spans="1:51">
+    <row r="14" ht="115.2" spans="1:51">
       <c r="A14" s="93" t="s">
         <v>183</v>
       </c>
@@ -8361,7 +8443,7 @@
       <c r="AX15" s="92"/>
       <c r="AY15" s="92"/>
     </row>
-    <row r="16" ht="67.5" spans="1:51">
+    <row r="16" ht="72" spans="1:51">
       <c r="A16" s="98"/>
       <c r="B16" s="99" t="s">
         <v>218</v>
@@ -8438,7 +8520,7 @@
       <c r="AX16" s="92"/>
       <c r="AY16" s="92"/>
     </row>
-    <row r="17" ht="81" spans="1:51">
+    <row r="17" ht="86.4" spans="1:51">
       <c r="A17" s="98"/>
       <c r="B17" s="99" t="s">
         <v>229</v>
@@ -8547,7 +8629,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="18" ht="81" spans="1:51">
+    <row r="18" ht="86.4" spans="1:51">
       <c r="A18" s="98"/>
       <c r="B18" s="99" t="s">
         <v>257</v>
@@ -8624,7 +8706,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="19" ht="40.5" spans="1:51">
+    <row r="19" ht="43.2" spans="1:51">
       <c r="A19" s="98"/>
       <c r="B19" s="99" t="s">
         <v>267</v>
@@ -8691,7 +8773,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="20" ht="54" spans="1:51">
+    <row r="20" ht="57.6" spans="1:51">
       <c r="A20" s="98"/>
       <c r="B20" s="99" t="s">
         <v>271</v>
@@ -8748,7 +8830,7 @@
       <c r="AX20" s="92"/>
       <c r="AY20" s="92"/>
     </row>
-    <row r="21" ht="81" spans="1:51">
+    <row r="21" ht="86.4" spans="1:51">
       <c r="A21" s="98"/>
       <c r="B21" s="103" t="s">
         <v>273</v>
@@ -8886,11 +8968,11 @@
       <c r="AX22" s="92"/>
       <c r="AY22" s="92"/>
     </row>
-    <row r="24" ht="108" spans="1:51">
+    <row r="24" ht="115.2" spans="1:51">
       <c r="A24" s="82" t="s">
         <v>285</v>
       </c>
-      <c r="B24" s="29" t="s">
+      <c r="B24" s="30" t="s">
         <v>286</v>
       </c>
       <c r="C24" s="87" t="s">
@@ -9043,7 +9125,7 @@
     </row>
     <row r="25" customFormat="1" spans="1:51">
       <c r="A25" s="84"/>
-      <c r="B25" s="29" t="s">
+      <c r="B25" s="30" t="s">
         <v>325</v>
       </c>
       <c r="C25" s="87"/>
@@ -9096,9 +9178,9 @@
       <c r="AX25" s="88"/>
       <c r="AY25" s="88"/>
     </row>
-    <row r="26" customFormat="1" ht="94.5" spans="1:51">
+    <row r="26" customFormat="1" ht="100.8" spans="1:51">
       <c r="A26" s="89"/>
-      <c r="B26" s="29" t="s">
+      <c r="B26" s="30" t="s">
         <v>326</v>
       </c>
       <c r="C26" s="87"/>
@@ -9161,7 +9243,7 @@
       <c r="AX26" s="88"/>
       <c r="AY26" s="88"/>
     </row>
-    <row r="27" s="66" customFormat="1" ht="27" spans="1:51">
+    <row r="27" s="66" customFormat="1" ht="28.8" spans="1:51">
       <c r="A27" s="90" t="s">
         <v>332</v>
       </c>
@@ -9248,7 +9330,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -9258,9 +9340,145 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="22.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="79.2222222222222" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="201.6" spans="1:2">
+      <c r="A1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="2" ht="57.6" spans="1:2">
+      <c r="A2" t="s">
+        <v>703</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="3" ht="144" spans="1:2">
+      <c r="A3" t="s">
+        <v>705</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>706</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="38.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="9.66666666666667" customWidth="1"/>
+    <col min="3" max="3" width="131.111111111111" customWidth="1"/>
+    <col min="4" max="4" width="43.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="16.4444444444444" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>707</v>
+      </c>
+      <c r="C1" t="s">
+        <v>708</v>
+      </c>
+      <c r="D1" t="s">
+        <v>709</v>
+      </c>
+      <c r="E1" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B2" t="s">
+        <v>712</v>
+      </c>
+      <c r="C2" t="s">
+        <v>713</v>
+      </c>
+      <c r="D2" t="s">
+        <v>714</v>
+      </c>
+      <c r="E2" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1"/>
+      <c r="B3" t="s">
+        <v>716</v>
+      </c>
+      <c r="C3" t="s">
+        <v>717</v>
+      </c>
+      <c r="D3" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1"/>
+      <c r="B4" t="s">
+        <v>719</v>
+      </c>
+      <c r="C4" t="s">
+        <v>720</v>
+      </c>
+      <c r="E4" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="C7" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="C8" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="C9" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="C10" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="C11" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>727</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -9270,214 +9488,214 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A18:X70"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="13.1083333333333" customWidth="1"/>
+    <col min="2" max="2" width="13.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="12.4916666666667" customWidth="1"/>
+    <col min="6" max="6" width="12.4907407407407" customWidth="1"/>
     <col min="7" max="7" width="11.9166666666667" customWidth="1"/>
-    <col min="8" max="8" width="13.1083333333333" customWidth="1"/>
-    <col min="9" max="9" width="13.225" customWidth="1"/>
+    <col min="8" max="8" width="13.1111111111111" customWidth="1"/>
+    <col min="9" max="9" width="13.2222222222222" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="9.775" customWidth="1"/>
-    <col min="12" max="12" width="4.775" customWidth="1"/>
+    <col min="11" max="11" width="9.77777777777778" customWidth="1"/>
+    <col min="12" max="12" width="4.77777777777778" customWidth="1"/>
     <col min="13" max="13" width="5.66666666666667" customWidth="1"/>
     <col min="15" max="15" width="9.66666666666667" customWidth="1"/>
     <col min="16" max="16" width="14.3333333333333" customWidth="1"/>
     <col min="17" max="17" width="9.66666666666667" customWidth="1"/>
-    <col min="19" max="19" width="11.4416666666667" customWidth="1"/>
-    <col min="20" max="20" width="13.5583333333333" customWidth="1"/>
-    <col min="21" max="21" width="12.2083333333333" customWidth="1"/>
-    <col min="23" max="23" width="12.8916666666667" customWidth="1"/>
-    <col min="24" max="24" width="10.225" customWidth="1"/>
+    <col min="19" max="19" width="11.4444444444444" customWidth="1"/>
+    <col min="20" max="20" width="13.5555555555556" customWidth="1"/>
+    <col min="21" max="21" width="12.2037037037037" customWidth="1"/>
+    <col min="23" max="23" width="12.8888888888889" customWidth="1"/>
+    <col min="24" max="24" width="10.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="18" ht="14.25" spans="1:24">
-      <c r="A18" s="61" t="s">
+    <row r="18" ht="15.15" spans="1:24">
+      <c r="A18" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="B18" s="61"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="61"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
     </row>
     <row r="19" spans="1:24">
-      <c r="A19" s="18" t="s">
+      <c r="A19" s="19" t="s">
         <v>335</v>
       </c>
-      <c r="B19" s="19" t="s">
+      <c r="B19" s="20" t="s">
         <v>336</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="C19" s="21" t="s">
         <v>337</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="D19" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="E19" s="20" t="s">
+      <c r="E19" s="21" t="s">
         <v>339</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="G19" s="20" t="s">
+      <c r="G19" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="H19" s="20"/>
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20" t="s">
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="21"/>
+      <c r="L19" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="M19" s="20"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="20"/>
-      <c r="P19" s="20"/>
-      <c r="Q19" s="20"/>
-      <c r="R19" s="20"/>
-      <c r="S19" s="20"/>
-      <c r="T19" s="20"/>
-      <c r="U19" s="20" t="s">
+      <c r="M19" s="21"/>
+      <c r="N19" s="21"/>
+      <c r="O19" s="21"/>
+      <c r="P19" s="21"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="21"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
+      <c r="U19" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="V19" s="20"/>
-      <c r="W19" s="20"/>
-      <c r="X19" s="21"/>
+      <c r="V19" s="21"/>
+      <c r="W19" s="21"/>
+      <c r="X19" s="22"/>
     </row>
     <row r="20" spans="1:24">
-      <c r="A20" s="22"/>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="24" t="s">
+      <c r="A20" s="23"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="25" t="s">
         <v>341</v>
       </c>
-      <c r="H20" s="24" t="s">
+      <c r="H20" s="25" t="s">
         <v>342</v>
       </c>
-      <c r="I20" s="25" t="s">
+      <c r="I20" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="J20" s="25"/>
-      <c r="K20" s="25"/>
-      <c r="L20" s="26" t="s">
+      <c r="J20" s="26"/>
+      <c r="K20" s="26"/>
+      <c r="L20" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="M20" s="26"/>
-      <c r="N20" s="26"/>
-      <c r="O20" s="26"/>
-      <c r="P20" s="26"/>
-      <c r="Q20" s="26"/>
-      <c r="R20" s="26"/>
-      <c r="S20" s="26"/>
-      <c r="T20" s="26"/>
-      <c r="U20" s="24" t="s">
+      <c r="M20" s="27"/>
+      <c r="N20" s="27"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="27"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="27"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="27"/>
+      <c r="U20" s="25" t="s">
         <v>345</v>
       </c>
-      <c r="V20" s="25" t="s">
+      <c r="V20" s="26" t="s">
         <v>346</v>
       </c>
-      <c r="W20" s="25"/>
-      <c r="X20" s="27"/>
-    </row>
-    <row r="21" ht="81.75" spans="1:24">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23"/>
-      <c r="C21" s="23"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
-      <c r="F21" s="23"/>
-      <c r="G21" s="28" t="s">
+      <c r="W20" s="26"/>
+      <c r="X20" s="28"/>
+    </row>
+    <row r="21" ht="87.15" spans="1:24">
+      <c r="A21" s="23"/>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="H21" s="28" t="s">
+      <c r="H21" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="I21" s="29" t="s">
+      <c r="I21" s="30" t="s">
         <v>347</v>
       </c>
-      <c r="J21" s="29" t="s">
+      <c r="J21" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="K21" s="29" t="s">
+      <c r="K21" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="L21" s="30" t="s">
+      <c r="L21" s="31" t="s">
         <v>348</v>
       </c>
-      <c r="M21" s="31" t="s">
+      <c r="M21" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="N21" s="30" t="s">
+      <c r="N21" s="31" t="s">
         <v>349</v>
       </c>
-      <c r="O21" s="31" t="s">
+      <c r="O21" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="P21" s="31" t="s">
+      <c r="P21" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="Q21" s="31" t="s">
+      <c r="Q21" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="R21" s="31" t="s">
+      <c r="R21" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="S21" s="30" t="s">
+      <c r="S21" s="31" t="s">
         <v>350</v>
       </c>
-      <c r="T21" s="30" t="s">
+      <c r="T21" s="31" t="s">
         <v>351</v>
       </c>
-      <c r="U21" s="28" t="s">
+      <c r="U21" s="29" t="s">
         <v>333</v>
       </c>
-      <c r="V21" s="29" t="s">
+      <c r="V21" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="W21" s="29" t="s">
+      <c r="W21" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="X21" s="32" t="s">
+      <c r="X21" s="33" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="22" s="17" customFormat="1" ht="94.5" spans="1:24">
-      <c r="A22" s="33" t="s">
+    <row r="22" s="17" customFormat="1" ht="100.8" spans="1:24">
+      <c r="A22" s="34" t="s">
         <v>352</v>
       </c>
-      <c r="B22" s="34" t="s">
+      <c r="B22" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="C22" s="35" t="s">
+      <c r="C22" s="36" t="s">
         <v>354</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="E22" s="35"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="36" t="s">
+      <c r="E22" s="36"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="37"/>
-      <c r="M22" s="37"/>
-      <c r="N22" s="37"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="38"/>
+      <c r="M22" s="38"/>
+      <c r="N22" s="38"/>
       <c r="O22" s="62" t="s">
         <v>219</v>
       </c>
@@ -9488,34 +9706,34 @@
       <c r="T22" s="62" t="s">
         <v>274</v>
       </c>
-      <c r="U22" s="36" t="s">
+      <c r="U22" s="37" t="s">
         <v>287</v>
       </c>
-      <c r="V22" s="36"/>
-      <c r="W22" s="36"/>
-      <c r="X22" s="40"/>
-    </row>
-    <row r="23" ht="94.5" spans="1:24">
-      <c r="A23" s="22"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="35" t="s">
+      <c r="V22" s="37"/>
+      <c r="W22" s="37"/>
+      <c r="X22" s="41"/>
+    </row>
+    <row r="23" ht="100.8" spans="1:24">
+      <c r="A23" s="23"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="36" t="s">
         <v>356</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="E23" s="35"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="36" t="s">
+      <c r="E23" s="36"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="37" t="s">
         <v>358</v>
       </c>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="37"/>
-      <c r="M23" s="37"/>
-      <c r="N23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="38"/>
+      <c r="M23" s="38"/>
+      <c r="N23" s="38"/>
       <c r="O23" s="62" t="s">
         <v>359</v>
       </c>
@@ -9526,104 +9744,104 @@
       <c r="T23" s="62" t="s">
         <v>274</v>
       </c>
-      <c r="U23" s="36" t="s">
+      <c r="U23" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="V23" s="36"/>
-      <c r="W23" s="36"/>
-      <c r="X23" s="40"/>
-    </row>
-    <row r="24" ht="81" spans="1:24">
-      <c r="A24" s="22"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="35" t="s">
+      <c r="V23" s="37"/>
+      <c r="W23" s="37"/>
+      <c r="X23" s="41"/>
+    </row>
+    <row r="24" ht="100.8" spans="1:24">
+      <c r="A24" s="23"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="36" t="s">
         <v>360</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="E24" s="35"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="36" t="s">
+      <c r="E24" s="36"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
-      <c r="K24" s="36"/>
-      <c r="L24" s="37"/>
-      <c r="M24" s="37"/>
-      <c r="N24" s="37"/>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="38"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
       <c r="O24" s="62"/>
       <c r="P24" s="63"/>
       <c r="Q24" s="63"/>
       <c r="R24" s="63"/>
       <c r="S24" s="63"/>
       <c r="T24" s="62"/>
-      <c r="U24" s="36" t="s">
+      <c r="U24" s="37" t="s">
         <v>362</v>
       </c>
-      <c r="V24" s="36"/>
-      <c r="W24" s="36"/>
-      <c r="X24" s="40"/>
-    </row>
-    <row r="25" ht="81" spans="1:24">
-      <c r="A25" s="22"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="35" t="s">
+      <c r="V24" s="37"/>
+      <c r="W24" s="37"/>
+      <c r="X24" s="41"/>
+    </row>
+    <row r="25" ht="86.4" spans="1:24">
+      <c r="A25" s="23"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="36" t="s">
         <v>363</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="E25" s="35"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="36" t="s">
+      <c r="E25" s="36"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="43" t="s">
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
+      <c r="M25" s="44"/>
+      <c r="N25" s="44"/>
       <c r="O25" s="62"/>
       <c r="P25" s="62"/>
       <c r="Q25" s="62"/>
       <c r="R25" s="62"/>
       <c r="S25" s="62"/>
       <c r="T25" s="62"/>
-      <c r="U25" s="36" t="s">
+      <c r="U25" s="37" t="s">
         <v>289</v>
       </c>
-      <c r="V25" s="36"/>
-      <c r="W25" s="36"/>
-      <c r="X25" s="40"/>
-    </row>
-    <row r="26" customFormat="1" ht="121.5" spans="1:24">
-      <c r="A26" s="22"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="35" t="s">
+      <c r="V25" s="37"/>
+      <c r="W25" s="37"/>
+      <c r="X25" s="41"/>
+    </row>
+    <row r="26" customFormat="1" ht="129.6" spans="1:24">
+      <c r="A26" s="23"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="36" t="s">
         <v>365</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="E26" s="35"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="36" t="s">
+      <c r="E26" s="36"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="37" t="s">
         <v>367</v>
       </c>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="36"/>
-      <c r="K26" s="36"/>
-      <c r="L26" s="43"/>
-      <c r="M26" s="43"/>
-      <c r="N26" s="43"/>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="44"/>
+      <c r="N26" s="44"/>
       <c r="O26" s="62"/>
       <c r="P26" s="62" t="s">
         <v>230</v>
@@ -9632,38 +9850,38 @@
       <c r="R26" s="62"/>
       <c r="S26" s="62"/>
       <c r="T26" s="62"/>
-      <c r="U26" s="36" t="s">
+      <c r="U26" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="V26" s="36"/>
-      <c r="W26" s="36"/>
-      <c r="X26" s="44" t="s">
+      <c r="V26" s="37"/>
+      <c r="W26" s="37"/>
+      <c r="X26" s="45" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="27" customFormat="1" ht="81" spans="1:24">
-      <c r="A27" s="22"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="35" t="s">
+    <row r="27" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A27" s="23"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="36" t="s">
         <v>368</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="E27" s="35"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="36" t="s">
+      <c r="E27" s="36"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="37" t="s">
         <v>370</v>
       </c>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="36"/>
-      <c r="L27" s="43" t="s">
+      <c r="H27" s="37"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="M27" s="43"/>
-      <c r="N27" s="43"/>
+      <c r="M27" s="44"/>
+      <c r="N27" s="44"/>
       <c r="O27" s="62"/>
       <c r="P27" s="62"/>
       <c r="Q27" s="62"/>
@@ -9672,34 +9890,34 @@
       </c>
       <c r="S27" s="62"/>
       <c r="T27" s="62"/>
-      <c r="U27" s="36" t="s">
+      <c r="U27" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="V27" s="36"/>
-      <c r="W27" s="36"/>
-      <c r="X27" s="40"/>
-    </row>
-    <row r="28" s="16" customFormat="1" ht="68.25" spans="1:24">
-      <c r="A28" s="22"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="35" t="s">
+      <c r="V27" s="37"/>
+      <c r="W27" s="37"/>
+      <c r="X27" s="41"/>
+    </row>
+    <row r="28" s="18" customFormat="1" ht="72.75" spans="1:24">
+      <c r="A28" s="23"/>
+      <c r="B28" s="35"/>
+      <c r="C28" s="36" t="s">
         <v>371</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="E28" s="35"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="36" t="s">
+      <c r="E28" s="36"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="36"/>
-      <c r="K28" s="36"/>
-      <c r="L28" s="43"/>
-      <c r="M28" s="43"/>
-      <c r="N28" s="43"/>
+      <c r="H28" s="37"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="44"/>
+      <c r="M28" s="44"/>
+      <c r="N28" s="44"/>
       <c r="O28" s="62"/>
       <c r="P28" s="62" t="s">
         <v>231</v>
@@ -9708,78 +9926,78 @@
       <c r="R28" s="62"/>
       <c r="S28" s="62"/>
       <c r="T28" s="62"/>
-      <c r="U28" s="36" t="s">
+      <c r="U28" s="37" t="s">
         <v>292</v>
       </c>
-      <c r="V28" s="36"/>
-      <c r="W28" s="36"/>
-      <c r="X28" s="40"/>
+      <c r="V28" s="37"/>
+      <c r="W28" s="37"/>
+      <c r="X28" s="41"/>
     </row>
     <row r="29" s="17" customFormat="1" ht="72" customHeight="1" spans="1:24">
-      <c r="A29" s="33" t="s">
+      <c r="A29" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="C29" s="35" t="s">
+      <c r="C29" s="36" t="s">
         <v>375</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="E29" s="35"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="36" t="s">
+      <c r="E29" s="36"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="36"/>
-      <c r="L29" s="43"/>
-      <c r="M29" s="43"/>
-      <c r="N29" s="43"/>
+      <c r="H29" s="37"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="44"/>
+      <c r="N29" s="44"/>
       <c r="O29" s="62"/>
       <c r="P29" s="62"/>
       <c r="Q29" s="62"/>
       <c r="R29" s="62"/>
       <c r="S29" s="62"/>
       <c r="T29" s="62"/>
-      <c r="U29" s="36" t="s">
+      <c r="U29" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="V29" s="36"/>
-      <c r="W29" s="36"/>
-      <c r="X29" s="40"/>
-    </row>
-    <row r="30" customFormat="1" ht="81" spans="1:24">
-      <c r="A30" s="22"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="35" t="s">
+      <c r="V29" s="37"/>
+      <c r="W29" s="37"/>
+      <c r="X29" s="41"/>
+    </row>
+    <row r="30" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A30" s="23"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="36" t="s">
         <v>377</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="E30" s="35"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="36" t="s">
+      <c r="E30" s="36"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="46" t="s">
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="47" t="s">
         <v>171</v>
       </c>
-      <c r="K30" s="46" t="s">
+      <c r="K30" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="L30" s="43" t="s">
+      <c r="L30" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="M30" s="43"/>
-      <c r="N30" s="43"/>
+      <c r="M30" s="44"/>
+      <c r="N30" s="44"/>
       <c r="O30" s="62" t="s">
         <v>379</v>
       </c>
@@ -9796,38 +10014,38 @@
       <c r="T30" s="62" t="s">
         <v>275</v>
       </c>
-      <c r="U30" s="36" t="s">
+      <c r="U30" s="37" t="s">
         <v>294</v>
       </c>
-      <c r="V30" s="36"/>
-      <c r="W30" s="36"/>
-      <c r="X30" s="40"/>
-    </row>
-    <row r="31" customFormat="1" ht="54" spans="1:24">
-      <c r="A31" s="22"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="35" t="s">
+      <c r="V30" s="37"/>
+      <c r="W30" s="37"/>
+      <c r="X30" s="41"/>
+    </row>
+    <row r="31" customFormat="1" ht="57.6" spans="1:24">
+      <c r="A31" s="23"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="36" t="s">
         <v>380</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="7" t="s">
         <v>381</v>
       </c>
-      <c r="E31" s="35"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="36" t="s">
+      <c r="E31" s="36"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="36"/>
-      <c r="K31" s="46" t="s">
+      <c r="H31" s="37"/>
+      <c r="I31" s="37"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="47" t="s">
         <v>175</v>
       </c>
-      <c r="L31" s="43" t="s">
+      <c r="L31" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M31" s="43"/>
-      <c r="N31" s="43"/>
+      <c r="M31" s="44"/>
+      <c r="N31" s="44"/>
       <c r="O31" s="62"/>
       <c r="P31" s="62" t="s">
         <v>233</v>
@@ -9840,114 +10058,114 @@
       <c r="T31" s="62" t="s">
         <v>276</v>
       </c>
-      <c r="U31" s="36" t="s">
+      <c r="U31" s="37" t="s">
         <v>295</v>
       </c>
-      <c r="V31" s="36"/>
-      <c r="W31" s="36"/>
-      <c r="X31" s="40"/>
+      <c r="V31" s="37"/>
+      <c r="W31" s="37"/>
+      <c r="X31" s="41"/>
     </row>
     <row r="32" customFormat="1" ht="82" customHeight="1" spans="1:24">
-      <c r="A32" s="22"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="35" t="s">
+      <c r="A32" s="23"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="36" t="s">
         <v>382</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="E32" s="35"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="36" t="s">
+      <c r="E32" s="36"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="43" t="s">
+      <c r="H32" s="37"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="M32" s="43"/>
-      <c r="N32" s="43"/>
+      <c r="M32" s="44"/>
+      <c r="N32" s="44"/>
       <c r="O32" s="62"/>
       <c r="P32" s="62"/>
       <c r="Q32" s="62"/>
       <c r="R32" s="62"/>
       <c r="S32" s="62"/>
       <c r="T32" s="62"/>
-      <c r="U32" s="36" t="s">
+      <c r="U32" s="37" t="s">
         <v>296</v>
       </c>
-      <c r="V32" s="36"/>
-      <c r="W32" s="36"/>
-      <c r="X32" s="44" t="s">
+      <c r="V32" s="37"/>
+      <c r="W32" s="37"/>
+      <c r="X32" s="45" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="81" spans="1:24">
-      <c r="A33" s="22"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="35" t="s">
+    <row r="33" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A33" s="23"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="36" t="s">
         <v>384</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="36" t="s">
+      <c r="E33" s="36"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="46" t="s">
+      <c r="H33" s="37"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="47" t="s">
         <v>172</v>
       </c>
-      <c r="K33" s="46" t="s">
+      <c r="K33" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="L33" s="43" t="s">
+      <c r="L33" s="44" t="s">
         <v>190</v>
       </c>
-      <c r="M33" s="43"/>
-      <c r="N33" s="43"/>
+      <c r="M33" s="44"/>
+      <c r="N33" s="44"/>
       <c r="O33" s="62"/>
       <c r="P33" s="62"/>
       <c r="Q33" s="62"/>
       <c r="R33" s="62"/>
       <c r="S33" s="62"/>
       <c r="T33" s="62"/>
-      <c r="U33" s="36" t="s">
+      <c r="U33" s="37" t="s">
         <v>386</v>
       </c>
-      <c r="V33" s="36"/>
-      <c r="W33" s="36"/>
-      <c r="X33" s="44" t="s">
+      <c r="V33" s="37"/>
+      <c r="W33" s="37"/>
+      <c r="X33" s="45" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="34" s="16" customFormat="1" ht="68.25" spans="1:24">
-      <c r="A34" s="22"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="35" t="s">
+    <row r="34" s="18" customFormat="1" ht="72.75" spans="1:24">
+      <c r="A34" s="23"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="36" t="s">
         <v>387</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="E34" s="35"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="36" t="s">
+      <c r="E34" s="36"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="43"/>
-      <c r="M34" s="43"/>
-      <c r="N34" s="43"/>
+      <c r="H34" s="37"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="44"/>
+      <c r="M34" s="44"/>
+      <c r="N34" s="44"/>
       <c r="O34" s="62"/>
       <c r="P34" s="62" t="s">
         <v>234</v>
@@ -9956,146 +10174,146 @@
       <c r="R34" s="62"/>
       <c r="S34" s="62"/>
       <c r="T34" s="62"/>
-      <c r="U34" s="36" t="s">
+      <c r="U34" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="V34" s="36"/>
-      <c r="W34" s="36"/>
-      <c r="X34" s="40"/>
+      <c r="V34" s="37"/>
+      <c r="W34" s="37"/>
+      <c r="X34" s="41"/>
     </row>
     <row r="35" s="17" customFormat="1" ht="82" customHeight="1" spans="1:24">
-      <c r="A35" s="33" t="s">
+      <c r="A35" s="34" t="s">
         <v>389</v>
       </c>
-      <c r="B35" s="34" t="s">
+      <c r="B35" s="35" t="s">
         <v>390</v>
       </c>
-      <c r="C35" s="35" t="s">
+      <c r="C35" s="36" t="s">
         <v>391</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="E35" s="35"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="36" t="s">
+      <c r="E35" s="36"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="36"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="43"/>
+      <c r="H35" s="37"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="37"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="44"/>
+      <c r="M35" s="44"/>
+      <c r="N35" s="44"/>
       <c r="O35" s="62"/>
       <c r="P35" s="62"/>
       <c r="Q35" s="62"/>
       <c r="R35" s="62"/>
       <c r="S35" s="62"/>
       <c r="T35" s="62"/>
-      <c r="U35" s="36" t="s">
+      <c r="U35" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="V35" s="36"/>
-      <c r="W35" s="36"/>
-      <c r="X35" s="40"/>
-    </row>
-    <row r="36" customFormat="1" ht="81" spans="1:24">
-      <c r="A36" s="22"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="35" t="s">
+      <c r="V35" s="37"/>
+      <c r="W35" s="37"/>
+      <c r="X35" s="41"/>
+    </row>
+    <row r="36" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A36" s="23"/>
+      <c r="B36" s="35"/>
+      <c r="C36" s="36" t="s">
         <v>393</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="E36" s="35"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="36" t="s">
+      <c r="E36" s="36"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
-      <c r="J36" s="36"/>
-      <c r="K36" s="36"/>
-      <c r="L36" s="43" t="s">
+      <c r="H36" s="37"/>
+      <c r="I36" s="37"/>
+      <c r="J36" s="37"/>
+      <c r="K36" s="37"/>
+      <c r="L36" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
+      <c r="M36" s="44"/>
+      <c r="N36" s="44"/>
       <c r="O36" s="62"/>
       <c r="P36" s="62"/>
       <c r="Q36" s="62"/>
       <c r="R36" s="62"/>
       <c r="S36" s="62"/>
       <c r="T36" s="62"/>
-      <c r="U36" s="36" t="s">
+      <c r="U36" s="37" t="s">
         <v>299</v>
       </c>
-      <c r="V36" s="36"/>
-      <c r="W36" s="36"/>
-      <c r="X36" s="40"/>
-    </row>
-    <row r="37" customFormat="1" ht="81" spans="1:24">
-      <c r="A37" s="22"/>
-      <c r="B37" s="34"/>
-      <c r="C37" s="35" t="s">
+      <c r="V36" s="37"/>
+      <c r="W36" s="37"/>
+      <c r="X36" s="41"/>
+    </row>
+    <row r="37" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A37" s="23"/>
+      <c r="B37" s="35"/>
+      <c r="C37" s="36" t="s">
         <v>395</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="E37" s="35"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="36" t="s">
+      <c r="E37" s="36"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="36"/>
-      <c r="K37" s="36"/>
-      <c r="L37" s="43" t="s">
+      <c r="H37" s="37"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="37"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="44" t="s">
         <v>192</v>
       </c>
-      <c r="M37" s="43"/>
-      <c r="N37" s="43"/>
+      <c r="M37" s="44"/>
+      <c r="N37" s="44"/>
       <c r="O37" s="62"/>
       <c r="P37" s="62"/>
       <c r="Q37" s="62"/>
       <c r="R37" s="62"/>
       <c r="S37" s="62"/>
       <c r="T37" s="62"/>
-      <c r="U37" s="36" t="s">
+      <c r="U37" s="37" t="s">
         <v>300</v>
       </c>
-      <c r="V37" s="36"/>
-      <c r="W37" s="36"/>
-      <c r="X37" s="40"/>
-    </row>
-    <row r="38" customFormat="1" ht="54" spans="1:24">
-      <c r="A38" s="22"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="35" t="s">
+      <c r="V37" s="37"/>
+      <c r="W37" s="37"/>
+      <c r="X37" s="41"/>
+    </row>
+    <row r="38" customFormat="1" ht="57.6" spans="1:24">
+      <c r="A38" s="23"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="36" t="s">
         <v>397</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="E38" s="35"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="36" t="s">
+      <c r="E38" s="36"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="36"/>
-      <c r="L38" s="43" t="s">
+      <c r="H38" s="37"/>
+      <c r="I38" s="37"/>
+      <c r="J38" s="37"/>
+      <c r="K38" s="37"/>
+      <c r="L38" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="M38" s="43"/>
-      <c r="N38" s="43"/>
+      <c r="M38" s="44"/>
+      <c r="N38" s="44"/>
       <c r="O38" s="62"/>
       <c r="P38" s="62" t="s">
         <v>235</v>
@@ -10104,36 +10322,36 @@
       <c r="R38" s="62"/>
       <c r="S38" s="62"/>
       <c r="T38" s="62"/>
-      <c r="U38" s="36" t="s">
+      <c r="U38" s="37" t="s">
         <v>301</v>
       </c>
-      <c r="V38" s="36"/>
-      <c r="W38" s="36"/>
-      <c r="X38" s="40"/>
+      <c r="V38" s="37"/>
+      <c r="W38" s="37"/>
+      <c r="X38" s="41"/>
     </row>
     <row r="39" customFormat="1" ht="137" customHeight="1" spans="1:24">
-      <c r="A39" s="22"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="35" t="s">
+      <c r="A39" s="23"/>
+      <c r="B39" s="35"/>
+      <c r="C39" s="36" t="s">
         <v>399</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="E39" s="35"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="36" t="s">
+      <c r="E39" s="36"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="36"/>
-      <c r="K39" s="36"/>
-      <c r="L39" s="43" t="s">
+      <c r="H39" s="37"/>
+      <c r="I39" s="37"/>
+      <c r="J39" s="37"/>
+      <c r="K39" s="37"/>
+      <c r="L39" s="44" t="s">
         <v>194</v>
       </c>
-      <c r="M39" s="43"/>
-      <c r="N39" s="43"/>
+      <c r="M39" s="44"/>
+      <c r="N39" s="44"/>
       <c r="O39" s="62"/>
       <c r="P39" s="62" t="s">
         <v>236</v>
@@ -10142,36 +10360,36 @@
       <c r="R39" s="62"/>
       <c r="S39" s="62"/>
       <c r="T39" s="62"/>
-      <c r="U39" s="36" t="s">
+      <c r="U39" s="37" t="s">
         <v>302</v>
       </c>
-      <c r="V39" s="36"/>
-      <c r="W39" s="36"/>
-      <c r="X39" s="40"/>
-    </row>
-    <row r="40" s="16" customFormat="1" ht="81.75" spans="1:24">
-      <c r="A40" s="22"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="35" t="s">
+      <c r="V39" s="37"/>
+      <c r="W39" s="37"/>
+      <c r="X39" s="41"/>
+    </row>
+    <row r="40" s="18" customFormat="1" ht="87.15" spans="1:24">
+      <c r="A40" s="23"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="36" t="s">
         <v>401</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="E40" s="35"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="36" t="s">
+      <c r="E40" s="36"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="36"/>
-      <c r="L40" s="43" t="s">
+      <c r="H40" s="37"/>
+      <c r="I40" s="37"/>
+      <c r="J40" s="37"/>
+      <c r="K40" s="37"/>
+      <c r="L40" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="M40" s="43"/>
-      <c r="N40" s="43"/>
+      <c r="M40" s="44"/>
+      <c r="N40" s="44"/>
       <c r="O40" s="62"/>
       <c r="P40" s="62" t="s">
         <v>237</v>
@@ -10180,74 +10398,74 @@
       <c r="R40" s="62"/>
       <c r="S40" s="62"/>
       <c r="T40" s="62"/>
-      <c r="U40" s="36" t="s">
+      <c r="U40" s="37" t="s">
         <v>303</v>
       </c>
-      <c r="V40" s="36"/>
-      <c r="W40" s="36"/>
-      <c r="X40" s="40"/>
-    </row>
-    <row r="41" s="17" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A41" s="33" t="s">
+      <c r="V40" s="37"/>
+      <c r="W40" s="37"/>
+      <c r="X40" s="41"/>
+    </row>
+    <row r="41" s="17" customFormat="1" ht="72" spans="1:24">
+      <c r="A41" s="34" t="s">
         <v>403</v>
       </c>
-      <c r="B41" s="34" t="s">
+      <c r="B41" s="35" t="s">
         <v>404</v>
       </c>
-      <c r="C41" s="35" t="s">
+      <c r="C41" s="36" t="s">
         <v>405</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="E41" s="35"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="36" t="s">
+      <c r="E41" s="36"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="36"/>
-      <c r="K41" s="36"/>
-      <c r="L41" s="43"/>
-      <c r="M41" s="43"/>
-      <c r="N41" s="43"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
+      <c r="J41" s="37"/>
+      <c r="K41" s="37"/>
+      <c r="L41" s="44"/>
+      <c r="M41" s="44"/>
+      <c r="N41" s="44"/>
       <c r="O41" s="62"/>
       <c r="P41" s="62"/>
       <c r="Q41" s="62"/>
       <c r="R41" s="62"/>
       <c r="S41" s="62"/>
       <c r="T41" s="62"/>
-      <c r="U41" s="36" t="s">
+      <c r="U41" s="37" t="s">
         <v>304</v>
       </c>
-      <c r="V41" s="36"/>
-      <c r="W41" s="36"/>
-      <c r="X41" s="40"/>
+      <c r="V41" s="37"/>
+      <c r="W41" s="37"/>
+      <c r="X41" s="41"/>
     </row>
     <row r="42" customFormat="1" ht="76" customHeight="1" spans="1:24">
-      <c r="A42" s="22"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="35" t="s">
+      <c r="A42" s="23"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="36" t="s">
         <v>407</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="E42" s="35"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="36" t="s">
+      <c r="E42" s="36"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="43" t="s">
+      <c r="H42" s="37"/>
+      <c r="I42" s="37"/>
+      <c r="J42" s="37"/>
+      <c r="K42" s="37"/>
+      <c r="L42" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="M42" s="43"/>
-      <c r="N42" s="43"/>
+      <c r="M42" s="44"/>
+      <c r="N42" s="44"/>
       <c r="O42" s="62"/>
       <c r="P42" s="62" t="s">
         <v>238</v>
@@ -10256,36 +10474,36 @@
       <c r="R42" s="62"/>
       <c r="S42" s="62"/>
       <c r="T42" s="62"/>
-      <c r="U42" s="36" t="s">
+      <c r="U42" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="V42" s="36"/>
-      <c r="W42" s="36"/>
-      <c r="X42" s="40"/>
-    </row>
-    <row r="43" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A43" s="22"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="35" t="s">
+      <c r="V42" s="37"/>
+      <c r="W42" s="37"/>
+      <c r="X42" s="41"/>
+    </row>
+    <row r="43" customFormat="1" ht="72" spans="1:24">
+      <c r="A43" s="23"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="36" t="s">
         <v>409</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="E43" s="35"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="36" t="s">
+      <c r="E43" s="36"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
-      <c r="J43" s="36"/>
-      <c r="K43" s="36"/>
-      <c r="L43" s="43" t="s">
+      <c r="H43" s="37"/>
+      <c r="I43" s="37"/>
+      <c r="J43" s="37"/>
+      <c r="K43" s="37"/>
+      <c r="L43" s="44" t="s">
         <v>196</v>
       </c>
-      <c r="M43" s="43"/>
-      <c r="N43" s="43"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
       <c r="O43" s="62"/>
       <c r="P43" s="62" t="s">
         <v>239</v>
@@ -10294,36 +10512,36 @@
       <c r="R43" s="62"/>
       <c r="S43" s="62"/>
       <c r="T43" s="62"/>
-      <c r="U43" s="36" t="s">
+      <c r="U43" s="37" t="s">
         <v>306</v>
       </c>
-      <c r="V43" s="36"/>
-      <c r="W43" s="36"/>
-      <c r="X43" s="40"/>
-    </row>
-    <row r="44" s="16" customFormat="1" ht="81.75" spans="1:24">
-      <c r="A44" s="22"/>
-      <c r="B44" s="34"/>
-      <c r="C44" s="35" t="s">
+      <c r="V43" s="37"/>
+      <c r="W43" s="37"/>
+      <c r="X43" s="41"/>
+    </row>
+    <row r="44" s="18" customFormat="1" ht="87.15" spans="1:24">
+      <c r="A44" s="23"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="36" t="s">
         <v>411</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="E44" s="35"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="36" t="s">
+      <c r="E44" s="36"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="43" t="s">
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
+      <c r="J44" s="37"/>
+      <c r="K44" s="37"/>
+      <c r="L44" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="M44" s="43"/>
-      <c r="N44" s="43"/>
+      <c r="M44" s="44"/>
+      <c r="N44" s="44"/>
       <c r="O44" s="62"/>
       <c r="P44" s="62" t="s">
         <v>240</v>
@@ -10332,40 +10550,40 @@
       <c r="R44" s="62"/>
       <c r="S44" s="62"/>
       <c r="T44" s="62"/>
-      <c r="U44" s="36" t="s">
+      <c r="U44" s="37" t="s">
         <v>413</v>
       </c>
-      <c r="V44" s="36"/>
-      <c r="W44" s="36"/>
-      <c r="X44" s="40"/>
-    </row>
-    <row r="45" s="17" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A45" s="33" t="s">
+      <c r="V44" s="37"/>
+      <c r="W44" s="37"/>
+      <c r="X44" s="41"/>
+    </row>
+    <row r="45" s="17" customFormat="1" ht="72" spans="1:24">
+      <c r="A45" s="34" t="s">
         <v>414</v>
       </c>
-      <c r="B45" s="34" t="s">
+      <c r="B45" s="35" t="s">
         <v>415</v>
       </c>
-      <c r="C45" s="35" t="s">
+      <c r="C45" s="36" t="s">
         <v>416</v>
       </c>
-      <c r="D45" s="5" t="s">
+      <c r="D45" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="E45" s="35"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="36" t="s">
+      <c r="E45" s="36"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H45" s="36"/>
-      <c r="I45" s="36"/>
-      <c r="J45" s="36"/>
-      <c r="K45" s="36"/>
-      <c r="L45" s="43" t="s">
+      <c r="H45" s="37"/>
+      <c r="I45" s="37"/>
+      <c r="J45" s="37"/>
+      <c r="K45" s="37"/>
+      <c r="L45" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="M45" s="43"/>
-      <c r="N45" s="43"/>
+      <c r="M45" s="44"/>
+      <c r="N45" s="44"/>
       <c r="O45" s="62" t="s">
         <v>418</v>
       </c>
@@ -10378,38 +10596,38 @@
       <c r="R45" s="62"/>
       <c r="S45" s="62"/>
       <c r="T45" s="62"/>
-      <c r="U45" s="36" t="s">
+      <c r="U45" s="37" t="s">
         <v>308</v>
       </c>
-      <c r="V45" s="36"/>
-      <c r="W45" s="36"/>
-      <c r="X45" s="40"/>
-    </row>
-    <row r="46" customFormat="1" ht="162" spans="1:24">
-      <c r="A46" s="22"/>
-      <c r="B46" s="34"/>
-      <c r="C46" s="35" t="s">
+      <c r="V45" s="37"/>
+      <c r="W45" s="37"/>
+      <c r="X45" s="41"/>
+    </row>
+    <row r="46" customFormat="1" ht="201.6" spans="1:24">
+      <c r="A46" s="23"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="36" t="s">
         <v>419</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="E46" s="35"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="36" t="s">
+      <c r="E46" s="36"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="46" t="s">
+      <c r="H46" s="37"/>
+      <c r="I46" s="37"/>
+      <c r="J46" s="37"/>
+      <c r="K46" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="L46" s="43" t="s">
+      <c r="L46" s="44" t="s">
         <v>199</v>
       </c>
-      <c r="M46" s="43"/>
-      <c r="N46" s="43"/>
+      <c r="M46" s="44"/>
+      <c r="N46" s="44"/>
       <c r="O46" s="62" t="s">
         <v>223</v>
       </c>
@@ -10422,36 +10640,36 @@
       <c r="R46" s="62"/>
       <c r="S46" s="62"/>
       <c r="T46" s="62"/>
-      <c r="U46" s="36" t="s">
+      <c r="U46" s="37" t="s">
         <v>309</v>
       </c>
-      <c r="V46" s="36"/>
-      <c r="W46" s="36"/>
-      <c r="X46" s="40"/>
-    </row>
-    <row r="47" s="16" customFormat="1" ht="135.75" spans="1:24">
-      <c r="A47" s="22"/>
-      <c r="B47" s="34"/>
-      <c r="C47" s="35" t="s">
+      <c r="V46" s="37"/>
+      <c r="W46" s="37"/>
+      <c r="X46" s="41"/>
+    </row>
+    <row r="47" s="18" customFormat="1" ht="144.75" spans="1:24">
+      <c r="A47" s="23"/>
+      <c r="B47" s="35"/>
+      <c r="C47" s="36" t="s">
         <v>421</v>
       </c>
-      <c r="D47" s="5" t="s">
+      <c r="D47" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="E47" s="35"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="36" t="s">
+      <c r="E47" s="36"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="H47" s="36"/>
-      <c r="I47" s="36"/>
-      <c r="J47" s="36"/>
-      <c r="K47" s="36"/>
-      <c r="L47" s="43" t="s">
+      <c r="H47" s="37"/>
+      <c r="I47" s="37"/>
+      <c r="J47" s="37"/>
+      <c r="K47" s="37"/>
+      <c r="L47" s="44" t="s">
         <v>200</v>
       </c>
-      <c r="M47" s="43"/>
-      <c r="N47" s="43"/>
+      <c r="M47" s="44"/>
+      <c r="N47" s="44"/>
       <c r="O47" s="62" t="s">
         <v>224</v>
       </c>
@@ -10464,40 +10682,40 @@
       <c r="R47" s="62"/>
       <c r="S47" s="62"/>
       <c r="T47" s="62"/>
-      <c r="U47" s="36" t="s">
+      <c r="U47" s="37" t="s">
         <v>310</v>
       </c>
-      <c r="V47" s="36"/>
-      <c r="W47" s="36"/>
-      <c r="X47" s="40"/>
-    </row>
-    <row r="48" s="17" customFormat="1" ht="94.5" spans="1:24">
-      <c r="A48" s="33" t="s">
+      <c r="V47" s="37"/>
+      <c r="W47" s="37"/>
+      <c r="X47" s="41"/>
+    </row>
+    <row r="48" s="17" customFormat="1" ht="100.8" spans="1:24">
+      <c r="A48" s="34" t="s">
         <v>423</v>
       </c>
-      <c r="B48" s="34" t="s">
+      <c r="B48" s="35" t="s">
         <v>424</v>
       </c>
-      <c r="C48" s="35" t="s">
+      <c r="C48" s="36" t="s">
         <v>425</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="E48" s="35"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="36" t="s">
+      <c r="E48" s="36"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H48" s="36"/>
-      <c r="I48" s="36"/>
-      <c r="J48" s="36"/>
-      <c r="K48" s="36"/>
-      <c r="L48" s="43" t="s">
+      <c r="H48" s="37"/>
+      <c r="I48" s="37"/>
+      <c r="J48" s="37"/>
+      <c r="K48" s="37"/>
+      <c r="L48" s="44" t="s">
         <v>201</v>
       </c>
-      <c r="M48" s="43"/>
-      <c r="N48" s="43"/>
+      <c r="M48" s="44"/>
+      <c r="N48" s="44"/>
       <c r="O48" s="62"/>
       <c r="P48" s="62"/>
       <c r="Q48" s="62" t="s">
@@ -10506,72 +10724,72 @@
       <c r="R48" s="62"/>
       <c r="S48" s="62"/>
       <c r="T48" s="62"/>
-      <c r="U48" s="36" t="s">
+      <c r="U48" s="37" t="s">
         <v>311</v>
       </c>
-      <c r="V48" s="36"/>
-      <c r="W48" s="36"/>
-      <c r="X48" s="40"/>
-    </row>
-    <row r="49" customFormat="1" ht="81" spans="1:24">
-      <c r="A49" s="22"/>
-      <c r="B49" s="34"/>
-      <c r="C49" s="35" t="s">
+      <c r="V48" s="37"/>
+      <c r="W48" s="37"/>
+      <c r="X48" s="41"/>
+    </row>
+    <row r="49" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A49" s="23"/>
+      <c r="B49" s="35"/>
+      <c r="C49" s="36" t="s">
         <v>427</v>
       </c>
-      <c r="D49" s="5" t="s">
+      <c r="D49" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="E49" s="35"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="36" t="s">
+      <c r="E49" s="36"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H49" s="36"/>
-      <c r="I49" s="36"/>
-      <c r="J49" s="36"/>
-      <c r="K49" s="36"/>
-      <c r="L49" s="43" t="s">
+      <c r="H49" s="37"/>
+      <c r="I49" s="37"/>
+      <c r="J49" s="37"/>
+      <c r="K49" s="37"/>
+      <c r="L49" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="M49" s="43"/>
-      <c r="N49" s="43"/>
+      <c r="M49" s="44"/>
+      <c r="N49" s="44"/>
       <c r="O49" s="62"/>
       <c r="P49" s="62"/>
       <c r="Q49" s="62"/>
       <c r="R49" s="62"/>
       <c r="S49" s="62"/>
       <c r="T49" s="62"/>
-      <c r="U49" s="36" t="s">
+      <c r="U49" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="V49" s="36"/>
-      <c r="W49" s="36"/>
-      <c r="X49" s="40"/>
-    </row>
-    <row r="50" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A50" s="22"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="35" t="s">
+      <c r="V49" s="37"/>
+      <c r="W49" s="37"/>
+      <c r="X49" s="41"/>
+    </row>
+    <row r="50" customFormat="1" ht="72" spans="1:24">
+      <c r="A50" s="23"/>
+      <c r="B50" s="35"/>
+      <c r="C50" s="36" t="s">
         <v>429</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="E50" s="35"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="36" t="s">
+      <c r="E50" s="36"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H50" s="36"/>
-      <c r="I50" s="36"/>
-      <c r="J50" s="36"/>
-      <c r="K50" s="36"/>
-      <c r="L50" s="43" t="s">
+      <c r="H50" s="37"/>
+      <c r="I50" s="37"/>
+      <c r="J50" s="37"/>
+      <c r="K50" s="37"/>
+      <c r="L50" s="44" t="s">
         <v>203</v>
       </c>
-      <c r="M50" s="43"/>
-      <c r="N50" s="43"/>
+      <c r="M50" s="44"/>
+      <c r="N50" s="44"/>
       <c r="O50" s="62"/>
       <c r="P50" s="62"/>
       <c r="Q50" s="62"/>
@@ -10582,36 +10800,36 @@
       <c r="T50" s="62" t="s">
         <v>277</v>
       </c>
-      <c r="U50" s="36" t="s">
+      <c r="U50" s="37" t="s">
         <v>313</v>
       </c>
-      <c r="V50" s="36"/>
-      <c r="W50" s="36"/>
-      <c r="X50" s="40"/>
-    </row>
-    <row r="51" customFormat="1" ht="81" spans="1:24">
-      <c r="A51" s="22"/>
-      <c r="B51" s="34"/>
-      <c r="C51" s="35" t="s">
+      <c r="V50" s="37"/>
+      <c r="W50" s="37"/>
+      <c r="X50" s="41"/>
+    </row>
+    <row r="51" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A51" s="23"/>
+      <c r="B51" s="35"/>
+      <c r="C51" s="36" t="s">
         <v>431</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="D51" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="E51" s="35"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="36" t="s">
+      <c r="E51" s="36"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H51" s="36"/>
-      <c r="I51" s="36"/>
-      <c r="J51" s="36"/>
-      <c r="K51" s="36"/>
-      <c r="L51" s="43" t="s">
+      <c r="H51" s="37"/>
+      <c r="I51" s="37"/>
+      <c r="J51" s="37"/>
+      <c r="K51" s="37"/>
+      <c r="L51" s="44" t="s">
         <v>204</v>
       </c>
-      <c r="M51" s="43"/>
-      <c r="N51" s="43"/>
+      <c r="M51" s="44"/>
+      <c r="N51" s="44"/>
       <c r="O51" s="62"/>
       <c r="P51" s="62"/>
       <c r="Q51" s="62"/>
@@ -10620,34 +10838,34 @@
       <c r="T51" s="62" t="s">
         <v>278</v>
       </c>
-      <c r="U51" s="36" t="s">
+      <c r="U51" s="37" t="s">
         <v>314</v>
       </c>
-      <c r="V51" s="36"/>
-      <c r="W51" s="36"/>
-      <c r="X51" s="40"/>
-    </row>
-    <row r="52" customFormat="1" ht="81" spans="1:24">
-      <c r="A52" s="22"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="35" t="s">
+      <c r="V51" s="37"/>
+      <c r="W51" s="37"/>
+      <c r="X51" s="41"/>
+    </row>
+    <row r="52" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A52" s="23"/>
+      <c r="B52" s="35"/>
+      <c r="C52" s="36" t="s">
         <v>433</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D52" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="E52" s="35"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="36" t="s">
+      <c r="E52" s="36"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="H52" s="36"/>
-      <c r="I52" s="36"/>
-      <c r="J52" s="36"/>
-      <c r="K52" s="36"/>
-      <c r="L52" s="43"/>
-      <c r="M52" s="43"/>
-      <c r="N52" s="43"/>
+      <c r="H52" s="37"/>
+      <c r="I52" s="37"/>
+      <c r="J52" s="37"/>
+      <c r="K52" s="37"/>
+      <c r="L52" s="44"/>
+      <c r="M52" s="44"/>
+      <c r="N52" s="44"/>
       <c r="O52" s="62"/>
       <c r="P52" s="62"/>
       <c r="Q52" s="62"/>
@@ -10656,36 +10874,36 @@
       <c r="T52" s="62" t="s">
         <v>279</v>
       </c>
-      <c r="U52" s="48" t="s">
+      <c r="U52" s="49" t="s">
         <v>315</v>
       </c>
-      <c r="V52" s="48"/>
-      <c r="W52" s="48"/>
-      <c r="X52" s="49"/>
-    </row>
-    <row r="53" s="16" customFormat="1" ht="95.25" spans="1:24">
-      <c r="A53" s="22"/>
-      <c r="B53" s="34"/>
-      <c r="C53" s="35" t="s">
+      <c r="V52" s="49"/>
+      <c r="W52" s="49"/>
+      <c r="X52" s="50"/>
+    </row>
+    <row r="53" s="18" customFormat="1" ht="115.95" spans="1:24">
+      <c r="A53" s="23"/>
+      <c r="B53" s="35"/>
+      <c r="C53" s="36" t="s">
         <v>435</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D53" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="E53" s="35"/>
-      <c r="F53" s="7"/>
-      <c r="G53" s="36" t="s">
+      <c r="E53" s="36"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H53" s="36"/>
-      <c r="I53" s="36"/>
-      <c r="J53" s="36"/>
-      <c r="K53" s="36"/>
-      <c r="L53" s="43" t="s">
+      <c r="H53" s="37"/>
+      <c r="I53" s="37"/>
+      <c r="J53" s="37"/>
+      <c r="K53" s="37"/>
+      <c r="L53" s="44" t="s">
         <v>205</v>
       </c>
-      <c r="M53" s="43"/>
-      <c r="N53" s="43"/>
+      <c r="M53" s="44"/>
+      <c r="N53" s="44"/>
       <c r="O53" s="62"/>
       <c r="P53" s="62" t="s">
         <v>244</v>
@@ -10694,40 +10912,40 @@
       <c r="R53" s="62"/>
       <c r="S53" s="62"/>
       <c r="T53" s="62"/>
-      <c r="U53" s="36" t="s">
+      <c r="U53" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="V53" s="36"/>
-      <c r="W53" s="36"/>
-      <c r="X53" s="40"/>
-    </row>
-    <row r="54" s="17" customFormat="1" ht="94.5" spans="1:24">
-      <c r="A54" s="33" t="s">
+      <c r="V53" s="37"/>
+      <c r="W53" s="37"/>
+      <c r="X53" s="41"/>
+    </row>
+    <row r="54" s="17" customFormat="1" ht="100.8" spans="1:24">
+      <c r="A54" s="34" t="s">
         <v>437</v>
       </c>
-      <c r="B54" s="34" t="s">
+      <c r="B54" s="35" t="s">
         <v>438</v>
       </c>
-      <c r="C54" s="35" t="s">
+      <c r="C54" s="36" t="s">
         <v>439</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D54" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="E54" s="35"/>
-      <c r="F54" s="7"/>
-      <c r="G54" s="36" t="s">
+      <c r="E54" s="36"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H54" s="36"/>
-      <c r="I54" s="36"/>
-      <c r="J54" s="36"/>
-      <c r="K54" s="36"/>
-      <c r="L54" s="43" t="s">
+      <c r="H54" s="37"/>
+      <c r="I54" s="37"/>
+      <c r="J54" s="37"/>
+      <c r="K54" s="37"/>
+      <c r="L54" s="44" t="s">
         <v>441</v>
       </c>
-      <c r="M54" s="43"/>
-      <c r="N54" s="43"/>
+      <c r="M54" s="44"/>
+      <c r="N54" s="44"/>
       <c r="O54" s="62"/>
       <c r="P54" s="62"/>
       <c r="Q54" s="62" t="s">
@@ -10738,38 +10956,38 @@
       <c r="T54" s="62" t="s">
         <v>280</v>
       </c>
-      <c r="U54" s="36" t="s">
+      <c r="U54" s="37" t="s">
         <v>316</v>
       </c>
-      <c r="V54" s="36"/>
-      <c r="W54" s="36"/>
-      <c r="X54" s="40"/>
-    </row>
-    <row r="55" customFormat="1" ht="108" spans="1:24">
-      <c r="A55" s="22"/>
-      <c r="B55" s="34"/>
-      <c r="C55" s="35" t="s">
+      <c r="V54" s="37"/>
+      <c r="W54" s="37"/>
+      <c r="X54" s="41"/>
+    </row>
+    <row r="55" customFormat="1" ht="144" spans="1:24">
+      <c r="A55" s="23"/>
+      <c r="B55" s="35"/>
+      <c r="C55" s="36" t="s">
         <v>442</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="D55" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="E55" s="35"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="36" t="s">
+      <c r="E55" s="36"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="H55" s="36"/>
-      <c r="I55" s="36"/>
-      <c r="J55" s="36"/>
-      <c r="K55" s="46" t="s">
+      <c r="H55" s="37"/>
+      <c r="I55" s="37"/>
+      <c r="J55" s="37"/>
+      <c r="K55" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="L55" s="43" t="s">
+      <c r="L55" s="44" t="s">
         <v>207</v>
       </c>
-      <c r="M55" s="43"/>
-      <c r="N55" s="43"/>
+      <c r="M55" s="44"/>
+      <c r="N55" s="44"/>
       <c r="O55" s="62"/>
       <c r="P55" s="62"/>
       <c r="Q55" s="62"/>
@@ -10780,34 +10998,34 @@
       <c r="T55" s="62" t="s">
         <v>281</v>
       </c>
-      <c r="U55" s="36" t="s">
+      <c r="U55" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="V55" s="36"/>
-      <c r="W55" s="36"/>
-      <c r="X55" s="40"/>
-    </row>
-    <row r="56" s="16" customFormat="1" ht="95.25" spans="1:24">
-      <c r="A56" s="22"/>
-      <c r="B56" s="34"/>
-      <c r="C56" s="35" t="s">
+      <c r="V55" s="37"/>
+      <c r="W55" s="37"/>
+      <c r="X55" s="41"/>
+    </row>
+    <row r="56" s="18" customFormat="1" ht="115.95" spans="1:24">
+      <c r="A56" s="23"/>
+      <c r="B56" s="35"/>
+      <c r="C56" s="36" t="s">
         <v>444</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="E56" s="35"/>
-      <c r="F56" s="7"/>
-      <c r="G56" s="36" t="s">
+      <c r="E56" s="36"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H56" s="36"/>
-      <c r="I56" s="36"/>
-      <c r="J56" s="36"/>
-      <c r="K56" s="36"/>
-      <c r="L56" s="43"/>
-      <c r="M56" s="43"/>
-      <c r="N56" s="43"/>
+      <c r="H56" s="37"/>
+      <c r="I56" s="37"/>
+      <c r="J56" s="37"/>
+      <c r="K56" s="37"/>
+      <c r="L56" s="44"/>
+      <c r="M56" s="44"/>
+      <c r="N56" s="44"/>
       <c r="O56" s="62"/>
       <c r="P56" s="62"/>
       <c r="Q56" s="62" t="s">
@@ -10816,38 +11034,38 @@
       <c r="R56" s="62"/>
       <c r="S56" s="62"/>
       <c r="T56" s="62"/>
-      <c r="U56" s="36" t="s">
+      <c r="U56" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="V56" s="36"/>
-      <c r="W56" s="36"/>
-      <c r="X56" s="40"/>
-    </row>
-    <row r="57" s="17" customFormat="1" ht="108" spans="1:24">
-      <c r="A57" s="33" t="s">
+      <c r="V56" s="37"/>
+      <c r="W56" s="37"/>
+      <c r="X56" s="41"/>
+    </row>
+    <row r="57" s="17" customFormat="1" ht="115.2" spans="1:24">
+      <c r="A57" s="34" t="s">
         <v>446</v>
       </c>
-      <c r="B57" s="34" t="s">
+      <c r="B57" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="C57" s="35" t="s">
+      <c r="C57" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="D57" s="50" t="s">
+      <c r="D57" s="51" t="s">
         <v>449</v>
       </c>
-      <c r="E57" s="35"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="36" t="s">
+      <c r="E57" s="36"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H57" s="36"/>
-      <c r="I57" s="36"/>
-      <c r="J57" s="36"/>
-      <c r="K57" s="36"/>
-      <c r="L57" s="43"/>
-      <c r="M57" s="43"/>
-      <c r="N57" s="43"/>
+      <c r="H57" s="37"/>
+      <c r="I57" s="37"/>
+      <c r="J57" s="37"/>
+      <c r="K57" s="37"/>
+      <c r="L57" s="44"/>
+      <c r="M57" s="44"/>
+      <c r="N57" s="44"/>
       <c r="O57" s="62"/>
       <c r="P57" s="62" t="s">
         <v>245</v>
@@ -10856,36 +11074,36 @@
       <c r="R57" s="62"/>
       <c r="S57" s="62"/>
       <c r="T57" s="62"/>
-      <c r="U57" s="36" t="s">
+      <c r="U57" s="37" t="s">
         <v>318</v>
       </c>
-      <c r="V57" s="36"/>
-      <c r="W57" s="36"/>
-      <c r="X57" s="40"/>
-    </row>
-    <row r="58" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A58" s="22"/>
-      <c r="B58" s="34"/>
-      <c r="C58" s="35" t="s">
+      <c r="V57" s="37"/>
+      <c r="W57" s="37"/>
+      <c r="X57" s="41"/>
+    </row>
+    <row r="58" customFormat="1" ht="72" spans="1:24">
+      <c r="A58" s="23"/>
+      <c r="B58" s="35"/>
+      <c r="C58" s="36" t="s">
         <v>450</v>
       </c>
-      <c r="D58" s="50" t="s">
+      <c r="D58" s="51" t="s">
         <v>451</v>
       </c>
-      <c r="E58" s="35"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="36" t="s">
+      <c r="E58" s="36"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="H58" s="36"/>
-      <c r="I58" s="36"/>
-      <c r="J58" s="36"/>
-      <c r="K58" s="36"/>
-      <c r="L58" s="43" t="s">
+      <c r="H58" s="37"/>
+      <c r="I58" s="37"/>
+      <c r="J58" s="37"/>
+      <c r="K58" s="37"/>
+      <c r="L58" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="M58" s="43"/>
-      <c r="N58" s="43"/>
+      <c r="M58" s="44"/>
+      <c r="N58" s="44"/>
       <c r="O58" s="62" t="s">
         <v>225</v>
       </c>
@@ -10896,36 +11114,36 @@
       <c r="R58" s="62"/>
       <c r="S58" s="62"/>
       <c r="T58" s="62"/>
-      <c r="U58" s="36" t="s">
+      <c r="U58" s="37" t="s">
         <v>319</v>
       </c>
-      <c r="V58" s="36"/>
-      <c r="W58" s="36"/>
-      <c r="X58" s="40"/>
-    </row>
-    <row r="59" customFormat="1" ht="81" spans="1:24">
-      <c r="A59" s="22"/>
-      <c r="B59" s="34"/>
-      <c r="C59" s="35" t="s">
+      <c r="V58" s="37"/>
+      <c r="W58" s="37"/>
+      <c r="X58" s="41"/>
+    </row>
+    <row r="59" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A59" s="23"/>
+      <c r="B59" s="35"/>
+      <c r="C59" s="36" t="s">
         <v>452</v>
       </c>
-      <c r="D59" s="50" t="s">
+      <c r="D59" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="E59" s="35"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="36" t="s">
+      <c r="E59" s="36"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H59" s="36"/>
-      <c r="I59" s="36"/>
-      <c r="J59" s="36"/>
-      <c r="K59" s="36"/>
-      <c r="L59" s="43" t="s">
+      <c r="H59" s="37"/>
+      <c r="I59" s="37"/>
+      <c r="J59" s="37"/>
+      <c r="K59" s="37"/>
+      <c r="L59" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="M59" s="43"/>
-      <c r="N59" s="43"/>
+      <c r="M59" s="44"/>
+      <c r="N59" s="44"/>
       <c r="O59" s="62"/>
       <c r="P59" s="62" t="s">
         <v>247</v>
@@ -10936,36 +11154,36 @@
       <c r="R59" s="62"/>
       <c r="S59" s="62"/>
       <c r="T59" s="62"/>
-      <c r="U59" s="36" t="s">
+      <c r="U59" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="V59" s="36"/>
-      <c r="W59" s="36"/>
-      <c r="X59" s="40"/>
-    </row>
-    <row r="60" customFormat="1" ht="81" spans="1:24">
-      <c r="A60" s="22"/>
-      <c r="B60" s="34"/>
-      <c r="C60" s="35" t="s">
+      <c r="V59" s="37"/>
+      <c r="W59" s="37"/>
+      <c r="X59" s="41"/>
+    </row>
+    <row r="60" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A60" s="23"/>
+      <c r="B60" s="35"/>
+      <c r="C60" s="36" t="s">
         <v>454</v>
       </c>
-      <c r="D60" s="50" t="s">
+      <c r="D60" s="51" t="s">
         <v>455</v>
       </c>
-      <c r="E60" s="35"/>
-      <c r="F60" s="7"/>
-      <c r="G60" s="36" t="s">
+      <c r="E60" s="36"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H60" s="36"/>
-      <c r="I60" s="36"/>
-      <c r="J60" s="36"/>
-      <c r="K60" s="36"/>
-      <c r="L60" s="43" t="s">
+      <c r="H60" s="37"/>
+      <c r="I60" s="37"/>
+      <c r="J60" s="37"/>
+      <c r="K60" s="37"/>
+      <c r="L60" s="44" t="s">
         <v>210</v>
       </c>
-      <c r="M60" s="43"/>
-      <c r="N60" s="43"/>
+      <c r="M60" s="44"/>
+      <c r="N60" s="44"/>
       <c r="O60" s="62" t="s">
         <v>226</v>
       </c>
@@ -10978,38 +11196,38 @@
       <c r="T60" s="62" t="s">
         <v>276</v>
       </c>
-      <c r="U60" s="48" t="s">
+      <c r="U60" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="V60" s="48"/>
-      <c r="W60" s="48"/>
-      <c r="X60" s="44" t="s">
+      <c r="V60" s="49"/>
+      <c r="W60" s="49"/>
+      <c r="X60" s="45" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="61" customFormat="1" ht="148.5" spans="1:24">
-      <c r="A61" s="22"/>
-      <c r="B61" s="34"/>
-      <c r="C61" s="35" t="s">
+    <row r="61" customFormat="1" ht="158.4" spans="1:24">
+      <c r="A61" s="23"/>
+      <c r="B61" s="35"/>
+      <c r="C61" s="36" t="s">
         <v>457</v>
       </c>
-      <c r="D61" s="50" t="s">
+      <c r="D61" s="51" t="s">
         <v>458</v>
       </c>
-      <c r="E61" s="35"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="36" t="s">
+      <c r="E61" s="36"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H61" s="36"/>
-      <c r="I61" s="36"/>
-      <c r="J61" s="36"/>
-      <c r="K61" s="36"/>
-      <c r="L61" s="43" t="s">
+      <c r="H61" s="37"/>
+      <c r="I61" s="37"/>
+      <c r="J61" s="37"/>
+      <c r="K61" s="37"/>
+      <c r="L61" s="44" t="s">
         <v>211</v>
       </c>
-      <c r="M61" s="43"/>
-      <c r="N61" s="43"/>
+      <c r="M61" s="44"/>
+      <c r="N61" s="44"/>
       <c r="O61" s="62" t="s">
         <v>226</v>
       </c>
@@ -11024,72 +11242,72 @@
       <c r="T61" s="62" t="s">
         <v>276</v>
       </c>
-      <c r="U61" s="36" t="s">
+      <c r="U61" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="V61" s="36"/>
-      <c r="W61" s="36"/>
-      <c r="X61" s="44" t="s">
+      <c r="V61" s="37"/>
+      <c r="W61" s="37"/>
+      <c r="X61" s="45" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="62" customFormat="1" ht="54" spans="1:24">
-      <c r="A62" s="22"/>
-      <c r="B62" s="34"/>
-      <c r="C62" s="35" t="s">
+    <row r="62" customFormat="1" ht="72" spans="1:24">
+      <c r="A62" s="23"/>
+      <c r="B62" s="35"/>
+      <c r="C62" s="36" t="s">
         <v>459</v>
       </c>
-      <c r="D62" s="50" t="s">
+      <c r="D62" s="51" t="s">
         <v>460</v>
       </c>
-      <c r="E62" s="35"/>
-      <c r="F62" s="7"/>
-      <c r="G62" s="36" t="s">
+      <c r="E62" s="36"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H62" s="36"/>
-      <c r="I62" s="36"/>
-      <c r="J62" s="36"/>
-      <c r="K62" s="36"/>
-      <c r="L62" s="43"/>
-      <c r="M62" s="43"/>
-      <c r="N62" s="43"/>
+      <c r="H62" s="37"/>
+      <c r="I62" s="37"/>
+      <c r="J62" s="37"/>
+      <c r="K62" s="37"/>
+      <c r="L62" s="44"/>
+      <c r="M62" s="44"/>
+      <c r="N62" s="44"/>
       <c r="O62" s="62"/>
       <c r="P62" s="62"/>
       <c r="Q62" s="62"/>
       <c r="R62" s="62"/>
       <c r="S62" s="62"/>
       <c r="T62" s="62"/>
-      <c r="U62" s="36" t="s">
+      <c r="U62" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="V62" s="36"/>
-      <c r="W62" s="36"/>
-      <c r="X62" s="40"/>
-    </row>
-    <row r="63" s="16" customFormat="1" ht="95.25" spans="1:24">
-      <c r="A63" s="22"/>
-      <c r="B63" s="34"/>
-      <c r="C63" s="35" t="s">
+      <c r="V62" s="37"/>
+      <c r="W62" s="37"/>
+      <c r="X62" s="41"/>
+    </row>
+    <row r="63" s="18" customFormat="1" ht="101.55" spans="1:24">
+      <c r="A63" s="23"/>
+      <c r="B63" s="35"/>
+      <c r="C63" s="36" t="s">
         <v>461</v>
       </c>
-      <c r="D63" s="50" t="s">
+      <c r="D63" s="51" t="s">
         <v>462</v>
       </c>
-      <c r="E63" s="35"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="36" t="s">
+      <c r="E63" s="36"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="H63" s="36"/>
-      <c r="I63" s="36"/>
-      <c r="J63" s="36"/>
-      <c r="K63" s="36"/>
-      <c r="L63" s="43" t="s">
+      <c r="H63" s="37"/>
+      <c r="I63" s="37"/>
+      <c r="J63" s="37"/>
+      <c r="K63" s="37"/>
+      <c r="L63" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="M63" s="43"/>
-      <c r="N63" s="43"/>
+      <c r="M63" s="44"/>
+      <c r="N63" s="44"/>
       <c r="O63" s="62"/>
       <c r="P63" s="62" t="s">
         <v>250</v>
@@ -11098,40 +11316,40 @@
       <c r="R63" s="62"/>
       <c r="S63" s="62"/>
       <c r="T63" s="62"/>
-      <c r="U63" s="36" t="s">
+      <c r="U63" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="V63" s="36"/>
-      <c r="W63" s="36"/>
-      <c r="X63" s="40"/>
-    </row>
-    <row r="64" s="17" customFormat="1" ht="121.5" spans="1:24">
-      <c r="A64" s="33" t="s">
+      <c r="V63" s="37"/>
+      <c r="W63" s="37"/>
+      <c r="X63" s="41"/>
+    </row>
+    <row r="64" s="17" customFormat="1" ht="129.6" spans="1:24">
+      <c r="A64" s="34" t="s">
         <v>463</v>
       </c>
-      <c r="B64" s="34" t="s">
+      <c r="B64" s="35" t="s">
         <v>464</v>
       </c>
-      <c r="C64" s="35" t="s">
+      <c r="C64" s="36" t="s">
         <v>465</v>
       </c>
-      <c r="D64" s="50" t="s">
+      <c r="D64" s="51" t="s">
         <v>466</v>
       </c>
-      <c r="E64" s="35"/>
-      <c r="F64" s="7"/>
-      <c r="G64" s="36" t="s">
+      <c r="E64" s="36"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="H64" s="36"/>
-      <c r="I64" s="36"/>
-      <c r="J64" s="36"/>
-      <c r="K64" s="36"/>
-      <c r="L64" s="43" t="s">
+      <c r="H64" s="37"/>
+      <c r="I64" s="37"/>
+      <c r="J64" s="37"/>
+      <c r="K64" s="37"/>
+      <c r="L64" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="M64" s="43"/>
-      <c r="N64" s="43"/>
+      <c r="M64" s="44"/>
+      <c r="N64" s="44"/>
       <c r="O64" s="62" t="s">
         <v>227</v>
       </c>
@@ -11142,36 +11360,36 @@
       <c r="R64" s="62"/>
       <c r="S64" s="62"/>
       <c r="T64" s="62"/>
-      <c r="U64" s="36" t="s">
+      <c r="U64" s="37" t="s">
         <v>320</v>
       </c>
-      <c r="V64" s="36"/>
-      <c r="W64" s="36"/>
-      <c r="X64" s="40"/>
-    </row>
-    <row r="65" customFormat="1" ht="40.5" spans="1:24">
-      <c r="A65" s="22"/>
-      <c r="B65" s="34"/>
-      <c r="C65" s="35" t="s">
+      <c r="V64" s="37"/>
+      <c r="W64" s="37"/>
+      <c r="X64" s="41"/>
+    </row>
+    <row r="65" customFormat="1" ht="43.2" spans="1:24">
+      <c r="A65" s="23"/>
+      <c r="B65" s="35"/>
+      <c r="C65" s="36" t="s">
         <v>467</v>
       </c>
-      <c r="D65" s="50" t="s">
+      <c r="D65" s="51" t="s">
         <v>468</v>
       </c>
-      <c r="E65" s="35"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="36" t="s">
+      <c r="E65" s="36"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="H65" s="36"/>
-      <c r="I65" s="36"/>
-      <c r="J65" s="36"/>
-      <c r="K65" s="36"/>
-      <c r="L65" s="43" t="s">
+      <c r="H65" s="37"/>
+      <c r="I65" s="37"/>
+      <c r="J65" s="37"/>
+      <c r="K65" s="37"/>
+      <c r="L65" s="44" t="s">
         <v>214</v>
       </c>
-      <c r="M65" s="43"/>
-      <c r="N65" s="43"/>
+      <c r="M65" s="44"/>
+      <c r="N65" s="44"/>
       <c r="O65" s="62"/>
       <c r="P65" s="62" t="s">
         <v>252</v>
@@ -11182,36 +11400,36 @@
       <c r="T65" s="62" t="s">
         <v>277</v>
       </c>
-      <c r="U65" s="36" t="s">
+      <c r="U65" s="37" t="s">
         <v>321</v>
       </c>
-      <c r="V65" s="36"/>
-      <c r="W65" s="36"/>
-      <c r="X65" s="40"/>
-    </row>
-    <row r="66" s="16" customFormat="1" ht="95.25" spans="1:24">
-      <c r="A66" s="22"/>
-      <c r="B66" s="34"/>
-      <c r="C66" s="35" t="s">
+      <c r="V65" s="37"/>
+      <c r="W65" s="37"/>
+      <c r="X65" s="41"/>
+    </row>
+    <row r="66" s="18" customFormat="1" ht="101.55" spans="1:24">
+      <c r="A66" s="23"/>
+      <c r="B66" s="35"/>
+      <c r="C66" s="36" t="s">
         <v>469</v>
       </c>
-      <c r="D66" s="50" t="s">
+      <c r="D66" s="51" t="s">
         <v>470</v>
       </c>
-      <c r="E66" s="35"/>
-      <c r="F66" s="7"/>
-      <c r="G66" s="36" t="s">
+      <c r="E66" s="36"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="H66" s="36"/>
-      <c r="I66" s="36"/>
-      <c r="J66" s="36"/>
-      <c r="K66" s="36"/>
-      <c r="L66" s="43" t="s">
+      <c r="H66" s="37"/>
+      <c r="I66" s="37"/>
+      <c r="J66" s="37"/>
+      <c r="K66" s="37"/>
+      <c r="L66" s="44" t="s">
         <v>215</v>
       </c>
-      <c r="M66" s="43"/>
-      <c r="N66" s="43"/>
+      <c r="M66" s="44"/>
+      <c r="N66" s="44"/>
       <c r="O66" s="62"/>
       <c r="P66" s="62" t="s">
         <v>253</v>
@@ -11220,38 +11438,38 @@
       <c r="R66" s="62"/>
       <c r="S66" s="62"/>
       <c r="T66" s="62"/>
-      <c r="U66" s="36" t="s">
+      <c r="U66" s="37" t="s">
         <v>322</v>
       </c>
-      <c r="V66" s="36"/>
-      <c r="W66" s="36"/>
-      <c r="X66" s="40"/>
-    </row>
-    <row r="67" s="17" customFormat="1" ht="148.5" spans="1:24">
-      <c r="A67" s="33" t="s">
+      <c r="V66" s="37"/>
+      <c r="W66" s="37"/>
+      <c r="X66" s="41"/>
+    </row>
+    <row r="67" s="17" customFormat="1" ht="158.4" spans="1:24">
+      <c r="A67" s="34" t="s">
         <v>471</v>
       </c>
-      <c r="B67" s="34" t="s">
+      <c r="B67" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="C67" s="35" t="s">
+      <c r="C67" s="36" t="s">
         <v>473</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="D67" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="E67" s="35"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="36" t="s">
+      <c r="E67" s="36"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="H67" s="36"/>
-      <c r="I67" s="36"/>
-      <c r="J67" s="36"/>
-      <c r="K67" s="36"/>
-      <c r="L67" s="43"/>
-      <c r="M67" s="43"/>
-      <c r="N67" s="43"/>
+      <c r="H67" s="37"/>
+      <c r="I67" s="37"/>
+      <c r="J67" s="37"/>
+      <c r="K67" s="37"/>
+      <c r="L67" s="44"/>
+      <c r="M67" s="44"/>
+      <c r="N67" s="44"/>
       <c r="O67" s="62" t="s">
         <v>228</v>
       </c>
@@ -11264,34 +11482,34 @@
       <c r="R67" s="62"/>
       <c r="S67" s="62"/>
       <c r="T67" s="62"/>
-      <c r="U67" s="36" t="s">
+      <c r="U67" s="37" t="s">
         <v>323</v>
       </c>
-      <c r="V67" s="36"/>
-      <c r="W67" s="36"/>
-      <c r="X67" s="40"/>
-    </row>
-    <row r="68" customFormat="1" ht="81" spans="1:24">
-      <c r="A68" s="22"/>
-      <c r="B68" s="34"/>
-      <c r="C68" s="35" t="s">
+      <c r="V67" s="37"/>
+      <c r="W67" s="37"/>
+      <c r="X67" s="41"/>
+    </row>
+    <row r="68" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A68" s="23"/>
+      <c r="B68" s="35"/>
+      <c r="C68" s="36" t="s">
         <v>475</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="D68" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="E68" s="35"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="36" t="s">
+      <c r="E68" s="36"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="H68" s="36"/>
-      <c r="I68" s="36"/>
-      <c r="J68" s="36"/>
-      <c r="K68" s="36"/>
-      <c r="L68" s="43"/>
-      <c r="M68" s="43"/>
-      <c r="N68" s="43"/>
+      <c r="H68" s="37"/>
+      <c r="I68" s="37"/>
+      <c r="J68" s="37"/>
+      <c r="K68" s="37"/>
+      <c r="L68" s="44"/>
+      <c r="M68" s="44"/>
+      <c r="N68" s="44"/>
       <c r="O68" s="62"/>
       <c r="P68" s="62" t="s">
         <v>255</v>
@@ -11302,36 +11520,36 @@
       <c r="R68" s="62"/>
       <c r="S68" s="62"/>
       <c r="T68" s="62"/>
-      <c r="U68" s="36" t="s">
+      <c r="U68" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="V68" s="36"/>
-      <c r="W68" s="36"/>
-      <c r="X68" s="40"/>
-    </row>
-    <row r="69" customFormat="1" ht="94.5" spans="1:24">
-      <c r="A69" s="22"/>
-      <c r="B69" s="34"/>
-      <c r="C69" s="35" t="s">
+      <c r="V68" s="37"/>
+      <c r="W68" s="37"/>
+      <c r="X68" s="41"/>
+    </row>
+    <row r="69" customFormat="1" ht="100.8" spans="1:24">
+      <c r="A69" s="23"/>
+      <c r="B69" s="35"/>
+      <c r="C69" s="36" t="s">
         <v>477</v>
       </c>
-      <c r="D69" s="50" t="s">
+      <c r="D69" s="51" t="s">
         <v>478</v>
       </c>
-      <c r="E69" s="35"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="36" t="s">
+      <c r="E69" s="36"/>
+      <c r="F69" s="9"/>
+      <c r="G69" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H69" s="36"/>
-      <c r="I69" s="36"/>
-      <c r="J69" s="36"/>
-      <c r="K69" s="36"/>
-      <c r="L69" s="43" t="s">
+      <c r="H69" s="37"/>
+      <c r="I69" s="37"/>
+      <c r="J69" s="37"/>
+      <c r="K69" s="37"/>
+      <c r="L69" s="44" t="s">
         <v>479</v>
       </c>
-      <c r="M69" s="43"/>
-      <c r="N69" s="43"/>
+      <c r="M69" s="44"/>
+      <c r="N69" s="44"/>
       <c r="O69" s="62"/>
       <c r="P69" s="62"/>
       <c r="Q69" s="62"/>
@@ -11340,34 +11558,34 @@
       <c r="T69" s="62" t="s">
         <v>282</v>
       </c>
-      <c r="U69" s="36" t="s">
+      <c r="U69" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="V69" s="36"/>
-      <c r="W69" s="36"/>
-      <c r="X69" s="40"/>
-    </row>
-    <row r="70" s="16" customFormat="1" ht="68.25" spans="1:24">
-      <c r="A70" s="51"/>
-      <c r="B70" s="52"/>
-      <c r="C70" s="53" t="s">
+      <c r="V69" s="37"/>
+      <c r="W69" s="37"/>
+      <c r="X69" s="41"/>
+    </row>
+    <row r="70" s="18" customFormat="1" ht="72.75" spans="1:24">
+      <c r="A70" s="52"/>
+      <c r="B70" s="53"/>
+      <c r="C70" s="54" t="s">
         <v>480</v>
       </c>
-      <c r="D70" s="54" t="s">
+      <c r="D70" s="55" t="s">
         <v>481</v>
       </c>
-      <c r="E70" s="53"/>
-      <c r="F70" s="55"/>
-      <c r="G70" s="56" t="s">
+      <c r="E70" s="54"/>
+      <c r="F70" s="56"/>
+      <c r="G70" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="H70" s="56"/>
-      <c r="I70" s="56"/>
-      <c r="J70" s="56"/>
-      <c r="K70" s="56"/>
-      <c r="L70" s="57"/>
-      <c r="M70" s="57"/>
-      <c r="N70" s="57"/>
+      <c r="H70" s="57"/>
+      <c r="I70" s="57"/>
+      <c r="J70" s="57"/>
+      <c r="K70" s="57"/>
+      <c r="L70" s="58"/>
+      <c r="M70" s="58"/>
+      <c r="N70" s="58"/>
       <c r="O70" s="64"/>
       <c r="P70" s="64" t="s">
         <v>256</v>
@@ -11382,12 +11600,12 @@
       <c r="T70" s="64" t="s">
         <v>283</v>
       </c>
-      <c r="U70" s="56" t="s">
+      <c r="U70" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="V70" s="56"/>
-      <c r="W70" s="56"/>
-      <c r="X70" s="60"/>
+      <c r="V70" s="57"/>
+      <c r="W70" s="57"/>
+      <c r="X70" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="180">
@@ -11581,7 +11799,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -11593,2027 +11811,2027 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:X53"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="13.1083333333333" customWidth="1"/>
+    <col min="2" max="2" width="13.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="12.4916666666667" customWidth="1"/>
+    <col min="6" max="6" width="12.4907407407407" customWidth="1"/>
     <col min="7" max="7" width="11.9166666666667" customWidth="1"/>
-    <col min="8" max="8" width="13.1083333333333" customWidth="1"/>
-    <col min="9" max="9" width="13.225" customWidth="1"/>
+    <col min="8" max="8" width="13.1111111111111" customWidth="1"/>
+    <col min="9" max="9" width="13.2222222222222" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="9.775" customWidth="1"/>
-    <col min="12" max="12" width="4.775" customWidth="1"/>
+    <col min="11" max="11" width="9.77777777777778" customWidth="1"/>
+    <col min="12" max="12" width="4.77777777777778" customWidth="1"/>
     <col min="13" max="13" width="5.66666666666667" customWidth="1"/>
     <col min="15" max="15" width="9.66666666666667" customWidth="1"/>
     <col min="16" max="16" width="14.3333333333333" customWidth="1"/>
     <col min="17" max="17" width="9.66666666666667" customWidth="1"/>
-    <col min="19" max="19" width="11.4416666666667" customWidth="1"/>
-    <col min="20" max="20" width="13.5583333333333" customWidth="1"/>
-    <col min="21" max="21" width="12.2083333333333" customWidth="1"/>
-    <col min="23" max="23" width="12.8916666666667" customWidth="1"/>
-    <col min="24" max="24" width="10.225" customWidth="1"/>
+    <col min="19" max="19" width="11.4444444444444" customWidth="1"/>
+    <col min="20" max="20" width="13.5555555555556" customWidth="1"/>
+    <col min="21" max="21" width="12.2037037037037" customWidth="1"/>
+    <col min="23" max="23" width="12.8888888888889" customWidth="1"/>
+    <col min="24" max="24" width="10.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>335</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="20" t="s">
         <v>336</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="21" t="s">
         <v>337</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="21" t="s">
         <v>339</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="G1" s="20" t="s">
+      <c r="G1" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20" t="s">
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-      <c r="T1" s="20"/>
-      <c r="U1" s="20" t="s">
+      <c r="M1" s="21"/>
+      <c r="N1" s="21"/>
+      <c r="O1" s="21"/>
+      <c r="P1" s="21"/>
+      <c r="Q1" s="21"/>
+      <c r="R1" s="21"/>
+      <c r="S1" s="21"/>
+      <c r="T1" s="21"/>
+      <c r="U1" s="21" t="s">
         <v>285</v>
       </c>
-      <c r="V1" s="20"/>
-      <c r="W1" s="20"/>
-      <c r="X1" s="21"/>
+      <c r="V1" s="21"/>
+      <c r="W1" s="21"/>
+      <c r="X1" s="22"/>
     </row>
     <row r="2" spans="1:24">
-      <c r="A2" s="22"/>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="24" t="s">
+      <c r="A2" s="23"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="25" t="s">
         <v>341</v>
       </c>
-      <c r="H2" s="24" t="s">
+      <c r="H2" s="25" t="s">
         <v>342</v>
       </c>
-      <c r="I2" s="25" t="s">
+      <c r="I2" s="26" t="s">
         <v>343</v>
       </c>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="26" t="s">
+      <c r="J2" s="26"/>
+      <c r="K2" s="26"/>
+      <c r="L2" s="27" t="s">
         <v>344</v>
       </c>
-      <c r="M2" s="26"/>
-      <c r="N2" s="26"/>
-      <c r="O2" s="26"/>
-      <c r="P2" s="26"/>
-      <c r="Q2" s="26"/>
-      <c r="R2" s="26"/>
-      <c r="S2" s="26"/>
-      <c r="T2" s="26"/>
-      <c r="U2" s="24" t="s">
+      <c r="M2" s="27"/>
+      <c r="N2" s="27"/>
+      <c r="O2" s="27"/>
+      <c r="P2" s="27"/>
+      <c r="Q2" s="27"/>
+      <c r="R2" s="27"/>
+      <c r="S2" s="27"/>
+      <c r="T2" s="27"/>
+      <c r="U2" s="25" t="s">
         <v>345</v>
       </c>
-      <c r="V2" s="25" t="s">
+      <c r="V2" s="26" t="s">
         <v>346</v>
       </c>
-      <c r="W2" s="25"/>
-      <c r="X2" s="27"/>
-    </row>
-    <row r="3" ht="81" spans="1:24">
-      <c r="A3" s="22"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="28" t="s">
+      <c r="W2" s="26"/>
+      <c r="X2" s="28"/>
+    </row>
+    <row r="3" ht="86.4" spans="1:24">
+      <c r="A3" s="23"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="29" t="s">
         <v>180</v>
       </c>
-      <c r="H3" s="28" t="s">
+      <c r="H3" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="I3" s="29" t="s">
+      <c r="I3" s="30" t="s">
         <v>347</v>
       </c>
-      <c r="J3" s="29" t="s">
+      <c r="J3" s="30" t="s">
         <v>170</v>
       </c>
-      <c r="K3" s="29" t="s">
+      <c r="K3" s="30" t="s">
         <v>173</v>
       </c>
-      <c r="L3" s="30" t="s">
+      <c r="L3" s="31" t="s">
         <v>348</v>
       </c>
-      <c r="M3" s="31" t="s">
+      <c r="M3" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="N3" s="30" t="s">
+      <c r="N3" s="31" t="s">
         <v>349</v>
       </c>
-      <c r="O3" s="31" t="s">
+      <c r="O3" s="32" t="s">
         <v>218</v>
       </c>
-      <c r="P3" s="31" t="s">
+      <c r="P3" s="32" t="s">
         <v>229</v>
       </c>
-      <c r="Q3" s="31" t="s">
+      <c r="Q3" s="32" t="s">
         <v>257</v>
       </c>
-      <c r="R3" s="31" t="s">
+      <c r="R3" s="32" t="s">
         <v>267</v>
       </c>
-      <c r="S3" s="30" t="s">
+      <c r="S3" s="31" t="s">
         <v>350</v>
       </c>
-      <c r="T3" s="30" t="s">
+      <c r="T3" s="31" t="s">
         <v>351</v>
       </c>
-      <c r="U3" s="28" t="s">
+      <c r="U3" s="29" t="s">
         <v>333</v>
       </c>
-      <c r="V3" s="29" t="s">
+      <c r="V3" s="30" t="s">
         <v>286</v>
       </c>
-      <c r="W3" s="29" t="s">
+      <c r="W3" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="X3" s="32" t="s">
+      <c r="X3" s="33" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="4" customFormat="1" ht="230.25" spans="1:24">
-      <c r="A4" s="22"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="29"/>
-      <c r="K4" s="29"/>
-      <c r="L4" s="30"/>
-      <c r="M4" s="31"/>
-      <c r="N4" s="30"/>
-      <c r="O4" s="30" t="s">
+    <row r="4" customFormat="1" ht="245.55" spans="1:24">
+      <c r="A4" s="23"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="30"/>
+      <c r="J4" s="30"/>
+      <c r="K4" s="30"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31" t="s">
         <v>482</v>
       </c>
-      <c r="P4" s="30" t="s">
+      <c r="P4" s="31" t="s">
         <v>483</v>
       </c>
-      <c r="Q4" s="31"/>
-      <c r="R4" s="30" t="s">
+      <c r="Q4" s="32"/>
+      <c r="R4" s="31" t="s">
         <v>268</v>
       </c>
-      <c r="S4" s="30" t="s">
+      <c r="S4" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="T4" s="30" t="s">
+      <c r="T4" s="31" t="s">
         <v>484</v>
       </c>
-      <c r="U4" s="28"/>
-      <c r="V4" s="29"/>
-      <c r="W4" s="29"/>
-      <c r="X4" s="32"/>
-    </row>
-    <row r="5" s="17" customFormat="1" ht="94.5" spans="1:24">
-      <c r="A5" s="33" t="s">
+      <c r="U4" s="29"/>
+      <c r="V4" s="30"/>
+      <c r="W4" s="30"/>
+      <c r="X4" s="33"/>
+    </row>
+    <row r="5" s="17" customFormat="1" ht="100.8" spans="1:24">
+      <c r="A5" s="34" t="s">
         <v>352</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="B5" s="35" t="s">
         <v>353</v>
       </c>
-      <c r="C5" s="35" t="s">
+      <c r="C5" s="36" t="s">
         <v>354</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="E5" s="35"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="36" t="s">
+      <c r="E5" s="36"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="H5" s="36"/>
-      <c r="I5" s="36"/>
-      <c r="J5" s="36"/>
-      <c r="K5" s="36"/>
-      <c r="L5" s="37"/>
-      <c r="M5" s="37"/>
-      <c r="N5" s="37"/>
-      <c r="O5" s="38"/>
-      <c r="P5" s="39"/>
-      <c r="Q5" s="39"/>
-      <c r="R5" s="39"/>
-      <c r="S5" s="39"/>
-      <c r="T5" s="38"/>
-      <c r="U5" s="36" t="s">
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="37"/>
+      <c r="K5" s="37"/>
+      <c r="L5" s="38"/>
+      <c r="M5" s="38"/>
+      <c r="N5" s="38"/>
+      <c r="O5" s="39"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="40"/>
+      <c r="R5" s="40"/>
+      <c r="S5" s="40"/>
+      <c r="T5" s="39"/>
+      <c r="U5" s="37" t="s">
         <v>287</v>
       </c>
-      <c r="V5" s="36"/>
-      <c r="W5" s="36"/>
-      <c r="X5" s="40"/>
-    </row>
-    <row r="6" ht="94.5" spans="1:24">
-      <c r="A6" s="22"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="35" t="s">
+      <c r="V5" s="37"/>
+      <c r="W5" s="37"/>
+      <c r="X5" s="41"/>
+    </row>
+    <row r="6" ht="100.8" spans="1:24">
+      <c r="A6" s="23"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="36" t="s">
         <v>356</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="E6" s="35"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="36" t="s">
+      <c r="E6" s="36"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="37" t="s">
         <v>358</v>
       </c>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="37"/>
-      <c r="M6" s="37"/>
-      <c r="N6" s="37"/>
-      <c r="O6" s="41"/>
-      <c r="P6" s="42"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="42"/>
-      <c r="S6" s="42"/>
-      <c r="T6" s="41"/>
-      <c r="U6" s="36" t="s">
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="43"/>
+      <c r="T6" s="42"/>
+      <c r="U6" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="V6" s="36"/>
-      <c r="W6" s="36"/>
-      <c r="X6" s="40"/>
-    </row>
-    <row r="7" ht="81" spans="1:24">
-      <c r="A7" s="22"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="35" t="s">
+      <c r="V6" s="37"/>
+      <c r="W6" s="37"/>
+      <c r="X6" s="41"/>
+    </row>
+    <row r="7" ht="100.8" spans="1:24">
+      <c r="A7" s="23"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="36" t="s">
         <v>360</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="E7" s="35"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="36" t="s">
+      <c r="E7" s="36"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="37"/>
-      <c r="M7" s="37"/>
-      <c r="N7" s="37"/>
-      <c r="O7" s="41"/>
-      <c r="P7" s="42"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="42"/>
-      <c r="S7" s="42"/>
-      <c r="T7" s="41"/>
-      <c r="U7" s="36" t="s">
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="37"/>
+      <c r="K7" s="37"/>
+      <c r="L7" s="38"/>
+      <c r="M7" s="38"/>
+      <c r="N7" s="38"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7" s="43"/>
+      <c r="S7" s="43"/>
+      <c r="T7" s="42"/>
+      <c r="U7" s="37" t="s">
         <v>362</v>
       </c>
-      <c r="V7" s="36"/>
-      <c r="W7" s="36"/>
-      <c r="X7" s="40"/>
-    </row>
-    <row r="8" ht="81" spans="1:24">
-      <c r="A8" s="22"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="35" t="s">
+      <c r="V7" s="37"/>
+      <c r="W7" s="37"/>
+      <c r="X7" s="41"/>
+    </row>
+    <row r="8" ht="86.4" spans="1:24">
+      <c r="A8" s="23"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="36" t="s">
         <v>363</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="E8" s="35"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="36" t="s">
+      <c r="E8" s="36"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="37" t="s">
         <v>151</v>
       </c>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="36"/>
-      <c r="L8" s="43" t="s">
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="44" t="s">
         <v>185</v>
       </c>
-      <c r="M8" s="43"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="42"/>
-      <c r="Q8" s="42"/>
-      <c r="R8" s="42"/>
-      <c r="S8" s="42"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="36" t="s">
+      <c r="M8" s="44"/>
+      <c r="N8" s="44"/>
+      <c r="O8" s="42"/>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8" s="43"/>
+      <c r="S8" s="43"/>
+      <c r="T8" s="42"/>
+      <c r="U8" s="37" t="s">
         <v>289</v>
       </c>
-      <c r="V8" s="36"/>
-      <c r="W8" s="36"/>
-      <c r="X8" s="40"/>
-    </row>
-    <row r="9" customFormat="1" ht="121.5" spans="1:24">
-      <c r="A9" s="22"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="35" t="s">
+      <c r="V8" s="37"/>
+      <c r="W8" s="37"/>
+      <c r="X8" s="41"/>
+    </row>
+    <row r="9" customFormat="1" ht="129.6" spans="1:24">
+      <c r="A9" s="23"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="36" t="s">
         <v>365</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="E9" s="35"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="36" t="s">
+      <c r="E9" s="36"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="37" t="s">
         <v>367</v>
       </c>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="43"/>
-      <c r="N9" s="43"/>
-      <c r="O9" s="41"/>
-      <c r="P9" s="42"/>
-      <c r="Q9" s="42"/>
-      <c r="R9" s="42"/>
-      <c r="S9" s="42"/>
-      <c r="T9" s="41"/>
-      <c r="U9" s="36" t="s">
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+      <c r="K9" s="37"/>
+      <c r="L9" s="44"/>
+      <c r="M9" s="44"/>
+      <c r="N9" s="44"/>
+      <c r="O9" s="42"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9" s="43"/>
+      <c r="S9" s="43"/>
+      <c r="T9" s="42"/>
+      <c r="U9" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="V9" s="36"/>
-      <c r="W9" s="36"/>
-      <c r="X9" s="44" t="s">
+      <c r="V9" s="37"/>
+      <c r="W9" s="37"/>
+      <c r="X9" s="45" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="10" customFormat="1" ht="81" spans="1:24">
-      <c r="A10" s="22"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="35" t="s">
+    <row r="10" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A10" s="23"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="36" t="s">
         <v>368</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="E10" s="35"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="36" t="s">
+      <c r="E10" s="36"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="37" t="s">
         <v>370</v>
       </c>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="43" t="s">
+      <c r="H10" s="37"/>
+      <c r="I10" s="37"/>
+      <c r="J10" s="37"/>
+      <c r="K10" s="37"/>
+      <c r="L10" s="44" t="s">
         <v>186</v>
       </c>
-      <c r="M10" s="43"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="41"/>
-      <c r="P10" s="42"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="42"/>
-      <c r="S10" s="42"/>
-      <c r="T10" s="41"/>
-      <c r="U10" s="36" t="s">
+      <c r="M10" s="44"/>
+      <c r="N10" s="44"/>
+      <c r="O10" s="42"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="43"/>
+      <c r="T10" s="42"/>
+      <c r="U10" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="V10" s="36"/>
-      <c r="W10" s="36"/>
-      <c r="X10" s="40"/>
-    </row>
-    <row r="11" s="16" customFormat="1" ht="68.25" spans="1:24">
-      <c r="A11" s="22"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="35" t="s">
+      <c r="V10" s="37"/>
+      <c r="W10" s="37"/>
+      <c r="X10" s="41"/>
+    </row>
+    <row r="11" s="18" customFormat="1" ht="72.75" spans="1:24">
+      <c r="A11" s="23"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="36" t="s">
         <v>371</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="E11" s="35"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="36" t="s">
+      <c r="E11" s="36"/>
+      <c r="F11" s="9"/>
+      <c r="G11" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="43"/>
-      <c r="M11" s="43"/>
-      <c r="N11" s="43"/>
-      <c r="O11" s="41"/>
-      <c r="P11" s="45"/>
-      <c r="Q11" s="45"/>
-      <c r="R11" s="42"/>
-      <c r="S11" s="42"/>
-      <c r="T11" s="41"/>
-      <c r="U11" s="36" t="s">
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" s="37"/>
+      <c r="K11" s="37"/>
+      <c r="L11" s="44"/>
+      <c r="M11" s="44"/>
+      <c r="N11" s="44"/>
+      <c r="O11" s="42"/>
+      <c r="P11" s="46"/>
+      <c r="Q11" s="46"/>
+      <c r="R11" s="43"/>
+      <c r="S11" s="43"/>
+      <c r="T11" s="42"/>
+      <c r="U11" s="37" t="s">
         <v>292</v>
       </c>
-      <c r="V11" s="36"/>
-      <c r="W11" s="36"/>
-      <c r="X11" s="40"/>
+      <c r="V11" s="37"/>
+      <c r="W11" s="37"/>
+      <c r="X11" s="41"/>
     </row>
     <row r="12" s="17" customFormat="1" ht="72" customHeight="1" spans="1:24">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="34" t="s">
         <v>373</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="35" t="s">
         <v>374</v>
       </c>
-      <c r="C12" s="35" t="s">
+      <c r="C12" s="36" t="s">
         <v>375</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="E12" s="35"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="36" t="s">
+      <c r="E12" s="36"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="43"/>
-      <c r="M12" s="43"/>
-      <c r="N12" s="43"/>
-      <c r="O12" s="41"/>
-      <c r="P12" s="38"/>
-      <c r="Q12" s="38" t="s">
+      <c r="H12" s="37"/>
+      <c r="I12" s="37"/>
+      <c r="J12" s="37"/>
+      <c r="K12" s="37"/>
+      <c r="L12" s="44"/>
+      <c r="M12" s="44"/>
+      <c r="N12" s="44"/>
+      <c r="O12" s="42"/>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="39" t="s">
         <v>485</v>
       </c>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="41"/>
-      <c r="U12" s="36" t="s">
+      <c r="R12" s="43"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="42"/>
+      <c r="U12" s="37" t="s">
         <v>293</v>
       </c>
-      <c r="V12" s="36"/>
-      <c r="W12" s="36"/>
-      <c r="X12" s="40"/>
-    </row>
-    <row r="13" customFormat="1" ht="81" spans="1:24">
-      <c r="A13" s="22"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="35" t="s">
+      <c r="V12" s="37"/>
+      <c r="W12" s="37"/>
+      <c r="X12" s="41"/>
+    </row>
+    <row r="13" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A13" s="23"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="36" t="s">
         <v>377</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="E13" s="35"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="36" t="s">
+      <c r="E13" s="36"/>
+      <c r="F13" s="9"/>
+      <c r="G13" s="37" t="s">
         <v>156</v>
       </c>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" s="46" t="s">
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" s="47" t="s">
         <v>171</v>
       </c>
-      <c r="K13" s="46" t="s">
+      <c r="K13" s="47" t="s">
         <v>174</v>
       </c>
-      <c r="L13" s="43" t="s">
+      <c r="L13" s="44" t="s">
         <v>187</v>
       </c>
-      <c r="M13" s="43"/>
-      <c r="N13" s="43"/>
-      <c r="O13" s="41"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="41"/>
-      <c r="R13" s="42"/>
-      <c r="S13" s="42"/>
-      <c r="T13" s="41"/>
-      <c r="U13" s="36" t="s">
+      <c r="M13" s="44"/>
+      <c r="N13" s="44"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="42"/>
+      <c r="R13" s="43"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="42"/>
+      <c r="U13" s="37" t="s">
         <v>294</v>
       </c>
-      <c r="V13" s="36"/>
-      <c r="W13" s="36"/>
-      <c r="X13" s="40"/>
-    </row>
-    <row r="14" customFormat="1" ht="54" spans="1:24">
-      <c r="A14" s="22"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="35" t="s">
+      <c r="V13" s="37"/>
+      <c r="W13" s="37"/>
+      <c r="X13" s="41"/>
+    </row>
+    <row r="14" customFormat="1" ht="57.6" spans="1:24">
+      <c r="A14" s="23"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="36" t="s">
         <v>380</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="E14" s="35"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="36" t="s">
+      <c r="E14" s="36"/>
+      <c r="F14" s="9"/>
+      <c r="G14" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H14" s="36"/>
-      <c r="I14" s="36"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="46" t="s">
+      <c r="H14" s="37"/>
+      <c r="I14" s="37"/>
+      <c r="J14" s="37"/>
+      <c r="K14" s="47" t="s">
         <v>175</v>
       </c>
-      <c r="L14" s="43" t="s">
+      <c r="L14" s="44" t="s">
         <v>188</v>
       </c>
-      <c r="M14" s="43"/>
-      <c r="N14" s="43"/>
-      <c r="O14" s="41"/>
-      <c r="P14" s="41"/>
-      <c r="Q14" s="41"/>
-      <c r="R14" s="42"/>
-      <c r="S14" s="42"/>
-      <c r="T14" s="41"/>
-      <c r="U14" s="36" t="s">
+      <c r="M14" s="44"/>
+      <c r="N14" s="44"/>
+      <c r="O14" s="42"/>
+      <c r="P14" s="42"/>
+      <c r="Q14" s="42"/>
+      <c r="R14" s="43"/>
+      <c r="S14" s="43"/>
+      <c r="T14" s="42"/>
+      <c r="U14" s="37" t="s">
         <v>295</v>
       </c>
-      <c r="V14" s="36"/>
-      <c r="W14" s="36"/>
-      <c r="X14" s="40"/>
+      <c r="V14" s="37"/>
+      <c r="W14" s="37"/>
+      <c r="X14" s="41"/>
     </row>
     <row r="15" customFormat="1" ht="82" customHeight="1" spans="1:24">
-      <c r="A15" s="22"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="35" t="s">
+      <c r="A15" s="23"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="36" t="s">
         <v>382</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="E15" s="35"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="36" t="s">
+      <c r="E15" s="36"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="37" t="s">
         <v>157</v>
       </c>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="36"/>
-      <c r="L15" s="43" t="s">
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="37"/>
+      <c r="K15" s="37"/>
+      <c r="L15" s="44" t="s">
         <v>189</v>
       </c>
-      <c r="M15" s="43"/>
-      <c r="N15" s="43"/>
-      <c r="O15" s="41"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="41"/>
-      <c r="R15" s="42"/>
-      <c r="S15" s="42"/>
-      <c r="T15" s="41"/>
-      <c r="U15" s="36" t="s">
+      <c r="M15" s="44"/>
+      <c r="N15" s="44"/>
+      <c r="O15" s="42"/>
+      <c r="P15" s="42"/>
+      <c r="Q15" s="42"/>
+      <c r="R15" s="43"/>
+      <c r="S15" s="43"/>
+      <c r="T15" s="42"/>
+      <c r="U15" s="37" t="s">
         <v>296</v>
       </c>
-      <c r="V15" s="36"/>
-      <c r="W15" s="36"/>
-      <c r="X15" s="44" t="s">
+      <c r="V15" s="37"/>
+      <c r="W15" s="37"/>
+      <c r="X15" s="45" t="s">
         <v>328</v>
       </c>
     </row>
-    <row r="16" customFormat="1" ht="81" spans="1:24">
-      <c r="A16" s="22"/>
-      <c r="B16" s="34"/>
-      <c r="C16" s="35" t="s">
+    <row r="16" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A16" s="23"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="36" t="s">
         <v>384</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="E16" s="35"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="36" t="s">
+      <c r="E16" s="36"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="37" t="s">
         <v>158</v>
       </c>
-      <c r="H16" s="36"/>
-      <c r="I16" s="36"/>
-      <c r="J16" s="46" t="s">
+      <c r="H16" s="37"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="47" t="s">
         <v>172</v>
       </c>
-      <c r="K16" s="46" t="s">
+      <c r="K16" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="L16" s="43" t="s">
+      <c r="L16" s="44" t="s">
         <v>190</v>
       </c>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="41"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="41"/>
-      <c r="R16" s="42"/>
-      <c r="S16" s="42"/>
-      <c r="T16" s="41"/>
-      <c r="U16" s="36" t="s">
+      <c r="M16" s="44"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="42"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="42"/>
+      <c r="R16" s="43"/>
+      <c r="S16" s="43"/>
+      <c r="T16" s="42"/>
+      <c r="U16" s="37" t="s">
         <v>386</v>
       </c>
-      <c r="V16" s="36"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="44" t="s">
+      <c r="V16" s="37"/>
+      <c r="W16" s="37"/>
+      <c r="X16" s="45" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="17" s="16" customFormat="1" ht="68.25" spans="1:24">
-      <c r="A17" s="22"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="35" t="s">
+    <row r="17" s="18" customFormat="1" ht="72.75" spans="1:24">
+      <c r="A17" s="23"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="36" t="s">
         <v>387</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="E17" s="35"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="36" t="s">
+      <c r="E17" s="36"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H17" s="36"/>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="36"/>
-      <c r="L17" s="43"/>
-      <c r="M17" s="43"/>
-      <c r="N17" s="43"/>
-      <c r="O17" s="41"/>
-      <c r="P17" s="47"/>
-      <c r="Q17" s="47"/>
-      <c r="R17" s="42"/>
-      <c r="S17" s="42"/>
-      <c r="T17" s="41"/>
-      <c r="U17" s="36" t="s">
+      <c r="H17" s="37"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="44"/>
+      <c r="M17" s="44"/>
+      <c r="N17" s="44"/>
+      <c r="O17" s="42"/>
+      <c r="P17" s="48"/>
+      <c r="Q17" s="48"/>
+      <c r="R17" s="43"/>
+      <c r="S17" s="43"/>
+      <c r="T17" s="42"/>
+      <c r="U17" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="36"/>
-      <c r="X17" s="40"/>
+      <c r="V17" s="37"/>
+      <c r="W17" s="37"/>
+      <c r="X17" s="41"/>
     </row>
     <row r="18" s="17" customFormat="1" ht="82" customHeight="1" spans="1:24">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="34" t="s">
         <v>389</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="B18" s="35" t="s">
         <v>390</v>
       </c>
-      <c r="C18" s="35" t="s">
+      <c r="C18" s="36" t="s">
         <v>391</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="E18" s="35"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="36" t="s">
+      <c r="E18" s="36"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="36"/>
-      <c r="K18" s="36"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="41"/>
-      <c r="P18" s="38" t="s">
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="44"/>
+      <c r="M18" s="44"/>
+      <c r="N18" s="44"/>
+      <c r="O18" s="42"/>
+      <c r="P18" s="39" t="s">
         <v>487</v>
       </c>
-      <c r="Q18" s="38"/>
-      <c r="R18" s="42"/>
-      <c r="S18" s="42"/>
-      <c r="T18" s="41"/>
-      <c r="U18" s="36" t="s">
+      <c r="Q18" s="39"/>
+      <c r="R18" s="43"/>
+      <c r="S18" s="43"/>
+      <c r="T18" s="42"/>
+      <c r="U18" s="37" t="s">
         <v>298</v>
       </c>
-      <c r="V18" s="36"/>
-      <c r="W18" s="36"/>
-      <c r="X18" s="40"/>
-    </row>
-    <row r="19" customFormat="1" ht="81" spans="1:24">
-      <c r="A19" s="22"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="35" t="s">
+      <c r="V18" s="37"/>
+      <c r="W18" s="37"/>
+      <c r="X18" s="41"/>
+    </row>
+    <row r="19" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A19" s="23"/>
+      <c r="B19" s="35"/>
+      <c r="C19" s="36" t="s">
         <v>393</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="E19" s="35"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="36" t="s">
+      <c r="E19" s="36"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="43" t="s">
+      <c r="H19" s="37"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="37"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="44" t="s">
         <v>191</v>
       </c>
-      <c r="M19" s="43"/>
-      <c r="N19" s="43"/>
-      <c r="O19" s="41"/>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="41"/>
-      <c r="R19" s="42"/>
-      <c r="S19" s="42"/>
-      <c r="T19" s="41"/>
-      <c r="U19" s="36" t="s">
+      <c r="M19" s="44"/>
+      <c r="N19" s="44"/>
+      <c r="O19" s="42"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="42"/>
+      <c r="R19" s="43"/>
+      <c r="S19" s="43"/>
+      <c r="T19" s="42"/>
+      <c r="U19" s="37" t="s">
         <v>299</v>
       </c>
-      <c r="V19" s="36"/>
-      <c r="W19" s="36"/>
-      <c r="X19" s="40"/>
-    </row>
-    <row r="20" customFormat="1" ht="81" spans="1:24">
-      <c r="A20" s="22"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="35" t="s">
+      <c r="V19" s="37"/>
+      <c r="W19" s="37"/>
+      <c r="X19" s="41"/>
+    </row>
+    <row r="20" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A20" s="23"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="36" t="s">
         <v>395</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="E20" s="35"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="36" t="s">
+      <c r="E20" s="36"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="43" t="s">
+      <c r="H20" s="37"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="37"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="44" t="s">
         <v>192</v>
       </c>
-      <c r="M20" s="43"/>
-      <c r="N20" s="43"/>
-      <c r="O20" s="41"/>
-      <c r="P20" s="41"/>
-      <c r="Q20" s="41"/>
-      <c r="R20" s="42"/>
-      <c r="S20" s="42"/>
-      <c r="T20" s="41"/>
-      <c r="U20" s="36" t="s">
+      <c r="M20" s="44"/>
+      <c r="N20" s="44"/>
+      <c r="O20" s="42"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="42"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="43"/>
+      <c r="T20" s="42"/>
+      <c r="U20" s="37" t="s">
         <v>300</v>
       </c>
-      <c r="V20" s="36"/>
-      <c r="W20" s="36"/>
-      <c r="X20" s="40"/>
+      <c r="V20" s="37"/>
+      <c r="W20" s="37"/>
+      <c r="X20" s="41"/>
     </row>
     <row r="21" customFormat="1" ht="57" customHeight="1" spans="1:24">
-      <c r="A21" s="22"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="35" t="s">
+      <c r="A21" s="23"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="36" t="s">
         <v>397</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="E21" s="35"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="36" t="s">
+      <c r="E21" s="36"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="43" t="s">
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="M21" s="43"/>
-      <c r="N21" s="43"/>
-      <c r="O21" s="41"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="41"/>
-      <c r="R21" s="42"/>
-      <c r="S21" s="42"/>
-      <c r="T21" s="41"/>
-      <c r="U21" s="36" t="s">
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="42"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="42"/>
+      <c r="R21" s="43"/>
+      <c r="S21" s="43"/>
+      <c r="T21" s="42"/>
+      <c r="U21" s="37" t="s">
         <v>301</v>
       </c>
-      <c r="V21" s="36"/>
-      <c r="W21" s="36"/>
-      <c r="X21" s="40"/>
+      <c r="V21" s="37"/>
+      <c r="W21" s="37"/>
+      <c r="X21" s="41"/>
     </row>
     <row r="22" customFormat="1" ht="137" customHeight="1" spans="1:24">
-      <c r="A22" s="22"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="35" t="s">
+      <c r="A22" s="23"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="36" t="s">
         <v>399</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="E22" s="35"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="36" t="s">
+      <c r="E22" s="36"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="43" t="s">
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="37"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="44" t="s">
         <v>194</v>
       </c>
-      <c r="M22" s="43"/>
-      <c r="N22" s="43"/>
-      <c r="O22" s="41"/>
-      <c r="P22" s="41"/>
-      <c r="Q22" s="41"/>
-      <c r="R22" s="42"/>
-      <c r="S22" s="42"/>
-      <c r="T22" s="41"/>
-      <c r="U22" s="36" t="s">
+      <c r="M22" s="44"/>
+      <c r="N22" s="44"/>
+      <c r="O22" s="42"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="42"/>
+      <c r="R22" s="43"/>
+      <c r="S22" s="43"/>
+      <c r="T22" s="42"/>
+      <c r="U22" s="37" t="s">
         <v>302</v>
       </c>
-      <c r="V22" s="36"/>
-      <c r="W22" s="36"/>
-      <c r="X22" s="40"/>
-    </row>
-    <row r="23" s="16" customFormat="1" ht="81.75" spans="1:24">
-      <c r="A23" s="22"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="35" t="s">
+      <c r="V22" s="37"/>
+      <c r="W22" s="37"/>
+      <c r="X22" s="41"/>
+    </row>
+    <row r="23" s="18" customFormat="1" ht="87.15" spans="1:24">
+      <c r="A23" s="23"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="36" t="s">
         <v>401</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="E23" s="35"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="36" t="s">
+      <c r="E23" s="36"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="43" t="s">
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="44" t="s">
         <v>195</v>
       </c>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
-      <c r="O23" s="41"/>
-      <c r="P23" s="47"/>
-      <c r="Q23" s="47"/>
-      <c r="R23" s="42"/>
-      <c r="S23" s="42"/>
-      <c r="T23" s="41"/>
-      <c r="U23" s="36" t="s">
+      <c r="M23" s="44"/>
+      <c r="N23" s="44"/>
+      <c r="O23" s="42"/>
+      <c r="P23" s="48"/>
+      <c r="Q23" s="48"/>
+      <c r="R23" s="43"/>
+      <c r="S23" s="43"/>
+      <c r="T23" s="42"/>
+      <c r="U23" s="37" t="s">
         <v>303</v>
       </c>
-      <c r="V23" s="36"/>
-      <c r="W23" s="36"/>
-      <c r="X23" s="40"/>
-    </row>
-    <row r="24" s="17" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A24" s="33" t="s">
+      <c r="V23" s="37"/>
+      <c r="W23" s="37"/>
+      <c r="X23" s="41"/>
+    </row>
+    <row r="24" s="17" customFormat="1" ht="72" spans="1:24">
+      <c r="A24" s="34" t="s">
         <v>403</v>
       </c>
-      <c r="B24" s="34" t="s">
+      <c r="B24" s="35" t="s">
         <v>404</v>
       </c>
-      <c r="C24" s="35" t="s">
+      <c r="C24" s="36" t="s">
         <v>405</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="E24" s="35"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="36" t="s">
+      <c r="E24" s="36"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
-      <c r="K24" s="36"/>
-      <c r="L24" s="43"/>
-      <c r="M24" s="43"/>
-      <c r="N24" s="43"/>
-      <c r="O24" s="41"/>
-      <c r="P24" s="38" t="s">
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="44"/>
+      <c r="M24" s="44"/>
+      <c r="N24" s="44"/>
+      <c r="O24" s="42"/>
+      <c r="P24" s="39" t="s">
         <v>488</v>
       </c>
-      <c r="Q24" s="38"/>
-      <c r="R24" s="42"/>
-      <c r="S24" s="42"/>
-      <c r="T24" s="41"/>
-      <c r="U24" s="36" t="s">
+      <c r="Q24" s="39"/>
+      <c r="R24" s="43"/>
+      <c r="S24" s="43"/>
+      <c r="T24" s="42"/>
+      <c r="U24" s="37" t="s">
         <v>304</v>
       </c>
-      <c r="V24" s="36"/>
-      <c r="W24" s="36"/>
-      <c r="X24" s="40"/>
+      <c r="V24" s="37"/>
+      <c r="W24" s="37"/>
+      <c r="X24" s="41"/>
     </row>
     <row r="25" customFormat="1" ht="76" customHeight="1" spans="1:24">
-      <c r="A25" s="22"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="35" t="s">
+      <c r="A25" s="23"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="36" t="s">
         <v>407</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="E25" s="35"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="36" t="s">
+      <c r="E25" s="36"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="43" t="s">
+      <c r="H25" s="37"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="37"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="44" t="s">
         <v>193</v>
       </c>
-      <c r="M25" s="43"/>
-      <c r="N25" s="43"/>
-      <c r="O25" s="41"/>
-      <c r="P25" s="41"/>
-      <c r="Q25" s="41"/>
-      <c r="R25" s="42"/>
-      <c r="S25" s="42"/>
-      <c r="T25" s="41"/>
-      <c r="U25" s="36" t="s">
+      <c r="M25" s="44"/>
+      <c r="N25" s="44"/>
+      <c r="O25" s="42"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="42"/>
+      <c r="R25" s="43"/>
+      <c r="S25" s="43"/>
+      <c r="T25" s="42"/>
+      <c r="U25" s="37" t="s">
         <v>305</v>
       </c>
-      <c r="V25" s="36"/>
-      <c r="W25" s="36"/>
-      <c r="X25" s="40"/>
-    </row>
-    <row r="26" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A26" s="22"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="35" t="s">
+      <c r="V25" s="37"/>
+      <c r="W25" s="37"/>
+      <c r="X25" s="41"/>
+    </row>
+    <row r="26" customFormat="1" ht="72" spans="1:24">
+      <c r="A26" s="23"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="36" t="s">
         <v>409</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="E26" s="35"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="36" t="s">
+      <c r="E26" s="36"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="37" t="s">
         <v>160</v>
       </c>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="36"/>
-      <c r="K26" s="36"/>
-      <c r="L26" s="43" t="s">
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="37"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="44" t="s">
         <v>196</v>
       </c>
-      <c r="M26" s="43"/>
-      <c r="N26" s="43"/>
-      <c r="O26" s="41"/>
-      <c r="P26" s="41"/>
-      <c r="Q26" s="41"/>
-      <c r="R26" s="42"/>
-      <c r="S26" s="42"/>
-      <c r="T26" s="41"/>
-      <c r="U26" s="36" t="s">
+      <c r="M26" s="44"/>
+      <c r="N26" s="44"/>
+      <c r="O26" s="42"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="42"/>
+      <c r="R26" s="43"/>
+      <c r="S26" s="43"/>
+      <c r="T26" s="42"/>
+      <c r="U26" s="37" t="s">
         <v>306</v>
       </c>
-      <c r="V26" s="36"/>
-      <c r="W26" s="36"/>
-      <c r="X26" s="40"/>
-    </row>
-    <row r="27" s="16" customFormat="1" ht="81.75" spans="1:24">
-      <c r="A27" s="22"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="35" t="s">
+      <c r="V26" s="37"/>
+      <c r="W26" s="37"/>
+      <c r="X26" s="41"/>
+    </row>
+    <row r="27" s="18" customFormat="1" ht="87.15" spans="1:24">
+      <c r="A27" s="23"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="36" t="s">
         <v>411</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="E27" s="35"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="36" t="s">
+      <c r="E27" s="36"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="36"/>
-      <c r="L27" s="43" t="s">
+      <c r="H27" s="37"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="44" t="s">
         <v>197</v>
       </c>
-      <c r="M27" s="43"/>
-      <c r="N27" s="43"/>
-      <c r="O27" s="41"/>
-      <c r="P27" s="47"/>
-      <c r="Q27" s="47"/>
-      <c r="R27" s="42"/>
-      <c r="S27" s="42"/>
-      <c r="T27" s="41"/>
-      <c r="U27" s="36" t="s">
+      <c r="M27" s="44"/>
+      <c r="N27" s="44"/>
+      <c r="O27" s="42"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="48"/>
+      <c r="R27" s="43"/>
+      <c r="S27" s="43"/>
+      <c r="T27" s="42"/>
+      <c r="U27" s="37" t="s">
         <v>413</v>
       </c>
-      <c r="V27" s="36"/>
-      <c r="W27" s="36"/>
-      <c r="X27" s="40"/>
-    </row>
-    <row r="28" s="17" customFormat="1" ht="54" spans="1:24">
-      <c r="A28" s="33" t="s">
+      <c r="V27" s="37"/>
+      <c r="W27" s="37"/>
+      <c r="X27" s="41"/>
+    </row>
+    <row r="28" s="17" customFormat="1" ht="57.6" spans="1:24">
+      <c r="A28" s="34" t="s">
         <v>414</v>
       </c>
-      <c r="B28" s="34" t="s">
+      <c r="B28" s="35" t="s">
         <v>415</v>
       </c>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>416</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="E28" s="35"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="36" t="s">
+      <c r="E28" s="36"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="36"/>
-      <c r="K28" s="36"/>
-      <c r="L28" s="43" t="s">
+      <c r="H28" s="37"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="44" t="s">
         <v>198</v>
       </c>
-      <c r="M28" s="43"/>
-      <c r="N28" s="43"/>
-      <c r="O28" s="41"/>
-      <c r="P28" s="38" t="s">
+      <c r="M28" s="44"/>
+      <c r="N28" s="44"/>
+      <c r="O28" s="42"/>
+      <c r="P28" s="39" t="s">
         <v>489</v>
       </c>
-      <c r="Q28" s="38" t="s">
+      <c r="Q28" s="39" t="s">
         <v>490</v>
       </c>
-      <c r="R28" s="42"/>
-      <c r="S28" s="42"/>
-      <c r="T28" s="41"/>
-      <c r="U28" s="36" t="s">
+      <c r="R28" s="43"/>
+      <c r="S28" s="43"/>
+      <c r="T28" s="42"/>
+      <c r="U28" s="37" t="s">
         <v>308</v>
       </c>
-      <c r="V28" s="36"/>
-      <c r="W28" s="36"/>
-      <c r="X28" s="40"/>
+      <c r="V28" s="37"/>
+      <c r="W28" s="37"/>
+      <c r="X28" s="41"/>
     </row>
     <row r="29" customFormat="1" ht="193" customHeight="1" spans="1:24">
-      <c r="A29" s="22"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="35" t="s">
+      <c r="A29" s="23"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="36" t="s">
         <v>419</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="E29" s="35"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="36" t="s">
+      <c r="E29" s="36"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="46" t="s">
+      <c r="H29" s="37"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="37"/>
+      <c r="K29" s="47" t="s">
         <v>177</v>
       </c>
-      <c r="L29" s="43" t="s">
+      <c r="L29" s="44" t="s">
         <v>199</v>
       </c>
-      <c r="M29" s="43"/>
-      <c r="N29" s="43"/>
-      <c r="O29" s="41"/>
-      <c r="P29" s="41"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="42"/>
-      <c r="S29" s="42"/>
-      <c r="T29" s="41"/>
-      <c r="U29" s="36" t="s">
+      <c r="M29" s="44"/>
+      <c r="N29" s="44"/>
+      <c r="O29" s="42"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="42"/>
+      <c r="R29" s="43"/>
+      <c r="S29" s="43"/>
+      <c r="T29" s="42"/>
+      <c r="U29" s="37" t="s">
         <v>309</v>
       </c>
-      <c r="V29" s="36"/>
-      <c r="W29" s="36"/>
-      <c r="X29" s="40"/>
-    </row>
-    <row r="30" s="16" customFormat="1" ht="135.75" spans="1:24">
-      <c r="A30" s="22"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="35" t="s">
+      <c r="V29" s="37"/>
+      <c r="W29" s="37"/>
+      <c r="X29" s="41"/>
+    </row>
+    <row r="30" s="18" customFormat="1" ht="144.75" spans="1:24">
+      <c r="A30" s="23"/>
+      <c r="B30" s="35"/>
+      <c r="C30" s="36" t="s">
         <v>421</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="E30" s="35"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="36" t="s">
+      <c r="E30" s="36"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="37" t="s">
         <v>162</v>
       </c>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="43" t="s">
+      <c r="H30" s="37"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="37"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="44" t="s">
         <v>200</v>
       </c>
-      <c r="M30" s="43"/>
-      <c r="N30" s="43"/>
-      <c r="O30" s="41"/>
-      <c r="P30" s="47"/>
-      <c r="Q30" s="47"/>
-      <c r="R30" s="42"/>
-      <c r="S30" s="42"/>
-      <c r="T30" s="41"/>
-      <c r="U30" s="36" t="s">
+      <c r="M30" s="44"/>
+      <c r="N30" s="44"/>
+      <c r="O30" s="42"/>
+      <c r="P30" s="48"/>
+      <c r="Q30" s="48"/>
+      <c r="R30" s="43"/>
+      <c r="S30" s="43"/>
+      <c r="T30" s="42"/>
+      <c r="U30" s="37" t="s">
         <v>310</v>
       </c>
-      <c r="V30" s="36"/>
-      <c r="W30" s="36"/>
-      <c r="X30" s="40"/>
-    </row>
-    <row r="31" s="17" customFormat="1" ht="94.5" spans="1:24">
-      <c r="A31" s="33" t="s">
+      <c r="V30" s="37"/>
+      <c r="W30" s="37"/>
+      <c r="X30" s="41"/>
+    </row>
+    <row r="31" s="17" customFormat="1" ht="100.8" spans="1:24">
+      <c r="A31" s="34" t="s">
         <v>423</v>
       </c>
-      <c r="B31" s="34" t="s">
+      <c r="B31" s="35" t="s">
         <v>424</v>
       </c>
-      <c r="C31" s="35" t="s">
+      <c r="C31" s="36" t="s">
         <v>425</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="D31" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="E31" s="35"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="36" t="s">
+      <c r="E31" s="36"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="36"/>
-      <c r="K31" s="36"/>
-      <c r="L31" s="43" t="s">
+      <c r="H31" s="37"/>
+      <c r="I31" s="37"/>
+      <c r="J31" s="37"/>
+      <c r="K31" s="37"/>
+      <c r="L31" s="44" t="s">
         <v>201</v>
       </c>
-      <c r="M31" s="43"/>
-      <c r="N31" s="43"/>
-      <c r="O31" s="41"/>
-      <c r="P31" s="38"/>
-      <c r="Q31" s="38"/>
-      <c r="R31" s="42"/>
-      <c r="S31" s="42"/>
-      <c r="T31" s="41"/>
-      <c r="U31" s="36" t="s">
+      <c r="M31" s="44"/>
+      <c r="N31" s="44"/>
+      <c r="O31" s="42"/>
+      <c r="P31" s="39"/>
+      <c r="Q31" s="39"/>
+      <c r="R31" s="43"/>
+      <c r="S31" s="43"/>
+      <c r="T31" s="42"/>
+      <c r="U31" s="37" t="s">
         <v>311</v>
       </c>
-      <c r="V31" s="36"/>
-      <c r="W31" s="36"/>
-      <c r="X31" s="40"/>
-    </row>
-    <row r="32" customFormat="1" ht="81" spans="1:24">
-      <c r="A32" s="22"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="35" t="s">
+      <c r="V31" s="37"/>
+      <c r="W31" s="37"/>
+      <c r="X31" s="41"/>
+    </row>
+    <row r="32" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A32" s="23"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="36" t="s">
         <v>427</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="E32" s="35"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="36" t="s">
+      <c r="E32" s="36"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="43" t="s">
+      <c r="H32" s="37"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="37"/>
+      <c r="K32" s="37"/>
+      <c r="L32" s="44" t="s">
         <v>202</v>
       </c>
-      <c r="M32" s="43"/>
-      <c r="N32" s="43"/>
-      <c r="O32" s="41"/>
-      <c r="P32" s="41"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="42"/>
-      <c r="S32" s="42"/>
-      <c r="T32" s="41"/>
-      <c r="U32" s="36" t="s">
+      <c r="M32" s="44"/>
+      <c r="N32" s="44"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="43"/>
+      <c r="S32" s="43"/>
+      <c r="T32" s="42"/>
+      <c r="U32" s="37" t="s">
         <v>312</v>
       </c>
-      <c r="V32" s="36"/>
-      <c r="W32" s="36"/>
-      <c r="X32" s="40"/>
-    </row>
-    <row r="33" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A33" s="22"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="35" t="s">
+      <c r="V32" s="37"/>
+      <c r="W32" s="37"/>
+      <c r="X32" s="41"/>
+    </row>
+    <row r="33" customFormat="1" ht="72" spans="1:24">
+      <c r="A33" s="23"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="36" t="s">
         <v>429</v>
       </c>
-      <c r="D33" s="5" t="s">
+      <c r="D33" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="E33" s="35"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="36" t="s">
+      <c r="E33" s="36"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="36"/>
-      <c r="K33" s="36"/>
-      <c r="L33" s="43" t="s">
+      <c r="H33" s="37"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="37"/>
+      <c r="L33" s="44" t="s">
         <v>203</v>
       </c>
-      <c r="M33" s="43"/>
-      <c r="N33" s="43"/>
-      <c r="O33" s="41"/>
-      <c r="P33" s="41"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="42"/>
-      <c r="S33" s="42"/>
-      <c r="T33" s="41"/>
-      <c r="U33" s="36" t="s">
+      <c r="M33" s="44"/>
+      <c r="N33" s="44"/>
+      <c r="O33" s="42"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="43"/>
+      <c r="S33" s="43"/>
+      <c r="T33" s="42"/>
+      <c r="U33" s="37" t="s">
         <v>313</v>
       </c>
-      <c r="V33" s="36"/>
-      <c r="W33" s="36"/>
-      <c r="X33" s="40"/>
-    </row>
-    <row r="34" customFormat="1" ht="81" spans="1:24">
-      <c r="A34" s="22"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="35" t="s">
+      <c r="V33" s="37"/>
+      <c r="W33" s="37"/>
+      <c r="X33" s="41"/>
+    </row>
+    <row r="34" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A34" s="23"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="36" t="s">
         <v>431</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="E34" s="35"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="36" t="s">
+      <c r="E34" s="36"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="43" t="s">
+      <c r="H34" s="37"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="44" t="s">
         <v>204</v>
       </c>
-      <c r="M34" s="43"/>
-      <c r="N34" s="43"/>
-      <c r="O34" s="41"/>
-      <c r="P34" s="41"/>
-      <c r="Q34" s="41"/>
-      <c r="R34" s="42"/>
-      <c r="S34" s="42"/>
-      <c r="T34" s="41"/>
-      <c r="U34" s="36" t="s">
+      <c r="M34" s="44"/>
+      <c r="N34" s="44"/>
+      <c r="O34" s="42"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="43"/>
+      <c r="S34" s="43"/>
+      <c r="T34" s="42"/>
+      <c r="U34" s="37" t="s">
         <v>314</v>
       </c>
-      <c r="V34" s="36"/>
-      <c r="W34" s="36"/>
-      <c r="X34" s="40"/>
-    </row>
-    <row r="35" customFormat="1" ht="81" spans="1:24">
-      <c r="A35" s="22"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="35" t="s">
+      <c r="V34" s="37"/>
+      <c r="W34" s="37"/>
+      <c r="X34" s="41"/>
+    </row>
+    <row r="35" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A35" s="23"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="36" t="s">
         <v>433</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="E35" s="35"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="36" t="s">
+      <c r="E35" s="36"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="37" t="s">
         <v>163</v>
       </c>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="36"/>
-      <c r="L35" s="43"/>
-      <c r="M35" s="43"/>
-      <c r="N35" s="43"/>
-      <c r="O35" s="41"/>
-      <c r="P35" s="41"/>
-      <c r="Q35" s="41"/>
-      <c r="R35" s="42"/>
-      <c r="S35" s="42"/>
-      <c r="T35" s="41"/>
-      <c r="U35" s="48" t="s">
+      <c r="H35" s="37"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="37"/>
+      <c r="K35" s="37"/>
+      <c r="L35" s="44"/>
+      <c r="M35" s="44"/>
+      <c r="N35" s="44"/>
+      <c r="O35" s="42"/>
+      <c r="P35" s="42"/>
+      <c r="Q35" s="42"/>
+      <c r="R35" s="43"/>
+      <c r="S35" s="43"/>
+      <c r="T35" s="42"/>
+      <c r="U35" s="49" t="s">
         <v>315</v>
       </c>
-      <c r="V35" s="48"/>
-      <c r="W35" s="48"/>
-      <c r="X35" s="49"/>
-    </row>
-    <row r="36" s="16" customFormat="1" ht="95.25" spans="1:24">
-      <c r="A36" s="22"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="35" t="s">
+      <c r="V35" s="49"/>
+      <c r="W35" s="49"/>
+      <c r="X35" s="50"/>
+    </row>
+    <row r="36" s="18" customFormat="1" ht="115.95" spans="1:24">
+      <c r="A36" s="23"/>
+      <c r="B36" s="35"/>
+      <c r="C36" s="36" t="s">
         <v>435</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="E36" s="35"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="36" t="s">
+      <c r="E36" s="36"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
-      <c r="J36" s="36"/>
-      <c r="K36" s="36"/>
-      <c r="L36" s="43" t="s">
+      <c r="H36" s="37"/>
+      <c r="I36" s="37"/>
+      <c r="J36" s="37"/>
+      <c r="K36" s="37"/>
+      <c r="L36" s="44" t="s">
         <v>205</v>
       </c>
-      <c r="M36" s="43"/>
-      <c r="N36" s="43"/>
-      <c r="O36" s="41"/>
-      <c r="P36" s="47"/>
-      <c r="Q36" s="47"/>
-      <c r="R36" s="42"/>
-      <c r="S36" s="42"/>
-      <c r="T36" s="41"/>
-      <c r="U36" s="36" t="s">
+      <c r="M36" s="44"/>
+      <c r="N36" s="44"/>
+      <c r="O36" s="42"/>
+      <c r="P36" s="48"/>
+      <c r="Q36" s="48"/>
+      <c r="R36" s="43"/>
+      <c r="S36" s="43"/>
+      <c r="T36" s="42"/>
+      <c r="U36" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="V36" s="36"/>
-      <c r="W36" s="36"/>
-      <c r="X36" s="40"/>
-    </row>
-    <row r="37" s="17" customFormat="1" ht="94.5" spans="1:24">
-      <c r="A37" s="33" t="s">
+      <c r="V36" s="37"/>
+      <c r="W36" s="37"/>
+      <c r="X36" s="41"/>
+    </row>
+    <row r="37" s="17" customFormat="1" ht="100.8" spans="1:24">
+      <c r="A37" s="34" t="s">
         <v>437</v>
       </c>
-      <c r="B37" s="34" t="s">
+      <c r="B37" s="35" t="s">
         <v>438</v>
       </c>
-      <c r="C37" s="35" t="s">
+      <c r="C37" s="36" t="s">
         <v>439</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="E37" s="35"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="36" t="s">
+      <c r="E37" s="36"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H37" s="36"/>
-      <c r="I37" s="36"/>
-      <c r="J37" s="36"/>
-      <c r="K37" s="36"/>
-      <c r="L37" s="43" t="s">
+      <c r="H37" s="37"/>
+      <c r="I37" s="37"/>
+      <c r="J37" s="37"/>
+      <c r="K37" s="37"/>
+      <c r="L37" s="44" t="s">
         <v>441</v>
       </c>
-      <c r="M37" s="43"/>
-      <c r="N37" s="43"/>
-      <c r="O37" s="41"/>
-      <c r="P37" s="38"/>
-      <c r="Q37" s="38" t="s">
+      <c r="M37" s="44"/>
+      <c r="N37" s="44"/>
+      <c r="O37" s="42"/>
+      <c r="P37" s="39"/>
+      <c r="Q37" s="39" t="s">
         <v>263</v>
       </c>
-      <c r="R37" s="42"/>
-      <c r="S37" s="42"/>
-      <c r="T37" s="41"/>
-      <c r="U37" s="36" t="s">
+      <c r="R37" s="43"/>
+      <c r="S37" s="43"/>
+      <c r="T37" s="42"/>
+      <c r="U37" s="37" t="s">
         <v>316</v>
       </c>
-      <c r="V37" s="36"/>
-      <c r="W37" s="36"/>
-      <c r="X37" s="40"/>
-    </row>
-    <row r="38" customFormat="1" ht="108" spans="1:24">
-      <c r="A38" s="22"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="35" t="s">
+      <c r="V37" s="37"/>
+      <c r="W37" s="37"/>
+      <c r="X37" s="41"/>
+    </row>
+    <row r="38" customFormat="1" ht="144" spans="1:24">
+      <c r="A38" s="23"/>
+      <c r="B38" s="35"/>
+      <c r="C38" s="36" t="s">
         <v>442</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="E38" s="35"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="36" t="s">
+      <c r="E38" s="36"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="H38" s="36"/>
-      <c r="I38" s="36"/>
-      <c r="J38" s="36"/>
-      <c r="K38" s="46" t="s">
+      <c r="H38" s="37"/>
+      <c r="I38" s="37"/>
+      <c r="J38" s="37"/>
+      <c r="K38" s="47" t="s">
         <v>178</v>
       </c>
-      <c r="L38" s="43" t="s">
+      <c r="L38" s="44" t="s">
         <v>207</v>
       </c>
-      <c r="M38" s="43"/>
-      <c r="N38" s="43"/>
-      <c r="O38" s="41"/>
-      <c r="P38" s="41"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="42"/>
-      <c r="S38" s="42"/>
-      <c r="T38" s="41"/>
-      <c r="U38" s="36" t="s">
+      <c r="M38" s="44"/>
+      <c r="N38" s="44"/>
+      <c r="O38" s="42"/>
+      <c r="P38" s="42"/>
+      <c r="Q38" s="42"/>
+      <c r="R38" s="43"/>
+      <c r="S38" s="43"/>
+      <c r="T38" s="42"/>
+      <c r="U38" s="37" t="s">
         <v>317</v>
       </c>
-      <c r="V38" s="36"/>
-      <c r="W38" s="36"/>
-      <c r="X38" s="40"/>
-    </row>
-    <row r="39" s="16" customFormat="1" ht="109" customHeight="1" spans="1:24">
-      <c r="A39" s="22"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="35" t="s">
+      <c r="V38" s="37"/>
+      <c r="W38" s="37"/>
+      <c r="X38" s="41"/>
+    </row>
+    <row r="39" s="18" customFormat="1" ht="109" customHeight="1" spans="1:24">
+      <c r="A39" s="23"/>
+      <c r="B39" s="35"/>
+      <c r="C39" s="36" t="s">
         <v>444</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="E39" s="35"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="36" t="s">
+      <c r="E39" s="36"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="36"/>
-      <c r="K39" s="36"/>
-      <c r="L39" s="43"/>
-      <c r="M39" s="43"/>
-      <c r="N39" s="43"/>
-      <c r="O39" s="41"/>
-      <c r="P39" s="47"/>
-      <c r="Q39" s="47"/>
-      <c r="R39" s="42"/>
-      <c r="S39" s="42"/>
-      <c r="T39" s="41"/>
-      <c r="U39" s="36" t="s">
+      <c r="H39" s="37"/>
+      <c r="I39" s="37"/>
+      <c r="J39" s="37"/>
+      <c r="K39" s="37"/>
+      <c r="L39" s="44"/>
+      <c r="M39" s="44"/>
+      <c r="N39" s="44"/>
+      <c r="O39" s="42"/>
+      <c r="P39" s="48"/>
+      <c r="Q39" s="48"/>
+      <c r="R39" s="43"/>
+      <c r="S39" s="43"/>
+      <c r="T39" s="42"/>
+      <c r="U39" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="V39" s="36"/>
-      <c r="W39" s="36"/>
-      <c r="X39" s="40"/>
-    </row>
-    <row r="40" s="17" customFormat="1" ht="108" spans="1:24">
-      <c r="A40" s="33" t="s">
+      <c r="V39" s="37"/>
+      <c r="W39" s="37"/>
+      <c r="X39" s="41"/>
+    </row>
+    <row r="40" s="17" customFormat="1" ht="115.2" spans="1:24">
+      <c r="A40" s="34" t="s">
         <v>446</v>
       </c>
-      <c r="B40" s="34" t="s">
+      <c r="B40" s="35" t="s">
         <v>447</v>
       </c>
-      <c r="C40" s="35" t="s">
+      <c r="C40" s="36" t="s">
         <v>448</v>
       </c>
-      <c r="D40" s="50" t="s">
+      <c r="D40" s="51" t="s">
         <v>449</v>
       </c>
-      <c r="E40" s="35"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="36" t="s">
+      <c r="E40" s="36"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H40" s="36"/>
-      <c r="I40" s="36"/>
-      <c r="J40" s="36"/>
-      <c r="K40" s="36"/>
-      <c r="L40" s="43"/>
-      <c r="M40" s="43"/>
-      <c r="N40" s="43"/>
-      <c r="O40" s="41"/>
-      <c r="P40" s="38" t="s">
+      <c r="H40" s="37"/>
+      <c r="I40" s="37"/>
+      <c r="J40" s="37"/>
+      <c r="K40" s="37"/>
+      <c r="L40" s="44"/>
+      <c r="M40" s="44"/>
+      <c r="N40" s="44"/>
+      <c r="O40" s="42"/>
+      <c r="P40" s="39" t="s">
         <v>491</v>
       </c>
-      <c r="Q40" s="38" t="s">
+      <c r="Q40" s="39" t="s">
         <v>264</v>
       </c>
-      <c r="R40" s="42"/>
-      <c r="S40" s="42"/>
-      <c r="T40" s="41"/>
-      <c r="U40" s="36" t="s">
+      <c r="R40" s="43"/>
+      <c r="S40" s="43"/>
+      <c r="T40" s="42"/>
+      <c r="U40" s="37" t="s">
         <v>318</v>
       </c>
-      <c r="V40" s="36"/>
-      <c r="W40" s="36"/>
-      <c r="X40" s="40"/>
+      <c r="V40" s="37"/>
+      <c r="W40" s="37"/>
+      <c r="X40" s="41"/>
     </row>
     <row r="41" customFormat="1" ht="67" customHeight="1" spans="1:24">
-      <c r="A41" s="22"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="35" t="s">
+      <c r="A41" s="23"/>
+      <c r="B41" s="35"/>
+      <c r="C41" s="36" t="s">
         <v>450</v>
       </c>
-      <c r="D41" s="50" t="s">
+      <c r="D41" s="51" t="s">
         <v>451</v>
       </c>
-      <c r="E41" s="35"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="36" t="s">
+      <c r="E41" s="36"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="H41" s="36"/>
-      <c r="I41" s="36"/>
-      <c r="J41" s="36"/>
-      <c r="K41" s="36"/>
-      <c r="L41" s="43" t="s">
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
+      <c r="J41" s="37"/>
+      <c r="K41" s="37"/>
+      <c r="L41" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="M41" s="43"/>
-      <c r="N41" s="43"/>
-      <c r="O41" s="41"/>
-      <c r="P41" s="41"/>
-      <c r="Q41" s="41"/>
-      <c r="R41" s="42"/>
-      <c r="S41" s="42"/>
-      <c r="T41" s="41"/>
-      <c r="U41" s="36" t="s">
+      <c r="M41" s="44"/>
+      <c r="N41" s="44"/>
+      <c r="O41" s="42"/>
+      <c r="P41" s="42"/>
+      <c r="Q41" s="42"/>
+      <c r="R41" s="43"/>
+      <c r="S41" s="43"/>
+      <c r="T41" s="42"/>
+      <c r="U41" s="37" t="s">
         <v>319</v>
       </c>
-      <c r="V41" s="36"/>
-      <c r="W41" s="36"/>
-      <c r="X41" s="40"/>
-    </row>
-    <row r="42" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A42" s="22"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="35" t="s">
+      <c r="V41" s="37"/>
+      <c r="W41" s="37"/>
+      <c r="X41" s="41"/>
+    </row>
+    <row r="42" customFormat="1" ht="72" spans="1:24">
+      <c r="A42" s="23"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="36" t="s">
         <v>452</v>
       </c>
-      <c r="D42" s="50" t="s">
+      <c r="D42" s="51" t="s">
         <v>453</v>
       </c>
-      <c r="E42" s="35"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="36" t="s">
+      <c r="E42" s="36"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="43" t="s">
+      <c r="H42" s="37"/>
+      <c r="I42" s="37"/>
+      <c r="J42" s="37"/>
+      <c r="K42" s="37"/>
+      <c r="L42" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="M42" s="43"/>
-      <c r="N42" s="43"/>
-      <c r="O42" s="41"/>
-      <c r="P42" s="41"/>
-      <c r="Q42" s="41"/>
-      <c r="R42" s="42"/>
-      <c r="S42" s="42"/>
-      <c r="T42" s="41"/>
-      <c r="U42" s="36" t="s">
+      <c r="M42" s="44"/>
+      <c r="N42" s="44"/>
+      <c r="O42" s="42"/>
+      <c r="P42" s="42"/>
+      <c r="Q42" s="42"/>
+      <c r="R42" s="43"/>
+      <c r="S42" s="43"/>
+      <c r="T42" s="42"/>
+      <c r="U42" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="V42" s="36"/>
-      <c r="W42" s="36"/>
-      <c r="X42" s="40"/>
-    </row>
-    <row r="43" customFormat="1" ht="81" spans="1:24">
-      <c r="A43" s="22"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="35" t="s">
+      <c r="V42" s="37"/>
+      <c r="W42" s="37"/>
+      <c r="X42" s="41"/>
+    </row>
+    <row r="43" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A43" s="23"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="36" t="s">
         <v>454</v>
       </c>
-      <c r="D43" s="50" t="s">
+      <c r="D43" s="51" t="s">
         <v>455</v>
       </c>
-      <c r="E43" s="35"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="36" t="s">
+      <c r="E43" s="36"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H43" s="36"/>
-      <c r="I43" s="36"/>
-      <c r="J43" s="36"/>
-      <c r="K43" s="36"/>
-      <c r="L43" s="43" t="s">
+      <c r="H43" s="37"/>
+      <c r="I43" s="37"/>
+      <c r="J43" s="37"/>
+      <c r="K43" s="37"/>
+      <c r="L43" s="44" t="s">
         <v>210</v>
       </c>
-      <c r="M43" s="43"/>
-      <c r="N43" s="43"/>
-      <c r="O43" s="41"/>
-      <c r="P43" s="41"/>
-      <c r="Q43" s="41"/>
-      <c r="R43" s="42"/>
-      <c r="S43" s="42"/>
-      <c r="T43" s="41"/>
-      <c r="U43" s="48" t="s">
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="42"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="42"/>
+      <c r="R43" s="43"/>
+      <c r="S43" s="43"/>
+      <c r="T43" s="42"/>
+      <c r="U43" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="V43" s="48"/>
-      <c r="W43" s="48"/>
-      <c r="X43" s="44" t="s">
+      <c r="V43" s="49"/>
+      <c r="W43" s="49"/>
+      <c r="X43" s="45" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="44" customFormat="1" ht="148.5" spans="1:24">
-      <c r="A44" s="22"/>
-      <c r="B44" s="34"/>
-      <c r="C44" s="35" t="s">
+    <row r="44" customFormat="1" ht="158.4" spans="1:24">
+      <c r="A44" s="23"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="36" t="s">
         <v>457</v>
       </c>
-      <c r="D44" s="50" t="s">
+      <c r="D44" s="51" t="s">
         <v>458</v>
       </c>
-      <c r="E44" s="35"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="36" t="s">
+      <c r="E44" s="36"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H44" s="36"/>
-      <c r="I44" s="36"/>
-      <c r="J44" s="36"/>
-      <c r="K44" s="36"/>
-      <c r="L44" s="43" t="s">
+      <c r="H44" s="37"/>
+      <c r="I44" s="37"/>
+      <c r="J44" s="37"/>
+      <c r="K44" s="37"/>
+      <c r="L44" s="44" t="s">
         <v>211</v>
       </c>
-      <c r="M44" s="43"/>
-      <c r="N44" s="43"/>
-      <c r="O44" s="41"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="41"/>
-      <c r="R44" s="42"/>
-      <c r="S44" s="42"/>
-      <c r="T44" s="41"/>
-      <c r="U44" s="36" t="s">
+      <c r="M44" s="44"/>
+      <c r="N44" s="44"/>
+      <c r="O44" s="42"/>
+      <c r="P44" s="42"/>
+      <c r="Q44" s="42"/>
+      <c r="R44" s="43"/>
+      <c r="S44" s="43"/>
+      <c r="T44" s="42"/>
+      <c r="U44" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="V44" s="36"/>
-      <c r="W44" s="36"/>
-      <c r="X44" s="44" t="s">
+      <c r="V44" s="37"/>
+      <c r="W44" s="37"/>
+      <c r="X44" s="45" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="45" customFormat="1" ht="54" spans="1:24">
-      <c r="A45" s="22"/>
-      <c r="B45" s="34"/>
-      <c r="C45" s="35" t="s">
+    <row r="45" customFormat="1" ht="72" spans="1:24">
+      <c r="A45" s="23"/>
+      <c r="B45" s="35"/>
+      <c r="C45" s="36" t="s">
         <v>459</v>
       </c>
-      <c r="D45" s="50" t="s">
+      <c r="D45" s="51" t="s">
         <v>460</v>
       </c>
-      <c r="E45" s="35"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="36" t="s">
+      <c r="E45" s="36"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H45" s="36"/>
-      <c r="I45" s="36"/>
-      <c r="J45" s="36"/>
-      <c r="K45" s="36"/>
-      <c r="L45" s="43"/>
-      <c r="M45" s="43"/>
-      <c r="N45" s="43"/>
-      <c r="O45" s="41"/>
-      <c r="P45" s="41"/>
-      <c r="Q45" s="41"/>
-      <c r="R45" s="42"/>
-      <c r="S45" s="42"/>
-      <c r="T45" s="41"/>
-      <c r="U45" s="36" t="s">
+      <c r="H45" s="37"/>
+      <c r="I45" s="37"/>
+      <c r="J45" s="37"/>
+      <c r="K45" s="37"/>
+      <c r="L45" s="44"/>
+      <c r="M45" s="44"/>
+      <c r="N45" s="44"/>
+      <c r="O45" s="42"/>
+      <c r="P45" s="42"/>
+      <c r="Q45" s="42"/>
+      <c r="R45" s="43"/>
+      <c r="S45" s="43"/>
+      <c r="T45" s="42"/>
+      <c r="U45" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="V45" s="36"/>
-      <c r="W45" s="36"/>
-      <c r="X45" s="40"/>
-    </row>
-    <row r="46" s="16" customFormat="1" ht="95.25" spans="1:24">
-      <c r="A46" s="22"/>
-      <c r="B46" s="34"/>
-      <c r="C46" s="35" t="s">
+      <c r="V45" s="37"/>
+      <c r="W45" s="37"/>
+      <c r="X45" s="41"/>
+    </row>
+    <row r="46" s="18" customFormat="1" ht="101.55" spans="1:24">
+      <c r="A46" s="23"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="36" t="s">
         <v>461</v>
       </c>
-      <c r="D46" s="50" t="s">
+      <c r="D46" s="51" t="s">
         <v>462</v>
       </c>
-      <c r="E46" s="35"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="36" t="s">
+      <c r="E46" s="36"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="37" t="s">
         <v>164</v>
       </c>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="43" t="s">
+      <c r="H46" s="37"/>
+      <c r="I46" s="37"/>
+      <c r="J46" s="37"/>
+      <c r="K46" s="37"/>
+      <c r="L46" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="M46" s="43"/>
-      <c r="N46" s="43"/>
-      <c r="O46" s="41"/>
-      <c r="P46" s="47"/>
-      <c r="Q46" s="47"/>
-      <c r="R46" s="42"/>
-      <c r="S46" s="42"/>
-      <c r="T46" s="41"/>
-      <c r="U46" s="36" t="s">
+      <c r="M46" s="44"/>
+      <c r="N46" s="44"/>
+      <c r="O46" s="42"/>
+      <c r="P46" s="48"/>
+      <c r="Q46" s="48"/>
+      <c r="R46" s="43"/>
+      <c r="S46" s="43"/>
+      <c r="T46" s="42"/>
+      <c r="U46" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="V46" s="36"/>
-      <c r="W46" s="36"/>
-      <c r="X46" s="40"/>
-    </row>
-    <row r="47" s="17" customFormat="1" ht="121.5" spans="1:24">
-      <c r="A47" s="33" t="s">
+      <c r="V46" s="37"/>
+      <c r="W46" s="37"/>
+      <c r="X46" s="41"/>
+    </row>
+    <row r="47" s="17" customFormat="1" ht="129.6" spans="1:24">
+      <c r="A47" s="34" t="s">
         <v>463</v>
       </c>
-      <c r="B47" s="34" t="s">
+      <c r="B47" s="35" t="s">
         <v>464</v>
       </c>
-      <c r="C47" s="35" t="s">
+      <c r="C47" s="36" t="s">
         <v>465</v>
       </c>
-      <c r="D47" s="50" t="s">
+      <c r="D47" s="51" t="s">
         <v>466</v>
       </c>
-      <c r="E47" s="35"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="36" t="s">
+      <c r="E47" s="36"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="37" t="s">
         <v>166</v>
       </c>
-      <c r="H47" s="36"/>
-      <c r="I47" s="36"/>
-      <c r="J47" s="36"/>
-      <c r="K47" s="36"/>
-      <c r="L47" s="43" t="s">
+      <c r="H47" s="37"/>
+      <c r="I47" s="37"/>
+      <c r="J47" s="37"/>
+      <c r="K47" s="37"/>
+      <c r="L47" s="44" t="s">
         <v>213</v>
       </c>
-      <c r="M47" s="43"/>
-      <c r="N47" s="43"/>
-      <c r="O47" s="41"/>
-      <c r="P47" s="38" t="s">
+      <c r="M47" s="44"/>
+      <c r="N47" s="44"/>
+      <c r="O47" s="42"/>
+      <c r="P47" s="39" t="s">
         <v>492</v>
       </c>
-      <c r="Q47" s="38"/>
-      <c r="R47" s="42"/>
-      <c r="S47" s="42"/>
-      <c r="T47" s="41"/>
-      <c r="U47" s="36" t="s">
+      <c r="Q47" s="39"/>
+      <c r="R47" s="43"/>
+      <c r="S47" s="43"/>
+      <c r="T47" s="42"/>
+      <c r="U47" s="37" t="s">
         <v>320</v>
       </c>
-      <c r="V47" s="36"/>
-      <c r="W47" s="36"/>
-      <c r="X47" s="40"/>
-    </row>
-    <row r="48" customFormat="1" ht="40.5" spans="1:24">
-      <c r="A48" s="22"/>
-      <c r="B48" s="34"/>
-      <c r="C48" s="35" t="s">
+      <c r="V47" s="37"/>
+      <c r="W47" s="37"/>
+      <c r="X47" s="41"/>
+    </row>
+    <row r="48" customFormat="1" ht="43.2" spans="1:24">
+      <c r="A48" s="23"/>
+      <c r="B48" s="35"/>
+      <c r="C48" s="36" t="s">
         <v>467</v>
       </c>
-      <c r="D48" s="50" t="s">
+      <c r="D48" s="51" t="s">
         <v>468</v>
       </c>
-      <c r="E48" s="35"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="36" t="s">
+      <c r="E48" s="36"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="37" t="s">
         <v>167</v>
       </c>
-      <c r="H48" s="36"/>
-      <c r="I48" s="36"/>
-      <c r="J48" s="36"/>
-      <c r="K48" s="36"/>
-      <c r="L48" s="43" t="s">
+      <c r="H48" s="37"/>
+      <c r="I48" s="37"/>
+      <c r="J48" s="37"/>
+      <c r="K48" s="37"/>
+      <c r="L48" s="44" t="s">
         <v>214</v>
       </c>
-      <c r="M48" s="43"/>
-      <c r="N48" s="43"/>
-      <c r="O48" s="41"/>
-      <c r="P48" s="41"/>
-      <c r="Q48" s="41"/>
-      <c r="R48" s="42"/>
-      <c r="S48" s="42"/>
-      <c r="T48" s="41"/>
-      <c r="U48" s="36" t="s">
+      <c r="M48" s="44"/>
+      <c r="N48" s="44"/>
+      <c r="O48" s="42"/>
+      <c r="P48" s="42"/>
+      <c r="Q48" s="42"/>
+      <c r="R48" s="43"/>
+      <c r="S48" s="43"/>
+      <c r="T48" s="42"/>
+      <c r="U48" s="37" t="s">
         <v>321</v>
       </c>
-      <c r="V48" s="36"/>
-      <c r="W48" s="36"/>
-      <c r="X48" s="40"/>
-    </row>
-    <row r="49" s="16" customFormat="1" ht="95.25" spans="1:24">
-      <c r="A49" s="22"/>
-      <c r="B49" s="34"/>
-      <c r="C49" s="35" t="s">
+      <c r="V48" s="37"/>
+      <c r="W48" s="37"/>
+      <c r="X48" s="41"/>
+    </row>
+    <row r="49" s="18" customFormat="1" ht="101.55" spans="1:24">
+      <c r="A49" s="23"/>
+      <c r="B49" s="35"/>
+      <c r="C49" s="36" t="s">
         <v>469</v>
       </c>
-      <c r="D49" s="50" t="s">
+      <c r="D49" s="51" t="s">
         <v>470</v>
       </c>
-      <c r="E49" s="35"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="36" t="s">
+      <c r="E49" s="36"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="37" t="s">
         <v>168</v>
       </c>
-      <c r="H49" s="36"/>
-      <c r="I49" s="36"/>
-      <c r="J49" s="36"/>
-      <c r="K49" s="36"/>
-      <c r="L49" s="43" t="s">
+      <c r="H49" s="37"/>
+      <c r="I49" s="37"/>
+      <c r="J49" s="37"/>
+      <c r="K49" s="37"/>
+      <c r="L49" s="44" t="s">
         <v>215</v>
       </c>
-      <c r="M49" s="43"/>
-      <c r="N49" s="43"/>
-      <c r="O49" s="41"/>
-      <c r="P49" s="47"/>
-      <c r="Q49" s="47"/>
-      <c r="R49" s="42"/>
-      <c r="S49" s="42"/>
-      <c r="T49" s="41"/>
-      <c r="U49" s="36" t="s">
+      <c r="M49" s="44"/>
+      <c r="N49" s="44"/>
+      <c r="O49" s="42"/>
+      <c r="P49" s="48"/>
+      <c r="Q49" s="48"/>
+      <c r="R49" s="43"/>
+      <c r="S49" s="43"/>
+      <c r="T49" s="42"/>
+      <c r="U49" s="37" t="s">
         <v>322</v>
       </c>
-      <c r="V49" s="36"/>
-      <c r="W49" s="36"/>
-      <c r="X49" s="40"/>
-    </row>
-    <row r="50" s="17" customFormat="1" ht="67.5" spans="1:24">
-      <c r="A50" s="33" t="s">
+      <c r="V49" s="37"/>
+      <c r="W49" s="37"/>
+      <c r="X49" s="41"/>
+    </row>
+    <row r="50" s="17" customFormat="1" ht="72" spans="1:24">
+      <c r="A50" s="34" t="s">
         <v>471</v>
       </c>
-      <c r="B50" s="34" t="s">
+      <c r="B50" s="35" t="s">
         <v>472</v>
       </c>
-      <c r="C50" s="35" t="s">
+      <c r="C50" s="36" t="s">
         <v>473</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="E50" s="35"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="36" t="s">
+      <c r="E50" s="36"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="H50" s="36"/>
-      <c r="I50" s="36"/>
-      <c r="J50" s="36"/>
-      <c r="K50" s="36"/>
-      <c r="L50" s="43"/>
-      <c r="M50" s="43"/>
-      <c r="N50" s="43"/>
-      <c r="O50" s="41"/>
-      <c r="P50" s="38" t="s">
+      <c r="H50" s="37"/>
+      <c r="I50" s="37"/>
+      <c r="J50" s="37"/>
+      <c r="K50" s="37"/>
+      <c r="L50" s="44"/>
+      <c r="M50" s="44"/>
+      <c r="N50" s="44"/>
+      <c r="O50" s="42"/>
+      <c r="P50" s="39" t="s">
         <v>245</v>
       </c>
-      <c r="Q50" s="38" t="s">
+      <c r="Q50" s="39" t="s">
         <v>493</v>
       </c>
-      <c r="R50" s="42"/>
-      <c r="S50" s="42"/>
-      <c r="T50" s="41"/>
-      <c r="U50" s="36" t="s">
+      <c r="R50" s="43"/>
+      <c r="S50" s="43"/>
+      <c r="T50" s="42"/>
+      <c r="U50" s="37" t="s">
         <v>323</v>
       </c>
-      <c r="V50" s="36"/>
-      <c r="W50" s="36"/>
-      <c r="X50" s="40"/>
-    </row>
-    <row r="51" customFormat="1" ht="81" spans="1:24">
-      <c r="A51" s="22"/>
-      <c r="B51" s="34"/>
-      <c r="C51" s="35" t="s">
+      <c r="V50" s="37"/>
+      <c r="W50" s="37"/>
+      <c r="X50" s="41"/>
+    </row>
+    <row r="51" customFormat="1" ht="86.4" spans="1:24">
+      <c r="A51" s="23"/>
+      <c r="B51" s="35"/>
+      <c r="C51" s="36" t="s">
         <v>475</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="D51" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="E51" s="35"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="36" t="s">
+      <c r="E51" s="36"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="37" t="s">
         <v>159</v>
       </c>
-      <c r="H51" s="36"/>
-      <c r="I51" s="36"/>
-      <c r="J51" s="36"/>
-      <c r="K51" s="36"/>
-      <c r="L51" s="43"/>
-      <c r="M51" s="43"/>
-      <c r="N51" s="43"/>
-      <c r="O51" s="41"/>
-      <c r="P51" s="41"/>
-      <c r="Q51" s="41"/>
-      <c r="R51" s="42"/>
-      <c r="S51" s="42"/>
-      <c r="T51" s="41"/>
-      <c r="U51" s="36" t="s">
+      <c r="H51" s="37"/>
+      <c r="I51" s="37"/>
+      <c r="J51" s="37"/>
+      <c r="K51" s="37"/>
+      <c r="L51" s="44"/>
+      <c r="M51" s="44"/>
+      <c r="N51" s="44"/>
+      <c r="O51" s="42"/>
+      <c r="P51" s="42"/>
+      <c r="Q51" s="42"/>
+      <c r="R51" s="43"/>
+      <c r="S51" s="43"/>
+      <c r="T51" s="42"/>
+      <c r="U51" s="37" t="s">
         <v>324</v>
       </c>
-      <c r="V51" s="36"/>
-      <c r="W51" s="36"/>
-      <c r="X51" s="40"/>
-    </row>
-    <row r="52" customFormat="1" ht="94.5" spans="1:24">
-      <c r="A52" s="22"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="35" t="s">
+      <c r="V51" s="37"/>
+      <c r="W51" s="37"/>
+      <c r="X51" s="41"/>
+    </row>
+    <row r="52" customFormat="1" ht="100.8" spans="1:24">
+      <c r="A52" s="23"/>
+      <c r="B52" s="35"/>
+      <c r="C52" s="36" t="s">
         <v>477</v>
       </c>
-      <c r="D52" s="50" t="s">
+      <c r="D52" s="51" t="s">
         <v>478</v>
       </c>
-      <c r="E52" s="35"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="36" t="s">
+      <c r="E52" s="36"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="37" t="s">
         <v>155</v>
       </c>
-      <c r="H52" s="36"/>
-      <c r="I52" s="36"/>
-      <c r="J52" s="36"/>
-      <c r="K52" s="36"/>
-      <c r="L52" s="43" t="s">
+      <c r="H52" s="37"/>
+      <c r="I52" s="37"/>
+      <c r="J52" s="37"/>
+      <c r="K52" s="37"/>
+      <c r="L52" s="44" t="s">
         <v>479</v>
       </c>
-      <c r="M52" s="43"/>
-      <c r="N52" s="43"/>
-      <c r="O52" s="41"/>
-      <c r="P52" s="41"/>
-      <c r="Q52" s="41"/>
-      <c r="R52" s="42"/>
-      <c r="S52" s="42"/>
-      <c r="T52" s="41"/>
-      <c r="U52" s="36" t="s">
+      <c r="M52" s="44"/>
+      <c r="N52" s="44"/>
+      <c r="O52" s="42"/>
+      <c r="P52" s="42"/>
+      <c r="Q52" s="42"/>
+      <c r="R52" s="43"/>
+      <c r="S52" s="43"/>
+      <c r="T52" s="42"/>
+      <c r="U52" s="37" t="s">
         <v>315</v>
       </c>
-      <c r="V52" s="36"/>
-      <c r="W52" s="36"/>
-      <c r="X52" s="40"/>
-    </row>
-    <row r="53" s="16" customFormat="1" ht="68.25" spans="1:24">
-      <c r="A53" s="51"/>
-      <c r="B53" s="52"/>
-      <c r="C53" s="53" t="s">
+      <c r="V52" s="37"/>
+      <c r="W52" s="37"/>
+      <c r="X52" s="41"/>
+    </row>
+    <row r="53" s="18" customFormat="1" ht="72.75" spans="1:24">
+      <c r="A53" s="52"/>
+      <c r="B53" s="53"/>
+      <c r="C53" s="54" t="s">
         <v>480</v>
       </c>
-      <c r="D53" s="54" t="s">
+      <c r="D53" s="55" t="s">
         <v>481</v>
       </c>
-      <c r="E53" s="53"/>
-      <c r="F53" s="55"/>
-      <c r="G53" s="56" t="s">
+      <c r="E53" s="54"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="H53" s="56"/>
-      <c r="I53" s="56"/>
-      <c r="J53" s="56"/>
-      <c r="K53" s="56"/>
-      <c r="L53" s="57"/>
-      <c r="M53" s="57"/>
-      <c r="N53" s="57"/>
-      <c r="O53" s="58"/>
-      <c r="P53" s="58"/>
-      <c r="Q53" s="58"/>
-      <c r="R53" s="59"/>
-      <c r="S53" s="59"/>
-      <c r="T53" s="58"/>
-      <c r="U53" s="56" t="s">
+      <c r="H53" s="57"/>
+      <c r="I53" s="57"/>
+      <c r="J53" s="57"/>
+      <c r="K53" s="57"/>
+      <c r="L53" s="58"/>
+      <c r="M53" s="58"/>
+      <c r="N53" s="58"/>
+      <c r="O53" s="59"/>
+      <c r="P53" s="59"/>
+      <c r="Q53" s="59"/>
+      <c r="R53" s="60"/>
+      <c r="S53" s="60"/>
+      <c r="T53" s="59"/>
+      <c r="U53" s="57" t="s">
         <v>155</v>
       </c>
-      <c r="V53" s="56"/>
-      <c r="W53" s="56"/>
-      <c r="X53" s="60"/>
+      <c r="V53" s="57"/>
+      <c r="W53" s="57"/>
+      <c r="X53" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="203">
@@ -13829,712 +14047,712 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E50"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="B1:F50"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="19.125" customWidth="1"/>
-    <col min="2" max="2" width="35.875" customWidth="1"/>
-    <col min="3" max="3" width="21.25" customWidth="1"/>
-    <col min="4" max="4" width="17.125" customWidth="1"/>
-    <col min="5" max="5" width="18.25" customWidth="1"/>
+    <col min="2" max="2" width="19.1296296296296" customWidth="1"/>
+    <col min="3" max="3" width="35.8796296296296" customWidth="1"/>
+    <col min="4" max="4" width="21.25" customWidth="1"/>
+    <col min="5" max="5" width="17.1296296296296" customWidth="1"/>
+    <col min="6" max="6" width="18.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="13" customFormat="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+    <row r="1" s="15" customFormat="1" spans="2:6">
+      <c r="B1" s="15" t="s">
         <v>494</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="15" t="s">
         <v>495</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="15" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="2" s="14" customFormat="1" spans="1:5">
-      <c r="A2" s="14" t="s">
+    <row r="2" s="16" customFormat="1" spans="2:6">
+      <c r="B2" s="16" t="s">
         <v>496</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="C2" s="16" t="s">
         <v>497</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="16" t="s">
         <v>498</v>
       </c>
-      <c r="E2" s="14" t="s">
+      <c r="F2" s="16" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="3" s="14" customFormat="1" spans="1:5">
-      <c r="A3" s="14" t="s">
+    <row r="3" s="16" customFormat="1" spans="2:6">
+      <c r="B3" s="16" t="s">
         <v>500</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="C3" s="16" t="s">
         <v>501</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="D3" s="16" t="s">
         <v>502</v>
       </c>
-      <c r="E3" s="14" t="s">
+      <c r="F3" s="16" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="4" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A4" s="14" t="s">
+    <row r="4" s="16" customFormat="1" ht="43.2" spans="2:6">
+      <c r="B4" s="16" t="s">
         <v>504</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="C4" s="16" t="s">
         <v>505</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="D4" s="16" t="s">
         <v>506</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="F4" s="2" t="s">
         <v>507</v>
       </c>
     </row>
-    <row r="5" s="14" customFormat="1" spans="1:5">
-      <c r="A5" s="14" t="s">
+    <row r="5" s="16" customFormat="1" spans="2:6">
+      <c r="B5" s="16" t="s">
         <v>508</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="16" t="s">
         <v>509</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="D5" s="16" t="s">
         <v>510</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="E5" s="16" t="s">
         <v>511</v>
       </c>
-      <c r="E5" s="14" t="s">
+      <c r="F5" s="16" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="6" s="14" customFormat="1" ht="40.5" spans="1:5">
-      <c r="A6" s="14" t="s">
+    <row r="6" s="16" customFormat="1" ht="28.8" spans="2:6">
+      <c r="B6" s="16" t="s">
         <v>513</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="C6" s="16" t="s">
         <v>514</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="D6" s="16" t="s">
         <v>515</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="F6" s="2" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="7" s="14" customFormat="1" spans="1:5">
-      <c r="A7" s="14" t="s">
+    <row r="7" s="16" customFormat="1" spans="2:6">
+      <c r="B7" s="16" t="s">
         <v>517</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="C7" s="16" t="s">
         <v>518</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="D7" s="16" t="s">
         <v>519</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="E7" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="F7" s="16" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="8" s="14" customFormat="1" ht="40.5" spans="1:5">
-      <c r="A8" s="14" t="s">
+    <row r="8" s="16" customFormat="1" spans="2:6">
+      <c r="B8" s="16" t="s">
         <v>521</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="C8" s="16" t="s">
         <v>522</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="F8" s="2" t="s">
         <v>523</v>
       </c>
     </row>
-    <row r="9" s="14" customFormat="1" spans="1:5">
-      <c r="A9" s="14" t="s">
+    <row r="9" s="16" customFormat="1" spans="2:6">
+      <c r="B9" s="16" t="s">
         <v>524</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="C9" s="16" t="s">
         <v>525</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="16" t="s">
         <v>526</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="E9" s="16" t="s">
         <v>527</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="F9" s="16" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="10" s="14" customFormat="1" spans="1:5">
-      <c r="A10" s="14" t="s">
+    <row r="10" s="16" customFormat="1" spans="2:6">
+      <c r="B10" s="16" t="s">
         <v>529</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C10" s="16" t="s">
         <v>530</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="D10" s="16" t="s">
         <v>531</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="E10" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="F10" s="16" t="s">
         <v>532</v>
       </c>
     </row>
-    <row r="11" s="14" customFormat="1" spans="1:5">
-      <c r="A11" s="14" t="s">
+    <row r="11" s="16" customFormat="1" spans="2:6">
+      <c r="B11" s="16" t="s">
         <v>533</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="16" t="s">
         <v>534</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="D11" s="16" t="s">
         <v>535</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="E11" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="F11" s="16" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="12" s="14" customFormat="1" ht="135" spans="1:5">
-      <c r="A12" s="14" t="s">
+    <row r="12" s="16" customFormat="1" ht="72" spans="2:6">
+      <c r="B12" s="16" t="s">
         <v>536</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="C12" s="16" t="s">
         <v>537</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="D12" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="E12" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="F12" s="16" t="s">
         <v>539</v>
       </c>
     </row>
-    <row r="13" s="14" customFormat="1" ht="81" spans="1:5">
-      <c r="A13" s="14" t="s">
+    <row r="13" s="16" customFormat="1" ht="28.8" spans="2:6">
+      <c r="B13" s="16" t="s">
         <v>540</v>
       </c>
-      <c r="B13" s="15" t="s">
+      <c r="C13" s="2" t="s">
         <v>541</v>
       </c>
     </row>
-    <row r="14" s="14" customFormat="1" spans="1:5">
-      <c r="A14" s="14" t="s">
+    <row r="14" s="16" customFormat="1" spans="2:6">
+      <c r="B14" s="16" t="s">
         <v>542</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="C14" s="16" t="s">
         <v>543</v>
       </c>
-      <c r="E14" s="14" t="s">
+      <c r="F14" s="16" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="15" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A15" s="14" t="s">
+    <row r="15" s="16" customFormat="1" ht="28.8" spans="2:6">
+      <c r="B15" s="16" t="s">
         <v>544</v>
       </c>
-      <c r="B15" s="15" t="s">
+      <c r="C15" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="D15" s="14" t="s">
+      <c r="E15" s="16" t="s">
         <v>546</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="F15" s="2" t="s">
         <v>547</v>
       </c>
     </row>
-    <row r="16" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A16" s="14" t="s">
+    <row r="16" s="16" customFormat="1" ht="43.2" spans="2:6">
+      <c r="B16" s="16" t="s">
         <v>548</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="C16" s="16" t="s">
         <v>549</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="E16" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="E16" s="14" t="s">
+      <c r="F16" s="16" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="17" s="14" customFormat="1" ht="40.5" spans="1:5">
-      <c r="A17" s="14" t="s">
+    <row r="17" s="16" customFormat="1" ht="28.8" spans="2:6">
+      <c r="B17" s="16" t="s">
         <v>551</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="C17" s="16" t="s">
         <v>552</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="E17" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="E17" s="14" t="s">
+      <c r="F17" s="16" t="s">
         <v>554</v>
       </c>
     </row>
-    <row r="18" s="14" customFormat="1" ht="135" spans="1:5">
-      <c r="A18" s="14" t="s">
+    <row r="18" s="16" customFormat="1" ht="100.8" spans="2:6">
+      <c r="B18" s="16" t="s">
         <v>555</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="C18" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="D18" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="E18" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="F18" s="2" t="s">
         <v>558</v>
       </c>
     </row>
-    <row r="19" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A19" s="14" t="s">
+    <row r="19" s="16" customFormat="1" ht="57.6" spans="2:6">
+      <c r="B19" s="16" t="s">
         <v>559</v>
       </c>
-      <c r="B19" s="15" t="s">
+      <c r="C19" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="E19" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="E19" s="14" t="s">
+      <c r="F19" s="16" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="20" s="14" customFormat="1" spans="1:5">
-      <c r="A20" s="14" t="s">
+    <row r="20" s="16" customFormat="1" spans="2:6">
+      <c r="B20" s="16" t="s">
         <v>562</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="C20" s="16" t="s">
         <v>563</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="F20" s="16" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="21" s="14" customFormat="1" ht="40.5" spans="1:5">
-      <c r="A21" s="14" t="s">
+    <row r="21" s="16" customFormat="1" ht="28.8" spans="2:6">
+      <c r="B21" s="16" t="s">
         <v>564</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="C21" s="16" t="s">
         <v>565</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="E21" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="F21" s="16" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="22" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A22" s="14" t="s">
+    <row r="22" s="16" customFormat="1" ht="57.6" spans="2:6">
+      <c r="B22" s="16" t="s">
         <v>567</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="C22" s="16" t="s">
         <v>568</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="D22" s="16" t="s">
         <v>569</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="E22" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="F22" s="2" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="23" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A23" s="14" t="s">
+    <row r="23" s="16" customFormat="1" ht="28.8" spans="2:6">
+      <c r="B23" s="16" t="s">
         <v>571</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="C23" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="C23" s="14" t="s">
+      <c r="D23" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="D23" s="14" t="s">
+      <c r="E23" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="F23" s="16" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="24" s="14" customFormat="1" ht="54" spans="1:5">
-      <c r="A24" s="14" t="s">
+    <row r="24" s="16" customFormat="1" ht="28.8" spans="2:6">
+      <c r="B24" s="16" t="s">
         <v>573</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="C24" s="16" t="s">
         <v>574</v>
       </c>
-      <c r="D24" s="14" t="s">
+      <c r="E24" s="16" t="s">
         <v>575</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="F24" s="2" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="25" s="14" customFormat="1" ht="121.5" spans="1:5">
-      <c r="A25" s="14" t="s">
+    <row r="25" s="16" customFormat="1" ht="57.6" spans="2:6">
+      <c r="B25" s="16" t="s">
         <v>576</v>
       </c>
-      <c r="B25" s="15" t="s">
+      <c r="C25" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="D25" s="2" t="s">
         <v>578</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="E25" s="2" t="s">
         <v>579</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="F25" s="2" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="26" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A26" s="14" t="s">
+    <row r="26" s="16" customFormat="1" ht="43.2" spans="2:6">
+      <c r="B26" s="16" t="s">
         <v>581</v>
       </c>
-      <c r="B26" s="15" t="s">
+      <c r="C26" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="D26" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="E26" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="F26" s="2" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="27" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A27" s="14" t="s">
+    <row r="27" s="16" customFormat="1" ht="28.8" spans="2:6">
+      <c r="B27" s="16" t="s">
         <v>584</v>
       </c>
-      <c r="B27" s="15" t="s">
+      <c r="C27" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="D27" s="14" t="s">
+      <c r="E27" s="16" t="s">
         <v>201</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="F27" s="2" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="28" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A28" s="14" t="s">
+    <row r="28" s="16" customFormat="1" ht="28.8" spans="2:6">
+      <c r="B28" s="16" t="s">
         <v>586</v>
       </c>
-      <c r="B28" s="15" t="s">
+      <c r="C28" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="D28" s="14" t="s">
+      <c r="E28" s="16" t="s">
         <v>588</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="F28" s="2" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="29" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A29" s="14" t="s">
+    <row r="29" s="16" customFormat="1" ht="43.2" spans="2:6">
+      <c r="B29" s="16" t="s">
         <v>590</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="C29" s="16" t="s">
         <v>591</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="E29" s="16" t="s">
         <v>592</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="F29" s="2" t="s">
         <v>593</v>
       </c>
     </row>
-    <row r="30" s="14" customFormat="1" ht="54" spans="1:5">
-      <c r="A30" s="14" t="s">
+    <row r="30" s="16" customFormat="1" ht="43.2" spans="2:6">
+      <c r="B30" s="16" t="s">
         <v>594</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="C30" s="16" t="s">
         <v>595</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="E30" s="2" t="s">
         <v>596</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="F30" s="2" t="s">
         <v>597</v>
       </c>
     </row>
-    <row r="31" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A31" s="14" t="s">
+    <row r="31" s="16" customFormat="1" ht="28.8" spans="2:6">
+      <c r="B31" s="16" t="s">
         <v>598</v>
       </c>
-      <c r="B31" s="15" t="s">
+      <c r="C31" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="D31" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="E31" s="14" t="s">
+      <c r="F31" s="16" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="32" s="14" customFormat="1" spans="1:5">
-      <c r="A32" s="14" t="s">
+    <row r="32" s="16" customFormat="1" spans="2:6">
+      <c r="B32" s="16" t="s">
         <v>600</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="C32" s="16" t="s">
         <v>601</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="E32" s="16" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="33" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A33" s="14" t="s">
+    <row r="33" s="16" customFormat="1" ht="43.2" spans="2:6">
+      <c r="B33" s="16" t="s">
         <v>602</v>
       </c>
-      <c r="B33" s="15" t="s">
+      <c r="C33" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="E33" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="E33" s="14" t="s">
+      <c r="F33" s="16" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="34" s="14" customFormat="1" ht="81" spans="1:5">
-      <c r="A34" s="14" t="s">
+    <row r="34" s="16" customFormat="1" ht="43.2" spans="2:6">
+      <c r="B34" s="16" t="s">
         <v>605</v>
       </c>
-      <c r="B34" s="15" t="s">
+      <c r="C34" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="D34" s="2" t="s">
         <v>607</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="E34" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="E34" s="14" t="s">
+      <c r="F34" s="16" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="35" s="14" customFormat="1" spans="1:5">
-      <c r="A35" s="14" t="s">
+    <row r="35" s="16" customFormat="1" spans="2:6">
+      <c r="B35" s="16" t="s">
         <v>608</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="C35" s="16" t="s">
         <v>609</v>
       </c>
     </row>
-    <row r="36" s="14" customFormat="1" ht="94.5" spans="1:5">
-      <c r="A36" s="14" t="s">
+    <row r="36" s="16" customFormat="1" ht="28.8" spans="2:6">
+      <c r="B36" s="16" t="s">
         <v>610</v>
       </c>
-      <c r="B36" s="15" t="s">
+      <c r="C36" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="E36" s="14" t="s">
+      <c r="F36" s="16" t="s">
         <v>318</v>
       </c>
     </row>
-    <row r="37" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A37" s="14" t="s">
+    <row r="37" s="16" customFormat="1" ht="28.8" spans="2:6">
+      <c r="B37" s="16" t="s">
         <v>612</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="C37" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="D37" s="16" t="s">
         <v>614</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="E37" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="F37" s="2" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="38" s="14" customFormat="1" spans="1:5">
-      <c r="A38" s="14" t="s">
+    <row r="38" s="16" customFormat="1" spans="2:6">
+      <c r="B38" s="16" t="s">
         <v>615</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="C38" s="16" t="s">
         <v>616</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="E38" s="16" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="39" s="14" customFormat="1" ht="94.5" spans="1:5">
-      <c r="A39" s="14" t="s">
+    <row r="39" s="16" customFormat="1" ht="43.2" spans="2:6">
+      <c r="B39" s="16" t="s">
         <v>617</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="C39" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="E39" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="E39" s="14" t="s">
+      <c r="F39" s="16" t="s">
         <v>330</v>
       </c>
     </row>
-    <row r="40" s="14" customFormat="1" ht="148.5" spans="1:5">
-      <c r="A40" s="14" t="s">
+    <row r="40" s="16" customFormat="1" ht="86.4" spans="2:6">
+      <c r="B40" s="16" t="s">
         <v>620</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="C40" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="E40" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="F40" s="2" t="s">
         <v>623</v>
       </c>
     </row>
-    <row r="41" s="14" customFormat="1" spans="1:5">
-      <c r="A41" s="14" t="s">
+    <row r="41" s="16" customFormat="1" spans="2:6">
+      <c r="B41" s="16" t="s">
         <v>624</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="C41" s="16" t="s">
         <v>625</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="F41" s="16" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="42" s="14" customFormat="1" ht="121.5" spans="1:5">
-      <c r="A42" s="14" t="s">
+    <row r="42" s="16" customFormat="1" ht="57.6" spans="2:6">
+      <c r="B42" s="16" t="s">
         <v>626</v>
       </c>
-      <c r="B42" s="15" t="s">
+      <c r="C42" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="D42" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="D42" s="14" t="s">
+      <c r="E42" s="16" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="43" s="14" customFormat="1" ht="175.5" spans="1:5">
-      <c r="A43" s="14" t="s">
+    <row r="43" s="16" customFormat="1" ht="115.2" spans="2:6">
+      <c r="B43" s="16" t="s">
         <v>629</v>
       </c>
-      <c r="B43" s="15" t="s">
+      <c r="C43" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="D43" s="16" t="s">
         <v>631</v>
       </c>
-      <c r="D43" s="14" t="s">
+      <c r="E43" s="16" t="s">
         <v>213</v>
       </c>
-      <c r="E43" s="15" t="s">
+      <c r="F43" s="2" t="s">
         <v>632</v>
       </c>
     </row>
-    <row r="44" s="14" customFormat="1" ht="54" spans="1:5">
-      <c r="A44" s="14" t="s">
+    <row r="44" s="16" customFormat="1" ht="43.2" spans="2:6">
+      <c r="B44" s="16" t="s">
         <v>633</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="C44" s="16" t="s">
         <v>634</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="D44" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="E44" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E44" s="15" t="s">
+      <c r="F44" s="2" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="45" s="14" customFormat="1" ht="121.5" spans="1:5">
-      <c r="A45" s="14" t="s">
+    <row r="45" s="16" customFormat="1" ht="72" spans="2:6">
+      <c r="B45" s="16" t="s">
         <v>635</v>
       </c>
-      <c r="B45" s="15" t="s">
+      <c r="C45" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="D45" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="F45" s="2" t="s">
         <v>637</v>
       </c>
     </row>
-    <row r="46" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A46" s="14" t="s">
+    <row r="46" s="16" customFormat="1" ht="28.8" spans="2:6">
+      <c r="B46" s="16" t="s">
         <v>638</v>
       </c>
-      <c r="B46" s="15" t="s">
+      <c r="C46" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="D46" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="E46" s="14" t="s">
+      <c r="F46" s="16" t="s">
         <v>641</v>
       </c>
     </row>
-    <row r="47" s="14" customFormat="1" ht="67.5" spans="1:5">
-      <c r="A47" s="14" t="s">
+    <row r="47" s="16" customFormat="1" ht="28.8" spans="2:6">
+      <c r="B47" s="16" t="s">
         <v>642</v>
       </c>
-      <c r="B47" s="15" t="s">
+      <c r="C47" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="C47" s="14" t="s">
+      <c r="D47" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="E47" s="14" t="s">
+      <c r="F47" s="16" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="48" s="14" customFormat="1" ht="94.5" spans="1:5">
-      <c r="A48" s="14" t="s">
+    <row r="48" s="16" customFormat="1" ht="43.2" spans="2:6">
+      <c r="B48" s="16" t="s">
         <v>644</v>
       </c>
-      <c r="B48" s="15" t="s">
+      <c r="C48" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="D48" s="14" t="s">
+      <c r="E48" s="16" t="s">
         <v>479</v>
       </c>
-      <c r="E48" s="14" t="s">
+      <c r="F48" s="16" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="49" s="14" customFormat="1" ht="94.5" spans="1:2">
-      <c r="A49" s="14" t="s">
+    <row r="49" s="16" customFormat="1" ht="43.2" spans="2:3">
+      <c r="B49" s="16" t="s">
         <v>646</v>
       </c>
-      <c r="B49" s="15" t="s">
+      <c r="C49" s="2" t="s">
         <v>647</v>
       </c>
     </row>
-    <row r="50" s="14" customFormat="1"/>
+    <row r="50" s="16" customFormat="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -14545,7 +14763,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -14557,7 +14775,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -14568,146 +14786,146 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="31" customWidth="1"/>
     <col min="3" max="3" width="21.25" customWidth="1"/>
-    <col min="4" max="4" width="77.1333333333333" customWidth="1"/>
+    <col min="4" max="4" width="77.1296296296296" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="11" t="s">
         <v>648</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="11" t="s">
         <v>649</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="9" t="s">
         <v>650</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="9" t="s">
         <v>651</v>
       </c>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="9"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="7" t="s">
+      <c r="A2" s="11"/>
+      <c r="B2" s="11"/>
+      <c r="C2" s="9" t="s">
         <v>652</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="9" t="s">
         <v>653</v>
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="7" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="9" t="s">
         <v>654</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="9" t="s">
         <v>655</v>
       </c>
     </row>
-    <row r="4" ht="94.5" spans="1:4">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="5" t="s">
+    <row r="4" ht="100.8" spans="1:4">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="7" t="s">
         <v>656</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="7" t="s">
         <v>657</v>
       </c>
     </row>
-    <row r="5" ht="27" spans="1:4">
-      <c r="A5" s="7" t="s">
+    <row r="5" ht="28.8" spans="1:4">
+      <c r="A5" s="9" t="s">
         <v>658</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>659</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="9" t="s">
         <v>660</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="9" t="s">
         <v>661</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="9" t="s">
         <v>662</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="9" t="s">
         <v>663</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="9" t="s">
         <v>664</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="9" t="s">
         <v>665</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>666</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="9" t="s">
         <v>667</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="12" t="s">
         <v>668</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="12" t="s">
         <v>669</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="9" t="s">
         <v>670</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="9" t="s">
         <v>671</v>
       </c>
     </row>
-    <row r="9" ht="27" spans="1:4">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="7" t="s">
+    <row r="9" ht="28.8" spans="1:4">
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="9" t="s">
         <v>672</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="7" t="s">
         <v>673</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="7" t="s">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="9" t="s">
         <v>674</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="9" t="s">
         <v>675</v>
       </c>
     </row>
-    <row r="11" ht="40.5" spans="1:4">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11"/>
-      <c r="C11" s="7" t="s">
+    <row r="11" ht="43.2" spans="1:4">
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="9" t="s">
         <v>676</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="7" t="s">
         <v>677</v>
       </c>
     </row>
-    <row r="12" ht="27" spans="1:4">
-      <c r="A12" s="12"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="7" t="s">
+    <row r="12" ht="28.8" spans="1:4">
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="9" t="s">
         <v>678</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="7" t="s">
         <v>679</v>
       </c>
     </row>
@@ -14727,159 +14945,159 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="39.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="39.8796296296296" customWidth="1"/>
     <col min="3" max="3" width="63.25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>668</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="4"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="3"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="5"/>
+      <c r="B2" s="6" t="s">
         <v>680</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="7" t="s">
         <v>681</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="6"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5" t="s">
+      <c r="A3" s="8"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7" t="s">
         <v>682</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="6"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5" t="s">
+      <c r="A4" s="8"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="7" t="s">
         <v>683</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="6"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="7" t="s">
         <v>684</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="6"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="5"/>
+      <c r="A6" s="8"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="7"/>
     </row>
     <row r="7" spans="1:3">
-      <c r="A7" s="6"/>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="8"/>
+      <c r="B7" s="10" t="s">
         <v>685</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="7" t="s">
         <v>686</v>
       </c>
     </row>
     <row r="8" spans="1:3">
-      <c r="A8" s="6"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5" t="s">
+      <c r="A8" s="8"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="7" t="s">
         <v>687</v>
       </c>
     </row>
     <row r="9" spans="1:3">
-      <c r="A9" s="6"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5" t="s">
+      <c r="A9" s="8"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="7" t="s">
         <v>688</v>
       </c>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="6"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="7" t="s">
         <v>689</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="5"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="7"/>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="6"/>
-      <c r="B12" s="8" t="s">
+      <c r="A12" s="8"/>
+      <c r="B12" s="10" t="s">
         <v>690</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>691</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="6"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="5" t="s">
+      <c r="A13" s="8"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="7" t="s">
         <v>692</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="6"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5" t="s">
+      <c r="A14" s="8"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="7" t="s">
         <v>693</v>
       </c>
     </row>
     <row r="15" spans="1:3">
-      <c r="A15" s="6"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5" t="s">
+      <c r="A15" s="8"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="7" t="s">
         <v>694</v>
       </c>
     </row>
     <row r="16" spans="1:3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5" t="s">
+      <c r="A16" s="8"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7" t="s">
         <v>695</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="5"/>
+      <c r="A17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="6"/>
-      <c r="B18" s="8" t="s">
+      <c r="A18" s="8"/>
+      <c r="B18" s="10" t="s">
         <v>696</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="9" t="s">
         <v>697</v>
       </c>
     </row>
     <row r="19" spans="1:3">
-      <c r="A19" s="6"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="7" t="s">
+      <c r="A19" s="8"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="9" t="s">
         <v>698</v>
       </c>
     </row>
     <row r="20" spans="1:3">
-      <c r="A20" s="6"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="7" t="s">
+      <c r="A20" s="8"/>
+      <c r="B20" s="6"/>
+      <c r="C20" s="9" t="s">
         <v>699</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="6"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="7" t="s">
+      <c r="A21" s="8"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="9" t="s">
         <v>700</v>
       </c>
     </row>

--- a/高项突击记忆笔记20260523.xlsx
+++ b/高项突击记忆笔记20260523.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="789" firstSheet="3" activeTab="12"/>
+    <workbookView windowWidth="12155" windowHeight="13344" tabRatio="789" firstSheet="9" activeTab="13"/>
   </bookViews>
   <sheets>
     <sheet name="49过程输入输出工具-横版" sheetId="1" state="hidden" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="案例答题技巧" sheetId="5" r:id="rId11"/>
     <sheet name="论文架构" sheetId="13" r:id="rId12"/>
     <sheet name="论文模板" sheetId="6" r:id="rId13"/>
+    <sheet name="论文技巧" sheetId="15" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2435" uniqueCount="1659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2443" uniqueCount="1667">
   <si>
     <t>项目整合管理</t>
   </si>
@@ -8230,6 +8231,9 @@
     <t>每个公司不一样，按照实际情况乱写吧</t>
   </si>
   <si>
+    <t>写段落子标题</t>
+  </si>
+  <si>
     <t>背景</t>
   </si>
   <si>
@@ -8239,13 +8243,34 @@
     <t>过渡</t>
   </si>
   <si>
-    <t xml:space="preserve">  智慧营销绩效管理平台作为破解某银行营销痛点、提升运营效能的关键项目，涵盖多模块、多资源，且建设周期固定，XXXX成为????(功能作用)、保障项目按期保质交付的核心支撑。结合本人作为项目经理的履职实践，下文将重点探讨本项目中XXXX的具体实施策略、执行过程及优化措施。</t>
+    <t xml:space="preserve">  因为本项目工期比较紧，成本结构比较复杂，相关干系人众多，项目涵盖多模块、多资源，整合管理又作为保障项目按期保质交付的核心支撑，所以做好整合管理显得尤为重要。我作为项目经理除了对其他领域尽职尽责之外，还特别对整合管理从以下几个方面进行管理：</t>
   </si>
   <si>
     <t>结尾</t>
   </si>
   <si>
     <t xml:space="preserve">  经过一年的攻坚建设，目前该智慧营销绩效平台已按计划顺利完成全部建设任务，如期交付使用。项目成功落地六大核心模块，实现全行8类营销相关数据统一汇聚，数据整合效率提升60%；绩效核算周期由原人工统计的7个工作日缩短至1个工作日，核算准确率达99.8%；营销资源投放精准度提升45%，营销ROI较以往提升30%，有效破解了银行营销管理痛点，显著提升了营销精细化运营水平与资源配置效率，为银行营销决策提供了科学支撑。作为该项目的项目经理，全程主导项目规划、实施与管控的经历，让我收获颇丰。我深刻体会到，金融科技项目的成功落地，离不开项目团队的高效协作、精准的需求把控与严谨的过程管理。同时，也认识到新兴技术与金融业务深度融合的重要性，未来我将总结本次项目经验，弥补工作中的不足，提升自身项目管理能力，为金融科技领域的高质量发展贡献更多力量。</t>
+  </si>
+  <si>
+    <t>每个段落标题下写作方式：衔接+先理论（下定义解释过程+作用）+举例子+稍微总结下</t>
+  </si>
+  <si>
+    <t>论文不能理论化，写记忆中的输入输出会工具会死的很惨，可以搞个把详细描述下，也可以完全不写</t>
+  </si>
+  <si>
+    <t>论文就需要很口语化的东西，天天背诵输入输出，很难过，很适合我这样喜欢乱七八糟扯淡的</t>
+  </si>
+  <si>
+    <t>举例的时候肯定不全，所以要配合收尾，不然感觉不全，举例子，那个好写写那个，只要在工作范围内就行，不强求</t>
+  </si>
+  <si>
+    <t>标题内如果有子题目，要重点写，其他的标题单纯描述的，随便咋写</t>
+  </si>
+  <si>
+    <t>如果有表，不能生硬的画出来，要举个例子，然后自然而然的带出来表，举例要和前面项目背景相关</t>
+  </si>
+  <si>
+    <t>画表要注意细节，表头居中带颜色，表格时间累加，表格列3行基本够用</t>
   </si>
 </sst>
 </file>
@@ -9674,8 +9699,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2794000" y="17536795"/>
-          <a:ext cx="5043805" cy="2710815"/>
+          <a:off x="2514600" y="18816955"/>
+          <a:ext cx="4562475" cy="2905125"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9721,8 +9746,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="9525" y="3952875"/>
-          <a:ext cx="6991985" cy="7565390"/>
+          <a:off x="9525" y="4215765"/>
+          <a:ext cx="6306185" cy="8068310"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9760,7 +9785,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9525" y="9525"/>
-          <a:ext cx="6922770" cy="3825240"/>
+          <a:ext cx="6236970" cy="4076700"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10027,43 +10052,43 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AY27"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="14.1083333333333" customWidth="1"/>
-    <col min="2" max="2" width="22.5583333333333" customWidth="1"/>
-    <col min="3" max="3" width="29.3833333333333" customWidth="1"/>
+    <col min="1" max="1" width="14.1111111111111" customWidth="1"/>
+    <col min="2" max="2" width="22.5555555555556" customWidth="1"/>
+    <col min="3" max="3" width="29.3796296296296" customWidth="1"/>
     <col min="4" max="4" width="33.75" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="28.1333333333333" customWidth="1"/>
-    <col min="7" max="7" width="29.3833333333333" customWidth="1"/>
+    <col min="6" max="6" width="28.1296296296296" customWidth="1"/>
+    <col min="7" max="7" width="29.3796296296296" customWidth="1"/>
     <col min="8" max="8" width="33.75" customWidth="1"/>
     <col min="9" max="9" width="31.5" customWidth="1"/>
-    <col min="10" max="10" width="29.3833333333333" customWidth="1"/>
-    <col min="11" max="12" width="24.8833333333333" customWidth="1"/>
-    <col min="13" max="13" width="24.1333333333333" customWidth="1"/>
-    <col min="14" max="15" width="24.8833333333333" customWidth="1"/>
-    <col min="16" max="16" width="29.3833333333333" customWidth="1"/>
-    <col min="17" max="17" width="24.8833333333333" customWidth="1"/>
-    <col min="18" max="18" width="29.3833333333333" customWidth="1"/>
+    <col min="10" max="10" width="29.3796296296296" customWidth="1"/>
+    <col min="11" max="12" width="24.8796296296296" customWidth="1"/>
+    <col min="13" max="13" width="24.1296296296296" customWidth="1"/>
+    <col min="14" max="15" width="24.8796296296296" customWidth="1"/>
+    <col min="16" max="16" width="29.3796296296296" customWidth="1"/>
+    <col min="17" max="17" width="24.8796296296296" customWidth="1"/>
+    <col min="18" max="18" width="29.3796296296296" customWidth="1"/>
     <col min="19" max="19" width="32.5" customWidth="1"/>
-    <col min="20" max="20" width="29.3833333333333" customWidth="1"/>
-    <col min="21" max="21" width="24.8833333333333" customWidth="1"/>
-    <col min="22" max="22" width="29.3833333333333" customWidth="1"/>
-    <col min="23" max="25" width="24.8833333333333" customWidth="1"/>
-    <col min="26" max="26" width="29.3833333333333" customWidth="1"/>
-    <col min="27" max="28" width="24.8833333333333" customWidth="1"/>
-    <col min="29" max="30" width="29.3833333333333" customWidth="1"/>
-    <col min="31" max="34" width="24.8833333333333" customWidth="1"/>
-    <col min="35" max="35" width="29.3833333333333" customWidth="1"/>
-    <col min="36" max="37" width="24.8833333333333" customWidth="1"/>
-    <col min="38" max="38" width="29.3833333333333" customWidth="1"/>
-    <col min="39" max="39" width="24.8833333333333" customWidth="1"/>
+    <col min="20" max="20" width="29.3796296296296" customWidth="1"/>
+    <col min="21" max="21" width="24.8796296296296" customWidth="1"/>
+    <col min="22" max="22" width="29.3796296296296" customWidth="1"/>
+    <col min="23" max="25" width="24.8796296296296" customWidth="1"/>
+    <col min="26" max="26" width="29.3796296296296" customWidth="1"/>
+    <col min="27" max="28" width="24.8796296296296" customWidth="1"/>
+    <col min="29" max="30" width="29.3796296296296" customWidth="1"/>
+    <col min="31" max="34" width="24.8796296296296" customWidth="1"/>
+    <col min="35" max="35" width="29.3796296296296" customWidth="1"/>
+    <col min="36" max="37" width="24.8796296296296" customWidth="1"/>
+    <col min="38" max="38" width="29.3796296296296" customWidth="1"/>
+    <col min="39" max="39" width="24.8796296296296" customWidth="1"/>
     <col min="40" max="41" width="33.75" customWidth="1"/>
-    <col min="42" max="43" width="29.3833333333333" customWidth="1"/>
-    <col min="44" max="44" width="24.8833333333333" customWidth="1"/>
-    <col min="45" max="45" width="29.3833333333333" customWidth="1"/>
-    <col min="46" max="47" width="24.8833333333333" customWidth="1"/>
-    <col min="48" max="48" width="27.1333333333333" customWidth="1"/>
+    <col min="42" max="43" width="29.3796296296296" customWidth="1"/>
+    <col min="44" max="44" width="24.8796296296296" customWidth="1"/>
+    <col min="45" max="45" width="29.3796296296296" customWidth="1"/>
+    <col min="46" max="47" width="24.8796296296296" customWidth="1"/>
+    <col min="48" max="48" width="27.1296296296296" customWidth="1"/>
     <col min="49" max="51" width="31.5" customWidth="1"/>
   </cols>
   <sheetData>
@@ -10364,7 +10389,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="4" s="90" customFormat="1" ht="108" spans="1:51">
+    <row r="4" s="90" customFormat="1" ht="115.2" spans="1:51">
       <c r="A4" s="102"/>
       <c r="B4" s="102"/>
       <c r="C4" s="58" t="s">
@@ -10515,7 +10540,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="5" s="90" customFormat="1" ht="94.5" spans="1:51">
+    <row r="5" s="90" customFormat="1" ht="100.8" spans="1:51">
       <c r="A5" s="102"/>
       <c r="B5" s="102"/>
       <c r="C5" s="58"/>
@@ -10614,7 +10639,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="6" s="90" customFormat="1" ht="27" spans="1:51">
+    <row r="6" s="90" customFormat="1" ht="28.8" spans="1:51">
       <c r="A6" s="102"/>
       <c r="B6" s="102"/>
       <c r="C6" s="105" t="s">
@@ -10765,7 +10790,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="7" s="90" customFormat="1" ht="54" spans="1:51">
+    <row r="7" s="90" customFormat="1" ht="57.6" spans="1:51">
       <c r="A7" s="106" t="s">
         <v>143</v>
       </c>
@@ -10920,7 +10945,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="8" ht="67.5" spans="1:51">
+    <row r="8" ht="72" spans="1:51">
       <c r="A8" s="108"/>
       <c r="B8" s="109" t="s">
         <v>147</v>
@@ -11073,7 +11098,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="9" ht="40.5" spans="1:51">
+    <row r="9" ht="43.2" spans="1:51">
       <c r="A9" s="108"/>
       <c r="B9" s="20" t="s">
         <v>170</v>
@@ -11132,7 +11157,7 @@
       <c r="AX9" s="112"/>
       <c r="AY9" s="112"/>
     </row>
-    <row r="10" ht="81" spans="1:51">
+    <row r="10" ht="86.4" spans="1:51">
       <c r="A10" s="113"/>
       <c r="B10" s="20" t="s">
         <v>173</v>
@@ -11311,7 +11336,7 @@
       <c r="AX12" s="23"/>
       <c r="AY12" s="23"/>
     </row>
-    <row r="14" ht="94.5" spans="1:51">
+    <row r="14" ht="115.2" spans="1:51">
       <c r="A14" s="117" t="s">
         <v>183</v>
       </c>
@@ -11489,7 +11514,7 @@
       <c r="AX15" s="116"/>
       <c r="AY15" s="116"/>
     </row>
-    <row r="16" ht="67.5" spans="1:51">
+    <row r="16" ht="72" spans="1:51">
       <c r="A16" s="122"/>
       <c r="B16" s="123" t="s">
         <v>218</v>
@@ -11566,7 +11591,7 @@
       <c r="AX16" s="116"/>
       <c r="AY16" s="116"/>
     </row>
-    <row r="17" ht="81" spans="1:51">
+    <row r="17" ht="86.4" spans="1:51">
       <c r="A17" s="122"/>
       <c r="B17" s="123" t="s">
         <v>229</v>
@@ -11675,7 +11700,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="18" ht="81" spans="1:51">
+    <row r="18" ht="86.4" spans="1:51">
       <c r="A18" s="122"/>
       <c r="B18" s="123" t="s">
         <v>257</v>
@@ -11752,7 +11777,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="19" ht="40.5" spans="1:51">
+    <row r="19" ht="43.2" spans="1:51">
       <c r="A19" s="122"/>
       <c r="B19" s="123" t="s">
         <v>267</v>
@@ -11819,7 +11844,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="20" ht="54" spans="1:51">
+    <row r="20" ht="57.6" spans="1:51">
       <c r="A20" s="122"/>
       <c r="B20" s="123" t="s">
         <v>271</v>
@@ -11876,7 +11901,7 @@
       <c r="AX20" s="116"/>
       <c r="AY20" s="116"/>
     </row>
-    <row r="21" ht="81" spans="1:51">
+    <row r="21" ht="86.4" spans="1:51">
       <c r="A21" s="122"/>
       <c r="B21" s="127" t="s">
         <v>273</v>
@@ -12014,7 +12039,7 @@
       <c r="AX22" s="116"/>
       <c r="AY22" s="116"/>
     </row>
-    <row r="24" ht="108" spans="1:51">
+    <row r="24" ht="115.2" spans="1:51">
       <c r="A24" s="106" t="s">
         <v>285</v>
       </c>
@@ -12224,7 +12249,7 @@
       <c r="AX25" s="112"/>
       <c r="AY25" s="112"/>
     </row>
-    <row r="26" customFormat="1" ht="94.5" spans="1:51">
+    <row r="26" customFormat="1" ht="100.8" spans="1:51">
       <c r="A26" s="113"/>
       <c r="B26" s="20" t="s">
         <v>326</v>
@@ -12289,7 +12314,7 @@
       <c r="AX26" s="112"/>
       <c r="AY26" s="112"/>
     </row>
-    <row r="27" s="23" customFormat="1" ht="27" spans="1:51">
+    <row r="27" s="23" customFormat="1" ht="28.8" spans="1:51">
       <c r="A27" s="114" t="s">
         <v>332</v>
       </c>
@@ -12376,10 +12401,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D792"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="27.6666666666667" customWidth="1"/>
-    <col min="2" max="2" width="39.8833333333333" customWidth="1"/>
+    <col min="2" max="2" width="39.8796296296296" customWidth="1"/>
     <col min="3" max="3" width="63.25" customWidth="1"/>
   </cols>
   <sheetData>
@@ -12552,7 +12577,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="28" ht="27" spans="1:3">
+    <row r="28" ht="28.8" spans="1:3">
       <c r="B28" s="15" t="s">
         <v>915</v>
       </c>
@@ -12560,7 +12585,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="29" ht="27" spans="1:3">
+    <row r="29" ht="28.8" spans="1:3">
       <c r="B29" s="15"/>
       <c r="C29" s="8" t="s">
         <v>917</v>
@@ -12651,7 +12676,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="47" spans="1:3">
+    <row r="47" ht="28.8" spans="1:3">
       <c r="B47" s="15"/>
       <c r="C47" s="8" t="s">
         <v>934</v>
@@ -12872,7 +12897,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="89" ht="40.5" spans="2:3">
+    <row r="89" ht="43.2" spans="2:3">
       <c r="B89" s="15" t="s">
         <v>973</v>
       </c>
@@ -12886,7 +12911,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="91" ht="27" spans="2:3">
+    <row r="91" ht="28.8" spans="2:3">
       <c r="B91" s="15"/>
       <c r="C91" s="8" t="s">
         <v>976</v>
@@ -12906,7 +12931,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="95" ht="27" spans="2:3">
+    <row r="95" ht="28.8" spans="2:3">
       <c r="B95" s="15"/>
       <c r="C95" s="8" t="s">
         <v>980</v>
@@ -12924,13 +12949,13 @@
         <v>982</v>
       </c>
     </row>
-    <row r="98" ht="27" spans="2:3">
+    <row r="98" ht="28.8" spans="2:3">
       <c r="B98" s="15"/>
       <c r="C98" s="8" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="99" ht="27" spans="2:3">
+    <row r="99" ht="43.2" spans="2:3">
       <c r="B99" s="15"/>
       <c r="C99" s="8" t="s">
         <v>984</v>
@@ -12982,19 +13007,19 @@
         <v>993</v>
       </c>
     </row>
-    <row r="109" ht="27" spans="2:3">
+    <row r="109" ht="28.8" spans="2:3">
       <c r="B109" s="15"/>
       <c r="C109" s="8" t="s">
         <v>994</v>
       </c>
     </row>
-    <row r="110" ht="27" spans="2:3">
+    <row r="110" ht="28.8" spans="2:3">
       <c r="B110" s="15"/>
       <c r="C110" s="8" t="s">
         <v>995</v>
       </c>
     </row>
-    <row r="111" ht="27" spans="2:3">
+    <row r="111" ht="28.8" spans="2:3">
       <c r="B111" s="15"/>
       <c r="C111" s="8" t="s">
         <v>996</v>
@@ -13265,7 +13290,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="163" spans="2:3">
+    <row r="163" ht="28.8" spans="2:3">
       <c r="B163" s="15"/>
       <c r="C163" s="8" t="s">
         <v>1046</v>
@@ -13380,7 +13405,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="186" ht="27" spans="1:3">
+    <row r="186" ht="28.8" spans="1:3">
       <c r="B186" s="15" t="s">
         <v>1066</v>
       </c>
@@ -13388,7 +13413,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="188" ht="27" spans="1:3">
+    <row r="188" ht="28.8" spans="1:3">
       <c r="B188" s="16" t="s">
         <v>1068</v>
       </c>
@@ -13396,7 +13421,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="189" ht="27" spans="1:3">
+    <row r="189" ht="28.8" spans="1:3">
       <c r="B189" s="16"/>
       <c r="C189" s="18" t="s">
         <v>1070</v>
@@ -13460,7 +13485,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="202" ht="27" spans="2:3">
+    <row r="202" ht="28.8" spans="2:3">
       <c r="B202" s="15" t="s">
         <v>1082</v>
       </c>
@@ -13468,13 +13493,13 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="203" ht="27" spans="2:3">
+    <row r="203" ht="28.8" spans="2:3">
       <c r="B203" s="15"/>
       <c r="C203" s="8" t="s">
         <v>1084</v>
       </c>
     </row>
-    <row r="205" ht="27" spans="2:3">
+    <row r="205" ht="28.8" spans="2:3">
       <c r="B205" s="15" t="s">
         <v>1085</v>
       </c>
@@ -13488,13 +13513,13 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="207" ht="27" spans="2:3">
+    <row r="207" ht="28.8" spans="2:3">
       <c r="B207" s="15"/>
       <c r="C207" s="8" t="s">
         <v>1088</v>
       </c>
     </row>
-    <row r="208" ht="27" spans="2:3">
+    <row r="208" ht="28.8" spans="2:3">
       <c r="B208" s="15"/>
       <c r="C208" s="8" t="s">
         <v>1089</v>
@@ -13521,7 +13546,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="214" ht="27" spans="1:3">
+    <row r="214" ht="28.8" spans="1:3">
       <c r="B214" s="15"/>
       <c r="C214" s="8" t="s">
         <v>1093</v>
@@ -13632,25 +13657,25 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="236" ht="27" spans="1:3">
+    <row r="236" ht="28.8" spans="1:3">
       <c r="B236" s="15"/>
       <c r="C236" s="8" t="s">
         <v>1113</v>
       </c>
     </row>
-    <row r="237" ht="27" spans="1:3">
+    <row r="237" ht="28.8" spans="1:3">
       <c r="B237" s="15"/>
       <c r="C237" s="8" t="s">
         <v>1114</v>
       </c>
     </row>
-    <row r="238" ht="27" spans="1:3">
+    <row r="238" ht="28.8" spans="1:3">
       <c r="B238" s="15"/>
       <c r="C238" s="8" t="s">
         <v>1115</v>
       </c>
     </row>
-    <row r="239" ht="27" spans="1:3">
+    <row r="239" ht="28.8" spans="1:3">
       <c r="B239" s="15"/>
       <c r="C239" s="8" t="s">
         <v>1116</v>
@@ -14071,7 +14096,7 @@
         <v>1194</v>
       </c>
     </row>
-    <row r="320" ht="27" spans="2:3">
+    <row r="320" ht="28.8" spans="2:3">
       <c r="B320" s="15"/>
       <c r="C320" s="8" t="s">
         <v>1195</v>
@@ -14097,7 +14122,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="325" ht="27" spans="2:4">
+    <row r="325" ht="28.8" spans="2:4">
       <c r="B325" s="15"/>
       <c r="C325" s="8" t="s">
         <v>1200</v>
@@ -14468,7 +14493,7 @@
         <v>1267</v>
       </c>
     </row>
-    <row r="397" ht="27" spans="2:3">
+    <row r="397" ht="28.8" spans="2:3">
       <c r="B397" s="15"/>
       <c r="C397" s="8" t="s">
         <v>1268</v>
@@ -15130,13 +15155,13 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="523" ht="27" spans="2:3">
+    <row r="523" ht="28.8" spans="2:3">
       <c r="B523" s="15"/>
       <c r="C523" s="8" t="s">
         <v>1387</v>
       </c>
     </row>
-    <row r="525" ht="27" spans="2:3">
+    <row r="525" ht="28.8" spans="2:3">
       <c r="B525" s="15" t="s">
         <v>1388</v>
       </c>
@@ -15150,7 +15175,7 @@
         <v>1390</v>
       </c>
     </row>
-    <row r="527" ht="27" spans="2:3">
+    <row r="527" ht="28.8" spans="2:3">
       <c r="B527" s="15"/>
       <c r="C527" s="8" t="s">
         <v>1391</v>
@@ -15267,7 +15292,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="546" ht="27" spans="1:3">
+    <row r="546" ht="28.8" spans="1:3">
       <c r="A546" s="15"/>
       <c r="B546" s="19"/>
       <c r="C546" s="8" t="s">
@@ -15442,7 +15467,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="573" ht="27" spans="1:3">
+    <row r="573" ht="28.8" spans="1:3">
       <c r="A573" s="15"/>
       <c r="B573" s="19"/>
       <c r="C573" s="8" t="s">
@@ -16295,7 +16320,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="706" ht="27" spans="2:3">
+    <row r="706" ht="28.8" spans="2:3">
       <c r="B706" s="15"/>
       <c r="C706" s="8" t="s">
         <v>1537</v>
@@ -16913,7 +16938,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -16923,14 +16948,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E24"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="38.8916666666667" customWidth="1"/>
+    <col min="1" max="1" width="38.8888888888889" customWidth="1"/>
     <col min="2" max="2" width="9.66666666666667" customWidth="1"/>
-    <col min="3" max="3" width="131.108333333333" customWidth="1"/>
-    <col min="4" max="4" width="43.4416666666667" customWidth="1"/>
-    <col min="5" max="5" width="16.4416666666667" customWidth="1"/>
+    <col min="3" max="3" width="131.111111111111" customWidth="1"/>
+    <col min="4" max="4" width="43.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="16.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -17056,6 +17081,11 @@
     <row r="24" spans="3:3">
       <c r="C24" t="s">
         <v>1652</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" t="s">
+        <v>1653</v>
       </c>
     </row>
   </sheetData>
@@ -17071,34 +17101,84 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="1"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="2" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="22.8916666666667" customWidth="1"/>
-    <col min="2" max="2" width="79.225" customWidth="1"/>
+    <col min="1" max="1" width="22.8888888888889" customWidth="1"/>
+    <col min="2" max="2" width="79.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="175.5" spans="1:2">
+    <row r="1" ht="201.6" spans="1:2">
       <c r="A1" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1654</v>
-      </c>
-    </row>
-    <row r="2" ht="54" spans="1:2">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="2" ht="57.6" spans="1:2">
       <c r="A2" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1656</v>
-      </c>
-    </row>
-    <row r="3" ht="121.5" spans="1:2">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="3" ht="144" spans="1:2">
       <c r="A3" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1658</v>
+        <v>1659</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A7"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6"/>
+  <cols>
+    <col min="1" max="1" width="115.444444444444" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" t="s">
+        <v>1666</v>
       </c>
     </row>
   </sheetData>
@@ -17111,31 +17191,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A18:X70"/>
-  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="13.1083333333333" customWidth="1"/>
+    <col min="2" max="2" width="13.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="15" customWidth="1"/>
-    <col min="6" max="6" width="12.4916666666667" customWidth="1"/>
+    <col min="6" max="6" width="12.4907407407407" customWidth="1"/>
     <col min="7" max="7" width="11.9166666666667" customWidth="1"/>
-    <col min="8" max="8" width="13.1083333333333" customWidth="1"/>
-    <col min="9" max="9" width="13.225" customWidth="1"/>
+    <col min="8" max="8" width="13.1111111111111" customWidth="1"/>
+    <col min="9" max="9" width="13.2222222222222" customWidth="1"/>
     <col min="10" max="10" width="13" customWidth="1"/>
-    <col min="11" max="11" width="9.775" customWidth="1"/>
-    <col min="12" max="12" width="4.775" customWidth="1"/>
+    <col min="11" max="11" width="9.77777777777778" customWidth="1"/>
+    <col min="12" max="12" width="4.77777777777778" customWidth="1"/>
     <col min="13" max="13" width="5.66666666666667" customWidth="1"/>
     <col min="15" max="15" width="9.66666666666667" customWidth="1"/>
     <col min="16" max="16" width="14.3333333333333" customWidth="1"/>
     <col min="17" max="17" width="9.66666666666667" customWidth="1"/>
-    <col min="19" max="19" width="11.4416666666667" customWidth="1"/>
-    <col min="20" max="20" width="13.5583333333333" customWidth="1"/>
-    <col min="21" max="21" width="12.2" customWidth="1"/>
-    <col min="23" max="23" width="12.8916666666667" customWidth="1"/>
-    <col min="24" max="24" width="10.225" customWidth="1"/>
+    <col min="19" max="19" width="11.4444444444444" customWidth="1"/>
+    <col min="20" max="20" width="13.5555555555556" customWidth="1"/>
+    <col min="21" max="21" width="12.2037037037037" customWidth="1"/>
+    <col min="23" max="23" width="12.8888888888889" customWidth="1"/>
+    <col min="24" max="24" width="10.2222222222222" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="18" ht="14.25" spans="1:24">
+    <row r="18" ht="15.15" spans="1:24">
       <c r="A18" s="2" t="s">
         <v>334</v>
       </c>
@@ -17232,7 +17312,7 @@
       <c r="W20" s="51"/>
       <c r="X20" s="53"/>
     </row>
-    <row r="21" ht="81.75" spans="1:24">
+    <row r="21" ht="87.15" spans="1:24">
       <c r="A21" s="48"/>
       <c r="B21" s="50"/>
       <c r="C21" s="50"/>
@@ -17294,7 +17374,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="22" s="41" customFormat="1" ht="94.5" spans="1:24">
+    <row r="22" s="41" customFormat="1" ht="100.8" spans="1:24">
       <c r="A22" s="56" t="s">
         <v>352</v>
       </c>
@@ -17336,7 +17416,7 @@
       <c r="W22" s="59"/>
       <c r="X22" s="63"/>
     </row>
-    <row r="23" ht="94.5" spans="1:24">
+    <row r="23" ht="100.8" spans="1:24">
       <c r="A23" s="48"/>
       <c r="B23" s="85"/>
       <c r="C23" s="58" t="s">
@@ -17374,7 +17454,7 @@
       <c r="W23" s="59"/>
       <c r="X23" s="63"/>
     </row>
-    <row r="24" ht="81" spans="1:24">
+    <row r="24" ht="100.8" spans="1:24">
       <c r="A24" s="48"/>
       <c r="B24" s="85"/>
       <c r="C24" s="58" t="s">
@@ -17408,7 +17488,7 @@
       <c r="W24" s="59"/>
       <c r="X24" s="63"/>
     </row>
-    <row r="25" ht="81" spans="1:24">
+    <row r="25" ht="86.4" spans="1:24">
       <c r="A25" s="48"/>
       <c r="B25" s="85"/>
       <c r="C25" s="58" t="s">
@@ -17444,7 +17524,7 @@
       <c r="W25" s="59"/>
       <c r="X25" s="63"/>
     </row>
-    <row r="26" customFormat="1" ht="121.5" spans="1:24">
+    <row r="26" customFormat="1" ht="129.6" spans="1:24">
       <c r="A26" s="48"/>
       <c r="B26" s="85"/>
       <c r="C26" s="58" t="s">
@@ -17482,7 +17562,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="27" customFormat="1" ht="81" spans="1:24">
+    <row r="27" customFormat="1" ht="86.4" spans="1:24">
       <c r="A27" s="48"/>
       <c r="B27" s="85"/>
       <c r="C27" s="58" t="s">
@@ -17520,7 +17600,7 @@
       <c r="W27" s="59"/>
       <c r="X27" s="63"/>
     </row>
-    <row r="28" s="42" customFormat="1" ht="68.25" spans="1:24">
+    <row r="28" s="42" customFormat="1" ht="72.75" spans="1:24">
       <c r="A28" s="48"/>
       <c r="B28" s="85"/>
       <c r="C28" s="58" t="s">
@@ -17594,7 +17674,7 @@
       <c r="W29" s="59"/>
       <c r="X29" s="63"/>
     </row>
-    <row r="30" customFormat="1" ht="81" spans="1:24">
+    <row r="30" customFormat="1" ht="86.4" spans="1:24">
       <c r="A30" s="48"/>
       <c r="B30" s="85"/>
       <c r="C30" s="58" t="s">
@@ -17644,7 +17724,7 @@
       <c r="W30" s="59"/>
       <c r="X30" s="63"/>
     </row>
-    <row r="31" customFormat="1" ht="54" spans="1:24">
+    <row r="31" customFormat="1" ht="57.6" spans="1:24">
       <c r="A31" s="48"/>
       <c r="B31" s="85"/>
       <c r="C31" s="58" t="s">
@@ -17726,7 +17806,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="33" customFormat="1" ht="81" spans="1:24">
+    <row r="33" customFormat="1" ht="86.4" spans="1:24">
       <c r="A33" s="48"/>
       <c r="B33" s="85"/>
       <c r="C33" s="58" t="s">
@@ -17768,7 +17848,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="34" s="42" customFormat="1" ht="68.25" spans="1:24">
+    <row r="34" s="42" customFormat="